--- a/Assets/Editor/DataDic/Data.xlsx
+++ b/Assets/Editor/DataDic/Data.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="995" uniqueCount="827">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="988" uniqueCount="821">
   <si>
     <t>Key</t>
   </si>
@@ -50,9 +50,6 @@
     <t>卧室</t>
   </si>
   <si>
-    <t>948</t>
-  </si>
-  <si>
     <t>植物店</t>
   </si>
   <si>
@@ -92,9 +89,6 @@
     <t>客栈二楼</t>
   </si>
   <si>
-    <t>1756</t>
-  </si>
-  <si>
     <t>武器店</t>
   </si>
   <si>
@@ -134,9 +128,6 @@
     <t>工坊</t>
   </si>
   <si>
-    <t>900</t>
-  </si>
-  <si>
     <t>畜牧店</t>
   </si>
   <si>
@@ -197,9 +188,6 @@
     <t>4409</t>
   </si>
   <si>
-    <t>5309</t>
-  </si>
-  <si>
     <t>纺织店</t>
   </si>
   <si>
@@ -230,9 +218,6 @@
     <t>占卜屋</t>
   </si>
   <si>
-    <t>3056</t>
-  </si>
-  <si>
     <t>帐篷内部</t>
   </si>
   <si>
@@ -246,9 +231,6 @@
   </si>
   <si>
     <t>客栈一楼</t>
-  </si>
-  <si>
-    <t>2497</t>
   </si>
   <si>
     <t>码头</t>
@@ -2901,250 +2883,250 @@
     </row>
     <row r="2" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B2" s="4" t="s">
-        <v>102</v>
+        <v>96</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>103</v>
+        <v>97</v>
       </c>
     </row>
     <row r="3" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B3" s="4" t="s">
-        <v>104</v>
+        <v>98</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>105</v>
+        <v>99</v>
       </c>
     </row>
     <row r="4" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B4" s="4" t="s">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>107</v>
+        <v>101</v>
       </c>
     </row>
     <row r="5" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B5" s="4" t="s">
-        <v>108</v>
+        <v>102</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>109</v>
+        <v>103</v>
       </c>
     </row>
     <row r="6" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B6" s="4" t="s">
-        <v>110</v>
+        <v>104</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>111</v>
+        <v>105</v>
       </c>
     </row>
     <row r="7" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B7" s="4" t="s">
-        <v>112</v>
+        <v>106</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>113</v>
+        <v>107</v>
       </c>
     </row>
     <row r="8" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B8" s="4" t="s">
-        <v>114</v>
+        <v>108</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>115</v>
+        <v>109</v>
       </c>
     </row>
     <row r="9" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B9" s="4" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>116</v>
+        <v>110</v>
       </c>
     </row>
     <row r="10" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B10" s="4" t="s">
-        <v>117</v>
+        <v>111</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>118</v>
+        <v>112</v>
       </c>
     </row>
     <row r="11" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B11" s="4" t="s">
-        <v>119</v>
+        <v>113</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>120</v>
+        <v>114</v>
       </c>
     </row>
     <row r="12" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B12" s="4" t="s">
-        <v>121</v>
+        <v>115</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>122</v>
+        <v>116</v>
       </c>
     </row>
     <row r="13" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B13" s="4" t="s">
-        <v>123</v>
+        <v>117</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>124</v>
+        <v>118</v>
       </c>
     </row>
     <row r="14" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B14" s="4" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>126</v>
+        <v>120</v>
       </c>
     </row>
     <row r="15" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B15" s="4" t="s">
-        <v>127</v>
+        <v>121</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>128</v>
+        <v>122</v>
       </c>
     </row>
     <row r="16" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B16" s="4" t="s">
-        <v>129</v>
+        <v>123</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>130</v>
+        <v>124</v>
       </c>
     </row>
     <row r="17" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B17" s="4" t="s">
-        <v>131</v>
+        <v>125</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
     </row>
     <row r="18" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B18" s="4" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>134</v>
+        <v>128</v>
       </c>
     </row>
     <row r="19" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B19" s="4" t="s">
-        <v>135</v>
+        <v>129</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>136</v>
+        <v>130</v>
       </c>
     </row>
     <row r="20" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B20" s="4" t="s">
-        <v>137</v>
+        <v>131</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>138</v>
+        <v>132</v>
       </c>
     </row>
     <row r="21" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B21" s="4" t="s">
-        <v>139</v>
+        <v>133</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>140</v>
+        <v>134</v>
       </c>
     </row>
     <row r="22" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B22" s="4" t="s">
-        <v>141</v>
+        <v>135</v>
       </c>
       <c r="C22" s="4" t="s">
-        <v>142</v>
+        <v>136</v>
       </c>
     </row>
     <row r="23" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B23" s="4" t="s">
-        <v>143</v>
+        <v>137</v>
       </c>
       <c r="C23" s="4" t="s">
-        <v>144</v>
+        <v>138</v>
       </c>
     </row>
     <row r="24" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B24" s="4" t="s">
-        <v>145</v>
+        <v>139</v>
       </c>
       <c r="C24" s="4" t="s">
-        <v>146</v>
+        <v>140</v>
       </c>
     </row>
     <row r="25" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B25" s="4" t="s">
-        <v>147</v>
+        <v>141</v>
       </c>
       <c r="C25" s="4" t="s">
-        <v>148</v>
+        <v>142</v>
       </c>
     </row>
     <row r="26" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B26" s="4" t="s">
-        <v>149</v>
+        <v>143</v>
       </c>
       <c r="C26" s="4" t="s">
-        <v>150</v>
+        <v>144</v>
       </c>
     </row>
     <row r="27" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B27" s="4" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="C27" s="4" t="s">
-        <v>151</v>
+        <v>145</v>
       </c>
     </row>
     <row r="28" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B28" s="4" t="s">
-        <v>152</v>
+        <v>146</v>
       </c>
       <c r="C28" s="4" t="s">
-        <v>153</v>
+        <v>147</v>
       </c>
     </row>
     <row r="29" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B29" s="4" t="s">
-        <v>154</v>
+        <v>148</v>
       </c>
       <c r="C29" s="4" t="s">
-        <v>155</v>
+        <v>149</v>
       </c>
     </row>
     <row r="30" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B30" s="4" t="s">
-        <v>156</v>
+        <v>150</v>
       </c>
       <c r="C30" s="4" t="s">
-        <v>157</v>
+        <v>151</v>
       </c>
     </row>
     <row r="31" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B31" s="4" t="s">
-        <v>158</v>
+        <v>152</v>
       </c>
       <c r="C31" s="4" t="s">
-        <v>159</v>
+        <v>153</v>
       </c>
     </row>
     <row r="32" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B32" s="4" t="s">
-        <v>160</v>
+        <v>154</v>
       </c>
       <c r="C32" s="4" t="s">
-        <v>161</v>
+        <v>155</v>
       </c>
     </row>
   </sheetData>
@@ -3158,6 +3140,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B1:O56"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="22.28515625" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B1" s="4" t="s">
@@ -3191,27 +3176,27 @@
         <v>6</v>
       </c>
       <c r="G4" s="5" t="s">
-        <v>818</v>
+        <v>812</v>
       </c>
       <c r="I4" s="6" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="J4" s="6" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="K4" s="4" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
     </row>
     <row r="5" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B5" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="C5" s="4" t="s">
         <v>8</v>
       </c>
+      <c r="C5" s="4">
+        <v>948</v>
+      </c>
       <c r="G5" s="5" t="s">
-        <v>819</v>
+        <v>813</v>
       </c>
       <c r="I5" t="str">
         <f>VLOOKUP(I4,$B:$C,2,FALSE)</f>
@@ -3221,17 +3206,17 @@
         <f t="shared" ref="J5:K5" si="0">VLOOKUP(J4,$B:$C,2,FALSE)</f>
         <v>2355</v>
       </c>
-      <c r="K5" s="4" t="str">
+      <c r="K5" s="4">
         <f t="shared" si="0"/>
         <v>2497</v>
       </c>
     </row>
     <row r="6" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B6" s="4" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G6" s="7" t="str">
         <f>G4&amp;","&amp;G5</f>
@@ -3255,45 +3240,45 @@
     </row>
     <row r="7" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B7" s="4" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G7" s="5" t="s">
-        <v>820</v>
+        <v>814</v>
       </c>
       <c r="I7" s="6" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="J7" s="6" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="K7" s="4" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="L7" s="4" t="s">
-        <v>96</v>
+        <v>90</v>
       </c>
       <c r="M7" s="4" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="N7" s="4" t="s">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="O7" s="4" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
     </row>
     <row r="8" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B8" s="4" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G8" s="5" t="s">
-        <v>824</v>
+        <v>818</v>
       </c>
       <c r="I8" s="4" t="str">
         <f>VLOOKUP(I7,$B:$C,2,FALSE)</f>
@@ -3303,7 +3288,7 @@
         <f t="shared" ref="J8" si="2">VLOOKUP(J7,$B:$C,2,FALSE)</f>
         <v>2355</v>
       </c>
-      <c r="K8" s="4" t="str">
+      <c r="K8" s="4">
         <f t="shared" ref="K8:L8" si="3">VLOOKUP(K7,$B:$C,2,FALSE)</f>
         <v>2497</v>
       </c>
@@ -3326,10 +3311,10 @@
     </row>
     <row r="9" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B9" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G9" s="7" t="str">
         <f>G7&amp;","&amp;G8</f>
@@ -3367,32 +3352,32 @@
     </row>
     <row r="10" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B10" s="4" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G10" s="5" t="s">
-        <v>825</v>
+        <v>819</v>
       </c>
     </row>
     <row r="11" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B11" s="4" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G11" s="5" t="s">
-        <v>826</v>
+        <v>820</v>
       </c>
     </row>
     <row r="12" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B12" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="C12" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
+      </c>
+      <c r="C12" s="4">
+        <v>1756</v>
       </c>
       <c r="F12" s="4"/>
       <c r="G12" s="7" t="str">
@@ -3410,10 +3395,10 @@
     </row>
     <row r="13" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B13" s="4" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="F13" s="4"/>
       <c r="G13" s="5"/>
@@ -3428,38 +3413,38 @@
     </row>
     <row r="14" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B14" s="4" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="F14" s="4"/>
       <c r="G14" s="5" t="s">
-        <v>826</v>
+        <v>820</v>
       </c>
       <c r="I14" s="4" t="s">
-        <v>96</v>
+        <v>90</v>
       </c>
       <c r="J14" s="4" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="K14" s="4" t="s">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="L14" s="4" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
     </row>
     <row r="15" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B15" s="4" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="F15" s="4"/>
       <c r="G15" s="5" t="s">
-        <v>822</v>
+        <v>816</v>
       </c>
       <c r="H15" s="4"/>
       <c r="I15" s="4" t="str">
@@ -3482,10 +3467,10 @@
     </row>
     <row r="16" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B16" s="4" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="G16" s="7" t="str">
         <f>G14&amp;","&amp;G15</f>
@@ -3513,36 +3498,36 @@
     </row>
     <row r="17" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B17" s="4" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="G17" s="5" t="s">
-        <v>821</v>
+        <v>815</v>
       </c>
       <c r="I17" s="4" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="J17" s="4" t="s">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="K17" s="4" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="L17" s="4" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
     </row>
     <row r="18" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B18" s="4" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="G18" s="5" t="s">
-        <v>823</v>
+        <v>817</v>
       </c>
       <c r="I18" s="4" t="str">
         <f>VLOOKUP(I17,$B:$C,2,FALSE)</f>
@@ -3556,17 +3541,17 @@
         <f t="shared" si="8"/>
         <v>512</v>
       </c>
-      <c r="L18" s="4" t="str">
+      <c r="L18" s="4">
         <f t="shared" si="8"/>
         <v>2497</v>
       </c>
     </row>
     <row r="19" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B19" s="4" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="G19" s="7" t="str">
         <f>G17&amp;","&amp;G18</f>
@@ -3594,35 +3579,35 @@
     </row>
     <row r="20" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B20" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="C20" s="4" t="s">
-        <v>36</v>
+        <v>34</v>
+      </c>
+      <c r="C20" s="4">
+        <v>900</v>
       </c>
       <c r="G20" s="5"/>
     </row>
     <row r="21" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B21" s="4" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
     </row>
     <row r="22" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B22" s="4" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="C22" s="4" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
     </row>
     <row r="23" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B23" s="4" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="C23" s="4" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="G23" t="str">
         <f>G6&amp;","&amp;G9&amp;","&amp;G12&amp;","&amp;G16&amp;","&amp;G19</f>
@@ -3632,280 +3617,280 @@
     </row>
     <row r="24" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B24" s="4" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="C24" s="4" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
     </row>
     <row r="25" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B25" s="4" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="C25" s="4" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="M25" s="4"/>
     </row>
     <row r="26" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B26" s="4" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="C26" s="4" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="M26" s="4"/>
     </row>
     <row r="27" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B27" s="4" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="C27" s="4" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="M27" s="4"/>
     </row>
     <row r="28" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B28" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="C28" s="4" t="s">
-        <v>51</v>
+        <v>49</v>
+      </c>
+      <c r="C28" s="4">
+        <v>1014</v>
       </c>
       <c r="M28" s="4"/>
     </row>
     <row r="29" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B29" s="4" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="C29" s="4" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="M29" s="4"/>
     </row>
     <row r="30" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B30" s="4" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="C30" s="4" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
     </row>
     <row r="31" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B31" s="4" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="C31" s="4" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="M31" s="4" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
     </row>
     <row r="32" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B32" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="C32" s="4" t="s">
-        <v>57</v>
+        <v>54</v>
+      </c>
+      <c r="C32" s="4">
+        <v>5309</v>
       </c>
       <c r="M32" s="4" t="s">
-        <v>82</v>
+        <v>76</v>
       </c>
     </row>
     <row r="33" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B33" s="4" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="C33" s="4" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="M33" s="4" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
     </row>
     <row r="34" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B34" s="4" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="C34" s="4" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
     </row>
     <row r="35" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B35" s="4" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="C35" s="4" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
     </row>
     <row r="36" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B36" s="4" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="C36" s="4" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
     </row>
     <row r="37" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B37" s="4" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="C37" s="4" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
     </row>
     <row r="38" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B38" s="4" t="s">
-        <v>69</v>
-      </c>
-      <c r="C38" s="4" t="s">
-        <v>68</v>
+        <v>64</v>
+      </c>
+      <c r="C38" s="4">
+        <v>3056</v>
       </c>
     </row>
     <row r="39" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B39" s="4" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="C39" s="4" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
     </row>
     <row r="40" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B40" s="4" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="C40" s="4" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
     </row>
     <row r="41" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B41" s="4" t="s">
-        <v>75</v>
-      </c>
-      <c r="C41" s="4" t="s">
-        <v>74</v>
+        <v>69</v>
+      </c>
+      <c r="C41" s="4">
+        <v>2497</v>
       </c>
     </row>
     <row r="42" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B42" s="4" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="C42" s="4" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
     </row>
     <row r="43" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B43" s="4" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="C43" s="4" t="s">
-        <v>78</v>
+        <v>72</v>
       </c>
     </row>
     <row r="44" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B44" s="4" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="C44" s="4" t="s">
-        <v>80</v>
+        <v>74</v>
       </c>
     </row>
     <row r="45" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B45" s="4" t="s">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="C45" s="4" t="s">
-        <v>81</v>
+        <v>75</v>
       </c>
     </row>
     <row r="46" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B46" s="4" t="s">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="C46" s="4" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
     </row>
     <row r="47" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B47" s="4" t="s">
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="C47" s="4" t="s">
-        <v>85</v>
+        <v>79</v>
       </c>
     </row>
     <row r="48" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B48" s="4" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="C48" s="4" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
     </row>
     <row r="49" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B49" s="4" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="C49" s="4" t="s">
-        <v>89</v>
+        <v>83</v>
       </c>
     </row>
     <row r="50" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B50" s="4" t="s">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c r="C50" s="4" t="s">
-        <v>91</v>
+        <v>85</v>
       </c>
     </row>
     <row r="51" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B51" s="4" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="C51" s="4" t="s">
-        <v>93</v>
+        <v>87</v>
       </c>
     </row>
     <row r="52" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B52" s="4" t="s">
-        <v>96</v>
+        <v>90</v>
       </c>
       <c r="C52" s="4" t="s">
-        <v>95</v>
+        <v>89</v>
       </c>
     </row>
     <row r="53" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B53" s="4" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C53" s="4" t="s">
-        <v>97</v>
+        <v>91</v>
       </c>
     </row>
     <row r="54" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B54" s="4" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C54" s="4" t="s">
-        <v>98</v>
+        <v>92</v>
       </c>
     </row>
     <row r="55" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B55" s="4" t="s">
-        <v>100</v>
+        <v>94</v>
       </c>
       <c r="C55" s="4" t="s">
-        <v>99</v>
+        <v>93</v>
       </c>
     </row>
     <row r="56" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B56" s="4" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C56" s="4" t="s">
-        <v>101</v>
+        <v>95</v>
       </c>
     </row>
   </sheetData>
@@ -3930,1690 +3915,1690 @@
     </row>
     <row r="2" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B2" s="4" t="s">
-        <v>162</v>
+        <v>156</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>163</v>
+        <v>157</v>
       </c>
     </row>
     <row r="3" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B3" s="4" t="s">
-        <v>164</v>
+        <v>158</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>165</v>
+        <v>159</v>
       </c>
     </row>
     <row r="4" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B4" s="4" t="s">
-        <v>166</v>
+        <v>160</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>167</v>
+        <v>161</v>
       </c>
     </row>
     <row r="5" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B5" s="4" t="s">
-        <v>168</v>
+        <v>162</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>169</v>
+        <v>163</v>
       </c>
     </row>
     <row r="6" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B6" s="4" t="s">
-        <v>170</v>
+        <v>164</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>171</v>
+        <v>165</v>
       </c>
     </row>
     <row r="7" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B7" s="4" t="s">
-        <v>104</v>
+        <v>98</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>172</v>
+        <v>166</v>
       </c>
     </row>
     <row r="8" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B8" s="4" t="s">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>172</v>
+        <v>166</v>
       </c>
     </row>
     <row r="9" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B9" s="4" t="s">
-        <v>173</v>
+        <v>167</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>172</v>
+        <v>166</v>
       </c>
     </row>
     <row r="10" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B10" s="4" t="s">
-        <v>108</v>
+        <v>102</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>174</v>
+        <v>168</v>
       </c>
     </row>
     <row r="11" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B11" s="4" t="s">
-        <v>110</v>
+        <v>104</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>175</v>
+        <v>169</v>
       </c>
     </row>
     <row r="12" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B12" s="4" t="s">
-        <v>112</v>
+        <v>106</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>176</v>
+        <v>170</v>
       </c>
     </row>
     <row r="13" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B13" s="4" t="s">
-        <v>177</v>
+        <v>171</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>178</v>
+        <v>172</v>
       </c>
     </row>
     <row r="14" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B14" s="4" t="s">
-        <v>114</v>
+        <v>108</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>179</v>
+        <v>173</v>
       </c>
     </row>
     <row r="15" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B15" s="4" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>180</v>
+        <v>174</v>
       </c>
     </row>
     <row r="16" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B16" s="4" t="s">
-        <v>117</v>
+        <v>111</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>181</v>
+        <v>175</v>
       </c>
     </row>
     <row r="17" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B17" s="4" t="s">
-        <v>119</v>
+        <v>113</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>182</v>
+        <v>176</v>
       </c>
     </row>
     <row r="18" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B18" s="4" t="s">
-        <v>121</v>
+        <v>115</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>183</v>
+        <v>177</v>
       </c>
     </row>
     <row r="19" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B19" s="4" t="s">
-        <v>123</v>
+        <v>117</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>184</v>
+        <v>178</v>
       </c>
     </row>
     <row r="20" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B20" s="4" t="s">
-        <v>185</v>
+        <v>179</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>186</v>
+        <v>180</v>
       </c>
     </row>
     <row r="21" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B21" s="4" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>187</v>
+        <v>181</v>
       </c>
     </row>
     <row r="22" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B22" s="4" t="s">
-        <v>127</v>
+        <v>121</v>
       </c>
       <c r="C22" s="4" t="s">
-        <v>188</v>
+        <v>182</v>
       </c>
     </row>
     <row r="23" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B23" s="4" t="s">
-        <v>129</v>
+        <v>123</v>
       </c>
       <c r="C23" s="4" t="s">
-        <v>189</v>
+        <v>183</v>
       </c>
     </row>
     <row r="24" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B24" s="4" t="s">
-        <v>131</v>
+        <v>125</v>
       </c>
       <c r="C24" s="4" t="s">
-        <v>190</v>
+        <v>184</v>
       </c>
     </row>
     <row r="25" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B25" s="4" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="C25" s="4" t="s">
-        <v>191</v>
+        <v>185</v>
       </c>
     </row>
     <row r="26" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B26" s="4" t="s">
-        <v>192</v>
+        <v>186</v>
       </c>
       <c r="C26" s="4" t="s">
-        <v>193</v>
+        <v>187</v>
       </c>
     </row>
     <row r="27" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B27" s="4" t="s">
-        <v>194</v>
+        <v>188</v>
       </c>
       <c r="C27" s="4" t="s">
-        <v>195</v>
+        <v>189</v>
       </c>
     </row>
     <row r="28" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B28" s="4" t="s">
-        <v>196</v>
+        <v>190</v>
       </c>
       <c r="C28" s="4" t="s">
-        <v>197</v>
+        <v>191</v>
       </c>
     </row>
     <row r="29" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B29" s="4" t="s">
-        <v>198</v>
+        <v>192</v>
       </c>
       <c r="C29" s="4" t="s">
-        <v>199</v>
+        <v>193</v>
       </c>
     </row>
     <row r="30" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B30" s="4" t="s">
-        <v>200</v>
+        <v>194</v>
       </c>
       <c r="C30" s="4" t="s">
-        <v>201</v>
+        <v>195</v>
       </c>
     </row>
     <row r="31" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B31" s="4" t="s">
-        <v>202</v>
+        <v>196</v>
       </c>
       <c r="C31" s="4" t="s">
-        <v>203</v>
+        <v>197</v>
       </c>
     </row>
     <row r="32" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B32" s="4" t="s">
-        <v>204</v>
+        <v>198</v>
       </c>
       <c r="C32" s="4" t="s">
-        <v>205</v>
+        <v>199</v>
       </c>
     </row>
     <row r="33" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B33" s="4" t="s">
-        <v>206</v>
+        <v>200</v>
       </c>
       <c r="C33" s="4" t="s">
-        <v>207</v>
+        <v>201</v>
       </c>
     </row>
     <row r="34" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B34" s="4" t="s">
-        <v>208</v>
+        <v>202</v>
       </c>
       <c r="C34" s="4" t="s">
-        <v>209</v>
+        <v>203</v>
       </c>
     </row>
     <row r="35" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B35" s="4" t="s">
-        <v>210</v>
+        <v>204</v>
       </c>
       <c r="C35" s="4" t="s">
-        <v>211</v>
+        <v>205</v>
       </c>
     </row>
     <row r="36" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B36" s="4" t="s">
-        <v>212</v>
+        <v>206</v>
       </c>
       <c r="C36" s="4" t="s">
-        <v>213</v>
+        <v>207</v>
       </c>
     </row>
     <row r="37" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B37" s="4" t="s">
-        <v>214</v>
+        <v>208</v>
       </c>
       <c r="C37" s="4" t="s">
-        <v>215</v>
+        <v>209</v>
       </c>
     </row>
     <row r="38" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B38" s="4" t="s">
-        <v>216</v>
+        <v>210</v>
       </c>
       <c r="C38" s="4" t="s">
-        <v>217</v>
+        <v>211</v>
       </c>
     </row>
     <row r="39" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B39" s="4" t="s">
-        <v>218</v>
+        <v>212</v>
       </c>
       <c r="C39" s="4" t="s">
-        <v>219</v>
+        <v>213</v>
       </c>
     </row>
     <row r="40" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B40" s="4" t="s">
-        <v>220</v>
+        <v>214</v>
       </c>
       <c r="C40" s="4" t="s">
-        <v>221</v>
+        <v>215</v>
       </c>
     </row>
     <row r="41" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B41" s="4" t="s">
-        <v>222</v>
+        <v>216</v>
       </c>
       <c r="C41" s="4" t="s">
-        <v>223</v>
+        <v>217</v>
       </c>
     </row>
     <row r="42" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B42" s="4" t="s">
-        <v>224</v>
+        <v>218</v>
       </c>
       <c r="C42" s="4" t="s">
-        <v>225</v>
+        <v>219</v>
       </c>
     </row>
     <row r="43" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B43" s="4" t="s">
-        <v>226</v>
+        <v>220</v>
       </c>
       <c r="C43" s="4" t="s">
-        <v>227</v>
+        <v>221</v>
       </c>
     </row>
     <row r="44" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B44" s="4" t="s">
-        <v>228</v>
+        <v>222</v>
       </c>
       <c r="C44" s="4" t="s">
-        <v>229</v>
+        <v>223</v>
       </c>
     </row>
     <row r="45" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B45" s="4" t="s">
-        <v>230</v>
+        <v>224</v>
       </c>
       <c r="C45" s="4" t="s">
-        <v>231</v>
+        <v>225</v>
       </c>
     </row>
     <row r="46" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B46" s="4" t="s">
-        <v>232</v>
+        <v>226</v>
       </c>
       <c r="C46" s="4" t="s">
-        <v>233</v>
+        <v>227</v>
       </c>
     </row>
     <row r="47" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B47" s="4" t="s">
-        <v>234</v>
+        <v>228</v>
       </c>
       <c r="C47" s="4" t="s">
-        <v>235</v>
+        <v>229</v>
       </c>
     </row>
     <row r="48" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B48" s="4" t="s">
-        <v>236</v>
+        <v>230</v>
       </c>
       <c r="C48" s="4" t="s">
-        <v>237</v>
+        <v>231</v>
       </c>
     </row>
     <row r="49" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B49" s="4" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="C49" s="4" t="s">
-        <v>239</v>
+        <v>233</v>
       </c>
     </row>
     <row r="50" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B50" s="4" t="s">
-        <v>240</v>
+        <v>234</v>
       </c>
       <c r="C50" s="4" t="s">
-        <v>241</v>
+        <v>235</v>
       </c>
     </row>
     <row r="51" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B51" s="4" t="s">
-        <v>242</v>
+        <v>236</v>
       </c>
       <c r="C51" s="4" t="s">
-        <v>243</v>
+        <v>237</v>
       </c>
     </row>
     <row r="52" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B52" s="4" t="s">
-        <v>244</v>
+        <v>238</v>
       </c>
       <c r="C52" s="4" t="s">
-        <v>245</v>
+        <v>239</v>
       </c>
     </row>
     <row r="53" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B53" s="4" t="s">
-        <v>246</v>
+        <v>240</v>
       </c>
       <c r="C53" s="4" t="s">
-        <v>247</v>
+        <v>241</v>
       </c>
     </row>
     <row r="54" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B54" s="4" t="s">
-        <v>248</v>
+        <v>242</v>
       </c>
       <c r="C54" s="4" t="s">
-        <v>249</v>
+        <v>243</v>
       </c>
     </row>
     <row r="55" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B55" s="4" t="s">
-        <v>250</v>
+        <v>244</v>
       </c>
       <c r="C55" s="4" t="s">
-        <v>251</v>
+        <v>245</v>
       </c>
     </row>
     <row r="56" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B56" s="4" t="s">
-        <v>252</v>
+        <v>246</v>
       </c>
       <c r="C56" s="4" t="s">
-        <v>253</v>
+        <v>247</v>
       </c>
     </row>
     <row r="57" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B57" s="4" t="s">
-        <v>254</v>
+        <v>248</v>
       </c>
       <c r="C57" s="4" t="s">
-        <v>255</v>
+        <v>249</v>
       </c>
     </row>
     <row r="58" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B58" s="4" t="s">
-        <v>256</v>
+        <v>250</v>
       </c>
       <c r="C58" s="4" t="s">
-        <v>257</v>
+        <v>251</v>
       </c>
     </row>
     <row r="59" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B59" s="4" t="s">
-        <v>258</v>
+        <v>252</v>
       </c>
       <c r="C59" s="4" t="s">
-        <v>259</v>
+        <v>253</v>
       </c>
     </row>
     <row r="60" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B60" s="4" t="s">
-        <v>260</v>
+        <v>254</v>
       </c>
       <c r="C60" s="4" t="s">
-        <v>261</v>
+        <v>255</v>
       </c>
     </row>
     <row r="61" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B61" s="4" t="s">
-        <v>262</v>
+        <v>256</v>
       </c>
       <c r="C61" s="4" t="s">
-        <v>263</v>
+        <v>257</v>
       </c>
     </row>
     <row r="62" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B62" s="4" t="s">
-        <v>264</v>
+        <v>258</v>
       </c>
       <c r="C62" s="4" t="s">
-        <v>265</v>
+        <v>259</v>
       </c>
     </row>
     <row r="63" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B63" s="4" t="s">
-        <v>266</v>
+        <v>260</v>
       </c>
       <c r="C63" s="4" t="s">
-        <v>267</v>
+        <v>261</v>
       </c>
     </row>
     <row r="64" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B64" s="4" t="s">
-        <v>268</v>
+        <v>262</v>
       </c>
       <c r="C64" s="4" t="s">
-        <v>269</v>
+        <v>263</v>
       </c>
     </row>
     <row r="65" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B65" s="4" t="s">
-        <v>270</v>
+        <v>264</v>
       </c>
       <c r="C65" s="4" t="s">
-        <v>271</v>
+        <v>265</v>
       </c>
     </row>
     <row r="66" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B66" s="4" t="s">
-        <v>272</v>
+        <v>266</v>
       </c>
       <c r="C66" s="4" t="s">
-        <v>273</v>
+        <v>267</v>
       </c>
     </row>
     <row r="67" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B67" s="4" t="s">
-        <v>274</v>
+        <v>268</v>
       </c>
       <c r="C67" s="4" t="s">
-        <v>275</v>
+        <v>269</v>
       </c>
     </row>
     <row r="68" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B68" s="4" t="s">
-        <v>276</v>
+        <v>270</v>
       </c>
       <c r="C68" s="4" t="s">
-        <v>277</v>
+        <v>271</v>
       </c>
     </row>
     <row r="69" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B69" s="4" t="s">
-        <v>278</v>
+        <v>272</v>
       </c>
       <c r="C69" s="4" t="s">
-        <v>279</v>
+        <v>273</v>
       </c>
     </row>
     <row r="70" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B70" s="4" t="s">
-        <v>280</v>
+        <v>274</v>
       </c>
       <c r="C70" s="4" t="s">
-        <v>281</v>
+        <v>275</v>
       </c>
     </row>
     <row r="71" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B71" s="4" t="s">
-        <v>282</v>
+        <v>276</v>
       </c>
       <c r="C71" s="4" t="s">
-        <v>283</v>
+        <v>277</v>
       </c>
     </row>
     <row r="72" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B72" s="4" t="s">
-        <v>284</v>
+        <v>278</v>
       </c>
       <c r="C72" s="4" t="s">
-        <v>285</v>
+        <v>279</v>
       </c>
     </row>
     <row r="73" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B73" s="4" t="s">
-        <v>286</v>
+        <v>280</v>
       </c>
       <c r="C73" s="4" t="s">
-        <v>287</v>
+        <v>281</v>
       </c>
     </row>
     <row r="74" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B74" s="4" t="s">
-        <v>288</v>
+        <v>282</v>
       </c>
       <c r="C74" s="4" t="s">
-        <v>289</v>
+        <v>283</v>
       </c>
     </row>
     <row r="75" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B75" s="4" t="s">
-        <v>290</v>
+        <v>284</v>
       </c>
       <c r="C75" s="4" t="s">
-        <v>291</v>
+        <v>285</v>
       </c>
     </row>
     <row r="76" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B76" s="4" t="s">
-        <v>292</v>
+        <v>286</v>
       </c>
       <c r="C76" s="4" t="s">
-        <v>293</v>
+        <v>287</v>
       </c>
     </row>
     <row r="77" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B77" s="4" t="s">
-        <v>294</v>
+        <v>288</v>
       </c>
       <c r="C77" s="4" t="s">
-        <v>295</v>
+        <v>289</v>
       </c>
     </row>
     <row r="78" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B78" s="4" t="s">
-        <v>296</v>
+        <v>290</v>
       </c>
       <c r="C78" s="4" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
     </row>
     <row r="79" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B79" s="4" t="s">
-        <v>297</v>
+        <v>291</v>
       </c>
       <c r="C79" s="4" t="s">
-        <v>298</v>
+        <v>292</v>
       </c>
     </row>
     <row r="80" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B80" s="4" t="s">
-        <v>299</v>
+        <v>293</v>
       </c>
       <c r="C80" s="4" t="s">
-        <v>300</v>
+        <v>294</v>
       </c>
     </row>
     <row r="81" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B81" s="4" t="s">
-        <v>301</v>
+        <v>295</v>
       </c>
       <c r="C81" s="4" t="s">
-        <v>302</v>
+        <v>296</v>
       </c>
     </row>
     <row r="82" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B82" s="4" t="s">
-        <v>303</v>
+        <v>297</v>
       </c>
       <c r="C82" s="4" t="s">
-        <v>304</v>
+        <v>298</v>
       </c>
     </row>
     <row r="83" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B83" s="4" t="s">
-        <v>305</v>
+        <v>299</v>
       </c>
       <c r="C83" s="4" t="s">
-        <v>306</v>
+        <v>300</v>
       </c>
     </row>
     <row r="84" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B84" s="4" t="s">
-        <v>307</v>
+        <v>301</v>
       </c>
       <c r="C84" s="4" t="s">
-        <v>308</v>
+        <v>302</v>
       </c>
     </row>
     <row r="85" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B85" s="4" t="s">
-        <v>309</v>
+        <v>303</v>
       </c>
       <c r="C85" s="4" t="s">
-        <v>310</v>
+        <v>304</v>
       </c>
     </row>
     <row r="86" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B86" s="4" t="s">
-        <v>311</v>
+        <v>305</v>
       </c>
       <c r="C86" s="4" t="s">
-        <v>312</v>
+        <v>306</v>
       </c>
     </row>
     <row r="87" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B87" s="4" t="s">
-        <v>313</v>
+        <v>307</v>
       </c>
       <c r="C87" s="4" t="s">
-        <v>314</v>
+        <v>308</v>
       </c>
     </row>
     <row r="88" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B88" s="4" t="s">
-        <v>315</v>
+        <v>309</v>
       </c>
       <c r="C88" s="4" t="s">
-        <v>316</v>
+        <v>310</v>
       </c>
     </row>
     <row r="89" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B89" s="4" t="s">
-        <v>317</v>
+        <v>311</v>
       </c>
       <c r="C89" s="4" t="s">
-        <v>318</v>
+        <v>312</v>
       </c>
     </row>
     <row r="90" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B90" s="4" t="s">
-        <v>319</v>
+        <v>313</v>
       </c>
       <c r="C90" s="4" t="s">
-        <v>320</v>
+        <v>314</v>
       </c>
     </row>
     <row r="91" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B91" s="4" t="s">
-        <v>321</v>
+        <v>315</v>
       </c>
       <c r="C91" s="4" t="s">
-        <v>322</v>
+        <v>316</v>
       </c>
     </row>
     <row r="92" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B92" s="4" t="s">
-        <v>323</v>
+        <v>317</v>
       </c>
       <c r="C92" s="4" t="s">
-        <v>324</v>
+        <v>318</v>
       </c>
     </row>
     <row r="93" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B93" s="4" t="s">
-        <v>325</v>
+        <v>319</v>
       </c>
       <c r="C93" s="4" t="s">
-        <v>326</v>
+        <v>320</v>
       </c>
     </row>
     <row r="94" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B94" s="4" t="s">
-        <v>327</v>
+        <v>321</v>
       </c>
       <c r="C94" s="4" t="s">
-        <v>328</v>
+        <v>322</v>
       </c>
     </row>
     <row r="95" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B95" s="4" t="s">
-        <v>329</v>
+        <v>323</v>
       </c>
       <c r="C95" s="4" t="s">
-        <v>330</v>
+        <v>324</v>
       </c>
     </row>
     <row r="96" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B96" s="4" t="s">
-        <v>331</v>
+        <v>325</v>
       </c>
       <c r="C96" s="4" t="s">
-        <v>332</v>
+        <v>326</v>
       </c>
     </row>
     <row r="97" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B97" s="4" t="s">
-        <v>333</v>
+        <v>327</v>
       </c>
       <c r="C97" s="4" t="s">
-        <v>334</v>
+        <v>328</v>
       </c>
     </row>
     <row r="98" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B98" s="4" t="s">
-        <v>335</v>
+        <v>329</v>
       </c>
       <c r="C98" s="4" t="s">
-        <v>336</v>
+        <v>330</v>
       </c>
     </row>
     <row r="99" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B99" s="4" t="s">
-        <v>337</v>
+        <v>331</v>
       </c>
       <c r="C99" s="4" t="s">
-        <v>338</v>
+        <v>332</v>
       </c>
     </row>
     <row r="100" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B100" s="4" t="s">
-        <v>135</v>
+        <v>129</v>
       </c>
       <c r="C100" s="4" t="s">
-        <v>339</v>
+        <v>333</v>
       </c>
     </row>
     <row r="101" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B101" s="4" t="s">
-        <v>137</v>
+        <v>131</v>
       </c>
       <c r="C101" s="4" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="102" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B102" s="4" t="s">
-        <v>340</v>
+        <v>334</v>
       </c>
       <c r="C102" s="4" t="s">
-        <v>341</v>
+        <v>335</v>
       </c>
     </row>
     <row r="103" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B103" s="4" t="s">
-        <v>139</v>
+        <v>133</v>
       </c>
       <c r="C103" s="4" t="s">
-        <v>342</v>
+        <v>336</v>
       </c>
     </row>
     <row r="104" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B104" s="4" t="s">
-        <v>343</v>
+        <v>337</v>
       </c>
       <c r="C104" s="4" t="s">
-        <v>344</v>
+        <v>338</v>
       </c>
     </row>
     <row r="105" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B105" s="4" t="s">
-        <v>141</v>
+        <v>135</v>
       </c>
       <c r="C105" s="4" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="106" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B106" s="4" t="s">
-        <v>143</v>
+        <v>137</v>
       </c>
       <c r="C106" s="4" t="s">
-        <v>345</v>
+        <v>339</v>
       </c>
     </row>
     <row r="107" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B107" s="4" t="s">
-        <v>346</v>
+        <v>340</v>
       </c>
       <c r="C107" s="4" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
     </row>
     <row r="108" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B108" s="4" t="s">
-        <v>347</v>
+        <v>341</v>
       </c>
       <c r="C108" s="4" t="s">
-        <v>348</v>
+        <v>342</v>
       </c>
     </row>
     <row r="109" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B109" s="4" t="s">
-        <v>145</v>
+        <v>139</v>
       </c>
       <c r="C109" s="4" t="s">
-        <v>349</v>
+        <v>343</v>
       </c>
     </row>
     <row r="110" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B110" s="4" t="s">
-        <v>147</v>
+        <v>141</v>
       </c>
       <c r="C110" s="4" t="s">
-        <v>350</v>
+        <v>344</v>
       </c>
     </row>
     <row r="111" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B111" s="4" t="s">
-        <v>149</v>
+        <v>143</v>
       </c>
       <c r="C111" s="4" t="s">
-        <v>351</v>
+        <v>345</v>
       </c>
     </row>
     <row r="112" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B112" s="4" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="C112" s="4" t="s">
-        <v>352</v>
+        <v>346</v>
       </c>
     </row>
     <row r="113" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B113" s="4" t="s">
-        <v>152</v>
+        <v>146</v>
       </c>
       <c r="C113" s="4" t="s">
-        <v>353</v>
+        <v>347</v>
       </c>
     </row>
     <row r="114" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B114" s="4" t="s">
-        <v>154</v>
+        <v>148</v>
       </c>
       <c r="C114" s="4" t="s">
-        <v>354</v>
+        <v>348</v>
       </c>
     </row>
     <row r="115" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B115" s="4" t="s">
-        <v>156</v>
+        <v>150</v>
       </c>
       <c r="C115" s="4" t="s">
-        <v>304</v>
+        <v>298</v>
       </c>
     </row>
     <row r="116" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B116" s="4" t="s">
-        <v>158</v>
+        <v>152</v>
       </c>
       <c r="C116" s="4" t="s">
-        <v>355</v>
+        <v>349</v>
       </c>
     </row>
     <row r="117" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B117" s="4" t="s">
-        <v>160</v>
+        <v>154</v>
       </c>
       <c r="C117" s="4" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
     </row>
     <row r="118" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B118" s="4" t="s">
-        <v>356</v>
+        <v>350</v>
       </c>
       <c r="C118" s="4" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="119" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B119" s="4" t="s">
-        <v>357</v>
+        <v>351</v>
       </c>
       <c r="C119" s="4" t="s">
-        <v>358</v>
+        <v>352</v>
       </c>
     </row>
     <row r="120" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B120" s="4" t="s">
-        <v>359</v>
+        <v>353</v>
       </c>
       <c r="C120" s="4" t="s">
-        <v>360</v>
+        <v>354</v>
       </c>
     </row>
     <row r="121" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B121" s="4" t="s">
-        <v>361</v>
+        <v>355</v>
       </c>
       <c r="C121" s="4" t="s">
-        <v>362</v>
+        <v>356</v>
       </c>
     </row>
     <row r="122" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B122" s="4" t="s">
-        <v>363</v>
+        <v>357</v>
       </c>
       <c r="C122" s="4" t="s">
-        <v>364</v>
+        <v>358</v>
       </c>
     </row>
     <row r="123" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B123" s="4" t="s">
-        <v>365</v>
+        <v>359</v>
       </c>
       <c r="C123" s="4" t="s">
-        <v>366</v>
+        <v>360</v>
       </c>
     </row>
     <row r="124" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B124" s="4" t="s">
-        <v>367</v>
+        <v>361</v>
       </c>
       <c r="C124" s="4" t="s">
-        <v>368</v>
+        <v>362</v>
       </c>
     </row>
     <row r="125" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B125" s="4" t="s">
-        <v>369</v>
+        <v>363</v>
       </c>
       <c r="C125" s="4" t="s">
-        <v>370</v>
+        <v>364</v>
       </c>
     </row>
     <row r="126" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B126" s="4" t="s">
-        <v>371</v>
+        <v>365</v>
       </c>
       <c r="C126" s="4" t="s">
-        <v>372</v>
+        <v>366</v>
       </c>
     </row>
     <row r="127" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B127" s="4" t="s">
-        <v>373</v>
+        <v>367</v>
       </c>
       <c r="C127" s="4" t="s">
-        <v>374</v>
+        <v>368</v>
       </c>
     </row>
     <row r="128" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B128" s="4" t="s">
-        <v>375</v>
+        <v>369</v>
       </c>
       <c r="C128" s="4" t="s">
-        <v>376</v>
+        <v>370</v>
       </c>
     </row>
     <row r="129" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B129" s="4" t="s">
-        <v>377</v>
+        <v>371</v>
       </c>
       <c r="C129" s="4" t="s">
-        <v>378</v>
+        <v>372</v>
       </c>
     </row>
     <row r="130" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B130" s="4" t="s">
-        <v>379</v>
+        <v>373</v>
       </c>
       <c r="C130" s="4" t="s">
-        <v>380</v>
+        <v>374</v>
       </c>
     </row>
     <row r="131" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B131" s="4" t="s">
-        <v>381</v>
+        <v>375</v>
       </c>
       <c r="C131" s="4" t="s">
-        <v>382</v>
+        <v>376</v>
       </c>
     </row>
     <row r="132" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B132" s="4" t="s">
-        <v>383</v>
+        <v>377</v>
       </c>
       <c r="C132" s="4" t="s">
-        <v>384</v>
+        <v>378</v>
       </c>
     </row>
     <row r="133" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B133" s="4" t="s">
-        <v>385</v>
+        <v>379</v>
       </c>
       <c r="C133" s="4" t="s">
-        <v>386</v>
+        <v>380</v>
       </c>
     </row>
     <row r="134" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B134" s="4" t="s">
-        <v>387</v>
+        <v>381</v>
       </c>
       <c r="C134" s="4" t="s">
-        <v>388</v>
+        <v>382</v>
       </c>
     </row>
     <row r="135" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B135" s="4" t="s">
-        <v>389</v>
+        <v>383</v>
       </c>
       <c r="C135" s="4" t="s">
-        <v>390</v>
+        <v>384</v>
       </c>
     </row>
     <row r="136" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B136" s="4" t="s">
-        <v>391</v>
+        <v>385</v>
       </c>
       <c r="C136" s="4" t="s">
-        <v>392</v>
+        <v>386</v>
       </c>
     </row>
     <row r="137" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B137" s="4" t="s">
-        <v>393</v>
+        <v>387</v>
       </c>
       <c r="C137" s="4" t="s">
-        <v>394</v>
+        <v>388</v>
       </c>
     </row>
     <row r="138" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B138" s="4" t="s">
-        <v>395</v>
+        <v>389</v>
       </c>
       <c r="C138" s="4" t="s">
-        <v>396</v>
+        <v>390</v>
       </c>
     </row>
     <row r="139" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B139" s="4" t="s">
-        <v>397</v>
+        <v>391</v>
       </c>
       <c r="C139" s="4" t="s">
-        <v>398</v>
+        <v>392</v>
       </c>
     </row>
     <row r="140" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B140" s="4" t="s">
-        <v>399</v>
+        <v>393</v>
       </c>
       <c r="C140" s="4" t="s">
-        <v>400</v>
+        <v>394</v>
       </c>
     </row>
     <row r="141" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B141" s="4" t="s">
-        <v>401</v>
+        <v>395</v>
       </c>
       <c r="C141" s="4" t="s">
-        <v>402</v>
+        <v>396</v>
       </c>
     </row>
     <row r="142" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B142" s="4" t="s">
-        <v>403</v>
+        <v>397</v>
       </c>
       <c r="C142" s="4" t="s">
-        <v>404</v>
+        <v>398</v>
       </c>
     </row>
     <row r="143" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B143" s="4" t="s">
-        <v>405</v>
+        <v>399</v>
       </c>
       <c r="C143" s="4" t="s">
-        <v>406</v>
+        <v>400</v>
       </c>
     </row>
     <row r="144" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B144" s="4" t="s">
-        <v>407</v>
+        <v>401</v>
       </c>
       <c r="C144" s="4" t="s">
-        <v>408</v>
+        <v>402</v>
       </c>
     </row>
     <row r="145" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B145" s="4" t="s">
-        <v>409</v>
+        <v>403</v>
       </c>
       <c r="C145" s="4" t="s">
-        <v>410</v>
+        <v>404</v>
       </c>
     </row>
     <row r="146" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B146" s="4" t="s">
-        <v>411</v>
+        <v>405</v>
       </c>
       <c r="C146" s="4" t="s">
-        <v>412</v>
+        <v>406</v>
       </c>
     </row>
     <row r="147" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B147" s="4" t="s">
-        <v>413</v>
+        <v>407</v>
       </c>
       <c r="C147" s="4" t="s">
-        <v>414</v>
+        <v>408</v>
       </c>
     </row>
     <row r="148" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B148" s="4" t="s">
-        <v>415</v>
+        <v>409</v>
       </c>
       <c r="C148" s="4" t="s">
-        <v>416</v>
+        <v>410</v>
       </c>
     </row>
     <row r="149" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B149" s="4" t="s">
-        <v>417</v>
+        <v>411</v>
       </c>
       <c r="C149" s="4" t="s">
-        <v>418</v>
+        <v>412</v>
       </c>
     </row>
     <row r="150" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B150" s="4" t="s">
-        <v>419</v>
+        <v>413</v>
       </c>
       <c r="C150" s="4" t="s">
-        <v>420</v>
+        <v>414</v>
       </c>
     </row>
     <row r="151" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B151" s="4" t="s">
-        <v>421</v>
+        <v>415</v>
       </c>
       <c r="C151" s="4" t="s">
-        <v>422</v>
+        <v>416</v>
       </c>
     </row>
     <row r="152" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B152" s="4" t="s">
-        <v>423</v>
+        <v>417</v>
       </c>
       <c r="C152" s="4" t="s">
-        <v>424</v>
+        <v>418</v>
       </c>
     </row>
     <row r="153" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B153" s="4" t="s">
-        <v>425</v>
+        <v>419</v>
       </c>
       <c r="C153" s="4" t="s">
-        <v>426</v>
+        <v>420</v>
       </c>
     </row>
     <row r="154" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B154" s="4" t="s">
-        <v>427</v>
+        <v>421</v>
       </c>
       <c r="C154" s="4" t="s">
-        <v>428</v>
+        <v>422</v>
       </c>
     </row>
     <row r="155" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B155" s="4" t="s">
-        <v>429</v>
+        <v>423</v>
       </c>
       <c r="C155" s="4" t="s">
-        <v>430</v>
+        <v>424</v>
       </c>
     </row>
     <row r="156" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B156" s="4" t="s">
-        <v>431</v>
+        <v>425</v>
       </c>
       <c r="C156" s="4" t="s">
-        <v>432</v>
+        <v>426</v>
       </c>
     </row>
     <row r="157" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B157" s="4" t="s">
-        <v>433</v>
+        <v>427</v>
       </c>
       <c r="C157" s="4" t="s">
-        <v>434</v>
+        <v>428</v>
       </c>
     </row>
     <row r="158" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B158" s="4" t="s">
-        <v>435</v>
+        <v>429</v>
       </c>
       <c r="C158" s="4" t="s">
-        <v>436</v>
+        <v>430</v>
       </c>
     </row>
     <row r="159" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B159" s="4" t="s">
-        <v>437</v>
+        <v>431</v>
       </c>
       <c r="C159" s="4" t="s">
-        <v>438</v>
+        <v>432</v>
       </c>
     </row>
     <row r="160" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B160" s="4" t="s">
-        <v>439</v>
+        <v>433</v>
       </c>
       <c r="C160" s="4" t="s">
-        <v>440</v>
+        <v>434</v>
       </c>
     </row>
     <row r="161" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B161" s="4" t="s">
-        <v>441</v>
+        <v>435</v>
       </c>
       <c r="C161" s="4" t="s">
-        <v>442</v>
+        <v>436</v>
       </c>
     </row>
     <row r="162" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B162" s="4" t="s">
-        <v>443</v>
+        <v>437</v>
       </c>
       <c r="C162" s="4" t="s">
-        <v>444</v>
+        <v>438</v>
       </c>
     </row>
     <row r="163" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B163" s="4" t="s">
-        <v>445</v>
+        <v>439</v>
       </c>
       <c r="C163" s="4" t="s">
-        <v>446</v>
+        <v>440</v>
       </c>
     </row>
     <row r="164" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B164" s="4" t="s">
-        <v>447</v>
+        <v>441</v>
       </c>
       <c r="C164" s="4" t="s">
-        <v>448</v>
+        <v>442</v>
       </c>
     </row>
     <row r="165" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B165" s="4" t="s">
-        <v>449</v>
+        <v>443</v>
       </c>
       <c r="C165" s="4" t="s">
-        <v>450</v>
+        <v>444</v>
       </c>
     </row>
     <row r="166" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B166" s="4" t="s">
-        <v>451</v>
+        <v>445</v>
       </c>
       <c r="C166" s="4" t="s">
-        <v>452</v>
+        <v>446</v>
       </c>
     </row>
     <row r="167" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B167" s="4" t="s">
-        <v>453</v>
+        <v>447</v>
       </c>
       <c r="C167" s="4" t="s">
-        <v>454</v>
+        <v>448</v>
       </c>
     </row>
     <row r="168" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B168" s="4" t="s">
-        <v>455</v>
+        <v>449</v>
       </c>
       <c r="C168" s="4" t="s">
-        <v>456</v>
+        <v>450</v>
       </c>
     </row>
     <row r="169" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B169" s="4" t="s">
-        <v>457</v>
+        <v>451</v>
       </c>
       <c r="C169" s="4" t="s">
-        <v>458</v>
+        <v>452</v>
       </c>
     </row>
     <row r="170" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B170" s="4" t="s">
-        <v>459</v>
+        <v>453</v>
       </c>
       <c r="C170" s="4" t="s">
-        <v>460</v>
+        <v>454</v>
       </c>
     </row>
     <row r="171" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B171" s="4" t="s">
-        <v>461</v>
+        <v>455</v>
       </c>
       <c r="C171" s="4" t="s">
-        <v>462</v>
+        <v>456</v>
       </c>
     </row>
     <row r="172" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B172" s="4" t="s">
-        <v>463</v>
+        <v>457</v>
       </c>
       <c r="C172" s="4" t="s">
-        <v>464</v>
+        <v>458</v>
       </c>
     </row>
     <row r="173" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B173" s="4" t="s">
-        <v>465</v>
+        <v>459</v>
       </c>
       <c r="C173" s="4" t="s">
-        <v>466</v>
+        <v>460</v>
       </c>
     </row>
     <row r="174" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B174" s="4" t="s">
-        <v>467</v>
+        <v>461</v>
       </c>
       <c r="C174" s="4" t="s">
-        <v>468</v>
+        <v>462</v>
       </c>
     </row>
     <row r="175" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B175" s="4" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="C175" s="4" t="s">
-        <v>469</v>
+        <v>463</v>
       </c>
     </row>
     <row r="176" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B176" s="4" t="s">
-        <v>470</v>
+        <v>464</v>
       </c>
       <c r="C176" s="4" t="s">
-        <v>471</v>
+        <v>465</v>
       </c>
     </row>
     <row r="177" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B177" s="4" t="s">
-        <v>472</v>
+        <v>466</v>
       </c>
       <c r="C177" s="4" t="s">
-        <v>473</v>
+        <v>467</v>
       </c>
     </row>
     <row r="178" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B178" s="4" t="s">
-        <v>474</v>
+        <v>468</v>
       </c>
       <c r="C178" s="4" t="s">
-        <v>475</v>
+        <v>469</v>
       </c>
     </row>
     <row r="179" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B179" s="4" t="s">
-        <v>476</v>
+        <v>470</v>
       </c>
       <c r="C179" s="4" t="s">
-        <v>477</v>
+        <v>471</v>
       </c>
     </row>
     <row r="180" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B180" s="4" t="s">
-        <v>478</v>
+        <v>472</v>
       </c>
       <c r="C180" s="4" t="s">
-        <v>479</v>
+        <v>473</v>
       </c>
     </row>
     <row r="181" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B181" s="4" t="s">
-        <v>480</v>
+        <v>474</v>
       </c>
       <c r="C181" s="4" t="s">
-        <v>481</v>
+        <v>475</v>
       </c>
     </row>
     <row r="182" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B182" s="4" t="s">
-        <v>482</v>
+        <v>476</v>
       </c>
       <c r="C182" s="4" t="s">
-        <v>483</v>
+        <v>477</v>
       </c>
     </row>
     <row r="183" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B183" s="4" t="s">
-        <v>484</v>
+        <v>478</v>
       </c>
       <c r="C183" s="4" t="s">
-        <v>485</v>
+        <v>479</v>
       </c>
     </row>
     <row r="184" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B184" s="4" t="s">
-        <v>486</v>
+        <v>480</v>
       </c>
       <c r="C184" s="4" t="s">
-        <v>487</v>
+        <v>481</v>
       </c>
     </row>
     <row r="185" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B185" s="4" t="s">
-        <v>488</v>
+        <v>482</v>
       </c>
       <c r="C185" s="4" t="s">
-        <v>489</v>
+        <v>483</v>
       </c>
     </row>
     <row r="186" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B186" s="4" t="s">
-        <v>490</v>
+        <v>484</v>
       </c>
       <c r="C186" s="4" t="s">
-        <v>491</v>
+        <v>485</v>
       </c>
     </row>
     <row r="187" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B187" s="4" t="s">
-        <v>492</v>
+        <v>486</v>
       </c>
       <c r="C187" s="4" t="s">
-        <v>493</v>
+        <v>487</v>
       </c>
     </row>
     <row r="188" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B188" s="4" t="s">
-        <v>494</v>
+        <v>488</v>
       </c>
       <c r="C188" s="4" t="s">
-        <v>495</v>
+        <v>489</v>
       </c>
     </row>
     <row r="189" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B189" s="4" t="s">
-        <v>496</v>
+        <v>490</v>
       </c>
       <c r="C189" s="4" t="s">
-        <v>497</v>
+        <v>491</v>
       </c>
     </row>
     <row r="190" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B190" s="4" t="s">
-        <v>498</v>
+        <v>492</v>
       </c>
       <c r="C190" s="4" t="s">
-        <v>499</v>
+        <v>493</v>
       </c>
     </row>
     <row r="191" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B191" s="4" t="s">
-        <v>500</v>
+        <v>494</v>
       </c>
       <c r="C191" s="4" t="s">
-        <v>501</v>
+        <v>495</v>
       </c>
     </row>
     <row r="192" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B192" s="4" t="s">
-        <v>502</v>
+        <v>496</v>
       </c>
       <c r="C192" s="4" t="s">
-        <v>503</v>
+        <v>497</v>
       </c>
     </row>
     <row r="193" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B193" s="4" t="s">
-        <v>504</v>
+        <v>498</v>
       </c>
       <c r="C193" s="4" t="s">
-        <v>505</v>
+        <v>499</v>
       </c>
     </row>
     <row r="194" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B194" s="4" t="s">
-        <v>506</v>
+        <v>500</v>
       </c>
       <c r="C194" s="4" t="s">
-        <v>507</v>
+        <v>501</v>
       </c>
     </row>
     <row r="195" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B195" s="4" t="s">
-        <v>508</v>
+        <v>502</v>
       </c>
       <c r="C195" s="4" t="s">
-        <v>509</v>
+        <v>503</v>
       </c>
     </row>
     <row r="196" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B196" s="4" t="s">
-        <v>510</v>
+        <v>504</v>
       </c>
       <c r="C196" s="4" t="s">
-        <v>511</v>
+        <v>505</v>
       </c>
     </row>
     <row r="197" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B197" s="4" t="s">
-        <v>512</v>
+        <v>506</v>
       </c>
       <c r="C197" s="4" t="s">
-        <v>513</v>
+        <v>507</v>
       </c>
     </row>
     <row r="198" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B198" s="4" t="s">
-        <v>514</v>
+        <v>508</v>
       </c>
       <c r="C198" s="4" t="s">
-        <v>515</v>
+        <v>509</v>
       </c>
     </row>
     <row r="199" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B199" s="4" t="s">
-        <v>516</v>
+        <v>510</v>
       </c>
       <c r="C199" s="4" t="s">
-        <v>517</v>
+        <v>511</v>
       </c>
     </row>
     <row r="200" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B200" s="4" t="s">
-        <v>518</v>
+        <v>512</v>
       </c>
       <c r="C200" s="4" t="s">
-        <v>519</v>
+        <v>513</v>
       </c>
     </row>
     <row r="201" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B201" s="4" t="s">
-        <v>520</v>
+        <v>514</v>
       </c>
       <c r="C201" s="4" t="s">
-        <v>521</v>
+        <v>515</v>
       </c>
     </row>
     <row r="202" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B202" s="4" t="s">
-        <v>522</v>
+        <v>516</v>
       </c>
       <c r="C202" s="4" t="s">
-        <v>523</v>
+        <v>517</v>
       </c>
     </row>
     <row r="203" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B203" s="4" t="s">
-        <v>524</v>
+        <v>518</v>
       </c>
       <c r="C203" s="4" t="s">
-        <v>487</v>
+        <v>481</v>
       </c>
     </row>
     <row r="204" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B204" s="4" t="s">
-        <v>525</v>
+        <v>519</v>
       </c>
       <c r="C204" s="4" t="s">
-        <v>526</v>
+        <v>520</v>
       </c>
     </row>
     <row r="205" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B205" s="4" t="s">
-        <v>527</v>
+        <v>521</v>
       </c>
       <c r="C205" s="4" t="s">
-        <v>528</v>
+        <v>522</v>
       </c>
     </row>
     <row r="206" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B206" s="4" t="s">
-        <v>529</v>
+        <v>523</v>
       </c>
       <c r="C206" s="4" t="s">
-        <v>530</v>
+        <v>524</v>
       </c>
     </row>
     <row r="207" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B207" s="4" t="s">
-        <v>531</v>
+        <v>525</v>
       </c>
       <c r="C207" s="4" t="s">
-        <v>532</v>
+        <v>526</v>
       </c>
     </row>
     <row r="208" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B208" s="4" t="s">
-        <v>533</v>
+        <v>527</v>
       </c>
       <c r="C208" s="4" t="s">
-        <v>534</v>
+        <v>528</v>
       </c>
     </row>
     <row r="209" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B209" s="4" t="s">
-        <v>535</v>
+        <v>529</v>
       </c>
       <c r="C209" s="4" t="s">
-        <v>536</v>
+        <v>530</v>
       </c>
     </row>
     <row r="210" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B210" s="4" t="s">
-        <v>537</v>
+        <v>531</v>
       </c>
       <c r="C210" s="4" t="s">
-        <v>538</v>
+        <v>532</v>
       </c>
     </row>
     <row r="211" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B211" s="4" t="s">
-        <v>539</v>
+        <v>533</v>
       </c>
       <c r="C211" s="4" t="s">
-        <v>540</v>
+        <v>534</v>
       </c>
     </row>
     <row r="212" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B212" s="4" t="s">
-        <v>541</v>
+        <v>535</v>
       </c>
       <c r="C212" s="4" t="s">
-        <v>542</v>
+        <v>536</v>
       </c>
     </row>
   </sheetData>
@@ -5637,778 +5622,778 @@
     </row>
     <row r="2" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B2" s="3" t="s">
-        <v>543</v>
+        <v>537</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>544</v>
+        <v>538</v>
       </c>
     </row>
     <row r="3" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B3" s="3" t="s">
-        <v>545</v>
+        <v>539</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>546</v>
+        <v>540</v>
       </c>
     </row>
     <row r="4" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B4" s="3" t="s">
-        <v>547</v>
+        <v>541</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>548</v>
+        <v>542</v>
       </c>
     </row>
     <row r="5" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B5" s="3" t="s">
-        <v>549</v>
+        <v>543</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>550</v>
+        <v>544</v>
       </c>
     </row>
     <row r="6" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B6" s="3" t="s">
-        <v>551</v>
+        <v>545</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>552</v>
+        <v>546</v>
       </c>
     </row>
     <row r="7" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B7" s="3" t="s">
-        <v>553</v>
+        <v>547</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>554</v>
+        <v>548</v>
       </c>
     </row>
     <row r="8" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B8" s="3" t="s">
-        <v>555</v>
+        <v>549</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>556</v>
+        <v>550</v>
       </c>
     </row>
     <row r="9" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B9" s="3" t="s">
-        <v>557</v>
+        <v>551</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>558</v>
+        <v>552</v>
       </c>
     </row>
     <row r="10" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B10" s="3" t="s">
-        <v>559</v>
+        <v>553</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>560</v>
+        <v>554</v>
       </c>
     </row>
     <row r="11" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B11" s="3" t="s">
-        <v>561</v>
+        <v>555</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>562</v>
+        <v>556</v>
       </c>
     </row>
     <row r="12" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B12" s="3" t="s">
-        <v>563</v>
+        <v>557</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>564</v>
+        <v>558</v>
       </c>
     </row>
     <row r="13" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B13" s="3" t="s">
-        <v>565</v>
+        <v>559</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>566</v>
+        <v>560</v>
       </c>
     </row>
     <row r="14" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B14" s="3" t="s">
-        <v>567</v>
+        <v>561</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>568</v>
+        <v>562</v>
       </c>
     </row>
     <row r="15" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B15" s="3" t="s">
-        <v>569</v>
+        <v>563</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>570</v>
+        <v>564</v>
       </c>
     </row>
     <row r="16" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B16" s="3" t="s">
-        <v>571</v>
+        <v>565</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>572</v>
+        <v>566</v>
       </c>
     </row>
     <row r="17" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B17" s="3" t="s">
-        <v>573</v>
+        <v>567</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>574</v>
+        <v>568</v>
       </c>
     </row>
     <row r="18" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B18" s="3" t="s">
-        <v>575</v>
+        <v>569</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>576</v>
+        <v>570</v>
       </c>
     </row>
     <row r="19" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B19" s="3" t="s">
-        <v>577</v>
+        <v>571</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>578</v>
+        <v>572</v>
       </c>
     </row>
     <row r="20" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B20" s="3" t="s">
-        <v>579</v>
+        <v>573</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>580</v>
+        <v>574</v>
       </c>
     </row>
     <row r="21" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B21" s="3" t="s">
-        <v>581</v>
+        <v>575</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>582</v>
+        <v>576</v>
       </c>
     </row>
     <row r="22" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B22" s="3" t="s">
-        <v>583</v>
+        <v>577</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>584</v>
+        <v>578</v>
       </c>
     </row>
     <row r="23" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B23" s="3" t="s">
-        <v>585</v>
+        <v>579</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>586</v>
+        <v>580</v>
       </c>
     </row>
     <row r="24" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B24" s="3" t="s">
-        <v>587</v>
+        <v>581</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>588</v>
+        <v>582</v>
       </c>
     </row>
     <row r="25" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B25" s="3" t="s">
-        <v>589</v>
+        <v>583</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>590</v>
+        <v>584</v>
       </c>
     </row>
     <row r="26" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B26" s="3" t="s">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>591</v>
+        <v>585</v>
       </c>
     </row>
     <row r="27" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B27" s="3" t="s">
-        <v>592</v>
+        <v>586</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>593</v>
+        <v>587</v>
       </c>
     </row>
     <row r="28" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B28" s="3" t="s">
-        <v>594</v>
+        <v>588</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>595</v>
+        <v>589</v>
       </c>
     </row>
     <row r="29" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B29" s="3" t="s">
-        <v>596</v>
+        <v>590</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>597</v>
+        <v>591</v>
       </c>
     </row>
     <row r="30" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B30" s="3" t="s">
-        <v>598</v>
+        <v>592</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>599</v>
+        <v>593</v>
       </c>
     </row>
     <row r="31" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B31" s="3" t="s">
-        <v>600</v>
+        <v>594</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>601</v>
+        <v>595</v>
       </c>
     </row>
     <row r="32" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B32" s="3" t="s">
-        <v>602</v>
+        <v>596</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>603</v>
+        <v>597</v>
       </c>
     </row>
     <row r="33" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B33" s="3" t="s">
-        <v>604</v>
+        <v>598</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>605</v>
+        <v>599</v>
       </c>
     </row>
     <row r="34" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B34" s="3" t="s">
-        <v>606</v>
+        <v>600</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>607</v>
+        <v>601</v>
       </c>
     </row>
     <row r="35" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B35" s="3" t="s">
-        <v>608</v>
+        <v>602</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>609</v>
+        <v>603</v>
       </c>
     </row>
     <row r="36" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B36" s="3" t="s">
-        <v>610</v>
+        <v>604</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>611</v>
+        <v>605</v>
       </c>
     </row>
     <row r="37" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B37" s="3" t="s">
-        <v>612</v>
+        <v>606</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>613</v>
+        <v>607</v>
       </c>
     </row>
     <row r="38" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B38" s="3" t="s">
-        <v>614</v>
+        <v>608</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>615</v>
+        <v>609</v>
       </c>
     </row>
     <row r="39" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B39" s="3" t="s">
-        <v>616</v>
+        <v>610</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>617</v>
+        <v>611</v>
       </c>
     </row>
     <row r="40" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B40" s="3" t="s">
-        <v>618</v>
+        <v>612</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>619</v>
+        <v>613</v>
       </c>
     </row>
     <row r="41" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B41" s="3" t="s">
-        <v>620</v>
+        <v>614</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>621</v>
+        <v>615</v>
       </c>
     </row>
     <row r="42" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B42" s="3" t="s">
-        <v>622</v>
+        <v>616</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>623</v>
+        <v>617</v>
       </c>
     </row>
     <row r="43" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B43" s="3" t="s">
-        <v>624</v>
+        <v>618</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>625</v>
+        <v>619</v>
       </c>
     </row>
     <row r="44" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B44" s="3" t="s">
-        <v>626</v>
+        <v>620</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>627</v>
+        <v>621</v>
       </c>
     </row>
     <row r="45" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B45" s="3" t="s">
-        <v>628</v>
+        <v>622</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>629</v>
+        <v>623</v>
       </c>
     </row>
     <row r="46" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B46" s="3" t="s">
-        <v>630</v>
+        <v>624</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>631</v>
+        <v>625</v>
       </c>
     </row>
     <row r="47" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B47" s="3" t="s">
-        <v>632</v>
+        <v>626</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>633</v>
+        <v>627</v>
       </c>
     </row>
     <row r="48" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B48" s="3" t="s">
-        <v>634</v>
+        <v>628</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>635</v>
+        <v>629</v>
       </c>
     </row>
     <row r="49" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B49" s="3" t="s">
-        <v>636</v>
+        <v>630</v>
       </c>
       <c r="C49" s="3" t="s">
-        <v>637</v>
+        <v>631</v>
       </c>
     </row>
     <row r="50" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B50" s="3" t="s">
-        <v>638</v>
+        <v>632</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>639</v>
+        <v>633</v>
       </c>
     </row>
     <row r="51" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B51" s="3" t="s">
-        <v>640</v>
+        <v>634</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>641</v>
+        <v>635</v>
       </c>
     </row>
     <row r="52" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B52" s="3" t="s">
-        <v>642</v>
+        <v>636</v>
       </c>
       <c r="C52" s="3" t="s">
-        <v>643</v>
+        <v>637</v>
       </c>
     </row>
     <row r="53" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B53" s="3" t="s">
-        <v>644</v>
+        <v>638</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>645</v>
+        <v>639</v>
       </c>
     </row>
     <row r="54" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B54" s="3" t="s">
-        <v>646</v>
+        <v>640</v>
       </c>
       <c r="C54" s="3" t="s">
-        <v>647</v>
+        <v>641</v>
       </c>
     </row>
     <row r="55" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B55" s="3" t="s">
-        <v>648</v>
+        <v>642</v>
       </c>
       <c r="C55" s="3" t="s">
-        <v>649</v>
+        <v>643</v>
       </c>
     </row>
     <row r="56" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B56" s="3" t="s">
-        <v>650</v>
+        <v>644</v>
       </c>
       <c r="C56" s="3" t="s">
-        <v>651</v>
+        <v>645</v>
       </c>
     </row>
     <row r="57" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B57" s="3" t="s">
-        <v>652</v>
+        <v>646</v>
       </c>
       <c r="C57" s="3" t="s">
-        <v>653</v>
+        <v>647</v>
       </c>
     </row>
     <row r="58" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B58" s="3" t="s">
-        <v>654</v>
+        <v>648</v>
       </c>
       <c r="C58" s="3" t="s">
-        <v>655</v>
+        <v>649</v>
       </c>
     </row>
     <row r="59" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B59" s="3" t="s">
-        <v>656</v>
+        <v>650</v>
       </c>
       <c r="C59" s="3" t="s">
-        <v>657</v>
+        <v>651</v>
       </c>
     </row>
     <row r="60" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B60" s="3" t="s">
-        <v>658</v>
+        <v>652</v>
       </c>
       <c r="C60" s="3" t="s">
-        <v>659</v>
+        <v>653</v>
       </c>
     </row>
     <row r="61" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B61" s="3" t="s">
-        <v>660</v>
+        <v>654</v>
       </c>
       <c r="C61" s="3" t="s">
-        <v>661</v>
+        <v>655</v>
       </c>
     </row>
     <row r="62" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B62" s="3" t="s">
-        <v>662</v>
+        <v>656</v>
       </c>
       <c r="C62" s="3" t="s">
-        <v>663</v>
+        <v>657</v>
       </c>
     </row>
     <row r="63" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B63" s="3" t="s">
-        <v>664</v>
+        <v>658</v>
       </c>
       <c r="C63" s="3" t="s">
-        <v>665</v>
+        <v>659</v>
       </c>
     </row>
     <row r="64" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B64" s="3" t="s">
-        <v>666</v>
+        <v>660</v>
       </c>
       <c r="C64" s="3" t="s">
-        <v>667</v>
+        <v>661</v>
       </c>
     </row>
     <row r="65" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B65" s="3" t="s">
-        <v>668</v>
+        <v>662</v>
       </c>
       <c r="C65" s="3" t="s">
-        <v>669</v>
+        <v>663</v>
       </c>
     </row>
     <row r="66" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B66" s="3" t="s">
-        <v>670</v>
+        <v>664</v>
       </c>
       <c r="C66" s="3" t="s">
-        <v>671</v>
+        <v>665</v>
       </c>
     </row>
     <row r="67" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B67" s="3" t="s">
-        <v>672</v>
+        <v>666</v>
       </c>
       <c r="C67" s="3" t="s">
-        <v>673</v>
+        <v>667</v>
       </c>
     </row>
     <row r="68" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B68" s="3" t="s">
-        <v>674</v>
+        <v>668</v>
       </c>
       <c r="C68" s="3" t="s">
-        <v>675</v>
+        <v>669</v>
       </c>
     </row>
     <row r="69" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B69" s="3" t="s">
-        <v>676</v>
+        <v>670</v>
       </c>
       <c r="C69" s="3" t="s">
-        <v>677</v>
+        <v>671</v>
       </c>
     </row>
     <row r="70" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B70" s="3" t="s">
-        <v>678</v>
+        <v>672</v>
       </c>
       <c r="C70" s="3" t="s">
-        <v>679</v>
+        <v>673</v>
       </c>
     </row>
     <row r="71" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B71" s="3" t="s">
-        <v>680</v>
+        <v>674</v>
       </c>
       <c r="C71" s="3" t="s">
-        <v>681</v>
+        <v>675</v>
       </c>
     </row>
     <row r="72" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B72" s="3" t="s">
-        <v>682</v>
+        <v>676</v>
       </c>
       <c r="C72" s="3" t="s">
-        <v>683</v>
+        <v>677</v>
       </c>
     </row>
     <row r="73" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B73" s="3" t="s">
-        <v>684</v>
+        <v>678</v>
       </c>
       <c r="C73" s="3" t="s">
-        <v>685</v>
+        <v>679</v>
       </c>
     </row>
     <row r="74" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B74" s="3" t="s">
-        <v>686</v>
+        <v>680</v>
       </c>
       <c r="C74" s="3" t="s">
-        <v>687</v>
+        <v>681</v>
       </c>
     </row>
     <row r="75" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B75" s="3" t="s">
-        <v>688</v>
+        <v>682</v>
       </c>
       <c r="C75" s="3" t="s">
-        <v>689</v>
+        <v>683</v>
       </c>
     </row>
     <row r="76" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B76" s="3" t="s">
-        <v>690</v>
+        <v>684</v>
       </c>
       <c r="C76" s="3" t="s">
-        <v>691</v>
+        <v>685</v>
       </c>
     </row>
     <row r="77" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B77" s="3" t="s">
-        <v>692</v>
+        <v>686</v>
       </c>
       <c r="C77" s="3" t="s">
-        <v>693</v>
+        <v>687</v>
       </c>
     </row>
     <row r="78" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B78" s="3" t="s">
-        <v>694</v>
+        <v>688</v>
       </c>
       <c r="C78" s="3" t="s">
-        <v>695</v>
+        <v>689</v>
       </c>
     </row>
     <row r="79" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B79" s="3" t="s">
-        <v>696</v>
+        <v>690</v>
       </c>
       <c r="C79" s="3" t="s">
-        <v>697</v>
+        <v>691</v>
       </c>
     </row>
     <row r="80" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B80" s="3" t="s">
-        <v>698</v>
+        <v>692</v>
       </c>
       <c r="C80" s="3" t="s">
-        <v>699</v>
+        <v>693</v>
       </c>
     </row>
     <row r="81" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B81" s="3" t="s">
-        <v>700</v>
+        <v>694</v>
       </c>
       <c r="C81" s="3" t="s">
-        <v>701</v>
+        <v>695</v>
       </c>
     </row>
     <row r="82" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B82" s="3" t="s">
-        <v>702</v>
+        <v>696</v>
       </c>
       <c r="C82" s="3" t="s">
-        <v>703</v>
+        <v>697</v>
       </c>
     </row>
     <row r="83" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B83" s="3" t="s">
-        <v>704</v>
+        <v>698</v>
       </c>
       <c r="C83" s="3" t="s">
-        <v>705</v>
+        <v>699</v>
       </c>
     </row>
     <row r="84" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B84" s="3" t="s">
-        <v>706</v>
+        <v>700</v>
       </c>
       <c r="C84" s="3" t="s">
-        <v>707</v>
+        <v>701</v>
       </c>
     </row>
     <row r="85" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B85" s="3" t="s">
-        <v>708</v>
+        <v>702</v>
       </c>
       <c r="C85" s="3" t="s">
-        <v>709</v>
+        <v>703</v>
       </c>
     </row>
     <row r="86" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B86" s="3" t="s">
-        <v>710</v>
+        <v>704</v>
       </c>
       <c r="C86" s="3" t="s">
-        <v>711</v>
+        <v>705</v>
       </c>
     </row>
     <row r="87" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B87" s="3" t="s">
-        <v>712</v>
+        <v>706</v>
       </c>
       <c r="C87" s="3" t="s">
-        <v>713</v>
+        <v>707</v>
       </c>
     </row>
     <row r="88" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B88" s="3" t="s">
-        <v>714</v>
+        <v>708</v>
       </c>
       <c r="C88" s="3" t="s">
-        <v>715</v>
+        <v>709</v>
       </c>
     </row>
     <row r="89" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B89" s="3" t="s">
-        <v>716</v>
+        <v>710</v>
       </c>
       <c r="C89" s="3" t="s">
-        <v>717</v>
+        <v>711</v>
       </c>
     </row>
     <row r="90" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B90" s="3" t="s">
-        <v>718</v>
+        <v>712</v>
       </c>
       <c r="C90" s="3" t="s">
-        <v>719</v>
+        <v>713</v>
       </c>
     </row>
     <row r="91" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B91" s="3" t="s">
-        <v>720</v>
+        <v>714</v>
       </c>
       <c r="C91" s="3" t="s">
-        <v>721</v>
+        <v>715</v>
       </c>
     </row>
     <row r="92" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B92" s="3" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="C92" s="3" t="s">
-        <v>723</v>
+        <v>717</v>
       </c>
     </row>
     <row r="93" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B93" s="3" t="s">
-        <v>724</v>
+        <v>718</v>
       </c>
       <c r="C93" s="3" t="s">
-        <v>725</v>
+        <v>719</v>
       </c>
     </row>
     <row r="94" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B94" s="3" t="s">
-        <v>726</v>
+        <v>720</v>
       </c>
       <c r="C94" s="3" t="s">
-        <v>727</v>
+        <v>721</v>
       </c>
     </row>
     <row r="95" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B95" s="3" t="s">
-        <v>728</v>
+        <v>722</v>
       </c>
       <c r="C95" s="3" t="s">
-        <v>729</v>
+        <v>723</v>
       </c>
     </row>
     <row r="96" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B96" s="3" t="s">
-        <v>730</v>
+        <v>724</v>
       </c>
       <c r="C96" s="3" t="s">
-        <v>731</v>
+        <v>725</v>
       </c>
     </row>
     <row r="97" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B97" s="3" t="s">
-        <v>732</v>
+        <v>726</v>
       </c>
       <c r="C97" s="3" t="s">
-        <v>733</v>
+        <v>727</v>
       </c>
     </row>
     <row r="98" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B98" s="3" t="s">
-        <v>734</v>
+        <v>728</v>
       </c>
       <c r="C98" s="3" t="s">
-        <v>735</v>
+        <v>729</v>
       </c>
     </row>
   </sheetData>
@@ -6432,226 +6417,226 @@
     </row>
     <row r="2" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B2" s="2" t="s">
-        <v>543</v>
+        <v>537</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>736</v>
+        <v>730</v>
       </c>
     </row>
     <row r="3" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B3" s="2" t="s">
-        <v>162</v>
+        <v>156</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>737</v>
+        <v>731</v>
       </c>
     </row>
     <row r="4" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B4" s="2" t="s">
-        <v>164</v>
+        <v>158</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>738</v>
+        <v>732</v>
       </c>
     </row>
     <row r="5" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B5" s="2" t="s">
-        <v>166</v>
+        <v>160</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>739</v>
+        <v>733</v>
       </c>
     </row>
     <row r="6" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B6" s="2" t="s">
-        <v>168</v>
+        <v>162</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>740</v>
+        <v>734</v>
       </c>
     </row>
     <row r="7" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B7" s="2" t="s">
-        <v>170</v>
+        <v>164</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>738</v>
+        <v>732</v>
       </c>
     </row>
     <row r="8" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B8" s="2" t="s">
-        <v>565</v>
+        <v>559</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>741</v>
+        <v>735</v>
       </c>
     </row>
     <row r="9" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B9" s="2" t="s">
-        <v>573</v>
+        <v>567</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>742</v>
+        <v>736</v>
       </c>
     </row>
     <row r="10" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B10" s="2" t="s">
-        <v>581</v>
+        <v>575</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>743</v>
+        <v>737</v>
       </c>
     </row>
     <row r="11" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B11" s="2" t="s">
-        <v>583</v>
+        <v>577</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>744</v>
+        <v>738</v>
       </c>
     </row>
     <row r="12" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B12" s="2" t="s">
-        <v>589</v>
+        <v>583</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>745</v>
+        <v>739</v>
       </c>
     </row>
     <row r="13" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B13" s="2" t="s">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>746</v>
+        <v>740</v>
       </c>
     </row>
     <row r="14" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B14" s="2" t="s">
-        <v>592</v>
+        <v>586</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>747</v>
+        <v>741</v>
       </c>
     </row>
     <row r="15" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B15" s="2" t="s">
-        <v>594</v>
+        <v>588</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>747</v>
+        <v>741</v>
       </c>
     </row>
     <row r="16" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B16" s="2" t="s">
-        <v>596</v>
+        <v>590</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>747</v>
+        <v>741</v>
       </c>
     </row>
     <row r="17" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B17" s="2" t="s">
-        <v>598</v>
+        <v>592</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>747</v>
+        <v>741</v>
       </c>
     </row>
     <row r="18" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B18" s="2" t="s">
-        <v>600</v>
+        <v>594</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>747</v>
+        <v>741</v>
       </c>
     </row>
     <row r="19" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B19" s="2" t="s">
-        <v>602</v>
+        <v>596</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>748</v>
+        <v>742</v>
       </c>
     </row>
     <row r="20" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B20" s="2" t="s">
-        <v>604</v>
+        <v>598</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>749</v>
+        <v>743</v>
       </c>
     </row>
     <row r="21" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B21" s="2" t="s">
-        <v>750</v>
+        <v>744</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>751</v>
+        <v>745</v>
       </c>
     </row>
     <row r="22" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B22" s="2" t="s">
-        <v>610</v>
+        <v>604</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>752</v>
+        <v>746</v>
       </c>
     </row>
     <row r="23" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B23" s="2" t="s">
-        <v>632</v>
+        <v>626</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>753</v>
+        <v>747</v>
       </c>
     </row>
     <row r="24" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B24" s="2" t="s">
-        <v>754</v>
+        <v>748</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>755</v>
+        <v>749</v>
       </c>
     </row>
     <row r="25" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B25" s="2" t="s">
-        <v>756</v>
+        <v>750</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>757</v>
+        <v>751</v>
       </c>
     </row>
     <row r="26" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B26" s="2" t="s">
-        <v>616</v>
+        <v>610</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>758</v>
+        <v>752</v>
       </c>
     </row>
     <row r="27" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B27" s="2" t="s">
-        <v>618</v>
+        <v>612</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>759</v>
+        <v>753</v>
       </c>
     </row>
     <row r="28" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B28" s="2" t="s">
-        <v>620</v>
+        <v>614</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>760</v>
+        <v>754</v>
       </c>
     </row>
     <row r="29" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B29" s="2" t="s">
-        <v>622</v>
+        <v>616</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>761</v>
+        <v>755</v>
       </c>
     </row>
     <row r="30" spans="2:3" x14ac:dyDescent="0.25">
@@ -6659,191 +6644,191 @@
         <v>6</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>762</v>
+        <v>756</v>
       </c>
     </row>
     <row r="31" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B31" s="2" t="s">
-        <v>624</v>
+        <v>618</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>763</v>
+        <v>757</v>
       </c>
     </row>
     <row r="32" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B32" s="2" t="s">
-        <v>626</v>
+        <v>620</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>764</v>
+        <v>758</v>
       </c>
     </row>
     <row r="33" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B33" s="2" t="s">
-        <v>628</v>
+        <v>622</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>765</v>
+        <v>759</v>
       </c>
     </row>
     <row r="34" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B34" s="2" t="s">
-        <v>630</v>
+        <v>624</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>766</v>
+        <v>760</v>
       </c>
     </row>
     <row r="35" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B35" s="2" t="s">
-        <v>654</v>
+        <v>648</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>767</v>
+        <v>761</v>
       </c>
     </row>
     <row r="36" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B36" s="2" t="s">
-        <v>634</v>
+        <v>628</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>768</v>
+        <v>762</v>
       </c>
     </row>
     <row r="37" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B37" s="2" t="s">
-        <v>636</v>
+        <v>630</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>769</v>
+        <v>763</v>
       </c>
     </row>
     <row r="38" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B38" s="2" t="s">
-        <v>638</v>
+        <v>632</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>770</v>
+        <v>764</v>
       </c>
     </row>
     <row r="39" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B39" s="2" t="s">
-        <v>640</v>
+        <v>634</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>771</v>
+        <v>765</v>
       </c>
     </row>
     <row r="40" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B40" s="2" t="s">
-        <v>642</v>
+        <v>636</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>772</v>
+        <v>766</v>
       </c>
     </row>
     <row r="41" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B41" s="2" t="s">
-        <v>644</v>
+        <v>638</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>773</v>
+        <v>767</v>
       </c>
     </row>
     <row r="42" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B42" s="2" t="s">
-        <v>646</v>
+        <v>640</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>774</v>
+        <v>768</v>
       </c>
     </row>
     <row r="43" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B43" s="2" t="s">
-        <v>648</v>
+        <v>642</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>775</v>
+        <v>769</v>
       </c>
     </row>
     <row r="44" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B44" s="2" t="s">
-        <v>650</v>
+        <v>644</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>776</v>
+        <v>770</v>
       </c>
     </row>
     <row r="45" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B45" s="2" t="s">
-        <v>652</v>
+        <v>646</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>752</v>
+        <v>746</v>
       </c>
     </row>
     <row r="46" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B46" s="2" t="s">
-        <v>656</v>
+        <v>650</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>777</v>
+        <v>771</v>
       </c>
     </row>
     <row r="47" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B47" s="2" t="s">
-        <v>778</v>
+        <v>772</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>779</v>
+        <v>773</v>
       </c>
     </row>
     <row r="48" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B48" s="2" t="s">
-        <v>488</v>
+        <v>482</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>780</v>
+        <v>774</v>
       </c>
     </row>
     <row r="49" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B49" s="2" t="s">
-        <v>490</v>
+        <v>484</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>781</v>
+        <v>775</v>
       </c>
     </row>
     <row r="50" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B50" s="2" t="s">
-        <v>492</v>
+        <v>486</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>782</v>
+        <v>776</v>
       </c>
     </row>
     <row r="51" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B51" s="2" t="s">
-        <v>494</v>
+        <v>488</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>783</v>
+        <v>777</v>
       </c>
     </row>
     <row r="52" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B52" s="2" t="s">
-        <v>496</v>
+        <v>490</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>784</v>
+        <v>778</v>
       </c>
     </row>
     <row r="53" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B53" s="2" t="s">
-        <v>785</v>
+        <v>779</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>786</v>
+        <v>780</v>
       </c>
     </row>
   </sheetData>
@@ -6867,242 +6852,242 @@
     </row>
     <row r="2" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B2" s="1" t="s">
-        <v>787</v>
+        <v>781</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>788</v>
+        <v>782</v>
       </c>
     </row>
     <row r="3" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B3" s="1" t="s">
-        <v>563</v>
+        <v>557</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>789</v>
+        <v>783</v>
       </c>
     </row>
     <row r="4" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B4" s="1" t="s">
-        <v>790</v>
+        <v>784</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>737</v>
+        <v>731</v>
       </c>
     </row>
     <row r="5" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B5" s="1" t="s">
-        <v>791</v>
+        <v>785</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>761</v>
+        <v>755</v>
       </c>
     </row>
     <row r="6" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B6" s="1" t="s">
-        <v>547</v>
+        <v>541</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>792</v>
+        <v>786</v>
       </c>
     </row>
     <row r="7" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B7" s="1" t="s">
-        <v>549</v>
+        <v>543</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>793</v>
+        <v>787</v>
       </c>
     </row>
     <row r="8" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B8" s="1" t="s">
-        <v>551</v>
+        <v>545</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>794</v>
+        <v>788</v>
       </c>
     </row>
     <row r="9" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B9" s="1" t="s">
-        <v>553</v>
+        <v>547</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>795</v>
+        <v>789</v>
       </c>
     </row>
     <row r="10" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B10" s="1" t="s">
-        <v>555</v>
+        <v>549</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>796</v>
+        <v>790</v>
       </c>
     </row>
     <row r="11" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B11" s="1" t="s">
-        <v>557</v>
+        <v>551</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>797</v>
+        <v>791</v>
       </c>
     </row>
     <row r="12" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B12" s="1" t="s">
-        <v>559</v>
+        <v>553</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>798</v>
+        <v>792</v>
       </c>
     </row>
     <row r="13" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B13" s="1" t="s">
-        <v>561</v>
+        <v>555</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>799</v>
+        <v>793</v>
       </c>
     </row>
     <row r="14" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B14" s="1" t="s">
-        <v>587</v>
+        <v>581</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>800</v>
+        <v>794</v>
       </c>
     </row>
     <row r="15" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B15" s="1" t="s">
-        <v>571</v>
+        <v>565</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>739</v>
+        <v>733</v>
       </c>
     </row>
     <row r="16" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B16" s="1" t="s">
-        <v>573</v>
+        <v>567</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>738</v>
+        <v>732</v>
       </c>
     </row>
     <row r="17" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B17" s="1" t="s">
-        <v>581</v>
+        <v>575</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>740</v>
+        <v>734</v>
       </c>
     </row>
     <row r="18" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B18" s="1" t="s">
-        <v>583</v>
+        <v>577</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>801</v>
+        <v>795</v>
       </c>
     </row>
     <row r="19" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B19" s="1" t="s">
-        <v>585</v>
+        <v>579</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>789</v>
+        <v>783</v>
       </c>
     </row>
     <row r="20" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B20" s="1" t="s">
-        <v>802</v>
+        <v>796</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>803</v>
+        <v>797</v>
       </c>
     </row>
     <row r="21" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B21" s="1" t="s">
-        <v>606</v>
+        <v>600</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>804</v>
+        <v>798</v>
       </c>
     </row>
     <row r="22" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B22" s="1" t="s">
-        <v>608</v>
+        <v>602</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>805</v>
+        <v>799</v>
       </c>
     </row>
     <row r="23" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B23" s="1" t="s">
-        <v>612</v>
+        <v>606</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>806</v>
+        <v>800</v>
       </c>
     </row>
     <row r="24" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B24" s="1" t="s">
-        <v>807</v>
+        <v>801</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>808</v>
+        <v>802</v>
       </c>
     </row>
     <row r="25" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B25" s="1" t="s">
-        <v>632</v>
+        <v>626</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>753</v>
+        <v>747</v>
       </c>
     </row>
     <row r="26" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B26" s="1" t="s">
-        <v>654</v>
+        <v>648</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>767</v>
+        <v>761</v>
       </c>
     </row>
     <row r="27" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B27" s="1" t="s">
-        <v>809</v>
+        <v>803</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>810</v>
+        <v>804</v>
       </c>
     </row>
     <row r="28" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B28" s="1" t="s">
-        <v>811</v>
+        <v>805</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>812</v>
+        <v>806</v>
       </c>
     </row>
     <row r="29" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B29" s="1" t="s">
-        <v>813</v>
+        <v>807</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>758</v>
+        <v>752</v>
       </c>
     </row>
     <row r="30" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B30" s="1" t="s">
-        <v>814</v>
+        <v>808</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>815</v>
+        <v>809</v>
       </c>
     </row>
     <row r="31" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B31" s="1" t="s">
-        <v>816</v>
+        <v>810</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>817</v>
+        <v>811</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/Editor/DataDic/Data.xlsx
+++ b/Assets/Editor/DataDic/Data.xlsx
@@ -5,7 +5,7 @@
   <workbookPr defaultThemeVersion="164011"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\MyGame\Rune Factory_hub\Assets\Editor\DataDic\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\MyGame\Rune Factory\Assets\Editor\DataDic\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="988" uniqueCount="821">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="987" uniqueCount="820">
   <si>
     <t>Key</t>
   </si>
@@ -285,9 +285,6 @@
   </si>
   <si>
     <t>科学研究室</t>
-  </si>
-  <si>
-    <t>547</t>
   </si>
   <si>
     <t>商店</t>
@@ -2883,58 +2880,58 @@
     </row>
     <row r="2" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B2" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="C2" s="4" t="s">
         <v>96</v>
-      </c>
-      <c r="C2" s="4" t="s">
-        <v>97</v>
       </c>
     </row>
     <row r="3" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B3" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="C3" s="4" t="s">
         <v>98</v>
-      </c>
-      <c r="C3" s="4" t="s">
-        <v>99</v>
       </c>
     </row>
     <row r="4" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B4" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="C4" s="4" t="s">
         <v>100</v>
-      </c>
-      <c r="C4" s="4" t="s">
-        <v>101</v>
       </c>
     </row>
     <row r="5" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B5" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="C5" s="4" t="s">
         <v>102</v>
-      </c>
-      <c r="C5" s="4" t="s">
-        <v>103</v>
       </c>
     </row>
     <row r="6" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B6" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="C6" s="4" t="s">
         <v>104</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>105</v>
       </c>
     </row>
     <row r="7" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B7" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="C7" s="4" t="s">
         <v>106</v>
-      </c>
-      <c r="C7" s="4" t="s">
-        <v>107</v>
       </c>
     </row>
     <row r="8" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B8" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="C8" s="4" t="s">
         <v>108</v>
-      </c>
-      <c r="C8" s="4" t="s">
-        <v>109</v>
       </c>
     </row>
     <row r="9" spans="2:3" x14ac:dyDescent="0.25">
@@ -2942,143 +2939,143 @@
         <v>48</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="10" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B10" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="C10" s="4" t="s">
         <v>111</v>
-      </c>
-      <c r="C10" s="4" t="s">
-        <v>112</v>
       </c>
     </row>
     <row r="11" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B11" s="4" t="s">
+        <v>112</v>
+      </c>
+      <c r="C11" s="4" t="s">
         <v>113</v>
-      </c>
-      <c r="C11" s="4" t="s">
-        <v>114</v>
       </c>
     </row>
     <row r="12" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B12" s="4" t="s">
+        <v>114</v>
+      </c>
+      <c r="C12" s="4" t="s">
         <v>115</v>
-      </c>
-      <c r="C12" s="4" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="13" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B13" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="C13" s="4" t="s">
         <v>117</v>
-      </c>
-      <c r="C13" s="4" t="s">
-        <v>118</v>
       </c>
     </row>
     <row r="14" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B14" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="C14" s="4" t="s">
         <v>119</v>
-      </c>
-      <c r="C14" s="4" t="s">
-        <v>120</v>
       </c>
     </row>
     <row r="15" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B15" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="C15" s="4" t="s">
         <v>121</v>
-      </c>
-      <c r="C15" s="4" t="s">
-        <v>122</v>
       </c>
     </row>
     <row r="16" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B16" s="4" t="s">
+        <v>122</v>
+      </c>
+      <c r="C16" s="4" t="s">
         <v>123</v>
-      </c>
-      <c r="C16" s="4" t="s">
-        <v>124</v>
       </c>
     </row>
     <row r="17" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B17" s="4" t="s">
+        <v>124</v>
+      </c>
+      <c r="C17" s="4" t="s">
         <v>125</v>
-      </c>
-      <c r="C17" s="4" t="s">
-        <v>126</v>
       </c>
     </row>
     <row r="18" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B18" s="4" t="s">
+        <v>126</v>
+      </c>
+      <c r="C18" s="4" t="s">
         <v>127</v>
-      </c>
-      <c r="C18" s="4" t="s">
-        <v>128</v>
       </c>
     </row>
     <row r="19" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B19" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="C19" s="4" t="s">
         <v>129</v>
-      </c>
-      <c r="C19" s="4" t="s">
-        <v>130</v>
       </c>
     </row>
     <row r="20" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B20" s="4" t="s">
+        <v>130</v>
+      </c>
+      <c r="C20" s="4" t="s">
         <v>131</v>
-      </c>
-      <c r="C20" s="4" t="s">
-        <v>132</v>
       </c>
     </row>
     <row r="21" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B21" s="4" t="s">
+        <v>132</v>
+      </c>
+      <c r="C21" s="4" t="s">
         <v>133</v>
-      </c>
-      <c r="C21" s="4" t="s">
-        <v>134</v>
       </c>
     </row>
     <row r="22" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B22" s="4" t="s">
+        <v>134</v>
+      </c>
+      <c r="C22" s="4" t="s">
         <v>135</v>
-      </c>
-      <c r="C22" s="4" t="s">
-        <v>136</v>
       </c>
     </row>
     <row r="23" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B23" s="4" t="s">
+        <v>136</v>
+      </c>
+      <c r="C23" s="4" t="s">
         <v>137</v>
-      </c>
-      <c r="C23" s="4" t="s">
-        <v>138</v>
       </c>
     </row>
     <row r="24" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B24" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="C24" s="4" t="s">
         <v>139</v>
-      </c>
-      <c r="C24" s="4" t="s">
-        <v>140</v>
       </c>
     </row>
     <row r="25" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B25" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="C25" s="4" t="s">
         <v>141</v>
-      </c>
-      <c r="C25" s="4" t="s">
-        <v>142</v>
       </c>
     </row>
     <row r="26" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B26" s="4" t="s">
+        <v>142</v>
+      </c>
+      <c r="C26" s="4" t="s">
         <v>143</v>
-      </c>
-      <c r="C26" s="4" t="s">
-        <v>144</v>
       </c>
     </row>
     <row r="27" spans="2:3" x14ac:dyDescent="0.25">
@@ -3086,47 +3083,47 @@
         <v>39</v>
       </c>
       <c r="C27" s="4" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
     <row r="28" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B28" s="4" t="s">
+        <v>145</v>
+      </c>
+      <c r="C28" s="4" t="s">
         <v>146</v>
-      </c>
-      <c r="C28" s="4" t="s">
-        <v>147</v>
       </c>
     </row>
     <row r="29" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B29" s="4" t="s">
+        <v>147</v>
+      </c>
+      <c r="C29" s="4" t="s">
         <v>148</v>
-      </c>
-      <c r="C29" s="4" t="s">
-        <v>149</v>
       </c>
     </row>
     <row r="30" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B30" s="4" t="s">
+        <v>149</v>
+      </c>
+      <c r="C30" s="4" t="s">
         <v>150</v>
-      </c>
-      <c r="C30" s="4" t="s">
-        <v>151</v>
       </c>
     </row>
     <row r="31" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B31" s="4" t="s">
+        <v>151</v>
+      </c>
+      <c r="C31" s="4" t="s">
         <v>152</v>
-      </c>
-      <c r="C31" s="4" t="s">
-        <v>153</v>
       </c>
     </row>
     <row r="32" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B32" s="4" t="s">
+        <v>153</v>
+      </c>
+      <c r="C32" s="4" t="s">
         <v>154</v>
-      </c>
-      <c r="C32" s="4" t="s">
-        <v>155</v>
       </c>
     </row>
   </sheetData>
@@ -3176,7 +3173,7 @@
         <v>6</v>
       </c>
       <c r="G4" s="5" t="s">
-        <v>812</v>
+        <v>811</v>
       </c>
       <c r="I4" s="6" t="s">
         <v>14</v>
@@ -3196,7 +3193,7 @@
         <v>948</v>
       </c>
       <c r="G5" s="5" t="s">
-        <v>813</v>
+        <v>812</v>
       </c>
       <c r="I5" t="str">
         <f>VLOOKUP(I4,$B:$C,2,FALSE)</f>
@@ -3246,7 +3243,7 @@
         <v>11</v>
       </c>
       <c r="G7" s="5" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="I7" s="6" t="s">
         <v>14</v>
@@ -3258,7 +3255,7 @@
         <v>69</v>
       </c>
       <c r="L7" s="4" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="M7" s="4" t="s">
         <v>57</v>
@@ -3278,7 +3275,7 @@
         <v>13</v>
       </c>
       <c r="G8" s="5" t="s">
-        <v>818</v>
+        <v>817</v>
       </c>
       <c r="I8" s="4" t="str">
         <f>VLOOKUP(I7,$B:$C,2,FALSE)</f>
@@ -3358,7 +3355,7 @@
         <v>17</v>
       </c>
       <c r="G10" s="5" t="s">
-        <v>819</v>
+        <v>818</v>
       </c>
     </row>
     <row r="11" spans="2:15" x14ac:dyDescent="0.25">
@@ -3369,7 +3366,7 @@
         <v>19</v>
       </c>
       <c r="G11" s="5" t="s">
-        <v>820</v>
+        <v>819</v>
       </c>
     </row>
     <row r="12" spans="2:15" x14ac:dyDescent="0.25">
@@ -3420,10 +3417,10 @@
       </c>
       <c r="F14" s="4"/>
       <c r="G14" s="5" t="s">
-        <v>820</v>
+        <v>819</v>
       </c>
       <c r="I14" s="4" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="J14" s="4" t="s">
         <v>57</v>
@@ -3444,7 +3441,7 @@
       </c>
       <c r="F15" s="4"/>
       <c r="G15" s="5" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
       <c r="H15" s="4"/>
       <c r="I15" s="4" t="str">
@@ -3504,7 +3501,7 @@
         <v>29</v>
       </c>
       <c r="G17" s="5" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
       <c r="I17" s="4" t="s">
         <v>57</v>
@@ -3527,7 +3524,7 @@
         <v>30</v>
       </c>
       <c r="G18" s="5" t="s">
-        <v>817</v>
+        <v>816</v>
       </c>
       <c r="I18" s="4" t="str">
         <f>VLOOKUP(I17,$B:$C,2,FALSE)</f>
@@ -3847,18 +3844,18 @@
     </row>
     <row r="51" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B51" s="4" t="s">
-        <v>88</v>
-      </c>
-      <c r="C51" s="4" t="s">
         <v>87</v>
+      </c>
+      <c r="C51" s="4">
+        <v>547</v>
       </c>
     </row>
     <row r="52" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B52" s="4" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C52" s="4" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="53" spans="2:3" x14ac:dyDescent="0.25">
@@ -3866,7 +3863,7 @@
         <v>18</v>
       </c>
       <c r="C53" s="4" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="54" spans="2:3" x14ac:dyDescent="0.25">
@@ -3874,15 +3871,15 @@
         <v>18</v>
       </c>
       <c r="C54" s="4" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="55" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B55" s="4" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C55" s="4" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="56" spans="2:3" x14ac:dyDescent="0.25">
@@ -3890,7 +3887,7 @@
         <v>18</v>
       </c>
       <c r="C56" s="4" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
   </sheetData>
@@ -3915,106 +3912,106 @@
     </row>
     <row r="2" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B2" s="4" t="s">
+        <v>155</v>
+      </c>
+      <c r="C2" s="4" t="s">
         <v>156</v>
-      </c>
-      <c r="C2" s="4" t="s">
-        <v>157</v>
       </c>
     </row>
     <row r="3" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B3" s="4" t="s">
+        <v>157</v>
+      </c>
+      <c r="C3" s="4" t="s">
         <v>158</v>
-      </c>
-      <c r="C3" s="4" t="s">
-        <v>159</v>
       </c>
     </row>
     <row r="4" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B4" s="4" t="s">
+        <v>159</v>
+      </c>
+      <c r="C4" s="4" t="s">
         <v>160</v>
-      </c>
-      <c r="C4" s="4" t="s">
-        <v>161</v>
       </c>
     </row>
     <row r="5" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B5" s="4" t="s">
+        <v>161</v>
+      </c>
+      <c r="C5" s="4" t="s">
         <v>162</v>
-      </c>
-      <c r="C5" s="4" t="s">
-        <v>163</v>
       </c>
     </row>
     <row r="6" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B6" s="4" t="s">
+        <v>163</v>
+      </c>
+      <c r="C6" s="4" t="s">
         <v>164</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="7" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B7" s="4" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
     </row>
     <row r="8" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B8" s="4" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
     </row>
     <row r="9" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B9" s="4" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
     </row>
     <row r="10" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B10" s="4" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="11" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B11" s="4" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
     </row>
     <row r="12" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B12" s="4" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
     </row>
     <row r="13" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B13" s="4" t="s">
+        <v>170</v>
+      </c>
+      <c r="C13" s="4" t="s">
         <v>171</v>
-      </c>
-      <c r="C13" s="4" t="s">
-        <v>172</v>
       </c>
     </row>
     <row r="14" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B14" s="4" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="15" spans="2:3" x14ac:dyDescent="0.25">
@@ -4022,508 +4019,508 @@
         <v>48</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="16" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B16" s="4" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="17" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B17" s="4" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
     <row r="18" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B18" s="4" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="19" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B19" s="4" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="20" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B20" s="4" t="s">
+        <v>178</v>
+      </c>
+      <c r="C20" s="4" t="s">
         <v>179</v>
-      </c>
-      <c r="C20" s="4" t="s">
-        <v>180</v>
       </c>
     </row>
     <row r="21" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B21" s="4" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="22" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B22" s="4" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="C22" s="4" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="23" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B23" s="4" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C23" s="4" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="24" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B24" s="4" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C24" s="4" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
     </row>
     <row r="25" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B25" s="4" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C25" s="4" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="26" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B26" s="4" t="s">
+        <v>185</v>
+      </c>
+      <c r="C26" s="4" t="s">
         <v>186</v>
-      </c>
-      <c r="C26" s="4" t="s">
-        <v>187</v>
       </c>
     </row>
     <row r="27" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B27" s="4" t="s">
+        <v>187</v>
+      </c>
+      <c r="C27" s="4" t="s">
         <v>188</v>
-      </c>
-      <c r="C27" s="4" t="s">
-        <v>189</v>
       </c>
     </row>
     <row r="28" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B28" s="4" t="s">
+        <v>189</v>
+      </c>
+      <c r="C28" s="4" t="s">
         <v>190</v>
-      </c>
-      <c r="C28" s="4" t="s">
-        <v>191</v>
       </c>
     </row>
     <row r="29" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B29" s="4" t="s">
+        <v>191</v>
+      </c>
+      <c r="C29" s="4" t="s">
         <v>192</v>
-      </c>
-      <c r="C29" s="4" t="s">
-        <v>193</v>
       </c>
     </row>
     <row r="30" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B30" s="4" t="s">
+        <v>193</v>
+      </c>
+      <c r="C30" s="4" t="s">
         <v>194</v>
-      </c>
-      <c r="C30" s="4" t="s">
-        <v>195</v>
       </c>
     </row>
     <row r="31" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B31" s="4" t="s">
+        <v>195</v>
+      </c>
+      <c r="C31" s="4" t="s">
         <v>196</v>
-      </c>
-      <c r="C31" s="4" t="s">
-        <v>197</v>
       </c>
     </row>
     <row r="32" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B32" s="4" t="s">
+        <v>197</v>
+      </c>
+      <c r="C32" s="4" t="s">
         <v>198</v>
-      </c>
-      <c r="C32" s="4" t="s">
-        <v>199</v>
       </c>
     </row>
     <row r="33" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B33" s="4" t="s">
+        <v>199</v>
+      </c>
+      <c r="C33" s="4" t="s">
         <v>200</v>
-      </c>
-      <c r="C33" s="4" t="s">
-        <v>201</v>
       </c>
     </row>
     <row r="34" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B34" s="4" t="s">
+        <v>201</v>
+      </c>
+      <c r="C34" s="4" t="s">
         <v>202</v>
-      </c>
-      <c r="C34" s="4" t="s">
-        <v>203</v>
       </c>
     </row>
     <row r="35" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B35" s="4" t="s">
+        <v>203</v>
+      </c>
+      <c r="C35" s="4" t="s">
         <v>204</v>
-      </c>
-      <c r="C35" s="4" t="s">
-        <v>205</v>
       </c>
     </row>
     <row r="36" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B36" s="4" t="s">
+        <v>205</v>
+      </c>
+      <c r="C36" s="4" t="s">
         <v>206</v>
-      </c>
-      <c r="C36" s="4" t="s">
-        <v>207</v>
       </c>
     </row>
     <row r="37" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B37" s="4" t="s">
+        <v>207</v>
+      </c>
+      <c r="C37" s="4" t="s">
         <v>208</v>
-      </c>
-      <c r="C37" s="4" t="s">
-        <v>209</v>
       </c>
     </row>
     <row r="38" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B38" s="4" t="s">
+        <v>209</v>
+      </c>
+      <c r="C38" s="4" t="s">
         <v>210</v>
-      </c>
-      <c r="C38" s="4" t="s">
-        <v>211</v>
       </c>
     </row>
     <row r="39" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B39" s="4" t="s">
+        <v>211</v>
+      </c>
+      <c r="C39" s="4" t="s">
         <v>212</v>
-      </c>
-      <c r="C39" s="4" t="s">
-        <v>213</v>
       </c>
     </row>
     <row r="40" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B40" s="4" t="s">
+        <v>213</v>
+      </c>
+      <c r="C40" s="4" t="s">
         <v>214</v>
-      </c>
-      <c r="C40" s="4" t="s">
-        <v>215</v>
       </c>
     </row>
     <row r="41" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B41" s="4" t="s">
+        <v>215</v>
+      </c>
+      <c r="C41" s="4" t="s">
         <v>216</v>
-      </c>
-      <c r="C41" s="4" t="s">
-        <v>217</v>
       </c>
     </row>
     <row r="42" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B42" s="4" t="s">
+        <v>217</v>
+      </c>
+      <c r="C42" s="4" t="s">
         <v>218</v>
-      </c>
-      <c r="C42" s="4" t="s">
-        <v>219</v>
       </c>
     </row>
     <row r="43" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B43" s="4" t="s">
+        <v>219</v>
+      </c>
+      <c r="C43" s="4" t="s">
         <v>220</v>
-      </c>
-      <c r="C43" s="4" t="s">
-        <v>221</v>
       </c>
     </row>
     <row r="44" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B44" s="4" t="s">
+        <v>221</v>
+      </c>
+      <c r="C44" s="4" t="s">
         <v>222</v>
-      </c>
-      <c r="C44" s="4" t="s">
-        <v>223</v>
       </c>
     </row>
     <row r="45" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B45" s="4" t="s">
+        <v>223</v>
+      </c>
+      <c r="C45" s="4" t="s">
         <v>224</v>
-      </c>
-      <c r="C45" s="4" t="s">
-        <v>225</v>
       </c>
     </row>
     <row r="46" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B46" s="4" t="s">
+        <v>225</v>
+      </c>
+      <c r="C46" s="4" t="s">
         <v>226</v>
-      </c>
-      <c r="C46" s="4" t="s">
-        <v>227</v>
       </c>
     </row>
     <row r="47" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B47" s="4" t="s">
+        <v>227</v>
+      </c>
+      <c r="C47" s="4" t="s">
         <v>228</v>
-      </c>
-      <c r="C47" s="4" t="s">
-        <v>229</v>
       </c>
     </row>
     <row r="48" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B48" s="4" t="s">
+        <v>229</v>
+      </c>
+      <c r="C48" s="4" t="s">
         <v>230</v>
-      </c>
-      <c r="C48" s="4" t="s">
-        <v>231</v>
       </c>
     </row>
     <row r="49" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B49" s="4" t="s">
+        <v>231</v>
+      </c>
+      <c r="C49" s="4" t="s">
         <v>232</v>
-      </c>
-      <c r="C49" s="4" t="s">
-        <v>233</v>
       </c>
     </row>
     <row r="50" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B50" s="4" t="s">
+        <v>233</v>
+      </c>
+      <c r="C50" s="4" t="s">
         <v>234</v>
-      </c>
-      <c r="C50" s="4" t="s">
-        <v>235</v>
       </c>
     </row>
     <row r="51" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B51" s="4" t="s">
+        <v>235</v>
+      </c>
+      <c r="C51" s="4" t="s">
         <v>236</v>
-      </c>
-      <c r="C51" s="4" t="s">
-        <v>237</v>
       </c>
     </row>
     <row r="52" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B52" s="4" t="s">
+        <v>237</v>
+      </c>
+      <c r="C52" s="4" t="s">
         <v>238</v>
-      </c>
-      <c r="C52" s="4" t="s">
-        <v>239</v>
       </c>
     </row>
     <row r="53" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B53" s="4" t="s">
+        <v>239</v>
+      </c>
+      <c r="C53" s="4" t="s">
         <v>240</v>
-      </c>
-      <c r="C53" s="4" t="s">
-        <v>241</v>
       </c>
     </row>
     <row r="54" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B54" s="4" t="s">
+        <v>241</v>
+      </c>
+      <c r="C54" s="4" t="s">
         <v>242</v>
-      </c>
-      <c r="C54" s="4" t="s">
-        <v>243</v>
       </c>
     </row>
     <row r="55" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B55" s="4" t="s">
+        <v>243</v>
+      </c>
+      <c r="C55" s="4" t="s">
         <v>244</v>
-      </c>
-      <c r="C55" s="4" t="s">
-        <v>245</v>
       </c>
     </row>
     <row r="56" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B56" s="4" t="s">
+        <v>245</v>
+      </c>
+      <c r="C56" s="4" t="s">
         <v>246</v>
-      </c>
-      <c r="C56" s="4" t="s">
-        <v>247</v>
       </c>
     </row>
     <row r="57" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B57" s="4" t="s">
+        <v>247</v>
+      </c>
+      <c r="C57" s="4" t="s">
         <v>248</v>
-      </c>
-      <c r="C57" s="4" t="s">
-        <v>249</v>
       </c>
     </row>
     <row r="58" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B58" s="4" t="s">
+        <v>249</v>
+      </c>
+      <c r="C58" s="4" t="s">
         <v>250</v>
-      </c>
-      <c r="C58" s="4" t="s">
-        <v>251</v>
       </c>
     </row>
     <row r="59" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B59" s="4" t="s">
+        <v>251</v>
+      </c>
+      <c r="C59" s="4" t="s">
         <v>252</v>
-      </c>
-      <c r="C59" s="4" t="s">
-        <v>253</v>
       </c>
     </row>
     <row r="60" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B60" s="4" t="s">
+        <v>253</v>
+      </c>
+      <c r="C60" s="4" t="s">
         <v>254</v>
-      </c>
-      <c r="C60" s="4" t="s">
-        <v>255</v>
       </c>
     </row>
     <row r="61" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B61" s="4" t="s">
+        <v>255</v>
+      </c>
+      <c r="C61" s="4" t="s">
         <v>256</v>
-      </c>
-      <c r="C61" s="4" t="s">
-        <v>257</v>
       </c>
     </row>
     <row r="62" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B62" s="4" t="s">
+        <v>257</v>
+      </c>
+      <c r="C62" s="4" t="s">
         <v>258</v>
-      </c>
-      <c r="C62" s="4" t="s">
-        <v>259</v>
       </c>
     </row>
     <row r="63" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B63" s="4" t="s">
+        <v>259</v>
+      </c>
+      <c r="C63" s="4" t="s">
         <v>260</v>
-      </c>
-      <c r="C63" s="4" t="s">
-        <v>261</v>
       </c>
     </row>
     <row r="64" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B64" s="4" t="s">
+        <v>261</v>
+      </c>
+      <c r="C64" s="4" t="s">
         <v>262</v>
-      </c>
-      <c r="C64" s="4" t="s">
-        <v>263</v>
       </c>
     </row>
     <row r="65" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B65" s="4" t="s">
+        <v>263</v>
+      </c>
+      <c r="C65" s="4" t="s">
         <v>264</v>
-      </c>
-      <c r="C65" s="4" t="s">
-        <v>265</v>
       </c>
     </row>
     <row r="66" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B66" s="4" t="s">
+        <v>265</v>
+      </c>
+      <c r="C66" s="4" t="s">
         <v>266</v>
-      </c>
-      <c r="C66" s="4" t="s">
-        <v>267</v>
       </c>
     </row>
     <row r="67" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B67" s="4" t="s">
+        <v>267</v>
+      </c>
+      <c r="C67" s="4" t="s">
         <v>268</v>
-      </c>
-      <c r="C67" s="4" t="s">
-        <v>269</v>
       </c>
     </row>
     <row r="68" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B68" s="4" t="s">
+        <v>269</v>
+      </c>
+      <c r="C68" s="4" t="s">
         <v>270</v>
-      </c>
-      <c r="C68" s="4" t="s">
-        <v>271</v>
       </c>
     </row>
     <row r="69" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B69" s="4" t="s">
+        <v>271</v>
+      </c>
+      <c r="C69" s="4" t="s">
         <v>272</v>
-      </c>
-      <c r="C69" s="4" t="s">
-        <v>273</v>
       </c>
     </row>
     <row r="70" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B70" s="4" t="s">
+        <v>273</v>
+      </c>
+      <c r="C70" s="4" t="s">
         <v>274</v>
-      </c>
-      <c r="C70" s="4" t="s">
-        <v>275</v>
       </c>
     </row>
     <row r="71" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B71" s="4" t="s">
+        <v>275</v>
+      </c>
+      <c r="C71" s="4" t="s">
         <v>276</v>
-      </c>
-      <c r="C71" s="4" t="s">
-        <v>277</v>
       </c>
     </row>
     <row r="72" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B72" s="4" t="s">
+        <v>277</v>
+      </c>
+      <c r="C72" s="4" t="s">
         <v>278</v>
-      </c>
-      <c r="C72" s="4" t="s">
-        <v>279</v>
       </c>
     </row>
     <row r="73" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B73" s="4" t="s">
+        <v>279</v>
+      </c>
+      <c r="C73" s="4" t="s">
         <v>280</v>
-      </c>
-      <c r="C73" s="4" t="s">
-        <v>281</v>
       </c>
     </row>
     <row r="74" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B74" s="4" t="s">
+        <v>281</v>
+      </c>
+      <c r="C74" s="4" t="s">
         <v>282</v>
-      </c>
-      <c r="C74" s="4" t="s">
-        <v>283</v>
       </c>
     </row>
     <row r="75" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B75" s="4" t="s">
+        <v>283</v>
+      </c>
+      <c r="C75" s="4" t="s">
         <v>284</v>
-      </c>
-      <c r="C75" s="4" t="s">
-        <v>285</v>
       </c>
     </row>
     <row r="76" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B76" s="4" t="s">
+        <v>285</v>
+      </c>
+      <c r="C76" s="4" t="s">
         <v>286</v>
-      </c>
-      <c r="C76" s="4" t="s">
-        <v>287</v>
       </c>
     </row>
     <row r="77" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B77" s="4" t="s">
+        <v>287</v>
+      </c>
+      <c r="C77" s="4" t="s">
         <v>288</v>
-      </c>
-      <c r="C77" s="4" t="s">
-        <v>289</v>
       </c>
     </row>
     <row r="78" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B78" s="4" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="C78" s="4" t="s">
         <v>46</v>
@@ -4531,183 +4528,183 @@
     </row>
     <row r="79" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B79" s="4" t="s">
+        <v>290</v>
+      </c>
+      <c r="C79" s="4" t="s">
         <v>291</v>
-      </c>
-      <c r="C79" s="4" t="s">
-        <v>292</v>
       </c>
     </row>
     <row r="80" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B80" s="4" t="s">
+        <v>292</v>
+      </c>
+      <c r="C80" s="4" t="s">
         <v>293</v>
-      </c>
-      <c r="C80" s="4" t="s">
-        <v>294</v>
       </c>
     </row>
     <row r="81" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B81" s="4" t="s">
+        <v>294</v>
+      </c>
+      <c r="C81" s="4" t="s">
         <v>295</v>
-      </c>
-      <c r="C81" s="4" t="s">
-        <v>296</v>
       </c>
     </row>
     <row r="82" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B82" s="4" t="s">
+        <v>296</v>
+      </c>
+      <c r="C82" s="4" t="s">
         <v>297</v>
-      </c>
-      <c r="C82" s="4" t="s">
-        <v>298</v>
       </c>
     </row>
     <row r="83" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B83" s="4" t="s">
+        <v>298</v>
+      </c>
+      <c r="C83" s="4" t="s">
         <v>299</v>
-      </c>
-      <c r="C83" s="4" t="s">
-        <v>300</v>
       </c>
     </row>
     <row r="84" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B84" s="4" t="s">
+        <v>300</v>
+      </c>
+      <c r="C84" s="4" t="s">
         <v>301</v>
-      </c>
-      <c r="C84" s="4" t="s">
-        <v>302</v>
       </c>
     </row>
     <row r="85" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B85" s="4" t="s">
+        <v>302</v>
+      </c>
+      <c r="C85" s="4" t="s">
         <v>303</v>
-      </c>
-      <c r="C85" s="4" t="s">
-        <v>304</v>
       </c>
     </row>
     <row r="86" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B86" s="4" t="s">
+        <v>304</v>
+      </c>
+      <c r="C86" s="4" t="s">
         <v>305</v>
-      </c>
-      <c r="C86" s="4" t="s">
-        <v>306</v>
       </c>
     </row>
     <row r="87" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B87" s="4" t="s">
+        <v>306</v>
+      </c>
+      <c r="C87" s="4" t="s">
         <v>307</v>
-      </c>
-      <c r="C87" s="4" t="s">
-        <v>308</v>
       </c>
     </row>
     <row r="88" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B88" s="4" t="s">
+        <v>308</v>
+      </c>
+      <c r="C88" s="4" t="s">
         <v>309</v>
-      </c>
-      <c r="C88" s="4" t="s">
-        <v>310</v>
       </c>
     </row>
     <row r="89" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B89" s="4" t="s">
+        <v>310</v>
+      </c>
+      <c r="C89" s="4" t="s">
         <v>311</v>
-      </c>
-      <c r="C89" s="4" t="s">
-        <v>312</v>
       </c>
     </row>
     <row r="90" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B90" s="4" t="s">
+        <v>312</v>
+      </c>
+      <c r="C90" s="4" t="s">
         <v>313</v>
-      </c>
-      <c r="C90" s="4" t="s">
-        <v>314</v>
       </c>
     </row>
     <row r="91" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B91" s="4" t="s">
+        <v>314</v>
+      </c>
+      <c r="C91" s="4" t="s">
         <v>315</v>
-      </c>
-      <c r="C91" s="4" t="s">
-        <v>316</v>
       </c>
     </row>
     <row r="92" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B92" s="4" t="s">
+        <v>316</v>
+      </c>
+      <c r="C92" s="4" t="s">
         <v>317</v>
-      </c>
-      <c r="C92" s="4" t="s">
-        <v>318</v>
       </c>
     </row>
     <row r="93" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B93" s="4" t="s">
+        <v>318</v>
+      </c>
+      <c r="C93" s="4" t="s">
         <v>319</v>
-      </c>
-      <c r="C93" s="4" t="s">
-        <v>320</v>
       </c>
     </row>
     <row r="94" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B94" s="4" t="s">
+        <v>320</v>
+      </c>
+      <c r="C94" s="4" t="s">
         <v>321</v>
-      </c>
-      <c r="C94" s="4" t="s">
-        <v>322</v>
       </c>
     </row>
     <row r="95" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B95" s="4" t="s">
+        <v>322</v>
+      </c>
+      <c r="C95" s="4" t="s">
         <v>323</v>
-      </c>
-      <c r="C95" s="4" t="s">
-        <v>324</v>
       </c>
     </row>
     <row r="96" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B96" s="4" t="s">
+        <v>324</v>
+      </c>
+      <c r="C96" s="4" t="s">
         <v>325</v>
-      </c>
-      <c r="C96" s="4" t="s">
-        <v>326</v>
       </c>
     </row>
     <row r="97" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B97" s="4" t="s">
+        <v>326</v>
+      </c>
+      <c r="C97" s="4" t="s">
         <v>327</v>
-      </c>
-      <c r="C97" s="4" t="s">
-        <v>328</v>
       </c>
     </row>
     <row r="98" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B98" s="4" t="s">
+        <v>328</v>
+      </c>
+      <c r="C98" s="4" t="s">
         <v>329</v>
-      </c>
-      <c r="C98" s="4" t="s">
-        <v>330</v>
       </c>
     </row>
     <row r="99" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B99" s="4" t="s">
+        <v>330</v>
+      </c>
+      <c r="C99" s="4" t="s">
         <v>331</v>
-      </c>
-      <c r="C99" s="4" t="s">
-        <v>332</v>
       </c>
     </row>
     <row r="100" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B100" s="4" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C100" s="4" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
     </row>
     <row r="101" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B101" s="4" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C101" s="4" t="s">
         <v>8</v>
@@ -4715,31 +4712,31 @@
     </row>
     <row r="102" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B102" s="4" t="s">
+        <v>333</v>
+      </c>
+      <c r="C102" s="4" t="s">
         <v>334</v>
-      </c>
-      <c r="C102" s="4" t="s">
-        <v>335</v>
       </c>
     </row>
     <row r="103" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B103" s="4" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C103" s="4" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
     </row>
     <row r="104" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B104" s="4" t="s">
+        <v>336</v>
+      </c>
+      <c r="C104" s="4" t="s">
         <v>337</v>
-      </c>
-      <c r="C104" s="4" t="s">
-        <v>338</v>
       </c>
     </row>
     <row r="105" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B105" s="4" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C105" s="4" t="s">
         <v>10</v>
@@ -4747,15 +4744,15 @@
     </row>
     <row r="106" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B106" s="4" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="C106" s="4" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
     </row>
     <row r="107" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B107" s="4" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="C107" s="4" t="s">
         <v>82</v>
@@ -4763,34 +4760,34 @@
     </row>
     <row r="108" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B108" s="4" t="s">
+        <v>340</v>
+      </c>
+      <c r="C108" s="4" t="s">
         <v>341</v>
-      </c>
-      <c r="C108" s="4" t="s">
-        <v>342</v>
       </c>
     </row>
     <row r="109" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B109" s="4" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C109" s="4" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
     </row>
     <row r="110" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B110" s="4" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="C110" s="4" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
     </row>
     <row r="111" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B111" s="4" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="C111" s="4" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
     </row>
     <row r="112" spans="2:3" x14ac:dyDescent="0.25">
@@ -4798,44 +4795,44 @@
         <v>39</v>
       </c>
       <c r="C112" s="4" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
     </row>
     <row r="113" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B113" s="4" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C113" s="4" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
     </row>
     <row r="114" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B114" s="4" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C114" s="4" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
     </row>
     <row r="115" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B115" s="4" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C115" s="4" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
     </row>
     <row r="116" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B116" s="4" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C116" s="4" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
     </row>
     <row r="117" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B117" s="4" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C117" s="4" t="s">
         <v>36</v>
@@ -4843,7 +4840,7 @@
     </row>
     <row r="118" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B118" s="4" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="C118" s="4" t="s">
         <v>23</v>
@@ -4851,450 +4848,450 @@
     </row>
     <row r="119" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B119" s="4" t="s">
+        <v>350</v>
+      </c>
+      <c r="C119" s="4" t="s">
         <v>351</v>
-      </c>
-      <c r="C119" s="4" t="s">
-        <v>352</v>
       </c>
     </row>
     <row r="120" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B120" s="4" t="s">
+        <v>352</v>
+      </c>
+      <c r="C120" s="4" t="s">
         <v>353</v>
-      </c>
-      <c r="C120" s="4" t="s">
-        <v>354</v>
       </c>
     </row>
     <row r="121" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B121" s="4" t="s">
+        <v>354</v>
+      </c>
+      <c r="C121" s="4" t="s">
         <v>355</v>
-      </c>
-      <c r="C121" s="4" t="s">
-        <v>356</v>
       </c>
     </row>
     <row r="122" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B122" s="4" t="s">
+        <v>356</v>
+      </c>
+      <c r="C122" s="4" t="s">
         <v>357</v>
-      </c>
-      <c r="C122" s="4" t="s">
-        <v>358</v>
       </c>
     </row>
     <row r="123" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B123" s="4" t="s">
+        <v>358</v>
+      </c>
+      <c r="C123" s="4" t="s">
         <v>359</v>
-      </c>
-      <c r="C123" s="4" t="s">
-        <v>360</v>
       </c>
     </row>
     <row r="124" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B124" s="4" t="s">
+        <v>360</v>
+      </c>
+      <c r="C124" s="4" t="s">
         <v>361</v>
-      </c>
-      <c r="C124" s="4" t="s">
-        <v>362</v>
       </c>
     </row>
     <row r="125" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B125" s="4" t="s">
+        <v>362</v>
+      </c>
+      <c r="C125" s="4" t="s">
         <v>363</v>
-      </c>
-      <c r="C125" s="4" t="s">
-        <v>364</v>
       </c>
     </row>
     <row r="126" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B126" s="4" t="s">
+        <v>364</v>
+      </c>
+      <c r="C126" s="4" t="s">
         <v>365</v>
-      </c>
-      <c r="C126" s="4" t="s">
-        <v>366</v>
       </c>
     </row>
     <row r="127" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B127" s="4" t="s">
+        <v>366</v>
+      </c>
+      <c r="C127" s="4" t="s">
         <v>367</v>
-      </c>
-      <c r="C127" s="4" t="s">
-        <v>368</v>
       </c>
     </row>
     <row r="128" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B128" s="4" t="s">
+        <v>368</v>
+      </c>
+      <c r="C128" s="4" t="s">
         <v>369</v>
-      </c>
-      <c r="C128" s="4" t="s">
-        <v>370</v>
       </c>
     </row>
     <row r="129" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B129" s="4" t="s">
+        <v>370</v>
+      </c>
+      <c r="C129" s="4" t="s">
         <v>371</v>
-      </c>
-      <c r="C129" s="4" t="s">
-        <v>372</v>
       </c>
     </row>
     <row r="130" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B130" s="4" t="s">
+        <v>372</v>
+      </c>
+      <c r="C130" s="4" t="s">
         <v>373</v>
-      </c>
-      <c r="C130" s="4" t="s">
-        <v>374</v>
       </c>
     </row>
     <row r="131" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B131" s="4" t="s">
+        <v>374</v>
+      </c>
+      <c r="C131" s="4" t="s">
         <v>375</v>
-      </c>
-      <c r="C131" s="4" t="s">
-        <v>376</v>
       </c>
     </row>
     <row r="132" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B132" s="4" t="s">
+        <v>376</v>
+      </c>
+      <c r="C132" s="4" t="s">
         <v>377</v>
-      </c>
-      <c r="C132" s="4" t="s">
-        <v>378</v>
       </c>
     </row>
     <row r="133" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B133" s="4" t="s">
+        <v>378</v>
+      </c>
+      <c r="C133" s="4" t="s">
         <v>379</v>
-      </c>
-      <c r="C133" s="4" t="s">
-        <v>380</v>
       </c>
     </row>
     <row r="134" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B134" s="4" t="s">
+        <v>380</v>
+      </c>
+      <c r="C134" s="4" t="s">
         <v>381</v>
-      </c>
-      <c r="C134" s="4" t="s">
-        <v>382</v>
       </c>
     </row>
     <row r="135" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B135" s="4" t="s">
+        <v>382</v>
+      </c>
+      <c r="C135" s="4" t="s">
         <v>383</v>
-      </c>
-      <c r="C135" s="4" t="s">
-        <v>384</v>
       </c>
     </row>
     <row r="136" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B136" s="4" t="s">
+        <v>384</v>
+      </c>
+      <c r="C136" s="4" t="s">
         <v>385</v>
-      </c>
-      <c r="C136" s="4" t="s">
-        <v>386</v>
       </c>
     </row>
     <row r="137" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B137" s="4" t="s">
+        <v>386</v>
+      </c>
+      <c r="C137" s="4" t="s">
         <v>387</v>
-      </c>
-      <c r="C137" s="4" t="s">
-        <v>388</v>
       </c>
     </row>
     <row r="138" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B138" s="4" t="s">
+        <v>388</v>
+      </c>
+      <c r="C138" s="4" t="s">
         <v>389</v>
-      </c>
-      <c r="C138" s="4" t="s">
-        <v>390</v>
       </c>
     </row>
     <row r="139" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B139" s="4" t="s">
+        <v>390</v>
+      </c>
+      <c r="C139" s="4" t="s">
         <v>391</v>
-      </c>
-      <c r="C139" s="4" t="s">
-        <v>392</v>
       </c>
     </row>
     <row r="140" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B140" s="4" t="s">
+        <v>392</v>
+      </c>
+      <c r="C140" s="4" t="s">
         <v>393</v>
-      </c>
-      <c r="C140" s="4" t="s">
-        <v>394</v>
       </c>
     </row>
     <row r="141" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B141" s="4" t="s">
+        <v>394</v>
+      </c>
+      <c r="C141" s="4" t="s">
         <v>395</v>
-      </c>
-      <c r="C141" s="4" t="s">
-        <v>396</v>
       </c>
     </row>
     <row r="142" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B142" s="4" t="s">
+        <v>396</v>
+      </c>
+      <c r="C142" s="4" t="s">
         <v>397</v>
-      </c>
-      <c r="C142" s="4" t="s">
-        <v>398</v>
       </c>
     </row>
     <row r="143" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B143" s="4" t="s">
+        <v>398</v>
+      </c>
+      <c r="C143" s="4" t="s">
         <v>399</v>
-      </c>
-      <c r="C143" s="4" t="s">
-        <v>400</v>
       </c>
     </row>
     <row r="144" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B144" s="4" t="s">
+        <v>400</v>
+      </c>
+      <c r="C144" s="4" t="s">
         <v>401</v>
-      </c>
-      <c r="C144" s="4" t="s">
-        <v>402</v>
       </c>
     </row>
     <row r="145" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B145" s="4" t="s">
+        <v>402</v>
+      </c>
+      <c r="C145" s="4" t="s">
         <v>403</v>
-      </c>
-      <c r="C145" s="4" t="s">
-        <v>404</v>
       </c>
     </row>
     <row r="146" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B146" s="4" t="s">
+        <v>404</v>
+      </c>
+      <c r="C146" s="4" t="s">
         <v>405</v>
-      </c>
-      <c r="C146" s="4" t="s">
-        <v>406</v>
       </c>
     </row>
     <row r="147" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B147" s="4" t="s">
+        <v>406</v>
+      </c>
+      <c r="C147" s="4" t="s">
         <v>407</v>
-      </c>
-      <c r="C147" s="4" t="s">
-        <v>408</v>
       </c>
     </row>
     <row r="148" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B148" s="4" t="s">
+        <v>408</v>
+      </c>
+      <c r="C148" s="4" t="s">
         <v>409</v>
-      </c>
-      <c r="C148" s="4" t="s">
-        <v>410</v>
       </c>
     </row>
     <row r="149" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B149" s="4" t="s">
+        <v>410</v>
+      </c>
+      <c r="C149" s="4" t="s">
         <v>411</v>
-      </c>
-      <c r="C149" s="4" t="s">
-        <v>412</v>
       </c>
     </row>
     <row r="150" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B150" s="4" t="s">
+        <v>412</v>
+      </c>
+      <c r="C150" s="4" t="s">
         <v>413</v>
-      </c>
-      <c r="C150" s="4" t="s">
-        <v>414</v>
       </c>
     </row>
     <row r="151" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B151" s="4" t="s">
+        <v>414</v>
+      </c>
+      <c r="C151" s="4" t="s">
         <v>415</v>
-      </c>
-      <c r="C151" s="4" t="s">
-        <v>416</v>
       </c>
     </row>
     <row r="152" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B152" s="4" t="s">
+        <v>416</v>
+      </c>
+      <c r="C152" s="4" t="s">
         <v>417</v>
-      </c>
-      <c r="C152" s="4" t="s">
-        <v>418</v>
       </c>
     </row>
     <row r="153" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B153" s="4" t="s">
+        <v>418</v>
+      </c>
+      <c r="C153" s="4" t="s">
         <v>419</v>
-      </c>
-      <c r="C153" s="4" t="s">
-        <v>420</v>
       </c>
     </row>
     <row r="154" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B154" s="4" t="s">
+        <v>420</v>
+      </c>
+      <c r="C154" s="4" t="s">
         <v>421</v>
-      </c>
-      <c r="C154" s="4" t="s">
-        <v>422</v>
       </c>
     </row>
     <row r="155" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B155" s="4" t="s">
+        <v>422</v>
+      </c>
+      <c r="C155" s="4" t="s">
         <v>423</v>
-      </c>
-      <c r="C155" s="4" t="s">
-        <v>424</v>
       </c>
     </row>
     <row r="156" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B156" s="4" t="s">
+        <v>424</v>
+      </c>
+      <c r="C156" s="4" t="s">
         <v>425</v>
-      </c>
-      <c r="C156" s="4" t="s">
-        <v>426</v>
       </c>
     </row>
     <row r="157" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B157" s="4" t="s">
+        <v>426</v>
+      </c>
+      <c r="C157" s="4" t="s">
         <v>427</v>
-      </c>
-      <c r="C157" s="4" t="s">
-        <v>428</v>
       </c>
     </row>
     <row r="158" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B158" s="4" t="s">
+        <v>428</v>
+      </c>
+      <c r="C158" s="4" t="s">
         <v>429</v>
-      </c>
-      <c r="C158" s="4" t="s">
-        <v>430</v>
       </c>
     </row>
     <row r="159" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B159" s="4" t="s">
+        <v>430</v>
+      </c>
+      <c r="C159" s="4" t="s">
         <v>431</v>
-      </c>
-      <c r="C159" s="4" t="s">
-        <v>432</v>
       </c>
     </row>
     <row r="160" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B160" s="4" t="s">
+        <v>432</v>
+      </c>
+      <c r="C160" s="4" t="s">
         <v>433</v>
-      </c>
-      <c r="C160" s="4" t="s">
-        <v>434</v>
       </c>
     </row>
     <row r="161" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B161" s="4" t="s">
+        <v>434</v>
+      </c>
+      <c r="C161" s="4" t="s">
         <v>435</v>
-      </c>
-      <c r="C161" s="4" t="s">
-        <v>436</v>
       </c>
     </row>
     <row r="162" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B162" s="4" t="s">
+        <v>436</v>
+      </c>
+      <c r="C162" s="4" t="s">
         <v>437</v>
-      </c>
-      <c r="C162" s="4" t="s">
-        <v>438</v>
       </c>
     </row>
     <row r="163" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B163" s="4" t="s">
+        <v>438</v>
+      </c>
+      <c r="C163" s="4" t="s">
         <v>439</v>
-      </c>
-      <c r="C163" s="4" t="s">
-        <v>440</v>
       </c>
     </row>
     <row r="164" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B164" s="4" t="s">
+        <v>440</v>
+      </c>
+      <c r="C164" s="4" t="s">
         <v>441</v>
-      </c>
-      <c r="C164" s="4" t="s">
-        <v>442</v>
       </c>
     </row>
     <row r="165" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B165" s="4" t="s">
+        <v>442</v>
+      </c>
+      <c r="C165" s="4" t="s">
         <v>443</v>
-      </c>
-      <c r="C165" s="4" t="s">
-        <v>444</v>
       </c>
     </row>
     <row r="166" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B166" s="4" t="s">
+        <v>444</v>
+      </c>
+      <c r="C166" s="4" t="s">
         <v>445</v>
-      </c>
-      <c r="C166" s="4" t="s">
-        <v>446</v>
       </c>
     </row>
     <row r="167" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B167" s="4" t="s">
+        <v>446</v>
+      </c>
+      <c r="C167" s="4" t="s">
         <v>447</v>
-      </c>
-      <c r="C167" s="4" t="s">
-        <v>448</v>
       </c>
     </row>
     <row r="168" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B168" s="4" t="s">
+        <v>448</v>
+      </c>
+      <c r="C168" s="4" t="s">
         <v>449</v>
-      </c>
-      <c r="C168" s="4" t="s">
-        <v>450</v>
       </c>
     </row>
     <row r="169" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B169" s="4" t="s">
+        <v>450</v>
+      </c>
+      <c r="C169" s="4" t="s">
         <v>451</v>
-      </c>
-      <c r="C169" s="4" t="s">
-        <v>452</v>
       </c>
     </row>
     <row r="170" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B170" s="4" t="s">
+        <v>452</v>
+      </c>
+      <c r="C170" s="4" t="s">
         <v>453</v>
-      </c>
-      <c r="C170" s="4" t="s">
-        <v>454</v>
       </c>
     </row>
     <row r="171" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B171" s="4" t="s">
+        <v>454</v>
+      </c>
+      <c r="C171" s="4" t="s">
         <v>455</v>
-      </c>
-      <c r="C171" s="4" t="s">
-        <v>456</v>
       </c>
     </row>
     <row r="172" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B172" s="4" t="s">
+        <v>456</v>
+      </c>
+      <c r="C172" s="4" t="s">
         <v>457</v>
-      </c>
-      <c r="C172" s="4" t="s">
-        <v>458</v>
       </c>
     </row>
     <row r="173" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B173" s="4" t="s">
+        <v>458</v>
+      </c>
+      <c r="C173" s="4" t="s">
         <v>459</v>
-      </c>
-      <c r="C173" s="4" t="s">
-        <v>460</v>
       </c>
     </row>
     <row r="174" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B174" s="4" t="s">
+        <v>460</v>
+      </c>
+      <c r="C174" s="4" t="s">
         <v>461</v>
-      </c>
-      <c r="C174" s="4" t="s">
-        <v>462</v>
       </c>
     </row>
     <row r="175" spans="2:3" x14ac:dyDescent="0.25">
@@ -5302,303 +5299,303 @@
         <v>45</v>
       </c>
       <c r="C175" s="4" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
     </row>
     <row r="176" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B176" s="4" t="s">
+        <v>463</v>
+      </c>
+      <c r="C176" s="4" t="s">
         <v>464</v>
-      </c>
-      <c r="C176" s="4" t="s">
-        <v>465</v>
       </c>
     </row>
     <row r="177" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B177" s="4" t="s">
+        <v>465</v>
+      </c>
+      <c r="C177" s="4" t="s">
         <v>466</v>
-      </c>
-      <c r="C177" s="4" t="s">
-        <v>467</v>
       </c>
     </row>
     <row r="178" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B178" s="4" t="s">
+        <v>467</v>
+      </c>
+      <c r="C178" s="4" t="s">
         <v>468</v>
-      </c>
-      <c r="C178" s="4" t="s">
-        <v>469</v>
       </c>
     </row>
     <row r="179" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B179" s="4" t="s">
+        <v>469</v>
+      </c>
+      <c r="C179" s="4" t="s">
         <v>470</v>
-      </c>
-      <c r="C179" s="4" t="s">
-        <v>471</v>
       </c>
     </row>
     <row r="180" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B180" s="4" t="s">
+        <v>471</v>
+      </c>
+      <c r="C180" s="4" t="s">
         <v>472</v>
-      </c>
-      <c r="C180" s="4" t="s">
-        <v>473</v>
       </c>
     </row>
     <row r="181" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B181" s="4" t="s">
+        <v>473</v>
+      </c>
+      <c r="C181" s="4" t="s">
         <v>474</v>
-      </c>
-      <c r="C181" s="4" t="s">
-        <v>475</v>
       </c>
     </row>
     <row r="182" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B182" s="4" t="s">
+        <v>475</v>
+      </c>
+      <c r="C182" s="4" t="s">
         <v>476</v>
-      </c>
-      <c r="C182" s="4" t="s">
-        <v>477</v>
       </c>
     </row>
     <row r="183" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B183" s="4" t="s">
+        <v>477</v>
+      </c>
+      <c r="C183" s="4" t="s">
         <v>478</v>
-      </c>
-      <c r="C183" s="4" t="s">
-        <v>479</v>
       </c>
     </row>
     <row r="184" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B184" s="4" t="s">
+        <v>479</v>
+      </c>
+      <c r="C184" s="4" t="s">
         <v>480</v>
-      </c>
-      <c r="C184" s="4" t="s">
-        <v>481</v>
       </c>
     </row>
     <row r="185" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B185" s="4" t="s">
+        <v>481</v>
+      </c>
+      <c r="C185" s="4" t="s">
         <v>482</v>
-      </c>
-      <c r="C185" s="4" t="s">
-        <v>483</v>
       </c>
     </row>
     <row r="186" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B186" s="4" t="s">
+        <v>483</v>
+      </c>
+      <c r="C186" s="4" t="s">
         <v>484</v>
-      </c>
-      <c r="C186" s="4" t="s">
-        <v>485</v>
       </c>
     </row>
     <row r="187" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B187" s="4" t="s">
+        <v>485</v>
+      </c>
+      <c r="C187" s="4" t="s">
         <v>486</v>
-      </c>
-      <c r="C187" s="4" t="s">
-        <v>487</v>
       </c>
     </row>
     <row r="188" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B188" s="4" t="s">
+        <v>487</v>
+      </c>
+      <c r="C188" s="4" t="s">
         <v>488</v>
-      </c>
-      <c r="C188" s="4" t="s">
-        <v>489</v>
       </c>
     </row>
     <row r="189" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B189" s="4" t="s">
+        <v>489</v>
+      </c>
+      <c r="C189" s="4" t="s">
         <v>490</v>
-      </c>
-      <c r="C189" s="4" t="s">
-        <v>491</v>
       </c>
     </row>
     <row r="190" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B190" s="4" t="s">
+        <v>491</v>
+      </c>
+      <c r="C190" s="4" t="s">
         <v>492</v>
-      </c>
-      <c r="C190" s="4" t="s">
-        <v>493</v>
       </c>
     </row>
     <row r="191" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B191" s="4" t="s">
+        <v>493</v>
+      </c>
+      <c r="C191" s="4" t="s">
         <v>494</v>
-      </c>
-      <c r="C191" s="4" t="s">
-        <v>495</v>
       </c>
     </row>
     <row r="192" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B192" s="4" t="s">
+        <v>495</v>
+      </c>
+      <c r="C192" s="4" t="s">
         <v>496</v>
-      </c>
-      <c r="C192" s="4" t="s">
-        <v>497</v>
       </c>
     </row>
     <row r="193" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B193" s="4" t="s">
+        <v>497</v>
+      </c>
+      <c r="C193" s="4" t="s">
         <v>498</v>
-      </c>
-      <c r="C193" s="4" t="s">
-        <v>499</v>
       </c>
     </row>
     <row r="194" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B194" s="4" t="s">
+        <v>499</v>
+      </c>
+      <c r="C194" s="4" t="s">
         <v>500</v>
-      </c>
-      <c r="C194" s="4" t="s">
-        <v>501</v>
       </c>
     </row>
     <row r="195" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B195" s="4" t="s">
+        <v>501</v>
+      </c>
+      <c r="C195" s="4" t="s">
         <v>502</v>
-      </c>
-      <c r="C195" s="4" t="s">
-        <v>503</v>
       </c>
     </row>
     <row r="196" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B196" s="4" t="s">
+        <v>503</v>
+      </c>
+      <c r="C196" s="4" t="s">
         <v>504</v>
-      </c>
-      <c r="C196" s="4" t="s">
-        <v>505</v>
       </c>
     </row>
     <row r="197" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B197" s="4" t="s">
+        <v>505</v>
+      </c>
+      <c r="C197" s="4" t="s">
         <v>506</v>
-      </c>
-      <c r="C197" s="4" t="s">
-        <v>507</v>
       </c>
     </row>
     <row r="198" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B198" s="4" t="s">
+        <v>507</v>
+      </c>
+      <c r="C198" s="4" t="s">
         <v>508</v>
-      </c>
-      <c r="C198" s="4" t="s">
-        <v>509</v>
       </c>
     </row>
     <row r="199" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B199" s="4" t="s">
+        <v>509</v>
+      </c>
+      <c r="C199" s="4" t="s">
         <v>510</v>
-      </c>
-      <c r="C199" s="4" t="s">
-        <v>511</v>
       </c>
     </row>
     <row r="200" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B200" s="4" t="s">
+        <v>511</v>
+      </c>
+      <c r="C200" s="4" t="s">
         <v>512</v>
-      </c>
-      <c r="C200" s="4" t="s">
-        <v>513</v>
       </c>
     </row>
     <row r="201" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B201" s="4" t="s">
+        <v>513</v>
+      </c>
+      <c r="C201" s="4" t="s">
         <v>514</v>
-      </c>
-      <c r="C201" s="4" t="s">
-        <v>515</v>
       </c>
     </row>
     <row r="202" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B202" s="4" t="s">
+        <v>515</v>
+      </c>
+      <c r="C202" s="4" t="s">
         <v>516</v>
-      </c>
-      <c r="C202" s="4" t="s">
-        <v>517</v>
       </c>
     </row>
     <row r="203" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B203" s="4" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="C203" s="4" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
     </row>
     <row r="204" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B204" s="4" t="s">
+        <v>518</v>
+      </c>
+      <c r="C204" s="4" t="s">
         <v>519</v>
-      </c>
-      <c r="C204" s="4" t="s">
-        <v>520</v>
       </c>
     </row>
     <row r="205" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B205" s="4" t="s">
+        <v>520</v>
+      </c>
+      <c r="C205" s="4" t="s">
         <v>521</v>
-      </c>
-      <c r="C205" s="4" t="s">
-        <v>522</v>
       </c>
     </row>
     <row r="206" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B206" s="4" t="s">
+        <v>522</v>
+      </c>
+      <c r="C206" s="4" t="s">
         <v>523</v>
-      </c>
-      <c r="C206" s="4" t="s">
-        <v>524</v>
       </c>
     </row>
     <row r="207" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B207" s="4" t="s">
+        <v>524</v>
+      </c>
+      <c r="C207" s="4" t="s">
         <v>525</v>
-      </c>
-      <c r="C207" s="4" t="s">
-        <v>526</v>
       </c>
     </row>
     <row r="208" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B208" s="4" t="s">
+        <v>526</v>
+      </c>
+      <c r="C208" s="4" t="s">
         <v>527</v>
-      </c>
-      <c r="C208" s="4" t="s">
-        <v>528</v>
       </c>
     </row>
     <row r="209" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B209" s="4" t="s">
+        <v>528</v>
+      </c>
+      <c r="C209" s="4" t="s">
         <v>529</v>
-      </c>
-      <c r="C209" s="4" t="s">
-        <v>530</v>
       </c>
     </row>
     <row r="210" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B210" s="4" t="s">
+        <v>530</v>
+      </c>
+      <c r="C210" s="4" t="s">
         <v>531</v>
-      </c>
-      <c r="C210" s="4" t="s">
-        <v>532</v>
       </c>
     </row>
     <row r="211" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B211" s="4" t="s">
+        <v>532</v>
+      </c>
+      <c r="C211" s="4" t="s">
         <v>533</v>
-      </c>
-      <c r="C211" s="4" t="s">
-        <v>534</v>
       </c>
     </row>
     <row r="212" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B212" s="4" t="s">
+        <v>534</v>
+      </c>
+      <c r="C212" s="4" t="s">
         <v>535</v>
-      </c>
-      <c r="C212" s="4" t="s">
-        <v>536</v>
       </c>
     </row>
   </sheetData>
@@ -5622,778 +5619,778 @@
     </row>
     <row r="2" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B2" s="3" t="s">
+        <v>536</v>
+      </c>
+      <c r="C2" s="3" t="s">
         <v>537</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>538</v>
       </c>
     </row>
     <row r="3" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B3" s="3" t="s">
+        <v>538</v>
+      </c>
+      <c r="C3" s="3" t="s">
         <v>539</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>540</v>
       </c>
     </row>
     <row r="4" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B4" s="3" t="s">
+        <v>540</v>
+      </c>
+      <c r="C4" s="3" t="s">
         <v>541</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>542</v>
       </c>
     </row>
     <row r="5" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B5" s="3" t="s">
+        <v>542</v>
+      </c>
+      <c r="C5" s="3" t="s">
         <v>543</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>544</v>
       </c>
     </row>
     <row r="6" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B6" s="3" t="s">
+        <v>544</v>
+      </c>
+      <c r="C6" s="3" t="s">
         <v>545</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>546</v>
       </c>
     </row>
     <row r="7" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B7" s="3" t="s">
+        <v>546</v>
+      </c>
+      <c r="C7" s="3" t="s">
         <v>547</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>548</v>
       </c>
     </row>
     <row r="8" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B8" s="3" t="s">
+        <v>548</v>
+      </c>
+      <c r="C8" s="3" t="s">
         <v>549</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>550</v>
       </c>
     </row>
     <row r="9" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B9" s="3" t="s">
+        <v>550</v>
+      </c>
+      <c r="C9" s="3" t="s">
         <v>551</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>552</v>
       </c>
     </row>
     <row r="10" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B10" s="3" t="s">
+        <v>552</v>
+      </c>
+      <c r="C10" s="3" t="s">
         <v>553</v>
-      </c>
-      <c r="C10" s="3" t="s">
-        <v>554</v>
       </c>
     </row>
     <row r="11" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B11" s="3" t="s">
+        <v>554</v>
+      </c>
+      <c r="C11" s="3" t="s">
         <v>555</v>
-      </c>
-      <c r="C11" s="3" t="s">
-        <v>556</v>
       </c>
     </row>
     <row r="12" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B12" s="3" t="s">
+        <v>556</v>
+      </c>
+      <c r="C12" s="3" t="s">
         <v>557</v>
-      </c>
-      <c r="C12" s="3" t="s">
-        <v>558</v>
       </c>
     </row>
     <row r="13" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B13" s="3" t="s">
+        <v>558</v>
+      </c>
+      <c r="C13" s="3" t="s">
         <v>559</v>
-      </c>
-      <c r="C13" s="3" t="s">
-        <v>560</v>
       </c>
     </row>
     <row r="14" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B14" s="3" t="s">
+        <v>560</v>
+      </c>
+      <c r="C14" s="3" t="s">
         <v>561</v>
-      </c>
-      <c r="C14" s="3" t="s">
-        <v>562</v>
       </c>
     </row>
     <row r="15" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B15" s="3" t="s">
+        <v>562</v>
+      </c>
+      <c r="C15" s="3" t="s">
         <v>563</v>
-      </c>
-      <c r="C15" s="3" t="s">
-        <v>564</v>
       </c>
     </row>
     <row r="16" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B16" s="3" t="s">
+        <v>564</v>
+      </c>
+      <c r="C16" s="3" t="s">
         <v>565</v>
-      </c>
-      <c r="C16" s="3" t="s">
-        <v>566</v>
       </c>
     </row>
     <row r="17" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B17" s="3" t="s">
+        <v>566</v>
+      </c>
+      <c r="C17" s="3" t="s">
         <v>567</v>
-      </c>
-      <c r="C17" s="3" t="s">
-        <v>568</v>
       </c>
     </row>
     <row r="18" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B18" s="3" t="s">
+        <v>568</v>
+      </c>
+      <c r="C18" s="3" t="s">
         <v>569</v>
-      </c>
-      <c r="C18" s="3" t="s">
-        <v>570</v>
       </c>
     </row>
     <row r="19" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B19" s="3" t="s">
+        <v>570</v>
+      </c>
+      <c r="C19" s="3" t="s">
         <v>571</v>
-      </c>
-      <c r="C19" s="3" t="s">
-        <v>572</v>
       </c>
     </row>
     <row r="20" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B20" s="3" t="s">
+        <v>572</v>
+      </c>
+      <c r="C20" s="3" t="s">
         <v>573</v>
-      </c>
-      <c r="C20" s="3" t="s">
-        <v>574</v>
       </c>
     </row>
     <row r="21" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B21" s="3" t="s">
+        <v>574</v>
+      </c>
+      <c r="C21" s="3" t="s">
         <v>575</v>
-      </c>
-      <c r="C21" s="3" t="s">
-        <v>576</v>
       </c>
     </row>
     <row r="22" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B22" s="3" t="s">
+        <v>576</v>
+      </c>
+      <c r="C22" s="3" t="s">
         <v>577</v>
-      </c>
-      <c r="C22" s="3" t="s">
-        <v>578</v>
       </c>
     </row>
     <row r="23" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B23" s="3" t="s">
+        <v>578</v>
+      </c>
+      <c r="C23" s="3" t="s">
         <v>579</v>
-      </c>
-      <c r="C23" s="3" t="s">
-        <v>580</v>
       </c>
     </row>
     <row r="24" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B24" s="3" t="s">
+        <v>580</v>
+      </c>
+      <c r="C24" s="3" t="s">
         <v>581</v>
-      </c>
-      <c r="C24" s="3" t="s">
-        <v>582</v>
       </c>
     </row>
     <row r="25" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B25" s="3" t="s">
+        <v>582</v>
+      </c>
+      <c r="C25" s="3" t="s">
         <v>583</v>
-      </c>
-      <c r="C25" s="3" t="s">
-        <v>584</v>
       </c>
     </row>
     <row r="26" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B26" s="3" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
     </row>
     <row r="27" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B27" s="3" t="s">
+        <v>585</v>
+      </c>
+      <c r="C27" s="3" t="s">
         <v>586</v>
-      </c>
-      <c r="C27" s="3" t="s">
-        <v>587</v>
       </c>
     </row>
     <row r="28" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B28" s="3" t="s">
+        <v>587</v>
+      </c>
+      <c r="C28" s="3" t="s">
         <v>588</v>
-      </c>
-      <c r="C28" s="3" t="s">
-        <v>589</v>
       </c>
     </row>
     <row r="29" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B29" s="3" t="s">
+        <v>589</v>
+      </c>
+      <c r="C29" s="3" t="s">
         <v>590</v>
-      </c>
-      <c r="C29" s="3" t="s">
-        <v>591</v>
       </c>
     </row>
     <row r="30" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B30" s="3" t="s">
+        <v>591</v>
+      </c>
+      <c r="C30" s="3" t="s">
         <v>592</v>
-      </c>
-      <c r="C30" s="3" t="s">
-        <v>593</v>
       </c>
     </row>
     <row r="31" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B31" s="3" t="s">
+        <v>593</v>
+      </c>
+      <c r="C31" s="3" t="s">
         <v>594</v>
-      </c>
-      <c r="C31" s="3" t="s">
-        <v>595</v>
       </c>
     </row>
     <row r="32" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B32" s="3" t="s">
+        <v>595</v>
+      </c>
+      <c r="C32" s="3" t="s">
         <v>596</v>
-      </c>
-      <c r="C32" s="3" t="s">
-        <v>597</v>
       </c>
     </row>
     <row r="33" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B33" s="3" t="s">
+        <v>597</v>
+      </c>
+      <c r="C33" s="3" t="s">
         <v>598</v>
-      </c>
-      <c r="C33" s="3" t="s">
-        <v>599</v>
       </c>
     </row>
     <row r="34" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B34" s="3" t="s">
+        <v>599</v>
+      </c>
+      <c r="C34" s="3" t="s">
         <v>600</v>
-      </c>
-      <c r="C34" s="3" t="s">
-        <v>601</v>
       </c>
     </row>
     <row r="35" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B35" s="3" t="s">
+        <v>601</v>
+      </c>
+      <c r="C35" s="3" t="s">
         <v>602</v>
-      </c>
-      <c r="C35" s="3" t="s">
-        <v>603</v>
       </c>
     </row>
     <row r="36" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B36" s="3" t="s">
+        <v>603</v>
+      </c>
+      <c r="C36" s="3" t="s">
         <v>604</v>
-      </c>
-      <c r="C36" s="3" t="s">
-        <v>605</v>
       </c>
     </row>
     <row r="37" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B37" s="3" t="s">
+        <v>605</v>
+      </c>
+      <c r="C37" s="3" t="s">
         <v>606</v>
-      </c>
-      <c r="C37" s="3" t="s">
-        <v>607</v>
       </c>
     </row>
     <row r="38" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B38" s="3" t="s">
+        <v>607</v>
+      </c>
+      <c r="C38" s="3" t="s">
         <v>608</v>
-      </c>
-      <c r="C38" s="3" t="s">
-        <v>609</v>
       </c>
     </row>
     <row r="39" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B39" s="3" t="s">
+        <v>609</v>
+      </c>
+      <c r="C39" s="3" t="s">
         <v>610</v>
-      </c>
-      <c r="C39" s="3" t="s">
-        <v>611</v>
       </c>
     </row>
     <row r="40" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B40" s="3" t="s">
+        <v>611</v>
+      </c>
+      <c r="C40" s="3" t="s">
         <v>612</v>
-      </c>
-      <c r="C40" s="3" t="s">
-        <v>613</v>
       </c>
     </row>
     <row r="41" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B41" s="3" t="s">
+        <v>613</v>
+      </c>
+      <c r="C41" s="3" t="s">
         <v>614</v>
-      </c>
-      <c r="C41" s="3" t="s">
-        <v>615</v>
       </c>
     </row>
     <row r="42" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B42" s="3" t="s">
+        <v>615</v>
+      </c>
+      <c r="C42" s="3" t="s">
         <v>616</v>
-      </c>
-      <c r="C42" s="3" t="s">
-        <v>617</v>
       </c>
     </row>
     <row r="43" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B43" s="3" t="s">
+        <v>617</v>
+      </c>
+      <c r="C43" s="3" t="s">
         <v>618</v>
-      </c>
-      <c r="C43" s="3" t="s">
-        <v>619</v>
       </c>
     </row>
     <row r="44" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B44" s="3" t="s">
+        <v>619</v>
+      </c>
+      <c r="C44" s="3" t="s">
         <v>620</v>
-      </c>
-      <c r="C44" s="3" t="s">
-        <v>621</v>
       </c>
     </row>
     <row r="45" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B45" s="3" t="s">
+        <v>621</v>
+      </c>
+      <c r="C45" s="3" t="s">
         <v>622</v>
-      </c>
-      <c r="C45" s="3" t="s">
-        <v>623</v>
       </c>
     </row>
     <row r="46" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B46" s="3" t="s">
+        <v>623</v>
+      </c>
+      <c r="C46" s="3" t="s">
         <v>624</v>
-      </c>
-      <c r="C46" s="3" t="s">
-        <v>625</v>
       </c>
     </row>
     <row r="47" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B47" s="3" t="s">
+        <v>625</v>
+      </c>
+      <c r="C47" s="3" t="s">
         <v>626</v>
-      </c>
-      <c r="C47" s="3" t="s">
-        <v>627</v>
       </c>
     </row>
     <row r="48" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B48" s="3" t="s">
+        <v>627</v>
+      </c>
+      <c r="C48" s="3" t="s">
         <v>628</v>
-      </c>
-      <c r="C48" s="3" t="s">
-        <v>629</v>
       </c>
     </row>
     <row r="49" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B49" s="3" t="s">
+        <v>629</v>
+      </c>
+      <c r="C49" s="3" t="s">
         <v>630</v>
-      </c>
-      <c r="C49" s="3" t="s">
-        <v>631</v>
       </c>
     </row>
     <row r="50" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B50" s="3" t="s">
+        <v>631</v>
+      </c>
+      <c r="C50" s="3" t="s">
         <v>632</v>
-      </c>
-      <c r="C50" s="3" t="s">
-        <v>633</v>
       </c>
     </row>
     <row r="51" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B51" s="3" t="s">
+        <v>633</v>
+      </c>
+      <c r="C51" s="3" t="s">
         <v>634</v>
-      </c>
-      <c r="C51" s="3" t="s">
-        <v>635</v>
       </c>
     </row>
     <row r="52" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B52" s="3" t="s">
+        <v>635</v>
+      </c>
+      <c r="C52" s="3" t="s">
         <v>636</v>
-      </c>
-      <c r="C52" s="3" t="s">
-        <v>637</v>
       </c>
     </row>
     <row r="53" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B53" s="3" t="s">
+        <v>637</v>
+      </c>
+      <c r="C53" s="3" t="s">
         <v>638</v>
-      </c>
-      <c r="C53" s="3" t="s">
-        <v>639</v>
       </c>
     </row>
     <row r="54" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B54" s="3" t="s">
+        <v>639</v>
+      </c>
+      <c r="C54" s="3" t="s">
         <v>640</v>
-      </c>
-      <c r="C54" s="3" t="s">
-        <v>641</v>
       </c>
     </row>
     <row r="55" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B55" s="3" t="s">
+        <v>641</v>
+      </c>
+      <c r="C55" s="3" t="s">
         <v>642</v>
-      </c>
-      <c r="C55" s="3" t="s">
-        <v>643</v>
       </c>
     </row>
     <row r="56" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B56" s="3" t="s">
+        <v>643</v>
+      </c>
+      <c r="C56" s="3" t="s">
         <v>644</v>
-      </c>
-      <c r="C56" s="3" t="s">
-        <v>645</v>
       </c>
     </row>
     <row r="57" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B57" s="3" t="s">
+        <v>645</v>
+      </c>
+      <c r="C57" s="3" t="s">
         <v>646</v>
-      </c>
-      <c r="C57" s="3" t="s">
-        <v>647</v>
       </c>
     </row>
     <row r="58" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B58" s="3" t="s">
+        <v>647</v>
+      </c>
+      <c r="C58" s="3" t="s">
         <v>648</v>
-      </c>
-      <c r="C58" s="3" t="s">
-        <v>649</v>
       </c>
     </row>
     <row r="59" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B59" s="3" t="s">
+        <v>649</v>
+      </c>
+      <c r="C59" s="3" t="s">
         <v>650</v>
-      </c>
-      <c r="C59" s="3" t="s">
-        <v>651</v>
       </c>
     </row>
     <row r="60" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B60" s="3" t="s">
+        <v>651</v>
+      </c>
+      <c r="C60" s="3" t="s">
         <v>652</v>
-      </c>
-      <c r="C60" s="3" t="s">
-        <v>653</v>
       </c>
     </row>
     <row r="61" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B61" s="3" t="s">
+        <v>653</v>
+      </c>
+      <c r="C61" s="3" t="s">
         <v>654</v>
-      </c>
-      <c r="C61" s="3" t="s">
-        <v>655</v>
       </c>
     </row>
     <row r="62" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B62" s="3" t="s">
+        <v>655</v>
+      </c>
+      <c r="C62" s="3" t="s">
         <v>656</v>
-      </c>
-      <c r="C62" s="3" t="s">
-        <v>657</v>
       </c>
     </row>
     <row r="63" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B63" s="3" t="s">
+        <v>657</v>
+      </c>
+      <c r="C63" s="3" t="s">
         <v>658</v>
-      </c>
-      <c r="C63" s="3" t="s">
-        <v>659</v>
       </c>
     </row>
     <row r="64" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B64" s="3" t="s">
+        <v>659</v>
+      </c>
+      <c r="C64" s="3" t="s">
         <v>660</v>
-      </c>
-      <c r="C64" s="3" t="s">
-        <v>661</v>
       </c>
     </row>
     <row r="65" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B65" s="3" t="s">
+        <v>661</v>
+      </c>
+      <c r="C65" s="3" t="s">
         <v>662</v>
-      </c>
-      <c r="C65" s="3" t="s">
-        <v>663</v>
       </c>
     </row>
     <row r="66" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B66" s="3" t="s">
+        <v>663</v>
+      </c>
+      <c r="C66" s="3" t="s">
         <v>664</v>
-      </c>
-      <c r="C66" s="3" t="s">
-        <v>665</v>
       </c>
     </row>
     <row r="67" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B67" s="3" t="s">
+        <v>665</v>
+      </c>
+      <c r="C67" s="3" t="s">
         <v>666</v>
-      </c>
-      <c r="C67" s="3" t="s">
-        <v>667</v>
       </c>
     </row>
     <row r="68" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B68" s="3" t="s">
+        <v>667</v>
+      </c>
+      <c r="C68" s="3" t="s">
         <v>668</v>
-      </c>
-      <c r="C68" s="3" t="s">
-        <v>669</v>
       </c>
     </row>
     <row r="69" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B69" s="3" t="s">
+        <v>669</v>
+      </c>
+      <c r="C69" s="3" t="s">
         <v>670</v>
-      </c>
-      <c r="C69" s="3" t="s">
-        <v>671</v>
       </c>
     </row>
     <row r="70" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B70" s="3" t="s">
+        <v>671</v>
+      </c>
+      <c r="C70" s="3" t="s">
         <v>672</v>
-      </c>
-      <c r="C70" s="3" t="s">
-        <v>673</v>
       </c>
     </row>
     <row r="71" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B71" s="3" t="s">
+        <v>673</v>
+      </c>
+      <c r="C71" s="3" t="s">
         <v>674</v>
-      </c>
-      <c r="C71" s="3" t="s">
-        <v>675</v>
       </c>
     </row>
     <row r="72" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B72" s="3" t="s">
+        <v>675</v>
+      </c>
+      <c r="C72" s="3" t="s">
         <v>676</v>
-      </c>
-      <c r="C72" s="3" t="s">
-        <v>677</v>
       </c>
     </row>
     <row r="73" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B73" s="3" t="s">
+        <v>677</v>
+      </c>
+      <c r="C73" s="3" t="s">
         <v>678</v>
-      </c>
-      <c r="C73" s="3" t="s">
-        <v>679</v>
       </c>
     </row>
     <row r="74" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B74" s="3" t="s">
+        <v>679</v>
+      </c>
+      <c r="C74" s="3" t="s">
         <v>680</v>
-      </c>
-      <c r="C74" s="3" t="s">
-        <v>681</v>
       </c>
     </row>
     <row r="75" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B75" s="3" t="s">
+        <v>681</v>
+      </c>
+      <c r="C75" s="3" t="s">
         <v>682</v>
-      </c>
-      <c r="C75" s="3" t="s">
-        <v>683</v>
       </c>
     </row>
     <row r="76" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B76" s="3" t="s">
+        <v>683</v>
+      </c>
+      <c r="C76" s="3" t="s">
         <v>684</v>
-      </c>
-      <c r="C76" s="3" t="s">
-        <v>685</v>
       </c>
     </row>
     <row r="77" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B77" s="3" t="s">
+        <v>685</v>
+      </c>
+      <c r="C77" s="3" t="s">
         <v>686</v>
-      </c>
-      <c r="C77" s="3" t="s">
-        <v>687</v>
       </c>
     </row>
     <row r="78" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B78" s="3" t="s">
+        <v>687</v>
+      </c>
+      <c r="C78" s="3" t="s">
         <v>688</v>
-      </c>
-      <c r="C78" s="3" t="s">
-        <v>689</v>
       </c>
     </row>
     <row r="79" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B79" s="3" t="s">
+        <v>689</v>
+      </c>
+      <c r="C79" s="3" t="s">
         <v>690</v>
-      </c>
-      <c r="C79" s="3" t="s">
-        <v>691</v>
       </c>
     </row>
     <row r="80" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B80" s="3" t="s">
+        <v>691</v>
+      </c>
+      <c r="C80" s="3" t="s">
         <v>692</v>
-      </c>
-      <c r="C80" s="3" t="s">
-        <v>693</v>
       </c>
     </row>
     <row r="81" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B81" s="3" t="s">
+        <v>693</v>
+      </c>
+      <c r="C81" s="3" t="s">
         <v>694</v>
-      </c>
-      <c r="C81" s="3" t="s">
-        <v>695</v>
       </c>
     </row>
     <row r="82" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B82" s="3" t="s">
+        <v>695</v>
+      </c>
+      <c r="C82" s="3" t="s">
         <v>696</v>
-      </c>
-      <c r="C82" s="3" t="s">
-        <v>697</v>
       </c>
     </row>
     <row r="83" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B83" s="3" t="s">
+        <v>697</v>
+      </c>
+      <c r="C83" s="3" t="s">
         <v>698</v>
-      </c>
-      <c r="C83" s="3" t="s">
-        <v>699</v>
       </c>
     </row>
     <row r="84" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B84" s="3" t="s">
+        <v>699</v>
+      </c>
+      <c r="C84" s="3" t="s">
         <v>700</v>
-      </c>
-      <c r="C84" s="3" t="s">
-        <v>701</v>
       </c>
     </row>
     <row r="85" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B85" s="3" t="s">
+        <v>701</v>
+      </c>
+      <c r="C85" s="3" t="s">
         <v>702</v>
-      </c>
-      <c r="C85" s="3" t="s">
-        <v>703</v>
       </c>
     </row>
     <row r="86" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B86" s="3" t="s">
+        <v>703</v>
+      </c>
+      <c r="C86" s="3" t="s">
         <v>704</v>
-      </c>
-      <c r="C86" s="3" t="s">
-        <v>705</v>
       </c>
     </row>
     <row r="87" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B87" s="3" t="s">
+        <v>705</v>
+      </c>
+      <c r="C87" s="3" t="s">
         <v>706</v>
-      </c>
-      <c r="C87" s="3" t="s">
-        <v>707</v>
       </c>
     </row>
     <row r="88" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B88" s="3" t="s">
+        <v>707</v>
+      </c>
+      <c r="C88" s="3" t="s">
         <v>708</v>
-      </c>
-      <c r="C88" s="3" t="s">
-        <v>709</v>
       </c>
     </row>
     <row r="89" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B89" s="3" t="s">
+        <v>709</v>
+      </c>
+      <c r="C89" s="3" t="s">
         <v>710</v>
-      </c>
-      <c r="C89" s="3" t="s">
-        <v>711</v>
       </c>
     </row>
     <row r="90" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B90" s="3" t="s">
+        <v>711</v>
+      </c>
+      <c r="C90" s="3" t="s">
         <v>712</v>
-      </c>
-      <c r="C90" s="3" t="s">
-        <v>713</v>
       </c>
     </row>
     <row r="91" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B91" s="3" t="s">
+        <v>713</v>
+      </c>
+      <c r="C91" s="3" t="s">
         <v>714</v>
-      </c>
-      <c r="C91" s="3" t="s">
-        <v>715</v>
       </c>
     </row>
     <row r="92" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B92" s="3" t="s">
+        <v>715</v>
+      </c>
+      <c r="C92" s="3" t="s">
         <v>716</v>
-      </c>
-      <c r="C92" s="3" t="s">
-        <v>717</v>
       </c>
     </row>
     <row r="93" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B93" s="3" t="s">
+        <v>717</v>
+      </c>
+      <c r="C93" s="3" t="s">
         <v>718</v>
-      </c>
-      <c r="C93" s="3" t="s">
-        <v>719</v>
       </c>
     </row>
     <row r="94" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B94" s="3" t="s">
+        <v>719</v>
+      </c>
+      <c r="C94" s="3" t="s">
         <v>720</v>
-      </c>
-      <c r="C94" s="3" t="s">
-        <v>721</v>
       </c>
     </row>
     <row r="95" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B95" s="3" t="s">
+        <v>721</v>
+      </c>
+      <c r="C95" s="3" t="s">
         <v>722</v>
-      </c>
-      <c r="C95" s="3" t="s">
-        <v>723</v>
       </c>
     </row>
     <row r="96" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B96" s="3" t="s">
+        <v>723</v>
+      </c>
+      <c r="C96" s="3" t="s">
         <v>724</v>
-      </c>
-      <c r="C96" s="3" t="s">
-        <v>725</v>
       </c>
     </row>
     <row r="97" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B97" s="3" t="s">
+        <v>725</v>
+      </c>
+      <c r="C97" s="3" t="s">
         <v>726</v>
-      </c>
-      <c r="C97" s="3" t="s">
-        <v>727</v>
       </c>
     </row>
     <row r="98" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B98" s="3" t="s">
+        <v>727</v>
+      </c>
+      <c r="C98" s="3" t="s">
         <v>728</v>
-      </c>
-      <c r="C98" s="3" t="s">
-        <v>729</v>
       </c>
     </row>
   </sheetData>
@@ -6417,226 +6414,226 @@
     </row>
     <row r="2" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B2" s="2" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
     </row>
     <row r="3" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B3" s="2" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>731</v>
+        <v>730</v>
       </c>
     </row>
     <row r="4" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B4" s="2" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
     </row>
     <row r="5" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B5" s="2" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
     </row>
     <row r="6" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B6" s="2" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>734</v>
+        <v>733</v>
       </c>
     </row>
     <row r="7" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B7" s="2" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
     </row>
     <row r="8" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B8" s="2" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
     </row>
     <row r="9" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B9" s="2" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
     </row>
     <row r="10" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B10" s="2" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
     </row>
     <row r="11" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B11" s="2" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
     </row>
     <row r="12" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B12" s="2" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
     </row>
     <row r="13" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B13" s="2" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
     </row>
     <row r="14" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B14" s="2" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>741</v>
+        <v>740</v>
       </c>
     </row>
     <row r="15" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B15" s="2" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>741</v>
+        <v>740</v>
       </c>
     </row>
     <row r="16" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B16" s="2" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>741</v>
+        <v>740</v>
       </c>
     </row>
     <row r="17" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B17" s="2" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>741</v>
+        <v>740</v>
       </c>
     </row>
     <row r="18" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B18" s="2" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>741</v>
+        <v>740</v>
       </c>
     </row>
     <row r="19" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B19" s="2" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>742</v>
+        <v>741</v>
       </c>
     </row>
     <row r="20" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B20" s="2" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>743</v>
+        <v>742</v>
       </c>
     </row>
     <row r="21" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B21" s="2" t="s">
+        <v>743</v>
+      </c>
+      <c r="C21" s="2" t="s">
         <v>744</v>
-      </c>
-      <c r="C21" s="2" t="s">
-        <v>745</v>
       </c>
     </row>
     <row r="22" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B22" s="2" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>746</v>
+        <v>745</v>
       </c>
     </row>
     <row r="23" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B23" s="2" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>747</v>
+        <v>746</v>
       </c>
     </row>
     <row r="24" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B24" s="2" t="s">
+        <v>747</v>
+      </c>
+      <c r="C24" s="2" t="s">
         <v>748</v>
-      </c>
-      <c r="C24" s="2" t="s">
-        <v>749</v>
       </c>
     </row>
     <row r="25" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B25" s="2" t="s">
+        <v>749</v>
+      </c>
+      <c r="C25" s="2" t="s">
         <v>750</v>
-      </c>
-      <c r="C25" s="2" t="s">
-        <v>751</v>
       </c>
     </row>
     <row r="26" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B26" s="2" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>752</v>
+        <v>751</v>
       </c>
     </row>
     <row r="27" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B27" s="2" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
     </row>
     <row r="28" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B28" s="2" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>754</v>
+        <v>753</v>
       </c>
     </row>
     <row r="29" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B29" s="2" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
     </row>
     <row r="30" spans="2:3" x14ac:dyDescent="0.25">
@@ -6644,191 +6641,191 @@
         <v>6</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
     </row>
     <row r="31" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B31" s="2" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
     </row>
     <row r="32" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B32" s="2" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
     </row>
     <row r="33" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B33" s="2" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
     </row>
     <row r="34" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B34" s="2" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
     </row>
     <row r="35" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B35" s="2" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>761</v>
+        <v>760</v>
       </c>
     </row>
     <row r="36" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B36" s="2" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>762</v>
+        <v>761</v>
       </c>
     </row>
     <row r="37" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B37" s="2" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
     </row>
     <row r="38" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B38" s="2" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>764</v>
+        <v>763</v>
       </c>
     </row>
     <row r="39" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B39" s="2" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>765</v>
+        <v>764</v>
       </c>
     </row>
     <row r="40" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B40" s="2" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
     </row>
     <row r="41" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B41" s="2" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>767</v>
+        <v>766</v>
       </c>
     </row>
     <row r="42" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B42" s="2" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>768</v>
+        <v>767</v>
       </c>
     </row>
     <row r="43" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B43" s="2" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>769</v>
+        <v>768</v>
       </c>
     </row>
     <row r="44" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B44" s="2" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
     </row>
     <row r="45" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B45" s="2" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>746</v>
+        <v>745</v>
       </c>
     </row>
     <row r="46" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B46" s="2" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>771</v>
+        <v>770</v>
       </c>
     </row>
     <row r="47" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B47" s="2" t="s">
+        <v>771</v>
+      </c>
+      <c r="C47" s="2" t="s">
         <v>772</v>
-      </c>
-      <c r="C47" s="2" t="s">
-        <v>773</v>
       </c>
     </row>
     <row r="48" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B48" s="2" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>774</v>
+        <v>773</v>
       </c>
     </row>
     <row r="49" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B49" s="2" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>775</v>
+        <v>774</v>
       </c>
     </row>
     <row r="50" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B50" s="2" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>776</v>
+        <v>775</v>
       </c>
     </row>
     <row r="51" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B51" s="2" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
     </row>
     <row r="52" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B52" s="2" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
     </row>
     <row r="53" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B53" s="2" t="s">
+        <v>778</v>
+      </c>
+      <c r="C53" s="2" t="s">
         <v>779</v>
-      </c>
-      <c r="C53" s="2" t="s">
-        <v>780</v>
       </c>
     </row>
   </sheetData>
@@ -6852,242 +6849,242 @@
     </row>
     <row r="2" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B2" s="1" t="s">
+        <v>780</v>
+      </c>
+      <c r="C2" s="1" t="s">
         <v>781</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>782</v>
       </c>
     </row>
     <row r="3" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B3" s="1" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>783</v>
+        <v>782</v>
       </c>
     </row>
     <row r="4" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B4" s="1" t="s">
-        <v>784</v>
+        <v>783</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>731</v>
+        <v>730</v>
       </c>
     </row>
     <row r="5" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B5" s="1" t="s">
-        <v>785</v>
+        <v>784</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
     </row>
     <row r="6" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B6" s="1" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>786</v>
+        <v>785</v>
       </c>
     </row>
     <row r="7" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B7" s="1" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
     </row>
     <row r="8" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B8" s="1" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
     </row>
     <row r="9" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B9" s="1" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>789</v>
+        <v>788</v>
       </c>
     </row>
     <row r="10" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B10" s="1" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>790</v>
+        <v>789</v>
       </c>
     </row>
     <row r="11" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B11" s="1" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>791</v>
+        <v>790</v>
       </c>
     </row>
     <row r="12" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B12" s="1" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>792</v>
+        <v>791</v>
       </c>
     </row>
     <row r="13" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B13" s="1" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>793</v>
+        <v>792</v>
       </c>
     </row>
     <row r="14" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B14" s="1" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>794</v>
+        <v>793</v>
       </c>
     </row>
     <row r="15" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B15" s="1" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
     </row>
     <row r="16" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B16" s="1" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
     </row>
     <row r="17" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B17" s="1" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>734</v>
+        <v>733</v>
       </c>
     </row>
     <row r="18" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B18" s="1" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>795</v>
+        <v>794</v>
       </c>
     </row>
     <row r="19" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B19" s="1" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>783</v>
+        <v>782</v>
       </c>
     </row>
     <row r="20" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B20" s="1" t="s">
+        <v>795</v>
+      </c>
+      <c r="C20" s="1" t="s">
         <v>796</v>
-      </c>
-      <c r="C20" s="1" t="s">
-        <v>797</v>
       </c>
     </row>
     <row r="21" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B21" s="1" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
     </row>
     <row r="22" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B22" s="1" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
     </row>
     <row r="23" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B23" s="1" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
     </row>
     <row r="24" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B24" s="1" t="s">
+        <v>800</v>
+      </c>
+      <c r="C24" s="1" t="s">
         <v>801</v>
-      </c>
-      <c r="C24" s="1" t="s">
-        <v>802</v>
       </c>
     </row>
     <row r="25" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B25" s="1" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>747</v>
+        <v>746</v>
       </c>
     </row>
     <row r="26" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B26" s="1" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>761</v>
+        <v>760</v>
       </c>
     </row>
     <row r="27" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B27" s="1" t="s">
+        <v>802</v>
+      </c>
+      <c r="C27" s="1" t="s">
         <v>803</v>
-      </c>
-      <c r="C27" s="1" t="s">
-        <v>804</v>
       </c>
     </row>
     <row r="28" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B28" s="1" t="s">
+        <v>804</v>
+      </c>
+      <c r="C28" s="1" t="s">
         <v>805</v>
-      </c>
-      <c r="C28" s="1" t="s">
-        <v>806</v>
       </c>
     </row>
     <row r="29" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B29" s="1" t="s">
-        <v>807</v>
+        <v>806</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>752</v>
+        <v>751</v>
       </c>
     </row>
     <row r="30" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B30" s="1" t="s">
+        <v>807</v>
+      </c>
+      <c r="C30" s="1" t="s">
         <v>808</v>
-      </c>
-      <c r="C30" s="1" t="s">
-        <v>809</v>
       </c>
     </row>
     <row r="31" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B31" s="1" t="s">
+        <v>809</v>
+      </c>
+      <c r="C31" s="1" t="s">
         <v>810</v>
-      </c>
-      <c r="C31" s="1" t="s">
-        <v>811</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/Editor/DataDic/Data.xlsx
+++ b/Assets/Editor/DataDic/Data.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="17385" windowHeight="7860" activeTab="1"/>
+    <workbookView minimized="1" xWindow="0" yWindow="0" windowWidth="17385" windowHeight="7860" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="FishData" sheetId="1" r:id="rId1"/>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="987" uniqueCount="820">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="986" uniqueCount="819">
   <si>
     <t>Key</t>
   </si>
@@ -63,9 +63,6 @@
   </si>
   <si>
     <t>村公所卧室</t>
-  </si>
-  <si>
-    <t>874</t>
   </si>
   <si>
     <t>后山</t>
@@ -2880,250 +2877,250 @@
     </row>
     <row r="2" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B2" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="C2" s="4" t="s">
         <v>95</v>
-      </c>
-      <c r="C2" s="4" t="s">
-        <v>96</v>
       </c>
     </row>
     <row r="3" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B3" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="C3" s="4" t="s">
         <v>97</v>
-      </c>
-      <c r="C3" s="4" t="s">
-        <v>98</v>
       </c>
     </row>
     <row r="4" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B4" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="C4" s="4" t="s">
         <v>99</v>
-      </c>
-      <c r="C4" s="4" t="s">
-        <v>100</v>
       </c>
     </row>
     <row r="5" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B5" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="C5" s="4" t="s">
         <v>101</v>
-      </c>
-      <c r="C5" s="4" t="s">
-        <v>102</v>
       </c>
     </row>
     <row r="6" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B6" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="C6" s="4" t="s">
         <v>103</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>104</v>
       </c>
     </row>
     <row r="7" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B7" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="C7" s="4" t="s">
         <v>105</v>
-      </c>
-      <c r="C7" s="4" t="s">
-        <v>106</v>
       </c>
     </row>
     <row r="8" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B8" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="C8" s="4" t="s">
         <v>107</v>
-      </c>
-      <c r="C8" s="4" t="s">
-        <v>108</v>
       </c>
     </row>
     <row r="9" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B9" s="4" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="10" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B10" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="C10" s="4" t="s">
         <v>110</v>
-      </c>
-      <c r="C10" s="4" t="s">
-        <v>111</v>
       </c>
     </row>
     <row r="11" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B11" s="4" t="s">
+        <v>111</v>
+      </c>
+      <c r="C11" s="4" t="s">
         <v>112</v>
-      </c>
-      <c r="C11" s="4" t="s">
-        <v>113</v>
       </c>
     </row>
     <row r="12" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B12" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="C12" s="4" t="s">
         <v>114</v>
-      </c>
-      <c r="C12" s="4" t="s">
-        <v>115</v>
       </c>
     </row>
     <row r="13" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B13" s="4" t="s">
+        <v>115</v>
+      </c>
+      <c r="C13" s="4" t="s">
         <v>116</v>
-      </c>
-      <c r="C13" s="4" t="s">
-        <v>117</v>
       </c>
     </row>
     <row r="14" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B14" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="C14" s="4" t="s">
         <v>118</v>
-      </c>
-      <c r="C14" s="4" t="s">
-        <v>119</v>
       </c>
     </row>
     <row r="15" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B15" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="C15" s="4" t="s">
         <v>120</v>
-      </c>
-      <c r="C15" s="4" t="s">
-        <v>121</v>
       </c>
     </row>
     <row r="16" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B16" s="4" t="s">
+        <v>121</v>
+      </c>
+      <c r="C16" s="4" t="s">
         <v>122</v>
-      </c>
-      <c r="C16" s="4" t="s">
-        <v>123</v>
       </c>
     </row>
     <row r="17" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B17" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="C17" s="4" t="s">
         <v>124</v>
-      </c>
-      <c r="C17" s="4" t="s">
-        <v>125</v>
       </c>
     </row>
     <row r="18" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B18" s="4" t="s">
+        <v>125</v>
+      </c>
+      <c r="C18" s="4" t="s">
         <v>126</v>
-      </c>
-      <c r="C18" s="4" t="s">
-        <v>127</v>
       </c>
     </row>
     <row r="19" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B19" s="4" t="s">
+        <v>127</v>
+      </c>
+      <c r="C19" s="4" t="s">
         <v>128</v>
-      </c>
-      <c r="C19" s="4" t="s">
-        <v>129</v>
       </c>
     </row>
     <row r="20" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B20" s="4" t="s">
+        <v>129</v>
+      </c>
+      <c r="C20" s="4" t="s">
         <v>130</v>
-      </c>
-      <c r="C20" s="4" t="s">
-        <v>131</v>
       </c>
     </row>
     <row r="21" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B21" s="4" t="s">
+        <v>131</v>
+      </c>
+      <c r="C21" s="4" t="s">
         <v>132</v>
-      </c>
-      <c r="C21" s="4" t="s">
-        <v>133</v>
       </c>
     </row>
     <row r="22" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B22" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="C22" s="4" t="s">
         <v>134</v>
-      </c>
-      <c r="C22" s="4" t="s">
-        <v>135</v>
       </c>
     </row>
     <row r="23" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B23" s="4" t="s">
+        <v>135</v>
+      </c>
+      <c r="C23" s="4" t="s">
         <v>136</v>
-      </c>
-      <c r="C23" s="4" t="s">
-        <v>137</v>
       </c>
     </row>
     <row r="24" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B24" s="4" t="s">
+        <v>137</v>
+      </c>
+      <c r="C24" s="4" t="s">
         <v>138</v>
-      </c>
-      <c r="C24" s="4" t="s">
-        <v>139</v>
       </c>
     </row>
     <row r="25" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B25" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="C25" s="4" t="s">
         <v>140</v>
-      </c>
-      <c r="C25" s="4" t="s">
-        <v>141</v>
       </c>
     </row>
     <row r="26" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B26" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="C26" s="4" t="s">
         <v>142</v>
-      </c>
-      <c r="C26" s="4" t="s">
-        <v>143</v>
       </c>
     </row>
     <row r="27" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B27" s="4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C27" s="4" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
     </row>
     <row r="28" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B28" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="C28" s="4" t="s">
         <v>145</v>
-      </c>
-      <c r="C28" s="4" t="s">
-        <v>146</v>
       </c>
     </row>
     <row r="29" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B29" s="4" t="s">
+        <v>146</v>
+      </c>
+      <c r="C29" s="4" t="s">
         <v>147</v>
-      </c>
-      <c r="C29" s="4" t="s">
-        <v>148</v>
       </c>
     </row>
     <row r="30" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B30" s="4" t="s">
+        <v>148</v>
+      </c>
+      <c r="C30" s="4" t="s">
         <v>149</v>
-      </c>
-      <c r="C30" s="4" t="s">
-        <v>150</v>
       </c>
     </row>
     <row r="31" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B31" s="4" t="s">
+        <v>150</v>
+      </c>
+      <c r="C31" s="4" t="s">
         <v>151</v>
-      </c>
-      <c r="C31" s="4" t="s">
-        <v>152</v>
       </c>
     </row>
     <row r="32" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B32" s="4" t="s">
+        <v>152</v>
+      </c>
+      <c r="C32" s="4" t="s">
         <v>153</v>
-      </c>
-      <c r="C32" s="4" t="s">
-        <v>154</v>
       </c>
     </row>
   </sheetData>
@@ -3173,16 +3170,16 @@
         <v>6</v>
       </c>
       <c r="G4" s="5" t="s">
-        <v>811</v>
+        <v>810</v>
       </c>
       <c r="I4" s="6" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="J4" s="6" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="K4" s="4" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="5" spans="2:15" x14ac:dyDescent="0.25">
@@ -3193,9 +3190,9 @@
         <v>948</v>
       </c>
       <c r="G5" s="5" t="s">
-        <v>812</v>
-      </c>
-      <c r="I5" t="str">
+        <v>811</v>
+      </c>
+      <c r="I5">
         <f>VLOOKUP(I4,$B:$C,2,FALSE)</f>
         <v>874</v>
       </c>
@@ -3220,7 +3217,7 @@
         <v>6,0,9,0</v>
       </c>
       <c r="H6" s="7"/>
-      <c r="I6" s="7" t="str">
+      <c r="I6" s="7">
         <f>I5</f>
         <v>874</v>
       </c>
@@ -3243,41 +3240,41 @@
         <v>11</v>
       </c>
       <c r="G7" s="5" t="s">
-        <v>813</v>
+        <v>812</v>
       </c>
       <c r="I7" s="6" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="J7" s="6" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="K7" s="4" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="L7" s="4" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="M7" s="4" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="N7" s="4" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="O7" s="4" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="8" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B8" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="C8" s="4" t="s">
         <v>13</v>
       </c>
+      <c r="C8" s="4">
+        <v>874</v>
+      </c>
       <c r="G8" s="5" t="s">
-        <v>817</v>
-      </c>
-      <c r="I8" s="4" t="str">
+        <v>816</v>
+      </c>
+      <c r="I8" s="4">
         <f>VLOOKUP(I7,$B:$C,2,FALSE)</f>
         <v>874</v>
       </c>
@@ -3308,17 +3305,17 @@
     </row>
     <row r="9" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B9" s="4" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G9" s="7" t="str">
         <f>G7&amp;","&amp;G8</f>
         <v>9,0,17,30</v>
       </c>
       <c r="H9" s="7"/>
-      <c r="I9" s="7" t="str">
+      <c r="I9" s="7">
         <f>I8</f>
         <v>874</v>
       </c>
@@ -3349,29 +3346,29 @@
     </row>
     <row r="10" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B10" s="4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="G10" s="5" t="s">
-        <v>818</v>
+        <v>817</v>
       </c>
     </row>
     <row r="11" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B11" s="4" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G11" s="5" t="s">
-        <v>819</v>
+        <v>818</v>
       </c>
     </row>
     <row r="12" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B12" s="4" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C12" s="4">
         <v>1756</v>
@@ -3392,10 +3389,10 @@
     </row>
     <row r="13" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B13" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F13" s="4"/>
       <c r="G13" s="5"/>
@@ -3410,38 +3407,38 @@
     </row>
     <row r="14" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B14" s="4" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F14" s="4"/>
       <c r="G14" s="5" t="s">
-        <v>819</v>
+        <v>818</v>
       </c>
       <c r="I14" s="4" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="J14" s="4" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="K14" s="4" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="L14" s="4" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="15" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B15" s="4" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F15" s="4"/>
       <c r="G15" s="5" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
       <c r="H15" s="4"/>
       <c r="I15" s="4" t="str">
@@ -3464,10 +3461,10 @@
     </row>
     <row r="16" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B16" s="4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G16" s="7" t="str">
         <f>G14&amp;","&amp;G15</f>
@@ -3495,36 +3492,36 @@
     </row>
     <row r="17" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B17" s="4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G17" s="5" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="I17" s="4" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="J17" s="4" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="K17" s="4" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="L17" s="4" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="18" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B18" s="4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G18" s="5" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
       <c r="I18" s="4" t="str">
         <f>VLOOKUP(I17,$B:$C,2,FALSE)</f>
@@ -3545,10 +3542,10 @@
     </row>
     <row r="19" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B19" s="4" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G19" s="7" t="str">
         <f>G17&amp;","&amp;G18</f>
@@ -3576,7 +3573,7 @@
     </row>
     <row r="20" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B20" s="4" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C20" s="4">
         <v>900</v>
@@ -3585,26 +3582,26 @@
     </row>
     <row r="21" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B21" s="4" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="22" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B22" s="4" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C22" s="4" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="23" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B23" s="4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C23" s="4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="G23" t="str">
         <f>G6&amp;","&amp;G9&amp;","&amp;G12&amp;","&amp;G16&amp;","&amp;G19</f>
@@ -3614,42 +3611,42 @@
     </row>
     <row r="24" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B24" s="4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C24" s="4" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="25" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B25" s="4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C25" s="4" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="M25" s="4"/>
     </row>
     <row r="26" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B26" s="4" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C26" s="4" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="M26" s="4"/>
     </row>
     <row r="27" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B27" s="4" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C27" s="4" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="M27" s="4"/>
     </row>
     <row r="28" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B28" s="4" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C28" s="4">
         <v>1014</v>
@@ -3658,89 +3655,89 @@
     </row>
     <row r="29" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B29" s="4" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C29" s="4" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="M29" s="4"/>
     </row>
     <row r="30" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B30" s="4" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C30" s="4" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="31" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B31" s="4" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C31" s="4" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="M31" s="4" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="32" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B32" s="4" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C32" s="4">
         <v>5309</v>
       </c>
       <c r="M32" s="4" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="33" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B33" s="4" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C33" s="4" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="M33" s="4" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="34" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B34" s="4" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C34" s="4" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="35" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B35" s="4" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C35" s="4" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="36" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B36" s="4" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C36" s="4" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="37" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B37" s="4" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C37" s="4" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="38" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B38" s="4" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C38" s="4">
         <v>3056</v>
@@ -3748,23 +3745,23 @@
     </row>
     <row r="39" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B39" s="4" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C39" s="4" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="40" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B40" s="4" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C40" s="4" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="41" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B41" s="4" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C41" s="4">
         <v>2497</v>
@@ -3772,79 +3769,79 @@
     </row>
     <row r="42" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B42" s="4" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C42" s="4" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="43" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B43" s="4" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C43" s="4" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="44" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B44" s="4" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C44" s="4" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="45" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B45" s="4" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C45" s="4" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="46" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B46" s="4" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C46" s="4" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="47" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B47" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C47" s="4" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="48" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B48" s="4" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C48" s="4" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="49" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B49" s="4" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C49" s="4" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="50" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B50" s="4" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C50" s="4" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="51" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B51" s="4" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C51" s="4">
         <v>547</v>
@@ -3852,42 +3849,42 @@
     </row>
     <row r="52" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B52" s="4" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C52" s="4" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="53" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B53" s="4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C53" s="4" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="54" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B54" s="4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C54" s="4" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="55" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B55" s="4" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C55" s="4" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="56" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B56" s="4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C56" s="4" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
   </sheetData>
@@ -3912,799 +3909,799 @@
     </row>
     <row r="2" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B2" s="4" t="s">
+        <v>154</v>
+      </c>
+      <c r="C2" s="4" t="s">
         <v>155</v>
-      </c>
-      <c r="C2" s="4" t="s">
-        <v>156</v>
       </c>
     </row>
     <row r="3" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B3" s="4" t="s">
+        <v>156</v>
+      </c>
+      <c r="C3" s="4" t="s">
         <v>157</v>
-      </c>
-      <c r="C3" s="4" t="s">
-        <v>158</v>
       </c>
     </row>
     <row r="4" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B4" s="4" t="s">
+        <v>158</v>
+      </c>
+      <c r="C4" s="4" t="s">
         <v>159</v>
-      </c>
-      <c r="C4" s="4" t="s">
-        <v>160</v>
       </c>
     </row>
     <row r="5" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B5" s="4" t="s">
+        <v>160</v>
+      </c>
+      <c r="C5" s="4" t="s">
         <v>161</v>
-      </c>
-      <c r="C5" s="4" t="s">
-        <v>162</v>
       </c>
     </row>
     <row r="6" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B6" s="4" t="s">
+        <v>162</v>
+      </c>
+      <c r="C6" s="4" t="s">
         <v>163</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>164</v>
       </c>
     </row>
     <row r="7" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B7" s="4" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="8" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B8" s="4" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="9" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B9" s="4" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="10" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B10" s="4" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
     </row>
     <row r="11" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B11" s="4" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="12" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B12" s="4" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
     </row>
     <row r="13" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B13" s="4" t="s">
+        <v>169</v>
+      </c>
+      <c r="C13" s="4" t="s">
         <v>170</v>
-      </c>
-      <c r="C13" s="4" t="s">
-        <v>171</v>
       </c>
     </row>
     <row r="14" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B14" s="4" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="15" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B15" s="4" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="16" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B16" s="4" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="17" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B17" s="4" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="18" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B18" s="4" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
     <row r="19" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B19" s="4" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="20" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B20" s="4" t="s">
+        <v>177</v>
+      </c>
+      <c r="C20" s="4" t="s">
         <v>178</v>
-      </c>
-      <c r="C20" s="4" t="s">
-        <v>179</v>
       </c>
     </row>
     <row r="21" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B21" s="4" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="22" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B22" s="4" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C22" s="4" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="23" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B23" s="4" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C23" s="4" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="24" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B24" s="4" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C24" s="4" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="25" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B25" s="4" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C25" s="4" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
     </row>
     <row r="26" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B26" s="4" t="s">
+        <v>184</v>
+      </c>
+      <c r="C26" s="4" t="s">
         <v>185</v>
-      </c>
-      <c r="C26" s="4" t="s">
-        <v>186</v>
       </c>
     </row>
     <row r="27" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B27" s="4" t="s">
+        <v>186</v>
+      </c>
+      <c r="C27" s="4" t="s">
         <v>187</v>
-      </c>
-      <c r="C27" s="4" t="s">
-        <v>188</v>
       </c>
     </row>
     <row r="28" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B28" s="4" t="s">
+        <v>188</v>
+      </c>
+      <c r="C28" s="4" t="s">
         <v>189</v>
-      </c>
-      <c r="C28" s="4" t="s">
-        <v>190</v>
       </c>
     </row>
     <row r="29" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B29" s="4" t="s">
+        <v>190</v>
+      </c>
+      <c r="C29" s="4" t="s">
         <v>191</v>
-      </c>
-      <c r="C29" s="4" t="s">
-        <v>192</v>
       </c>
     </row>
     <row r="30" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B30" s="4" t="s">
+        <v>192</v>
+      </c>
+      <c r="C30" s="4" t="s">
         <v>193</v>
-      </c>
-      <c r="C30" s="4" t="s">
-        <v>194</v>
       </c>
     </row>
     <row r="31" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B31" s="4" t="s">
+        <v>194</v>
+      </c>
+      <c r="C31" s="4" t="s">
         <v>195</v>
-      </c>
-      <c r="C31" s="4" t="s">
-        <v>196</v>
       </c>
     </row>
     <row r="32" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B32" s="4" t="s">
+        <v>196</v>
+      </c>
+      <c r="C32" s="4" t="s">
         <v>197</v>
-      </c>
-      <c r="C32" s="4" t="s">
-        <v>198</v>
       </c>
     </row>
     <row r="33" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B33" s="4" t="s">
+        <v>198</v>
+      </c>
+      <c r="C33" s="4" t="s">
         <v>199</v>
-      </c>
-      <c r="C33" s="4" t="s">
-        <v>200</v>
       </c>
     </row>
     <row r="34" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B34" s="4" t="s">
+        <v>200</v>
+      </c>
+      <c r="C34" s="4" t="s">
         <v>201</v>
-      </c>
-      <c r="C34" s="4" t="s">
-        <v>202</v>
       </c>
     </row>
     <row r="35" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B35" s="4" t="s">
+        <v>202</v>
+      </c>
+      <c r="C35" s="4" t="s">
         <v>203</v>
-      </c>
-      <c r="C35" s="4" t="s">
-        <v>204</v>
       </c>
     </row>
     <row r="36" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B36" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C36" s="4" t="s">
         <v>205</v>
-      </c>
-      <c r="C36" s="4" t="s">
-        <v>206</v>
       </c>
     </row>
     <row r="37" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B37" s="4" t="s">
+        <v>206</v>
+      </c>
+      <c r="C37" s="4" t="s">
         <v>207</v>
-      </c>
-      <c r="C37" s="4" t="s">
-        <v>208</v>
       </c>
     </row>
     <row r="38" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B38" s="4" t="s">
+        <v>208</v>
+      </c>
+      <c r="C38" s="4" t="s">
         <v>209</v>
-      </c>
-      <c r="C38" s="4" t="s">
-        <v>210</v>
       </c>
     </row>
     <row r="39" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B39" s="4" t="s">
+        <v>210</v>
+      </c>
+      <c r="C39" s="4" t="s">
         <v>211</v>
-      </c>
-      <c r="C39" s="4" t="s">
-        <v>212</v>
       </c>
     </row>
     <row r="40" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B40" s="4" t="s">
+        <v>212</v>
+      </c>
+      <c r="C40" s="4" t="s">
         <v>213</v>
-      </c>
-      <c r="C40" s="4" t="s">
-        <v>214</v>
       </c>
     </row>
     <row r="41" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B41" s="4" t="s">
+        <v>214</v>
+      </c>
+      <c r="C41" s="4" t="s">
         <v>215</v>
-      </c>
-      <c r="C41" s="4" t="s">
-        <v>216</v>
       </c>
     </row>
     <row r="42" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B42" s="4" t="s">
+        <v>216</v>
+      </c>
+      <c r="C42" s="4" t="s">
         <v>217</v>
-      </c>
-      <c r="C42" s="4" t="s">
-        <v>218</v>
       </c>
     </row>
     <row r="43" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B43" s="4" t="s">
+        <v>218</v>
+      </c>
+      <c r="C43" s="4" t="s">
         <v>219</v>
-      </c>
-      <c r="C43" s="4" t="s">
-        <v>220</v>
       </c>
     </row>
     <row r="44" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B44" s="4" t="s">
+        <v>220</v>
+      </c>
+      <c r="C44" s="4" t="s">
         <v>221</v>
-      </c>
-      <c r="C44" s="4" t="s">
-        <v>222</v>
       </c>
     </row>
     <row r="45" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B45" s="4" t="s">
+        <v>222</v>
+      </c>
+      <c r="C45" s="4" t="s">
         <v>223</v>
-      </c>
-      <c r="C45" s="4" t="s">
-        <v>224</v>
       </c>
     </row>
     <row r="46" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B46" s="4" t="s">
+        <v>224</v>
+      </c>
+      <c r="C46" s="4" t="s">
         <v>225</v>
-      </c>
-      <c r="C46" s="4" t="s">
-        <v>226</v>
       </c>
     </row>
     <row r="47" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B47" s="4" t="s">
+        <v>226</v>
+      </c>
+      <c r="C47" s="4" t="s">
         <v>227</v>
-      </c>
-      <c r="C47" s="4" t="s">
-        <v>228</v>
       </c>
     </row>
     <row r="48" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B48" s="4" t="s">
+        <v>228</v>
+      </c>
+      <c r="C48" s="4" t="s">
         <v>229</v>
-      </c>
-      <c r="C48" s="4" t="s">
-        <v>230</v>
       </c>
     </row>
     <row r="49" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B49" s="4" t="s">
+        <v>230</v>
+      </c>
+      <c r="C49" s="4" t="s">
         <v>231</v>
-      </c>
-      <c r="C49" s="4" t="s">
-        <v>232</v>
       </c>
     </row>
     <row r="50" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B50" s="4" t="s">
+        <v>232</v>
+      </c>
+      <c r="C50" s="4" t="s">
         <v>233</v>
-      </c>
-      <c r="C50" s="4" t="s">
-        <v>234</v>
       </c>
     </row>
     <row r="51" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B51" s="4" t="s">
+        <v>234</v>
+      </c>
+      <c r="C51" s="4" t="s">
         <v>235</v>
-      </c>
-      <c r="C51" s="4" t="s">
-        <v>236</v>
       </c>
     </row>
     <row r="52" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B52" s="4" t="s">
+        <v>236</v>
+      </c>
+      <c r="C52" s="4" t="s">
         <v>237</v>
-      </c>
-      <c r="C52" s="4" t="s">
-        <v>238</v>
       </c>
     </row>
     <row r="53" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B53" s="4" t="s">
+        <v>238</v>
+      </c>
+      <c r="C53" s="4" t="s">
         <v>239</v>
-      </c>
-      <c r="C53" s="4" t="s">
-        <v>240</v>
       </c>
     </row>
     <row r="54" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B54" s="4" t="s">
+        <v>240</v>
+      </c>
+      <c r="C54" s="4" t="s">
         <v>241</v>
-      </c>
-      <c r="C54" s="4" t="s">
-        <v>242</v>
       </c>
     </row>
     <row r="55" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B55" s="4" t="s">
+        <v>242</v>
+      </c>
+      <c r="C55" s="4" t="s">
         <v>243</v>
-      </c>
-      <c r="C55" s="4" t="s">
-        <v>244</v>
       </c>
     </row>
     <row r="56" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B56" s="4" t="s">
+        <v>244</v>
+      </c>
+      <c r="C56" s="4" t="s">
         <v>245</v>
-      </c>
-      <c r="C56" s="4" t="s">
-        <v>246</v>
       </c>
     </row>
     <row r="57" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B57" s="4" t="s">
+        <v>246</v>
+      </c>
+      <c r="C57" s="4" t="s">
         <v>247</v>
-      </c>
-      <c r="C57" s="4" t="s">
-        <v>248</v>
       </c>
     </row>
     <row r="58" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B58" s="4" t="s">
+        <v>248</v>
+      </c>
+      <c r="C58" s="4" t="s">
         <v>249</v>
-      </c>
-      <c r="C58" s="4" t="s">
-        <v>250</v>
       </c>
     </row>
     <row r="59" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B59" s="4" t="s">
+        <v>250</v>
+      </c>
+      <c r="C59" s="4" t="s">
         <v>251</v>
-      </c>
-      <c r="C59" s="4" t="s">
-        <v>252</v>
       </c>
     </row>
     <row r="60" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B60" s="4" t="s">
+        <v>252</v>
+      </c>
+      <c r="C60" s="4" t="s">
         <v>253</v>
-      </c>
-      <c r="C60" s="4" t="s">
-        <v>254</v>
       </c>
     </row>
     <row r="61" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B61" s="4" t="s">
+        <v>254</v>
+      </c>
+      <c r="C61" s="4" t="s">
         <v>255</v>
-      </c>
-      <c r="C61" s="4" t="s">
-        <v>256</v>
       </c>
     </row>
     <row r="62" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B62" s="4" t="s">
+        <v>256</v>
+      </c>
+      <c r="C62" s="4" t="s">
         <v>257</v>
-      </c>
-      <c r="C62" s="4" t="s">
-        <v>258</v>
       </c>
     </row>
     <row r="63" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B63" s="4" t="s">
+        <v>258</v>
+      </c>
+      <c r="C63" s="4" t="s">
         <v>259</v>
-      </c>
-      <c r="C63" s="4" t="s">
-        <v>260</v>
       </c>
     </row>
     <row r="64" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B64" s="4" t="s">
+        <v>260</v>
+      </c>
+      <c r="C64" s="4" t="s">
         <v>261</v>
-      </c>
-      <c r="C64" s="4" t="s">
-        <v>262</v>
       </c>
     </row>
     <row r="65" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B65" s="4" t="s">
+        <v>262</v>
+      </c>
+      <c r="C65" s="4" t="s">
         <v>263</v>
-      </c>
-      <c r="C65" s="4" t="s">
-        <v>264</v>
       </c>
     </row>
     <row r="66" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B66" s="4" t="s">
+        <v>264</v>
+      </c>
+      <c r="C66" s="4" t="s">
         <v>265</v>
-      </c>
-      <c r="C66" s="4" t="s">
-        <v>266</v>
       </c>
     </row>
     <row r="67" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B67" s="4" t="s">
+        <v>266</v>
+      </c>
+      <c r="C67" s="4" t="s">
         <v>267</v>
-      </c>
-      <c r="C67" s="4" t="s">
-        <v>268</v>
       </c>
     </row>
     <row r="68" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B68" s="4" t="s">
+        <v>268</v>
+      </c>
+      <c r="C68" s="4" t="s">
         <v>269</v>
-      </c>
-      <c r="C68" s="4" t="s">
-        <v>270</v>
       </c>
     </row>
     <row r="69" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B69" s="4" t="s">
+        <v>270</v>
+      </c>
+      <c r="C69" s="4" t="s">
         <v>271</v>
-      </c>
-      <c r="C69" s="4" t="s">
-        <v>272</v>
       </c>
     </row>
     <row r="70" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B70" s="4" t="s">
+        <v>272</v>
+      </c>
+      <c r="C70" s="4" t="s">
         <v>273</v>
-      </c>
-      <c r="C70" s="4" t="s">
-        <v>274</v>
       </c>
     </row>
     <row r="71" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B71" s="4" t="s">
+        <v>274</v>
+      </c>
+      <c r="C71" s="4" t="s">
         <v>275</v>
-      </c>
-      <c r="C71" s="4" t="s">
-        <v>276</v>
       </c>
     </row>
     <row r="72" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B72" s="4" t="s">
+        <v>276</v>
+      </c>
+      <c r="C72" s="4" t="s">
         <v>277</v>
-      </c>
-      <c r="C72" s="4" t="s">
-        <v>278</v>
       </c>
     </row>
     <row r="73" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B73" s="4" t="s">
+        <v>278</v>
+      </c>
+      <c r="C73" s="4" t="s">
         <v>279</v>
-      </c>
-      <c r="C73" s="4" t="s">
-        <v>280</v>
       </c>
     </row>
     <row r="74" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B74" s="4" t="s">
+        <v>280</v>
+      </c>
+      <c r="C74" s="4" t="s">
         <v>281</v>
-      </c>
-      <c r="C74" s="4" t="s">
-        <v>282</v>
       </c>
     </row>
     <row r="75" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B75" s="4" t="s">
+        <v>282</v>
+      </c>
+      <c r="C75" s="4" t="s">
         <v>283</v>
-      </c>
-      <c r="C75" s="4" t="s">
-        <v>284</v>
       </c>
     </row>
     <row r="76" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B76" s="4" t="s">
+        <v>284</v>
+      </c>
+      <c r="C76" s="4" t="s">
         <v>285</v>
-      </c>
-      <c r="C76" s="4" t="s">
-        <v>286</v>
       </c>
     </row>
     <row r="77" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B77" s="4" t="s">
+        <v>286</v>
+      </c>
+      <c r="C77" s="4" t="s">
         <v>287</v>
-      </c>
-      <c r="C77" s="4" t="s">
-        <v>288</v>
       </c>
     </row>
     <row r="78" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B78" s="4" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="C78" s="4" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="79" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B79" s="4" t="s">
+        <v>289</v>
+      </c>
+      <c r="C79" s="4" t="s">
         <v>290</v>
-      </c>
-      <c r="C79" s="4" t="s">
-        <v>291</v>
       </c>
     </row>
     <row r="80" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B80" s="4" t="s">
+        <v>291</v>
+      </c>
+      <c r="C80" s="4" t="s">
         <v>292</v>
-      </c>
-      <c r="C80" s="4" t="s">
-        <v>293</v>
       </c>
     </row>
     <row r="81" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B81" s="4" t="s">
+        <v>293</v>
+      </c>
+      <c r="C81" s="4" t="s">
         <v>294</v>
-      </c>
-      <c r="C81" s="4" t="s">
-        <v>295</v>
       </c>
     </row>
     <row r="82" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B82" s="4" t="s">
+        <v>295</v>
+      </c>
+      <c r="C82" s="4" t="s">
         <v>296</v>
-      </c>
-      <c r="C82" s="4" t="s">
-        <v>297</v>
       </c>
     </row>
     <row r="83" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B83" s="4" t="s">
+        <v>297</v>
+      </c>
+      <c r="C83" s="4" t="s">
         <v>298</v>
-      </c>
-      <c r="C83" s="4" t="s">
-        <v>299</v>
       </c>
     </row>
     <row r="84" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B84" s="4" t="s">
+        <v>299</v>
+      </c>
+      <c r="C84" s="4" t="s">
         <v>300</v>
-      </c>
-      <c r="C84" s="4" t="s">
-        <v>301</v>
       </c>
     </row>
     <row r="85" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B85" s="4" t="s">
+        <v>301</v>
+      </c>
+      <c r="C85" s="4" t="s">
         <v>302</v>
-      </c>
-      <c r="C85" s="4" t="s">
-        <v>303</v>
       </c>
     </row>
     <row r="86" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B86" s="4" t="s">
+        <v>303</v>
+      </c>
+      <c r="C86" s="4" t="s">
         <v>304</v>
-      </c>
-      <c r="C86" s="4" t="s">
-        <v>305</v>
       </c>
     </row>
     <row r="87" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B87" s="4" t="s">
+        <v>305</v>
+      </c>
+      <c r="C87" s="4" t="s">
         <v>306</v>
-      </c>
-      <c r="C87" s="4" t="s">
-        <v>307</v>
       </c>
     </row>
     <row r="88" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B88" s="4" t="s">
+        <v>307</v>
+      </c>
+      <c r="C88" s="4" t="s">
         <v>308</v>
-      </c>
-      <c r="C88" s="4" t="s">
-        <v>309</v>
       </c>
     </row>
     <row r="89" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B89" s="4" t="s">
+        <v>309</v>
+      </c>
+      <c r="C89" s="4" t="s">
         <v>310</v>
-      </c>
-      <c r="C89" s="4" t="s">
-        <v>311</v>
       </c>
     </row>
     <row r="90" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B90" s="4" t="s">
+        <v>311</v>
+      </c>
+      <c r="C90" s="4" t="s">
         <v>312</v>
-      </c>
-      <c r="C90" s="4" t="s">
-        <v>313</v>
       </c>
     </row>
     <row r="91" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B91" s="4" t="s">
+        <v>313</v>
+      </c>
+      <c r="C91" s="4" t="s">
         <v>314</v>
-      </c>
-      <c r="C91" s="4" t="s">
-        <v>315</v>
       </c>
     </row>
     <row r="92" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B92" s="4" t="s">
+        <v>315</v>
+      </c>
+      <c r="C92" s="4" t="s">
         <v>316</v>
-      </c>
-      <c r="C92" s="4" t="s">
-        <v>317</v>
       </c>
     </row>
     <row r="93" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B93" s="4" t="s">
+        <v>317</v>
+      </c>
+      <c r="C93" s="4" t="s">
         <v>318</v>
-      </c>
-      <c r="C93" s="4" t="s">
-        <v>319</v>
       </c>
     </row>
     <row r="94" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B94" s="4" t="s">
+        <v>319</v>
+      </c>
+      <c r="C94" s="4" t="s">
         <v>320</v>
-      </c>
-      <c r="C94" s="4" t="s">
-        <v>321</v>
       </c>
     </row>
     <row r="95" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B95" s="4" t="s">
+        <v>321</v>
+      </c>
+      <c r="C95" s="4" t="s">
         <v>322</v>
-      </c>
-      <c r="C95" s="4" t="s">
-        <v>323</v>
       </c>
     </row>
     <row r="96" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B96" s="4" t="s">
+        <v>323</v>
+      </c>
+      <c r="C96" s="4" t="s">
         <v>324</v>
-      </c>
-      <c r="C96" s="4" t="s">
-        <v>325</v>
       </c>
     </row>
     <row r="97" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B97" s="4" t="s">
+        <v>325</v>
+      </c>
+      <c r="C97" s="4" t="s">
         <v>326</v>
-      </c>
-      <c r="C97" s="4" t="s">
-        <v>327</v>
       </c>
     </row>
     <row r="98" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B98" s="4" t="s">
+        <v>327</v>
+      </c>
+      <c r="C98" s="4" t="s">
         <v>328</v>
-      </c>
-      <c r="C98" s="4" t="s">
-        <v>329</v>
       </c>
     </row>
     <row r="99" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B99" s="4" t="s">
+        <v>329</v>
+      </c>
+      <c r="C99" s="4" t="s">
         <v>330</v>
-      </c>
-      <c r="C99" s="4" t="s">
-        <v>331</v>
       </c>
     </row>
     <row r="100" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B100" s="4" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C100" s="4" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
     </row>
     <row r="101" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B101" s="4" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C101" s="4" t="s">
         <v>8</v>
@@ -4712,31 +4709,31 @@
     </row>
     <row r="102" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B102" s="4" t="s">
+        <v>332</v>
+      </c>
+      <c r="C102" s="4" t="s">
         <v>333</v>
-      </c>
-      <c r="C102" s="4" t="s">
-        <v>334</v>
       </c>
     </row>
     <row r="103" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B103" s="4" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C103" s="4" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
     </row>
     <row r="104" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B104" s="4" t="s">
+        <v>335</v>
+      </c>
+      <c r="C104" s="4" t="s">
         <v>336</v>
-      </c>
-      <c r="C104" s="4" t="s">
-        <v>337</v>
       </c>
     </row>
     <row r="105" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B105" s="4" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C105" s="4" t="s">
         <v>10</v>
@@ -4744,858 +4741,858 @@
     </row>
     <row r="106" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B106" s="4" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C106" s="4" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
     </row>
     <row r="107" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B107" s="4" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="C107" s="4" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="108" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B108" s="4" t="s">
+        <v>339</v>
+      </c>
+      <c r="C108" s="4" t="s">
         <v>340</v>
-      </c>
-      <c r="C108" s="4" t="s">
-        <v>341</v>
       </c>
     </row>
     <row r="109" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B109" s="4" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="C109" s="4" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
     </row>
     <row r="110" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B110" s="4" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C110" s="4" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
     </row>
     <row r="111" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B111" s="4" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="C111" s="4" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
     </row>
     <row r="112" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B112" s="4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C112" s="4" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
     </row>
     <row r="113" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B113" s="4" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C113" s="4" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
     </row>
     <row r="114" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B114" s="4" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C114" s="4" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
     </row>
     <row r="115" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B115" s="4" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C115" s="4" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
     </row>
     <row r="116" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B116" s="4" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="C116" s="4" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
     </row>
     <row r="117" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B117" s="4" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C117" s="4" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="118" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B118" s="4" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="C118" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="119" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B119" s="4" t="s">
+        <v>349</v>
+      </c>
+      <c r="C119" s="4" t="s">
         <v>350</v>
-      </c>
-      <c r="C119" s="4" t="s">
-        <v>351</v>
       </c>
     </row>
     <row r="120" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B120" s="4" t="s">
+        <v>351</v>
+      </c>
+      <c r="C120" s="4" t="s">
         <v>352</v>
-      </c>
-      <c r="C120" s="4" t="s">
-        <v>353</v>
       </c>
     </row>
     <row r="121" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B121" s="4" t="s">
+        <v>353</v>
+      </c>
+      <c r="C121" s="4" t="s">
         <v>354</v>
-      </c>
-      <c r="C121" s="4" t="s">
-        <v>355</v>
       </c>
     </row>
     <row r="122" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B122" s="4" t="s">
+        <v>355</v>
+      </c>
+      <c r="C122" s="4" t="s">
         <v>356</v>
-      </c>
-      <c r="C122" s="4" t="s">
-        <v>357</v>
       </c>
     </row>
     <row r="123" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B123" s="4" t="s">
+        <v>357</v>
+      </c>
+      <c r="C123" s="4" t="s">
         <v>358</v>
-      </c>
-      <c r="C123" s="4" t="s">
-        <v>359</v>
       </c>
     </row>
     <row r="124" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B124" s="4" t="s">
+        <v>359</v>
+      </c>
+      <c r="C124" s="4" t="s">
         <v>360</v>
-      </c>
-      <c r="C124" s="4" t="s">
-        <v>361</v>
       </c>
     </row>
     <row r="125" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B125" s="4" t="s">
+        <v>361</v>
+      </c>
+      <c r="C125" s="4" t="s">
         <v>362</v>
-      </c>
-      <c r="C125" s="4" t="s">
-        <v>363</v>
       </c>
     </row>
     <row r="126" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B126" s="4" t="s">
+        <v>363</v>
+      </c>
+      <c r="C126" s="4" t="s">
         <v>364</v>
-      </c>
-      <c r="C126" s="4" t="s">
-        <v>365</v>
       </c>
     </row>
     <row r="127" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B127" s="4" t="s">
+        <v>365</v>
+      </c>
+      <c r="C127" s="4" t="s">
         <v>366</v>
-      </c>
-      <c r="C127" s="4" t="s">
-        <v>367</v>
       </c>
     </row>
     <row r="128" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B128" s="4" t="s">
+        <v>367</v>
+      </c>
+      <c r="C128" s="4" t="s">
         <v>368</v>
-      </c>
-      <c r="C128" s="4" t="s">
-        <v>369</v>
       </c>
     </row>
     <row r="129" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B129" s="4" t="s">
+        <v>369</v>
+      </c>
+      <c r="C129" s="4" t="s">
         <v>370</v>
-      </c>
-      <c r="C129" s="4" t="s">
-        <v>371</v>
       </c>
     </row>
     <row r="130" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B130" s="4" t="s">
+        <v>371</v>
+      </c>
+      <c r="C130" s="4" t="s">
         <v>372</v>
-      </c>
-      <c r="C130" s="4" t="s">
-        <v>373</v>
       </c>
     </row>
     <row r="131" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B131" s="4" t="s">
+        <v>373</v>
+      </c>
+      <c r="C131" s="4" t="s">
         <v>374</v>
-      </c>
-      <c r="C131" s="4" t="s">
-        <v>375</v>
       </c>
     </row>
     <row r="132" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B132" s="4" t="s">
+        <v>375</v>
+      </c>
+      <c r="C132" s="4" t="s">
         <v>376</v>
-      </c>
-      <c r="C132" s="4" t="s">
-        <v>377</v>
       </c>
     </row>
     <row r="133" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B133" s="4" t="s">
+        <v>377</v>
+      </c>
+      <c r="C133" s="4" t="s">
         <v>378</v>
-      </c>
-      <c r="C133" s="4" t="s">
-        <v>379</v>
       </c>
     </row>
     <row r="134" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B134" s="4" t="s">
+        <v>379</v>
+      </c>
+      <c r="C134" s="4" t="s">
         <v>380</v>
-      </c>
-      <c r="C134" s="4" t="s">
-        <v>381</v>
       </c>
     </row>
     <row r="135" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B135" s="4" t="s">
+        <v>381</v>
+      </c>
+      <c r="C135" s="4" t="s">
         <v>382</v>
-      </c>
-      <c r="C135" s="4" t="s">
-        <v>383</v>
       </c>
     </row>
     <row r="136" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B136" s="4" t="s">
+        <v>383</v>
+      </c>
+      <c r="C136" s="4" t="s">
         <v>384</v>
-      </c>
-      <c r="C136" s="4" t="s">
-        <v>385</v>
       </c>
     </row>
     <row r="137" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B137" s="4" t="s">
+        <v>385</v>
+      </c>
+      <c r="C137" s="4" t="s">
         <v>386</v>
-      </c>
-      <c r="C137" s="4" t="s">
-        <v>387</v>
       </c>
     </row>
     <row r="138" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B138" s="4" t="s">
+        <v>387</v>
+      </c>
+      <c r="C138" s="4" t="s">
         <v>388</v>
-      </c>
-      <c r="C138" s="4" t="s">
-        <v>389</v>
       </c>
     </row>
     <row r="139" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B139" s="4" t="s">
+        <v>389</v>
+      </c>
+      <c r="C139" s="4" t="s">
         <v>390</v>
-      </c>
-      <c r="C139" s="4" t="s">
-        <v>391</v>
       </c>
     </row>
     <row r="140" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B140" s="4" t="s">
+        <v>391</v>
+      </c>
+      <c r="C140" s="4" t="s">
         <v>392</v>
-      </c>
-      <c r="C140" s="4" t="s">
-        <v>393</v>
       </c>
     </row>
     <row r="141" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B141" s="4" t="s">
+        <v>393</v>
+      </c>
+      <c r="C141" s="4" t="s">
         <v>394</v>
-      </c>
-      <c r="C141" s="4" t="s">
-        <v>395</v>
       </c>
     </row>
     <row r="142" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B142" s="4" t="s">
+        <v>395</v>
+      </c>
+      <c r="C142" s="4" t="s">
         <v>396</v>
-      </c>
-      <c r="C142" s="4" t="s">
-        <v>397</v>
       </c>
     </row>
     <row r="143" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B143" s="4" t="s">
+        <v>397</v>
+      </c>
+      <c r="C143" s="4" t="s">
         <v>398</v>
-      </c>
-      <c r="C143" s="4" t="s">
-        <v>399</v>
       </c>
     </row>
     <row r="144" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B144" s="4" t="s">
+        <v>399</v>
+      </c>
+      <c r="C144" s="4" t="s">
         <v>400</v>
-      </c>
-      <c r="C144" s="4" t="s">
-        <v>401</v>
       </c>
     </row>
     <row r="145" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B145" s="4" t="s">
+        <v>401</v>
+      </c>
+      <c r="C145" s="4" t="s">
         <v>402</v>
-      </c>
-      <c r="C145" s="4" t="s">
-        <v>403</v>
       </c>
     </row>
     <row r="146" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B146" s="4" t="s">
+        <v>403</v>
+      </c>
+      <c r="C146" s="4" t="s">
         <v>404</v>
-      </c>
-      <c r="C146" s="4" t="s">
-        <v>405</v>
       </c>
     </row>
     <row r="147" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B147" s="4" t="s">
+        <v>405</v>
+      </c>
+      <c r="C147" s="4" t="s">
         <v>406</v>
-      </c>
-      <c r="C147" s="4" t="s">
-        <v>407</v>
       </c>
     </row>
     <row r="148" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B148" s="4" t="s">
+        <v>407</v>
+      </c>
+      <c r="C148" s="4" t="s">
         <v>408</v>
-      </c>
-      <c r="C148" s="4" t="s">
-        <v>409</v>
       </c>
     </row>
     <row r="149" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B149" s="4" t="s">
+        <v>409</v>
+      </c>
+      <c r="C149" s="4" t="s">
         <v>410</v>
-      </c>
-      <c r="C149" s="4" t="s">
-        <v>411</v>
       </c>
     </row>
     <row r="150" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B150" s="4" t="s">
+        <v>411</v>
+      </c>
+      <c r="C150" s="4" t="s">
         <v>412</v>
-      </c>
-      <c r="C150" s="4" t="s">
-        <v>413</v>
       </c>
     </row>
     <row r="151" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B151" s="4" t="s">
+        <v>413</v>
+      </c>
+      <c r="C151" s="4" t="s">
         <v>414</v>
-      </c>
-      <c r="C151" s="4" t="s">
-        <v>415</v>
       </c>
     </row>
     <row r="152" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B152" s="4" t="s">
+        <v>415</v>
+      </c>
+      <c r="C152" s="4" t="s">
         <v>416</v>
-      </c>
-      <c r="C152" s="4" t="s">
-        <v>417</v>
       </c>
     </row>
     <row r="153" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B153" s="4" t="s">
+        <v>417</v>
+      </c>
+      <c r="C153" s="4" t="s">
         <v>418</v>
-      </c>
-      <c r="C153" s="4" t="s">
-        <v>419</v>
       </c>
     </row>
     <row r="154" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B154" s="4" t="s">
+        <v>419</v>
+      </c>
+      <c r="C154" s="4" t="s">
         <v>420</v>
-      </c>
-      <c r="C154" s="4" t="s">
-        <v>421</v>
       </c>
     </row>
     <row r="155" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B155" s="4" t="s">
+        <v>421</v>
+      </c>
+      <c r="C155" s="4" t="s">
         <v>422</v>
-      </c>
-      <c r="C155" s="4" t="s">
-        <v>423</v>
       </c>
     </row>
     <row r="156" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B156" s="4" t="s">
+        <v>423</v>
+      </c>
+      <c r="C156" s="4" t="s">
         <v>424</v>
-      </c>
-      <c r="C156" s="4" t="s">
-        <v>425</v>
       </c>
     </row>
     <row r="157" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B157" s="4" t="s">
+        <v>425</v>
+      </c>
+      <c r="C157" s="4" t="s">
         <v>426</v>
-      </c>
-      <c r="C157" s="4" t="s">
-        <v>427</v>
       </c>
     </row>
     <row r="158" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B158" s="4" t="s">
+        <v>427</v>
+      </c>
+      <c r="C158" s="4" t="s">
         <v>428</v>
-      </c>
-      <c r="C158" s="4" t="s">
-        <v>429</v>
       </c>
     </row>
     <row r="159" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B159" s="4" t="s">
+        <v>429</v>
+      </c>
+      <c r="C159" s="4" t="s">
         <v>430</v>
-      </c>
-      <c r="C159" s="4" t="s">
-        <v>431</v>
       </c>
     </row>
     <row r="160" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B160" s="4" t="s">
+        <v>431</v>
+      </c>
+      <c r="C160" s="4" t="s">
         <v>432</v>
-      </c>
-      <c r="C160" s="4" t="s">
-        <v>433</v>
       </c>
     </row>
     <row r="161" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B161" s="4" t="s">
+        <v>433</v>
+      </c>
+      <c r="C161" s="4" t="s">
         <v>434</v>
-      </c>
-      <c r="C161" s="4" t="s">
-        <v>435</v>
       </c>
     </row>
     <row r="162" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B162" s="4" t="s">
+        <v>435</v>
+      </c>
+      <c r="C162" s="4" t="s">
         <v>436</v>
-      </c>
-      <c r="C162" s="4" t="s">
-        <v>437</v>
       </c>
     </row>
     <row r="163" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B163" s="4" t="s">
+        <v>437</v>
+      </c>
+      <c r="C163" s="4" t="s">
         <v>438</v>
-      </c>
-      <c r="C163" s="4" t="s">
-        <v>439</v>
       </c>
     </row>
     <row r="164" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B164" s="4" t="s">
+        <v>439</v>
+      </c>
+      <c r="C164" s="4" t="s">
         <v>440</v>
-      </c>
-      <c r="C164" s="4" t="s">
-        <v>441</v>
       </c>
     </row>
     <row r="165" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B165" s="4" t="s">
+        <v>441</v>
+      </c>
+      <c r="C165" s="4" t="s">
         <v>442</v>
-      </c>
-      <c r="C165" s="4" t="s">
-        <v>443</v>
       </c>
     </row>
     <row r="166" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B166" s="4" t="s">
+        <v>443</v>
+      </c>
+      <c r="C166" s="4" t="s">
         <v>444</v>
-      </c>
-      <c r="C166" s="4" t="s">
-        <v>445</v>
       </c>
     </row>
     <row r="167" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B167" s="4" t="s">
+        <v>445</v>
+      </c>
+      <c r="C167" s="4" t="s">
         <v>446</v>
-      </c>
-      <c r="C167" s="4" t="s">
-        <v>447</v>
       </c>
     </row>
     <row r="168" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B168" s="4" t="s">
+        <v>447</v>
+      </c>
+      <c r="C168" s="4" t="s">
         <v>448</v>
-      </c>
-      <c r="C168" s="4" t="s">
-        <v>449</v>
       </c>
     </row>
     <row r="169" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B169" s="4" t="s">
+        <v>449</v>
+      </c>
+      <c r="C169" s="4" t="s">
         <v>450</v>
-      </c>
-      <c r="C169" s="4" t="s">
-        <v>451</v>
       </c>
     </row>
     <row r="170" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B170" s="4" t="s">
+        <v>451</v>
+      </c>
+      <c r="C170" s="4" t="s">
         <v>452</v>
-      </c>
-      <c r="C170" s="4" t="s">
-        <v>453</v>
       </c>
     </row>
     <row r="171" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B171" s="4" t="s">
+        <v>453</v>
+      </c>
+      <c r="C171" s="4" t="s">
         <v>454</v>
-      </c>
-      <c r="C171" s="4" t="s">
-        <v>455</v>
       </c>
     </row>
     <row r="172" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B172" s="4" t="s">
+        <v>455</v>
+      </c>
+      <c r="C172" s="4" t="s">
         <v>456</v>
-      </c>
-      <c r="C172" s="4" t="s">
-        <v>457</v>
       </c>
     </row>
     <row r="173" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B173" s="4" t="s">
+        <v>457</v>
+      </c>
+      <c r="C173" s="4" t="s">
         <v>458</v>
-      </c>
-      <c r="C173" s="4" t="s">
-        <v>459</v>
       </c>
     </row>
     <row r="174" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B174" s="4" t="s">
+        <v>459</v>
+      </c>
+      <c r="C174" s="4" t="s">
         <v>460</v>
-      </c>
-      <c r="C174" s="4" t="s">
-        <v>461</v>
       </c>
     </row>
     <row r="175" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B175" s="4" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C175" s="4" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
     </row>
     <row r="176" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B176" s="4" t="s">
+        <v>462</v>
+      </c>
+      <c r="C176" s="4" t="s">
         <v>463</v>
-      </c>
-      <c r="C176" s="4" t="s">
-        <v>464</v>
       </c>
     </row>
     <row r="177" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B177" s="4" t="s">
+        <v>464</v>
+      </c>
+      <c r="C177" s="4" t="s">
         <v>465</v>
-      </c>
-      <c r="C177" s="4" t="s">
-        <v>466</v>
       </c>
     </row>
     <row r="178" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B178" s="4" t="s">
+        <v>466</v>
+      </c>
+      <c r="C178" s="4" t="s">
         <v>467</v>
-      </c>
-      <c r="C178" s="4" t="s">
-        <v>468</v>
       </c>
     </row>
     <row r="179" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B179" s="4" t="s">
+        <v>468</v>
+      </c>
+      <c r="C179" s="4" t="s">
         <v>469</v>
-      </c>
-      <c r="C179" s="4" t="s">
-        <v>470</v>
       </c>
     </row>
     <row r="180" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B180" s="4" t="s">
+        <v>470</v>
+      </c>
+      <c r="C180" s="4" t="s">
         <v>471</v>
-      </c>
-      <c r="C180" s="4" t="s">
-        <v>472</v>
       </c>
     </row>
     <row r="181" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B181" s="4" t="s">
+        <v>472</v>
+      </c>
+      <c r="C181" s="4" t="s">
         <v>473</v>
-      </c>
-      <c r="C181" s="4" t="s">
-        <v>474</v>
       </c>
     </row>
     <row r="182" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B182" s="4" t="s">
+        <v>474</v>
+      </c>
+      <c r="C182" s="4" t="s">
         <v>475</v>
-      </c>
-      <c r="C182" s="4" t="s">
-        <v>476</v>
       </c>
     </row>
     <row r="183" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B183" s="4" t="s">
+        <v>476</v>
+      </c>
+      <c r="C183" s="4" t="s">
         <v>477</v>
-      </c>
-      <c r="C183" s="4" t="s">
-        <v>478</v>
       </c>
     </row>
     <row r="184" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B184" s="4" t="s">
+        <v>478</v>
+      </c>
+      <c r="C184" s="4" t="s">
         <v>479</v>
-      </c>
-      <c r="C184" s="4" t="s">
-        <v>480</v>
       </c>
     </row>
     <row r="185" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B185" s="4" t="s">
+        <v>480</v>
+      </c>
+      <c r="C185" s="4" t="s">
         <v>481</v>
-      </c>
-      <c r="C185" s="4" t="s">
-        <v>482</v>
       </c>
     </row>
     <row r="186" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B186" s="4" t="s">
+        <v>482</v>
+      </c>
+      <c r="C186" s="4" t="s">
         <v>483</v>
-      </c>
-      <c r="C186" s="4" t="s">
-        <v>484</v>
       </c>
     </row>
     <row r="187" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B187" s="4" t="s">
+        <v>484</v>
+      </c>
+      <c r="C187" s="4" t="s">
         <v>485</v>
-      </c>
-      <c r="C187" s="4" t="s">
-        <v>486</v>
       </c>
     </row>
     <row r="188" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B188" s="4" t="s">
+        <v>486</v>
+      </c>
+      <c r="C188" s="4" t="s">
         <v>487</v>
-      </c>
-      <c r="C188" s="4" t="s">
-        <v>488</v>
       </c>
     </row>
     <row r="189" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B189" s="4" t="s">
+        <v>488</v>
+      </c>
+      <c r="C189" s="4" t="s">
         <v>489</v>
-      </c>
-      <c r="C189" s="4" t="s">
-        <v>490</v>
       </c>
     </row>
     <row r="190" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B190" s="4" t="s">
+        <v>490</v>
+      </c>
+      <c r="C190" s="4" t="s">
         <v>491</v>
-      </c>
-      <c r="C190" s="4" t="s">
-        <v>492</v>
       </c>
     </row>
     <row r="191" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B191" s="4" t="s">
+        <v>492</v>
+      </c>
+      <c r="C191" s="4" t="s">
         <v>493</v>
-      </c>
-      <c r="C191" s="4" t="s">
-        <v>494</v>
       </c>
     </row>
     <row r="192" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B192" s="4" t="s">
+        <v>494</v>
+      </c>
+      <c r="C192" s="4" t="s">
         <v>495</v>
-      </c>
-      <c r="C192" s="4" t="s">
-        <v>496</v>
       </c>
     </row>
     <row r="193" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B193" s="4" t="s">
+        <v>496</v>
+      </c>
+      <c r="C193" s="4" t="s">
         <v>497</v>
-      </c>
-      <c r="C193" s="4" t="s">
-        <v>498</v>
       </c>
     </row>
     <row r="194" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B194" s="4" t="s">
+        <v>498</v>
+      </c>
+      <c r="C194" s="4" t="s">
         <v>499</v>
-      </c>
-      <c r="C194" s="4" t="s">
-        <v>500</v>
       </c>
     </row>
     <row r="195" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B195" s="4" t="s">
+        <v>500</v>
+      </c>
+      <c r="C195" s="4" t="s">
         <v>501</v>
-      </c>
-      <c r="C195" s="4" t="s">
-        <v>502</v>
       </c>
     </row>
     <row r="196" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B196" s="4" t="s">
+        <v>502</v>
+      </c>
+      <c r="C196" s="4" t="s">
         <v>503</v>
-      </c>
-      <c r="C196" s="4" t="s">
-        <v>504</v>
       </c>
     </row>
     <row r="197" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B197" s="4" t="s">
+        <v>504</v>
+      </c>
+      <c r="C197" s="4" t="s">
         <v>505</v>
-      </c>
-      <c r="C197" s="4" t="s">
-        <v>506</v>
       </c>
     </row>
     <row r="198" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B198" s="4" t="s">
+        <v>506</v>
+      </c>
+      <c r="C198" s="4" t="s">
         <v>507</v>
-      </c>
-      <c r="C198" s="4" t="s">
-        <v>508</v>
       </c>
     </row>
     <row r="199" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B199" s="4" t="s">
+        <v>508</v>
+      </c>
+      <c r="C199" s="4" t="s">
         <v>509</v>
-      </c>
-      <c r="C199" s="4" t="s">
-        <v>510</v>
       </c>
     </row>
     <row r="200" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B200" s="4" t="s">
+        <v>510</v>
+      </c>
+      <c r="C200" s="4" t="s">
         <v>511</v>
-      </c>
-      <c r="C200" s="4" t="s">
-        <v>512</v>
       </c>
     </row>
     <row r="201" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B201" s="4" t="s">
+        <v>512</v>
+      </c>
+      <c r="C201" s="4" t="s">
         <v>513</v>
-      </c>
-      <c r="C201" s="4" t="s">
-        <v>514</v>
       </c>
     </row>
     <row r="202" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B202" s="4" t="s">
+        <v>514</v>
+      </c>
+      <c r="C202" s="4" t="s">
         <v>515</v>
-      </c>
-      <c r="C202" s="4" t="s">
-        <v>516</v>
       </c>
     </row>
     <row r="203" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B203" s="4" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="C203" s="4" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
     </row>
     <row r="204" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B204" s="4" t="s">
+        <v>517</v>
+      </c>
+      <c r="C204" s="4" t="s">
         <v>518</v>
-      </c>
-      <c r="C204" s="4" t="s">
-        <v>519</v>
       </c>
     </row>
     <row r="205" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B205" s="4" t="s">
+        <v>519</v>
+      </c>
+      <c r="C205" s="4" t="s">
         <v>520</v>
-      </c>
-      <c r="C205" s="4" t="s">
-        <v>521</v>
       </c>
     </row>
     <row r="206" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B206" s="4" t="s">
+        <v>521</v>
+      </c>
+      <c r="C206" s="4" t="s">
         <v>522</v>
-      </c>
-      <c r="C206" s="4" t="s">
-        <v>523</v>
       </c>
     </row>
     <row r="207" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B207" s="4" t="s">
+        <v>523</v>
+      </c>
+      <c r="C207" s="4" t="s">
         <v>524</v>
-      </c>
-      <c r="C207" s="4" t="s">
-        <v>525</v>
       </c>
     </row>
     <row r="208" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B208" s="4" t="s">
+        <v>525</v>
+      </c>
+      <c r="C208" s="4" t="s">
         <v>526</v>
-      </c>
-      <c r="C208" s="4" t="s">
-        <v>527</v>
       </c>
     </row>
     <row r="209" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B209" s="4" t="s">
+        <v>527</v>
+      </c>
+      <c r="C209" s="4" t="s">
         <v>528</v>
-      </c>
-      <c r="C209" s="4" t="s">
-        <v>529</v>
       </c>
     </row>
     <row r="210" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B210" s="4" t="s">
+        <v>529</v>
+      </c>
+      <c r="C210" s="4" t="s">
         <v>530</v>
-      </c>
-      <c r="C210" s="4" t="s">
-        <v>531</v>
       </c>
     </row>
     <row r="211" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B211" s="4" t="s">
+        <v>531</v>
+      </c>
+      <c r="C211" s="4" t="s">
         <v>532</v>
-      </c>
-      <c r="C211" s="4" t="s">
-        <v>533</v>
       </c>
     </row>
     <row r="212" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B212" s="4" t="s">
+        <v>533</v>
+      </c>
+      <c r="C212" s="4" t="s">
         <v>534</v>
-      </c>
-      <c r="C212" s="4" t="s">
-        <v>535</v>
       </c>
     </row>
   </sheetData>
@@ -5619,778 +5616,778 @@
     </row>
     <row r="2" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B2" s="3" t="s">
+        <v>535</v>
+      </c>
+      <c r="C2" s="3" t="s">
         <v>536</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>537</v>
       </c>
     </row>
     <row r="3" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B3" s="3" t="s">
+        <v>537</v>
+      </c>
+      <c r="C3" s="3" t="s">
         <v>538</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>539</v>
       </c>
     </row>
     <row r="4" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B4" s="3" t="s">
+        <v>539</v>
+      </c>
+      <c r="C4" s="3" t="s">
         <v>540</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>541</v>
       </c>
     </row>
     <row r="5" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B5" s="3" t="s">
+        <v>541</v>
+      </c>
+      <c r="C5" s="3" t="s">
         <v>542</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>543</v>
       </c>
     </row>
     <row r="6" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B6" s="3" t="s">
+        <v>543</v>
+      </c>
+      <c r="C6" s="3" t="s">
         <v>544</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>545</v>
       </c>
     </row>
     <row r="7" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B7" s="3" t="s">
+        <v>545</v>
+      </c>
+      <c r="C7" s="3" t="s">
         <v>546</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>547</v>
       </c>
     </row>
     <row r="8" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B8" s="3" t="s">
+        <v>547</v>
+      </c>
+      <c r="C8" s="3" t="s">
         <v>548</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>549</v>
       </c>
     </row>
     <row r="9" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B9" s="3" t="s">
+        <v>549</v>
+      </c>
+      <c r="C9" s="3" t="s">
         <v>550</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>551</v>
       </c>
     </row>
     <row r="10" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B10" s="3" t="s">
+        <v>551</v>
+      </c>
+      <c r="C10" s="3" t="s">
         <v>552</v>
-      </c>
-      <c r="C10" s="3" t="s">
-        <v>553</v>
       </c>
     </row>
     <row r="11" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B11" s="3" t="s">
+        <v>553</v>
+      </c>
+      <c r="C11" s="3" t="s">
         <v>554</v>
-      </c>
-      <c r="C11" s="3" t="s">
-        <v>555</v>
       </c>
     </row>
     <row r="12" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B12" s="3" t="s">
+        <v>555</v>
+      </c>
+      <c r="C12" s="3" t="s">
         <v>556</v>
-      </c>
-      <c r="C12" s="3" t="s">
-        <v>557</v>
       </c>
     </row>
     <row r="13" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B13" s="3" t="s">
+        <v>557</v>
+      </c>
+      <c r="C13" s="3" t="s">
         <v>558</v>
-      </c>
-      <c r="C13" s="3" t="s">
-        <v>559</v>
       </c>
     </row>
     <row r="14" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B14" s="3" t="s">
+        <v>559</v>
+      </c>
+      <c r="C14" s="3" t="s">
         <v>560</v>
-      </c>
-      <c r="C14" s="3" t="s">
-        <v>561</v>
       </c>
     </row>
     <row r="15" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B15" s="3" t="s">
+        <v>561</v>
+      </c>
+      <c r="C15" s="3" t="s">
         <v>562</v>
-      </c>
-      <c r="C15" s="3" t="s">
-        <v>563</v>
       </c>
     </row>
     <row r="16" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B16" s="3" t="s">
+        <v>563</v>
+      </c>
+      <c r="C16" s="3" t="s">
         <v>564</v>
-      </c>
-      <c r="C16" s="3" t="s">
-        <v>565</v>
       </c>
     </row>
     <row r="17" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B17" s="3" t="s">
+        <v>565</v>
+      </c>
+      <c r="C17" s="3" t="s">
         <v>566</v>
-      </c>
-      <c r="C17" s="3" t="s">
-        <v>567</v>
       </c>
     </row>
     <row r="18" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B18" s="3" t="s">
+        <v>567</v>
+      </c>
+      <c r="C18" s="3" t="s">
         <v>568</v>
-      </c>
-      <c r="C18" s="3" t="s">
-        <v>569</v>
       </c>
     </row>
     <row r="19" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B19" s="3" t="s">
+        <v>569</v>
+      </c>
+      <c r="C19" s="3" t="s">
         <v>570</v>
-      </c>
-      <c r="C19" s="3" t="s">
-        <v>571</v>
       </c>
     </row>
     <row r="20" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B20" s="3" t="s">
+        <v>571</v>
+      </c>
+      <c r="C20" s="3" t="s">
         <v>572</v>
-      </c>
-      <c r="C20" s="3" t="s">
-        <v>573</v>
       </c>
     </row>
     <row r="21" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B21" s="3" t="s">
+        <v>573</v>
+      </c>
+      <c r="C21" s="3" t="s">
         <v>574</v>
-      </c>
-      <c r="C21" s="3" t="s">
-        <v>575</v>
       </c>
     </row>
     <row r="22" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B22" s="3" t="s">
+        <v>575</v>
+      </c>
+      <c r="C22" s="3" t="s">
         <v>576</v>
-      </c>
-      <c r="C22" s="3" t="s">
-        <v>577</v>
       </c>
     </row>
     <row r="23" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B23" s="3" t="s">
+        <v>577</v>
+      </c>
+      <c r="C23" s="3" t="s">
         <v>578</v>
-      </c>
-      <c r="C23" s="3" t="s">
-        <v>579</v>
       </c>
     </row>
     <row r="24" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B24" s="3" t="s">
+        <v>579</v>
+      </c>
+      <c r="C24" s="3" t="s">
         <v>580</v>
-      </c>
-      <c r="C24" s="3" t="s">
-        <v>581</v>
       </c>
     </row>
     <row r="25" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B25" s="3" t="s">
+        <v>581</v>
+      </c>
+      <c r="C25" s="3" t="s">
         <v>582</v>
-      </c>
-      <c r="C25" s="3" t="s">
-        <v>583</v>
       </c>
     </row>
     <row r="26" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B26" s="3" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
     </row>
     <row r="27" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B27" s="3" t="s">
+        <v>584</v>
+      </c>
+      <c r="C27" s="3" t="s">
         <v>585</v>
-      </c>
-      <c r="C27" s="3" t="s">
-        <v>586</v>
       </c>
     </row>
     <row r="28" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B28" s="3" t="s">
+        <v>586</v>
+      </c>
+      <c r="C28" s="3" t="s">
         <v>587</v>
-      </c>
-      <c r="C28" s="3" t="s">
-        <v>588</v>
       </c>
     </row>
     <row r="29" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B29" s="3" t="s">
+        <v>588</v>
+      </c>
+      <c r="C29" s="3" t="s">
         <v>589</v>
-      </c>
-      <c r="C29" s="3" t="s">
-        <v>590</v>
       </c>
     </row>
     <row r="30" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B30" s="3" t="s">
+        <v>590</v>
+      </c>
+      <c r="C30" s="3" t="s">
         <v>591</v>
-      </c>
-      <c r="C30" s="3" t="s">
-        <v>592</v>
       </c>
     </row>
     <row r="31" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B31" s="3" t="s">
+        <v>592</v>
+      </c>
+      <c r="C31" s="3" t="s">
         <v>593</v>
-      </c>
-      <c r="C31" s="3" t="s">
-        <v>594</v>
       </c>
     </row>
     <row r="32" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B32" s="3" t="s">
+        <v>594</v>
+      </c>
+      <c r="C32" s="3" t="s">
         <v>595</v>
-      </c>
-      <c r="C32" s="3" t="s">
-        <v>596</v>
       </c>
     </row>
     <row r="33" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B33" s="3" t="s">
+        <v>596</v>
+      </c>
+      <c r="C33" s="3" t="s">
         <v>597</v>
-      </c>
-      <c r="C33" s="3" t="s">
-        <v>598</v>
       </c>
     </row>
     <row r="34" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B34" s="3" t="s">
+        <v>598</v>
+      </c>
+      <c r="C34" s="3" t="s">
         <v>599</v>
-      </c>
-      <c r="C34" s="3" t="s">
-        <v>600</v>
       </c>
     </row>
     <row r="35" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B35" s="3" t="s">
+        <v>600</v>
+      </c>
+      <c r="C35" s="3" t="s">
         <v>601</v>
-      </c>
-      <c r="C35" s="3" t="s">
-        <v>602</v>
       </c>
     </row>
     <row r="36" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B36" s="3" t="s">
+        <v>602</v>
+      </c>
+      <c r="C36" s="3" t="s">
         <v>603</v>
-      </c>
-      <c r="C36" s="3" t="s">
-        <v>604</v>
       </c>
     </row>
     <row r="37" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B37" s="3" t="s">
+        <v>604</v>
+      </c>
+      <c r="C37" s="3" t="s">
         <v>605</v>
-      </c>
-      <c r="C37" s="3" t="s">
-        <v>606</v>
       </c>
     </row>
     <row r="38" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B38" s="3" t="s">
+        <v>606</v>
+      </c>
+      <c r="C38" s="3" t="s">
         <v>607</v>
-      </c>
-      <c r="C38" s="3" t="s">
-        <v>608</v>
       </c>
     </row>
     <row r="39" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B39" s="3" t="s">
+        <v>608</v>
+      </c>
+      <c r="C39" s="3" t="s">
         <v>609</v>
-      </c>
-      <c r="C39" s="3" t="s">
-        <v>610</v>
       </c>
     </row>
     <row r="40" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B40" s="3" t="s">
+        <v>610</v>
+      </c>
+      <c r="C40" s="3" t="s">
         <v>611</v>
-      </c>
-      <c r="C40" s="3" t="s">
-        <v>612</v>
       </c>
     </row>
     <row r="41" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B41" s="3" t="s">
+        <v>612</v>
+      </c>
+      <c r="C41" s="3" t="s">
         <v>613</v>
-      </c>
-      <c r="C41" s="3" t="s">
-        <v>614</v>
       </c>
     </row>
     <row r="42" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B42" s="3" t="s">
+        <v>614</v>
+      </c>
+      <c r="C42" s="3" t="s">
         <v>615</v>
-      </c>
-      <c r="C42" s="3" t="s">
-        <v>616</v>
       </c>
     </row>
     <row r="43" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B43" s="3" t="s">
+        <v>616</v>
+      </c>
+      <c r="C43" s="3" t="s">
         <v>617</v>
-      </c>
-      <c r="C43" s="3" t="s">
-        <v>618</v>
       </c>
     </row>
     <row r="44" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B44" s="3" t="s">
+        <v>618</v>
+      </c>
+      <c r="C44" s="3" t="s">
         <v>619</v>
-      </c>
-      <c r="C44" s="3" t="s">
-        <v>620</v>
       </c>
     </row>
     <row r="45" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B45" s="3" t="s">
+        <v>620</v>
+      </c>
+      <c r="C45" s="3" t="s">
         <v>621</v>
-      </c>
-      <c r="C45" s="3" t="s">
-        <v>622</v>
       </c>
     </row>
     <row r="46" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B46" s="3" t="s">
+        <v>622</v>
+      </c>
+      <c r="C46" s="3" t="s">
         <v>623</v>
-      </c>
-      <c r="C46" s="3" t="s">
-        <v>624</v>
       </c>
     </row>
     <row r="47" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B47" s="3" t="s">
+        <v>624</v>
+      </c>
+      <c r="C47" s="3" t="s">
         <v>625</v>
-      </c>
-      <c r="C47" s="3" t="s">
-        <v>626</v>
       </c>
     </row>
     <row r="48" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B48" s="3" t="s">
+        <v>626</v>
+      </c>
+      <c r="C48" s="3" t="s">
         <v>627</v>
-      </c>
-      <c r="C48" s="3" t="s">
-        <v>628</v>
       </c>
     </row>
     <row r="49" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B49" s="3" t="s">
+        <v>628</v>
+      </c>
+      <c r="C49" s="3" t="s">
         <v>629</v>
-      </c>
-      <c r="C49" s="3" t="s">
-        <v>630</v>
       </c>
     </row>
     <row r="50" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B50" s="3" t="s">
+        <v>630</v>
+      </c>
+      <c r="C50" s="3" t="s">
         <v>631</v>
-      </c>
-      <c r="C50" s="3" t="s">
-        <v>632</v>
       </c>
     </row>
     <row r="51" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B51" s="3" t="s">
+        <v>632</v>
+      </c>
+      <c r="C51" s="3" t="s">
         <v>633</v>
-      </c>
-      <c r="C51" s="3" t="s">
-        <v>634</v>
       </c>
     </row>
     <row r="52" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B52" s="3" t="s">
+        <v>634</v>
+      </c>
+      <c r="C52" s="3" t="s">
         <v>635</v>
-      </c>
-      <c r="C52" s="3" t="s">
-        <v>636</v>
       </c>
     </row>
     <row r="53" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B53" s="3" t="s">
+        <v>636</v>
+      </c>
+      <c r="C53" s="3" t="s">
         <v>637</v>
-      </c>
-      <c r="C53" s="3" t="s">
-        <v>638</v>
       </c>
     </row>
     <row r="54" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B54" s="3" t="s">
+        <v>638</v>
+      </c>
+      <c r="C54" s="3" t="s">
         <v>639</v>
-      </c>
-      <c r="C54" s="3" t="s">
-        <v>640</v>
       </c>
     </row>
     <row r="55" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B55" s="3" t="s">
+        <v>640</v>
+      </c>
+      <c r="C55" s="3" t="s">
         <v>641</v>
-      </c>
-      <c r="C55" s="3" t="s">
-        <v>642</v>
       </c>
     </row>
     <row r="56" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B56" s="3" t="s">
+        <v>642</v>
+      </c>
+      <c r="C56" s="3" t="s">
         <v>643</v>
-      </c>
-      <c r="C56" s="3" t="s">
-        <v>644</v>
       </c>
     </row>
     <row r="57" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B57" s="3" t="s">
+        <v>644</v>
+      </c>
+      <c r="C57" s="3" t="s">
         <v>645</v>
-      </c>
-      <c r="C57" s="3" t="s">
-        <v>646</v>
       </c>
     </row>
     <row r="58" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B58" s="3" t="s">
+        <v>646</v>
+      </c>
+      <c r="C58" s="3" t="s">
         <v>647</v>
-      </c>
-      <c r="C58" s="3" t="s">
-        <v>648</v>
       </c>
     </row>
     <row r="59" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B59" s="3" t="s">
+        <v>648</v>
+      </c>
+      <c r="C59" s="3" t="s">
         <v>649</v>
-      </c>
-      <c r="C59" s="3" t="s">
-        <v>650</v>
       </c>
     </row>
     <row r="60" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B60" s="3" t="s">
+        <v>650</v>
+      </c>
+      <c r="C60" s="3" t="s">
         <v>651</v>
-      </c>
-      <c r="C60" s="3" t="s">
-        <v>652</v>
       </c>
     </row>
     <row r="61" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B61" s="3" t="s">
+        <v>652</v>
+      </c>
+      <c r="C61" s="3" t="s">
         <v>653</v>
-      </c>
-      <c r="C61" s="3" t="s">
-        <v>654</v>
       </c>
     </row>
     <row r="62" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B62" s="3" t="s">
+        <v>654</v>
+      </c>
+      <c r="C62" s="3" t="s">
         <v>655</v>
-      </c>
-      <c r="C62" s="3" t="s">
-        <v>656</v>
       </c>
     </row>
     <row r="63" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B63" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C63" s="3" t="s">
         <v>657</v>
-      </c>
-      <c r="C63" s="3" t="s">
-        <v>658</v>
       </c>
     </row>
     <row r="64" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B64" s="3" t="s">
+        <v>658</v>
+      </c>
+      <c r="C64" s="3" t="s">
         <v>659</v>
-      </c>
-      <c r="C64" s="3" t="s">
-        <v>660</v>
       </c>
     </row>
     <row r="65" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B65" s="3" t="s">
+        <v>660</v>
+      </c>
+      <c r="C65" s="3" t="s">
         <v>661</v>
-      </c>
-      <c r="C65" s="3" t="s">
-        <v>662</v>
       </c>
     </row>
     <row r="66" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B66" s="3" t="s">
+        <v>662</v>
+      </c>
+      <c r="C66" s="3" t="s">
         <v>663</v>
-      </c>
-      <c r="C66" s="3" t="s">
-        <v>664</v>
       </c>
     </row>
     <row r="67" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B67" s="3" t="s">
+        <v>664</v>
+      </c>
+      <c r="C67" s="3" t="s">
         <v>665</v>
-      </c>
-      <c r="C67" s="3" t="s">
-        <v>666</v>
       </c>
     </row>
     <row r="68" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B68" s="3" t="s">
+        <v>666</v>
+      </c>
+      <c r="C68" s="3" t="s">
         <v>667</v>
-      </c>
-      <c r="C68" s="3" t="s">
-        <v>668</v>
       </c>
     </row>
     <row r="69" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B69" s="3" t="s">
+        <v>668</v>
+      </c>
+      <c r="C69" s="3" t="s">
         <v>669</v>
-      </c>
-      <c r="C69" s="3" t="s">
-        <v>670</v>
       </c>
     </row>
     <row r="70" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B70" s="3" t="s">
+        <v>670</v>
+      </c>
+      <c r="C70" s="3" t="s">
         <v>671</v>
-      </c>
-      <c r="C70" s="3" t="s">
-        <v>672</v>
       </c>
     </row>
     <row r="71" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B71" s="3" t="s">
+        <v>672</v>
+      </c>
+      <c r="C71" s="3" t="s">
         <v>673</v>
-      </c>
-      <c r="C71" s="3" t="s">
-        <v>674</v>
       </c>
     </row>
     <row r="72" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B72" s="3" t="s">
+        <v>674</v>
+      </c>
+      <c r="C72" s="3" t="s">
         <v>675</v>
-      </c>
-      <c r="C72" s="3" t="s">
-        <v>676</v>
       </c>
     </row>
     <row r="73" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B73" s="3" t="s">
+        <v>676</v>
+      </c>
+      <c r="C73" s="3" t="s">
         <v>677</v>
-      </c>
-      <c r="C73" s="3" t="s">
-        <v>678</v>
       </c>
     </row>
     <row r="74" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B74" s="3" t="s">
+        <v>678</v>
+      </c>
+      <c r="C74" s="3" t="s">
         <v>679</v>
-      </c>
-      <c r="C74" s="3" t="s">
-        <v>680</v>
       </c>
     </row>
     <row r="75" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B75" s="3" t="s">
+        <v>680</v>
+      </c>
+      <c r="C75" s="3" t="s">
         <v>681</v>
-      </c>
-      <c r="C75" s="3" t="s">
-        <v>682</v>
       </c>
     </row>
     <row r="76" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B76" s="3" t="s">
+        <v>682</v>
+      </c>
+      <c r="C76" s="3" t="s">
         <v>683</v>
-      </c>
-      <c r="C76" s="3" t="s">
-        <v>684</v>
       </c>
     </row>
     <row r="77" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B77" s="3" t="s">
+        <v>684</v>
+      </c>
+      <c r="C77" s="3" t="s">
         <v>685</v>
-      </c>
-      <c r="C77" s="3" t="s">
-        <v>686</v>
       </c>
     </row>
     <row r="78" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B78" s="3" t="s">
+        <v>686</v>
+      </c>
+      <c r="C78" s="3" t="s">
         <v>687</v>
-      </c>
-      <c r="C78" s="3" t="s">
-        <v>688</v>
       </c>
     </row>
     <row r="79" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B79" s="3" t="s">
+        <v>688</v>
+      </c>
+      <c r="C79" s="3" t="s">
         <v>689</v>
-      </c>
-      <c r="C79" s="3" t="s">
-        <v>690</v>
       </c>
     </row>
     <row r="80" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B80" s="3" t="s">
+        <v>690</v>
+      </c>
+      <c r="C80" s="3" t="s">
         <v>691</v>
-      </c>
-      <c r="C80" s="3" t="s">
-        <v>692</v>
       </c>
     </row>
     <row r="81" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B81" s="3" t="s">
+        <v>692</v>
+      </c>
+      <c r="C81" s="3" t="s">
         <v>693</v>
-      </c>
-      <c r="C81" s="3" t="s">
-        <v>694</v>
       </c>
     </row>
     <row r="82" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B82" s="3" t="s">
+        <v>694</v>
+      </c>
+      <c r="C82" s="3" t="s">
         <v>695</v>
-      </c>
-      <c r="C82" s="3" t="s">
-        <v>696</v>
       </c>
     </row>
     <row r="83" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B83" s="3" t="s">
+        <v>696</v>
+      </c>
+      <c r="C83" s="3" t="s">
         <v>697</v>
-      </c>
-      <c r="C83" s="3" t="s">
-        <v>698</v>
       </c>
     </row>
     <row r="84" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B84" s="3" t="s">
+        <v>698</v>
+      </c>
+      <c r="C84" s="3" t="s">
         <v>699</v>
-      </c>
-      <c r="C84" s="3" t="s">
-        <v>700</v>
       </c>
     </row>
     <row r="85" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B85" s="3" t="s">
+        <v>700</v>
+      </c>
+      <c r="C85" s="3" t="s">
         <v>701</v>
-      </c>
-      <c r="C85" s="3" t="s">
-        <v>702</v>
       </c>
     </row>
     <row r="86" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B86" s="3" t="s">
+        <v>702</v>
+      </c>
+      <c r="C86" s="3" t="s">
         <v>703</v>
-      </c>
-      <c r="C86" s="3" t="s">
-        <v>704</v>
       </c>
     </row>
     <row r="87" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B87" s="3" t="s">
+        <v>704</v>
+      </c>
+      <c r="C87" s="3" t="s">
         <v>705</v>
-      </c>
-      <c r="C87" s="3" t="s">
-        <v>706</v>
       </c>
     </row>
     <row r="88" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B88" s="3" t="s">
+        <v>706</v>
+      </c>
+      <c r="C88" s="3" t="s">
         <v>707</v>
-      </c>
-      <c r="C88" s="3" t="s">
-        <v>708</v>
       </c>
     </row>
     <row r="89" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B89" s="3" t="s">
+        <v>708</v>
+      </c>
+      <c r="C89" s="3" t="s">
         <v>709</v>
-      </c>
-      <c r="C89" s="3" t="s">
-        <v>710</v>
       </c>
     </row>
     <row r="90" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B90" s="3" t="s">
+        <v>710</v>
+      </c>
+      <c r="C90" s="3" t="s">
         <v>711</v>
-      </c>
-      <c r="C90" s="3" t="s">
-        <v>712</v>
       </c>
     </row>
     <row r="91" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B91" s="3" t="s">
+        <v>712</v>
+      </c>
+      <c r="C91" s="3" t="s">
         <v>713</v>
-      </c>
-      <c r="C91" s="3" t="s">
-        <v>714</v>
       </c>
     </row>
     <row r="92" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B92" s="3" t="s">
+        <v>714</v>
+      </c>
+      <c r="C92" s="3" t="s">
         <v>715</v>
-      </c>
-      <c r="C92" s="3" t="s">
-        <v>716</v>
       </c>
     </row>
     <row r="93" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B93" s="3" t="s">
+        <v>716</v>
+      </c>
+      <c r="C93" s="3" t="s">
         <v>717</v>
-      </c>
-      <c r="C93" s="3" t="s">
-        <v>718</v>
       </c>
     </row>
     <row r="94" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B94" s="3" t="s">
+        <v>718</v>
+      </c>
+      <c r="C94" s="3" t="s">
         <v>719</v>
-      </c>
-      <c r="C94" s="3" t="s">
-        <v>720</v>
       </c>
     </row>
     <row r="95" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B95" s="3" t="s">
+        <v>720</v>
+      </c>
+      <c r="C95" s="3" t="s">
         <v>721</v>
-      </c>
-      <c r="C95" s="3" t="s">
-        <v>722</v>
       </c>
     </row>
     <row r="96" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B96" s="3" t="s">
+        <v>722</v>
+      </c>
+      <c r="C96" s="3" t="s">
         <v>723</v>
-      </c>
-      <c r="C96" s="3" t="s">
-        <v>724</v>
       </c>
     </row>
     <row r="97" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B97" s="3" t="s">
+        <v>724</v>
+      </c>
+      <c r="C97" s="3" t="s">
         <v>725</v>
-      </c>
-      <c r="C97" s="3" t="s">
-        <v>726</v>
       </c>
     </row>
     <row r="98" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B98" s="3" t="s">
+        <v>726</v>
+      </c>
+      <c r="C98" s="3" t="s">
         <v>727</v>
-      </c>
-      <c r="C98" s="3" t="s">
-        <v>728</v>
       </c>
     </row>
   </sheetData>
@@ -6414,226 +6411,226 @@
     </row>
     <row r="2" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B2" s="2" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
     </row>
     <row r="3" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B3" s="2" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
     </row>
     <row r="4" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B4" s="2" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>731</v>
+        <v>730</v>
       </c>
     </row>
     <row r="5" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B5" s="2" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
     </row>
     <row r="6" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B6" s="2" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
     </row>
     <row r="7" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B7" s="2" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>731</v>
+        <v>730</v>
       </c>
     </row>
     <row r="8" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B8" s="2" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>734</v>
+        <v>733</v>
       </c>
     </row>
     <row r="9" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B9" s="2" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
     </row>
     <row r="10" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B10" s="2" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
     </row>
     <row r="11" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B11" s="2" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
     </row>
     <row r="12" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B12" s="2" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
     </row>
     <row r="13" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B13" s="2" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
     </row>
     <row r="14" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B14" s="2" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
     </row>
     <row r="15" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B15" s="2" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
     </row>
     <row r="16" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B16" s="2" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
     </row>
     <row r="17" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B17" s="2" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
     </row>
     <row r="18" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B18" s="2" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
     </row>
     <row r="19" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B19" s="2" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>741</v>
+        <v>740</v>
       </c>
     </row>
     <row r="20" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B20" s="2" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>742</v>
+        <v>741</v>
       </c>
     </row>
     <row r="21" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B21" s="2" t="s">
+        <v>742</v>
+      </c>
+      <c r="C21" s="2" t="s">
         <v>743</v>
-      </c>
-      <c r="C21" s="2" t="s">
-        <v>744</v>
       </c>
     </row>
     <row r="22" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B22" s="2" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>745</v>
+        <v>744</v>
       </c>
     </row>
     <row r="23" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B23" s="2" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>746</v>
+        <v>745</v>
       </c>
     </row>
     <row r="24" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B24" s="2" t="s">
+        <v>746</v>
+      </c>
+      <c r="C24" s="2" t="s">
         <v>747</v>
-      </c>
-      <c r="C24" s="2" t="s">
-        <v>748</v>
       </c>
     </row>
     <row r="25" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B25" s="2" t="s">
+        <v>748</v>
+      </c>
+      <c r="C25" s="2" t="s">
         <v>749</v>
-      </c>
-      <c r="C25" s="2" t="s">
-        <v>750</v>
       </c>
     </row>
     <row r="26" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B26" s="2" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>751</v>
+        <v>750</v>
       </c>
     </row>
     <row r="27" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B27" s="2" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>752</v>
+        <v>751</v>
       </c>
     </row>
     <row r="28" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B28" s="2" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
     </row>
     <row r="29" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B29" s="2" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>754</v>
+        <v>753</v>
       </c>
     </row>
     <row r="30" spans="2:3" x14ac:dyDescent="0.25">
@@ -6641,191 +6638,191 @@
         <v>6</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
     </row>
     <row r="31" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B31" s="2" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
     </row>
     <row r="32" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B32" s="2" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
     </row>
     <row r="33" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B33" s="2" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
     </row>
     <row r="34" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B34" s="2" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
     </row>
     <row r="35" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B35" s="2" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
     </row>
     <row r="36" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B36" s="2" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>761</v>
+        <v>760</v>
       </c>
     </row>
     <row r="37" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B37" s="2" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>762</v>
+        <v>761</v>
       </c>
     </row>
     <row r="38" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B38" s="2" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
     </row>
     <row r="39" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B39" s="2" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>764</v>
+        <v>763</v>
       </c>
     </row>
     <row r="40" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B40" s="2" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>765</v>
+        <v>764</v>
       </c>
     </row>
     <row r="41" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B41" s="2" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
     </row>
     <row r="42" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B42" s="2" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>767</v>
+        <v>766</v>
       </c>
     </row>
     <row r="43" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B43" s="2" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>768</v>
+        <v>767</v>
       </c>
     </row>
     <row r="44" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B44" s="2" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>769</v>
+        <v>768</v>
       </c>
     </row>
     <row r="45" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B45" s="2" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>745</v>
+        <v>744</v>
       </c>
     </row>
     <row r="46" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B46" s="2" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
     </row>
     <row r="47" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B47" s="2" t="s">
+        <v>770</v>
+      </c>
+      <c r="C47" s="2" t="s">
         <v>771</v>
-      </c>
-      <c r="C47" s="2" t="s">
-        <v>772</v>
       </c>
     </row>
     <row r="48" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B48" s="2" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>773</v>
+        <v>772</v>
       </c>
     </row>
     <row r="49" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B49" s="2" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>774</v>
+        <v>773</v>
       </c>
     </row>
     <row r="50" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B50" s="2" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>775</v>
+        <v>774</v>
       </c>
     </row>
     <row r="51" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B51" s="2" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>776</v>
+        <v>775</v>
       </c>
     </row>
     <row r="52" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B52" s="2" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
     </row>
     <row r="53" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B53" s="2" t="s">
+        <v>777</v>
+      </c>
+      <c r="C53" s="2" t="s">
         <v>778</v>
-      </c>
-      <c r="C53" s="2" t="s">
-        <v>779</v>
       </c>
     </row>
   </sheetData>
@@ -6849,242 +6846,242 @@
     </row>
     <row r="2" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B2" s="1" t="s">
+        <v>779</v>
+      </c>
+      <c r="C2" s="1" t="s">
         <v>780</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>781</v>
       </c>
     </row>
     <row r="3" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B3" s="1" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>782</v>
+        <v>781</v>
       </c>
     </row>
     <row r="4" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B4" s="1" t="s">
-        <v>783</v>
+        <v>782</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
     </row>
     <row r="5" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B5" s="1" t="s">
-        <v>784</v>
+        <v>783</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>754</v>
+        <v>753</v>
       </c>
     </row>
     <row r="6" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B6" s="1" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>785</v>
+        <v>784</v>
       </c>
     </row>
     <row r="7" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B7" s="1" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>786</v>
+        <v>785</v>
       </c>
     </row>
     <row r="8" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B8" s="1" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
     </row>
     <row r="9" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B9" s="1" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
     </row>
     <row r="10" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B10" s="1" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>789</v>
+        <v>788</v>
       </c>
     </row>
     <row r="11" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B11" s="1" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>790</v>
+        <v>789</v>
       </c>
     </row>
     <row r="12" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B12" s="1" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>791</v>
+        <v>790</v>
       </c>
     </row>
     <row r="13" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B13" s="1" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>792</v>
+        <v>791</v>
       </c>
     </row>
     <row r="14" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B14" s="1" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>793</v>
+        <v>792</v>
       </c>
     </row>
     <row r="15" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B15" s="1" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
     </row>
     <row r="16" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B16" s="1" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>731</v>
+        <v>730</v>
       </c>
     </row>
     <row r="17" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B17" s="1" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
     </row>
     <row r="18" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B18" s="1" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>794</v>
+        <v>793</v>
       </c>
     </row>
     <row r="19" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B19" s="1" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>782</v>
+        <v>781</v>
       </c>
     </row>
     <row r="20" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B20" s="1" t="s">
+        <v>794</v>
+      </c>
+      <c r="C20" s="1" t="s">
         <v>795</v>
-      </c>
-      <c r="C20" s="1" t="s">
-        <v>796</v>
       </c>
     </row>
     <row r="21" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B21" s="1" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
     </row>
     <row r="22" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B22" s="1" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
     </row>
     <row r="23" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B23" s="1" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
     </row>
     <row r="24" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B24" s="1" t="s">
+        <v>799</v>
+      </c>
+      <c r="C24" s="1" t="s">
         <v>800</v>
-      </c>
-      <c r="C24" s="1" t="s">
-        <v>801</v>
       </c>
     </row>
     <row r="25" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B25" s="1" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>746</v>
+        <v>745</v>
       </c>
     </row>
     <row r="26" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B26" s="1" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
     </row>
     <row r="27" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B27" s="1" t="s">
+        <v>801</v>
+      </c>
+      <c r="C27" s="1" t="s">
         <v>802</v>
-      </c>
-      <c r="C27" s="1" t="s">
-        <v>803</v>
       </c>
     </row>
     <row r="28" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B28" s="1" t="s">
+        <v>803</v>
+      </c>
+      <c r="C28" s="1" t="s">
         <v>804</v>
-      </c>
-      <c r="C28" s="1" t="s">
-        <v>805</v>
       </c>
     </row>
     <row r="29" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B29" s="1" t="s">
-        <v>806</v>
+        <v>805</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>751</v>
+        <v>750</v>
       </c>
     </row>
     <row r="30" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B30" s="1" t="s">
+        <v>806</v>
+      </c>
+      <c r="C30" s="1" t="s">
         <v>807</v>
-      </c>
-      <c r="C30" s="1" t="s">
-        <v>808</v>
       </c>
     </row>
     <row r="31" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B31" s="1" t="s">
+        <v>808</v>
+      </c>
+      <c r="C31" s="1" t="s">
         <v>809</v>
-      </c>
-      <c r="C31" s="1" t="s">
-        <v>810</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/Editor/DataDic/Data.xlsx
+++ b/Assets/Editor/DataDic/Data.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView minimized="1" xWindow="0" yWindow="0" windowWidth="17385" windowHeight="7860" activeTab="1"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="17385" windowHeight="7860" firstSheet="1" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="FishData" sheetId="1" r:id="rId1"/>

--- a/Assets/Editor/DataDic/Data.xlsx
+++ b/Assets/Editor/DataDic/Data.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="17385" windowHeight="7860" firstSheet="1" activeTab="3"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="17385" windowHeight="7860" firstSheet="1" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="FishData" sheetId="1" r:id="rId1"/>

--- a/Assets/Editor/DataDic/Data.xlsx
+++ b/Assets/Editor/DataDic/Data.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="17385" windowHeight="7860" firstSheet="1" activeTab="1"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="17385" windowHeight="7860" firstSheet="1" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="FishData" sheetId="1" r:id="rId1"/>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="986" uniqueCount="819">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="985" uniqueCount="818">
   <si>
     <t>Key</t>
   </si>
@@ -882,9 +882,6 @@
   </si>
   <si>
     <t>春战场</t>
-  </si>
-  <si>
-    <t>1077</t>
   </si>
   <si>
     <t>秋战场</t>
@@ -3170,7 +3167,7 @@
         <v>6</v>
       </c>
       <c r="G4" s="5" t="s">
-        <v>810</v>
+        <v>809</v>
       </c>
       <c r="I4" s="6" t="s">
         <v>13</v>
@@ -3190,7 +3187,7 @@
         <v>948</v>
       </c>
       <c r="G5" s="5" t="s">
-        <v>811</v>
+        <v>810</v>
       </c>
       <c r="I5">
         <f>VLOOKUP(I4,$B:$C,2,FALSE)</f>
@@ -3240,7 +3237,7 @@
         <v>11</v>
       </c>
       <c r="G7" s="5" t="s">
-        <v>812</v>
+        <v>811</v>
       </c>
       <c r="I7" s="6" t="s">
         <v>13</v>
@@ -3272,7 +3269,7 @@
         <v>874</v>
       </c>
       <c r="G8" s="5" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
       <c r="I8" s="4">
         <f>VLOOKUP(I7,$B:$C,2,FALSE)</f>
@@ -3352,7 +3349,7 @@
         <v>16</v>
       </c>
       <c r="G10" s="5" t="s">
-        <v>817</v>
+        <v>816</v>
       </c>
     </row>
     <row r="11" spans="2:15" x14ac:dyDescent="0.25">
@@ -3363,7 +3360,7 @@
         <v>18</v>
       </c>
       <c r="G11" s="5" t="s">
-        <v>818</v>
+        <v>817</v>
       </c>
     </row>
     <row r="12" spans="2:15" x14ac:dyDescent="0.25">
@@ -3414,7 +3411,7 @@
       </c>
       <c r="F14" s="4"/>
       <c r="G14" s="5" t="s">
-        <v>818</v>
+        <v>817</v>
       </c>
       <c r="I14" s="4" t="s">
         <v>88</v>
@@ -3438,7 +3435,7 @@
       </c>
       <c r="F15" s="4"/>
       <c r="G15" s="5" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="H15" s="4"/>
       <c r="I15" s="4" t="str">
@@ -3498,7 +3495,7 @@
         <v>28</v>
       </c>
       <c r="G17" s="5" t="s">
-        <v>813</v>
+        <v>812</v>
       </c>
       <c r="I17" s="4" t="s">
         <v>56</v>
@@ -3521,7 +3518,7 @@
         <v>29</v>
       </c>
       <c r="G18" s="5" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
       <c r="I18" s="4" t="str">
         <f>VLOOKUP(I17,$B:$C,2,FALSE)</f>
@@ -4508,16 +4505,16 @@
       </c>
     </row>
     <row r="77" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B77" s="4" t="s">
+      <c r="B77" s="4">
+        <v>1077</v>
+      </c>
+      <c r="C77" s="4" t="s">
         <v>286</v>
-      </c>
-      <c r="C77" s="4" t="s">
-        <v>287</v>
       </c>
     </row>
     <row r="78" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B78" s="4" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="C78" s="4" t="s">
         <v>45</v>
@@ -4525,170 +4522,170 @@
     </row>
     <row r="79" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B79" s="4" t="s">
+        <v>288</v>
+      </c>
+      <c r="C79" s="4" t="s">
         <v>289</v>
-      </c>
-      <c r="C79" s="4" t="s">
-        <v>290</v>
       </c>
     </row>
     <row r="80" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B80" s="4" t="s">
+        <v>290</v>
+      </c>
+      <c r="C80" s="4" t="s">
         <v>291</v>
-      </c>
-      <c r="C80" s="4" t="s">
-        <v>292</v>
       </c>
     </row>
     <row r="81" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B81" s="4" t="s">
+        <v>292</v>
+      </c>
+      <c r="C81" s="4" t="s">
         <v>293</v>
-      </c>
-      <c r="C81" s="4" t="s">
-        <v>294</v>
       </c>
     </row>
     <row r="82" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B82" s="4" t="s">
+        <v>294</v>
+      </c>
+      <c r="C82" s="4" t="s">
         <v>295</v>
-      </c>
-      <c r="C82" s="4" t="s">
-        <v>296</v>
       </c>
     </row>
     <row r="83" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B83" s="4" t="s">
+        <v>296</v>
+      </c>
+      <c r="C83" s="4" t="s">
         <v>297</v>
-      </c>
-      <c r="C83" s="4" t="s">
-        <v>298</v>
       </c>
     </row>
     <row r="84" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B84" s="4" t="s">
+        <v>298</v>
+      </c>
+      <c r="C84" s="4" t="s">
         <v>299</v>
-      </c>
-      <c r="C84" s="4" t="s">
-        <v>300</v>
       </c>
     </row>
     <row r="85" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B85" s="4" t="s">
+        <v>300</v>
+      </c>
+      <c r="C85" s="4" t="s">
         <v>301</v>
-      </c>
-      <c r="C85" s="4" t="s">
-        <v>302</v>
       </c>
     </row>
     <row r="86" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B86" s="4" t="s">
+        <v>302</v>
+      </c>
+      <c r="C86" s="4" t="s">
         <v>303</v>
-      </c>
-      <c r="C86" s="4" t="s">
-        <v>304</v>
       </c>
     </row>
     <row r="87" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B87" s="4" t="s">
+        <v>304</v>
+      </c>
+      <c r="C87" s="4" t="s">
         <v>305</v>
-      </c>
-      <c r="C87" s="4" t="s">
-        <v>306</v>
       </c>
     </row>
     <row r="88" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B88" s="4" t="s">
+        <v>306</v>
+      </c>
+      <c r="C88" s="4" t="s">
         <v>307</v>
-      </c>
-      <c r="C88" s="4" t="s">
-        <v>308</v>
       </c>
     </row>
     <row r="89" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B89" s="4" t="s">
+        <v>308</v>
+      </c>
+      <c r="C89" s="4" t="s">
         <v>309</v>
-      </c>
-      <c r="C89" s="4" t="s">
-        <v>310</v>
       </c>
     </row>
     <row r="90" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B90" s="4" t="s">
+        <v>310</v>
+      </c>
+      <c r="C90" s="4" t="s">
         <v>311</v>
-      </c>
-      <c r="C90" s="4" t="s">
-        <v>312</v>
       </c>
     </row>
     <row r="91" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B91" s="4" t="s">
+        <v>312</v>
+      </c>
+      <c r="C91" s="4" t="s">
         <v>313</v>
-      </c>
-      <c r="C91" s="4" t="s">
-        <v>314</v>
       </c>
     </row>
     <row r="92" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B92" s="4" t="s">
+        <v>314</v>
+      </c>
+      <c r="C92" s="4" t="s">
         <v>315</v>
-      </c>
-      <c r="C92" s="4" t="s">
-        <v>316</v>
       </c>
     </row>
     <row r="93" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B93" s="4" t="s">
+        <v>316</v>
+      </c>
+      <c r="C93" s="4" t="s">
         <v>317</v>
-      </c>
-      <c r="C93" s="4" t="s">
-        <v>318</v>
       </c>
     </row>
     <row r="94" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B94" s="4" t="s">
+        <v>318</v>
+      </c>
+      <c r="C94" s="4" t="s">
         <v>319</v>
-      </c>
-      <c r="C94" s="4" t="s">
-        <v>320</v>
       </c>
     </row>
     <row r="95" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B95" s="4" t="s">
+        <v>320</v>
+      </c>
+      <c r="C95" s="4" t="s">
         <v>321</v>
-      </c>
-      <c r="C95" s="4" t="s">
-        <v>322</v>
       </c>
     </row>
     <row r="96" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B96" s="4" t="s">
+        <v>322</v>
+      </c>
+      <c r="C96" s="4" t="s">
         <v>323</v>
-      </c>
-      <c r="C96" s="4" t="s">
-        <v>324</v>
       </c>
     </row>
     <row r="97" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B97" s="4" t="s">
+        <v>324</v>
+      </c>
+      <c r="C97" s="4" t="s">
         <v>325</v>
-      </c>
-      <c r="C97" s="4" t="s">
-        <v>326</v>
       </c>
     </row>
     <row r="98" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B98" s="4" t="s">
+        <v>326</v>
+      </c>
+      <c r="C98" s="4" t="s">
         <v>327</v>
-      </c>
-      <c r="C98" s="4" t="s">
-        <v>328</v>
       </c>
     </row>
     <row r="99" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B99" s="4" t="s">
+        <v>328</v>
+      </c>
+      <c r="C99" s="4" t="s">
         <v>329</v>
-      </c>
-      <c r="C99" s="4" t="s">
-        <v>330</v>
       </c>
     </row>
     <row r="100" spans="2:3" x14ac:dyDescent="0.25">
@@ -4696,7 +4693,7 @@
         <v>127</v>
       </c>
       <c r="C100" s="4" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
     </row>
     <row r="101" spans="2:3" x14ac:dyDescent="0.25">
@@ -4709,10 +4706,10 @@
     </row>
     <row r="102" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B102" s="4" t="s">
+        <v>331</v>
+      </c>
+      <c r="C102" s="4" t="s">
         <v>332</v>
-      </c>
-      <c r="C102" s="4" t="s">
-        <v>333</v>
       </c>
     </row>
     <row r="103" spans="2:3" x14ac:dyDescent="0.25">
@@ -4720,15 +4717,15 @@
         <v>131</v>
       </c>
       <c r="C103" s="4" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
     </row>
     <row r="104" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B104" s="4" t="s">
+        <v>334</v>
+      </c>
+      <c r="C104" s="4" t="s">
         <v>335</v>
-      </c>
-      <c r="C104" s="4" t="s">
-        <v>336</v>
       </c>
     </row>
     <row r="105" spans="2:3" x14ac:dyDescent="0.25">
@@ -4744,12 +4741,12 @@
         <v>135</v>
       </c>
       <c r="C106" s="4" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
     </row>
     <row r="107" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B107" s="4" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="C107" s="4" t="s">
         <v>81</v>
@@ -4757,10 +4754,10 @@
     </row>
     <row r="108" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B108" s="4" t="s">
+        <v>338</v>
+      </c>
+      <c r="C108" s="4" t="s">
         <v>339</v>
-      </c>
-      <c r="C108" s="4" t="s">
-        <v>340</v>
       </c>
     </row>
     <row r="109" spans="2:3" x14ac:dyDescent="0.25">
@@ -4768,7 +4765,7 @@
         <v>137</v>
       </c>
       <c r="C109" s="4" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
     </row>
     <row r="110" spans="2:3" x14ac:dyDescent="0.25">
@@ -4776,7 +4773,7 @@
         <v>139</v>
       </c>
       <c r="C110" s="4" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
     </row>
     <row r="111" spans="2:3" x14ac:dyDescent="0.25">
@@ -4784,7 +4781,7 @@
         <v>141</v>
       </c>
       <c r="C111" s="4" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
     </row>
     <row r="112" spans="2:3" x14ac:dyDescent="0.25">
@@ -4792,7 +4789,7 @@
         <v>38</v>
       </c>
       <c r="C112" s="4" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
     </row>
     <row r="113" spans="2:3" x14ac:dyDescent="0.25">
@@ -4800,7 +4797,7 @@
         <v>144</v>
       </c>
       <c r="C113" s="4" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
     </row>
     <row r="114" spans="2:3" x14ac:dyDescent="0.25">
@@ -4808,7 +4805,7 @@
         <v>146</v>
       </c>
       <c r="C114" s="4" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
     </row>
     <row r="115" spans="2:3" x14ac:dyDescent="0.25">
@@ -4816,7 +4813,7 @@
         <v>148</v>
       </c>
       <c r="C115" s="4" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
     </row>
     <row r="116" spans="2:3" x14ac:dyDescent="0.25">
@@ -4824,7 +4821,7 @@
         <v>150</v>
       </c>
       <c r="C116" s="4" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
     </row>
     <row r="117" spans="2:3" x14ac:dyDescent="0.25">
@@ -4837,7 +4834,7 @@
     </row>
     <row r="118" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B118" s="4" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="C118" s="4" t="s">
         <v>22</v>
@@ -4845,450 +4842,450 @@
     </row>
     <row r="119" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B119" s="4" t="s">
+        <v>348</v>
+      </c>
+      <c r="C119" s="4" t="s">
         <v>349</v>
-      </c>
-      <c r="C119" s="4" t="s">
-        <v>350</v>
       </c>
     </row>
     <row r="120" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B120" s="4" t="s">
+        <v>350</v>
+      </c>
+      <c r="C120" s="4" t="s">
         <v>351</v>
-      </c>
-      <c r="C120" s="4" t="s">
-        <v>352</v>
       </c>
     </row>
     <row r="121" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B121" s="4" t="s">
+        <v>352</v>
+      </c>
+      <c r="C121" s="4" t="s">
         <v>353</v>
-      </c>
-      <c r="C121" s="4" t="s">
-        <v>354</v>
       </c>
     </row>
     <row r="122" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B122" s="4" t="s">
+        <v>354</v>
+      </c>
+      <c r="C122" s="4" t="s">
         <v>355</v>
-      </c>
-      <c r="C122" s="4" t="s">
-        <v>356</v>
       </c>
     </row>
     <row r="123" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B123" s="4" t="s">
+        <v>356</v>
+      </c>
+      <c r="C123" s="4" t="s">
         <v>357</v>
-      </c>
-      <c r="C123" s="4" t="s">
-        <v>358</v>
       </c>
     </row>
     <row r="124" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B124" s="4" t="s">
+        <v>358</v>
+      </c>
+      <c r="C124" s="4" t="s">
         <v>359</v>
-      </c>
-      <c r="C124" s="4" t="s">
-        <v>360</v>
       </c>
     </row>
     <row r="125" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B125" s="4" t="s">
+        <v>360</v>
+      </c>
+      <c r="C125" s="4" t="s">
         <v>361</v>
-      </c>
-      <c r="C125" s="4" t="s">
-        <v>362</v>
       </c>
     </row>
     <row r="126" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B126" s="4" t="s">
+        <v>362</v>
+      </c>
+      <c r="C126" s="4" t="s">
         <v>363</v>
-      </c>
-      <c r="C126" s="4" t="s">
-        <v>364</v>
       </c>
     </row>
     <row r="127" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B127" s="4" t="s">
+        <v>364</v>
+      </c>
+      <c r="C127" s="4" t="s">
         <v>365</v>
-      </c>
-      <c r="C127" s="4" t="s">
-        <v>366</v>
       </c>
     </row>
     <row r="128" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B128" s="4" t="s">
+        <v>366</v>
+      </c>
+      <c r="C128" s="4" t="s">
         <v>367</v>
-      </c>
-      <c r="C128" s="4" t="s">
-        <v>368</v>
       </c>
     </row>
     <row r="129" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B129" s="4" t="s">
+        <v>368</v>
+      </c>
+      <c r="C129" s="4" t="s">
         <v>369</v>
-      </c>
-      <c r="C129" s="4" t="s">
-        <v>370</v>
       </c>
     </row>
     <row r="130" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B130" s="4" t="s">
+        <v>370</v>
+      </c>
+      <c r="C130" s="4" t="s">
         <v>371</v>
-      </c>
-      <c r="C130" s="4" t="s">
-        <v>372</v>
       </c>
     </row>
     <row r="131" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B131" s="4" t="s">
+        <v>372</v>
+      </c>
+      <c r="C131" s="4" t="s">
         <v>373</v>
-      </c>
-      <c r="C131" s="4" t="s">
-        <v>374</v>
       </c>
     </row>
     <row r="132" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B132" s="4" t="s">
+        <v>374</v>
+      </c>
+      <c r="C132" s="4" t="s">
         <v>375</v>
-      </c>
-      <c r="C132" s="4" t="s">
-        <v>376</v>
       </c>
     </row>
     <row r="133" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B133" s="4" t="s">
+        <v>376</v>
+      </c>
+      <c r="C133" s="4" t="s">
         <v>377</v>
-      </c>
-      <c r="C133" s="4" t="s">
-        <v>378</v>
       </c>
     </row>
     <row r="134" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B134" s="4" t="s">
+        <v>378</v>
+      </c>
+      <c r="C134" s="4" t="s">
         <v>379</v>
-      </c>
-      <c r="C134" s="4" t="s">
-        <v>380</v>
       </c>
     </row>
     <row r="135" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B135" s="4" t="s">
+        <v>380</v>
+      </c>
+      <c r="C135" s="4" t="s">
         <v>381</v>
-      </c>
-      <c r="C135" s="4" t="s">
-        <v>382</v>
       </c>
     </row>
     <row r="136" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B136" s="4" t="s">
+        <v>382</v>
+      </c>
+      <c r="C136" s="4" t="s">
         <v>383</v>
-      </c>
-      <c r="C136" s="4" t="s">
-        <v>384</v>
       </c>
     </row>
     <row r="137" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B137" s="4" t="s">
+        <v>384</v>
+      </c>
+      <c r="C137" s="4" t="s">
         <v>385</v>
-      </c>
-      <c r="C137" s="4" t="s">
-        <v>386</v>
       </c>
     </row>
     <row r="138" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B138" s="4" t="s">
+        <v>386</v>
+      </c>
+      <c r="C138" s="4" t="s">
         <v>387</v>
-      </c>
-      <c r="C138" s="4" t="s">
-        <v>388</v>
       </c>
     </row>
     <row r="139" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B139" s="4" t="s">
+        <v>388</v>
+      </c>
+      <c r="C139" s="4" t="s">
         <v>389</v>
-      </c>
-      <c r="C139" s="4" t="s">
-        <v>390</v>
       </c>
     </row>
     <row r="140" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B140" s="4" t="s">
+        <v>390</v>
+      </c>
+      <c r="C140" s="4" t="s">
         <v>391</v>
-      </c>
-      <c r="C140" s="4" t="s">
-        <v>392</v>
       </c>
     </row>
     <row r="141" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B141" s="4" t="s">
+        <v>392</v>
+      </c>
+      <c r="C141" s="4" t="s">
         <v>393</v>
-      </c>
-      <c r="C141" s="4" t="s">
-        <v>394</v>
       </c>
     </row>
     <row r="142" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B142" s="4" t="s">
+        <v>394</v>
+      </c>
+      <c r="C142" s="4" t="s">
         <v>395</v>
-      </c>
-      <c r="C142" s="4" t="s">
-        <v>396</v>
       </c>
     </row>
     <row r="143" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B143" s="4" t="s">
+        <v>396</v>
+      </c>
+      <c r="C143" s="4" t="s">
         <v>397</v>
-      </c>
-      <c r="C143" s="4" t="s">
-        <v>398</v>
       </c>
     </row>
     <row r="144" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B144" s="4" t="s">
+        <v>398</v>
+      </c>
+      <c r="C144" s="4" t="s">
         <v>399</v>
-      </c>
-      <c r="C144" s="4" t="s">
-        <v>400</v>
       </c>
     </row>
     <row r="145" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B145" s="4" t="s">
+        <v>400</v>
+      </c>
+      <c r="C145" s="4" t="s">
         <v>401</v>
-      </c>
-      <c r="C145" s="4" t="s">
-        <v>402</v>
       </c>
     </row>
     <row r="146" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B146" s="4" t="s">
+        <v>402</v>
+      </c>
+      <c r="C146" s="4" t="s">
         <v>403</v>
-      </c>
-      <c r="C146" s="4" t="s">
-        <v>404</v>
       </c>
     </row>
     <row r="147" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B147" s="4" t="s">
+        <v>404</v>
+      </c>
+      <c r="C147" s="4" t="s">
         <v>405</v>
-      </c>
-      <c r="C147" s="4" t="s">
-        <v>406</v>
       </c>
     </row>
     <row r="148" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B148" s="4" t="s">
+        <v>406</v>
+      </c>
+      <c r="C148" s="4" t="s">
         <v>407</v>
-      </c>
-      <c r="C148" s="4" t="s">
-        <v>408</v>
       </c>
     </row>
     <row r="149" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B149" s="4" t="s">
+        <v>408</v>
+      </c>
+      <c r="C149" s="4" t="s">
         <v>409</v>
-      </c>
-      <c r="C149" s="4" t="s">
-        <v>410</v>
       </c>
     </row>
     <row r="150" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B150" s="4" t="s">
+        <v>410</v>
+      </c>
+      <c r="C150" s="4" t="s">
         <v>411</v>
-      </c>
-      <c r="C150" s="4" t="s">
-        <v>412</v>
       </c>
     </row>
     <row r="151" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B151" s="4" t="s">
+        <v>412</v>
+      </c>
+      <c r="C151" s="4" t="s">
         <v>413</v>
-      </c>
-      <c r="C151" s="4" t="s">
-        <v>414</v>
       </c>
     </row>
     <row r="152" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B152" s="4" t="s">
+        <v>414</v>
+      </c>
+      <c r="C152" s="4" t="s">
         <v>415</v>
-      </c>
-      <c r="C152" s="4" t="s">
-        <v>416</v>
       </c>
     </row>
     <row r="153" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B153" s="4" t="s">
+        <v>416</v>
+      </c>
+      <c r="C153" s="4" t="s">
         <v>417</v>
-      </c>
-      <c r="C153" s="4" t="s">
-        <v>418</v>
       </c>
     </row>
     <row r="154" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B154" s="4" t="s">
+        <v>418</v>
+      </c>
+      <c r="C154" s="4" t="s">
         <v>419</v>
-      </c>
-      <c r="C154" s="4" t="s">
-        <v>420</v>
       </c>
     </row>
     <row r="155" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B155" s="4" t="s">
+        <v>420</v>
+      </c>
+      <c r="C155" s="4" t="s">
         <v>421</v>
-      </c>
-      <c r="C155" s="4" t="s">
-        <v>422</v>
       </c>
     </row>
     <row r="156" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B156" s="4" t="s">
+        <v>422</v>
+      </c>
+      <c r="C156" s="4" t="s">
         <v>423</v>
-      </c>
-      <c r="C156" s="4" t="s">
-        <v>424</v>
       </c>
     </row>
     <row r="157" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B157" s="4" t="s">
+        <v>424</v>
+      </c>
+      <c r="C157" s="4" t="s">
         <v>425</v>
-      </c>
-      <c r="C157" s="4" t="s">
-        <v>426</v>
       </c>
     </row>
     <row r="158" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B158" s="4" t="s">
+        <v>426</v>
+      </c>
+      <c r="C158" s="4" t="s">
         <v>427</v>
-      </c>
-      <c r="C158" s="4" t="s">
-        <v>428</v>
       </c>
     </row>
     <row r="159" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B159" s="4" t="s">
+        <v>428</v>
+      </c>
+      <c r="C159" s="4" t="s">
         <v>429</v>
-      </c>
-      <c r="C159" s="4" t="s">
-        <v>430</v>
       </c>
     </row>
     <row r="160" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B160" s="4" t="s">
+        <v>430</v>
+      </c>
+      <c r="C160" s="4" t="s">
         <v>431</v>
-      </c>
-      <c r="C160" s="4" t="s">
-        <v>432</v>
       </c>
     </row>
     <row r="161" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B161" s="4" t="s">
+        <v>432</v>
+      </c>
+      <c r="C161" s="4" t="s">
         <v>433</v>
-      </c>
-      <c r="C161" s="4" t="s">
-        <v>434</v>
       </c>
     </row>
     <row r="162" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B162" s="4" t="s">
+        <v>434</v>
+      </c>
+      <c r="C162" s="4" t="s">
         <v>435</v>
-      </c>
-      <c r="C162" s="4" t="s">
-        <v>436</v>
       </c>
     </row>
     <row r="163" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B163" s="4" t="s">
+        <v>436</v>
+      </c>
+      <c r="C163" s="4" t="s">
         <v>437</v>
-      </c>
-      <c r="C163" s="4" t="s">
-        <v>438</v>
       </c>
     </row>
     <row r="164" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B164" s="4" t="s">
+        <v>438</v>
+      </c>
+      <c r="C164" s="4" t="s">
         <v>439</v>
-      </c>
-      <c r="C164" s="4" t="s">
-        <v>440</v>
       </c>
     </row>
     <row r="165" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B165" s="4" t="s">
+        <v>440</v>
+      </c>
+      <c r="C165" s="4" t="s">
         <v>441</v>
-      </c>
-      <c r="C165" s="4" t="s">
-        <v>442</v>
       </c>
     </row>
     <row r="166" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B166" s="4" t="s">
+        <v>442</v>
+      </c>
+      <c r="C166" s="4" t="s">
         <v>443</v>
-      </c>
-      <c r="C166" s="4" t="s">
-        <v>444</v>
       </c>
     </row>
     <row r="167" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B167" s="4" t="s">
+        <v>444</v>
+      </c>
+      <c r="C167" s="4" t="s">
         <v>445</v>
-      </c>
-      <c r="C167" s="4" t="s">
-        <v>446</v>
       </c>
     </row>
     <row r="168" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B168" s="4" t="s">
+        <v>446</v>
+      </c>
+      <c r="C168" s="4" t="s">
         <v>447</v>
-      </c>
-      <c r="C168" s="4" t="s">
-        <v>448</v>
       </c>
     </row>
     <row r="169" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B169" s="4" t="s">
+        <v>448</v>
+      </c>
+      <c r="C169" s="4" t="s">
         <v>449</v>
-      </c>
-      <c r="C169" s="4" t="s">
-        <v>450</v>
       </c>
     </row>
     <row r="170" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B170" s="4" t="s">
+        <v>450</v>
+      </c>
+      <c r="C170" s="4" t="s">
         <v>451</v>
-      </c>
-      <c r="C170" s="4" t="s">
-        <v>452</v>
       </c>
     </row>
     <row r="171" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B171" s="4" t="s">
+        <v>452</v>
+      </c>
+      <c r="C171" s="4" t="s">
         <v>453</v>
-      </c>
-      <c r="C171" s="4" t="s">
-        <v>454</v>
       </c>
     </row>
     <row r="172" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B172" s="4" t="s">
+        <v>454</v>
+      </c>
+      <c r="C172" s="4" t="s">
         <v>455</v>
-      </c>
-      <c r="C172" s="4" t="s">
-        <v>456</v>
       </c>
     </row>
     <row r="173" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B173" s="4" t="s">
+        <v>456</v>
+      </c>
+      <c r="C173" s="4" t="s">
         <v>457</v>
-      </c>
-      <c r="C173" s="4" t="s">
-        <v>458</v>
       </c>
     </row>
     <row r="174" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B174" s="4" t="s">
+        <v>458</v>
+      </c>
+      <c r="C174" s="4" t="s">
         <v>459</v>
-      </c>
-      <c r="C174" s="4" t="s">
-        <v>460</v>
       </c>
     </row>
     <row r="175" spans="2:3" x14ac:dyDescent="0.25">
@@ -5296,303 +5293,303 @@
         <v>44</v>
       </c>
       <c r="C175" s="4" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
     </row>
     <row r="176" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B176" s="4" t="s">
+        <v>461</v>
+      </c>
+      <c r="C176" s="4" t="s">
         <v>462</v>
-      </c>
-      <c r="C176" s="4" t="s">
-        <v>463</v>
       </c>
     </row>
     <row r="177" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B177" s="4" t="s">
+        <v>463</v>
+      </c>
+      <c r="C177" s="4" t="s">
         <v>464</v>
-      </c>
-      <c r="C177" s="4" t="s">
-        <v>465</v>
       </c>
     </row>
     <row r="178" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B178" s="4" t="s">
+        <v>465</v>
+      </c>
+      <c r="C178" s="4" t="s">
         <v>466</v>
-      </c>
-      <c r="C178" s="4" t="s">
-        <v>467</v>
       </c>
     </row>
     <row r="179" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B179" s="4" t="s">
+        <v>467</v>
+      </c>
+      <c r="C179" s="4" t="s">
         <v>468</v>
-      </c>
-      <c r="C179" s="4" t="s">
-        <v>469</v>
       </c>
     </row>
     <row r="180" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B180" s="4" t="s">
+        <v>469</v>
+      </c>
+      <c r="C180" s="4" t="s">
         <v>470</v>
-      </c>
-      <c r="C180" s="4" t="s">
-        <v>471</v>
       </c>
     </row>
     <row r="181" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B181" s="4" t="s">
+        <v>471</v>
+      </c>
+      <c r="C181" s="4" t="s">
         <v>472</v>
-      </c>
-      <c r="C181" s="4" t="s">
-        <v>473</v>
       </c>
     </row>
     <row r="182" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B182" s="4" t="s">
+        <v>473</v>
+      </c>
+      <c r="C182" s="4" t="s">
         <v>474</v>
-      </c>
-      <c r="C182" s="4" t="s">
-        <v>475</v>
       </c>
     </row>
     <row r="183" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B183" s="4" t="s">
+        <v>475</v>
+      </c>
+      <c r="C183" s="4" t="s">
         <v>476</v>
-      </c>
-      <c r="C183" s="4" t="s">
-        <v>477</v>
       </c>
     </row>
     <row r="184" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B184" s="4" t="s">
+        <v>477</v>
+      </c>
+      <c r="C184" s="4" t="s">
         <v>478</v>
-      </c>
-      <c r="C184" s="4" t="s">
-        <v>479</v>
       </c>
     </row>
     <row r="185" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B185" s="4" t="s">
+        <v>479</v>
+      </c>
+      <c r="C185" s="4" t="s">
         <v>480</v>
-      </c>
-      <c r="C185" s="4" t="s">
-        <v>481</v>
       </c>
     </row>
     <row r="186" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B186" s="4" t="s">
+        <v>481</v>
+      </c>
+      <c r="C186" s="4" t="s">
         <v>482</v>
-      </c>
-      <c r="C186" s="4" t="s">
-        <v>483</v>
       </c>
     </row>
     <row r="187" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B187" s="4" t="s">
+        <v>483</v>
+      </c>
+      <c r="C187" s="4" t="s">
         <v>484</v>
-      </c>
-      <c r="C187" s="4" t="s">
-        <v>485</v>
       </c>
     </row>
     <row r="188" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B188" s="4" t="s">
+        <v>485</v>
+      </c>
+      <c r="C188" s="4" t="s">
         <v>486</v>
-      </c>
-      <c r="C188" s="4" t="s">
-        <v>487</v>
       </c>
     </row>
     <row r="189" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B189" s="4" t="s">
+        <v>487</v>
+      </c>
+      <c r="C189" s="4" t="s">
         <v>488</v>
-      </c>
-      <c r="C189" s="4" t="s">
-        <v>489</v>
       </c>
     </row>
     <row r="190" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B190" s="4" t="s">
+        <v>489</v>
+      </c>
+      <c r="C190" s="4" t="s">
         <v>490</v>
-      </c>
-      <c r="C190" s="4" t="s">
-        <v>491</v>
       </c>
     </row>
     <row r="191" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B191" s="4" t="s">
+        <v>491</v>
+      </c>
+      <c r="C191" s="4" t="s">
         <v>492</v>
-      </c>
-      <c r="C191" s="4" t="s">
-        <v>493</v>
       </c>
     </row>
     <row r="192" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B192" s="4" t="s">
+        <v>493</v>
+      </c>
+      <c r="C192" s="4" t="s">
         <v>494</v>
-      </c>
-      <c r="C192" s="4" t="s">
-        <v>495</v>
       </c>
     </row>
     <row r="193" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B193" s="4" t="s">
+        <v>495</v>
+      </c>
+      <c r="C193" s="4" t="s">
         <v>496</v>
-      </c>
-      <c r="C193" s="4" t="s">
-        <v>497</v>
       </c>
     </row>
     <row r="194" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B194" s="4" t="s">
+        <v>497</v>
+      </c>
+      <c r="C194" s="4" t="s">
         <v>498</v>
-      </c>
-      <c r="C194" s="4" t="s">
-        <v>499</v>
       </c>
     </row>
     <row r="195" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B195" s="4" t="s">
+        <v>499</v>
+      </c>
+      <c r="C195" s="4" t="s">
         <v>500</v>
-      </c>
-      <c r="C195" s="4" t="s">
-        <v>501</v>
       </c>
     </row>
     <row r="196" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B196" s="4" t="s">
+        <v>501</v>
+      </c>
+      <c r="C196" s="4" t="s">
         <v>502</v>
-      </c>
-      <c r="C196" s="4" t="s">
-        <v>503</v>
       </c>
     </row>
     <row r="197" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B197" s="4" t="s">
+        <v>503</v>
+      </c>
+      <c r="C197" s="4" t="s">
         <v>504</v>
-      </c>
-      <c r="C197" s="4" t="s">
-        <v>505</v>
       </c>
     </row>
     <row r="198" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B198" s="4" t="s">
+        <v>505</v>
+      </c>
+      <c r="C198" s="4" t="s">
         <v>506</v>
-      </c>
-      <c r="C198" s="4" t="s">
-        <v>507</v>
       </c>
     </row>
     <row r="199" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B199" s="4" t="s">
+        <v>507</v>
+      </c>
+      <c r="C199" s="4" t="s">
         <v>508</v>
-      </c>
-      <c r="C199" s="4" t="s">
-        <v>509</v>
       </c>
     </row>
     <row r="200" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B200" s="4" t="s">
+        <v>509</v>
+      </c>
+      <c r="C200" s="4" t="s">
         <v>510</v>
-      </c>
-      <c r="C200" s="4" t="s">
-        <v>511</v>
       </c>
     </row>
     <row r="201" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B201" s="4" t="s">
+        <v>511</v>
+      </c>
+      <c r="C201" s="4" t="s">
         <v>512</v>
-      </c>
-      <c r="C201" s="4" t="s">
-        <v>513</v>
       </c>
     </row>
     <row r="202" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B202" s="4" t="s">
+        <v>513</v>
+      </c>
+      <c r="C202" s="4" t="s">
         <v>514</v>
-      </c>
-      <c r="C202" s="4" t="s">
-        <v>515</v>
       </c>
     </row>
     <row r="203" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B203" s="4" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="C203" s="4" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
     </row>
     <row r="204" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B204" s="4" t="s">
+        <v>516</v>
+      </c>
+      <c r="C204" s="4" t="s">
         <v>517</v>
-      </c>
-      <c r="C204" s="4" t="s">
-        <v>518</v>
       </c>
     </row>
     <row r="205" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B205" s="4" t="s">
+        <v>518</v>
+      </c>
+      <c r="C205" s="4" t="s">
         <v>519</v>
-      </c>
-      <c r="C205" s="4" t="s">
-        <v>520</v>
       </c>
     </row>
     <row r="206" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B206" s="4" t="s">
+        <v>520</v>
+      </c>
+      <c r="C206" s="4" t="s">
         <v>521</v>
-      </c>
-      <c r="C206" s="4" t="s">
-        <v>522</v>
       </c>
     </row>
     <row r="207" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B207" s="4" t="s">
+        <v>522</v>
+      </c>
+      <c r="C207" s="4" t="s">
         <v>523</v>
-      </c>
-      <c r="C207" s="4" t="s">
-        <v>524</v>
       </c>
     </row>
     <row r="208" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B208" s="4" t="s">
+        <v>524</v>
+      </c>
+      <c r="C208" s="4" t="s">
         <v>525</v>
-      </c>
-      <c r="C208" s="4" t="s">
-        <v>526</v>
       </c>
     </row>
     <row r="209" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B209" s="4" t="s">
+        <v>526</v>
+      </c>
+      <c r="C209" s="4" t="s">
         <v>527</v>
-      </c>
-      <c r="C209" s="4" t="s">
-        <v>528</v>
       </c>
     </row>
     <row r="210" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B210" s="4" t="s">
+        <v>528</v>
+      </c>
+      <c r="C210" s="4" t="s">
         <v>529</v>
-      </c>
-      <c r="C210" s="4" t="s">
-        <v>530</v>
       </c>
     </row>
     <row r="211" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B211" s="4" t="s">
+        <v>530</v>
+      </c>
+      <c r="C211" s="4" t="s">
         <v>531</v>
-      </c>
-      <c r="C211" s="4" t="s">
-        <v>532</v>
       </c>
     </row>
     <row r="212" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B212" s="4" t="s">
+        <v>532</v>
+      </c>
+      <c r="C212" s="4" t="s">
         <v>533</v>
-      </c>
-      <c r="C212" s="4" t="s">
-        <v>534</v>
       </c>
     </row>
   </sheetData>
@@ -5616,194 +5613,194 @@
     </row>
     <row r="2" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B2" s="3" t="s">
+        <v>534</v>
+      </c>
+      <c r="C2" s="3" t="s">
         <v>535</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>536</v>
       </c>
     </row>
     <row r="3" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B3" s="3" t="s">
+        <v>536</v>
+      </c>
+      <c r="C3" s="3" t="s">
         <v>537</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>538</v>
       </c>
     </row>
     <row r="4" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B4" s="3" t="s">
+        <v>538</v>
+      </c>
+      <c r="C4" s="3" t="s">
         <v>539</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>540</v>
       </c>
     </row>
     <row r="5" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B5" s="3" t="s">
+        <v>540</v>
+      </c>
+      <c r="C5" s="3" t="s">
         <v>541</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>542</v>
       </c>
     </row>
     <row r="6" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B6" s="3" t="s">
+        <v>542</v>
+      </c>
+      <c r="C6" s="3" t="s">
         <v>543</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>544</v>
       </c>
     </row>
     <row r="7" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B7" s="3" t="s">
+        <v>544</v>
+      </c>
+      <c r="C7" s="3" t="s">
         <v>545</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>546</v>
       </c>
     </row>
     <row r="8" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B8" s="3" t="s">
+        <v>546</v>
+      </c>
+      <c r="C8" s="3" t="s">
         <v>547</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>548</v>
       </c>
     </row>
     <row r="9" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B9" s="3" t="s">
+        <v>548</v>
+      </c>
+      <c r="C9" s="3" t="s">
         <v>549</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>550</v>
       </c>
     </row>
     <row r="10" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B10" s="3" t="s">
+        <v>550</v>
+      </c>
+      <c r="C10" s="3" t="s">
         <v>551</v>
-      </c>
-      <c r="C10" s="3" t="s">
-        <v>552</v>
       </c>
     </row>
     <row r="11" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B11" s="3" t="s">
+        <v>552</v>
+      </c>
+      <c r="C11" s="3" t="s">
         <v>553</v>
-      </c>
-      <c r="C11" s="3" t="s">
-        <v>554</v>
       </c>
     </row>
     <row r="12" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B12" s="3" t="s">
+        <v>554</v>
+      </c>
+      <c r="C12" s="3" t="s">
         <v>555</v>
-      </c>
-      <c r="C12" s="3" t="s">
-        <v>556</v>
       </c>
     </row>
     <row r="13" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B13" s="3" t="s">
+        <v>556</v>
+      </c>
+      <c r="C13" s="3" t="s">
         <v>557</v>
-      </c>
-      <c r="C13" s="3" t="s">
-        <v>558</v>
       </c>
     </row>
     <row r="14" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B14" s="3" t="s">
+        <v>558</v>
+      </c>
+      <c r="C14" s="3" t="s">
         <v>559</v>
-      </c>
-      <c r="C14" s="3" t="s">
-        <v>560</v>
       </c>
     </row>
     <row r="15" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B15" s="3" t="s">
+        <v>560</v>
+      </c>
+      <c r="C15" s="3" t="s">
         <v>561</v>
-      </c>
-      <c r="C15" s="3" t="s">
-        <v>562</v>
       </c>
     </row>
     <row r="16" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B16" s="3" t="s">
+        <v>562</v>
+      </c>
+      <c r="C16" s="3" t="s">
         <v>563</v>
-      </c>
-      <c r="C16" s="3" t="s">
-        <v>564</v>
       </c>
     </row>
     <row r="17" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B17" s="3" t="s">
+        <v>564</v>
+      </c>
+      <c r="C17" s="3" t="s">
         <v>565</v>
-      </c>
-      <c r="C17" s="3" t="s">
-        <v>566</v>
       </c>
     </row>
     <row r="18" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B18" s="3" t="s">
+        <v>566</v>
+      </c>
+      <c r="C18" s="3" t="s">
         <v>567</v>
-      </c>
-      <c r="C18" s="3" t="s">
-        <v>568</v>
       </c>
     </row>
     <row r="19" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B19" s="3" t="s">
+        <v>568</v>
+      </c>
+      <c r="C19" s="3" t="s">
         <v>569</v>
-      </c>
-      <c r="C19" s="3" t="s">
-        <v>570</v>
       </c>
     </row>
     <row r="20" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B20" s="3" t="s">
+        <v>570</v>
+      </c>
+      <c r="C20" s="3" t="s">
         <v>571</v>
-      </c>
-      <c r="C20" s="3" t="s">
-        <v>572</v>
       </c>
     </row>
     <row r="21" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B21" s="3" t="s">
+        <v>572</v>
+      </c>
+      <c r="C21" s="3" t="s">
         <v>573</v>
-      </c>
-      <c r="C21" s="3" t="s">
-        <v>574</v>
       </c>
     </row>
     <row r="22" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B22" s="3" t="s">
+        <v>574</v>
+      </c>
+      <c r="C22" s="3" t="s">
         <v>575</v>
-      </c>
-      <c r="C22" s="3" t="s">
-        <v>576</v>
       </c>
     </row>
     <row r="23" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B23" s="3" t="s">
+        <v>576</v>
+      </c>
+      <c r="C23" s="3" t="s">
         <v>577</v>
-      </c>
-      <c r="C23" s="3" t="s">
-        <v>578</v>
       </c>
     </row>
     <row r="24" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B24" s="3" t="s">
+        <v>578</v>
+      </c>
+      <c r="C24" s="3" t="s">
         <v>579</v>
-      </c>
-      <c r="C24" s="3" t="s">
-        <v>580</v>
       </c>
     </row>
     <row r="25" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B25" s="3" t="s">
+        <v>580</v>
+      </c>
+      <c r="C25" s="3" t="s">
         <v>581</v>
-      </c>
-      <c r="C25" s="3" t="s">
-        <v>582</v>
       </c>
     </row>
     <row r="26" spans="2:3" x14ac:dyDescent="0.25">
@@ -5811,583 +5808,583 @@
         <v>87</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
     </row>
     <row r="27" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B27" s="3" t="s">
+        <v>583</v>
+      </c>
+      <c r="C27" s="3" t="s">
         <v>584</v>
-      </c>
-      <c r="C27" s="3" t="s">
-        <v>585</v>
       </c>
     </row>
     <row r="28" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B28" s="3" t="s">
+        <v>585</v>
+      </c>
+      <c r="C28" s="3" t="s">
         <v>586</v>
-      </c>
-      <c r="C28" s="3" t="s">
-        <v>587</v>
       </c>
     </row>
     <row r="29" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B29" s="3" t="s">
+        <v>587</v>
+      </c>
+      <c r="C29" s="3" t="s">
         <v>588</v>
-      </c>
-      <c r="C29" s="3" t="s">
-        <v>589</v>
       </c>
     </row>
     <row r="30" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B30" s="3" t="s">
+        <v>589</v>
+      </c>
+      <c r="C30" s="3" t="s">
         <v>590</v>
-      </c>
-      <c r="C30" s="3" t="s">
-        <v>591</v>
       </c>
     </row>
     <row r="31" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B31" s="3" t="s">
+        <v>591</v>
+      </c>
+      <c r="C31" s="3" t="s">
         <v>592</v>
-      </c>
-      <c r="C31" s="3" t="s">
-        <v>593</v>
       </c>
     </row>
     <row r="32" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B32" s="3" t="s">
+        <v>593</v>
+      </c>
+      <c r="C32" s="3" t="s">
         <v>594</v>
-      </c>
-      <c r="C32" s="3" t="s">
-        <v>595</v>
       </c>
     </row>
     <row r="33" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B33" s="3" t="s">
+        <v>595</v>
+      </c>
+      <c r="C33" s="3" t="s">
         <v>596</v>
-      </c>
-      <c r="C33" s="3" t="s">
-        <v>597</v>
       </c>
     </row>
     <row r="34" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B34" s="3" t="s">
+        <v>597</v>
+      </c>
+      <c r="C34" s="3" t="s">
         <v>598</v>
-      </c>
-      <c r="C34" s="3" t="s">
-        <v>599</v>
       </c>
     </row>
     <row r="35" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B35" s="3" t="s">
+        <v>599</v>
+      </c>
+      <c r="C35" s="3" t="s">
         <v>600</v>
-      </c>
-      <c r="C35" s="3" t="s">
-        <v>601</v>
       </c>
     </row>
     <row r="36" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B36" s="3" t="s">
+        <v>601</v>
+      </c>
+      <c r="C36" s="3" t="s">
         <v>602</v>
-      </c>
-      <c r="C36" s="3" t="s">
-        <v>603</v>
       </c>
     </row>
     <row r="37" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B37" s="3" t="s">
+        <v>603</v>
+      </c>
+      <c r="C37" s="3" t="s">
         <v>604</v>
-      </c>
-      <c r="C37" s="3" t="s">
-        <v>605</v>
       </c>
     </row>
     <row r="38" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B38" s="3" t="s">
+        <v>605</v>
+      </c>
+      <c r="C38" s="3" t="s">
         <v>606</v>
-      </c>
-      <c r="C38" s="3" t="s">
-        <v>607</v>
       </c>
     </row>
     <row r="39" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B39" s="3" t="s">
+        <v>607</v>
+      </c>
+      <c r="C39" s="3" t="s">
         <v>608</v>
-      </c>
-      <c r="C39" s="3" t="s">
-        <v>609</v>
       </c>
     </row>
     <row r="40" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B40" s="3" t="s">
+        <v>609</v>
+      </c>
+      <c r="C40" s="3" t="s">
         <v>610</v>
-      </c>
-      <c r="C40" s="3" t="s">
-        <v>611</v>
       </c>
     </row>
     <row r="41" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B41" s="3" t="s">
+        <v>611</v>
+      </c>
+      <c r="C41" s="3" t="s">
         <v>612</v>
-      </c>
-      <c r="C41" s="3" t="s">
-        <v>613</v>
       </c>
     </row>
     <row r="42" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B42" s="3" t="s">
+        <v>613</v>
+      </c>
+      <c r="C42" s="3" t="s">
         <v>614</v>
-      </c>
-      <c r="C42" s="3" t="s">
-        <v>615</v>
       </c>
     </row>
     <row r="43" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B43" s="3" t="s">
+        <v>615</v>
+      </c>
+      <c r="C43" s="3" t="s">
         <v>616</v>
-      </c>
-      <c r="C43" s="3" t="s">
-        <v>617</v>
       </c>
     </row>
     <row r="44" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B44" s="3" t="s">
+        <v>617</v>
+      </c>
+      <c r="C44" s="3" t="s">
         <v>618</v>
-      </c>
-      <c r="C44" s="3" t="s">
-        <v>619</v>
       </c>
     </row>
     <row r="45" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B45" s="3" t="s">
+        <v>619</v>
+      </c>
+      <c r="C45" s="3" t="s">
         <v>620</v>
-      </c>
-      <c r="C45" s="3" t="s">
-        <v>621</v>
       </c>
     </row>
     <row r="46" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B46" s="3" t="s">
+        <v>621</v>
+      </c>
+      <c r="C46" s="3" t="s">
         <v>622</v>
-      </c>
-      <c r="C46" s="3" t="s">
-        <v>623</v>
       </c>
     </row>
     <row r="47" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B47" s="3" t="s">
+        <v>623</v>
+      </c>
+      <c r="C47" s="3" t="s">
         <v>624</v>
-      </c>
-      <c r="C47" s="3" t="s">
-        <v>625</v>
       </c>
     </row>
     <row r="48" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B48" s="3" t="s">
+        <v>625</v>
+      </c>
+      <c r="C48" s="3" t="s">
         <v>626</v>
-      </c>
-      <c r="C48" s="3" t="s">
-        <v>627</v>
       </c>
     </row>
     <row r="49" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B49" s="3" t="s">
+        <v>627</v>
+      </c>
+      <c r="C49" s="3" t="s">
         <v>628</v>
-      </c>
-      <c r="C49" s="3" t="s">
-        <v>629</v>
       </c>
     </row>
     <row r="50" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B50" s="3" t="s">
+        <v>629</v>
+      </c>
+      <c r="C50" s="3" t="s">
         <v>630</v>
-      </c>
-      <c r="C50" s="3" t="s">
-        <v>631</v>
       </c>
     </row>
     <row r="51" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B51" s="3" t="s">
+        <v>631</v>
+      </c>
+      <c r="C51" s="3" t="s">
         <v>632</v>
-      </c>
-      <c r="C51" s="3" t="s">
-        <v>633</v>
       </c>
     </row>
     <row r="52" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B52" s="3" t="s">
+        <v>633</v>
+      </c>
+      <c r="C52" s="3" t="s">
         <v>634</v>
-      </c>
-      <c r="C52" s="3" t="s">
-        <v>635</v>
       </c>
     </row>
     <row r="53" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B53" s="3" t="s">
+        <v>635</v>
+      </c>
+      <c r="C53" s="3" t="s">
         <v>636</v>
-      </c>
-      <c r="C53" s="3" t="s">
-        <v>637</v>
       </c>
     </row>
     <row r="54" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B54" s="3" t="s">
+        <v>637</v>
+      </c>
+      <c r="C54" s="3" t="s">
         <v>638</v>
-      </c>
-      <c r="C54" s="3" t="s">
-        <v>639</v>
       </c>
     </row>
     <row r="55" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B55" s="3" t="s">
+        <v>639</v>
+      </c>
+      <c r="C55" s="3" t="s">
         <v>640</v>
-      </c>
-      <c r="C55" s="3" t="s">
-        <v>641</v>
       </c>
     </row>
     <row r="56" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B56" s="3" t="s">
+        <v>641</v>
+      </c>
+      <c r="C56" s="3" t="s">
         <v>642</v>
-      </c>
-      <c r="C56" s="3" t="s">
-        <v>643</v>
       </c>
     </row>
     <row r="57" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B57" s="3" t="s">
+        <v>643</v>
+      </c>
+      <c r="C57" s="3" t="s">
         <v>644</v>
-      </c>
-      <c r="C57" s="3" t="s">
-        <v>645</v>
       </c>
     </row>
     <row r="58" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B58" s="3" t="s">
+        <v>645</v>
+      </c>
+      <c r="C58" s="3" t="s">
         <v>646</v>
-      </c>
-      <c r="C58" s="3" t="s">
-        <v>647</v>
       </c>
     </row>
     <row r="59" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B59" s="3" t="s">
+        <v>647</v>
+      </c>
+      <c r="C59" s="3" t="s">
         <v>648</v>
-      </c>
-      <c r="C59" s="3" t="s">
-        <v>649</v>
       </c>
     </row>
     <row r="60" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B60" s="3" t="s">
+        <v>649</v>
+      </c>
+      <c r="C60" s="3" t="s">
         <v>650</v>
-      </c>
-      <c r="C60" s="3" t="s">
-        <v>651</v>
       </c>
     </row>
     <row r="61" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B61" s="3" t="s">
+        <v>651</v>
+      </c>
+      <c r="C61" s="3" t="s">
         <v>652</v>
-      </c>
-      <c r="C61" s="3" t="s">
-        <v>653</v>
       </c>
     </row>
     <row r="62" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B62" s="3" t="s">
+        <v>653</v>
+      </c>
+      <c r="C62" s="3" t="s">
         <v>654</v>
-      </c>
-      <c r="C62" s="3" t="s">
-        <v>655</v>
       </c>
     </row>
     <row r="63" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B63" s="3" t="s">
+        <v>655</v>
+      </c>
+      <c r="C63" s="3" t="s">
         <v>656</v>
-      </c>
-      <c r="C63" s="3" t="s">
-        <v>657</v>
       </c>
     </row>
     <row r="64" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B64" s="3" t="s">
+        <v>657</v>
+      </c>
+      <c r="C64" s="3" t="s">
         <v>658</v>
-      </c>
-      <c r="C64" s="3" t="s">
-        <v>659</v>
       </c>
     </row>
     <row r="65" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B65" s="3" t="s">
+        <v>659</v>
+      </c>
+      <c r="C65" s="3" t="s">
         <v>660</v>
-      </c>
-      <c r="C65" s="3" t="s">
-        <v>661</v>
       </c>
     </row>
     <row r="66" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B66" s="3" t="s">
+        <v>661</v>
+      </c>
+      <c r="C66" s="3" t="s">
         <v>662</v>
-      </c>
-      <c r="C66" s="3" t="s">
-        <v>663</v>
       </c>
     </row>
     <row r="67" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B67" s="3" t="s">
+        <v>663</v>
+      </c>
+      <c r="C67" s="3" t="s">
         <v>664</v>
-      </c>
-      <c r="C67" s="3" t="s">
-        <v>665</v>
       </c>
     </row>
     <row r="68" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B68" s="3" t="s">
+        <v>665</v>
+      </c>
+      <c r="C68" s="3" t="s">
         <v>666</v>
-      </c>
-      <c r="C68" s="3" t="s">
-        <v>667</v>
       </c>
     </row>
     <row r="69" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B69" s="3" t="s">
+        <v>667</v>
+      </c>
+      <c r="C69" s="3" t="s">
         <v>668</v>
-      </c>
-      <c r="C69" s="3" t="s">
-        <v>669</v>
       </c>
     </row>
     <row r="70" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B70" s="3" t="s">
+        <v>669</v>
+      </c>
+      <c r="C70" s="3" t="s">
         <v>670</v>
-      </c>
-      <c r="C70" s="3" t="s">
-        <v>671</v>
       </c>
     </row>
     <row r="71" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B71" s="3" t="s">
+        <v>671</v>
+      </c>
+      <c r="C71" s="3" t="s">
         <v>672</v>
-      </c>
-      <c r="C71" s="3" t="s">
-        <v>673</v>
       </c>
     </row>
     <row r="72" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B72" s="3" t="s">
+        <v>673</v>
+      </c>
+      <c r="C72" s="3" t="s">
         <v>674</v>
-      </c>
-      <c r="C72" s="3" t="s">
-        <v>675</v>
       </c>
     </row>
     <row r="73" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B73" s="3" t="s">
+        <v>675</v>
+      </c>
+      <c r="C73" s="3" t="s">
         <v>676</v>
-      </c>
-      <c r="C73" s="3" t="s">
-        <v>677</v>
       </c>
     </row>
     <row r="74" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B74" s="3" t="s">
+        <v>677</v>
+      </c>
+      <c r="C74" s="3" t="s">
         <v>678</v>
-      </c>
-      <c r="C74" s="3" t="s">
-        <v>679</v>
       </c>
     </row>
     <row r="75" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B75" s="3" t="s">
+        <v>679</v>
+      </c>
+      <c r="C75" s="3" t="s">
         <v>680</v>
-      </c>
-      <c r="C75" s="3" t="s">
-        <v>681</v>
       </c>
     </row>
     <row r="76" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B76" s="3" t="s">
+        <v>681</v>
+      </c>
+      <c r="C76" s="3" t="s">
         <v>682</v>
-      </c>
-      <c r="C76" s="3" t="s">
-        <v>683</v>
       </c>
     </row>
     <row r="77" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B77" s="3" t="s">
+        <v>683</v>
+      </c>
+      <c r="C77" s="3" t="s">
         <v>684</v>
-      </c>
-      <c r="C77" s="3" t="s">
-        <v>685</v>
       </c>
     </row>
     <row r="78" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B78" s="3" t="s">
+        <v>685</v>
+      </c>
+      <c r="C78" s="3" t="s">
         <v>686</v>
-      </c>
-      <c r="C78" s="3" t="s">
-        <v>687</v>
       </c>
     </row>
     <row r="79" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B79" s="3" t="s">
+        <v>687</v>
+      </c>
+      <c r="C79" s="3" t="s">
         <v>688</v>
-      </c>
-      <c r="C79" s="3" t="s">
-        <v>689</v>
       </c>
     </row>
     <row r="80" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B80" s="3" t="s">
+        <v>689</v>
+      </c>
+      <c r="C80" s="3" t="s">
         <v>690</v>
-      </c>
-      <c r="C80" s="3" t="s">
-        <v>691</v>
       </c>
     </row>
     <row r="81" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B81" s="3" t="s">
+        <v>691</v>
+      </c>
+      <c r="C81" s="3" t="s">
         <v>692</v>
-      </c>
-      <c r="C81" s="3" t="s">
-        <v>693</v>
       </c>
     </row>
     <row r="82" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B82" s="3" t="s">
+        <v>693</v>
+      </c>
+      <c r="C82" s="3" t="s">
         <v>694</v>
-      </c>
-      <c r="C82" s="3" t="s">
-        <v>695</v>
       </c>
     </row>
     <row r="83" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B83" s="3" t="s">
+        <v>695</v>
+      </c>
+      <c r="C83" s="3" t="s">
         <v>696</v>
-      </c>
-      <c r="C83" s="3" t="s">
-        <v>697</v>
       </c>
     </row>
     <row r="84" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B84" s="3" t="s">
+        <v>697</v>
+      </c>
+      <c r="C84" s="3" t="s">
         <v>698</v>
-      </c>
-      <c r="C84" s="3" t="s">
-        <v>699</v>
       </c>
     </row>
     <row r="85" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B85" s="3" t="s">
+        <v>699</v>
+      </c>
+      <c r="C85" s="3" t="s">
         <v>700</v>
-      </c>
-      <c r="C85" s="3" t="s">
-        <v>701</v>
       </c>
     </row>
     <row r="86" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B86" s="3" t="s">
+        <v>701</v>
+      </c>
+      <c r="C86" s="3" t="s">
         <v>702</v>
-      </c>
-      <c r="C86" s="3" t="s">
-        <v>703</v>
       </c>
     </row>
     <row r="87" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B87" s="3" t="s">
+        <v>703</v>
+      </c>
+      <c r="C87" s="3" t="s">
         <v>704</v>
-      </c>
-      <c r="C87" s="3" t="s">
-        <v>705</v>
       </c>
     </row>
     <row r="88" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B88" s="3" t="s">
+        <v>705</v>
+      </c>
+      <c r="C88" s="3" t="s">
         <v>706</v>
-      </c>
-      <c r="C88" s="3" t="s">
-        <v>707</v>
       </c>
     </row>
     <row r="89" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B89" s="3" t="s">
+        <v>707</v>
+      </c>
+      <c r="C89" s="3" t="s">
         <v>708</v>
-      </c>
-      <c r="C89" s="3" t="s">
-        <v>709</v>
       </c>
     </row>
     <row r="90" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B90" s="3" t="s">
+        <v>709</v>
+      </c>
+      <c r="C90" s="3" t="s">
         <v>710</v>
-      </c>
-      <c r="C90" s="3" t="s">
-        <v>711</v>
       </c>
     </row>
     <row r="91" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B91" s="3" t="s">
+        <v>711</v>
+      </c>
+      <c r="C91" s="3" t="s">
         <v>712</v>
-      </c>
-      <c r="C91" s="3" t="s">
-        <v>713</v>
       </c>
     </row>
     <row r="92" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B92" s="3" t="s">
+        <v>713</v>
+      </c>
+      <c r="C92" s="3" t="s">
         <v>714</v>
-      </c>
-      <c r="C92" s="3" t="s">
-        <v>715</v>
       </c>
     </row>
     <row r="93" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B93" s="3" t="s">
+        <v>715</v>
+      </c>
+      <c r="C93" s="3" t="s">
         <v>716</v>
-      </c>
-      <c r="C93" s="3" t="s">
-        <v>717</v>
       </c>
     </row>
     <row r="94" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B94" s="3" t="s">
+        <v>717</v>
+      </c>
+      <c r="C94" s="3" t="s">
         <v>718</v>
-      </c>
-      <c r="C94" s="3" t="s">
-        <v>719</v>
       </c>
     </row>
     <row r="95" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B95" s="3" t="s">
+        <v>719</v>
+      </c>
+      <c r="C95" s="3" t="s">
         <v>720</v>
-      </c>
-      <c r="C95" s="3" t="s">
-        <v>721</v>
       </c>
     </row>
     <row r="96" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B96" s="3" t="s">
+        <v>721</v>
+      </c>
+      <c r="C96" s="3" t="s">
         <v>722</v>
-      </c>
-      <c r="C96" s="3" t="s">
-        <v>723</v>
       </c>
     </row>
     <row r="97" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B97" s="3" t="s">
+        <v>723</v>
+      </c>
+      <c r="C97" s="3" t="s">
         <v>724</v>
-      </c>
-      <c r="C97" s="3" t="s">
-        <v>725</v>
       </c>
     </row>
     <row r="98" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B98" s="3" t="s">
+        <v>725</v>
+      </c>
+      <c r="C98" s="3" t="s">
         <v>726</v>
-      </c>
-      <c r="C98" s="3" t="s">
-        <v>727</v>
       </c>
     </row>
   </sheetData>
@@ -6411,10 +6408,10 @@
     </row>
     <row r="2" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B2" s="2" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>728</v>
+        <v>727</v>
       </c>
     </row>
     <row r="3" spans="2:3" x14ac:dyDescent="0.25">
@@ -6422,7 +6419,7 @@
         <v>154</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
     </row>
     <row r="4" spans="2:3" x14ac:dyDescent="0.25">
@@ -6430,7 +6427,7 @@
         <v>156</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
     </row>
     <row r="5" spans="2:3" x14ac:dyDescent="0.25">
@@ -6438,7 +6435,7 @@
         <v>158</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>731</v>
+        <v>730</v>
       </c>
     </row>
     <row r="6" spans="2:3" x14ac:dyDescent="0.25">
@@ -6446,7 +6443,7 @@
         <v>160</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
     </row>
     <row r="7" spans="2:3" x14ac:dyDescent="0.25">
@@ -6454,47 +6451,47 @@
         <v>162</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
     </row>
     <row r="8" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B8" s="2" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
     </row>
     <row r="9" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B9" s="2" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>734</v>
+        <v>733</v>
       </c>
     </row>
     <row r="10" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B10" s="2" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
     </row>
     <row r="11" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B11" s="2" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
     </row>
     <row r="12" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B12" s="2" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
     </row>
     <row r="13" spans="2:3" x14ac:dyDescent="0.25">
@@ -6502,135 +6499,135 @@
         <v>87</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
     </row>
     <row r="14" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B14" s="2" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
     </row>
     <row r="15" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B15" s="2" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
     </row>
     <row r="16" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B16" s="2" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
     </row>
     <row r="17" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B17" s="2" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
     </row>
     <row r="18" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B18" s="2" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
     </row>
     <row r="19" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B19" s="2" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
     </row>
     <row r="20" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B20" s="2" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>741</v>
+        <v>740</v>
       </c>
     </row>
     <row r="21" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B21" s="2" t="s">
+        <v>741</v>
+      </c>
+      <c r="C21" s="2" t="s">
         <v>742</v>
-      </c>
-      <c r="C21" s="2" t="s">
-        <v>743</v>
       </c>
     </row>
     <row r="22" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B22" s="2" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>744</v>
+        <v>743</v>
       </c>
     </row>
     <row r="23" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B23" s="2" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>745</v>
+        <v>744</v>
       </c>
     </row>
     <row r="24" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B24" s="2" t="s">
+        <v>745</v>
+      </c>
+      <c r="C24" s="2" t="s">
         <v>746</v>
-      </c>
-      <c r="C24" s="2" t="s">
-        <v>747</v>
       </c>
     </row>
     <row r="25" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B25" s="2" t="s">
+        <v>747</v>
+      </c>
+      <c r="C25" s="2" t="s">
         <v>748</v>
-      </c>
-      <c r="C25" s="2" t="s">
-        <v>749</v>
       </c>
     </row>
     <row r="26" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B26" s="2" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>750</v>
+        <v>749</v>
       </c>
     </row>
     <row r="27" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B27" s="2" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>751</v>
+        <v>750</v>
       </c>
     </row>
     <row r="28" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B28" s="2" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>752</v>
+        <v>751</v>
       </c>
     </row>
     <row r="29" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B29" s="2" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
     </row>
     <row r="30" spans="2:3" x14ac:dyDescent="0.25">
@@ -6638,191 +6635,191 @@
         <v>6</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>754</v>
+        <v>753</v>
       </c>
     </row>
     <row r="31" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B31" s="2" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
     </row>
     <row r="32" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B32" s="2" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
     </row>
     <row r="33" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B33" s="2" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
     </row>
     <row r="34" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B34" s="2" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
     </row>
     <row r="35" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B35" s="2" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
     </row>
     <row r="36" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B36" s="2" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
     </row>
     <row r="37" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B37" s="2" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>761</v>
+        <v>760</v>
       </c>
     </row>
     <row r="38" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B38" s="2" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>762</v>
+        <v>761</v>
       </c>
     </row>
     <row r="39" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B39" s="2" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
     </row>
     <row r="40" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B40" s="2" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>764</v>
+        <v>763</v>
       </c>
     </row>
     <row r="41" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B41" s="2" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>765</v>
+        <v>764</v>
       </c>
     </row>
     <row r="42" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B42" s="2" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
     </row>
     <row r="43" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B43" s="2" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>767</v>
+        <v>766</v>
       </c>
     </row>
     <row r="44" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B44" s="2" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>768</v>
+        <v>767</v>
       </c>
     </row>
     <row r="45" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B45" s="2" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>744</v>
+        <v>743</v>
       </c>
     </row>
     <row r="46" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B46" s="2" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>769</v>
+        <v>768</v>
       </c>
     </row>
     <row r="47" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B47" s="2" t="s">
+        <v>769</v>
+      </c>
+      <c r="C47" s="2" t="s">
         <v>770</v>
-      </c>
-      <c r="C47" s="2" t="s">
-        <v>771</v>
       </c>
     </row>
     <row r="48" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B48" s="2" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>772</v>
+        <v>771</v>
       </c>
     </row>
     <row r="49" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B49" s="2" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>773</v>
+        <v>772</v>
       </c>
     </row>
     <row r="50" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B50" s="2" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>774</v>
+        <v>773</v>
       </c>
     </row>
     <row r="51" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B51" s="2" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>775</v>
+        <v>774</v>
       </c>
     </row>
     <row r="52" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B52" s="2" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>776</v>
+        <v>775</v>
       </c>
     </row>
     <row r="53" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B53" s="2" t="s">
+        <v>776</v>
+      </c>
+      <c r="C53" s="2" t="s">
         <v>777</v>
-      </c>
-      <c r="C53" s="2" t="s">
-        <v>778</v>
       </c>
     </row>
   </sheetData>
@@ -6846,242 +6843,242 @@
     </row>
     <row r="2" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B2" s="1" t="s">
+        <v>778</v>
+      </c>
+      <c r="C2" s="1" t="s">
         <v>779</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>780</v>
       </c>
     </row>
     <row r="3" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B3" s="1" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
     </row>
     <row r="4" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B4" s="1" t="s">
-        <v>782</v>
+        <v>781</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
     </row>
     <row r="5" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B5" s="1" t="s">
-        <v>783</v>
+        <v>782</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
     </row>
     <row r="6" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B6" s="1" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>784</v>
+        <v>783</v>
       </c>
     </row>
     <row r="7" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B7" s="1" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>785</v>
+        <v>784</v>
       </c>
     </row>
     <row r="8" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B8" s="1" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>786</v>
+        <v>785</v>
       </c>
     </row>
     <row r="9" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B9" s="1" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
     </row>
     <row r="10" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B10" s="1" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
     </row>
     <row r="11" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B11" s="1" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>789</v>
+        <v>788</v>
       </c>
     </row>
     <row r="12" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B12" s="1" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>790</v>
+        <v>789</v>
       </c>
     </row>
     <row r="13" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B13" s="1" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>791</v>
+        <v>790</v>
       </c>
     </row>
     <row r="14" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B14" s="1" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>792</v>
+        <v>791</v>
       </c>
     </row>
     <row r="15" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B15" s="1" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>731</v>
+        <v>730</v>
       </c>
     </row>
     <row r="16" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B16" s="1" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
     </row>
     <row r="17" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B17" s="1" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
     </row>
     <row r="18" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B18" s="1" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>793</v>
+        <v>792</v>
       </c>
     </row>
     <row r="19" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B19" s="1" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
     </row>
     <row r="20" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B20" s="1" t="s">
+        <v>793</v>
+      </c>
+      <c r="C20" s="1" t="s">
         <v>794</v>
-      </c>
-      <c r="C20" s="1" t="s">
-        <v>795</v>
       </c>
     </row>
     <row r="21" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B21" s="1" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>796</v>
+        <v>795</v>
       </c>
     </row>
     <row r="22" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B22" s="1" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
     </row>
     <row r="23" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B23" s="1" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
     </row>
     <row r="24" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B24" s="1" t="s">
+        <v>798</v>
+      </c>
+      <c r="C24" s="1" t="s">
         <v>799</v>
-      </c>
-      <c r="C24" s="1" t="s">
-        <v>800</v>
       </c>
     </row>
     <row r="25" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B25" s="1" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>745</v>
+        <v>744</v>
       </c>
     </row>
     <row r="26" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B26" s="1" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
     </row>
     <row r="27" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B27" s="1" t="s">
+        <v>800</v>
+      </c>
+      <c r="C27" s="1" t="s">
         <v>801</v>
-      </c>
-      <c r="C27" s="1" t="s">
-        <v>802</v>
       </c>
     </row>
     <row r="28" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B28" s="1" t="s">
+        <v>802</v>
+      </c>
+      <c r="C28" s="1" t="s">
         <v>803</v>
-      </c>
-      <c r="C28" s="1" t="s">
-        <v>804</v>
       </c>
     </row>
     <row r="29" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B29" s="1" t="s">
-        <v>805</v>
+        <v>804</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>750</v>
+        <v>749</v>
       </c>
     </row>
     <row r="30" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B30" s="1" t="s">
+        <v>805</v>
+      </c>
+      <c r="C30" s="1" t="s">
         <v>806</v>
-      </c>
-      <c r="C30" s="1" t="s">
-        <v>807</v>
       </c>
     </row>
     <row r="31" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B31" s="1" t="s">
+        <v>807</v>
+      </c>
+      <c r="C31" s="1" t="s">
         <v>808</v>
-      </c>
-      <c r="C31" s="1" t="s">
-        <v>809</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/Editor/DataDic/Data.xlsx
+++ b/Assets/Editor/DataDic/Data.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="17385" windowHeight="7860" firstSheet="1" activeTab="2"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="17385" windowHeight="7860" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="FishData" sheetId="1" r:id="rId1"/>
@@ -18,14 +18,14 @@
     <sheet name="GameActionData" sheetId="5" r:id="rId4"/>
     <sheet name="GameEventData" sheetId="6" r:id="rId5"/>
     <sheet name="OperateData" sheetId="7" r:id="rId6"/>
-    <sheet name="NPCFunctionData" sheetId="8" r:id="rId11"/>
+    <sheet name="NPCFunctionData" sheetId="8" r:id="rId7"/>
   </sheets>
-  <calcPr calcId="162913" fullCalcOnLoad="1"/>
+  <calcPr calcId="162913"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="824" uniqueCount="824">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1011" uniqueCount="824">
   <si>
     <t>Key</t>
   </si>
@@ -633,10 +633,10 @@
     <t>405</t>
   </si>
   <si>
-    <r xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+    <r>
       <t>6</t>
     </r>
-    <r xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+    <r>
       <rPr>
         <sz val="11"/>
         <rFont val="Calibri"/>
@@ -644,7 +644,7 @@
       </rPr>
       <t>,0</t>
     </r>
-    <phoneticPr xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" fontId="0" type="noConversion"/>
+    <phoneticPr fontId="0" type="noConversion"/>
   </si>
   <si>
     <t>后山</t>
@@ -659,10 +659,10 @@
     <t>植物店</t>
   </si>
   <si>
-    <r xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+    <r>
       <t>9</t>
     </r>
-    <r xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+    <r>
       <rPr>
         <sz val="11"/>
         <rFont val="Calibri"/>
@@ -670,7 +670,7 @@
       </rPr>
       <t>,0</t>
     </r>
-    <phoneticPr xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" fontId="0" type="noConversion"/>
+    <phoneticPr fontId="0" type="noConversion"/>
   </si>
   <si>
     <t>教堂</t>
@@ -2525,8 +2525,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
@@ -2540,6 +2539,12 @@
       <sz val="11"/>
       <name val="Calibri"/>
       <family val="2"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
     </font>
   </fonts>
   <fills count="3">
@@ -2569,16 +2574,16 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="10">
-    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="0" applyProtection="1"/>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="0" applyProtection="1"/>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="0" applyProtection="1"/>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="0" applyProtection="1"/>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="0" applyProtection="1"/>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="0" applyProtection="1"/>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="0" applyProtection="1"/>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="2" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="0" applyProtection="1"/>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="1" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="0" applyProtection="1"/>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="2" applyFill="1" borderId="0" applyBorder="1" xfId="0" applyProtection="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -2862,7 +2867,7 @@
   <dimension ref="B1:C32"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B1" s="6" t="s">
         <v>0</v>
       </c>
@@ -2870,7 +2875,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B2" s="6" t="s">
         <v>722</v>
       </c>
@@ -2878,7 +2883,7 @@
         <v>723</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B3" s="6" t="s">
         <v>303</v>
       </c>
@@ -2886,7 +2891,7 @@
         <v>724</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B4" s="6" t="s">
         <v>305</v>
       </c>
@@ -2894,7 +2899,7 @@
         <v>725</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B5" s="6" t="s">
         <v>307</v>
       </c>
@@ -2902,7 +2907,7 @@
         <v>726</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B6" s="6" t="s">
         <v>309</v>
       </c>
@@ -2910,7 +2915,7 @@
         <v>727</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B7" s="6" t="s">
         <v>311</v>
       </c>
@@ -2918,7 +2923,7 @@
         <v>728</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B8" s="6" t="s">
         <v>315</v>
       </c>
@@ -2926,7 +2931,7 @@
         <v>729</v>
       </c>
     </row>
-    <row r="9">
+    <row r="9" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B9" s="6" t="s">
         <v>317</v>
       </c>
@@ -2934,7 +2939,7 @@
         <v>730</v>
       </c>
     </row>
-    <row r="10">
+    <row r="10" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B10" s="6" t="s">
         <v>319</v>
       </c>
@@ -2942,7 +2947,7 @@
         <v>731</v>
       </c>
     </row>
-    <row r="11">
+    <row r="11" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B11" s="6" t="s">
         <v>321</v>
       </c>
@@ -2950,7 +2955,7 @@
         <v>732</v>
       </c>
     </row>
-    <row r="12">
+    <row r="12" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B12" s="6" t="s">
         <v>323</v>
       </c>
@@ -2958,7 +2963,7 @@
         <v>733</v>
       </c>
     </row>
-    <row r="13">
+    <row r="13" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B13" s="6" t="s">
         <v>325</v>
       </c>
@@ -2966,7 +2971,7 @@
         <v>734</v>
       </c>
     </row>
-    <row r="14">
+    <row r="14" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B14" s="6" t="s">
         <v>329</v>
       </c>
@@ -2974,7 +2979,7 @@
         <v>735</v>
       </c>
     </row>
-    <row r="15">
+    <row r="15" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B15" s="6" t="s">
         <v>331</v>
       </c>
@@ -2982,7 +2987,7 @@
         <v>736</v>
       </c>
     </row>
-    <row r="16">
+    <row r="16" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B16" s="6" t="s">
         <v>333</v>
       </c>
@@ -2990,7 +2995,7 @@
         <v>737</v>
       </c>
     </row>
-    <row r="17">
+    <row r="17" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B17" s="6" t="s">
         <v>335</v>
       </c>
@@ -2998,7 +3003,7 @@
         <v>738</v>
       </c>
     </row>
-    <row r="18">
+    <row r="18" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B18" s="6" t="s">
         <v>337</v>
       </c>
@@ -3006,7 +3011,7 @@
         <v>739</v>
       </c>
     </row>
-    <row r="19">
+    <row r="19" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B19" s="6" t="s">
         <v>485</v>
       </c>
@@ -3014,7 +3019,7 @@
         <v>740</v>
       </c>
     </row>
-    <row r="20">
+    <row r="20" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B20" s="6" t="s">
         <v>487</v>
       </c>
@@ -3022,7 +3027,7 @@
         <v>741</v>
       </c>
     </row>
-    <row r="21">
+    <row r="21" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B21" s="6" t="s">
         <v>490</v>
       </c>
@@ -3030,7 +3035,7 @@
         <v>742</v>
       </c>
     </row>
-    <row r="22">
+    <row r="22" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B22" s="6" t="s">
         <v>494</v>
       </c>
@@ -3038,7 +3043,7 @@
         <v>743</v>
       </c>
     </row>
-    <row r="23">
+    <row r="23" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B23" s="6" t="s">
         <v>495</v>
       </c>
@@ -3046,7 +3051,7 @@
         <v>744</v>
       </c>
     </row>
-    <row r="24">
+    <row r="24" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B24" s="6" t="s">
         <v>500</v>
       </c>
@@ -3054,7 +3059,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="25">
+    <row r="25" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B25" s="6" t="s">
         <v>502</v>
       </c>
@@ -3062,7 +3067,7 @@
         <v>746</v>
       </c>
     </row>
-    <row r="26">
+    <row r="26" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B26" s="6" t="s">
         <v>504</v>
       </c>
@@ -3070,7 +3075,7 @@
         <v>747</v>
       </c>
     </row>
-    <row r="27">
+    <row r="27" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B27" s="6" t="s">
         <v>246</v>
       </c>
@@ -3078,7 +3083,7 @@
         <v>748</v>
       </c>
     </row>
-    <row r="28">
+    <row r="28" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B28" s="6" t="s">
         <v>507</v>
       </c>
@@ -3086,7 +3091,7 @@
         <v>749</v>
       </c>
     </row>
-    <row r="29">
+    <row r="29" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B29" s="6" t="s">
         <v>509</v>
       </c>
@@ -3094,7 +3099,7 @@
         <v>750</v>
       </c>
     </row>
-    <row r="30">
+    <row r="30" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B30" s="6" t="s">
         <v>511</v>
       </c>
@@ -3102,7 +3107,7 @@
         <v>751</v>
       </c>
     </row>
-    <row r="31">
+    <row r="31" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B31" s="6" t="s">
         <v>512</v>
       </c>
@@ -3110,7 +3115,7 @@
         <v>752</v>
       </c>
     </row>
-    <row r="32">
+    <row r="32" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B32" s="6" t="s">
         <v>514</v>
       </c>
@@ -3122,7 +3127,6 @@
   <phoneticPr fontId="0" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="1200" verticalDpi="1200"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
@@ -3131,10 +3135,10 @@
   <dimension ref="B1:O56"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="22.28515625" customWidth="1" style="2"/>
+    <col min="2" max="2" width="22.28515625" style="2" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B1" s="6" t="s">
         <v>1</v>
       </c>
@@ -3142,7 +3146,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B2" s="6" t="s">
         <v>196</v>
       </c>
@@ -3150,7 +3154,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B3" s="6" t="s">
         <v>198</v>
       </c>
@@ -3158,7 +3162,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B4" s="6" t="s">
         <v>200</v>
       </c>
@@ -3178,7 +3182,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B5" s="6" t="s">
         <v>206</v>
       </c>
@@ -3193,7 +3197,7 @@
         <v>874</v>
       </c>
       <c r="J5" s="6" t="str">
-        <f ref="J5:K5" t="shared" si="0">VLOOKUP(J4,$B:$C,2,FALSE)</f>
+        <f t="shared" ref="J5:K5" si="0">VLOOKUP(J4,$B:$C,2,FALSE)</f>
         <v>2355</v>
       </c>
       <c r="K5" s="6">
@@ -3201,7 +3205,7 @@
         <v>2497</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B6" s="6" t="s">
         <v>208</v>
       </c>
@@ -3228,7 +3232,7 @@
       <c r="L6" s="6"/>
       <c r="M6" s="9"/>
     </row>
-    <row r="7">
+    <row r="7" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B7" s="6" t="s">
         <v>210</v>
       </c>
@@ -3260,7 +3264,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B8" s="6" t="s">
         <v>203</v>
       </c>
@@ -3279,11 +3283,11 @@
         <v>2355</v>
       </c>
       <c r="K8" s="6">
-        <f ref="K8:L8" t="shared" si="3">VLOOKUP(K7,$B:$C,2,FALSE)</f>
+        <f t="shared" ref="K8:L8" si="1">VLOOKUP(K7,$B:$C,2,FALSE)</f>
         <v>2497</v>
       </c>
       <c r="L8" s="6" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>302</v>
       </c>
       <c r="M8" s="6" t="str">
@@ -3291,15 +3295,15 @@
         <v>889</v>
       </c>
       <c r="N8" s="6" t="str">
-        <f ref="N8:O8" t="shared" si="5">VLOOKUP(N7,$B:$C,2,FALSE)</f>
+        <f t="shared" ref="N8:O8" si="2">VLOOKUP(N7,$B:$C,2,FALSE)</f>
         <v>695</v>
       </c>
       <c r="O8" s="6" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="2"/>
         <v>512</v>
       </c>
     </row>
-    <row r="9">
+    <row r="9" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B9" s="6" t="s">
         <v>217</v>
       </c>
@@ -3320,19 +3324,19 @@
         <v>874,2355</v>
       </c>
       <c r="K9" s="9" t="str">
-        <f ref="K9:N9" t="shared" si="6">J9&amp;","&amp;K8</f>
+        <f t="shared" ref="K9:N9" si="3">J9&amp;","&amp;K8</f>
         <v>874,2355,2497</v>
       </c>
       <c r="L9" s="9" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="3"/>
         <v>874,2355,2497,302</v>
       </c>
       <c r="M9" s="9" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="3"/>
         <v>874,2355,2497,302,889</v>
       </c>
       <c r="N9" s="9" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="3"/>
         <v>874,2355,2497,302,889,695</v>
       </c>
       <c r="O9" s="9" t="str">
@@ -3340,7 +3344,7 @@
         <v>874,2355,2497,302,889,695,512</v>
       </c>
     </row>
-    <row r="10">
+    <row r="10" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B10" s="6" t="s">
         <v>219</v>
       </c>
@@ -3351,7 +3355,7 @@
         <v>216</v>
       </c>
     </row>
-    <row r="11">
+    <row r="11" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B11" s="6" t="s">
         <v>221</v>
       </c>
@@ -3362,7 +3366,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="12">
+    <row r="12" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B12" s="6" t="s">
         <v>224</v>
       </c>
@@ -3383,7 +3387,7 @@
       <c r="N12" s="6"/>
       <c r="O12" s="6"/>
     </row>
-    <row r="13">
+    <row r="13" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B13" s="6" t="s">
         <v>225</v>
       </c>
@@ -3401,7 +3405,7 @@
       <c r="N13" s="6"/>
       <c r="O13" s="6"/>
     </row>
-    <row r="14">
+    <row r="14" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B14" s="6" t="s">
         <v>227</v>
       </c>
@@ -3425,7 +3429,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="15">
+    <row r="15" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B15" s="6" t="s">
         <v>229</v>
       </c>
@@ -3442,20 +3446,20 @@
         <v>302</v>
       </c>
       <c r="J15" s="6" t="str">
-        <f ref="J15:L15" t="shared" si="7">VLOOKUP(J14,$B:$C,2,FALSE)</f>
+        <f t="shared" ref="J15:L15" si="4">VLOOKUP(J14,$B:$C,2,FALSE)</f>
         <v>889</v>
       </c>
       <c r="K15" s="6" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="4"/>
         <v>695</v>
       </c>
       <c r="L15" s="6" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="4"/>
         <v>512</v>
       </c>
       <c r="M15" s="6"/>
     </row>
-    <row r="16">
+    <row r="16" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B16" s="6" t="s">
         <v>219</v>
       </c>
@@ -3486,7 +3490,7 @@
       <c r="M16" s="9"/>
       <c r="N16" s="9"/>
     </row>
-    <row r="17">
+    <row r="17" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B17" s="6" t="s">
         <v>219</v>
       </c>
@@ -3509,7 +3513,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="18">
+    <row r="18" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B18" s="6" t="s">
         <v>235</v>
       </c>
@@ -3524,19 +3528,19 @@
         <v>889</v>
       </c>
       <c r="J18" s="6" t="str">
-        <f ref="J18:L18" t="shared" si="8">VLOOKUP(J17,$B:$C,2,FALSE)</f>
+        <f t="shared" ref="J18:L18" si="5">VLOOKUP(J17,$B:$C,2,FALSE)</f>
         <v>695</v>
       </c>
       <c r="K18" s="6" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="5"/>
         <v>512</v>
       </c>
       <c r="L18" s="6">
-        <f t="shared" si="8"/>
+        <f t="shared" si="5"/>
         <v>2497</v>
       </c>
     </row>
-    <row r="19">
+    <row r="19" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B19" s="6" t="s">
         <v>238</v>
       </c>
@@ -3557,17 +3561,17 @@
         <v>889,695</v>
       </c>
       <c r="K19" s="9" t="str">
-        <f ref="K19:L19" t="shared" si="9">J19&amp;","&amp;K18</f>
+        <f t="shared" ref="K19:L19" si="6">J19&amp;","&amp;K18</f>
         <v>889,695,512</v>
       </c>
       <c r="L19" s="9" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="6"/>
         <v>889,695,512,2497</v>
       </c>
       <c r="M19" s="9"/>
       <c r="N19" s="9"/>
     </row>
-    <row r="20">
+    <row r="20" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B20" s="6" t="s">
         <v>240</v>
       </c>
@@ -3576,7 +3580,7 @@
       </c>
       <c r="G20" s="7"/>
     </row>
-    <row r="21">
+    <row r="21" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B21" s="6" t="s">
         <v>241</v>
       </c>
@@ -3584,7 +3588,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="22">
+    <row r="22" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B22" s="6" t="s">
         <v>243</v>
       </c>
@@ -3592,7 +3596,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="23">
+    <row r="23" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B23" s="6" t="s">
         <v>245</v>
       </c>
@@ -3605,7 +3609,7 @@
       </c>
       <c r="M23" s="6"/>
     </row>
-    <row r="24">
+    <row r="24" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B24" s="6" t="s">
         <v>204</v>
       </c>
@@ -3613,7 +3617,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="25">
+    <row r="25" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B25" s="6" t="s">
         <v>248</v>
       </c>
@@ -3622,7 +3626,7 @@
       </c>
       <c r="M25" s="6"/>
     </row>
-    <row r="26">
+    <row r="26" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B26" s="6" t="s">
         <v>250</v>
       </c>
@@ -3631,7 +3635,7 @@
       </c>
       <c r="M26" s="6"/>
     </row>
-    <row r="27">
+    <row r="27" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B27" s="6" t="s">
         <v>227</v>
       </c>
@@ -3640,7 +3644,7 @@
       </c>
       <c r="M27" s="6"/>
     </row>
-    <row r="28">
+    <row r="28" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B28" s="6" t="s">
         <v>253</v>
       </c>
@@ -3649,7 +3653,7 @@
       </c>
       <c r="M28" s="6"/>
     </row>
-    <row r="29">
+    <row r="29" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B29" s="6" t="s">
         <v>227</v>
       </c>
@@ -3658,7 +3662,7 @@
       </c>
       <c r="M29" s="6"/>
     </row>
-    <row r="30">
+    <row r="30" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B30" s="6" t="s">
         <v>215</v>
       </c>
@@ -3666,7 +3670,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="31">
+    <row r="31" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B31" s="6" t="s">
         <v>227</v>
       </c>
@@ -3677,7 +3681,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="32">
+    <row r="32" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B32" s="6" t="s">
         <v>257</v>
       </c>
@@ -3688,7 +3692,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="33">
+    <row r="33" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B33" s="6" t="s">
         <v>227</v>
       </c>
@@ -3699,7 +3703,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="34">
+    <row r="34" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B34" s="6" t="s">
         <v>213</v>
       </c>
@@ -3707,7 +3711,7 @@
         <v>259</v>
       </c>
     </row>
-    <row r="35">
+    <row r="35" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B35" s="6" t="s">
         <v>260</v>
       </c>
@@ -3715,7 +3719,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="36">
+    <row r="36" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B36" s="6" t="s">
         <v>262</v>
       </c>
@@ -3723,7 +3727,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="37">
+    <row r="37" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B37" s="6" t="s">
         <v>264</v>
       </c>
@@ -3731,7 +3735,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="38">
+    <row r="38" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B38" s="6" t="s">
         <v>266</v>
       </c>
@@ -3739,7 +3743,7 @@
         <v>3056</v>
       </c>
     </row>
-    <row r="39">
+    <row r="39" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B39" s="6" t="s">
         <v>267</v>
       </c>
@@ -3747,7 +3751,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="40">
+    <row r="40" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B40" s="6" t="s">
         <v>269</v>
       </c>
@@ -3755,7 +3759,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="41">
+    <row r="41" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B41" s="6" t="s">
         <v>205</v>
       </c>
@@ -3763,7 +3767,7 @@
         <v>2497</v>
       </c>
     </row>
-    <row r="42">
+    <row r="42" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B42" s="6" t="s">
         <v>271</v>
       </c>
@@ -3771,7 +3775,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="43">
+    <row r="43" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B43" s="6" t="s">
         <v>273</v>
       </c>
@@ -3779,7 +3783,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="44">
+    <row r="44" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B44" s="6" t="s">
         <v>227</v>
       </c>
@@ -3787,7 +3791,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="45">
+    <row r="45" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B45" s="6" t="s">
         <v>214</v>
       </c>
@@ -3795,7 +3799,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="46">
+    <row r="46" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B46" s="6" t="s">
         <v>277</v>
       </c>
@@ -3803,7 +3807,7 @@
         <v>278</v>
       </c>
     </row>
-    <row r="47">
+    <row r="47" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B47" s="6" t="s">
         <v>279</v>
       </c>
@@ -3811,7 +3815,7 @@
         <v>280</v>
       </c>
     </row>
-    <row r="48">
+    <row r="48" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B48" s="6" t="s">
         <v>281</v>
       </c>
@@ -3819,7 +3823,7 @@
         <v>282</v>
       </c>
     </row>
-    <row r="49">
+    <row r="49" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B49" s="6" t="s">
         <v>283</v>
       </c>
@@ -3827,7 +3831,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="50">
+    <row r="50" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B50" s="6" t="s">
         <v>285</v>
       </c>
@@ -3835,7 +3839,7 @@
         <v>286</v>
       </c>
     </row>
-    <row r="51">
+    <row r="51" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B51" s="6" t="s">
         <v>287</v>
       </c>
@@ -3843,7 +3847,7 @@
         <v>547</v>
       </c>
     </row>
-    <row r="52">
+    <row r="52" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B52" s="6" t="s">
         <v>212</v>
       </c>
@@ -3851,7 +3855,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="53">
+    <row r="53" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B53" s="6" t="s">
         <v>219</v>
       </c>
@@ -3859,7 +3863,7 @@
         <v>288</v>
       </c>
     </row>
-    <row r="54">
+    <row r="54" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B54" s="6" t="s">
         <v>219</v>
       </c>
@@ -3867,7 +3871,7 @@
         <v>289</v>
       </c>
     </row>
-    <row r="55">
+    <row r="55" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B55" s="6" t="s">
         <v>290</v>
       </c>
@@ -3875,7 +3879,7 @@
         <v>291</v>
       </c>
     </row>
-    <row r="56">
+    <row r="56" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B56" s="6" t="s">
         <v>219</v>
       </c>
@@ -3886,8 +3890,7 @@
   </sheetData>
   <phoneticPr fontId="0" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="1200" verticalDpi="1200"/>
-  <headerFooter/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -3896,7 +3899,7 @@
   <dimension ref="B1:C212"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B1" s="6" t="s">
         <v>0</v>
       </c>
@@ -3904,7 +3907,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B2" s="6" t="s">
         <v>293</v>
       </c>
@@ -3912,7 +3915,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B3" s="6" t="s">
         <v>295</v>
       </c>
@@ -3920,7 +3923,7 @@
         <v>296</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B4" s="6" t="s">
         <v>297</v>
       </c>
@@ -3928,7 +3931,7 @@
         <v>298</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B5" s="6" t="s">
         <v>299</v>
       </c>
@@ -3936,7 +3939,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B6" s="6" t="s">
         <v>301</v>
       </c>
@@ -3944,7 +3947,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B7" s="6" t="s">
         <v>303</v>
       </c>
@@ -3952,7 +3955,7 @@
         <v>304</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B8" s="6" t="s">
         <v>305</v>
       </c>
@@ -3960,7 +3963,7 @@
         <v>304</v>
       </c>
     </row>
-    <row r="9">
+    <row r="9" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B9" s="6" t="s">
         <v>306</v>
       </c>
@@ -3968,7 +3971,7 @@
         <v>304</v>
       </c>
     </row>
-    <row r="10">
+    <row r="10" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B10" s="6" t="s">
         <v>307</v>
       </c>
@@ -3976,7 +3979,7 @@
         <v>308</v>
       </c>
     </row>
-    <row r="11">
+    <row r="11" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B11" s="6" t="s">
         <v>309</v>
       </c>
@@ -3984,7 +3987,7 @@
         <v>310</v>
       </c>
     </row>
-    <row r="12">
+    <row r="12" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B12" s="6" t="s">
         <v>311</v>
       </c>
@@ -3992,7 +3995,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="13">
+    <row r="13" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B13" s="6" t="s">
         <v>313</v>
       </c>
@@ -4000,7 +4003,7 @@
         <v>314</v>
       </c>
     </row>
-    <row r="14">
+    <row r="14" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B14" s="6" t="s">
         <v>315</v>
       </c>
@@ -4008,7 +4011,7 @@
         <v>316</v>
       </c>
     </row>
-    <row r="15">
+    <row r="15" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B15" s="6" t="s">
         <v>317</v>
       </c>
@@ -4016,7 +4019,7 @@
         <v>318</v>
       </c>
     </row>
-    <row r="16">
+    <row r="16" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B16" s="6" t="s">
         <v>319</v>
       </c>
@@ -4024,7 +4027,7 @@
         <v>320</v>
       </c>
     </row>
-    <row r="17">
+    <row r="17" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B17" s="6" t="s">
         <v>321</v>
       </c>
@@ -4032,7 +4035,7 @@
         <v>322</v>
       </c>
     </row>
-    <row r="18">
+    <row r="18" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B18" s="6" t="s">
         <v>323</v>
       </c>
@@ -4040,7 +4043,7 @@
         <v>324</v>
       </c>
     </row>
-    <row r="19">
+    <row r="19" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B19" s="6" t="s">
         <v>325</v>
       </c>
@@ -4048,7 +4051,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="20">
+    <row r="20" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B20" s="6" t="s">
         <v>327</v>
       </c>
@@ -4056,7 +4059,7 @@
         <v>328</v>
       </c>
     </row>
-    <row r="21">
+    <row r="21" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B21" s="6" t="s">
         <v>329</v>
       </c>
@@ -4064,7 +4067,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="22">
+    <row r="22" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B22" s="6" t="s">
         <v>331</v>
       </c>
@@ -4072,7 +4075,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="23">
+    <row r="23" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B23" s="6" t="s">
         <v>333</v>
       </c>
@@ -4080,7 +4083,7 @@
         <v>334</v>
       </c>
     </row>
-    <row r="24">
+    <row r="24" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B24" s="6" t="s">
         <v>335</v>
       </c>
@@ -4088,7 +4091,7 @@
         <v>336</v>
       </c>
     </row>
-    <row r="25">
+    <row r="25" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B25" s="6" t="s">
         <v>337</v>
       </c>
@@ -4096,7 +4099,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="26">
+    <row r="26" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B26" s="6" t="s">
         <v>339</v>
       </c>
@@ -4104,7 +4107,7 @@
         <v>340</v>
       </c>
     </row>
-    <row r="27">
+    <row r="27" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B27" s="6" t="s">
         <v>341</v>
       </c>
@@ -4112,7 +4115,7 @@
         <v>342</v>
       </c>
     </row>
-    <row r="28">
+    <row r="28" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B28" s="6" t="s">
         <v>343</v>
       </c>
@@ -4120,7 +4123,7 @@
         <v>344</v>
       </c>
     </row>
-    <row r="29">
+    <row r="29" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B29" s="6" t="s">
         <v>345</v>
       </c>
@@ -4128,7 +4131,7 @@
         <v>346</v>
       </c>
     </row>
-    <row r="30">
+    <row r="30" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B30" s="6" t="s">
         <v>347</v>
       </c>
@@ -4136,7 +4139,7 @@
         <v>348</v>
       </c>
     </row>
-    <row r="31">
+    <row r="31" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B31" s="6" t="s">
         <v>349</v>
       </c>
@@ -4144,7 +4147,7 @@
         <v>350</v>
       </c>
     </row>
-    <row r="32">
+    <row r="32" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B32" s="6" t="s">
         <v>351</v>
       </c>
@@ -4152,7 +4155,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="33">
+    <row r="33" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B33" s="6" t="s">
         <v>353</v>
       </c>
@@ -4160,7 +4163,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="34">
+    <row r="34" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B34" s="6" t="s">
         <v>355</v>
       </c>
@@ -4168,7 +4171,7 @@
         <v>356</v>
       </c>
     </row>
-    <row r="35">
+    <row r="35" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B35" s="6" t="s">
         <v>357</v>
       </c>
@@ -4176,7 +4179,7 @@
         <v>358</v>
       </c>
     </row>
-    <row r="36">
+    <row r="36" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B36" s="6" t="s">
         <v>359</v>
       </c>
@@ -4184,7 +4187,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="37">
+    <row r="37" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B37" s="6" t="s">
         <v>361</v>
       </c>
@@ -4192,7 +4195,7 @@
         <v>362</v>
       </c>
     </row>
-    <row r="38">
+    <row r="38" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B38" s="6" t="s">
         <v>363</v>
       </c>
@@ -4200,7 +4203,7 @@
         <v>364</v>
       </c>
     </row>
-    <row r="39">
+    <row r="39" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B39" s="6" t="s">
         <v>365</v>
       </c>
@@ -4208,7 +4211,7 @@
         <v>366</v>
       </c>
     </row>
-    <row r="40">
+    <row r="40" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B40" s="6" t="s">
         <v>367</v>
       </c>
@@ -4216,7 +4219,7 @@
         <v>368</v>
       </c>
     </row>
-    <row r="41">
+    <row r="41" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B41" s="6" t="s">
         <v>369</v>
       </c>
@@ -4224,7 +4227,7 @@
         <v>370</v>
       </c>
     </row>
-    <row r="42">
+    <row r="42" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B42" s="6" t="s">
         <v>371</v>
       </c>
@@ -4232,7 +4235,7 @@
         <v>372</v>
       </c>
     </row>
-    <row r="43">
+    <row r="43" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B43" s="6" t="s">
         <v>373</v>
       </c>
@@ -4240,7 +4243,7 @@
         <v>374</v>
       </c>
     </row>
-    <row r="44">
+    <row r="44" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B44" s="6" t="s">
         <v>375</v>
       </c>
@@ -4248,7 +4251,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="45">
+    <row r="45" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B45" s="6" t="s">
         <v>377</v>
       </c>
@@ -4256,7 +4259,7 @@
         <v>378</v>
       </c>
     </row>
-    <row r="46">
+    <row r="46" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B46" s="6" t="s">
         <v>379</v>
       </c>
@@ -4264,7 +4267,7 @@
         <v>380</v>
       </c>
     </row>
-    <row r="47">
+    <row r="47" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B47" s="6" t="s">
         <v>381</v>
       </c>
@@ -4272,7 +4275,7 @@
         <v>382</v>
       </c>
     </row>
-    <row r="48">
+    <row r="48" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B48" s="6" t="s">
         <v>383</v>
       </c>
@@ -4280,7 +4283,7 @@
         <v>384</v>
       </c>
     </row>
-    <row r="49">
+    <row r="49" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B49" s="6" t="s">
         <v>385</v>
       </c>
@@ -4288,7 +4291,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="50">
+    <row r="50" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B50" s="6" t="s">
         <v>387</v>
       </c>
@@ -4296,7 +4299,7 @@
         <v>388</v>
       </c>
     </row>
-    <row r="51">
+    <row r="51" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B51" s="6" t="s">
         <v>389</v>
       </c>
@@ -4304,7 +4307,7 @@
         <v>390</v>
       </c>
     </row>
-    <row r="52">
+    <row r="52" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B52" s="6" t="s">
         <v>391</v>
       </c>
@@ -4312,7 +4315,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="53">
+    <row r="53" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B53" s="6" t="s">
         <v>393</v>
       </c>
@@ -4320,7 +4323,7 @@
         <v>394</v>
       </c>
     </row>
-    <row r="54">
+    <row r="54" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B54" s="6" t="s">
         <v>395</v>
       </c>
@@ -4328,7 +4331,7 @@
         <v>396</v>
       </c>
     </row>
-    <row r="55">
+    <row r="55" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B55" s="6" t="s">
         <v>397</v>
       </c>
@@ -4336,7 +4339,7 @@
         <v>398</v>
       </c>
     </row>
-    <row r="56">
+    <row r="56" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B56" s="6" t="s">
         <v>399</v>
       </c>
@@ -4344,7 +4347,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="57">
+    <row r="57" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B57" s="6" t="s">
         <v>401</v>
       </c>
@@ -4352,7 +4355,7 @@
         <v>402</v>
       </c>
     </row>
-    <row r="58">
+    <row r="58" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B58" s="6" t="s">
         <v>403</v>
       </c>
@@ -4360,7 +4363,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="59">
+    <row r="59" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B59" s="6" t="s">
         <v>405</v>
       </c>
@@ -4368,7 +4371,7 @@
         <v>406</v>
       </c>
     </row>
-    <row r="60">
+    <row r="60" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B60" s="6" t="s">
         <v>407</v>
       </c>
@@ -4376,7 +4379,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="61">
+    <row r="61" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B61" s="6" t="s">
         <v>409</v>
       </c>
@@ -4384,7 +4387,7 @@
         <v>410</v>
       </c>
     </row>
-    <row r="62">
+    <row r="62" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B62" s="6" t="s">
         <v>411</v>
       </c>
@@ -4392,7 +4395,7 @@
         <v>412</v>
       </c>
     </row>
-    <row r="63">
+    <row r="63" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B63" s="6" t="s">
         <v>413</v>
       </c>
@@ -4400,7 +4403,7 @@
         <v>414</v>
       </c>
     </row>
-    <row r="64">
+    <row r="64" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B64" s="6" t="s">
         <v>415</v>
       </c>
@@ -4408,7 +4411,7 @@
         <v>416</v>
       </c>
     </row>
-    <row r="65">
+    <row r="65" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B65" s="6" t="s">
         <v>417</v>
       </c>
@@ -4416,7 +4419,7 @@
         <v>418</v>
       </c>
     </row>
-    <row r="66">
+    <row r="66" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B66" s="6" t="s">
         <v>419</v>
       </c>
@@ -4424,7 +4427,7 @@
         <v>420</v>
       </c>
     </row>
-    <row r="67">
+    <row r="67" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B67" s="6" t="s">
         <v>421</v>
       </c>
@@ -4432,7 +4435,7 @@
         <v>422</v>
       </c>
     </row>
-    <row r="68">
+    <row r="68" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B68" s="6" t="s">
         <v>423</v>
       </c>
@@ -4440,7 +4443,7 @@
         <v>424</v>
       </c>
     </row>
-    <row r="69">
+    <row r="69" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B69" s="6" t="s">
         <v>425</v>
       </c>
@@ -4448,7 +4451,7 @@
         <v>426</v>
       </c>
     </row>
-    <row r="70">
+    <row r="70" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B70" s="6" t="s">
         <v>427</v>
       </c>
@@ -4456,7 +4459,7 @@
         <v>428</v>
       </c>
     </row>
-    <row r="71">
+    <row r="71" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B71" s="6" t="s">
         <v>429</v>
       </c>
@@ -4464,7 +4467,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="72">
+    <row r="72" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B72" s="6" t="s">
         <v>431</v>
       </c>
@@ -4472,7 +4475,7 @@
         <v>432</v>
       </c>
     </row>
-    <row r="73">
+    <row r="73" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B73" s="6" t="s">
         <v>433</v>
       </c>
@@ -4480,7 +4483,7 @@
         <v>434</v>
       </c>
     </row>
-    <row r="74">
+    <row r="74" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B74" s="6" t="s">
         <v>435</v>
       </c>
@@ -4488,7 +4491,7 @@
         <v>436</v>
       </c>
     </row>
-    <row r="75">
+    <row r="75" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B75" s="6" t="s">
         <v>437</v>
       </c>
@@ -4496,7 +4499,7 @@
         <v>438</v>
       </c>
     </row>
-    <row r="76">
+    <row r="76" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B76" s="6" t="s">
         <v>439</v>
       </c>
@@ -4504,7 +4507,7 @@
         <v>440</v>
       </c>
     </row>
-    <row r="77">
+    <row r="77" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B77" s="6">
         <v>1077</v>
       </c>
@@ -4512,7 +4515,7 @@
         <v>441</v>
       </c>
     </row>
-    <row r="78">
+    <row r="78" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B78" s="6" t="s">
         <v>442</v>
       </c>
@@ -4520,7 +4523,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="79">
+    <row r="79" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B79" s="6" t="s">
         <v>443</v>
       </c>
@@ -4528,7 +4531,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="80">
+    <row r="80" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B80" s="6" t="s">
         <v>445</v>
       </c>
@@ -4536,7 +4539,7 @@
         <v>446</v>
       </c>
     </row>
-    <row r="81">
+    <row r="81" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B81" s="6" t="s">
         <v>447</v>
       </c>
@@ -4544,7 +4547,7 @@
         <v>448</v>
       </c>
     </row>
-    <row r="82">
+    <row r="82" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B82" s="6" t="s">
         <v>449</v>
       </c>
@@ -4552,7 +4555,7 @@
         <v>450</v>
       </c>
     </row>
-    <row r="83">
+    <row r="83" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B83" s="6" t="s">
         <v>451</v>
       </c>
@@ -4560,7 +4563,7 @@
         <v>452</v>
       </c>
     </row>
-    <row r="84">
+    <row r="84" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B84" s="6" t="s">
         <v>453</v>
       </c>
@@ -4568,7 +4571,7 @@
         <v>454</v>
       </c>
     </row>
-    <row r="85">
+    <row r="85" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B85" s="6" t="s">
         <v>455</v>
       </c>
@@ -4576,7 +4579,7 @@
         <v>456</v>
       </c>
     </row>
-    <row r="86">
+    <row r="86" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B86" s="6" t="s">
         <v>457</v>
       </c>
@@ -4584,7 +4587,7 @@
         <v>458</v>
       </c>
     </row>
-    <row r="87">
+    <row r="87" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B87" s="6" t="s">
         <v>459</v>
       </c>
@@ -4592,7 +4595,7 @@
         <v>460</v>
       </c>
     </row>
-    <row r="88">
+    <row r="88" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B88" s="6" t="s">
         <v>461</v>
       </c>
@@ -4600,7 +4603,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="89">
+    <row r="89" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B89" s="6" t="s">
         <v>463</v>
       </c>
@@ -4608,7 +4611,7 @@
         <v>464</v>
       </c>
     </row>
-    <row r="90">
+    <row r="90" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B90" s="6" t="s">
         <v>465</v>
       </c>
@@ -4616,7 +4619,7 @@
         <v>466</v>
       </c>
     </row>
-    <row r="91">
+    <row r="91" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B91" s="6" t="s">
         <v>467</v>
       </c>
@@ -4624,7 +4627,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="92">
+    <row r="92" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B92" s="6" t="s">
         <v>469</v>
       </c>
@@ -4632,7 +4635,7 @@
         <v>470</v>
       </c>
     </row>
-    <row r="93">
+    <row r="93" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B93" s="6" t="s">
         <v>471</v>
       </c>
@@ -4640,7 +4643,7 @@
         <v>472</v>
       </c>
     </row>
-    <row r="94">
+    <row r="94" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B94" s="6" t="s">
         <v>473</v>
       </c>
@@ -4648,7 +4651,7 @@
         <v>474</v>
       </c>
     </row>
-    <row r="95">
+    <row r="95" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B95" s="6" t="s">
         <v>475</v>
       </c>
@@ -4656,7 +4659,7 @@
         <v>476</v>
       </c>
     </row>
-    <row r="96">
+    <row r="96" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B96" s="6" t="s">
         <v>477</v>
       </c>
@@ -4664,7 +4667,7 @@
         <v>478</v>
       </c>
     </row>
-    <row r="97">
+    <row r="97" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B97" s="6" t="s">
         <v>479</v>
       </c>
@@ -4672,7 +4675,7 @@
         <v>480</v>
       </c>
     </row>
-    <row r="98">
+    <row r="98" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B98" s="6" t="s">
         <v>481</v>
       </c>
@@ -4680,7 +4683,7 @@
         <v>482</v>
       </c>
     </row>
-    <row r="99">
+    <row r="99" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B99" s="6" t="s">
         <v>483</v>
       </c>
@@ -4688,7 +4691,7 @@
         <v>484</v>
       </c>
     </row>
-    <row r="100">
+    <row r="100" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B100" s="6" t="s">
         <v>485</v>
       </c>
@@ -4696,7 +4699,7 @@
         <v>486</v>
       </c>
     </row>
-    <row r="101">
+    <row r="101" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B101" s="6" t="s">
         <v>487</v>
       </c>
@@ -4704,7 +4707,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="102">
+    <row r="102" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B102" s="6" t="s">
         <v>488</v>
       </c>
@@ -4712,7 +4715,7 @@
         <v>489</v>
       </c>
     </row>
-    <row r="103">
+    <row r="103" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B103" s="6" t="s">
         <v>490</v>
       </c>
@@ -4720,7 +4723,7 @@
         <v>491</v>
       </c>
     </row>
-    <row r="104">
+    <row r="104" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B104" s="6" t="s">
         <v>492</v>
       </c>
@@ -4728,7 +4731,7 @@
         <v>493</v>
       </c>
     </row>
-    <row r="105">
+    <row r="105" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B105" s="6" t="s">
         <v>494</v>
       </c>
@@ -4736,7 +4739,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="106">
+    <row r="106" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B106" s="6" t="s">
         <v>495</v>
       </c>
@@ -4744,7 +4747,7 @@
         <v>496</v>
       </c>
     </row>
-    <row r="107">
+    <row r="107" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B107" s="6" t="s">
         <v>497</v>
       </c>
@@ -4752,7 +4755,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="108">
+    <row r="108" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B108" s="6" t="s">
         <v>498</v>
       </c>
@@ -4760,7 +4763,7 @@
         <v>499</v>
       </c>
     </row>
-    <row r="109">
+    <row r="109" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B109" s="6" t="s">
         <v>500</v>
       </c>
@@ -4768,7 +4771,7 @@
         <v>501</v>
       </c>
     </row>
-    <row r="110">
+    <row r="110" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B110" s="6" t="s">
         <v>502</v>
       </c>
@@ -4776,7 +4779,7 @@
         <v>503</v>
       </c>
     </row>
-    <row r="111">
+    <row r="111" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B111" s="6" t="s">
         <v>504</v>
       </c>
@@ -4784,7 +4787,7 @@
         <v>505</v>
       </c>
     </row>
-    <row r="112">
+    <row r="112" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B112" s="6" t="s">
         <v>246</v>
       </c>
@@ -4792,7 +4795,7 @@
         <v>506</v>
       </c>
     </row>
-    <row r="113">
+    <row r="113" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B113" s="6" t="s">
         <v>507</v>
       </c>
@@ -4800,7 +4803,7 @@
         <v>508</v>
       </c>
     </row>
-    <row r="114">
+    <row r="114" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B114" s="6" t="s">
         <v>509</v>
       </c>
@@ -4808,7 +4811,7 @@
         <v>510</v>
       </c>
     </row>
-    <row r="115">
+    <row r="115" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B115" s="6" t="s">
         <v>511</v>
       </c>
@@ -4816,7 +4819,7 @@
         <v>450</v>
       </c>
     </row>
-    <row r="116">
+    <row r="116" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B116" s="6" t="s">
         <v>512</v>
       </c>
@@ -4824,7 +4827,7 @@
         <v>513</v>
       </c>
     </row>
-    <row r="117">
+    <row r="117" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B117" s="6" t="s">
         <v>514</v>
       </c>
@@ -4832,7 +4835,7 @@
         <v>241</v>
       </c>
     </row>
-    <row r="118">
+    <row r="118" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B118" s="6" t="s">
         <v>515</v>
       </c>
@@ -4840,7 +4843,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="119">
+    <row r="119" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B119" s="6" t="s">
         <v>516</v>
       </c>
@@ -4848,7 +4851,7 @@
         <v>517</v>
       </c>
     </row>
-    <row r="120">
+    <row r="120" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B120" s="6" t="s">
         <v>518</v>
       </c>
@@ -4856,7 +4859,7 @@
         <v>519</v>
       </c>
     </row>
-    <row r="121">
+    <row r="121" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B121" s="6" t="s">
         <v>520</v>
       </c>
@@ -4864,7 +4867,7 @@
         <v>521</v>
       </c>
     </row>
-    <row r="122">
+    <row r="122" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B122" s="6" t="s">
         <v>522</v>
       </c>
@@ -4872,7 +4875,7 @@
         <v>523</v>
       </c>
     </row>
-    <row r="123">
+    <row r="123" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B123" s="6" t="s">
         <v>524</v>
       </c>
@@ -4880,7 +4883,7 @@
         <v>525</v>
       </c>
     </row>
-    <row r="124">
+    <row r="124" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B124" s="6" t="s">
         <v>526</v>
       </c>
@@ -4888,7 +4891,7 @@
         <v>527</v>
       </c>
     </row>
-    <row r="125">
+    <row r="125" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B125" s="6" t="s">
         <v>528</v>
       </c>
@@ -4896,7 +4899,7 @@
         <v>529</v>
       </c>
     </row>
-    <row r="126">
+    <row r="126" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B126" s="6" t="s">
         <v>530</v>
       </c>
@@ -4904,7 +4907,7 @@
         <v>531</v>
       </c>
     </row>
-    <row r="127">
+    <row r="127" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B127" s="6" t="s">
         <v>532</v>
       </c>
@@ -4912,7 +4915,7 @@
         <v>533</v>
       </c>
     </row>
-    <row r="128">
+    <row r="128" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B128" s="6" t="s">
         <v>534</v>
       </c>
@@ -4920,7 +4923,7 @@
         <v>535</v>
       </c>
     </row>
-    <row r="129">
+    <row r="129" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B129" s="6" t="s">
         <v>536</v>
       </c>
@@ -4928,7 +4931,7 @@
         <v>537</v>
       </c>
     </row>
-    <row r="130">
+    <row r="130" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B130" s="6" t="s">
         <v>538</v>
       </c>
@@ -4936,7 +4939,7 @@
         <v>539</v>
       </c>
     </row>
-    <row r="131">
+    <row r="131" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B131" s="6" t="s">
         <v>540</v>
       </c>
@@ -4944,7 +4947,7 @@
         <v>541</v>
       </c>
     </row>
-    <row r="132">
+    <row r="132" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B132" s="6" t="s">
         <v>542</v>
       </c>
@@ -4952,7 +4955,7 @@
         <v>543</v>
       </c>
     </row>
-    <row r="133">
+    <row r="133" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B133" s="6" t="s">
         <v>544</v>
       </c>
@@ -4960,7 +4963,7 @@
         <v>545</v>
       </c>
     </row>
-    <row r="134">
+    <row r="134" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B134" s="6" t="s">
         <v>546</v>
       </c>
@@ -4968,7 +4971,7 @@
         <v>547</v>
       </c>
     </row>
-    <row r="135">
+    <row r="135" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B135" s="6" t="s">
         <v>548</v>
       </c>
@@ -4976,7 +4979,7 @@
         <v>549</v>
       </c>
     </row>
-    <row r="136">
+    <row r="136" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B136" s="6" t="s">
         <v>550</v>
       </c>
@@ -4984,7 +4987,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="137">
+    <row r="137" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B137" s="6" t="s">
         <v>552</v>
       </c>
@@ -4992,7 +4995,7 @@
         <v>553</v>
       </c>
     </row>
-    <row r="138">
+    <row r="138" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B138" s="6" t="s">
         <v>554</v>
       </c>
@@ -5000,7 +5003,7 @@
         <v>555</v>
       </c>
     </row>
-    <row r="139">
+    <row r="139" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B139" s="6" t="s">
         <v>556</v>
       </c>
@@ -5008,7 +5011,7 @@
         <v>557</v>
       </c>
     </row>
-    <row r="140">
+    <row r="140" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B140" s="6" t="s">
         <v>558</v>
       </c>
@@ -5016,7 +5019,7 @@
         <v>559</v>
       </c>
     </row>
-    <row r="141">
+    <row r="141" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B141" s="6" t="s">
         <v>560</v>
       </c>
@@ -5024,7 +5027,7 @@
         <v>561</v>
       </c>
     </row>
-    <row r="142">
+    <row r="142" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B142" s="6" t="s">
         <v>562</v>
       </c>
@@ -5032,7 +5035,7 @@
         <v>563</v>
       </c>
     </row>
-    <row r="143">
+    <row r="143" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B143" s="6" t="s">
         <v>564</v>
       </c>
@@ -5040,7 +5043,7 @@
         <v>565</v>
       </c>
     </row>
-    <row r="144">
+    <row r="144" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B144" s="6" t="s">
         <v>566</v>
       </c>
@@ -5048,7 +5051,7 @@
         <v>567</v>
       </c>
     </row>
-    <row r="145">
+    <row r="145" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B145" s="6" t="s">
         <v>568</v>
       </c>
@@ -5056,7 +5059,7 @@
         <v>569</v>
       </c>
     </row>
-    <row r="146">
+    <row r="146" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B146" s="6" t="s">
         <v>570</v>
       </c>
@@ -5064,7 +5067,7 @@
         <v>571</v>
       </c>
     </row>
-    <row r="147">
+    <row r="147" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B147" s="6" t="s">
         <v>572</v>
       </c>
@@ -5072,7 +5075,7 @@
         <v>573</v>
       </c>
     </row>
-    <row r="148">
+    <row r="148" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B148" s="6" t="s">
         <v>574</v>
       </c>
@@ -5080,7 +5083,7 @@
         <v>575</v>
       </c>
     </row>
-    <row r="149">
+    <row r="149" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B149" s="6" t="s">
         <v>576</v>
       </c>
@@ -5088,7 +5091,7 @@
         <v>577</v>
       </c>
     </row>
-    <row r="150">
+    <row r="150" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B150" s="6" t="s">
         <v>578</v>
       </c>
@@ -5096,7 +5099,7 @@
         <v>579</v>
       </c>
     </row>
-    <row r="151">
+    <row r="151" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B151" s="6" t="s">
         <v>580</v>
       </c>
@@ -5104,7 +5107,7 @@
         <v>581</v>
       </c>
     </row>
-    <row r="152">
+    <row r="152" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B152" s="6" t="s">
         <v>582</v>
       </c>
@@ -5112,7 +5115,7 @@
         <v>583</v>
       </c>
     </row>
-    <row r="153">
+    <row r="153" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B153" s="6" t="s">
         <v>584</v>
       </c>
@@ -5120,7 +5123,7 @@
         <v>585</v>
       </c>
     </row>
-    <row r="154">
+    <row r="154" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B154" s="6" t="s">
         <v>586</v>
       </c>
@@ -5128,7 +5131,7 @@
         <v>587</v>
       </c>
     </row>
-    <row r="155">
+    <row r="155" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B155" s="6" t="s">
         <v>588</v>
       </c>
@@ -5136,7 +5139,7 @@
         <v>589</v>
       </c>
     </row>
-    <row r="156">
+    <row r="156" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B156" s="6" t="s">
         <v>590</v>
       </c>
@@ -5144,7 +5147,7 @@
         <v>591</v>
       </c>
     </row>
-    <row r="157">
+    <row r="157" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B157" s="6" t="s">
         <v>592</v>
       </c>
@@ -5152,7 +5155,7 @@
         <v>593</v>
       </c>
     </row>
-    <row r="158">
+    <row r="158" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B158" s="6" t="s">
         <v>594</v>
       </c>
@@ -5160,7 +5163,7 @@
         <v>595</v>
       </c>
     </row>
-    <row r="159">
+    <row r="159" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B159" s="6" t="s">
         <v>596</v>
       </c>
@@ -5168,7 +5171,7 @@
         <v>597</v>
       </c>
     </row>
-    <row r="160">
+    <row r="160" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B160" s="6" t="s">
         <v>598</v>
       </c>
@@ -5176,7 +5179,7 @@
         <v>599</v>
       </c>
     </row>
-    <row r="161">
+    <row r="161" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B161" s="6" t="s">
         <v>600</v>
       </c>
@@ -5184,7 +5187,7 @@
         <v>601</v>
       </c>
     </row>
-    <row r="162">
+    <row r="162" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B162" s="6" t="s">
         <v>602</v>
       </c>
@@ -5192,7 +5195,7 @@
         <v>603</v>
       </c>
     </row>
-    <row r="163">
+    <row r="163" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B163" s="6" t="s">
         <v>604</v>
       </c>
@@ -5200,7 +5203,7 @@
         <v>605</v>
       </c>
     </row>
-    <row r="164">
+    <row r="164" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B164" s="6" t="s">
         <v>606</v>
       </c>
@@ -5208,7 +5211,7 @@
         <v>607</v>
       </c>
     </row>
-    <row r="165">
+    <row r="165" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B165" s="6" t="s">
         <v>608</v>
       </c>
@@ -5216,7 +5219,7 @@
         <v>609</v>
       </c>
     </row>
-    <row r="166">
+    <row r="166" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B166" s="6" t="s">
         <v>610</v>
       </c>
@@ -5224,7 +5227,7 @@
         <v>611</v>
       </c>
     </row>
-    <row r="167">
+    <row r="167" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B167" s="6" t="s">
         <v>612</v>
       </c>
@@ -5232,7 +5235,7 @@
         <v>613</v>
       </c>
     </row>
-    <row r="168">
+    <row r="168" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B168" s="6" t="s">
         <v>614</v>
       </c>
@@ -5240,7 +5243,7 @@
         <v>615</v>
       </c>
     </row>
-    <row r="169">
+    <row r="169" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B169" s="6" t="s">
         <v>616</v>
       </c>
@@ -5248,7 +5251,7 @@
         <v>617</v>
       </c>
     </row>
-    <row r="170">
+    <row r="170" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B170" s="6" t="s">
         <v>618</v>
       </c>
@@ -5256,7 +5259,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="171">
+    <row r="171" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B171" s="6" t="s">
         <v>620</v>
       </c>
@@ -5264,7 +5267,7 @@
         <v>621</v>
       </c>
     </row>
-    <row r="172">
+    <row r="172" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B172" s="6" t="s">
         <v>622</v>
       </c>
@@ -5272,7 +5275,7 @@
         <v>623</v>
       </c>
     </row>
-    <row r="173">
+    <row r="173" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B173" s="6" t="s">
         <v>624</v>
       </c>
@@ -5280,7 +5283,7 @@
         <v>625</v>
       </c>
     </row>
-    <row r="174">
+    <row r="174" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B174" s="6" t="s">
         <v>626</v>
       </c>
@@ -5288,7 +5291,7 @@
         <v>627</v>
       </c>
     </row>
-    <row r="175">
+    <row r="175" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B175" s="6" t="s">
         <v>251</v>
       </c>
@@ -5296,7 +5299,7 @@
         <v>628</v>
       </c>
     </row>
-    <row r="176">
+    <row r="176" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B176" s="6" t="s">
         <v>629</v>
       </c>
@@ -5304,7 +5307,7 @@
         <v>630</v>
       </c>
     </row>
-    <row r="177">
+    <row r="177" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B177" s="6" t="s">
         <v>631</v>
       </c>
@@ -5312,7 +5315,7 @@
         <v>632</v>
       </c>
     </row>
-    <row r="178">
+    <row r="178" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B178" s="6" t="s">
         <v>633</v>
       </c>
@@ -5320,7 +5323,7 @@
         <v>634</v>
       </c>
     </row>
-    <row r="179">
+    <row r="179" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B179" s="6" t="s">
         <v>635</v>
       </c>
@@ -5328,7 +5331,7 @@
         <v>636</v>
       </c>
     </row>
-    <row r="180">
+    <row r="180" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B180" s="6" t="s">
         <v>637</v>
       </c>
@@ -5336,7 +5339,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="181">
+    <row r="181" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B181" s="6" t="s">
         <v>639</v>
       </c>
@@ -5344,7 +5347,7 @@
         <v>640</v>
       </c>
     </row>
-    <row r="182">
+    <row r="182" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B182" s="6" t="s">
         <v>641</v>
       </c>
@@ -5352,7 +5355,7 @@
         <v>642</v>
       </c>
     </row>
-    <row r="183">
+    <row r="183" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B183" s="6" t="s">
         <v>643</v>
       </c>
@@ -5360,7 +5363,7 @@
         <v>644</v>
       </c>
     </row>
-    <row r="184">
+    <row r="184" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B184" s="6" t="s">
         <v>645</v>
       </c>
@@ -5368,7 +5371,7 @@
         <v>646</v>
       </c>
     </row>
-    <row r="185">
+    <row r="185" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B185" s="6" t="s">
         <v>647</v>
       </c>
@@ -5376,7 +5379,7 @@
         <v>648</v>
       </c>
     </row>
-    <row r="186">
+    <row r="186" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B186" s="6" t="s">
         <v>649</v>
       </c>
@@ -5384,7 +5387,7 @@
         <v>650</v>
       </c>
     </row>
-    <row r="187">
+    <row r="187" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B187" s="6" t="s">
         <v>651</v>
       </c>
@@ -5392,7 +5395,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="188">
+    <row r="188" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B188" s="6" t="s">
         <v>653</v>
       </c>
@@ -5400,7 +5403,7 @@
         <v>654</v>
       </c>
     </row>
-    <row r="189">
+    <row r="189" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B189" s="6" t="s">
         <v>655</v>
       </c>
@@ -5408,7 +5411,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="190">
+    <row r="190" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B190" s="6" t="s">
         <v>657</v>
       </c>
@@ -5416,7 +5419,7 @@
         <v>658</v>
       </c>
     </row>
-    <row r="191">
+    <row r="191" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B191" s="6" t="s">
         <v>659</v>
       </c>
@@ -5424,7 +5427,7 @@
         <v>660</v>
       </c>
     </row>
-    <row r="192">
+    <row r="192" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B192" s="6" t="s">
         <v>661</v>
       </c>
@@ -5432,7 +5435,7 @@
         <v>662</v>
       </c>
     </row>
-    <row r="193">
+    <row r="193" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B193" s="6" t="s">
         <v>663</v>
       </c>
@@ -5440,7 +5443,7 @@
         <v>664</v>
       </c>
     </row>
-    <row r="194">
+    <row r="194" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B194" s="6" t="s">
         <v>665</v>
       </c>
@@ -5448,7 +5451,7 @@
         <v>666</v>
       </c>
     </row>
-    <row r="195">
+    <row r="195" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B195" s="6" t="s">
         <v>667</v>
       </c>
@@ -5456,7 +5459,7 @@
         <v>668</v>
       </c>
     </row>
-    <row r="196">
+    <row r="196" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B196" s="6" t="s">
         <v>669</v>
       </c>
@@ -5464,7 +5467,7 @@
         <v>670</v>
       </c>
     </row>
-    <row r="197">
+    <row r="197" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B197" s="6" t="s">
         <v>671</v>
       </c>
@@ -5472,7 +5475,7 @@
         <v>672</v>
       </c>
     </row>
-    <row r="198">
+    <row r="198" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B198" s="6" t="s">
         <v>673</v>
       </c>
@@ -5480,7 +5483,7 @@
         <v>674</v>
       </c>
     </row>
-    <row r="199">
+    <row r="199" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B199" s="6" t="s">
         <v>675</v>
       </c>
@@ -5488,7 +5491,7 @@
         <v>676</v>
       </c>
     </row>
-    <row r="200">
+    <row r="200" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B200" s="6" t="s">
         <v>677</v>
       </c>
@@ -5496,7 +5499,7 @@
         <v>678</v>
       </c>
     </row>
-    <row r="201">
+    <row r="201" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B201" s="6" t="s">
         <v>679</v>
       </c>
@@ -5504,7 +5507,7 @@
         <v>680</v>
       </c>
     </row>
-    <row r="202">
+    <row r="202" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B202" s="6" t="s">
         <v>681</v>
       </c>
@@ -5512,7 +5515,7 @@
         <v>682</v>
       </c>
     </row>
-    <row r="203">
+    <row r="203" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B203" s="6" t="s">
         <v>683</v>
       </c>
@@ -5520,7 +5523,7 @@
         <v>646</v>
       </c>
     </row>
-    <row r="204">
+    <row r="204" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B204" s="6" t="s">
         <v>684</v>
       </c>
@@ -5528,7 +5531,7 @@
         <v>685</v>
       </c>
     </row>
-    <row r="205">
+    <row r="205" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B205" s="6" t="s">
         <v>686</v>
       </c>
@@ -5536,7 +5539,7 @@
         <v>687</v>
       </c>
     </row>
-    <row r="206">
+    <row r="206" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B206" s="6" t="s">
         <v>688</v>
       </c>
@@ -5544,7 +5547,7 @@
         <v>689</v>
       </c>
     </row>
-    <row r="207">
+    <row r="207" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B207" s="6" t="s">
         <v>690</v>
       </c>
@@ -5552,7 +5555,7 @@
         <v>691</v>
       </c>
     </row>
-    <row r="208">
+    <row r="208" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B208" s="6" t="s">
         <v>692</v>
       </c>
@@ -5560,7 +5563,7 @@
         <v>693</v>
       </c>
     </row>
-    <row r="209">
+    <row r="209" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B209" s="6" t="s">
         <v>694</v>
       </c>
@@ -5568,7 +5571,7 @@
         <v>695</v>
       </c>
     </row>
-    <row r="210">
+    <row r="210" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B210" s="6" t="s">
         <v>696</v>
       </c>
@@ -5576,7 +5579,7 @@
         <v>697</v>
       </c>
     </row>
-    <row r="211">
+    <row r="211" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B211" s="6" t="s">
         <v>698</v>
       </c>
@@ -5584,7 +5587,7 @@
         <v>699</v>
       </c>
     </row>
-    <row r="212">
+    <row r="212" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B212" s="6" t="s">
         <v>700</v>
       </c>
@@ -5593,9 +5596,8 @@
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="3" type="noConversion"/>
+  <phoneticPr fontId="0" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
@@ -5604,7 +5606,7 @@
   <dimension ref="B1:C98"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B1" s="5" t="s">
         <v>0</v>
       </c>
@@ -5612,7 +5614,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B2" s="5" t="s">
         <v>2</v>
       </c>
@@ -5620,7 +5622,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B3" s="5" t="s">
         <v>4</v>
       </c>
@@ -5628,7 +5630,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B4" s="5" t="s">
         <v>6</v>
       </c>
@@ -5636,7 +5638,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B5" s="5" t="s">
         <v>8</v>
       </c>
@@ -5644,7 +5646,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B6" s="5" t="s">
         <v>10</v>
       </c>
@@ -5652,7 +5654,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B7" s="5" t="s">
         <v>12</v>
       </c>
@@ -5660,7 +5662,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B8" s="5" t="s">
         <v>14</v>
       </c>
@@ -5668,7 +5670,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="9">
+    <row r="9" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B9" s="5" t="s">
         <v>16</v>
       </c>
@@ -5676,7 +5678,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="10">
+    <row r="10" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B10" s="5" t="s">
         <v>18</v>
       </c>
@@ -5684,7 +5686,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="11">
+    <row r="11" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B11" s="5" t="s">
         <v>20</v>
       </c>
@@ -5692,7 +5694,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="12">
+    <row r="12" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B12" s="5" t="s">
         <v>22</v>
       </c>
@@ -5700,7 +5702,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="13">
+    <row r="13" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B13" s="5" t="s">
         <v>24</v>
       </c>
@@ -5708,7 +5710,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="14">
+    <row r="14" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B14" s="5" t="s">
         <v>26</v>
       </c>
@@ -5716,7 +5718,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="15">
+    <row r="15" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B15" s="5" t="s">
         <v>28</v>
       </c>
@@ -5724,7 +5726,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="16">
+    <row r="16" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B16" s="5" t="s">
         <v>30</v>
       </c>
@@ -5732,7 +5734,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="17">
+    <row r="17" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B17" s="5" t="s">
         <v>32</v>
       </c>
@@ -5740,7 +5742,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="18">
+    <row r="18" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B18" s="5" t="s">
         <v>34</v>
       </c>
@@ -5748,7 +5750,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="19">
+    <row r="19" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B19" s="5" t="s">
         <v>36</v>
       </c>
@@ -5756,7 +5758,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="20">
+    <row r="20" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B20" s="5" t="s">
         <v>38</v>
       </c>
@@ -5764,7 +5766,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="21">
+    <row r="21" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B21" s="5" t="s">
         <v>40</v>
       </c>
@@ -5772,7 +5774,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="22">
+    <row r="22" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B22" s="5" t="s">
         <v>42</v>
       </c>
@@ -5780,7 +5782,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="23">
+    <row r="23" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B23" s="5" t="s">
         <v>44</v>
       </c>
@@ -5788,7 +5790,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="24">
+    <row r="24" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B24" s="5" t="s">
         <v>46</v>
       </c>
@@ -5796,7 +5798,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="25">
+    <row r="25" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B25" s="5" t="s">
         <v>48</v>
       </c>
@@ -5804,7 +5806,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="26">
+    <row r="26" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B26" s="5" t="s">
         <v>50</v>
       </c>
@@ -5812,7 +5814,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="27">
+    <row r="27" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B27" s="5" t="s">
         <v>52</v>
       </c>
@@ -5820,7 +5822,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="28">
+    <row r="28" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B28" s="5" t="s">
         <v>54</v>
       </c>
@@ -5828,7 +5830,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="29">
+    <row r="29" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B29" s="5" t="s">
         <v>56</v>
       </c>
@@ -5836,7 +5838,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="30">
+    <row r="30" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B30" s="5" t="s">
         <v>58</v>
       </c>
@@ -5844,7 +5846,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="31">
+    <row r="31" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B31" s="5" t="s">
         <v>60</v>
       </c>
@@ -5852,7 +5854,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="32">
+    <row r="32" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B32" s="5" t="s">
         <v>62</v>
       </c>
@@ -5860,7 +5862,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="33">
+    <row r="33" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B33" s="5" t="s">
         <v>64</v>
       </c>
@@ -5868,7 +5870,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="34">
+    <row r="34" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B34" s="5" t="s">
         <v>66</v>
       </c>
@@ -5876,7 +5878,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="35">
+    <row r="35" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B35" s="5" t="s">
         <v>68</v>
       </c>
@@ -5884,7 +5886,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="36">
+    <row r="36" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B36" s="5" t="s">
         <v>70</v>
       </c>
@@ -5892,7 +5894,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="37">
+    <row r="37" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B37" s="5" t="s">
         <v>72</v>
       </c>
@@ -5900,7 +5902,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="38">
+    <row r="38" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B38" s="5" t="s">
         <v>74</v>
       </c>
@@ -5908,7 +5910,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="39">
+    <row r="39" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B39" s="5" t="s">
         <v>76</v>
       </c>
@@ -5916,7 +5918,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="40">
+    <row r="40" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B40" s="5" t="s">
         <v>78</v>
       </c>
@@ -5924,7 +5926,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="41">
+    <row r="41" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B41" s="5" t="s">
         <v>80</v>
       </c>
@@ -5932,7 +5934,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="42">
+    <row r="42" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B42" s="5" t="s">
         <v>82</v>
       </c>
@@ -5940,7 +5942,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="43">
+    <row r="43" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B43" s="5" t="s">
         <v>84</v>
       </c>
@@ -5948,7 +5950,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="44">
+    <row r="44" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B44" s="5" t="s">
         <v>86</v>
       </c>
@@ -5956,7 +5958,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="45">
+    <row r="45" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B45" s="5" t="s">
         <v>88</v>
       </c>
@@ -5964,7 +5966,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="46">
+    <row r="46" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B46" s="5" t="s">
         <v>90</v>
       </c>
@@ -5972,7 +5974,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="47">
+    <row r="47" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B47" s="5" t="s">
         <v>92</v>
       </c>
@@ -5980,7 +5982,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="48">
+    <row r="48" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B48" s="5" t="s">
         <v>94</v>
       </c>
@@ -5988,7 +5990,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="49">
+    <row r="49" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B49" s="5" t="s">
         <v>96</v>
       </c>
@@ -5996,7 +5998,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="50">
+    <row r="50" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B50" s="5" t="s">
         <v>98</v>
       </c>
@@ -6004,7 +6006,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="51">
+    <row r="51" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B51" s="5" t="s">
         <v>100</v>
       </c>
@@ -6012,7 +6014,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="52">
+    <row r="52" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B52" s="5" t="s">
         <v>102</v>
       </c>
@@ -6020,7 +6022,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="53">
+    <row r="53" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B53" s="5" t="s">
         <v>104</v>
       </c>
@@ -6028,7 +6030,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="54">
+    <row r="54" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B54" s="5" t="s">
         <v>106</v>
       </c>
@@ -6036,7 +6038,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="55">
+    <row r="55" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B55" s="5" t="s">
         <v>108</v>
       </c>
@@ -6044,7 +6046,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="56">
+    <row r="56" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B56" s="5" t="s">
         <v>110</v>
       </c>
@@ -6052,7 +6054,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="57">
+    <row r="57" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B57" s="5" t="s">
         <v>112</v>
       </c>
@@ -6060,7 +6062,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="58">
+    <row r="58" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B58" s="5" t="s">
         <v>114</v>
       </c>
@@ -6068,7 +6070,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="59">
+    <row r="59" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B59" s="5" t="s">
         <v>116</v>
       </c>
@@ -6076,7 +6078,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="60">
+    <row r="60" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B60" s="5" t="s">
         <v>118</v>
       </c>
@@ -6084,7 +6086,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="61">
+    <row r="61" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B61" s="5" t="s">
         <v>120</v>
       </c>
@@ -6092,7 +6094,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="62">
+    <row r="62" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B62" s="5" t="s">
         <v>122</v>
       </c>
@@ -6100,7 +6102,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="63">
+    <row r="63" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B63" s="5" t="s">
         <v>124</v>
       </c>
@@ -6108,7 +6110,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="64">
+    <row r="64" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B64" s="5" t="s">
         <v>126</v>
       </c>
@@ -6116,7 +6118,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="65">
+    <row r="65" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B65" s="5" t="s">
         <v>128</v>
       </c>
@@ -6124,7 +6126,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="66">
+    <row r="66" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B66" s="5" t="s">
         <v>130</v>
       </c>
@@ -6132,7 +6134,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="67">
+    <row r="67" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B67" s="5" t="s">
         <v>132</v>
       </c>
@@ -6140,7 +6142,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="68">
+    <row r="68" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B68" s="5" t="s">
         <v>134</v>
       </c>
@@ -6148,7 +6150,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="69">
+    <row r="69" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B69" s="5" t="s">
         <v>136</v>
       </c>
@@ -6156,7 +6158,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="70">
+    <row r="70" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B70" s="5" t="s">
         <v>138</v>
       </c>
@@ -6164,7 +6166,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="71">
+    <row r="71" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B71" s="5" t="s">
         <v>140</v>
       </c>
@@ -6172,7 +6174,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="72">
+    <row r="72" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B72" s="5" t="s">
         <v>142</v>
       </c>
@@ -6180,7 +6182,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="73">
+    <row r="73" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B73" s="5" t="s">
         <v>144</v>
       </c>
@@ -6188,7 +6190,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="74">
+    <row r="74" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B74" s="5" t="s">
         <v>146</v>
       </c>
@@ -6196,7 +6198,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="75">
+    <row r="75" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B75" s="5" t="s">
         <v>148</v>
       </c>
@@ -6204,7 +6206,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="76">
+    <row r="76" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B76" s="5" t="s">
         <v>150</v>
       </c>
@@ -6212,7 +6214,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="77">
+    <row r="77" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B77" s="5" t="s">
         <v>152</v>
       </c>
@@ -6220,7 +6222,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="78">
+    <row r="78" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B78" s="5" t="s">
         <v>154</v>
       </c>
@@ -6228,7 +6230,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="79">
+    <row r="79" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B79" s="5" t="s">
         <v>156</v>
       </c>
@@ -6236,7 +6238,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="80">
+    <row r="80" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B80" s="5" t="s">
         <v>158</v>
       </c>
@@ -6244,7 +6246,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="81">
+    <row r="81" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B81" s="5" t="s">
         <v>160</v>
       </c>
@@ -6252,7 +6254,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="82">
+    <row r="82" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B82" s="5" t="s">
         <v>162</v>
       </c>
@@ -6260,7 +6262,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="83">
+    <row r="83" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B83" s="5" t="s">
         <v>164</v>
       </c>
@@ -6268,7 +6270,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="84">
+    <row r="84" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B84" s="5" t="s">
         <v>166</v>
       </c>
@@ -6276,7 +6278,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="85">
+    <row r="85" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B85" s="5" t="s">
         <v>168</v>
       </c>
@@ -6284,7 +6286,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="86">
+    <row r="86" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B86" s="5" t="s">
         <v>170</v>
       </c>
@@ -6292,7 +6294,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="87">
+    <row r="87" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B87" s="5" t="s">
         <v>172</v>
       </c>
@@ -6300,7 +6302,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="88">
+    <row r="88" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B88" s="5" t="s">
         <v>174</v>
       </c>
@@ -6308,7 +6310,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="89">
+    <row r="89" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B89" s="5" t="s">
         <v>176</v>
       </c>
@@ -6316,7 +6318,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="90">
+    <row r="90" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B90" s="5" t="s">
         <v>178</v>
       </c>
@@ -6324,7 +6326,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="91">
+    <row r="91" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B91" s="5" t="s">
         <v>180</v>
       </c>
@@ -6332,7 +6334,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="92">
+    <row r="92" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B92" s="5" t="s">
         <v>182</v>
       </c>
@@ -6340,7 +6342,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="93">
+    <row r="93" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B93" s="5" t="s">
         <v>184</v>
       </c>
@@ -6348,7 +6350,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="94">
+    <row r="94" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B94" s="5" t="s">
         <v>186</v>
       </c>
@@ -6356,7 +6358,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="95">
+    <row r="95" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B95" s="5" t="s">
         <v>188</v>
       </c>
@@ -6364,7 +6366,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="96">
+    <row r="96" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B96" s="5" t="s">
         <v>190</v>
       </c>
@@ -6372,7 +6374,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="97">
+    <row r="97" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B97" s="5" t="s">
         <v>192</v>
       </c>
@@ -6380,7 +6382,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="98">
+    <row r="98" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B98" s="5" t="s">
         <v>194</v>
       </c>
@@ -6389,9 +6391,8 @@
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="3" type="noConversion"/>
+  <phoneticPr fontId="0" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
@@ -6400,7 +6401,7 @@
   <dimension ref="B1:C53"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B1" s="4" t="s">
         <v>0</v>
       </c>
@@ -6408,7 +6409,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B2" s="4" t="s">
         <v>2</v>
       </c>
@@ -6416,7 +6417,7 @@
         <v>754</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B3" s="4" t="s">
         <v>293</v>
       </c>
@@ -6424,7 +6425,7 @@
         <v>755</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B4" s="4" t="s">
         <v>295</v>
       </c>
@@ -6432,7 +6433,7 @@
         <v>756</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B5" s="4" t="s">
         <v>297</v>
       </c>
@@ -6440,7 +6441,7 @@
         <v>757</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B6" s="4" t="s">
         <v>299</v>
       </c>
@@ -6448,7 +6449,7 @@
         <v>758</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B7" s="4" t="s">
         <v>301</v>
       </c>
@@ -6456,7 +6457,7 @@
         <v>756</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B8" s="4" t="s">
         <v>24</v>
       </c>
@@ -6464,7 +6465,7 @@
         <v>759</v>
       </c>
     </row>
-    <row r="9">
+    <row r="9" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B9" s="4" t="s">
         <v>32</v>
       </c>
@@ -6472,7 +6473,7 @@
         <v>760</v>
       </c>
     </row>
-    <row r="10">
+    <row r="10" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B10" s="4" t="s">
         <v>40</v>
       </c>
@@ -6480,7 +6481,7 @@
         <v>761</v>
       </c>
     </row>
-    <row r="11">
+    <row r="11" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B11" s="4" t="s">
         <v>42</v>
       </c>
@@ -6488,7 +6489,7 @@
         <v>762</v>
       </c>
     </row>
-    <row r="12">
+    <row r="12" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B12" s="4" t="s">
         <v>48</v>
       </c>
@@ -6496,7 +6497,7 @@
         <v>763</v>
       </c>
     </row>
-    <row r="13">
+    <row r="13" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B13" s="4" t="s">
         <v>50</v>
       </c>
@@ -6504,7 +6505,7 @@
         <v>764</v>
       </c>
     </row>
-    <row r="14">
+    <row r="14" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B14" s="4" t="s">
         <v>52</v>
       </c>
@@ -6512,7 +6513,7 @@
         <v>765</v>
       </c>
     </row>
-    <row r="15">
+    <row r="15" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B15" s="4" t="s">
         <v>54</v>
       </c>
@@ -6520,7 +6521,7 @@
         <v>765</v>
       </c>
     </row>
-    <row r="16">
+    <row r="16" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B16" s="4" t="s">
         <v>56</v>
       </c>
@@ -6528,7 +6529,7 @@
         <v>765</v>
       </c>
     </row>
-    <row r="17">
+    <row r="17" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B17" s="4" t="s">
         <v>58</v>
       </c>
@@ -6536,7 +6537,7 @@
         <v>765</v>
       </c>
     </row>
-    <row r="18">
+    <row r="18" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B18" s="4" t="s">
         <v>60</v>
       </c>
@@ -6544,7 +6545,7 @@
         <v>765</v>
       </c>
     </row>
-    <row r="19">
+    <row r="19" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B19" s="4" t="s">
         <v>62</v>
       </c>
@@ -6552,7 +6553,7 @@
         <v>766</v>
       </c>
     </row>
-    <row r="20">
+    <row r="20" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B20" s="4" t="s">
         <v>64</v>
       </c>
@@ -6560,7 +6561,7 @@
         <v>767</v>
       </c>
     </row>
-    <row r="21">
+    <row r="21" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B21" s="4" t="s">
         <v>768</v>
       </c>
@@ -6568,7 +6569,7 @@
         <v>769</v>
       </c>
     </row>
-    <row r="22">
+    <row r="22" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B22" s="4" t="s">
         <v>70</v>
       </c>
@@ -6576,7 +6577,7 @@
         <v>770</v>
       </c>
     </row>
-    <row r="23">
+    <row r="23" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B23" s="4" t="s">
         <v>92</v>
       </c>
@@ -6584,7 +6585,7 @@
         <v>771</v>
       </c>
     </row>
-    <row r="24">
+    <row r="24" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B24" s="4" t="s">
         <v>772</v>
       </c>
@@ -6592,7 +6593,7 @@
         <v>773</v>
       </c>
     </row>
-    <row r="25">
+    <row r="25" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B25" s="4" t="s">
         <v>774</v>
       </c>
@@ -6600,7 +6601,7 @@
         <v>775</v>
       </c>
     </row>
-    <row r="26">
+    <row r="26" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B26" s="4" t="s">
         <v>76</v>
       </c>
@@ -6608,7 +6609,7 @@
         <v>776</v>
       </c>
     </row>
-    <row r="27">
+    <row r="27" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B27" s="4" t="s">
         <v>78</v>
       </c>
@@ -6616,7 +6617,7 @@
         <v>777</v>
       </c>
     </row>
-    <row r="28">
+    <row r="28" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B28" s="4" t="s">
         <v>80</v>
       </c>
@@ -6624,7 +6625,7 @@
         <v>778</v>
       </c>
     </row>
-    <row r="29">
+    <row r="29" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B29" s="4" t="s">
         <v>82</v>
       </c>
@@ -6632,7 +6633,7 @@
         <v>779</v>
       </c>
     </row>
-    <row r="30">
+    <row r="30" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B30" s="4" t="s">
         <v>201</v>
       </c>
@@ -6640,7 +6641,7 @@
         <v>780</v>
       </c>
     </row>
-    <row r="31">
+    <row r="31" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B31" s="4" t="s">
         <v>84</v>
       </c>
@@ -6648,7 +6649,7 @@
         <v>781</v>
       </c>
     </row>
-    <row r="32">
+    <row r="32" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B32" s="4" t="s">
         <v>86</v>
       </c>
@@ -6656,7 +6657,7 @@
         <v>782</v>
       </c>
     </row>
-    <row r="33">
+    <row r="33" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B33" s="4" t="s">
         <v>88</v>
       </c>
@@ -6664,7 +6665,7 @@
         <v>783</v>
       </c>
     </row>
-    <row r="34">
+    <row r="34" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B34" s="4" t="s">
         <v>90</v>
       </c>
@@ -6672,7 +6673,7 @@
         <v>784</v>
       </c>
     </row>
-    <row r="35">
+    <row r="35" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B35" s="4" t="s">
         <v>114</v>
       </c>
@@ -6680,7 +6681,7 @@
         <v>785</v>
       </c>
     </row>
-    <row r="36">
+    <row r="36" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B36" s="4" t="s">
         <v>94</v>
       </c>
@@ -6688,7 +6689,7 @@
         <v>786</v>
       </c>
     </row>
-    <row r="37">
+    <row r="37" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B37" s="4" t="s">
         <v>96</v>
       </c>
@@ -6696,7 +6697,7 @@
         <v>787</v>
       </c>
     </row>
-    <row r="38">
+    <row r="38" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B38" s="4" t="s">
         <v>98</v>
       </c>
@@ -6704,7 +6705,7 @@
         <v>788</v>
       </c>
     </row>
-    <row r="39">
+    <row r="39" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B39" s="4" t="s">
         <v>100</v>
       </c>
@@ -6712,7 +6713,7 @@
         <v>789</v>
       </c>
     </row>
-    <row r="40">
+    <row r="40" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B40" s="4" t="s">
         <v>102</v>
       </c>
@@ -6720,7 +6721,7 @@
         <v>790</v>
       </c>
     </row>
-    <row r="41">
+    <row r="41" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B41" s="4" t="s">
         <v>104</v>
       </c>
@@ -6728,7 +6729,7 @@
         <v>791</v>
       </c>
     </row>
-    <row r="42">
+    <row r="42" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B42" s="4" t="s">
         <v>106</v>
       </c>
@@ -6736,7 +6737,7 @@
         <v>792</v>
       </c>
     </row>
-    <row r="43">
+    <row r="43" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B43" s="4" t="s">
         <v>108</v>
       </c>
@@ -6744,7 +6745,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="44">
+    <row r="44" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B44" s="4" t="s">
         <v>110</v>
       </c>
@@ -6752,7 +6753,7 @@
         <v>794</v>
       </c>
     </row>
-    <row r="45">
+    <row r="45" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B45" s="4" t="s">
         <v>112</v>
       </c>
@@ -6760,7 +6761,7 @@
         <v>770</v>
       </c>
     </row>
-    <row r="46">
+    <row r="46" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B46" s="4" t="s">
         <v>116</v>
       </c>
@@ -6768,7 +6769,7 @@
         <v>795</v>
       </c>
     </row>
-    <row r="47">
+    <row r="47" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B47" s="4" t="s">
         <v>796</v>
       </c>
@@ -6776,7 +6777,7 @@
         <v>797</v>
       </c>
     </row>
-    <row r="48">
+    <row r="48" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B48" s="4" t="s">
         <v>647</v>
       </c>
@@ -6784,7 +6785,7 @@
         <v>798</v>
       </c>
     </row>
-    <row r="49">
+    <row r="49" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B49" s="4" t="s">
         <v>649</v>
       </c>
@@ -6792,7 +6793,7 @@
         <v>799</v>
       </c>
     </row>
-    <row r="50">
+    <row r="50" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B50" s="4" t="s">
         <v>651</v>
       </c>
@@ -6800,7 +6801,7 @@
         <v>800</v>
       </c>
     </row>
-    <row r="51">
+    <row r="51" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B51" s="4" t="s">
         <v>653</v>
       </c>
@@ -6808,7 +6809,7 @@
         <v>801</v>
       </c>
     </row>
-    <row r="52">
+    <row r="52" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B52" s="4" t="s">
         <v>655</v>
       </c>
@@ -6816,7 +6817,7 @@
         <v>802</v>
       </c>
     </row>
-    <row r="53">
+    <row r="53" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B53" s="4" t="s">
         <v>803</v>
       </c>
@@ -6825,9 +6826,8 @@
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="3" type="noConversion"/>
+  <phoneticPr fontId="0" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
@@ -6836,7 +6836,7 @@
   <dimension ref="B1:C31"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B1" s="3" t="s">
         <v>0</v>
       </c>
@@ -6844,7 +6844,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B2" s="3" t="s">
         <v>805</v>
       </c>
@@ -6852,7 +6852,7 @@
         <v>806</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B3" s="3" t="s">
         <v>22</v>
       </c>
@@ -6860,7 +6860,7 @@
         <v>707</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B4" s="3" t="s">
         <v>703</v>
       </c>
@@ -6868,7 +6868,7 @@
         <v>755</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B5" s="3" t="s">
         <v>705</v>
       </c>
@@ -6876,7 +6876,7 @@
         <v>779</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B6" s="3" t="s">
         <v>6</v>
       </c>
@@ -6884,7 +6884,7 @@
         <v>807</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B7" s="3" t="s">
         <v>8</v>
       </c>
@@ -6892,7 +6892,7 @@
         <v>808</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B8" s="3" t="s">
         <v>10</v>
       </c>
@@ -6900,7 +6900,7 @@
         <v>809</v>
       </c>
     </row>
-    <row r="9">
+    <row r="9" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B9" s="3" t="s">
         <v>12</v>
       </c>
@@ -6908,7 +6908,7 @@
         <v>810</v>
       </c>
     </row>
-    <row r="10">
+    <row r="10" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B10" s="3" t="s">
         <v>14</v>
       </c>
@@ -6916,7 +6916,7 @@
         <v>811</v>
       </c>
     </row>
-    <row r="11">
+    <row r="11" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B11" s="3" t="s">
         <v>16</v>
       </c>
@@ -6924,7 +6924,7 @@
         <v>812</v>
       </c>
     </row>
-    <row r="12">
+    <row r="12" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B12" s="3" t="s">
         <v>18</v>
       </c>
@@ -6932,7 +6932,7 @@
         <v>813</v>
       </c>
     </row>
-    <row r="13">
+    <row r="13" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B13" s="3" t="s">
         <v>20</v>
       </c>
@@ -6940,7 +6940,7 @@
         <v>814</v>
       </c>
     </row>
-    <row r="14">
+    <row r="14" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B14" s="3" t="s">
         <v>46</v>
       </c>
@@ -6948,7 +6948,7 @@
         <v>815</v>
       </c>
     </row>
-    <row r="15">
+    <row r="15" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B15" s="3" t="s">
         <v>30</v>
       </c>
@@ -6956,7 +6956,7 @@
         <v>757</v>
       </c>
     </row>
-    <row r="16">
+    <row r="16" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B16" s="3" t="s">
         <v>32</v>
       </c>
@@ -6964,7 +6964,7 @@
         <v>756</v>
       </c>
     </row>
-    <row r="17">
+    <row r="17" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B17" s="3" t="s">
         <v>40</v>
       </c>
@@ -6972,7 +6972,7 @@
         <v>758</v>
       </c>
     </row>
-    <row r="18">
+    <row r="18" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B18" s="3" t="s">
         <v>42</v>
       </c>
@@ -6980,7 +6980,7 @@
         <v>816</v>
       </c>
     </row>
-    <row r="19">
+    <row r="19" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B19" s="3" t="s">
         <v>44</v>
       </c>
@@ -6988,7 +6988,7 @@
         <v>707</v>
       </c>
     </row>
-    <row r="20">
+    <row r="20" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B20" s="3" t="s">
         <v>709</v>
       </c>
@@ -6996,7 +6996,7 @@
         <v>817</v>
       </c>
     </row>
-    <row r="21">
+    <row r="21" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B21" s="3" t="s">
         <v>66</v>
       </c>
@@ -7004,7 +7004,7 @@
         <v>818</v>
       </c>
     </row>
-    <row r="22">
+    <row r="22" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B22" s="3" t="s">
         <v>68</v>
       </c>
@@ -7012,7 +7012,7 @@
         <v>819</v>
       </c>
     </row>
-    <row r="23">
+    <row r="23" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B23" s="3" t="s">
         <v>72</v>
       </c>
@@ -7020,7 +7020,7 @@
         <v>706</v>
       </c>
     </row>
-    <row r="24">
+    <row r="24" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B24" s="3" t="s">
         <v>710</v>
       </c>
@@ -7028,7 +7028,7 @@
         <v>820</v>
       </c>
     </row>
-    <row r="25">
+    <row r="25" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B25" s="3" t="s">
         <v>92</v>
       </c>
@@ -7036,7 +7036,7 @@
         <v>771</v>
       </c>
     </row>
-    <row r="26">
+    <row r="26" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B26" s="3" t="s">
         <v>114</v>
       </c>
@@ -7044,7 +7044,7 @@
         <v>785</v>
       </c>
     </row>
-    <row r="27">
+    <row r="27" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B27" s="3" t="s">
         <v>712</v>
       </c>
@@ -7052,7 +7052,7 @@
         <v>708</v>
       </c>
     </row>
-    <row r="28">
+    <row r="28" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B28" s="3" t="s">
         <v>714</v>
       </c>
@@ -7060,7 +7060,7 @@
         <v>821</v>
       </c>
     </row>
-    <row r="29">
+    <row r="29" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B29" s="3" t="s">
         <v>716</v>
       </c>
@@ -7068,7 +7068,7 @@
         <v>776</v>
       </c>
     </row>
-    <row r="30">
+    <row r="30" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B30" s="3" t="s">
         <v>718</v>
       </c>
@@ -7076,131 +7076,131 @@
         <v>822</v>
       </c>
     </row>
-    <row r="31">
+    <row r="31" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B31" s="3" t="s">
         <v>720</v>
       </c>
       <c r="C31" s="3" t="s">
         <v>823</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="0" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="B1:C13"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B2" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>702</v>
+      </c>
+    </row>
+    <row r="3" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B3" s="1" t="s">
+        <v>703</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>704</v>
+      </c>
+    </row>
+    <row r="4" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B4" s="1" t="s">
+        <v>705</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>706</v>
+      </c>
+    </row>
+    <row r="5" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B5" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>707</v>
+      </c>
+    </row>
+    <row r="6" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B6" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>708</v>
+      </c>
+    </row>
+    <row r="7" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B7" s="1" t="s">
+        <v>709</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="8" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B8" s="1" t="s">
+        <v>710</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>711</v>
+      </c>
+    </row>
+    <row r="9" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B9" s="1" t="s">
+        <v>712</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>713</v>
+      </c>
+    </row>
+    <row r="10" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B10" s="1" t="s">
+        <v>714</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>715</v>
+      </c>
+    </row>
+    <row r="11" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B11" s="1" t="s">
+        <v>716</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="12" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B12" s="1" t="s">
+        <v>718</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="13" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B13" s="1" t="s">
+        <v>720</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>721</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <headerFooter/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="B1:C13"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="B1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="B2" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>702</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="B3" s="1" t="s">
-        <v>703</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>704</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="B4" s="1" t="s">
-        <v>705</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>706</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="B5" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>707</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="B6" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>708</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="B7" s="1" t="s">
-        <v>709</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>287</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="B8" s="1" t="s">
-        <v>710</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>711</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="B9" s="1" t="s">
-        <v>712</v>
-      </c>
-      <c r="C9" s="1" t="s">
-        <v>713</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="B10" s="1" t="s">
-        <v>714</v>
-      </c>
-      <c r="C10" s="1" t="s">
-        <v>715</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="B11" s="1" t="s">
-        <v>716</v>
-      </c>
-      <c r="C11" s="1" t="s">
-        <v>717</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="B12" s="1" t="s">
-        <v>718</v>
-      </c>
-      <c r="C12" s="1" t="s">
-        <v>719</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="B13" s="1" t="s">
-        <v>720</v>
-      </c>
-      <c r="C13" s="1" t="s">
-        <v>721</v>
-      </c>
-    </row>
-  </sheetData>
-  <headerFooter/>
 </worksheet>
 </file>
--- a/Assets/Editor/DataDic/Data.xlsx
+++ b/Assets/Editor/DataDic/Data.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="17385" windowHeight="7860" activeTab="1"/>
+    <workbookView minimized="1" xWindow="0" yWindow="0" windowWidth="17385" windowHeight="7860" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="FishData" sheetId="1" r:id="rId1"/>

--- a/Assets/Editor/DataDic/Data.xlsx
+++ b/Assets/Editor/DataDic/Data.xlsx
@@ -20,12 +20,12 @@
     <sheet name="OperateData" sheetId="7" r:id="rId6"/>
     <sheet name="NPCFunctionData" sheetId="8" r:id="rId7"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="162913" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1011" uniqueCount="824">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="848" uniqueCount="848">
   <si>
     <t>Key</t>
   </si>
@@ -633,10 +633,10 @@
     <t>405</t>
   </si>
   <si>
-    <r>
+    <r xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
       <t>6</t>
     </r>
-    <r>
+    <r xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
       <rPr>
         <sz val="11"/>
         <rFont val="Calibri"/>
@@ -644,7 +644,7 @@
       </rPr>
       <t>,0</t>
     </r>
-    <phoneticPr fontId="0" type="noConversion"/>
+    <phoneticPr xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" fontId="0" type="noConversion"/>
   </si>
   <si>
     <t>后山</t>
@@ -659,10 +659,10 @@
     <t>植物店</t>
   </si>
   <si>
-    <r>
+    <r xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
       <t>9</t>
     </r>
-    <r>
+    <r xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
       <rPr>
         <sz val="11"/>
         <rFont val="Calibri"/>
@@ -670,7 +670,7 @@
       </rPr>
       <t>,0</t>
     </r>
-    <phoneticPr fontId="0" type="noConversion"/>
+    <phoneticPr xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" fontId="0" type="noConversion"/>
   </si>
   <si>
     <t>教堂</t>
@@ -2155,377 +2155,450 @@
     <t>甜菜</t>
   </si>
   <si>
+    <t>1000</t>
+  </si>
+  <si>
+    <t>鲫鱼</t>
+  </si>
+  <si>
+    <t>鲮鱼</t>
+  </si>
+  <si>
+    <t>手套蟹.</t>
+  </si>
+  <si>
+    <t>丁鱼</t>
+  </si>
+  <si>
+    <t>锦鲤</t>
+  </si>
+  <si>
+    <t>线鱼</t>
+  </si>
+  <si>
+    <t>兰寿金鱼</t>
+  </si>
+  <si>
+    <t>樱桃鲑鱼</t>
+  </si>
+  <si>
+    <t>虹鳟鱼</t>
+  </si>
+  <si>
+    <t>鲷鱼</t>
+  </si>
+  <si>
+    <t>金鳟鱼</t>
+  </si>
+  <si>
+    <t>霓虹脂鲤</t>
+  </si>
+  <si>
+    <t>桃花鱼</t>
+  </si>
+  <si>
+    <t>鲑鱼</t>
+  </si>
+  <si>
+    <t>孔雀鱼</t>
+  </si>
+  <si>
+    <t>银龙鱼</t>
+  </si>
+  <si>
+    <t>洞穴天使鱼</t>
+  </si>
+  <si>
+    <t>沙丁鱼</t>
+  </si>
+  <si>
+    <t>竹荚鱼</t>
+  </si>
+  <si>
+    <t>海鳗</t>
+  </si>
+  <si>
+    <t>章鱼</t>
+  </si>
+  <si>
+    <t>比目鱼</t>
+  </si>
+  <si>
+    <t>河豚鱼</t>
+  </si>
+  <si>
+    <t>水母</t>
+  </si>
+  <si>
+    <t>条石鲷</t>
+  </si>
+  <si>
+    <t>红鲷鱼</t>
+  </si>
+  <si>
+    <t>蓝蟹</t>
+  </si>
+  <si>
+    <t>鲯鳅鱼</t>
+  </si>
+  <si>
+    <t>龙虾</t>
+  </si>
+  <si>
+    <t>金枪鱼</t>
+  </si>
+  <si>
+    <t>斑马狮子鱼</t>
+  </si>
+  <si>
+    <t>点击虚拟NPC</t>
+  </si>
+  <si>
+    <t>锄地</t>
+  </si>
+  <si>
+    <t>浇水</t>
+  </si>
+  <si>
+    <t>播种</t>
+  </si>
+  <si>
+    <t>收获</t>
+  </si>
+  <si>
+    <t>收割</t>
+  </si>
+  <si>
+    <t>铲除</t>
+  </si>
+  <si>
+    <t>点击虚拟NPC事件</t>
+  </si>
+  <si>
+    <t>移动物体事件</t>
+  </si>
+  <si>
+    <t>卸载战斗、恢复电影</t>
+  </si>
+  <si>
+    <t>春之山脉胜利</t>
+  </si>
+  <si>
+    <t>夏之丛林胜利</t>
+  </si>
+  <si>
+    <t>25</t>
+  </si>
+  <si>
+    <t>秋风之谷胜利</t>
+  </si>
+  <si>
+    <t>26</t>
+  </si>
+  <si>
+    <t>冬之雪原胜利</t>
+  </si>
+  <si>
+    <t>点击NPC赠送</t>
+  </si>
+  <si>
+    <t>301</t>
+  </si>
+  <si>
+    <t>表白</t>
+  </si>
+  <si>
+    <t>打开商店</t>
+  </si>
+  <si>
+    <t>队伍邀请</t>
+  </si>
+  <si>
+    <t>分配牧场</t>
+  </si>
+  <si>
+    <t>放生动物</t>
+  </si>
+  <si>
+    <t>310</t>
+  </si>
+  <si>
+    <t>投喂动物</t>
+  </si>
+  <si>
+    <t>311</t>
+  </si>
+  <si>
+    <t>打开天气预报</t>
+  </si>
+  <si>
+    <t>312</t>
+  </si>
+  <si>
+    <t>第一次离开家</t>
+  </si>
+  <si>
+    <t>313</t>
+  </si>
+  <si>
+    <t>查看角色</t>
+  </si>
+  <si>
+    <t>打开联装背包</t>
+  </si>
+  <si>
+    <t>垂钓</t>
+  </si>
+  <si>
+    <t>400</t>
+  </si>
+  <si>
+    <t>创建或打开杂物箱</t>
+  </si>
+  <si>
+    <t>4001</t>
+  </si>
+  <si>
+    <t>商店地图事件</t>
+  </si>
+  <si>
+    <t>坐下</t>
+  </si>
+  <si>
+    <t>离开椅子</t>
+  </si>
+  <si>
+    <t>选择睡眠</t>
+  </si>
+  <si>
+    <t>跳转地图到卧室</t>
+  </si>
+  <si>
+    <t>跳转地图 卧室-大厅</t>
+  </si>
+  <si>
+    <t>商店开门</t>
+  </si>
+  <si>
+    <t>商店关门</t>
+  </si>
+  <si>
+    <t>关闭栅栏</t>
+  </si>
+  <si>
+    <t>打开栅栏</t>
+  </si>
+  <si>
+    <t>收竿</t>
+  </si>
+  <si>
+    <t>装满水</t>
+  </si>
+  <si>
+    <t>第一晚限制</t>
+  </si>
+  <si>
+    <t>赠送礼物</t>
+  </si>
+  <si>
+    <t>打开春战场</t>
+  </si>
+  <si>
+    <t>打开夏战场</t>
+  </si>
+  <si>
+    <t>打开秋战场</t>
+  </si>
+  <si>
+    <t>打开冬战场</t>
+  </si>
+  <si>
+    <t>打开商店界面</t>
+  </si>
+  <si>
+    <t>建造牲畜棚</t>
+  </si>
+  <si>
+    <t>升级牧场</t>
+  </si>
+  <si>
+    <t>坐到沙发上</t>
+  </si>
+  <si>
+    <t>离开沙发</t>
+  </si>
+  <si>
+    <t>500</t>
+  </si>
+  <si>
+    <t>第一天睡醒</t>
+  </si>
+  <si>
+    <t>7000</t>
+  </si>
+  <si>
+    <t>传送事件</t>
+  </si>
+  <si>
+    <t>7001</t>
+  </si>
+  <si>
+    <t>吃食物</t>
+  </si>
+  <si>
+    <t>点击NPC事件</t>
+  </si>
+  <si>
+    <t>点击布莱兹</t>
+  </si>
+  <si>
+    <t>点击玛德琳</t>
+  </si>
+  <si>
+    <t>点击丝特芬妮</t>
+  </si>
+  <si>
+    <t>点击格吉尔</t>
+  </si>
+  <si>
+    <t>8100</t>
+  </si>
+  <si>
+    <t>点击鸡</t>
+  </si>
+  <si>
+    <t>90</t>
+  </si>
+  <si>
+    <t>春战斗胜利</t>
+  </si>
+  <si>
+    <t>97</t>
+  </si>
+  <si>
+    <t>第一次战斗结束</t>
+  </si>
+  <si>
+    <t>0</t>
+  </si>
+  <si>
+    <t>....</t>
+  </si>
+  <si>
+    <t>查看</t>
+  </si>
+  <si>
+    <t>10</t>
+  </si>
+  <si>
+    <t>11</t>
+  </si>
+  <si>
+    <t>开始营业</t>
+  </si>
+  <si>
+    <t>结束营业</t>
+  </si>
+  <si>
+    <t>打开</t>
+  </si>
+  <si>
+    <t>关闭</t>
+  </si>
+  <si>
+    <t>装水</t>
+  </si>
+  <si>
+    <t>查看植物店</t>
+  </si>
+  <si>
+    <t>查看家具店</t>
+  </si>
+  <si>
+    <t>查看动物店</t>
+  </si>
+  <si>
+    <t>移动</t>
+  </si>
+  <si>
+    <t>开始生产</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>设置</t>
+  </si>
+  <si>
+    <t>建造牧场</t>
+  </si>
+  <si>
+    <t>扩建</t>
+  </si>
+  <si>
+    <t>投喂</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>聊天</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>6</t>
+  </si>
+  <si>
+    <t>打开箱子</t>
+  </si>
+  <si>
+    <t>7</t>
+  </si>
+  <si>
+    <t>8</t>
+  </si>
+  <si>
+    <t>站起</t>
+  </si>
+  <si>
+    <t>9</t>
+  </si>
+  <si>
+    <t>睡眠</t>
+  </si>
+  <si>
     <t>赠送</t>
   </si>
   <si>
-    <t>10</t>
-  </si>
-  <si>
     <t>放生</t>
   </si>
   <si>
-    <t>11</t>
-  </si>
-  <si>
-    <t>投喂</t>
-  </si>
-  <si>
-    <t>查看</t>
-  </si>
-  <si>
-    <t>表白</t>
-  </si>
-  <si>
-    <t>3</t>
-  </si>
-  <si>
-    <t>4</t>
-  </si>
-  <si>
     <t>组队</t>
   </si>
   <si>
-    <t>5</t>
-  </si>
-  <si>
     <t>约会</t>
   </si>
   <si>
-    <t>6</t>
-  </si>
-  <si>
     <t>结婚</t>
   </si>
   <si>
-    <t>7</t>
-  </si>
-  <si>
     <t>分手</t>
   </si>
   <si>
-    <t>8</t>
-  </si>
-  <si>
     <t>索要</t>
   </si>
   <si>
-    <t>9</t>
-  </si>
-  <si>
     <t>分配</t>
-  </si>
-  <si>
-    <t>1000</t>
-  </si>
-  <si>
-    <t>鲫鱼</t>
-  </si>
-  <si>
-    <t>鲮鱼</t>
-  </si>
-  <si>
-    <t>手套蟹.</t>
-  </si>
-  <si>
-    <t>丁鱼</t>
-  </si>
-  <si>
-    <t>锦鲤</t>
-  </si>
-  <si>
-    <t>线鱼</t>
-  </si>
-  <si>
-    <t>兰寿金鱼</t>
-  </si>
-  <si>
-    <t>樱桃鲑鱼</t>
-  </si>
-  <si>
-    <t>虹鳟鱼</t>
-  </si>
-  <si>
-    <t>鲷鱼</t>
-  </si>
-  <si>
-    <t>金鳟鱼</t>
-  </si>
-  <si>
-    <t>霓虹脂鲤</t>
-  </si>
-  <si>
-    <t>桃花鱼</t>
-  </si>
-  <si>
-    <t>鲑鱼</t>
-  </si>
-  <si>
-    <t>孔雀鱼</t>
-  </si>
-  <si>
-    <t>银龙鱼</t>
-  </si>
-  <si>
-    <t>洞穴天使鱼</t>
-  </si>
-  <si>
-    <t>沙丁鱼</t>
-  </si>
-  <si>
-    <t>竹荚鱼</t>
-  </si>
-  <si>
-    <t>海鳗</t>
-  </si>
-  <si>
-    <t>章鱼</t>
-  </si>
-  <si>
-    <t>比目鱼</t>
-  </si>
-  <si>
-    <t>河豚鱼</t>
-  </si>
-  <si>
-    <t>水母</t>
-  </si>
-  <si>
-    <t>条石鲷</t>
-  </si>
-  <si>
-    <t>红鲷鱼</t>
-  </si>
-  <si>
-    <t>蓝蟹</t>
-  </si>
-  <si>
-    <t>鲯鳅鱼</t>
-  </si>
-  <si>
-    <t>龙虾</t>
-  </si>
-  <si>
-    <t>金枪鱼</t>
-  </si>
-  <si>
-    <t>斑马狮子鱼</t>
-  </si>
-  <si>
-    <t>点击虚拟NPC</t>
-  </si>
-  <si>
-    <t>锄地</t>
-  </si>
-  <si>
-    <t>浇水</t>
-  </si>
-  <si>
-    <t>播种</t>
-  </si>
-  <si>
-    <t>收获</t>
-  </si>
-  <si>
-    <t>点击虚拟NPC事件</t>
-  </si>
-  <si>
-    <t>移动物体事件</t>
-  </si>
-  <si>
-    <t>卸载战斗、恢复电影</t>
-  </si>
-  <si>
-    <t>春之山脉胜利</t>
-  </si>
-  <si>
-    <t>点击NPC赠送</t>
-  </si>
-  <si>
-    <t>打开商店</t>
-  </si>
-  <si>
-    <t>队伍邀请</t>
-  </si>
-  <si>
-    <t>分配牧场</t>
-  </si>
-  <si>
-    <t>放生动物</t>
-  </si>
-  <si>
-    <t>310</t>
-  </si>
-  <si>
-    <t>投喂动物</t>
-  </si>
-  <si>
-    <t>打开联装背包</t>
-  </si>
-  <si>
-    <t>垂钓</t>
-  </si>
-  <si>
-    <t>400</t>
-  </si>
-  <si>
-    <t>创建或打开杂物箱</t>
-  </si>
-  <si>
-    <t>4001</t>
-  </si>
-  <si>
-    <t>商店地图事件</t>
-  </si>
-  <si>
-    <t>坐下</t>
-  </si>
-  <si>
-    <t>离开椅子</t>
-  </si>
-  <si>
-    <t>选择睡眠</t>
-  </si>
-  <si>
-    <t>跳转地图到卧室</t>
-  </si>
-  <si>
-    <t>跳转地图 卧室-大厅</t>
-  </si>
-  <si>
-    <t>商店开门</t>
-  </si>
-  <si>
-    <t>商店关门</t>
-  </si>
-  <si>
-    <t>关闭栅栏</t>
-  </si>
-  <si>
-    <t>打开栅栏</t>
-  </si>
-  <si>
-    <t>收竿</t>
-  </si>
-  <si>
-    <t>装满水</t>
-  </si>
-  <si>
-    <t>第一晚限制</t>
-  </si>
-  <si>
-    <t>赠送礼物</t>
-  </si>
-  <si>
-    <t>打开春战场</t>
-  </si>
-  <si>
-    <t>打开夏战场</t>
-  </si>
-  <si>
-    <t>打开秋战场</t>
-  </si>
-  <si>
-    <t>打开冬战场</t>
-  </si>
-  <si>
-    <t>打开商店界面</t>
-  </si>
-  <si>
-    <t>建造牲畜棚</t>
-  </si>
-  <si>
-    <t>升级牧场</t>
-  </si>
-  <si>
-    <t>500</t>
-  </si>
-  <si>
-    <t>第一天睡醒</t>
-  </si>
-  <si>
-    <t>点击NPC事件</t>
-  </si>
-  <si>
-    <t>点击布莱兹</t>
-  </si>
-  <si>
-    <t>点击玛德琳</t>
-  </si>
-  <si>
-    <t>点击丝特芬妮</t>
-  </si>
-  <si>
-    <t>点击格吉尔</t>
-  </si>
-  <si>
-    <t>8100</t>
-  </si>
-  <si>
-    <t>点击鸡</t>
-  </si>
-  <si>
-    <t>0</t>
-  </si>
-  <si>
-    <t>....</t>
-  </si>
-  <si>
-    <t>开始营业</t>
-  </si>
-  <si>
-    <t>结束营业</t>
-  </si>
-  <si>
-    <t>打开</t>
-  </si>
-  <si>
-    <t>关闭</t>
-  </si>
-  <si>
-    <t>装水</t>
-  </si>
-  <si>
-    <t>查看植物店</t>
-  </si>
-  <si>
-    <t>查看家具店</t>
-  </si>
-  <si>
-    <t>查看动物店</t>
-  </si>
-  <si>
-    <t>移动</t>
-  </si>
-  <si>
-    <t>开始生产</t>
-  </si>
-  <si>
-    <t>设置</t>
-  </si>
-  <si>
-    <t>建造牧场</t>
-  </si>
-  <si>
-    <t>扩建</t>
-  </si>
-  <si>
-    <t>聊天</t>
-  </si>
-  <si>
-    <t>打开箱子</t>
-  </si>
-  <si>
-    <t>站起</t>
-  </si>
-  <si>
-    <t>睡眠</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="4" x14ac:knownFonts="1">
+  <numFmts count="0"/>
+  <fonts count="3">
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
@@ -2539,12 +2612,6 @@
       <sz val="11"/>
       <name val="Calibri"/>
       <family val="2"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <name val="宋体"/>
-      <family val="3"/>
-      <charset val="134"/>
     </font>
   </fonts>
   <fills count="3">
@@ -2574,16 +2641,16 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="10">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1"/>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="0" applyProtection="1"/>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="0" applyProtection="1"/>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="0" applyProtection="1"/>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="0" applyProtection="1"/>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="0" applyProtection="1"/>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="0" applyProtection="1"/>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="0" applyProtection="1"/>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="2" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="0" applyProtection="1"/>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="1" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="0" applyProtection="1"/>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="2" applyFill="1" borderId="0" applyBorder="1" xfId="0" applyProtection="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -2867,7 +2934,7 @@
   <dimension ref="B1:C32"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="1">
       <c r="B1" s="6" t="s">
         <v>0</v>
       </c>
@@ -2875,258 +2942,259 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="2">
       <c r="B2" s="6" t="s">
-        <v>722</v>
+        <v>702</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>723</v>
-      </c>
-    </row>
-    <row r="3" spans="2:3" x14ac:dyDescent="0.25">
+        <v>703</v>
+      </c>
+    </row>
+    <row r="3">
       <c r="B3" s="6" t="s">
         <v>303</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>724</v>
-      </c>
-    </row>
-    <row r="4" spans="2:3" x14ac:dyDescent="0.25">
+        <v>704</v>
+      </c>
+    </row>
+    <row r="4">
       <c r="B4" s="6" t="s">
         <v>305</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>725</v>
-      </c>
-    </row>
-    <row r="5" spans="2:3" x14ac:dyDescent="0.25">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="5">
       <c r="B5" s="6" t="s">
         <v>307</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>726</v>
-      </c>
-    </row>
-    <row r="6" spans="2:3" x14ac:dyDescent="0.25">
+        <v>706</v>
+      </c>
+    </row>
+    <row r="6">
       <c r="B6" s="6" t="s">
         <v>309</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>727</v>
-      </c>
-    </row>
-    <row r="7" spans="2:3" x14ac:dyDescent="0.25">
+        <v>707</v>
+      </c>
+    </row>
+    <row r="7">
       <c r="B7" s="6" t="s">
         <v>311</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>728</v>
-      </c>
-    </row>
-    <row r="8" spans="2:3" x14ac:dyDescent="0.25">
+        <v>708</v>
+      </c>
+    </row>
+    <row r="8">
       <c r="B8" s="6" t="s">
         <v>315</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>729</v>
-      </c>
-    </row>
-    <row r="9" spans="2:3" x14ac:dyDescent="0.25">
+        <v>709</v>
+      </c>
+    </row>
+    <row r="9">
       <c r="B9" s="6" t="s">
         <v>317</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>730</v>
-      </c>
-    </row>
-    <row r="10" spans="2:3" x14ac:dyDescent="0.25">
+        <v>710</v>
+      </c>
+    </row>
+    <row r="10">
       <c r="B10" s="6" t="s">
         <v>319</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>731</v>
-      </c>
-    </row>
-    <row r="11" spans="2:3" x14ac:dyDescent="0.25">
+        <v>711</v>
+      </c>
+    </row>
+    <row r="11">
       <c r="B11" s="6" t="s">
         <v>321</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>732</v>
-      </c>
-    </row>
-    <row r="12" spans="2:3" x14ac:dyDescent="0.25">
+        <v>712</v>
+      </c>
+    </row>
+    <row r="12">
       <c r="B12" s="6" t="s">
         <v>323</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>733</v>
-      </c>
-    </row>
-    <row r="13" spans="2:3" x14ac:dyDescent="0.25">
+        <v>713</v>
+      </c>
+    </row>
+    <row r="13">
       <c r="B13" s="6" t="s">
         <v>325</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>734</v>
-      </c>
-    </row>
-    <row r="14" spans="2:3" x14ac:dyDescent="0.25">
+        <v>714</v>
+      </c>
+    </row>
+    <row r="14">
       <c r="B14" s="6" t="s">
         <v>329</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>735</v>
-      </c>
-    </row>
-    <row r="15" spans="2:3" x14ac:dyDescent="0.25">
+        <v>715</v>
+      </c>
+    </row>
+    <row r="15">
       <c r="B15" s="6" t="s">
         <v>331</v>
       </c>
       <c r="C15" s="6" t="s">
-        <v>736</v>
-      </c>
-    </row>
-    <row r="16" spans="2:3" x14ac:dyDescent="0.25">
+        <v>716</v>
+      </c>
+    </row>
+    <row r="16">
       <c r="B16" s="6" t="s">
         <v>333</v>
       </c>
       <c r="C16" s="6" t="s">
-        <v>737</v>
-      </c>
-    </row>
-    <row r="17" spans="2:3" x14ac:dyDescent="0.25">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="17">
       <c r="B17" s="6" t="s">
         <v>335</v>
       </c>
       <c r="C17" s="6" t="s">
-        <v>738</v>
-      </c>
-    </row>
-    <row r="18" spans="2:3" x14ac:dyDescent="0.25">
+        <v>718</v>
+      </c>
+    </row>
+    <row r="18">
       <c r="B18" s="6" t="s">
         <v>337</v>
       </c>
       <c r="C18" s="6" t="s">
-        <v>739</v>
-      </c>
-    </row>
-    <row r="19" spans="2:3" x14ac:dyDescent="0.25">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="19">
       <c r="B19" s="6" t="s">
         <v>485</v>
       </c>
       <c r="C19" s="6" t="s">
-        <v>740</v>
-      </c>
-    </row>
-    <row r="20" spans="2:3" x14ac:dyDescent="0.25">
+        <v>720</v>
+      </c>
+    </row>
+    <row r="20">
       <c r="B20" s="6" t="s">
         <v>487</v>
       </c>
       <c r="C20" s="6" t="s">
-        <v>741</v>
-      </c>
-    </row>
-    <row r="21" spans="2:3" x14ac:dyDescent="0.25">
+        <v>721</v>
+      </c>
+    </row>
+    <row r="21">
       <c r="B21" s="6" t="s">
         <v>490</v>
       </c>
       <c r="C21" s="6" t="s">
-        <v>742</v>
-      </c>
-    </row>
-    <row r="22" spans="2:3" x14ac:dyDescent="0.25">
+        <v>722</v>
+      </c>
+    </row>
+    <row r="22">
       <c r="B22" s="6" t="s">
         <v>494</v>
       </c>
       <c r="C22" s="6" t="s">
-        <v>743</v>
-      </c>
-    </row>
-    <row r="23" spans="2:3" x14ac:dyDescent="0.25">
+        <v>723</v>
+      </c>
+    </row>
+    <row r="23">
       <c r="B23" s="6" t="s">
         <v>495</v>
       </c>
       <c r="C23" s="6" t="s">
-        <v>744</v>
-      </c>
-    </row>
-    <row r="24" spans="2:3" x14ac:dyDescent="0.25">
+        <v>724</v>
+      </c>
+    </row>
+    <row r="24">
       <c r="B24" s="6" t="s">
         <v>500</v>
       </c>
       <c r="C24" s="6" t="s">
-        <v>745</v>
-      </c>
-    </row>
-    <row r="25" spans="2:3" x14ac:dyDescent="0.25">
+        <v>725</v>
+      </c>
+    </row>
+    <row r="25">
       <c r="B25" s="6" t="s">
         <v>502</v>
       </c>
       <c r="C25" s="6" t="s">
-        <v>746</v>
-      </c>
-    </row>
-    <row r="26" spans="2:3" x14ac:dyDescent="0.25">
+        <v>726</v>
+      </c>
+    </row>
+    <row r="26">
       <c r="B26" s="6" t="s">
         <v>504</v>
       </c>
       <c r="C26" s="6" t="s">
-        <v>747</v>
-      </c>
-    </row>
-    <row r="27" spans="2:3" x14ac:dyDescent="0.25">
+        <v>727</v>
+      </c>
+    </row>
+    <row r="27">
       <c r="B27" s="6" t="s">
         <v>246</v>
       </c>
       <c r="C27" s="6" t="s">
-        <v>748</v>
-      </c>
-    </row>
-    <row r="28" spans="2:3" x14ac:dyDescent="0.25">
+        <v>728</v>
+      </c>
+    </row>
+    <row r="28">
       <c r="B28" s="6" t="s">
         <v>507</v>
       </c>
       <c r="C28" s="6" t="s">
-        <v>749</v>
-      </c>
-    </row>
-    <row r="29" spans="2:3" x14ac:dyDescent="0.25">
+        <v>729</v>
+      </c>
+    </row>
+    <row r="29">
       <c r="B29" s="6" t="s">
         <v>509</v>
       </c>
       <c r="C29" s="6" t="s">
-        <v>750</v>
-      </c>
-    </row>
-    <row r="30" spans="2:3" x14ac:dyDescent="0.25">
+        <v>730</v>
+      </c>
+    </row>
+    <row r="30">
       <c r="B30" s="6" t="s">
         <v>511</v>
       </c>
       <c r="C30" s="6" t="s">
-        <v>751</v>
-      </c>
-    </row>
-    <row r="31" spans="2:3" x14ac:dyDescent="0.25">
+        <v>731</v>
+      </c>
+    </row>
+    <row r="31">
       <c r="B31" s="6" t="s">
         <v>512</v>
       </c>
       <c r="C31" s="6" t="s">
-        <v>752</v>
-      </c>
-    </row>
-    <row r="32" spans="2:3" x14ac:dyDescent="0.25">
+        <v>732</v>
+      </c>
+    </row>
+    <row r="32">
       <c r="B32" s="6" t="s">
         <v>514</v>
       </c>
       <c r="C32" s="6" t="s">
-        <v>753</v>
+        <v>733</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="0" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="1200" verticalDpi="1200"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
@@ -3135,10 +3203,10 @@
   <dimension ref="B1:O56"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="22.28515625" style="2" customWidth="1"/>
+    <col min="2" max="2" width="22.28515625" customWidth="1" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="1">
       <c r="B1" s="6" t="s">
         <v>1</v>
       </c>
@@ -3146,7 +3214,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="2">
       <c r="B2" s="6" t="s">
         <v>196</v>
       </c>
@@ -3154,7 +3222,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="3" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="3">
       <c r="B3" s="6" t="s">
         <v>198</v>
       </c>
@@ -3162,7 +3230,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="4" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="4">
       <c r="B4" s="6" t="s">
         <v>200</v>
       </c>
@@ -3182,7 +3250,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="5" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="5">
       <c r="B5" s="6" t="s">
         <v>206</v>
       </c>
@@ -3192,12 +3260,12 @@
       <c r="G5" s="7" t="s">
         <v>207</v>
       </c>
-      <c r="I5" s="2">
+      <c r="I5" s="3">
         <f>VLOOKUP(I4,$B:$C,2,FALSE)</f>
         <v>874</v>
       </c>
       <c r="J5" s="6" t="str">
-        <f t="shared" ref="J5:K5" si="0">VLOOKUP(J4,$B:$C,2,FALSE)</f>
+        <f ref="J5:K5" t="shared" si="0">VLOOKUP(J4,$B:$C,2,FALSE)</f>
         <v>2355</v>
       </c>
       <c r="K5" s="6">
@@ -3205,7 +3273,7 @@
         <v>2497</v>
       </c>
     </row>
-    <row r="6" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="6">
       <c r="B6" s="6" t="s">
         <v>208</v>
       </c>
@@ -3232,7 +3300,7 @@
       <c r="L6" s="6"/>
       <c r="M6" s="9"/>
     </row>
-    <row r="7" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="7">
       <c r="B7" s="6" t="s">
         <v>210</v>
       </c>
@@ -3264,7 +3332,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="8" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="8">
       <c r="B8" s="6" t="s">
         <v>203</v>
       </c>
@@ -3283,7 +3351,7 @@
         <v>2355</v>
       </c>
       <c r="K8" s="6">
-        <f t="shared" ref="K8:L8" si="1">VLOOKUP(K7,$B:$C,2,FALSE)</f>
+        <f ref="K8:L8" t="shared" si="1">VLOOKUP(K7,$B:$C,2,FALSE)</f>
         <v>2497</v>
       </c>
       <c r="L8" s="6" t="str">
@@ -3295,7 +3363,7 @@
         <v>889</v>
       </c>
       <c r="N8" s="6" t="str">
-        <f t="shared" ref="N8:O8" si="2">VLOOKUP(N7,$B:$C,2,FALSE)</f>
+        <f ref="N8:O8" t="shared" si="2">VLOOKUP(N7,$B:$C,2,FALSE)</f>
         <v>695</v>
       </c>
       <c r="O8" s="6" t="str">
@@ -3303,7 +3371,7 @@
         <v>512</v>
       </c>
     </row>
-    <row r="9" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="9">
       <c r="B9" s="6" t="s">
         <v>217</v>
       </c>
@@ -3324,7 +3392,7 @@
         <v>874,2355</v>
       </c>
       <c r="K9" s="9" t="str">
-        <f t="shared" ref="K9:N9" si="3">J9&amp;","&amp;K8</f>
+        <f ref="K9:N9" t="shared" si="3">J9&amp;","&amp;K8</f>
         <v>874,2355,2497</v>
       </c>
       <c r="L9" s="9" t="str">
@@ -3344,7 +3412,7 @@
         <v>874,2355,2497,302,889,695,512</v>
       </c>
     </row>
-    <row r="10" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="10">
       <c r="B10" s="6" t="s">
         <v>219</v>
       </c>
@@ -3355,7 +3423,7 @@
         <v>216</v>
       </c>
     </row>
-    <row r="11" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="11">
       <c r="B11" s="6" t="s">
         <v>221</v>
       </c>
@@ -3366,7 +3434,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="12" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="12">
       <c r="B12" s="6" t="s">
         <v>224</v>
       </c>
@@ -3387,7 +3455,7 @@
       <c r="N12" s="6"/>
       <c r="O12" s="6"/>
     </row>
-    <row r="13" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="13">
       <c r="B13" s="6" t="s">
         <v>225</v>
       </c>
@@ -3405,7 +3473,7 @@
       <c r="N13" s="6"/>
       <c r="O13" s="6"/>
     </row>
-    <row r="14" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="14">
       <c r="B14" s="6" t="s">
         <v>227</v>
       </c>
@@ -3429,7 +3497,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="15" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="15">
       <c r="B15" s="6" t="s">
         <v>229</v>
       </c>
@@ -3446,7 +3514,7 @@
         <v>302</v>
       </c>
       <c r="J15" s="6" t="str">
-        <f t="shared" ref="J15:L15" si="4">VLOOKUP(J14,$B:$C,2,FALSE)</f>
+        <f ref="J15:L15" t="shared" si="4">VLOOKUP(J14,$B:$C,2,FALSE)</f>
         <v>889</v>
       </c>
       <c r="K15" s="6" t="str">
@@ -3459,7 +3527,7 @@
       </c>
       <c r="M15" s="6"/>
     </row>
-    <row r="16" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="16">
       <c r="B16" s="6" t="s">
         <v>219</v>
       </c>
@@ -3490,7 +3558,7 @@
       <c r="M16" s="9"/>
       <c r="N16" s="9"/>
     </row>
-    <row r="17" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="17">
       <c r="B17" s="6" t="s">
         <v>219</v>
       </c>
@@ -3513,7 +3581,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="18" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="18">
       <c r="B18" s="6" t="s">
         <v>235</v>
       </c>
@@ -3528,7 +3596,7 @@
         <v>889</v>
       </c>
       <c r="J18" s="6" t="str">
-        <f t="shared" ref="J18:L18" si="5">VLOOKUP(J17,$B:$C,2,FALSE)</f>
+        <f ref="J18:L18" t="shared" si="5">VLOOKUP(J17,$B:$C,2,FALSE)</f>
         <v>695</v>
       </c>
       <c r="K18" s="6" t="str">
@@ -3540,7 +3608,7 @@
         <v>2497</v>
       </c>
     </row>
-    <row r="19" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="19">
       <c r="B19" s="6" t="s">
         <v>238</v>
       </c>
@@ -3561,7 +3629,7 @@
         <v>889,695</v>
       </c>
       <c r="K19" s="9" t="str">
-        <f t="shared" ref="K19:L19" si="6">J19&amp;","&amp;K18</f>
+        <f ref="K19:L19" t="shared" si="6">J19&amp;","&amp;K18</f>
         <v>889,695,512</v>
       </c>
       <c r="L19" s="9" t="str">
@@ -3571,7 +3639,7 @@
       <c r="M19" s="9"/>
       <c r="N19" s="9"/>
     </row>
-    <row r="20" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="20">
       <c r="B20" s="6" t="s">
         <v>240</v>
       </c>
@@ -3580,7 +3648,7 @@
       </c>
       <c r="G20" s="7"/>
     </row>
-    <row r="21" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="21">
       <c r="B21" s="6" t="s">
         <v>241</v>
       </c>
@@ -3588,7 +3656,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="22" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="22">
       <c r="B22" s="6" t="s">
         <v>243</v>
       </c>
@@ -3596,20 +3664,20 @@
         <v>244</v>
       </c>
     </row>
-    <row r="23" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="23">
       <c r="B23" s="6" t="s">
         <v>245</v>
       </c>
       <c r="C23" s="6" t="s">
         <v>246</v>
       </c>
-      <c r="G23" s="2" t="str">
+      <c r="G23" s="3" t="str">
         <f>G6&amp;","&amp;G9&amp;","&amp;G12&amp;","&amp;G16&amp;","&amp;G19</f>
         <v>6,0,9,0,9,0,17,30,17,30,19,30,19,30, 22,0,22,0,24,0</v>
       </c>
       <c r="M23" s="6"/>
     </row>
-    <row r="24" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="24">
       <c r="B24" s="6" t="s">
         <v>204</v>
       </c>
@@ -3617,7 +3685,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="25" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="25">
       <c r="B25" s="6" t="s">
         <v>248</v>
       </c>
@@ -3626,7 +3694,7 @@
       </c>
       <c r="M25" s="6"/>
     </row>
-    <row r="26" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="26">
       <c r="B26" s="6" t="s">
         <v>250</v>
       </c>
@@ -3635,7 +3703,7 @@
       </c>
       <c r="M26" s="6"/>
     </row>
-    <row r="27" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="27">
       <c r="B27" s="6" t="s">
         <v>227</v>
       </c>
@@ -3644,7 +3712,7 @@
       </c>
       <c r="M27" s="6"/>
     </row>
-    <row r="28" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="28">
       <c r="B28" s="6" t="s">
         <v>253</v>
       </c>
@@ -3653,7 +3721,7 @@
       </c>
       <c r="M28" s="6"/>
     </row>
-    <row r="29" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="29">
       <c r="B29" s="6" t="s">
         <v>227</v>
       </c>
@@ -3662,7 +3730,7 @@
       </c>
       <c r="M29" s="6"/>
     </row>
-    <row r="30" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="30">
       <c r="B30" s="6" t="s">
         <v>215</v>
       </c>
@@ -3670,7 +3738,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="31" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="31">
       <c r="B31" s="6" t="s">
         <v>227</v>
       </c>
@@ -3681,7 +3749,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="32" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="32">
       <c r="B32" s="6" t="s">
         <v>257</v>
       </c>
@@ -3692,7 +3760,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="33" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="33">
       <c r="B33" s="6" t="s">
         <v>227</v>
       </c>
@@ -3703,7 +3771,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="34" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="34">
       <c r="B34" s="6" t="s">
         <v>213</v>
       </c>
@@ -3711,7 +3779,7 @@
         <v>259</v>
       </c>
     </row>
-    <row r="35" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="35">
       <c r="B35" s="6" t="s">
         <v>260</v>
       </c>
@@ -3719,7 +3787,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="36" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="36">
       <c r="B36" s="6" t="s">
         <v>262</v>
       </c>
@@ -3727,7 +3795,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="37" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="37">
       <c r="B37" s="6" t="s">
         <v>264</v>
       </c>
@@ -3735,7 +3803,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="38" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="38">
       <c r="B38" s="6" t="s">
         <v>266</v>
       </c>
@@ -3743,7 +3811,7 @@
         <v>3056</v>
       </c>
     </row>
-    <row r="39" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="39">
       <c r="B39" s="6" t="s">
         <v>267</v>
       </c>
@@ -3751,7 +3819,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="40" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="40">
       <c r="B40" s="6" t="s">
         <v>269</v>
       </c>
@@ -3759,7 +3827,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="41" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="41">
       <c r="B41" s="6" t="s">
         <v>205</v>
       </c>
@@ -3767,7 +3835,7 @@
         <v>2497</v>
       </c>
     </row>
-    <row r="42" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="42">
       <c r="B42" s="6" t="s">
         <v>271</v>
       </c>
@@ -3775,7 +3843,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="43" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="43">
       <c r="B43" s="6" t="s">
         <v>273</v>
       </c>
@@ -3783,7 +3851,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="44" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="44">
       <c r="B44" s="6" t="s">
         <v>227</v>
       </c>
@@ -3791,7 +3859,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="45" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="45">
       <c r="B45" s="6" t="s">
         <v>214</v>
       </c>
@@ -3799,7 +3867,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="46" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="46">
       <c r="B46" s="6" t="s">
         <v>277</v>
       </c>
@@ -3807,7 +3875,7 @@
         <v>278</v>
       </c>
     </row>
-    <row r="47" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="47">
       <c r="B47" s="6" t="s">
         <v>279</v>
       </c>
@@ -3815,7 +3883,7 @@
         <v>280</v>
       </c>
     </row>
-    <row r="48" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="48">
       <c r="B48" s="6" t="s">
         <v>281</v>
       </c>
@@ -3823,7 +3891,7 @@
         <v>282</v>
       </c>
     </row>
-    <row r="49" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="49">
       <c r="B49" s="6" t="s">
         <v>283</v>
       </c>
@@ -3831,7 +3899,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="50" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="50">
       <c r="B50" s="6" t="s">
         <v>285</v>
       </c>
@@ -3839,7 +3907,7 @@
         <v>286</v>
       </c>
     </row>
-    <row r="51" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="51">
       <c r="B51" s="6" t="s">
         <v>287</v>
       </c>
@@ -3847,7 +3915,7 @@
         <v>547</v>
       </c>
     </row>
-    <row r="52" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="52">
       <c r="B52" s="6" t="s">
         <v>212</v>
       </c>
@@ -3855,7 +3923,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="53" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="53">
       <c r="B53" s="6" t="s">
         <v>219</v>
       </c>
@@ -3863,7 +3931,7 @@
         <v>288</v>
       </c>
     </row>
-    <row r="54" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="54">
       <c r="B54" s="6" t="s">
         <v>219</v>
       </c>
@@ -3871,7 +3939,7 @@
         <v>289</v>
       </c>
     </row>
-    <row r="55" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="55">
       <c r="B55" s="6" t="s">
         <v>290</v>
       </c>
@@ -3879,7 +3947,7 @@
         <v>291</v>
       </c>
     </row>
-    <row r="56" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="56">
       <c r="B56" s="6" t="s">
         <v>219</v>
       </c>
@@ -3890,7 +3958,8 @@
   </sheetData>
   <phoneticPr fontId="0" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="1200" verticalDpi="1200"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
@@ -3899,7 +3968,7 @@
   <dimension ref="B1:C212"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="1">
       <c r="B1" s="6" t="s">
         <v>0</v>
       </c>
@@ -3907,7 +3976,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="2">
       <c r="B2" s="6" t="s">
         <v>293</v>
       </c>
@@ -3915,7 +3984,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="3" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="3">
       <c r="B3" s="6" t="s">
         <v>295</v>
       </c>
@@ -3923,7 +3992,7 @@
         <v>296</v>
       </c>
     </row>
-    <row r="4" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="4">
       <c r="B4" s="6" t="s">
         <v>297</v>
       </c>
@@ -3931,7 +4000,7 @@
         <v>298</v>
       </c>
     </row>
-    <row r="5" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="5">
       <c r="B5" s="6" t="s">
         <v>299</v>
       </c>
@@ -3939,7 +4008,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="6" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="6">
       <c r="B6" s="6" t="s">
         <v>301</v>
       </c>
@@ -3947,7 +4016,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="7" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="7">
       <c r="B7" s="6" t="s">
         <v>303</v>
       </c>
@@ -3955,7 +4024,7 @@
         <v>304</v>
       </c>
     </row>
-    <row r="8" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="8">
       <c r="B8" s="6" t="s">
         <v>305</v>
       </c>
@@ -3963,7 +4032,7 @@
         <v>304</v>
       </c>
     </row>
-    <row r="9" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="9">
       <c r="B9" s="6" t="s">
         <v>306</v>
       </c>
@@ -3971,7 +4040,7 @@
         <v>304</v>
       </c>
     </row>
-    <row r="10" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="10">
       <c r="B10" s="6" t="s">
         <v>307</v>
       </c>
@@ -3979,7 +4048,7 @@
         <v>308</v>
       </c>
     </row>
-    <row r="11" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="11">
       <c r="B11" s="6" t="s">
         <v>309</v>
       </c>
@@ -3987,7 +4056,7 @@
         <v>310</v>
       </c>
     </row>
-    <row r="12" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="12">
       <c r="B12" s="6" t="s">
         <v>311</v>
       </c>
@@ -3995,7 +4064,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="13" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="13">
       <c r="B13" s="6" t="s">
         <v>313</v>
       </c>
@@ -4003,7 +4072,7 @@
         <v>314</v>
       </c>
     </row>
-    <row r="14" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="14">
       <c r="B14" s="6" t="s">
         <v>315</v>
       </c>
@@ -4011,7 +4080,7 @@
         <v>316</v>
       </c>
     </row>
-    <row r="15" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="15">
       <c r="B15" s="6" t="s">
         <v>317</v>
       </c>
@@ -4019,7 +4088,7 @@
         <v>318</v>
       </c>
     </row>
-    <row r="16" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="16">
       <c r="B16" s="6" t="s">
         <v>319</v>
       </c>
@@ -4027,7 +4096,7 @@
         <v>320</v>
       </c>
     </row>
-    <row r="17" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="17">
       <c r="B17" s="6" t="s">
         <v>321</v>
       </c>
@@ -4035,7 +4104,7 @@
         <v>322</v>
       </c>
     </row>
-    <row r="18" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="18">
       <c r="B18" s="6" t="s">
         <v>323</v>
       </c>
@@ -4043,7 +4112,7 @@
         <v>324</v>
       </c>
     </row>
-    <row r="19" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="19">
       <c r="B19" s="6" t="s">
         <v>325</v>
       </c>
@@ -4051,7 +4120,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="20" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="20">
       <c r="B20" s="6" t="s">
         <v>327</v>
       </c>
@@ -4059,7 +4128,7 @@
         <v>328</v>
       </c>
     </row>
-    <row r="21" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="21">
       <c r="B21" s="6" t="s">
         <v>329</v>
       </c>
@@ -4067,7 +4136,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="22" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="22">
       <c r="B22" s="6" t="s">
         <v>331</v>
       </c>
@@ -4075,7 +4144,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="23" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="23">
       <c r="B23" s="6" t="s">
         <v>333</v>
       </c>
@@ -4083,7 +4152,7 @@
         <v>334</v>
       </c>
     </row>
-    <row r="24" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="24">
       <c r="B24" s="6" t="s">
         <v>335</v>
       </c>
@@ -4091,7 +4160,7 @@
         <v>336</v>
       </c>
     </row>
-    <row r="25" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="25">
       <c r="B25" s="6" t="s">
         <v>337</v>
       </c>
@@ -4099,7 +4168,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="26" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="26">
       <c r="B26" s="6" t="s">
         <v>339</v>
       </c>
@@ -4107,7 +4176,7 @@
         <v>340</v>
       </c>
     </row>
-    <row r="27" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="27">
       <c r="B27" s="6" t="s">
         <v>341</v>
       </c>
@@ -4115,7 +4184,7 @@
         <v>342</v>
       </c>
     </row>
-    <row r="28" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="28">
       <c r="B28" s="6" t="s">
         <v>343</v>
       </c>
@@ -4123,7 +4192,7 @@
         <v>344</v>
       </c>
     </row>
-    <row r="29" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="29">
       <c r="B29" s="6" t="s">
         <v>345</v>
       </c>
@@ -4131,7 +4200,7 @@
         <v>346</v>
       </c>
     </row>
-    <row r="30" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="30">
       <c r="B30" s="6" t="s">
         <v>347</v>
       </c>
@@ -4139,7 +4208,7 @@
         <v>348</v>
       </c>
     </row>
-    <row r="31" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="31">
       <c r="B31" s="6" t="s">
         <v>349</v>
       </c>
@@ -4147,7 +4216,7 @@
         <v>350</v>
       </c>
     </row>
-    <row r="32" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="32">
       <c r="B32" s="6" t="s">
         <v>351</v>
       </c>
@@ -4155,7 +4224,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="33" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="33">
       <c r="B33" s="6" t="s">
         <v>353</v>
       </c>
@@ -4163,7 +4232,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="34" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="34">
       <c r="B34" s="6" t="s">
         <v>355</v>
       </c>
@@ -4171,7 +4240,7 @@
         <v>356</v>
       </c>
     </row>
-    <row r="35" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="35">
       <c r="B35" s="6" t="s">
         <v>357</v>
       </c>
@@ -4179,7 +4248,7 @@
         <v>358</v>
       </c>
     </row>
-    <row r="36" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="36">
       <c r="B36" s="6" t="s">
         <v>359</v>
       </c>
@@ -4187,7 +4256,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="37" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="37">
       <c r="B37" s="6" t="s">
         <v>361</v>
       </c>
@@ -4195,7 +4264,7 @@
         <v>362</v>
       </c>
     </row>
-    <row r="38" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="38">
       <c r="B38" s="6" t="s">
         <v>363</v>
       </c>
@@ -4203,7 +4272,7 @@
         <v>364</v>
       </c>
     </row>
-    <row r="39" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="39">
       <c r="B39" s="6" t="s">
         <v>365</v>
       </c>
@@ -4211,7 +4280,7 @@
         <v>366</v>
       </c>
     </row>
-    <row r="40" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="40">
       <c r="B40" s="6" t="s">
         <v>367</v>
       </c>
@@ -4219,7 +4288,7 @@
         <v>368</v>
       </c>
     </row>
-    <row r="41" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="41">
       <c r="B41" s="6" t="s">
         <v>369</v>
       </c>
@@ -4227,7 +4296,7 @@
         <v>370</v>
       </c>
     </row>
-    <row r="42" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="42">
       <c r="B42" s="6" t="s">
         <v>371</v>
       </c>
@@ -4235,7 +4304,7 @@
         <v>372</v>
       </c>
     </row>
-    <row r="43" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="43">
       <c r="B43" s="6" t="s">
         <v>373</v>
       </c>
@@ -4243,7 +4312,7 @@
         <v>374</v>
       </c>
     </row>
-    <row r="44" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="44">
       <c r="B44" s="6" t="s">
         <v>375</v>
       </c>
@@ -4251,7 +4320,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="45" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="45">
       <c r="B45" s="6" t="s">
         <v>377</v>
       </c>
@@ -4259,7 +4328,7 @@
         <v>378</v>
       </c>
     </row>
-    <row r="46" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="46">
       <c r="B46" s="6" t="s">
         <v>379</v>
       </c>
@@ -4267,7 +4336,7 @@
         <v>380</v>
       </c>
     </row>
-    <row r="47" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="47">
       <c r="B47" s="6" t="s">
         <v>381</v>
       </c>
@@ -4275,7 +4344,7 @@
         <v>382</v>
       </c>
     </row>
-    <row r="48" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="48">
       <c r="B48" s="6" t="s">
         <v>383</v>
       </c>
@@ -4283,7 +4352,7 @@
         <v>384</v>
       </c>
     </row>
-    <row r="49" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="49">
       <c r="B49" s="6" t="s">
         <v>385</v>
       </c>
@@ -4291,7 +4360,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="50" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="50">
       <c r="B50" s="6" t="s">
         <v>387</v>
       </c>
@@ -4299,7 +4368,7 @@
         <v>388</v>
       </c>
     </row>
-    <row r="51" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="51">
       <c r="B51" s="6" t="s">
         <v>389</v>
       </c>
@@ -4307,7 +4376,7 @@
         <v>390</v>
       </c>
     </row>
-    <row r="52" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="52">
       <c r="B52" s="6" t="s">
         <v>391</v>
       </c>
@@ -4315,7 +4384,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="53" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="53">
       <c r="B53" s="6" t="s">
         <v>393</v>
       </c>
@@ -4323,7 +4392,7 @@
         <v>394</v>
       </c>
     </row>
-    <row r="54" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="54">
       <c r="B54" s="6" t="s">
         <v>395</v>
       </c>
@@ -4331,7 +4400,7 @@
         <v>396</v>
       </c>
     </row>
-    <row r="55" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="55">
       <c r="B55" s="6" t="s">
         <v>397</v>
       </c>
@@ -4339,7 +4408,7 @@
         <v>398</v>
       </c>
     </row>
-    <row r="56" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="56">
       <c r="B56" s="6" t="s">
         <v>399</v>
       </c>
@@ -4347,7 +4416,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="57" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="57">
       <c r="B57" s="6" t="s">
         <v>401</v>
       </c>
@@ -4355,7 +4424,7 @@
         <v>402</v>
       </c>
     </row>
-    <row r="58" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="58">
       <c r="B58" s="6" t="s">
         <v>403</v>
       </c>
@@ -4363,7 +4432,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="59" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="59">
       <c r="B59" s="6" t="s">
         <v>405</v>
       </c>
@@ -4371,7 +4440,7 @@
         <v>406</v>
       </c>
     </row>
-    <row r="60" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="60">
       <c r="B60" s="6" t="s">
         <v>407</v>
       </c>
@@ -4379,7 +4448,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="61" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="61">
       <c r="B61" s="6" t="s">
         <v>409</v>
       </c>
@@ -4387,7 +4456,7 @@
         <v>410</v>
       </c>
     </row>
-    <row r="62" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="62">
       <c r="B62" s="6" t="s">
         <v>411</v>
       </c>
@@ -4395,7 +4464,7 @@
         <v>412</v>
       </c>
     </row>
-    <row r="63" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="63">
       <c r="B63" s="6" t="s">
         <v>413</v>
       </c>
@@ -4403,7 +4472,7 @@
         <v>414</v>
       </c>
     </row>
-    <row r="64" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="64">
       <c r="B64" s="6" t="s">
         <v>415</v>
       </c>
@@ -4411,7 +4480,7 @@
         <v>416</v>
       </c>
     </row>
-    <row r="65" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="65">
       <c r="B65" s="6" t="s">
         <v>417</v>
       </c>
@@ -4419,7 +4488,7 @@
         <v>418</v>
       </c>
     </row>
-    <row r="66" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="66">
       <c r="B66" s="6" t="s">
         <v>419</v>
       </c>
@@ -4427,7 +4496,7 @@
         <v>420</v>
       </c>
     </row>
-    <row r="67" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="67">
       <c r="B67" s="6" t="s">
         <v>421</v>
       </c>
@@ -4435,7 +4504,7 @@
         <v>422</v>
       </c>
     </row>
-    <row r="68" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="68">
       <c r="B68" s="6" t="s">
         <v>423</v>
       </c>
@@ -4443,7 +4512,7 @@
         <v>424</v>
       </c>
     </row>
-    <row r="69" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="69">
       <c r="B69" s="6" t="s">
         <v>425</v>
       </c>
@@ -4451,7 +4520,7 @@
         <v>426</v>
       </c>
     </row>
-    <row r="70" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="70">
       <c r="B70" s="6" t="s">
         <v>427</v>
       </c>
@@ -4459,7 +4528,7 @@
         <v>428</v>
       </c>
     </row>
-    <row r="71" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="71">
       <c r="B71" s="6" t="s">
         <v>429</v>
       </c>
@@ -4467,7 +4536,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="72" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="72">
       <c r="B72" s="6" t="s">
         <v>431</v>
       </c>
@@ -4475,7 +4544,7 @@
         <v>432</v>
       </c>
     </row>
-    <row r="73" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="73">
       <c r="B73" s="6" t="s">
         <v>433</v>
       </c>
@@ -4483,7 +4552,7 @@
         <v>434</v>
       </c>
     </row>
-    <row r="74" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="74">
       <c r="B74" s="6" t="s">
         <v>435</v>
       </c>
@@ -4491,7 +4560,7 @@
         <v>436</v>
       </c>
     </row>
-    <row r="75" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="75">
       <c r="B75" s="6" t="s">
         <v>437</v>
       </c>
@@ -4499,7 +4568,7 @@
         <v>438</v>
       </c>
     </row>
-    <row r="76" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="76">
       <c r="B76" s="6" t="s">
         <v>439</v>
       </c>
@@ -4507,7 +4576,7 @@
         <v>440</v>
       </c>
     </row>
-    <row r="77" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="77">
       <c r="B77" s="6">
         <v>1077</v>
       </c>
@@ -4515,7 +4584,7 @@
         <v>441</v>
       </c>
     </row>
-    <row r="78" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="78">
       <c r="B78" s="6" t="s">
         <v>442</v>
       </c>
@@ -4523,7 +4592,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="79" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="79">
       <c r="B79" s="6" t="s">
         <v>443</v>
       </c>
@@ -4531,7 +4600,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="80" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="80">
       <c r="B80" s="6" t="s">
         <v>445</v>
       </c>
@@ -4539,7 +4608,7 @@
         <v>446</v>
       </c>
     </row>
-    <row r="81" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="81">
       <c r="B81" s="6" t="s">
         <v>447</v>
       </c>
@@ -4547,7 +4616,7 @@
         <v>448</v>
       </c>
     </row>
-    <row r="82" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="82">
       <c r="B82" s="6" t="s">
         <v>449</v>
       </c>
@@ -4555,7 +4624,7 @@
         <v>450</v>
       </c>
     </row>
-    <row r="83" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="83">
       <c r="B83" s="6" t="s">
         <v>451</v>
       </c>
@@ -4563,7 +4632,7 @@
         <v>452</v>
       </c>
     </row>
-    <row r="84" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="84">
       <c r="B84" s="6" t="s">
         <v>453</v>
       </c>
@@ -4571,7 +4640,7 @@
         <v>454</v>
       </c>
     </row>
-    <row r="85" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="85">
       <c r="B85" s="6" t="s">
         <v>455</v>
       </c>
@@ -4579,7 +4648,7 @@
         <v>456</v>
       </c>
     </row>
-    <row r="86" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="86">
       <c r="B86" s="6" t="s">
         <v>457</v>
       </c>
@@ -4587,7 +4656,7 @@
         <v>458</v>
       </c>
     </row>
-    <row r="87" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="87">
       <c r="B87" s="6" t="s">
         <v>459</v>
       </c>
@@ -4595,7 +4664,7 @@
         <v>460</v>
       </c>
     </row>
-    <row r="88" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="88">
       <c r="B88" s="6" t="s">
         <v>461</v>
       </c>
@@ -4603,7 +4672,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="89" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="89">
       <c r="B89" s="6" t="s">
         <v>463</v>
       </c>
@@ -4611,7 +4680,7 @@
         <v>464</v>
       </c>
     </row>
-    <row r="90" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="90">
       <c r="B90" s="6" t="s">
         <v>465</v>
       </c>
@@ -4619,7 +4688,7 @@
         <v>466</v>
       </c>
     </row>
-    <row r="91" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="91">
       <c r="B91" s="6" t="s">
         <v>467</v>
       </c>
@@ -4627,7 +4696,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="92" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="92">
       <c r="B92" s="6" t="s">
         <v>469</v>
       </c>
@@ -4635,7 +4704,7 @@
         <v>470</v>
       </c>
     </row>
-    <row r="93" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="93">
       <c r="B93" s="6" t="s">
         <v>471</v>
       </c>
@@ -4643,7 +4712,7 @@
         <v>472</v>
       </c>
     </row>
-    <row r="94" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="94">
       <c r="B94" s="6" t="s">
         <v>473</v>
       </c>
@@ -4651,7 +4720,7 @@
         <v>474</v>
       </c>
     </row>
-    <row r="95" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="95">
       <c r="B95" s="6" t="s">
         <v>475</v>
       </c>
@@ -4659,7 +4728,7 @@
         <v>476</v>
       </c>
     </row>
-    <row r="96" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="96">
       <c r="B96" s="6" t="s">
         <v>477</v>
       </c>
@@ -4667,7 +4736,7 @@
         <v>478</v>
       </c>
     </row>
-    <row r="97" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="97">
       <c r="B97" s="6" t="s">
         <v>479</v>
       </c>
@@ -4675,7 +4744,7 @@
         <v>480</v>
       </c>
     </row>
-    <row r="98" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="98">
       <c r="B98" s="6" t="s">
         <v>481</v>
       </c>
@@ -4683,7 +4752,7 @@
         <v>482</v>
       </c>
     </row>
-    <row r="99" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="99">
       <c r="B99" s="6" t="s">
         <v>483</v>
       </c>
@@ -4691,7 +4760,7 @@
         <v>484</v>
       </c>
     </row>
-    <row r="100" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="100">
       <c r="B100" s="6" t="s">
         <v>485</v>
       </c>
@@ -4699,7 +4768,7 @@
         <v>486</v>
       </c>
     </row>
-    <row r="101" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="101">
       <c r="B101" s="6" t="s">
         <v>487</v>
       </c>
@@ -4707,7 +4776,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="102" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="102">
       <c r="B102" s="6" t="s">
         <v>488</v>
       </c>
@@ -4715,7 +4784,7 @@
         <v>489</v>
       </c>
     </row>
-    <row r="103" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="103">
       <c r="B103" s="6" t="s">
         <v>490</v>
       </c>
@@ -4723,7 +4792,7 @@
         <v>491</v>
       </c>
     </row>
-    <row r="104" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="104">
       <c r="B104" s="6" t="s">
         <v>492</v>
       </c>
@@ -4731,7 +4800,7 @@
         <v>493</v>
       </c>
     </row>
-    <row r="105" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="105">
       <c r="B105" s="6" t="s">
         <v>494</v>
       </c>
@@ -4739,7 +4808,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="106" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="106">
       <c r="B106" s="6" t="s">
         <v>495</v>
       </c>
@@ -4747,7 +4816,7 @@
         <v>496</v>
       </c>
     </row>
-    <row r="107" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="107">
       <c r="B107" s="6" t="s">
         <v>497</v>
       </c>
@@ -4755,7 +4824,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="108" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="108">
       <c r="B108" s="6" t="s">
         <v>498</v>
       </c>
@@ -4763,7 +4832,7 @@
         <v>499</v>
       </c>
     </row>
-    <row r="109" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="109">
       <c r="B109" s="6" t="s">
         <v>500</v>
       </c>
@@ -4771,7 +4840,7 @@
         <v>501</v>
       </c>
     </row>
-    <row r="110" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="110">
       <c r="B110" s="6" t="s">
         <v>502</v>
       </c>
@@ -4779,7 +4848,7 @@
         <v>503</v>
       </c>
     </row>
-    <row r="111" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="111">
       <c r="B111" s="6" t="s">
         <v>504</v>
       </c>
@@ -4787,7 +4856,7 @@
         <v>505</v>
       </c>
     </row>
-    <row r="112" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="112">
       <c r="B112" s="6" t="s">
         <v>246</v>
       </c>
@@ -4795,7 +4864,7 @@
         <v>506</v>
       </c>
     </row>
-    <row r="113" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="113">
       <c r="B113" s="6" t="s">
         <v>507</v>
       </c>
@@ -4803,7 +4872,7 @@
         <v>508</v>
       </c>
     </row>
-    <row r="114" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="114">
       <c r="B114" s="6" t="s">
         <v>509</v>
       </c>
@@ -4811,7 +4880,7 @@
         <v>510</v>
       </c>
     </row>
-    <row r="115" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="115">
       <c r="B115" s="6" t="s">
         <v>511</v>
       </c>
@@ -4819,7 +4888,7 @@
         <v>450</v>
       </c>
     </row>
-    <row r="116" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="116">
       <c r="B116" s="6" t="s">
         <v>512</v>
       </c>
@@ -4827,7 +4896,7 @@
         <v>513</v>
       </c>
     </row>
-    <row r="117" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="117">
       <c r="B117" s="6" t="s">
         <v>514</v>
       </c>
@@ -4835,7 +4904,7 @@
         <v>241</v>
       </c>
     </row>
-    <row r="118" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="118">
       <c r="B118" s="6" t="s">
         <v>515</v>
       </c>
@@ -4843,7 +4912,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="119" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="119">
       <c r="B119" s="6" t="s">
         <v>516</v>
       </c>
@@ -4851,7 +4920,7 @@
         <v>517</v>
       </c>
     </row>
-    <row r="120" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="120">
       <c r="B120" s="6" t="s">
         <v>518</v>
       </c>
@@ -4859,7 +4928,7 @@
         <v>519</v>
       </c>
     </row>
-    <row r="121" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="121">
       <c r="B121" s="6" t="s">
         <v>520</v>
       </c>
@@ -4867,7 +4936,7 @@
         <v>521</v>
       </c>
     </row>
-    <row r="122" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="122">
       <c r="B122" s="6" t="s">
         <v>522</v>
       </c>
@@ -4875,7 +4944,7 @@
         <v>523</v>
       </c>
     </row>
-    <row r="123" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="123">
       <c r="B123" s="6" t="s">
         <v>524</v>
       </c>
@@ -4883,7 +4952,7 @@
         <v>525</v>
       </c>
     </row>
-    <row r="124" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="124">
       <c r="B124" s="6" t="s">
         <v>526</v>
       </c>
@@ -4891,7 +4960,7 @@
         <v>527</v>
       </c>
     </row>
-    <row r="125" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="125">
       <c r="B125" s="6" t="s">
         <v>528</v>
       </c>
@@ -4899,7 +4968,7 @@
         <v>529</v>
       </c>
     </row>
-    <row r="126" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="126">
       <c r="B126" s="6" t="s">
         <v>530</v>
       </c>
@@ -4907,7 +4976,7 @@
         <v>531</v>
       </c>
     </row>
-    <row r="127" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="127">
       <c r="B127" s="6" t="s">
         <v>532</v>
       </c>
@@ -4915,7 +4984,7 @@
         <v>533</v>
       </c>
     </row>
-    <row r="128" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="128">
       <c r="B128" s="6" t="s">
         <v>534</v>
       </c>
@@ -4923,7 +4992,7 @@
         <v>535</v>
       </c>
     </row>
-    <row r="129" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="129">
       <c r="B129" s="6" t="s">
         <v>536</v>
       </c>
@@ -4931,7 +5000,7 @@
         <v>537</v>
       </c>
     </row>
-    <row r="130" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="130">
       <c r="B130" s="6" t="s">
         <v>538</v>
       </c>
@@ -4939,7 +5008,7 @@
         <v>539</v>
       </c>
     </row>
-    <row r="131" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="131">
       <c r="B131" s="6" t="s">
         <v>540</v>
       </c>
@@ -4947,7 +5016,7 @@
         <v>541</v>
       </c>
     </row>
-    <row r="132" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="132">
       <c r="B132" s="6" t="s">
         <v>542</v>
       </c>
@@ -4955,7 +5024,7 @@
         <v>543</v>
       </c>
     </row>
-    <row r="133" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="133">
       <c r="B133" s="6" t="s">
         <v>544</v>
       </c>
@@ -4963,7 +5032,7 @@
         <v>545</v>
       </c>
     </row>
-    <row r="134" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="134">
       <c r="B134" s="6" t="s">
         <v>546</v>
       </c>
@@ -4971,7 +5040,7 @@
         <v>547</v>
       </c>
     </row>
-    <row r="135" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="135">
       <c r="B135" s="6" t="s">
         <v>548</v>
       </c>
@@ -4979,7 +5048,7 @@
         <v>549</v>
       </c>
     </row>
-    <row r="136" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="136">
       <c r="B136" s="6" t="s">
         <v>550</v>
       </c>
@@ -4987,7 +5056,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="137" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="137">
       <c r="B137" s="6" t="s">
         <v>552</v>
       </c>
@@ -4995,7 +5064,7 @@
         <v>553</v>
       </c>
     </row>
-    <row r="138" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="138">
       <c r="B138" s="6" t="s">
         <v>554</v>
       </c>
@@ -5003,7 +5072,7 @@
         <v>555</v>
       </c>
     </row>
-    <row r="139" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="139">
       <c r="B139" s="6" t="s">
         <v>556</v>
       </c>
@@ -5011,7 +5080,7 @@
         <v>557</v>
       </c>
     </row>
-    <row r="140" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="140">
       <c r="B140" s="6" t="s">
         <v>558</v>
       </c>
@@ -5019,7 +5088,7 @@
         <v>559</v>
       </c>
     </row>
-    <row r="141" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="141">
       <c r="B141" s="6" t="s">
         <v>560</v>
       </c>
@@ -5027,7 +5096,7 @@
         <v>561</v>
       </c>
     </row>
-    <row r="142" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="142">
       <c r="B142" s="6" t="s">
         <v>562</v>
       </c>
@@ -5035,7 +5104,7 @@
         <v>563</v>
       </c>
     </row>
-    <row r="143" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="143">
       <c r="B143" s="6" t="s">
         <v>564</v>
       </c>
@@ -5043,7 +5112,7 @@
         <v>565</v>
       </c>
     </row>
-    <row r="144" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="144">
       <c r="B144" s="6" t="s">
         <v>566</v>
       </c>
@@ -5051,7 +5120,7 @@
         <v>567</v>
       </c>
     </row>
-    <row r="145" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="145">
       <c r="B145" s="6" t="s">
         <v>568</v>
       </c>
@@ -5059,7 +5128,7 @@
         <v>569</v>
       </c>
     </row>
-    <row r="146" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="146">
       <c r="B146" s="6" t="s">
         <v>570</v>
       </c>
@@ -5067,7 +5136,7 @@
         <v>571</v>
       </c>
     </row>
-    <row r="147" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="147">
       <c r="B147" s="6" t="s">
         <v>572</v>
       </c>
@@ -5075,7 +5144,7 @@
         <v>573</v>
       </c>
     </row>
-    <row r="148" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="148">
       <c r="B148" s="6" t="s">
         <v>574</v>
       </c>
@@ -5083,7 +5152,7 @@
         <v>575</v>
       </c>
     </row>
-    <row r="149" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="149">
       <c r="B149" s="6" t="s">
         <v>576</v>
       </c>
@@ -5091,7 +5160,7 @@
         <v>577</v>
       </c>
     </row>
-    <row r="150" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="150">
       <c r="B150" s="6" t="s">
         <v>578</v>
       </c>
@@ -5099,7 +5168,7 @@
         <v>579</v>
       </c>
     </row>
-    <row r="151" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="151">
       <c r="B151" s="6" t="s">
         <v>580</v>
       </c>
@@ -5107,7 +5176,7 @@
         <v>581</v>
       </c>
     </row>
-    <row r="152" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="152">
       <c r="B152" s="6" t="s">
         <v>582</v>
       </c>
@@ -5115,7 +5184,7 @@
         <v>583</v>
       </c>
     </row>
-    <row r="153" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="153">
       <c r="B153" s="6" t="s">
         <v>584</v>
       </c>
@@ -5123,7 +5192,7 @@
         <v>585</v>
       </c>
     </row>
-    <row r="154" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="154">
       <c r="B154" s="6" t="s">
         <v>586</v>
       </c>
@@ -5131,7 +5200,7 @@
         <v>587</v>
       </c>
     </row>
-    <row r="155" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="155">
       <c r="B155" s="6" t="s">
         <v>588</v>
       </c>
@@ -5139,7 +5208,7 @@
         <v>589</v>
       </c>
     </row>
-    <row r="156" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="156">
       <c r="B156" s="6" t="s">
         <v>590</v>
       </c>
@@ -5147,7 +5216,7 @@
         <v>591</v>
       </c>
     </row>
-    <row r="157" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="157">
       <c r="B157" s="6" t="s">
         <v>592</v>
       </c>
@@ -5155,7 +5224,7 @@
         <v>593</v>
       </c>
     </row>
-    <row r="158" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="158">
       <c r="B158" s="6" t="s">
         <v>594</v>
       </c>
@@ -5163,7 +5232,7 @@
         <v>595</v>
       </c>
     </row>
-    <row r="159" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="159">
       <c r="B159" s="6" t="s">
         <v>596</v>
       </c>
@@ -5171,7 +5240,7 @@
         <v>597</v>
       </c>
     </row>
-    <row r="160" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="160">
       <c r="B160" s="6" t="s">
         <v>598</v>
       </c>
@@ -5179,7 +5248,7 @@
         <v>599</v>
       </c>
     </row>
-    <row r="161" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="161">
       <c r="B161" s="6" t="s">
         <v>600</v>
       </c>
@@ -5187,7 +5256,7 @@
         <v>601</v>
       </c>
     </row>
-    <row r="162" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="162">
       <c r="B162" s="6" t="s">
         <v>602</v>
       </c>
@@ -5195,7 +5264,7 @@
         <v>603</v>
       </c>
     </row>
-    <row r="163" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="163">
       <c r="B163" s="6" t="s">
         <v>604</v>
       </c>
@@ -5203,7 +5272,7 @@
         <v>605</v>
       </c>
     </row>
-    <row r="164" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="164">
       <c r="B164" s="6" t="s">
         <v>606</v>
       </c>
@@ -5211,7 +5280,7 @@
         <v>607</v>
       </c>
     </row>
-    <row r="165" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="165">
       <c r="B165" s="6" t="s">
         <v>608</v>
       </c>
@@ -5219,7 +5288,7 @@
         <v>609</v>
       </c>
     </row>
-    <row r="166" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="166">
       <c r="B166" s="6" t="s">
         <v>610</v>
       </c>
@@ -5227,7 +5296,7 @@
         <v>611</v>
       </c>
     </row>
-    <row r="167" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="167">
       <c r="B167" s="6" t="s">
         <v>612</v>
       </c>
@@ -5235,7 +5304,7 @@
         <v>613</v>
       </c>
     </row>
-    <row r="168" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="168">
       <c r="B168" s="6" t="s">
         <v>614</v>
       </c>
@@ -5243,7 +5312,7 @@
         <v>615</v>
       </c>
     </row>
-    <row r="169" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="169">
       <c r="B169" s="6" t="s">
         <v>616</v>
       </c>
@@ -5251,7 +5320,7 @@
         <v>617</v>
       </c>
     </row>
-    <row r="170" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="170">
       <c r="B170" s="6" t="s">
         <v>618</v>
       </c>
@@ -5259,7 +5328,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="171" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="171">
       <c r="B171" s="6" t="s">
         <v>620</v>
       </c>
@@ -5267,7 +5336,7 @@
         <v>621</v>
       </c>
     </row>
-    <row r="172" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="172">
       <c r="B172" s="6" t="s">
         <v>622</v>
       </c>
@@ -5275,7 +5344,7 @@
         <v>623</v>
       </c>
     </row>
-    <row r="173" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="173">
       <c r="B173" s="6" t="s">
         <v>624</v>
       </c>
@@ -5283,7 +5352,7 @@
         <v>625</v>
       </c>
     </row>
-    <row r="174" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="174">
       <c r="B174" s="6" t="s">
         <v>626</v>
       </c>
@@ -5291,7 +5360,7 @@
         <v>627</v>
       </c>
     </row>
-    <row r="175" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="175">
       <c r="B175" s="6" t="s">
         <v>251</v>
       </c>
@@ -5299,7 +5368,7 @@
         <v>628</v>
       </c>
     </row>
-    <row r="176" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="176">
       <c r="B176" s="6" t="s">
         <v>629</v>
       </c>
@@ -5307,7 +5376,7 @@
         <v>630</v>
       </c>
     </row>
-    <row r="177" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="177">
       <c r="B177" s="6" t="s">
         <v>631</v>
       </c>
@@ -5315,7 +5384,7 @@
         <v>632</v>
       </c>
     </row>
-    <row r="178" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="178">
       <c r="B178" s="6" t="s">
         <v>633</v>
       </c>
@@ -5323,7 +5392,7 @@
         <v>634</v>
       </c>
     </row>
-    <row r="179" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="179">
       <c r="B179" s="6" t="s">
         <v>635</v>
       </c>
@@ -5331,7 +5400,7 @@
         <v>636</v>
       </c>
     </row>
-    <row r="180" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="180">
       <c r="B180" s="6" t="s">
         <v>637</v>
       </c>
@@ -5339,7 +5408,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="181" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="181">
       <c r="B181" s="6" t="s">
         <v>639</v>
       </c>
@@ -5347,7 +5416,7 @@
         <v>640</v>
       </c>
     </row>
-    <row r="182" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="182">
       <c r="B182" s="6" t="s">
         <v>641</v>
       </c>
@@ -5355,7 +5424,7 @@
         <v>642</v>
       </c>
     </row>
-    <row r="183" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="183">
       <c r="B183" s="6" t="s">
         <v>643</v>
       </c>
@@ -5363,7 +5432,7 @@
         <v>644</v>
       </c>
     </row>
-    <row r="184" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="184">
       <c r="B184" s="6" t="s">
         <v>645</v>
       </c>
@@ -5371,7 +5440,7 @@
         <v>646</v>
       </c>
     </row>
-    <row r="185" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="185">
       <c r="B185" s="6" t="s">
         <v>647</v>
       </c>
@@ -5379,7 +5448,7 @@
         <v>648</v>
       </c>
     </row>
-    <row r="186" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="186">
       <c r="B186" s="6" t="s">
         <v>649</v>
       </c>
@@ -5387,7 +5456,7 @@
         <v>650</v>
       </c>
     </row>
-    <row r="187" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="187">
       <c r="B187" s="6" t="s">
         <v>651</v>
       </c>
@@ -5395,7 +5464,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="188" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="188">
       <c r="B188" s="6" t="s">
         <v>653</v>
       </c>
@@ -5403,7 +5472,7 @@
         <v>654</v>
       </c>
     </row>
-    <row r="189" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="189">
       <c r="B189" s="6" t="s">
         <v>655</v>
       </c>
@@ -5411,7 +5480,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="190" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="190">
       <c r="B190" s="6" t="s">
         <v>657</v>
       </c>
@@ -5419,7 +5488,7 @@
         <v>658</v>
       </c>
     </row>
-    <row r="191" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="191">
       <c r="B191" s="6" t="s">
         <v>659</v>
       </c>
@@ -5427,7 +5496,7 @@
         <v>660</v>
       </c>
     </row>
-    <row r="192" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="192">
       <c r="B192" s="6" t="s">
         <v>661</v>
       </c>
@@ -5435,7 +5504,7 @@
         <v>662</v>
       </c>
     </row>
-    <row r="193" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="193">
       <c r="B193" s="6" t="s">
         <v>663</v>
       </c>
@@ -5443,7 +5512,7 @@
         <v>664</v>
       </c>
     </row>
-    <row r="194" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="194">
       <c r="B194" s="6" t="s">
         <v>665</v>
       </c>
@@ -5451,7 +5520,7 @@
         <v>666</v>
       </c>
     </row>
-    <row r="195" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="195">
       <c r="B195" s="6" t="s">
         <v>667</v>
       </c>
@@ -5459,7 +5528,7 @@
         <v>668</v>
       </c>
     </row>
-    <row r="196" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="196">
       <c r="B196" s="6" t="s">
         <v>669</v>
       </c>
@@ -5467,7 +5536,7 @@
         <v>670</v>
       </c>
     </row>
-    <row r="197" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="197">
       <c r="B197" s="6" t="s">
         <v>671</v>
       </c>
@@ -5475,7 +5544,7 @@
         <v>672</v>
       </c>
     </row>
-    <row r="198" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="198">
       <c r="B198" s="6" t="s">
         <v>673</v>
       </c>
@@ -5483,7 +5552,7 @@
         <v>674</v>
       </c>
     </row>
-    <row r="199" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="199">
       <c r="B199" s="6" t="s">
         <v>675</v>
       </c>
@@ -5491,7 +5560,7 @@
         <v>676</v>
       </c>
     </row>
-    <row r="200" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="200">
       <c r="B200" s="6" t="s">
         <v>677</v>
       </c>
@@ -5499,7 +5568,7 @@
         <v>678</v>
       </c>
     </row>
-    <row r="201" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="201">
       <c r="B201" s="6" t="s">
         <v>679</v>
       </c>
@@ -5507,7 +5576,7 @@
         <v>680</v>
       </c>
     </row>
-    <row r="202" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="202">
       <c r="B202" s="6" t="s">
         <v>681</v>
       </c>
@@ -5515,7 +5584,7 @@
         <v>682</v>
       </c>
     </row>
-    <row r="203" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="203">
       <c r="B203" s="6" t="s">
         <v>683</v>
       </c>
@@ -5523,7 +5592,7 @@
         <v>646</v>
       </c>
     </row>
-    <row r="204" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="204">
       <c r="B204" s="6" t="s">
         <v>684</v>
       </c>
@@ -5531,7 +5600,7 @@
         <v>685</v>
       </c>
     </row>
-    <row r="205" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="205">
       <c r="B205" s="6" t="s">
         <v>686</v>
       </c>
@@ -5539,7 +5608,7 @@
         <v>687</v>
       </c>
     </row>
-    <row r="206" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="206">
       <c r="B206" s="6" t="s">
         <v>688</v>
       </c>
@@ -5547,7 +5616,7 @@
         <v>689</v>
       </c>
     </row>
-    <row r="207" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="207">
       <c r="B207" s="6" t="s">
         <v>690</v>
       </c>
@@ -5555,7 +5624,7 @@
         <v>691</v>
       </c>
     </row>
-    <row r="208" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="208">
       <c r="B208" s="6" t="s">
         <v>692</v>
       </c>
@@ -5563,7 +5632,7 @@
         <v>693</v>
       </c>
     </row>
-    <row r="209" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="209">
       <c r="B209" s="6" t="s">
         <v>694</v>
       </c>
@@ -5571,7 +5640,7 @@
         <v>695</v>
       </c>
     </row>
-    <row r="210" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="210">
       <c r="B210" s="6" t="s">
         <v>696</v>
       </c>
@@ -5579,7 +5648,7 @@
         <v>697</v>
       </c>
     </row>
-    <row r="211" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="211">
       <c r="B211" s="6" t="s">
         <v>698</v>
       </c>
@@ -5587,7 +5656,7 @@
         <v>699</v>
       </c>
     </row>
-    <row r="212" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="212">
       <c r="B212" s="6" t="s">
         <v>700</v>
       </c>
@@ -5598,6 +5667,7 @@
   </sheetData>
   <phoneticPr fontId="0" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
@@ -5606,7 +5676,7 @@
   <dimension ref="B1:C98"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="1">
       <c r="B1" s="5" t="s">
         <v>0</v>
       </c>
@@ -5614,7 +5684,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="2">
       <c r="B2" s="5" t="s">
         <v>2</v>
       </c>
@@ -5622,7 +5692,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="3">
       <c r="B3" s="5" t="s">
         <v>4</v>
       </c>
@@ -5630,7 +5700,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="4">
       <c r="B4" s="5" t="s">
         <v>6</v>
       </c>
@@ -5638,7 +5708,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="5" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="5">
       <c r="B5" s="5" t="s">
         <v>8</v>
       </c>
@@ -5646,7 +5716,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="6" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="6">
       <c r="B6" s="5" t="s">
         <v>10</v>
       </c>
@@ -5654,7 +5724,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="7" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="7">
       <c r="B7" s="5" t="s">
         <v>12</v>
       </c>
@@ -5662,7 +5732,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="8" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="8">
       <c r="B8" s="5" t="s">
         <v>14</v>
       </c>
@@ -5670,7 +5740,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="9" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="9">
       <c r="B9" s="5" t="s">
         <v>16</v>
       </c>
@@ -5678,7 +5748,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="10" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="10">
       <c r="B10" s="5" t="s">
         <v>18</v>
       </c>
@@ -5686,7 +5756,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="11" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="11">
       <c r="B11" s="5" t="s">
         <v>20</v>
       </c>
@@ -5694,7 +5764,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="12" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="12">
       <c r="B12" s="5" t="s">
         <v>22</v>
       </c>
@@ -5702,7 +5772,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="13" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="13">
       <c r="B13" s="5" t="s">
         <v>24</v>
       </c>
@@ -5710,7 +5780,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="14" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="14">
       <c r="B14" s="5" t="s">
         <v>26</v>
       </c>
@@ -5718,7 +5788,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="15" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="15">
       <c r="B15" s="5" t="s">
         <v>28</v>
       </c>
@@ -5726,7 +5796,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="16" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="16">
       <c r="B16" s="5" t="s">
         <v>30</v>
       </c>
@@ -5734,7 +5804,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="17" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="17">
       <c r="B17" s="5" t="s">
         <v>32</v>
       </c>
@@ -5742,7 +5812,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="18" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="18">
       <c r="B18" s="5" t="s">
         <v>34</v>
       </c>
@@ -5750,7 +5820,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="19" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="19">
       <c r="B19" s="5" t="s">
         <v>36</v>
       </c>
@@ -5758,7 +5828,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="20" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="20">
       <c r="B20" s="5" t="s">
         <v>38</v>
       </c>
@@ -5766,7 +5836,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="21" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="21">
       <c r="B21" s="5" t="s">
         <v>40</v>
       </c>
@@ -5774,7 +5844,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="22" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="22">
       <c r="B22" s="5" t="s">
         <v>42</v>
       </c>
@@ -5782,7 +5852,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="23" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="23">
       <c r="B23" s="5" t="s">
         <v>44</v>
       </c>
@@ -5790,7 +5860,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="24" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="24">
       <c r="B24" s="5" t="s">
         <v>46</v>
       </c>
@@ -5798,7 +5868,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="25" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="25">
       <c r="B25" s="5" t="s">
         <v>48</v>
       </c>
@@ -5806,7 +5876,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="26" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="26">
       <c r="B26" s="5" t="s">
         <v>50</v>
       </c>
@@ -5814,7 +5884,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="27" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="27">
       <c r="B27" s="5" t="s">
         <v>52</v>
       </c>
@@ -5822,7 +5892,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="28" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="28">
       <c r="B28" s="5" t="s">
         <v>54</v>
       </c>
@@ -5830,7 +5900,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="29" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="29">
       <c r="B29" s="5" t="s">
         <v>56</v>
       </c>
@@ -5838,7 +5908,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="30" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="30">
       <c r="B30" s="5" t="s">
         <v>58</v>
       </c>
@@ -5846,7 +5916,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="31" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="31">
       <c r="B31" s="5" t="s">
         <v>60</v>
       </c>
@@ -5854,7 +5924,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="32" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="32">
       <c r="B32" s="5" t="s">
         <v>62</v>
       </c>
@@ -5862,7 +5932,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="33" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="33">
       <c r="B33" s="5" t="s">
         <v>64</v>
       </c>
@@ -5870,7 +5940,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="34" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="34">
       <c r="B34" s="5" t="s">
         <v>66</v>
       </c>
@@ -5878,7 +5948,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="35" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="35">
       <c r="B35" s="5" t="s">
         <v>68</v>
       </c>
@@ -5886,7 +5956,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="36" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="36">
       <c r="B36" s="5" t="s">
         <v>70</v>
       </c>
@@ -5894,7 +5964,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="37" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="37">
       <c r="B37" s="5" t="s">
         <v>72</v>
       </c>
@@ -5902,7 +5972,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="38" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="38">
       <c r="B38" s="5" t="s">
         <v>74</v>
       </c>
@@ -5910,7 +5980,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="39" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="39">
       <c r="B39" s="5" t="s">
         <v>76</v>
       </c>
@@ -5918,7 +5988,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="40" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="40">
       <c r="B40" s="5" t="s">
         <v>78</v>
       </c>
@@ -5926,7 +5996,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="41" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="41">
       <c r="B41" s="5" t="s">
         <v>80</v>
       </c>
@@ -5934,7 +6004,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="42" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="42">
       <c r="B42" s="5" t="s">
         <v>82</v>
       </c>
@@ -5942,7 +6012,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="43" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="43">
       <c r="B43" s="5" t="s">
         <v>84</v>
       </c>
@@ -5950,7 +6020,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="44" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="44">
       <c r="B44" s="5" t="s">
         <v>86</v>
       </c>
@@ -5958,7 +6028,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="45" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="45">
       <c r="B45" s="5" t="s">
         <v>88</v>
       </c>
@@ -5966,7 +6036,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="46" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="46">
       <c r="B46" s="5" t="s">
         <v>90</v>
       </c>
@@ -5974,7 +6044,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="47" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="47">
       <c r="B47" s="5" t="s">
         <v>92</v>
       </c>
@@ -5982,7 +6052,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="48" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="48">
       <c r="B48" s="5" t="s">
         <v>94</v>
       </c>
@@ -5990,7 +6060,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="49" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="49">
       <c r="B49" s="5" t="s">
         <v>96</v>
       </c>
@@ -5998,7 +6068,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="50" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="50">
       <c r="B50" s="5" t="s">
         <v>98</v>
       </c>
@@ -6006,7 +6076,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="51" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="51">
       <c r="B51" s="5" t="s">
         <v>100</v>
       </c>
@@ -6014,7 +6084,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="52" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="52">
       <c r="B52" s="5" t="s">
         <v>102</v>
       </c>
@@ -6022,7 +6092,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="53" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="53">
       <c r="B53" s="5" t="s">
         <v>104</v>
       </c>
@@ -6030,7 +6100,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="54" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="54">
       <c r="B54" s="5" t="s">
         <v>106</v>
       </c>
@@ -6038,7 +6108,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="55" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="55">
       <c r="B55" s="5" t="s">
         <v>108</v>
       </c>
@@ -6046,7 +6116,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="56" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="56">
       <c r="B56" s="5" t="s">
         <v>110</v>
       </c>
@@ -6054,7 +6124,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="57" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="57">
       <c r="B57" s="5" t="s">
         <v>112</v>
       </c>
@@ -6062,7 +6132,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="58" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="58">
       <c r="B58" s="5" t="s">
         <v>114</v>
       </c>
@@ -6070,7 +6140,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="59" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="59">
       <c r="B59" s="5" t="s">
         <v>116</v>
       </c>
@@ -6078,7 +6148,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="60" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="60">
       <c r="B60" s="5" t="s">
         <v>118</v>
       </c>
@@ -6086,7 +6156,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="61" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="61">
       <c r="B61" s="5" t="s">
         <v>120</v>
       </c>
@@ -6094,7 +6164,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="62" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="62">
       <c r="B62" s="5" t="s">
         <v>122</v>
       </c>
@@ -6102,7 +6172,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="63" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="63">
       <c r="B63" s="5" t="s">
         <v>124</v>
       </c>
@@ -6110,7 +6180,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="64" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="64">
       <c r="B64" s="5" t="s">
         <v>126</v>
       </c>
@@ -6118,7 +6188,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="65" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="65">
       <c r="B65" s="5" t="s">
         <v>128</v>
       </c>
@@ -6126,7 +6196,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="66" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="66">
       <c r="B66" s="5" t="s">
         <v>130</v>
       </c>
@@ -6134,7 +6204,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="67" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="67">
       <c r="B67" s="5" t="s">
         <v>132</v>
       </c>
@@ -6142,7 +6212,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="68" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="68">
       <c r="B68" s="5" t="s">
         <v>134</v>
       </c>
@@ -6150,7 +6220,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="69" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="69">
       <c r="B69" s="5" t="s">
         <v>136</v>
       </c>
@@ -6158,7 +6228,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="70" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="70">
       <c r="B70" s="5" t="s">
         <v>138</v>
       </c>
@@ -6166,7 +6236,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="71" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="71">
       <c r="B71" s="5" t="s">
         <v>140</v>
       </c>
@@ -6174,7 +6244,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="72" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="72">
       <c r="B72" s="5" t="s">
         <v>142</v>
       </c>
@@ -6182,7 +6252,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="73" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="73">
       <c r="B73" s="5" t="s">
         <v>144</v>
       </c>
@@ -6190,7 +6260,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="74" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="74">
       <c r="B74" s="5" t="s">
         <v>146</v>
       </c>
@@ -6198,7 +6268,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="75" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="75">
       <c r="B75" s="5" t="s">
         <v>148</v>
       </c>
@@ -6206,7 +6276,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="76" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="76">
       <c r="B76" s="5" t="s">
         <v>150</v>
       </c>
@@ -6214,7 +6284,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="77" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="77">
       <c r="B77" s="5" t="s">
         <v>152</v>
       </c>
@@ -6222,7 +6292,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="78" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="78">
       <c r="B78" s="5" t="s">
         <v>154</v>
       </c>
@@ -6230,7 +6300,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="79" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="79">
       <c r="B79" s="5" t="s">
         <v>156</v>
       </c>
@@ -6238,7 +6308,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="80" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="80">
       <c r="B80" s="5" t="s">
         <v>158</v>
       </c>
@@ -6246,7 +6316,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="81" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="81">
       <c r="B81" s="5" t="s">
         <v>160</v>
       </c>
@@ -6254,7 +6324,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="82" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="82">
       <c r="B82" s="5" t="s">
         <v>162</v>
       </c>
@@ -6262,7 +6332,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="83" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="83">
       <c r="B83" s="5" t="s">
         <v>164</v>
       </c>
@@ -6270,7 +6340,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="84" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="84">
       <c r="B84" s="5" t="s">
         <v>166</v>
       </c>
@@ -6278,7 +6348,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="85" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="85">
       <c r="B85" s="5" t="s">
         <v>168</v>
       </c>
@@ -6286,7 +6356,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="86" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="86">
       <c r="B86" s="5" t="s">
         <v>170</v>
       </c>
@@ -6294,7 +6364,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="87" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="87">
       <c r="B87" s="5" t="s">
         <v>172</v>
       </c>
@@ -6302,7 +6372,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="88" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="88">
       <c r="B88" s="5" t="s">
         <v>174</v>
       </c>
@@ -6310,7 +6380,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="89" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="89">
       <c r="B89" s="5" t="s">
         <v>176</v>
       </c>
@@ -6318,7 +6388,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="90" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="90">
       <c r="B90" s="5" t="s">
         <v>178</v>
       </c>
@@ -6326,7 +6396,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="91" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="91">
       <c r="B91" s="5" t="s">
         <v>180</v>
       </c>
@@ -6334,7 +6404,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="92" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="92">
       <c r="B92" s="5" t="s">
         <v>182</v>
       </c>
@@ -6342,7 +6412,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="93" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="93">
       <c r="B93" s="5" t="s">
         <v>184</v>
       </c>
@@ -6350,7 +6420,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="94" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="94">
       <c r="B94" s="5" t="s">
         <v>186</v>
       </c>
@@ -6358,7 +6428,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="95" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="95">
       <c r="B95" s="5" t="s">
         <v>188</v>
       </c>
@@ -6366,7 +6436,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="96" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="96">
       <c r="B96" s="5" t="s">
         <v>190</v>
       </c>
@@ -6374,7 +6444,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="97" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="97">
       <c r="B97" s="5" t="s">
         <v>192</v>
       </c>
@@ -6382,7 +6452,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="98" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="98">
       <c r="B98" s="5" t="s">
         <v>194</v>
       </c>
@@ -6393,441 +6463,563 @@
   </sheetData>
   <phoneticPr fontId="0" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="B1:C53"/>
+  <dimension ref="B1:C68"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B1" s="4" t="s">
+    <row r="1">
+      <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="4" t="s">
+      <c r="C1" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B2" s="4" t="s">
+    <row r="2">
+      <c r="B2" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="4" t="s">
+      <c r="C2" s="1" t="s">
+        <v>734</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="B3" s="1" t="s">
+        <v>293</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="B4" s="1" t="s">
+        <v>295</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>736</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="B5" s="1" t="s">
+        <v>297</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>737</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="B6" s="1" t="s">
+        <v>299</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="B7" s="1" t="s">
+        <v>301</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>736</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="B8" s="1" t="s">
+        <v>303</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>739</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="B9" s="1" t="s">
+        <v>305</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="B10" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>741</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="B11" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>742</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="B12" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>743</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="B13" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>744</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="B14" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>745</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="B15" s="1" t="s">
+        <v>746</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>747</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="B16" s="1" t="s">
+        <v>748</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>749</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="B18" s="1" t="s">
+        <v>751</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>752</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="B19" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>753</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="C20" s="1" t="s">
         <v>754</v>
       </c>
     </row>
-    <row r="3" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B3" s="4" t="s">
-        <v>293</v>
-      </c>
-      <c r="C3" s="4" t="s">
+    <row r="21">
+      <c r="B21" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>754</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="B22" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>754</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="B23" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>754</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="B24" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>754</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="B25" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="C25" s="1" t="s">
         <v>755</v>
       </c>
     </row>
-    <row r="4" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B4" s="4" t="s">
-        <v>295</v>
-      </c>
-      <c r="C4" s="4" t="s">
+    <row r="26">
+      <c r="B26" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="C26" s="1" t="s">
         <v>756</v>
       </c>
     </row>
-    <row r="5" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B5" s="4" t="s">
-        <v>297</v>
-      </c>
-      <c r="C5" s="4" t="s">
+    <row r="27">
+      <c r="B27" s="1" t="s">
         <v>757</v>
       </c>
-    </row>
-    <row r="6" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B6" s="4" t="s">
-        <v>299</v>
-      </c>
-      <c r="C6" s="4" t="s">
+      <c r="C27" s="1" t="s">
         <v>758</v>
       </c>
     </row>
-    <row r="7" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B7" s="4" t="s">
-        <v>301</v>
-      </c>
-      <c r="C7" s="4" t="s">
-        <v>756</v>
-      </c>
-    </row>
-    <row r="8" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B8" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="C8" s="4" t="s">
+    <row r="28">
+      <c r="B28" s="1" t="s">
         <v>759</v>
       </c>
-    </row>
-    <row r="9" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B9" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="C9" s="4" t="s">
+      <c r="C28" s="1" t="s">
         <v>760</v>
       </c>
     </row>
-    <row r="10" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B10" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="C10" s="4" t="s">
+    <row r="29">
+      <c r="B29" s="1" t="s">
         <v>761</v>
       </c>
-    </row>
-    <row r="11" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B11" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="C11" s="4" t="s">
+      <c r="C29" s="1" t="s">
         <v>762</v>
       </c>
     </row>
-    <row r="12" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B12" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="C12" s="4" t="s">
+    <row r="30">
+      <c r="B30" s="1" t="s">
         <v>763</v>
       </c>
-    </row>
-    <row r="13" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B13" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="C13" s="4" t="s">
+      <c r="C30" s="1" t="s">
         <v>764</v>
       </c>
     </row>
-    <row r="14" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B14" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="C14" s="4" t="s">
+    <row r="31">
+      <c r="B31" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="C31" s="1" t="s">
         <v>765</v>
       </c>
     </row>
-    <row r="15" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B15" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="C15" s="4" t="s">
+    <row r="32">
+      <c r="B32" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="C32" s="1" t="s">
+        <v>766</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="B33" s="1" t="s">
+        <v>767</v>
+      </c>
+      <c r="C33" s="1" t="s">
+        <v>768</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="B34" s="1" t="s">
+        <v>769</v>
+      </c>
+      <c r="C34" s="1" t="s">
+        <v>770</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="B35" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="C35" s="1" t="s">
+        <v>771</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="B36" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="C36" s="1" t="s">
+        <v>772</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="B37" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="C37" s="1" t="s">
+        <v>773</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="B38" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="C38" s="1" t="s">
+        <v>774</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="B39" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="C39" s="1" t="s">
+        <v>775</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="B40" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="C40" s="1" t="s">
+        <v>776</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="B41" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="C41" s="1" t="s">
+        <v>777</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="B42" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="C42" s="1" t="s">
+        <v>778</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="B43" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="C43" s="1" t="s">
+        <v>779</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="B44" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="C44" s="1" t="s">
+        <v>780</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="B45" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="C45" s="1" t="s">
+        <v>781</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="B46" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="C46" s="1" t="s">
+        <v>782</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="B47" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="C47" s="1" t="s">
+        <v>783</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="B48" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="C48" s="1" t="s">
+        <v>784</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="B49" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="C49" s="1" t="s">
+        <v>785</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="B50" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="C50" s="1" t="s">
+        <v>786</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="B51" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="C51" s="1" t="s">
+        <v>787</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="B52" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="C52" s="1" t="s">
+        <v>788</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="B53" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="C53" s="1" t="s">
+        <v>789</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="B54" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="C54" s="1" t="s">
         <v>765</v>
       </c>
     </row>
-    <row r="16" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B16" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="C16" s="4" t="s">
-        <v>765</v>
-      </c>
-    </row>
-    <row r="17" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B17" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="C17" s="4" t="s">
-        <v>765</v>
-      </c>
-    </row>
-    <row r="18" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B18" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="C18" s="4" t="s">
-        <v>765</v>
-      </c>
-    </row>
-    <row r="19" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B19" s="4" t="s">
-        <v>62</v>
-      </c>
-      <c r="C19" s="4" t="s">
-        <v>766</v>
-      </c>
-    </row>
-    <row r="20" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B20" s="4" t="s">
-        <v>64</v>
-      </c>
-      <c r="C20" s="4" t="s">
-        <v>767</v>
-      </c>
-    </row>
-    <row r="21" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B21" s="4" t="s">
-        <v>768</v>
-      </c>
-      <c r="C21" s="4" t="s">
-        <v>769</v>
-      </c>
-    </row>
-    <row r="22" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B22" s="4" t="s">
-        <v>70</v>
-      </c>
-      <c r="C22" s="4" t="s">
-        <v>770</v>
-      </c>
-    </row>
-    <row r="23" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B23" s="4" t="s">
-        <v>92</v>
-      </c>
-      <c r="C23" s="4" t="s">
-        <v>771</v>
-      </c>
-    </row>
-    <row r="24" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B24" s="4" t="s">
-        <v>772</v>
-      </c>
-      <c r="C24" s="4" t="s">
-        <v>773</v>
-      </c>
-    </row>
-    <row r="25" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B25" s="4" t="s">
-        <v>774</v>
-      </c>
-      <c r="C25" s="4" t="s">
-        <v>775</v>
-      </c>
-    </row>
-    <row r="26" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B26" s="4" t="s">
-        <v>76</v>
-      </c>
-      <c r="C26" s="4" t="s">
-        <v>776</v>
-      </c>
-    </row>
-    <row r="27" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B27" s="4" t="s">
-        <v>78</v>
-      </c>
-      <c r="C27" s="4" t="s">
-        <v>777</v>
-      </c>
-    </row>
-    <row r="28" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B28" s="4" t="s">
-        <v>80</v>
-      </c>
-      <c r="C28" s="4" t="s">
-        <v>778</v>
-      </c>
-    </row>
-    <row r="29" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B29" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="C29" s="4" t="s">
-        <v>779</v>
-      </c>
-    </row>
-    <row r="30" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B30" s="4" t="s">
-        <v>201</v>
-      </c>
-      <c r="C30" s="4" t="s">
-        <v>780</v>
-      </c>
-    </row>
-    <row r="31" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B31" s="4" t="s">
-        <v>84</v>
-      </c>
-      <c r="C31" s="4" t="s">
-        <v>781</v>
-      </c>
-    </row>
-    <row r="32" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B32" s="4" t="s">
-        <v>86</v>
-      </c>
-      <c r="C32" s="4" t="s">
-        <v>782</v>
-      </c>
-    </row>
-    <row r="33" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B33" s="4" t="s">
-        <v>88</v>
-      </c>
-      <c r="C33" s="4" t="s">
-        <v>783</v>
-      </c>
-    </row>
-    <row r="34" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B34" s="4" t="s">
-        <v>90</v>
-      </c>
-      <c r="C34" s="4" t="s">
-        <v>784</v>
-      </c>
-    </row>
-    <row r="35" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B35" s="4" t="s">
-        <v>114</v>
-      </c>
-      <c r="C35" s="4" t="s">
-        <v>785</v>
-      </c>
-    </row>
-    <row r="36" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B36" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="C36" s="4" t="s">
-        <v>786</v>
-      </c>
-    </row>
-    <row r="37" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B37" s="4" t="s">
-        <v>96</v>
-      </c>
-      <c r="C37" s="4" t="s">
-        <v>787</v>
-      </c>
-    </row>
-    <row r="38" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B38" s="4" t="s">
-        <v>98</v>
-      </c>
-      <c r="C38" s="4" t="s">
-        <v>788</v>
-      </c>
-    </row>
-    <row r="39" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B39" s="4" t="s">
-        <v>100</v>
-      </c>
-      <c r="C39" s="4" t="s">
-        <v>789</v>
-      </c>
-    </row>
-    <row r="40" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B40" s="4" t="s">
-        <v>102</v>
-      </c>
-      <c r="C40" s="4" t="s">
+    <row r="55">
+      <c r="B55" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="C55" s="1" t="s">
         <v>790</v>
       </c>
     </row>
-    <row r="41" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B41" s="4" t="s">
-        <v>104</v>
-      </c>
-      <c r="C41" s="4" t="s">
+    <row r="56">
+      <c r="B56" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="C56" s="1" t="s">
         <v>791</v>
       </c>
     </row>
-    <row r="42" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B42" s="4" t="s">
-        <v>106</v>
-      </c>
-      <c r="C42" s="4" t="s">
+    <row r="57">
+      <c r="B57" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="C57" s="1" t="s">
         <v>792</v>
       </c>
     </row>
-    <row r="43" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B43" s="4" t="s">
-        <v>108</v>
-      </c>
-      <c r="C43" s="4" t="s">
+    <row r="58">
+      <c r="B58" s="1" t="s">
         <v>793</v>
       </c>
-    </row>
-    <row r="44" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B44" s="4" t="s">
-        <v>110</v>
-      </c>
-      <c r="C44" s="4" t="s">
+      <c r="C58" s="1" t="s">
         <v>794</v>
       </c>
     </row>
-    <row r="45" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B45" s="4" t="s">
-        <v>112</v>
-      </c>
-      <c r="C45" s="4" t="s">
-        <v>770</v>
-      </c>
-    </row>
-    <row r="46" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B46" s="4" t="s">
-        <v>116</v>
-      </c>
-      <c r="C46" s="4" t="s">
+    <row r="59">
+      <c r="B59" s="1" t="s">
         <v>795</v>
       </c>
-    </row>
-    <row r="47" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B47" s="4" t="s">
+      <c r="C59" s="1" t="s">
         <v>796</v>
       </c>
-      <c r="C47" s="4" t="s">
+    </row>
+    <row r="60">
+      <c r="B60" s="1" t="s">
         <v>797</v>
       </c>
-    </row>
-    <row r="48" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B48" s="4" t="s">
+      <c r="C60" s="1" t="s">
+        <v>798</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="B61" s="1" t="s">
         <v>647</v>
       </c>
-      <c r="C48" s="4" t="s">
-        <v>798</v>
-      </c>
-    </row>
-    <row r="49" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B49" s="4" t="s">
+      <c r="C61" s="1" t="s">
+        <v>799</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="B62" s="1" t="s">
         <v>649</v>
       </c>
-      <c r="C49" s="4" t="s">
-        <v>799</v>
-      </c>
-    </row>
-    <row r="50" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B50" s="4" t="s">
+      <c r="C62" s="1" t="s">
+        <v>800</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="B63" s="1" t="s">
         <v>651</v>
       </c>
-      <c r="C50" s="4" t="s">
-        <v>800</v>
-      </c>
-    </row>
-    <row r="51" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B51" s="4" t="s">
+      <c r="C63" s="1" t="s">
+        <v>801</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="B64" s="1" t="s">
         <v>653</v>
       </c>
-      <c r="C51" s="4" t="s">
-        <v>801</v>
-      </c>
-    </row>
-    <row r="52" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B52" s="4" t="s">
+      <c r="C64" s="1" t="s">
+        <v>802</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="B65" s="1" t="s">
         <v>655</v>
       </c>
-      <c r="C52" s="4" t="s">
-        <v>802</v>
-      </c>
-    </row>
-    <row r="53" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B53" s="4" t="s">
+      <c r="C65" s="1" t="s">
         <v>803</v>
       </c>
-      <c r="C53" s="4" t="s">
+    </row>
+    <row r="66">
+      <c r="B66" s="1" t="s">
         <v>804</v>
+      </c>
+      <c r="C66" s="1" t="s">
+        <v>805</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="B67" s="1" t="s">
+        <v>806</v>
+      </c>
+      <c r="C67" s="1" t="s">
+        <v>807</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="B68" s="1" t="s">
+        <v>808</v>
+      </c>
+      <c r="C68" s="1" t="s">
+        <v>809</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="0" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
@@ -6836,257 +7028,258 @@
   <dimension ref="B1:C31"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B1" s="3" t="s">
+    <row r="1">
+      <c r="B1" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="4" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B2" s="3" t="s">
-        <v>805</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>806</v>
-      </c>
-    </row>
-    <row r="3" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B3" s="3" t="s">
+    <row r="2">
+      <c r="B2" s="4" t="s">
+        <v>810</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>811</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="B3" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="C3" s="3" t="s">
-        <v>707</v>
-      </c>
-    </row>
-    <row r="4" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B4" s="3" t="s">
-        <v>703</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>755</v>
-      </c>
-    </row>
-    <row r="5" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B5" s="3" t="s">
-        <v>705</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>779</v>
-      </c>
-    </row>
-    <row r="6" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B6" s="3" t="s">
+      <c r="C3" s="4" t="s">
+        <v>812</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="B4" s="4" t="s">
+        <v>813</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="B5" s="4" t="s">
+        <v>814</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>774</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="B6" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="C6" s="3" t="s">
-        <v>807</v>
-      </c>
-    </row>
-    <row r="7" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B7" s="3" t="s">
+      <c r="C6" s="4" t="s">
+        <v>815</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="B7" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="C7" s="3" t="s">
-        <v>808</v>
-      </c>
-    </row>
-    <row r="8" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B8" s="3" t="s">
+      <c r="C7" s="4" t="s">
+        <v>816</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="B8" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="C8" s="3" t="s">
-        <v>809</v>
-      </c>
-    </row>
-    <row r="9" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B9" s="3" t="s">
+      <c r="C8" s="4" t="s">
+        <v>817</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="B9" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="C9" s="3" t="s">
-        <v>810</v>
-      </c>
-    </row>
-    <row r="10" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B10" s="3" t="s">
+      <c r="C9" s="4" t="s">
+        <v>818</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="B10" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="C10" s="3" t="s">
-        <v>811</v>
-      </c>
-    </row>
-    <row r="11" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B11" s="3" t="s">
+      <c r="C10" s="4" t="s">
+        <v>819</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="B11" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="C11" s="3" t="s">
+      <c r="C11" s="4" t="s">
+        <v>820</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="B12" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="C12" s="4" t="s">
+        <v>821</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="B13" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="C13" s="4" t="s">
+        <v>822</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="B14" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="C14" s="4" t="s">
+        <v>823</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="B15" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="C15" s="4" t="s">
+        <v>737</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="B16" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="C16" s="4" t="s">
+        <v>736</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="C17" s="4" t="s">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="B18" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="C18" s="4" t="s">
+        <v>824</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="B19" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="C19" s="4" t="s">
         <v>812</v>
       </c>
     </row>
-    <row r="12" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B12" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="C12" s="3" t="s">
-        <v>813</v>
-      </c>
-    </row>
-    <row r="13" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B13" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="C13" s="3" t="s">
-        <v>814</v>
-      </c>
-    </row>
-    <row r="14" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B14" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="C14" s="3" t="s">
-        <v>815</v>
-      </c>
-    </row>
-    <row r="15" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B15" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="C15" s="3" t="s">
-        <v>757</v>
-      </c>
-    </row>
-    <row r="16" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B16" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="C16" s="3" t="s">
-        <v>756</v>
-      </c>
-    </row>
-    <row r="17" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B17" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="C17" s="3" t="s">
-        <v>758</v>
-      </c>
-    </row>
-    <row r="18" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B18" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="C18" s="3" t="s">
-        <v>816</v>
-      </c>
-    </row>
-    <row r="19" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B19" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="C19" s="3" t="s">
-        <v>707</v>
-      </c>
-    </row>
-    <row r="20" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B20" s="3" t="s">
-        <v>709</v>
-      </c>
-      <c r="C20" s="3" t="s">
-        <v>817</v>
-      </c>
-    </row>
-    <row r="21" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B21" s="3" t="s">
+    <row r="20">
+      <c r="B20" s="4" t="s">
+        <v>825</v>
+      </c>
+      <c r="C20" s="4" t="s">
+        <v>826</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="B21" s="4" t="s">
         <v>66</v>
       </c>
-      <c r="C21" s="3" t="s">
-        <v>818</v>
-      </c>
-    </row>
-    <row r="22" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B22" s="3" t="s">
+      <c r="C21" s="4" t="s">
+        <v>827</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="B22" s="4" t="s">
         <v>68</v>
       </c>
-      <c r="C22" s="3" t="s">
-        <v>819</v>
-      </c>
-    </row>
-    <row r="23" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B23" s="3" t="s">
+      <c r="C22" s="4" t="s">
+        <v>828</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="B23" s="4" t="s">
         <v>72</v>
       </c>
-      <c r="C23" s="3" t="s">
-        <v>706</v>
-      </c>
-    </row>
-    <row r="24" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B24" s="3" t="s">
-        <v>710</v>
-      </c>
-      <c r="C24" s="3" t="s">
-        <v>820</v>
-      </c>
-    </row>
-    <row r="25" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B25" s="3" t="s">
+      <c r="C23" s="4" t="s">
+        <v>829</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="B24" s="4" t="s">
+        <v>830</v>
+      </c>
+      <c r="C24" s="4" t="s">
+        <v>831</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="B25" s="4" t="s">
         <v>92</v>
       </c>
-      <c r="C25" s="3" t="s">
+      <c r="C25" s="4" t="s">
+        <v>766</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="B26" s="4" t="s">
+        <v>114</v>
+      </c>
+      <c r="C26" s="4" t="s">
+        <v>780</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="B27" s="4" t="s">
+        <v>832</v>
+      </c>
+      <c r="C27" s="4" t="s">
+        <v>752</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="B28" s="4" t="s">
+        <v>833</v>
+      </c>
+      <c r="C28" s="4" t="s">
+        <v>834</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="B29" s="4" t="s">
+        <v>835</v>
+      </c>
+      <c r="C29" s="4" t="s">
         <v>771</v>
       </c>
     </row>
-    <row r="26" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B26" s="3" t="s">
-        <v>114</v>
-      </c>
-      <c r="C26" s="3" t="s">
-        <v>785</v>
-      </c>
-    </row>
-    <row r="27" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B27" s="3" t="s">
-        <v>712</v>
-      </c>
-      <c r="C27" s="3" t="s">
-        <v>708</v>
-      </c>
-    </row>
-    <row r="28" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B28" s="3" t="s">
-        <v>714</v>
-      </c>
-      <c r="C28" s="3" t="s">
-        <v>821</v>
-      </c>
-    </row>
-    <row r="29" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B29" s="3" t="s">
-        <v>716</v>
-      </c>
-      <c r="C29" s="3" t="s">
-        <v>776</v>
-      </c>
-    </row>
-    <row r="30" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B30" s="3" t="s">
-        <v>718</v>
-      </c>
-      <c r="C30" s="3" t="s">
-        <v>822</v>
-      </c>
-    </row>
-    <row r="31" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B31" s="3" t="s">
-        <v>720</v>
-      </c>
-      <c r="C31" s="3" t="s">
-        <v>823</v>
+    <row r="30">
+      <c r="B30" s="4" t="s">
+        <v>836</v>
+      </c>
+      <c r="C30" s="4" t="s">
+        <v>837</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="B31" s="4" t="s">
+        <v>838</v>
+      </c>
+      <c r="C31" s="4" t="s">
+        <v>839</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="0" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
@@ -7095,112 +7288,113 @@
   <dimension ref="B1:C13"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B1" s="1" t="s">
+    <row r="1">
+      <c r="B1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="2" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B2" s="1" t="s">
+    <row r="2">
+      <c r="B2" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="C2" s="1" t="s">
-        <v>702</v>
-      </c>
-    </row>
-    <row r="3" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B3" s="1" t="s">
-        <v>703</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>704</v>
-      </c>
-    </row>
-    <row r="4" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B4" s="1" t="s">
-        <v>705</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>706</v>
-      </c>
-    </row>
-    <row r="5" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B5" s="1" t="s">
+      <c r="C2" s="2" t="s">
+        <v>840</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="B3" s="2" t="s">
+        <v>813</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>841</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="B4" s="2" t="s">
+        <v>814</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>829</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="B5" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="C5" s="1" t="s">
-        <v>707</v>
-      </c>
-    </row>
-    <row r="6" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B6" s="1" t="s">
+      <c r="C5" s="2" t="s">
+        <v>812</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="B6" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="C6" s="1" t="s">
-        <v>708</v>
-      </c>
-    </row>
-    <row r="7" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B7" s="1" t="s">
-        <v>709</v>
-      </c>
-      <c r="C7" s="1" t="s">
+      <c r="C6" s="2" t="s">
+        <v>752</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="B7" s="2" t="s">
+        <v>825</v>
+      </c>
+      <c r="C7" s="2" t="s">
         <v>287</v>
       </c>
     </row>
-    <row r="8" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B8" s="1" t="s">
-        <v>710</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>711</v>
-      </c>
-    </row>
-    <row r="9" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B9" s="1" t="s">
-        <v>712</v>
-      </c>
-      <c r="C9" s="1" t="s">
-        <v>713</v>
-      </c>
-    </row>
-    <row r="10" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B10" s="1" t="s">
-        <v>714</v>
-      </c>
-      <c r="C10" s="1" t="s">
-        <v>715</v>
-      </c>
-    </row>
-    <row r="11" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B11" s="1" t="s">
-        <v>716</v>
-      </c>
-      <c r="C11" s="1" t="s">
-        <v>717</v>
-      </c>
-    </row>
-    <row r="12" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B12" s="1" t="s">
-        <v>718</v>
-      </c>
-      <c r="C12" s="1" t="s">
-        <v>719</v>
-      </c>
-    </row>
-    <row r="13" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B13" s="1" t="s">
-        <v>720</v>
-      </c>
-      <c r="C13" s="1" t="s">
-        <v>721</v>
+    <row r="8">
+      <c r="B8" s="2" t="s">
+        <v>830</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>842</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="B9" s="2" t="s">
+        <v>832</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>843</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="B10" s="2" t="s">
+        <v>833</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>844</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="B11" s="2" t="s">
+        <v>835</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>845</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="B12" s="2" t="s">
+        <v>836</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>846</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="B13" s="2" t="s">
+        <v>838</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>847</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter/>
 </worksheet>
 </file>
--- a/Assets/Editor/DataDic/Data.xlsx
+++ b/Assets/Editor/DataDic/Data.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView minimized="1" xWindow="0" yWindow="0" windowWidth="17385" windowHeight="7860" activeTab="1"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="17385" windowHeight="7860" firstSheet="2" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="FishData" sheetId="1" r:id="rId1"/>
@@ -20,12 +20,12 @@
     <sheet name="OperateData" sheetId="7" r:id="rId6"/>
     <sheet name="NPCFunctionData" sheetId="8" r:id="rId7"/>
   </sheets>
-  <calcPr calcId="162913" fullCalcOnLoad="1"/>
+  <calcPr calcId="162913"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="848" uniqueCount="848">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1041" uniqueCount="848">
   <si>
     <t>Key</t>
   </si>
@@ -633,10 +633,10 @@
     <t>405</t>
   </si>
   <si>
-    <r xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+    <r>
       <t>6</t>
     </r>
-    <r xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+    <r>
       <rPr>
         <sz val="11"/>
         <rFont val="Calibri"/>
@@ -644,7 +644,7 @@
       </rPr>
       <t>,0</t>
     </r>
-    <phoneticPr xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" fontId="0" type="noConversion"/>
+    <phoneticPr fontId="0" type="noConversion"/>
   </si>
   <si>
     <t>后山</t>
@@ -659,10 +659,10 @@
     <t>植物店</t>
   </si>
   <si>
-    <r xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+    <r>
       <t>9</t>
     </r>
-    <r xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+    <r>
       <rPr>
         <sz val="11"/>
         <rFont val="Calibri"/>
@@ -670,7 +670,7 @@
       </rPr>
       <t>,0</t>
     </r>
-    <phoneticPr xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" fontId="0" type="noConversion"/>
+    <phoneticPr fontId="0" type="noConversion"/>
   </si>
   <si>
     <t>教堂</t>
@@ -2597,8 +2597,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
@@ -2641,16 +2640,16 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="10">
-    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="0" applyProtection="1"/>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="0" applyProtection="1"/>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="0" applyProtection="1"/>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="0" applyProtection="1"/>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="0" applyProtection="1"/>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="0" applyProtection="1"/>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="0" applyProtection="1"/>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="2" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="0" applyProtection="1"/>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="1" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="0" applyProtection="1"/>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="2" applyFill="1" borderId="0" applyBorder="1" xfId="0" applyProtection="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -2934,7 +2933,7 @@
   <dimension ref="B1:C32"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B1" s="6" t="s">
         <v>0</v>
       </c>
@@ -2942,7 +2941,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B2" s="6" t="s">
         <v>702</v>
       </c>
@@ -2950,7 +2949,7 @@
         <v>703</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B3" s="6" t="s">
         <v>303</v>
       </c>
@@ -2958,7 +2957,7 @@
         <v>704</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B4" s="6" t="s">
         <v>305</v>
       </c>
@@ -2966,7 +2965,7 @@
         <v>705</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B5" s="6" t="s">
         <v>307</v>
       </c>
@@ -2974,7 +2973,7 @@
         <v>706</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B6" s="6" t="s">
         <v>309</v>
       </c>
@@ -2982,7 +2981,7 @@
         <v>707</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B7" s="6" t="s">
         <v>311</v>
       </c>
@@ -2990,7 +2989,7 @@
         <v>708</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B8" s="6" t="s">
         <v>315</v>
       </c>
@@ -2998,7 +2997,7 @@
         <v>709</v>
       </c>
     </row>
-    <row r="9">
+    <row r="9" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B9" s="6" t="s">
         <v>317</v>
       </c>
@@ -3006,7 +3005,7 @@
         <v>710</v>
       </c>
     </row>
-    <row r="10">
+    <row r="10" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B10" s="6" t="s">
         <v>319</v>
       </c>
@@ -3014,7 +3013,7 @@
         <v>711</v>
       </c>
     </row>
-    <row r="11">
+    <row r="11" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B11" s="6" t="s">
         <v>321</v>
       </c>
@@ -3022,7 +3021,7 @@
         <v>712</v>
       </c>
     </row>
-    <row r="12">
+    <row r="12" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B12" s="6" t="s">
         <v>323</v>
       </c>
@@ -3030,7 +3029,7 @@
         <v>713</v>
       </c>
     </row>
-    <row r="13">
+    <row r="13" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B13" s="6" t="s">
         <v>325</v>
       </c>
@@ -3038,7 +3037,7 @@
         <v>714</v>
       </c>
     </row>
-    <row r="14">
+    <row r="14" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B14" s="6" t="s">
         <v>329</v>
       </c>
@@ -3046,7 +3045,7 @@
         <v>715</v>
       </c>
     </row>
-    <row r="15">
+    <row r="15" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B15" s="6" t="s">
         <v>331</v>
       </c>
@@ -3054,7 +3053,7 @@
         <v>716</v>
       </c>
     </row>
-    <row r="16">
+    <row r="16" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B16" s="6" t="s">
         <v>333</v>
       </c>
@@ -3062,7 +3061,7 @@
         <v>717</v>
       </c>
     </row>
-    <row r="17">
+    <row r="17" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B17" s="6" t="s">
         <v>335</v>
       </c>
@@ -3070,7 +3069,7 @@
         <v>718</v>
       </c>
     </row>
-    <row r="18">
+    <row r="18" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B18" s="6" t="s">
         <v>337</v>
       </c>
@@ -3078,7 +3077,7 @@
         <v>719</v>
       </c>
     </row>
-    <row r="19">
+    <row r="19" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B19" s="6" t="s">
         <v>485</v>
       </c>
@@ -3086,7 +3085,7 @@
         <v>720</v>
       </c>
     </row>
-    <row r="20">
+    <row r="20" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B20" s="6" t="s">
         <v>487</v>
       </c>
@@ -3094,7 +3093,7 @@
         <v>721</v>
       </c>
     </row>
-    <row r="21">
+    <row r="21" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B21" s="6" t="s">
         <v>490</v>
       </c>
@@ -3102,7 +3101,7 @@
         <v>722</v>
       </c>
     </row>
-    <row r="22">
+    <row r="22" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B22" s="6" t="s">
         <v>494</v>
       </c>
@@ -3110,7 +3109,7 @@
         <v>723</v>
       </c>
     </row>
-    <row r="23">
+    <row r="23" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B23" s="6" t="s">
         <v>495</v>
       </c>
@@ -3118,7 +3117,7 @@
         <v>724</v>
       </c>
     </row>
-    <row r="24">
+    <row r="24" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B24" s="6" t="s">
         <v>500</v>
       </c>
@@ -3126,7 +3125,7 @@
         <v>725</v>
       </c>
     </row>
-    <row r="25">
+    <row r="25" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B25" s="6" t="s">
         <v>502</v>
       </c>
@@ -3134,7 +3133,7 @@
         <v>726</v>
       </c>
     </row>
-    <row r="26">
+    <row r="26" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B26" s="6" t="s">
         <v>504</v>
       </c>
@@ -3142,7 +3141,7 @@
         <v>727</v>
       </c>
     </row>
-    <row r="27">
+    <row r="27" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B27" s="6" t="s">
         <v>246</v>
       </c>
@@ -3150,7 +3149,7 @@
         <v>728</v>
       </c>
     </row>
-    <row r="28">
+    <row r="28" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B28" s="6" t="s">
         <v>507</v>
       </c>
@@ -3158,7 +3157,7 @@
         <v>729</v>
       </c>
     </row>
-    <row r="29">
+    <row r="29" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B29" s="6" t="s">
         <v>509</v>
       </c>
@@ -3166,7 +3165,7 @@
         <v>730</v>
       </c>
     </row>
-    <row r="30">
+    <row r="30" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B30" s="6" t="s">
         <v>511</v>
       </c>
@@ -3174,7 +3173,7 @@
         <v>731</v>
       </c>
     </row>
-    <row r="31">
+    <row r="31" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B31" s="6" t="s">
         <v>512</v>
       </c>
@@ -3182,7 +3181,7 @@
         <v>732</v>
       </c>
     </row>
-    <row r="32">
+    <row r="32" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B32" s="6" t="s">
         <v>514</v>
       </c>
@@ -3194,7 +3193,6 @@
   <phoneticPr fontId="0" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="1200" verticalDpi="1200"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
@@ -3203,10 +3201,10 @@
   <dimension ref="B1:O56"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="22.28515625" customWidth="1" style="3"/>
+    <col min="2" max="2" width="22.28515625" style="3" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B1" s="6" t="s">
         <v>1</v>
       </c>
@@ -3214,7 +3212,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B2" s="6" t="s">
         <v>196</v>
       </c>
@@ -3222,7 +3220,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B3" s="6" t="s">
         <v>198</v>
       </c>
@@ -3230,7 +3228,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B4" s="6" t="s">
         <v>200</v>
       </c>
@@ -3250,7 +3248,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B5" s="6" t="s">
         <v>206</v>
       </c>
@@ -3265,7 +3263,7 @@
         <v>874</v>
       </c>
       <c r="J5" s="6" t="str">
-        <f ref="J5:K5" t="shared" si="0">VLOOKUP(J4,$B:$C,2,FALSE)</f>
+        <f t="shared" ref="J5:K5" si="0">VLOOKUP(J4,$B:$C,2,FALSE)</f>
         <v>2355</v>
       </c>
       <c r="K5" s="6">
@@ -3273,7 +3271,7 @@
         <v>2497</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B6" s="6" t="s">
         <v>208</v>
       </c>
@@ -3300,7 +3298,7 @@
       <c r="L6" s="6"/>
       <c r="M6" s="9"/>
     </row>
-    <row r="7">
+    <row r="7" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B7" s="6" t="s">
         <v>210</v>
       </c>
@@ -3332,7 +3330,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B8" s="6" t="s">
         <v>203</v>
       </c>
@@ -3351,7 +3349,7 @@
         <v>2355</v>
       </c>
       <c r="K8" s="6">
-        <f ref="K8:L8" t="shared" si="1">VLOOKUP(K7,$B:$C,2,FALSE)</f>
+        <f t="shared" ref="K8:L8" si="1">VLOOKUP(K7,$B:$C,2,FALSE)</f>
         <v>2497</v>
       </c>
       <c r="L8" s="6" t="str">
@@ -3363,7 +3361,7 @@
         <v>889</v>
       </c>
       <c r="N8" s="6" t="str">
-        <f ref="N8:O8" t="shared" si="2">VLOOKUP(N7,$B:$C,2,FALSE)</f>
+        <f t="shared" ref="N8:O8" si="2">VLOOKUP(N7,$B:$C,2,FALSE)</f>
         <v>695</v>
       </c>
       <c r="O8" s="6" t="str">
@@ -3371,7 +3369,7 @@
         <v>512</v>
       </c>
     </row>
-    <row r="9">
+    <row r="9" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B9" s="6" t="s">
         <v>217</v>
       </c>
@@ -3392,7 +3390,7 @@
         <v>874,2355</v>
       </c>
       <c r="K9" s="9" t="str">
-        <f ref="K9:N9" t="shared" si="3">J9&amp;","&amp;K8</f>
+        <f t="shared" ref="K9:N9" si="3">J9&amp;","&amp;K8</f>
         <v>874,2355,2497</v>
       </c>
       <c r="L9" s="9" t="str">
@@ -3412,7 +3410,7 @@
         <v>874,2355,2497,302,889,695,512</v>
       </c>
     </row>
-    <row r="10">
+    <row r="10" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B10" s="6" t="s">
         <v>219</v>
       </c>
@@ -3423,7 +3421,7 @@
         <v>216</v>
       </c>
     </row>
-    <row r="11">
+    <row r="11" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B11" s="6" t="s">
         <v>221</v>
       </c>
@@ -3434,7 +3432,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="12">
+    <row r="12" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B12" s="6" t="s">
         <v>224</v>
       </c>
@@ -3455,7 +3453,7 @@
       <c r="N12" s="6"/>
       <c r="O12" s="6"/>
     </row>
-    <row r="13">
+    <row r="13" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B13" s="6" t="s">
         <v>225</v>
       </c>
@@ -3473,7 +3471,7 @@
       <c r="N13" s="6"/>
       <c r="O13" s="6"/>
     </row>
-    <row r="14">
+    <row r="14" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B14" s="6" t="s">
         <v>227</v>
       </c>
@@ -3497,7 +3495,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="15">
+    <row r="15" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B15" s="6" t="s">
         <v>229</v>
       </c>
@@ -3514,7 +3512,7 @@
         <v>302</v>
       </c>
       <c r="J15" s="6" t="str">
-        <f ref="J15:L15" t="shared" si="4">VLOOKUP(J14,$B:$C,2,FALSE)</f>
+        <f t="shared" ref="J15:L15" si="4">VLOOKUP(J14,$B:$C,2,FALSE)</f>
         <v>889</v>
       </c>
       <c r="K15" s="6" t="str">
@@ -3527,7 +3525,7 @@
       </c>
       <c r="M15" s="6"/>
     </row>
-    <row r="16">
+    <row r="16" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B16" s="6" t="s">
         <v>219</v>
       </c>
@@ -3558,7 +3556,7 @@
       <c r="M16" s="9"/>
       <c r="N16" s="9"/>
     </row>
-    <row r="17">
+    <row r="17" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B17" s="6" t="s">
         <v>219</v>
       </c>
@@ -3581,7 +3579,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="18">
+    <row r="18" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B18" s="6" t="s">
         <v>235</v>
       </c>
@@ -3596,7 +3594,7 @@
         <v>889</v>
       </c>
       <c r="J18" s="6" t="str">
-        <f ref="J18:L18" t="shared" si="5">VLOOKUP(J17,$B:$C,2,FALSE)</f>
+        <f t="shared" ref="J18:L18" si="5">VLOOKUP(J17,$B:$C,2,FALSE)</f>
         <v>695</v>
       </c>
       <c r="K18" s="6" t="str">
@@ -3608,7 +3606,7 @@
         <v>2497</v>
       </c>
     </row>
-    <row r="19">
+    <row r="19" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B19" s="6" t="s">
         <v>238</v>
       </c>
@@ -3629,7 +3627,7 @@
         <v>889,695</v>
       </c>
       <c r="K19" s="9" t="str">
-        <f ref="K19:L19" t="shared" si="6">J19&amp;","&amp;K18</f>
+        <f t="shared" ref="K19:L19" si="6">J19&amp;","&amp;K18</f>
         <v>889,695,512</v>
       </c>
       <c r="L19" s="9" t="str">
@@ -3639,7 +3637,7 @@
       <c r="M19" s="9"/>
       <c r="N19" s="9"/>
     </row>
-    <row r="20">
+    <row r="20" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B20" s="6" t="s">
         <v>240</v>
       </c>
@@ -3648,7 +3646,7 @@
       </c>
       <c r="G20" s="7"/>
     </row>
-    <row r="21">
+    <row r="21" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B21" s="6" t="s">
         <v>241</v>
       </c>
@@ -3656,7 +3654,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="22">
+    <row r="22" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B22" s="6" t="s">
         <v>243</v>
       </c>
@@ -3664,7 +3662,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="23">
+    <row r="23" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B23" s="6" t="s">
         <v>245</v>
       </c>
@@ -3677,7 +3675,7 @@
       </c>
       <c r="M23" s="6"/>
     </row>
-    <row r="24">
+    <row r="24" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B24" s="6" t="s">
         <v>204</v>
       </c>
@@ -3685,7 +3683,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="25">
+    <row r="25" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B25" s="6" t="s">
         <v>248</v>
       </c>
@@ -3694,7 +3692,7 @@
       </c>
       <c r="M25" s="6"/>
     </row>
-    <row r="26">
+    <row r="26" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B26" s="6" t="s">
         <v>250</v>
       </c>
@@ -3703,7 +3701,7 @@
       </c>
       <c r="M26" s="6"/>
     </row>
-    <row r="27">
+    <row r="27" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B27" s="6" t="s">
         <v>227</v>
       </c>
@@ -3712,7 +3710,7 @@
       </c>
       <c r="M27" s="6"/>
     </row>
-    <row r="28">
+    <row r="28" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B28" s="6" t="s">
         <v>253</v>
       </c>
@@ -3721,7 +3719,7 @@
       </c>
       <c r="M28" s="6"/>
     </row>
-    <row r="29">
+    <row r="29" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B29" s="6" t="s">
         <v>227</v>
       </c>
@@ -3730,7 +3728,7 @@
       </c>
       <c r="M29" s="6"/>
     </row>
-    <row r="30">
+    <row r="30" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B30" s="6" t="s">
         <v>215</v>
       </c>
@@ -3738,7 +3736,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="31">
+    <row r="31" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B31" s="6" t="s">
         <v>227</v>
       </c>
@@ -3749,7 +3747,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="32">
+    <row r="32" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B32" s="6" t="s">
         <v>257</v>
       </c>
@@ -3760,7 +3758,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="33">
+    <row r="33" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B33" s="6" t="s">
         <v>227</v>
       </c>
@@ -3771,7 +3769,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="34">
+    <row r="34" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B34" s="6" t="s">
         <v>213</v>
       </c>
@@ -3779,7 +3777,7 @@
         <v>259</v>
       </c>
     </row>
-    <row r="35">
+    <row r="35" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B35" s="6" t="s">
         <v>260</v>
       </c>
@@ -3787,7 +3785,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="36">
+    <row r="36" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B36" s="6" t="s">
         <v>262</v>
       </c>
@@ -3795,7 +3793,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="37">
+    <row r="37" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B37" s="6" t="s">
         <v>264</v>
       </c>
@@ -3803,7 +3801,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="38">
+    <row r="38" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B38" s="6" t="s">
         <v>266</v>
       </c>
@@ -3811,7 +3809,7 @@
         <v>3056</v>
       </c>
     </row>
-    <row r="39">
+    <row r="39" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B39" s="6" t="s">
         <v>267</v>
       </c>
@@ -3819,7 +3817,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="40">
+    <row r="40" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B40" s="6" t="s">
         <v>269</v>
       </c>
@@ -3827,7 +3825,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="41">
+    <row r="41" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B41" s="6" t="s">
         <v>205</v>
       </c>
@@ -3835,7 +3833,7 @@
         <v>2497</v>
       </c>
     </row>
-    <row r="42">
+    <row r="42" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B42" s="6" t="s">
         <v>271</v>
       </c>
@@ -3843,7 +3841,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="43">
+    <row r="43" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B43" s="6" t="s">
         <v>273</v>
       </c>
@@ -3851,7 +3849,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="44">
+    <row r="44" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B44" s="6" t="s">
         <v>227</v>
       </c>
@@ -3859,7 +3857,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="45">
+    <row r="45" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B45" s="6" t="s">
         <v>214</v>
       </c>
@@ -3867,7 +3865,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="46">
+    <row r="46" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B46" s="6" t="s">
         <v>277</v>
       </c>
@@ -3875,7 +3873,7 @@
         <v>278</v>
       </c>
     </row>
-    <row r="47">
+    <row r="47" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B47" s="6" t="s">
         <v>279</v>
       </c>
@@ -3883,7 +3881,7 @@
         <v>280</v>
       </c>
     </row>
-    <row r="48">
+    <row r="48" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B48" s="6" t="s">
         <v>281</v>
       </c>
@@ -3891,7 +3889,7 @@
         <v>282</v>
       </c>
     </row>
-    <row r="49">
+    <row r="49" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B49" s="6" t="s">
         <v>283</v>
       </c>
@@ -3899,7 +3897,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="50">
+    <row r="50" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B50" s="6" t="s">
         <v>285</v>
       </c>
@@ -3907,7 +3905,7 @@
         <v>286</v>
       </c>
     </row>
-    <row r="51">
+    <row r="51" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B51" s="6" t="s">
         <v>287</v>
       </c>
@@ -3915,7 +3913,7 @@
         <v>547</v>
       </c>
     </row>
-    <row r="52">
+    <row r="52" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B52" s="6" t="s">
         <v>212</v>
       </c>
@@ -3923,7 +3921,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="53">
+    <row r="53" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B53" s="6" t="s">
         <v>219</v>
       </c>
@@ -3931,7 +3929,7 @@
         <v>288</v>
       </c>
     </row>
-    <row r="54">
+    <row r="54" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B54" s="6" t="s">
         <v>219</v>
       </c>
@@ -3939,7 +3937,7 @@
         <v>289</v>
       </c>
     </row>
-    <row r="55">
+    <row r="55" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B55" s="6" t="s">
         <v>290</v>
       </c>
@@ -3947,7 +3945,7 @@
         <v>291</v>
       </c>
     </row>
-    <row r="56">
+    <row r="56" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B56" s="6" t="s">
         <v>219</v>
       </c>
@@ -3958,8 +3956,7 @@
   </sheetData>
   <phoneticPr fontId="0" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="1200" verticalDpi="1200"/>
-  <headerFooter/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -3968,7 +3965,7 @@
   <dimension ref="B1:C212"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B1" s="6" t="s">
         <v>0</v>
       </c>
@@ -3976,7 +3973,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B2" s="6" t="s">
         <v>293</v>
       </c>
@@ -3984,7 +3981,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B3" s="6" t="s">
         <v>295</v>
       </c>
@@ -3992,7 +3989,7 @@
         <v>296</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B4" s="6" t="s">
         <v>297</v>
       </c>
@@ -4000,7 +3997,7 @@
         <v>298</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B5" s="6" t="s">
         <v>299</v>
       </c>
@@ -4008,7 +4005,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B6" s="6" t="s">
         <v>301</v>
       </c>
@@ -4016,7 +4013,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B7" s="6" t="s">
         <v>303</v>
       </c>
@@ -4024,7 +4021,7 @@
         <v>304</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B8" s="6" t="s">
         <v>305</v>
       </c>
@@ -4032,7 +4029,7 @@
         <v>304</v>
       </c>
     </row>
-    <row r="9">
+    <row r="9" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B9" s="6" t="s">
         <v>306</v>
       </c>
@@ -4040,7 +4037,7 @@
         <v>304</v>
       </c>
     </row>
-    <row r="10">
+    <row r="10" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B10" s="6" t="s">
         <v>307</v>
       </c>
@@ -4048,7 +4045,7 @@
         <v>308</v>
       </c>
     </row>
-    <row r="11">
+    <row r="11" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B11" s="6" t="s">
         <v>309</v>
       </c>
@@ -4056,7 +4053,7 @@
         <v>310</v>
       </c>
     </row>
-    <row r="12">
+    <row r="12" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B12" s="6" t="s">
         <v>311</v>
       </c>
@@ -4064,7 +4061,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="13">
+    <row r="13" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B13" s="6" t="s">
         <v>313</v>
       </c>
@@ -4072,7 +4069,7 @@
         <v>314</v>
       </c>
     </row>
-    <row r="14">
+    <row r="14" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B14" s="6" t="s">
         <v>315</v>
       </c>
@@ -4080,7 +4077,7 @@
         <v>316</v>
       </c>
     </row>
-    <row r="15">
+    <row r="15" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B15" s="6" t="s">
         <v>317</v>
       </c>
@@ -4088,7 +4085,7 @@
         <v>318</v>
       </c>
     </row>
-    <row r="16">
+    <row r="16" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B16" s="6" t="s">
         <v>319</v>
       </c>
@@ -4096,7 +4093,7 @@
         <v>320</v>
       </c>
     </row>
-    <row r="17">
+    <row r="17" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B17" s="6" t="s">
         <v>321</v>
       </c>
@@ -4104,7 +4101,7 @@
         <v>322</v>
       </c>
     </row>
-    <row r="18">
+    <row r="18" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B18" s="6" t="s">
         <v>323</v>
       </c>
@@ -4112,7 +4109,7 @@
         <v>324</v>
       </c>
     </row>
-    <row r="19">
+    <row r="19" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B19" s="6" t="s">
         <v>325</v>
       </c>
@@ -4120,7 +4117,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="20">
+    <row r="20" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B20" s="6" t="s">
         <v>327</v>
       </c>
@@ -4128,7 +4125,7 @@
         <v>328</v>
       </c>
     </row>
-    <row r="21">
+    <row r="21" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B21" s="6" t="s">
         <v>329</v>
       </c>
@@ -4136,7 +4133,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="22">
+    <row r="22" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B22" s="6" t="s">
         <v>331</v>
       </c>
@@ -4144,7 +4141,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="23">
+    <row r="23" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B23" s="6" t="s">
         <v>333</v>
       </c>
@@ -4152,7 +4149,7 @@
         <v>334</v>
       </c>
     </row>
-    <row r="24">
+    <row r="24" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B24" s="6" t="s">
         <v>335</v>
       </c>
@@ -4160,7 +4157,7 @@
         <v>336</v>
       </c>
     </row>
-    <row r="25">
+    <row r="25" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B25" s="6" t="s">
         <v>337</v>
       </c>
@@ -4168,7 +4165,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="26">
+    <row r="26" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B26" s="6" t="s">
         <v>339</v>
       </c>
@@ -4176,7 +4173,7 @@
         <v>340</v>
       </c>
     </row>
-    <row r="27">
+    <row r="27" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B27" s="6" t="s">
         <v>341</v>
       </c>
@@ -4184,7 +4181,7 @@
         <v>342</v>
       </c>
     </row>
-    <row r="28">
+    <row r="28" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B28" s="6" t="s">
         <v>343</v>
       </c>
@@ -4192,7 +4189,7 @@
         <v>344</v>
       </c>
     </row>
-    <row r="29">
+    <row r="29" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B29" s="6" t="s">
         <v>345</v>
       </c>
@@ -4200,7 +4197,7 @@
         <v>346</v>
       </c>
     </row>
-    <row r="30">
+    <row r="30" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B30" s="6" t="s">
         <v>347</v>
       </c>
@@ -4208,7 +4205,7 @@
         <v>348</v>
       </c>
     </row>
-    <row r="31">
+    <row r="31" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B31" s="6" t="s">
         <v>349</v>
       </c>
@@ -4216,7 +4213,7 @@
         <v>350</v>
       </c>
     </row>
-    <row r="32">
+    <row r="32" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B32" s="6" t="s">
         <v>351</v>
       </c>
@@ -4224,7 +4221,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="33">
+    <row r="33" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B33" s="6" t="s">
         <v>353</v>
       </c>
@@ -4232,7 +4229,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="34">
+    <row r="34" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B34" s="6" t="s">
         <v>355</v>
       </c>
@@ -4240,7 +4237,7 @@
         <v>356</v>
       </c>
     </row>
-    <row r="35">
+    <row r="35" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B35" s="6" t="s">
         <v>357</v>
       </c>
@@ -4248,7 +4245,7 @@
         <v>358</v>
       </c>
     </row>
-    <row r="36">
+    <row r="36" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B36" s="6" t="s">
         <v>359</v>
       </c>
@@ -4256,7 +4253,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="37">
+    <row r="37" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B37" s="6" t="s">
         <v>361</v>
       </c>
@@ -4264,7 +4261,7 @@
         <v>362</v>
       </c>
     </row>
-    <row r="38">
+    <row r="38" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B38" s="6" t="s">
         <v>363</v>
       </c>
@@ -4272,7 +4269,7 @@
         <v>364</v>
       </c>
     </row>
-    <row r="39">
+    <row r="39" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B39" s="6" t="s">
         <v>365</v>
       </c>
@@ -4280,7 +4277,7 @@
         <v>366</v>
       </c>
     </row>
-    <row r="40">
+    <row r="40" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B40" s="6" t="s">
         <v>367</v>
       </c>
@@ -4288,7 +4285,7 @@
         <v>368</v>
       </c>
     </row>
-    <row r="41">
+    <row r="41" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B41" s="6" t="s">
         <v>369</v>
       </c>
@@ -4296,7 +4293,7 @@
         <v>370</v>
       </c>
     </row>
-    <row r="42">
+    <row r="42" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B42" s="6" t="s">
         <v>371</v>
       </c>
@@ -4304,7 +4301,7 @@
         <v>372</v>
       </c>
     </row>
-    <row r="43">
+    <row r="43" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B43" s="6" t="s">
         <v>373</v>
       </c>
@@ -4312,7 +4309,7 @@
         <v>374</v>
       </c>
     </row>
-    <row r="44">
+    <row r="44" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B44" s="6" t="s">
         <v>375</v>
       </c>
@@ -4320,7 +4317,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="45">
+    <row r="45" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B45" s="6" t="s">
         <v>377</v>
       </c>
@@ -4328,7 +4325,7 @@
         <v>378</v>
       </c>
     </row>
-    <row r="46">
+    <row r="46" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B46" s="6" t="s">
         <v>379</v>
       </c>
@@ -4336,7 +4333,7 @@
         <v>380</v>
       </c>
     </row>
-    <row r="47">
+    <row r="47" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B47" s="6" t="s">
         <v>381</v>
       </c>
@@ -4344,7 +4341,7 @@
         <v>382</v>
       </c>
     </row>
-    <row r="48">
+    <row r="48" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B48" s="6" t="s">
         <v>383</v>
       </c>
@@ -4352,7 +4349,7 @@
         <v>384</v>
       </c>
     </row>
-    <row r="49">
+    <row r="49" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B49" s="6" t="s">
         <v>385</v>
       </c>
@@ -4360,7 +4357,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="50">
+    <row r="50" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B50" s="6" t="s">
         <v>387</v>
       </c>
@@ -4368,7 +4365,7 @@
         <v>388</v>
       </c>
     </row>
-    <row r="51">
+    <row r="51" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B51" s="6" t="s">
         <v>389</v>
       </c>
@@ -4376,7 +4373,7 @@
         <v>390</v>
       </c>
     </row>
-    <row r="52">
+    <row r="52" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B52" s="6" t="s">
         <v>391</v>
       </c>
@@ -4384,7 +4381,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="53">
+    <row r="53" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B53" s="6" t="s">
         <v>393</v>
       </c>
@@ -4392,7 +4389,7 @@
         <v>394</v>
       </c>
     </row>
-    <row r="54">
+    <row r="54" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B54" s="6" t="s">
         <v>395</v>
       </c>
@@ -4400,7 +4397,7 @@
         <v>396</v>
       </c>
     </row>
-    <row r="55">
+    <row r="55" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B55" s="6" t="s">
         <v>397</v>
       </c>
@@ -4408,7 +4405,7 @@
         <v>398</v>
       </c>
     </row>
-    <row r="56">
+    <row r="56" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B56" s="6" t="s">
         <v>399</v>
       </c>
@@ -4416,7 +4413,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="57">
+    <row r="57" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B57" s="6" t="s">
         <v>401</v>
       </c>
@@ -4424,7 +4421,7 @@
         <v>402</v>
       </c>
     </row>
-    <row r="58">
+    <row r="58" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B58" s="6" t="s">
         <v>403</v>
       </c>
@@ -4432,7 +4429,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="59">
+    <row r="59" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B59" s="6" t="s">
         <v>405</v>
       </c>
@@ -4440,7 +4437,7 @@
         <v>406</v>
       </c>
     </row>
-    <row r="60">
+    <row r="60" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B60" s="6" t="s">
         <v>407</v>
       </c>
@@ -4448,7 +4445,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="61">
+    <row r="61" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B61" s="6" t="s">
         <v>409</v>
       </c>
@@ -4456,7 +4453,7 @@
         <v>410</v>
       </c>
     </row>
-    <row r="62">
+    <row r="62" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B62" s="6" t="s">
         <v>411</v>
       </c>
@@ -4464,7 +4461,7 @@
         <v>412</v>
       </c>
     </row>
-    <row r="63">
+    <row r="63" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B63" s="6" t="s">
         <v>413</v>
       </c>
@@ -4472,7 +4469,7 @@
         <v>414</v>
       </c>
     </row>
-    <row r="64">
+    <row r="64" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B64" s="6" t="s">
         <v>415</v>
       </c>
@@ -4480,7 +4477,7 @@
         <v>416</v>
       </c>
     </row>
-    <row r="65">
+    <row r="65" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B65" s="6" t="s">
         <v>417</v>
       </c>
@@ -4488,7 +4485,7 @@
         <v>418</v>
       </c>
     </row>
-    <row r="66">
+    <row r="66" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B66" s="6" t="s">
         <v>419</v>
       </c>
@@ -4496,7 +4493,7 @@
         <v>420</v>
       </c>
     </row>
-    <row r="67">
+    <row r="67" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B67" s="6" t="s">
         <v>421</v>
       </c>
@@ -4504,7 +4501,7 @@
         <v>422</v>
       </c>
     </row>
-    <row r="68">
+    <row r="68" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B68" s="6" t="s">
         <v>423</v>
       </c>
@@ -4512,7 +4509,7 @@
         <v>424</v>
       </c>
     </row>
-    <row r="69">
+    <row r="69" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B69" s="6" t="s">
         <v>425</v>
       </c>
@@ -4520,7 +4517,7 @@
         <v>426</v>
       </c>
     </row>
-    <row r="70">
+    <row r="70" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B70" s="6" t="s">
         <v>427</v>
       </c>
@@ -4528,7 +4525,7 @@
         <v>428</v>
       </c>
     </row>
-    <row r="71">
+    <row r="71" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B71" s="6" t="s">
         <v>429</v>
       </c>
@@ -4536,7 +4533,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="72">
+    <row r="72" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B72" s="6" t="s">
         <v>431</v>
       </c>
@@ -4544,7 +4541,7 @@
         <v>432</v>
       </c>
     </row>
-    <row r="73">
+    <row r="73" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B73" s="6" t="s">
         <v>433</v>
       </c>
@@ -4552,7 +4549,7 @@
         <v>434</v>
       </c>
     </row>
-    <row r="74">
+    <row r="74" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B74" s="6" t="s">
         <v>435</v>
       </c>
@@ -4560,7 +4557,7 @@
         <v>436</v>
       </c>
     </row>
-    <row r="75">
+    <row r="75" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B75" s="6" t="s">
         <v>437</v>
       </c>
@@ -4568,7 +4565,7 @@
         <v>438</v>
       </c>
     </row>
-    <row r="76">
+    <row r="76" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B76" s="6" t="s">
         <v>439</v>
       </c>
@@ -4576,7 +4573,7 @@
         <v>440</v>
       </c>
     </row>
-    <row r="77">
+    <row r="77" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B77" s="6">
         <v>1077</v>
       </c>
@@ -4584,7 +4581,7 @@
         <v>441</v>
       </c>
     </row>
-    <row r="78">
+    <row r="78" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B78" s="6" t="s">
         <v>442</v>
       </c>
@@ -4592,7 +4589,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="79">
+    <row r="79" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B79" s="6" t="s">
         <v>443</v>
       </c>
@@ -4600,7 +4597,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="80">
+    <row r="80" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B80" s="6" t="s">
         <v>445</v>
       </c>
@@ -4608,7 +4605,7 @@
         <v>446</v>
       </c>
     </row>
-    <row r="81">
+    <row r="81" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B81" s="6" t="s">
         <v>447</v>
       </c>
@@ -4616,7 +4613,7 @@
         <v>448</v>
       </c>
     </row>
-    <row r="82">
+    <row r="82" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B82" s="6" t="s">
         <v>449</v>
       </c>
@@ -4624,7 +4621,7 @@
         <v>450</v>
       </c>
     </row>
-    <row r="83">
+    <row r="83" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B83" s="6" t="s">
         <v>451</v>
       </c>
@@ -4632,7 +4629,7 @@
         <v>452</v>
       </c>
     </row>
-    <row r="84">
+    <row r="84" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B84" s="6" t="s">
         <v>453</v>
       </c>
@@ -4640,7 +4637,7 @@
         <v>454</v>
       </c>
     </row>
-    <row r="85">
+    <row r="85" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B85" s="6" t="s">
         <v>455</v>
       </c>
@@ -4648,7 +4645,7 @@
         <v>456</v>
       </c>
     </row>
-    <row r="86">
+    <row r="86" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B86" s="6" t="s">
         <v>457</v>
       </c>
@@ -4656,7 +4653,7 @@
         <v>458</v>
       </c>
     </row>
-    <row r="87">
+    <row r="87" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B87" s="6" t="s">
         <v>459</v>
       </c>
@@ -4664,7 +4661,7 @@
         <v>460</v>
       </c>
     </row>
-    <row r="88">
+    <row r="88" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B88" s="6" t="s">
         <v>461</v>
       </c>
@@ -4672,7 +4669,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="89">
+    <row r="89" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B89" s="6" t="s">
         <v>463</v>
       </c>
@@ -4680,7 +4677,7 @@
         <v>464</v>
       </c>
     </row>
-    <row r="90">
+    <row r="90" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B90" s="6" t="s">
         <v>465</v>
       </c>
@@ -4688,7 +4685,7 @@
         <v>466</v>
       </c>
     </row>
-    <row r="91">
+    <row r="91" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B91" s="6" t="s">
         <v>467</v>
       </c>
@@ -4696,7 +4693,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="92">
+    <row r="92" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B92" s="6" t="s">
         <v>469</v>
       </c>
@@ -4704,7 +4701,7 @@
         <v>470</v>
       </c>
     </row>
-    <row r="93">
+    <row r="93" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B93" s="6" t="s">
         <v>471</v>
       </c>
@@ -4712,7 +4709,7 @@
         <v>472</v>
       </c>
     </row>
-    <row r="94">
+    <row r="94" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B94" s="6" t="s">
         <v>473</v>
       </c>
@@ -4720,7 +4717,7 @@
         <v>474</v>
       </c>
     </row>
-    <row r="95">
+    <row r="95" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B95" s="6" t="s">
         <v>475</v>
       </c>
@@ -4728,7 +4725,7 @@
         <v>476</v>
       </c>
     </row>
-    <row r="96">
+    <row r="96" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B96" s="6" t="s">
         <v>477</v>
       </c>
@@ -4736,7 +4733,7 @@
         <v>478</v>
       </c>
     </row>
-    <row r="97">
+    <row r="97" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B97" s="6" t="s">
         <v>479</v>
       </c>
@@ -4744,7 +4741,7 @@
         <v>480</v>
       </c>
     </row>
-    <row r="98">
+    <row r="98" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B98" s="6" t="s">
         <v>481</v>
       </c>
@@ -4752,7 +4749,7 @@
         <v>482</v>
       </c>
     </row>
-    <row r="99">
+    <row r="99" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B99" s="6" t="s">
         <v>483</v>
       </c>
@@ -4760,7 +4757,7 @@
         <v>484</v>
       </c>
     </row>
-    <row r="100">
+    <row r="100" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B100" s="6" t="s">
         <v>485</v>
       </c>
@@ -4768,7 +4765,7 @@
         <v>486</v>
       </c>
     </row>
-    <row r="101">
+    <row r="101" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B101" s="6" t="s">
         <v>487</v>
       </c>
@@ -4776,7 +4773,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="102">
+    <row r="102" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B102" s="6" t="s">
         <v>488</v>
       </c>
@@ -4784,7 +4781,7 @@
         <v>489</v>
       </c>
     </row>
-    <row r="103">
+    <row r="103" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B103" s="6" t="s">
         <v>490</v>
       </c>
@@ -4792,7 +4789,7 @@
         <v>491</v>
       </c>
     </row>
-    <row r="104">
+    <row r="104" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B104" s="6" t="s">
         <v>492</v>
       </c>
@@ -4800,7 +4797,7 @@
         <v>493</v>
       </c>
     </row>
-    <row r="105">
+    <row r="105" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B105" s="6" t="s">
         <v>494</v>
       </c>
@@ -4808,7 +4805,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="106">
+    <row r="106" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B106" s="6" t="s">
         <v>495</v>
       </c>
@@ -4816,7 +4813,7 @@
         <v>496</v>
       </c>
     </row>
-    <row r="107">
+    <row r="107" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B107" s="6" t="s">
         <v>497</v>
       </c>
@@ -4824,7 +4821,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="108">
+    <row r="108" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B108" s="6" t="s">
         <v>498</v>
       </c>
@@ -4832,7 +4829,7 @@
         <v>499</v>
       </c>
     </row>
-    <row r="109">
+    <row r="109" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B109" s="6" t="s">
         <v>500</v>
       </c>
@@ -4840,7 +4837,7 @@
         <v>501</v>
       </c>
     </row>
-    <row r="110">
+    <row r="110" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B110" s="6" t="s">
         <v>502</v>
       </c>
@@ -4848,7 +4845,7 @@
         <v>503</v>
       </c>
     </row>
-    <row r="111">
+    <row r="111" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B111" s="6" t="s">
         <v>504</v>
       </c>
@@ -4856,7 +4853,7 @@
         <v>505</v>
       </c>
     </row>
-    <row r="112">
+    <row r="112" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B112" s="6" t="s">
         <v>246</v>
       </c>
@@ -4864,7 +4861,7 @@
         <v>506</v>
       </c>
     </row>
-    <row r="113">
+    <row r="113" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B113" s="6" t="s">
         <v>507</v>
       </c>
@@ -4872,7 +4869,7 @@
         <v>508</v>
       </c>
     </row>
-    <row r="114">
+    <row r="114" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B114" s="6" t="s">
         <v>509</v>
       </c>
@@ -4880,7 +4877,7 @@
         <v>510</v>
       </c>
     </row>
-    <row r="115">
+    <row r="115" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B115" s="6" t="s">
         <v>511</v>
       </c>
@@ -4888,7 +4885,7 @@
         <v>450</v>
       </c>
     </row>
-    <row r="116">
+    <row r="116" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B116" s="6" t="s">
         <v>512</v>
       </c>
@@ -4896,7 +4893,7 @@
         <v>513</v>
       </c>
     </row>
-    <row r="117">
+    <row r="117" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B117" s="6" t="s">
         <v>514</v>
       </c>
@@ -4904,7 +4901,7 @@
         <v>241</v>
       </c>
     </row>
-    <row r="118">
+    <row r="118" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B118" s="6" t="s">
         <v>515</v>
       </c>
@@ -4912,7 +4909,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="119">
+    <row r="119" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B119" s="6" t="s">
         <v>516</v>
       </c>
@@ -4920,7 +4917,7 @@
         <v>517</v>
       </c>
     </row>
-    <row r="120">
+    <row r="120" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B120" s="6" t="s">
         <v>518</v>
       </c>
@@ -4928,7 +4925,7 @@
         <v>519</v>
       </c>
     </row>
-    <row r="121">
+    <row r="121" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B121" s="6" t="s">
         <v>520</v>
       </c>
@@ -4936,7 +4933,7 @@
         <v>521</v>
       </c>
     </row>
-    <row r="122">
+    <row r="122" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B122" s="6" t="s">
         <v>522</v>
       </c>
@@ -4944,7 +4941,7 @@
         <v>523</v>
       </c>
     </row>
-    <row r="123">
+    <row r="123" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B123" s="6" t="s">
         <v>524</v>
       </c>
@@ -4952,7 +4949,7 @@
         <v>525</v>
       </c>
     </row>
-    <row r="124">
+    <row r="124" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B124" s="6" t="s">
         <v>526</v>
       </c>
@@ -4960,7 +4957,7 @@
         <v>527</v>
       </c>
     </row>
-    <row r="125">
+    <row r="125" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B125" s="6" t="s">
         <v>528</v>
       </c>
@@ -4968,7 +4965,7 @@
         <v>529</v>
       </c>
     </row>
-    <row r="126">
+    <row r="126" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B126" s="6" t="s">
         <v>530</v>
       </c>
@@ -4976,7 +4973,7 @@
         <v>531</v>
       </c>
     </row>
-    <row r="127">
+    <row r="127" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B127" s="6" t="s">
         <v>532</v>
       </c>
@@ -4984,7 +4981,7 @@
         <v>533</v>
       </c>
     </row>
-    <row r="128">
+    <row r="128" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B128" s="6" t="s">
         <v>534</v>
       </c>
@@ -4992,7 +4989,7 @@
         <v>535</v>
       </c>
     </row>
-    <row r="129">
+    <row r="129" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B129" s="6" t="s">
         <v>536</v>
       </c>
@@ -5000,7 +4997,7 @@
         <v>537</v>
       </c>
     </row>
-    <row r="130">
+    <row r="130" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B130" s="6" t="s">
         <v>538</v>
       </c>
@@ -5008,7 +5005,7 @@
         <v>539</v>
       </c>
     </row>
-    <row r="131">
+    <row r="131" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B131" s="6" t="s">
         <v>540</v>
       </c>
@@ -5016,7 +5013,7 @@
         <v>541</v>
       </c>
     </row>
-    <row r="132">
+    <row r="132" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B132" s="6" t="s">
         <v>542</v>
       </c>
@@ -5024,7 +5021,7 @@
         <v>543</v>
       </c>
     </row>
-    <row r="133">
+    <row r="133" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B133" s="6" t="s">
         <v>544</v>
       </c>
@@ -5032,7 +5029,7 @@
         <v>545</v>
       </c>
     </row>
-    <row r="134">
+    <row r="134" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B134" s="6" t="s">
         <v>546</v>
       </c>
@@ -5040,7 +5037,7 @@
         <v>547</v>
       </c>
     </row>
-    <row r="135">
+    <row r="135" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B135" s="6" t="s">
         <v>548</v>
       </c>
@@ -5048,7 +5045,7 @@
         <v>549</v>
       </c>
     </row>
-    <row r="136">
+    <row r="136" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B136" s="6" t="s">
         <v>550</v>
       </c>
@@ -5056,7 +5053,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="137">
+    <row r="137" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B137" s="6" t="s">
         <v>552</v>
       </c>
@@ -5064,7 +5061,7 @@
         <v>553</v>
       </c>
     </row>
-    <row r="138">
+    <row r="138" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B138" s="6" t="s">
         <v>554</v>
       </c>
@@ -5072,7 +5069,7 @@
         <v>555</v>
       </c>
     </row>
-    <row r="139">
+    <row r="139" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B139" s="6" t="s">
         <v>556</v>
       </c>
@@ -5080,7 +5077,7 @@
         <v>557</v>
       </c>
     </row>
-    <row r="140">
+    <row r="140" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B140" s="6" t="s">
         <v>558</v>
       </c>
@@ -5088,7 +5085,7 @@
         <v>559</v>
       </c>
     </row>
-    <row r="141">
+    <row r="141" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B141" s="6" t="s">
         <v>560</v>
       </c>
@@ -5096,7 +5093,7 @@
         <v>561</v>
       </c>
     </row>
-    <row r="142">
+    <row r="142" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B142" s="6" t="s">
         <v>562</v>
       </c>
@@ -5104,7 +5101,7 @@
         <v>563</v>
       </c>
     </row>
-    <row r="143">
+    <row r="143" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B143" s="6" t="s">
         <v>564</v>
       </c>
@@ -5112,7 +5109,7 @@
         <v>565</v>
       </c>
     </row>
-    <row r="144">
+    <row r="144" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B144" s="6" t="s">
         <v>566</v>
       </c>
@@ -5120,7 +5117,7 @@
         <v>567</v>
       </c>
     </row>
-    <row r="145">
+    <row r="145" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B145" s="6" t="s">
         <v>568</v>
       </c>
@@ -5128,7 +5125,7 @@
         <v>569</v>
       </c>
     </row>
-    <row r="146">
+    <row r="146" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B146" s="6" t="s">
         <v>570</v>
       </c>
@@ -5136,7 +5133,7 @@
         <v>571</v>
       </c>
     </row>
-    <row r="147">
+    <row r="147" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B147" s="6" t="s">
         <v>572</v>
       </c>
@@ -5144,7 +5141,7 @@
         <v>573</v>
       </c>
     </row>
-    <row r="148">
+    <row r="148" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B148" s="6" t="s">
         <v>574</v>
       </c>
@@ -5152,7 +5149,7 @@
         <v>575</v>
       </c>
     </row>
-    <row r="149">
+    <row r="149" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B149" s="6" t="s">
         <v>576</v>
       </c>
@@ -5160,7 +5157,7 @@
         <v>577</v>
       </c>
     </row>
-    <row r="150">
+    <row r="150" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B150" s="6" t="s">
         <v>578</v>
       </c>
@@ -5168,7 +5165,7 @@
         <v>579</v>
       </c>
     </row>
-    <row r="151">
+    <row r="151" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B151" s="6" t="s">
         <v>580</v>
       </c>
@@ -5176,7 +5173,7 @@
         <v>581</v>
       </c>
     </row>
-    <row r="152">
+    <row r="152" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B152" s="6" t="s">
         <v>582</v>
       </c>
@@ -5184,7 +5181,7 @@
         <v>583</v>
       </c>
     </row>
-    <row r="153">
+    <row r="153" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B153" s="6" t="s">
         <v>584</v>
       </c>
@@ -5192,7 +5189,7 @@
         <v>585</v>
       </c>
     </row>
-    <row r="154">
+    <row r="154" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B154" s="6" t="s">
         <v>586</v>
       </c>
@@ -5200,7 +5197,7 @@
         <v>587</v>
       </c>
     </row>
-    <row r="155">
+    <row r="155" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B155" s="6" t="s">
         <v>588</v>
       </c>
@@ -5208,7 +5205,7 @@
         <v>589</v>
       </c>
     </row>
-    <row r="156">
+    <row r="156" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B156" s="6" t="s">
         <v>590</v>
       </c>
@@ -5216,7 +5213,7 @@
         <v>591</v>
       </c>
     </row>
-    <row r="157">
+    <row r="157" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B157" s="6" t="s">
         <v>592</v>
       </c>
@@ -5224,7 +5221,7 @@
         <v>593</v>
       </c>
     </row>
-    <row r="158">
+    <row r="158" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B158" s="6" t="s">
         <v>594</v>
       </c>
@@ -5232,7 +5229,7 @@
         <v>595</v>
       </c>
     </row>
-    <row r="159">
+    <row r="159" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B159" s="6" t="s">
         <v>596</v>
       </c>
@@ -5240,7 +5237,7 @@
         <v>597</v>
       </c>
     </row>
-    <row r="160">
+    <row r="160" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B160" s="6" t="s">
         <v>598</v>
       </c>
@@ -5248,7 +5245,7 @@
         <v>599</v>
       </c>
     </row>
-    <row r="161">
+    <row r="161" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B161" s="6" t="s">
         <v>600</v>
       </c>
@@ -5256,7 +5253,7 @@
         <v>601</v>
       </c>
     </row>
-    <row r="162">
+    <row r="162" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B162" s="6" t="s">
         <v>602</v>
       </c>
@@ -5264,7 +5261,7 @@
         <v>603</v>
       </c>
     </row>
-    <row r="163">
+    <row r="163" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B163" s="6" t="s">
         <v>604</v>
       </c>
@@ -5272,7 +5269,7 @@
         <v>605</v>
       </c>
     </row>
-    <row r="164">
+    <row r="164" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B164" s="6" t="s">
         <v>606</v>
       </c>
@@ -5280,7 +5277,7 @@
         <v>607</v>
       </c>
     </row>
-    <row r="165">
+    <row r="165" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B165" s="6" t="s">
         <v>608</v>
       </c>
@@ -5288,7 +5285,7 @@
         <v>609</v>
       </c>
     </row>
-    <row r="166">
+    <row r="166" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B166" s="6" t="s">
         <v>610</v>
       </c>
@@ -5296,7 +5293,7 @@
         <v>611</v>
       </c>
     </row>
-    <row r="167">
+    <row r="167" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B167" s="6" t="s">
         <v>612</v>
       </c>
@@ -5304,7 +5301,7 @@
         <v>613</v>
       </c>
     </row>
-    <row r="168">
+    <row r="168" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B168" s="6" t="s">
         <v>614</v>
       </c>
@@ -5312,7 +5309,7 @@
         <v>615</v>
       </c>
     </row>
-    <row r="169">
+    <row r="169" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B169" s="6" t="s">
         <v>616</v>
       </c>
@@ -5320,7 +5317,7 @@
         <v>617</v>
       </c>
     </row>
-    <row r="170">
+    <row r="170" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B170" s="6" t="s">
         <v>618</v>
       </c>
@@ -5328,7 +5325,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="171">
+    <row r="171" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B171" s="6" t="s">
         <v>620</v>
       </c>
@@ -5336,7 +5333,7 @@
         <v>621</v>
       </c>
     </row>
-    <row r="172">
+    <row r="172" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B172" s="6" t="s">
         <v>622</v>
       </c>
@@ -5344,7 +5341,7 @@
         <v>623</v>
       </c>
     </row>
-    <row r="173">
+    <row r="173" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B173" s="6" t="s">
         <v>624</v>
       </c>
@@ -5352,7 +5349,7 @@
         <v>625</v>
       </c>
     </row>
-    <row r="174">
+    <row r="174" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B174" s="6" t="s">
         <v>626</v>
       </c>
@@ -5360,7 +5357,7 @@
         <v>627</v>
       </c>
     </row>
-    <row r="175">
+    <row r="175" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B175" s="6" t="s">
         <v>251</v>
       </c>
@@ -5368,7 +5365,7 @@
         <v>628</v>
       </c>
     </row>
-    <row r="176">
+    <row r="176" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B176" s="6" t="s">
         <v>629</v>
       </c>
@@ -5376,7 +5373,7 @@
         <v>630</v>
       </c>
     </row>
-    <row r="177">
+    <row r="177" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B177" s="6" t="s">
         <v>631</v>
       </c>
@@ -5384,7 +5381,7 @@
         <v>632</v>
       </c>
     </row>
-    <row r="178">
+    <row r="178" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B178" s="6" t="s">
         <v>633</v>
       </c>
@@ -5392,7 +5389,7 @@
         <v>634</v>
       </c>
     </row>
-    <row r="179">
+    <row r="179" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B179" s="6" t="s">
         <v>635</v>
       </c>
@@ -5400,7 +5397,7 @@
         <v>636</v>
       </c>
     </row>
-    <row r="180">
+    <row r="180" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B180" s="6" t="s">
         <v>637</v>
       </c>
@@ -5408,7 +5405,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="181">
+    <row r="181" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B181" s="6" t="s">
         <v>639</v>
       </c>
@@ -5416,7 +5413,7 @@
         <v>640</v>
       </c>
     </row>
-    <row r="182">
+    <row r="182" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B182" s="6" t="s">
         <v>641</v>
       </c>
@@ -5424,7 +5421,7 @@
         <v>642</v>
       </c>
     </row>
-    <row r="183">
+    <row r="183" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B183" s="6" t="s">
         <v>643</v>
       </c>
@@ -5432,7 +5429,7 @@
         <v>644</v>
       </c>
     </row>
-    <row r="184">
+    <row r="184" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B184" s="6" t="s">
         <v>645</v>
       </c>
@@ -5440,7 +5437,7 @@
         <v>646</v>
       </c>
     </row>
-    <row r="185">
+    <row r="185" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B185" s="6" t="s">
         <v>647</v>
       </c>
@@ -5448,7 +5445,7 @@
         <v>648</v>
       </c>
     </row>
-    <row r="186">
+    <row r="186" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B186" s="6" t="s">
         <v>649</v>
       </c>
@@ -5456,7 +5453,7 @@
         <v>650</v>
       </c>
     </row>
-    <row r="187">
+    <row r="187" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B187" s="6" t="s">
         <v>651</v>
       </c>
@@ -5464,7 +5461,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="188">
+    <row r="188" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B188" s="6" t="s">
         <v>653</v>
       </c>
@@ -5472,7 +5469,7 @@
         <v>654</v>
       </c>
     </row>
-    <row r="189">
+    <row r="189" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B189" s="6" t="s">
         <v>655</v>
       </c>
@@ -5480,7 +5477,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="190">
+    <row r="190" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B190" s="6" t="s">
         <v>657</v>
       </c>
@@ -5488,7 +5485,7 @@
         <v>658</v>
       </c>
     </row>
-    <row r="191">
+    <row r="191" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B191" s="6" t="s">
         <v>659</v>
       </c>
@@ -5496,7 +5493,7 @@
         <v>660</v>
       </c>
     </row>
-    <row r="192">
+    <row r="192" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B192" s="6" t="s">
         <v>661</v>
       </c>
@@ -5504,7 +5501,7 @@
         <v>662</v>
       </c>
     </row>
-    <row r="193">
+    <row r="193" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B193" s="6" t="s">
         <v>663</v>
       </c>
@@ -5512,7 +5509,7 @@
         <v>664</v>
       </c>
     </row>
-    <row r="194">
+    <row r="194" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B194" s="6" t="s">
         <v>665</v>
       </c>
@@ -5520,7 +5517,7 @@
         <v>666</v>
       </c>
     </row>
-    <row r="195">
+    <row r="195" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B195" s="6" t="s">
         <v>667</v>
       </c>
@@ -5528,7 +5525,7 @@
         <v>668</v>
       </c>
     </row>
-    <row r="196">
+    <row r="196" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B196" s="6" t="s">
         <v>669</v>
       </c>
@@ -5536,7 +5533,7 @@
         <v>670</v>
       </c>
     </row>
-    <row r="197">
+    <row r="197" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B197" s="6" t="s">
         <v>671</v>
       </c>
@@ -5544,7 +5541,7 @@
         <v>672</v>
       </c>
     </row>
-    <row r="198">
+    <row r="198" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B198" s="6" t="s">
         <v>673</v>
       </c>
@@ -5552,7 +5549,7 @@
         <v>674</v>
       </c>
     </row>
-    <row r="199">
+    <row r="199" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B199" s="6" t="s">
         <v>675</v>
       </c>
@@ -5560,7 +5557,7 @@
         <v>676</v>
       </c>
     </row>
-    <row r="200">
+    <row r="200" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B200" s="6" t="s">
         <v>677</v>
       </c>
@@ -5568,7 +5565,7 @@
         <v>678</v>
       </c>
     </row>
-    <row r="201">
+    <row r="201" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B201" s="6" t="s">
         <v>679</v>
       </c>
@@ -5576,7 +5573,7 @@
         <v>680</v>
       </c>
     </row>
-    <row r="202">
+    <row r="202" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B202" s="6" t="s">
         <v>681</v>
       </c>
@@ -5584,7 +5581,7 @@
         <v>682</v>
       </c>
     </row>
-    <row r="203">
+    <row r="203" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B203" s="6" t="s">
         <v>683</v>
       </c>
@@ -5592,7 +5589,7 @@
         <v>646</v>
       </c>
     </row>
-    <row r="204">
+    <row r="204" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B204" s="6" t="s">
         <v>684</v>
       </c>
@@ -5600,7 +5597,7 @@
         <v>685</v>
       </c>
     </row>
-    <row r="205">
+    <row r="205" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B205" s="6" t="s">
         <v>686</v>
       </c>
@@ -5608,7 +5605,7 @@
         <v>687</v>
       </c>
     </row>
-    <row r="206">
+    <row r="206" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B206" s="6" t="s">
         <v>688</v>
       </c>
@@ -5616,7 +5613,7 @@
         <v>689</v>
       </c>
     </row>
-    <row r="207">
+    <row r="207" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B207" s="6" t="s">
         <v>690</v>
       </c>
@@ -5624,7 +5621,7 @@
         <v>691</v>
       </c>
     </row>
-    <row r="208">
+    <row r="208" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B208" s="6" t="s">
         <v>692</v>
       </c>
@@ -5632,7 +5629,7 @@
         <v>693</v>
       </c>
     </row>
-    <row r="209">
+    <row r="209" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B209" s="6" t="s">
         <v>694</v>
       </c>
@@ -5640,7 +5637,7 @@
         <v>695</v>
       </c>
     </row>
-    <row r="210">
+    <row r="210" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B210" s="6" t="s">
         <v>696</v>
       </c>
@@ -5648,7 +5645,7 @@
         <v>697</v>
       </c>
     </row>
-    <row r="211">
+    <row r="211" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B211" s="6" t="s">
         <v>698</v>
       </c>
@@ -5656,7 +5653,7 @@
         <v>699</v>
       </c>
     </row>
-    <row r="212">
+    <row r="212" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B212" s="6" t="s">
         <v>700</v>
       </c>
@@ -5667,7 +5664,6 @@
   </sheetData>
   <phoneticPr fontId="0" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
@@ -5676,7 +5672,7 @@
   <dimension ref="B1:C98"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B1" s="5" t="s">
         <v>0</v>
       </c>
@@ -5684,7 +5680,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B2" s="5" t="s">
         <v>2</v>
       </c>
@@ -5692,7 +5688,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B3" s="5" t="s">
         <v>4</v>
       </c>
@@ -5700,7 +5696,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B4" s="5" t="s">
         <v>6</v>
       </c>
@@ -5708,7 +5704,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B5" s="5" t="s">
         <v>8</v>
       </c>
@@ -5716,7 +5712,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B6" s="5" t="s">
         <v>10</v>
       </c>
@@ -5724,7 +5720,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B7" s="5" t="s">
         <v>12</v>
       </c>
@@ -5732,7 +5728,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B8" s="5" t="s">
         <v>14</v>
       </c>
@@ -5740,7 +5736,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="9">
+    <row r="9" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B9" s="5" t="s">
         <v>16</v>
       </c>
@@ -5748,7 +5744,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="10">
+    <row r="10" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B10" s="5" t="s">
         <v>18</v>
       </c>
@@ -5756,7 +5752,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="11">
+    <row r="11" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B11" s="5" t="s">
         <v>20</v>
       </c>
@@ -5764,7 +5760,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="12">
+    <row r="12" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B12" s="5" t="s">
         <v>22</v>
       </c>
@@ -5772,7 +5768,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="13">
+    <row r="13" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B13" s="5" t="s">
         <v>24</v>
       </c>
@@ -5780,7 +5776,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="14">
+    <row r="14" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B14" s="5" t="s">
         <v>26</v>
       </c>
@@ -5788,7 +5784,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="15">
+    <row r="15" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B15" s="5" t="s">
         <v>28</v>
       </c>
@@ -5796,7 +5792,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="16">
+    <row r="16" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B16" s="5" t="s">
         <v>30</v>
       </c>
@@ -5804,7 +5800,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="17">
+    <row r="17" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B17" s="5" t="s">
         <v>32</v>
       </c>
@@ -5812,7 +5808,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="18">
+    <row r="18" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B18" s="5" t="s">
         <v>34</v>
       </c>
@@ -5820,7 +5816,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="19">
+    <row r="19" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B19" s="5" t="s">
         <v>36</v>
       </c>
@@ -5828,7 +5824,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="20">
+    <row r="20" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B20" s="5" t="s">
         <v>38</v>
       </c>
@@ -5836,7 +5832,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="21">
+    <row r="21" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B21" s="5" t="s">
         <v>40</v>
       </c>
@@ -5844,7 +5840,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="22">
+    <row r="22" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B22" s="5" t="s">
         <v>42</v>
       </c>
@@ -5852,7 +5848,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="23">
+    <row r="23" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B23" s="5" t="s">
         <v>44</v>
       </c>
@@ -5860,7 +5856,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="24">
+    <row r="24" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B24" s="5" t="s">
         <v>46</v>
       </c>
@@ -5868,7 +5864,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="25">
+    <row r="25" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B25" s="5" t="s">
         <v>48</v>
       </c>
@@ -5876,7 +5872,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="26">
+    <row r="26" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B26" s="5" t="s">
         <v>50</v>
       </c>
@@ -5884,7 +5880,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="27">
+    <row r="27" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B27" s="5" t="s">
         <v>52</v>
       </c>
@@ -5892,7 +5888,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="28">
+    <row r="28" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B28" s="5" t="s">
         <v>54</v>
       </c>
@@ -5900,7 +5896,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="29">
+    <row r="29" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B29" s="5" t="s">
         <v>56</v>
       </c>
@@ -5908,7 +5904,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="30">
+    <row r="30" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B30" s="5" t="s">
         <v>58</v>
       </c>
@@ -5916,7 +5912,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="31">
+    <row r="31" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B31" s="5" t="s">
         <v>60</v>
       </c>
@@ -5924,7 +5920,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="32">
+    <row r="32" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B32" s="5" t="s">
         <v>62</v>
       </c>
@@ -5932,7 +5928,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="33">
+    <row r="33" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B33" s="5" t="s">
         <v>64</v>
       </c>
@@ -5940,7 +5936,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="34">
+    <row r="34" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B34" s="5" t="s">
         <v>66</v>
       </c>
@@ -5948,7 +5944,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="35">
+    <row r="35" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B35" s="5" t="s">
         <v>68</v>
       </c>
@@ -5956,7 +5952,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="36">
+    <row r="36" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B36" s="5" t="s">
         <v>70</v>
       </c>
@@ -5964,7 +5960,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="37">
+    <row r="37" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B37" s="5" t="s">
         <v>72</v>
       </c>
@@ -5972,7 +5968,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="38">
+    <row r="38" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B38" s="5" t="s">
         <v>74</v>
       </c>
@@ -5980,7 +5976,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="39">
+    <row r="39" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B39" s="5" t="s">
         <v>76</v>
       </c>
@@ -5988,7 +5984,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="40">
+    <row r="40" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B40" s="5" t="s">
         <v>78</v>
       </c>
@@ -5996,7 +5992,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="41">
+    <row r="41" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B41" s="5" t="s">
         <v>80</v>
       </c>
@@ -6004,7 +6000,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="42">
+    <row r="42" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B42" s="5" t="s">
         <v>82</v>
       </c>
@@ -6012,7 +6008,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="43">
+    <row r="43" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B43" s="5" t="s">
         <v>84</v>
       </c>
@@ -6020,7 +6016,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="44">
+    <row r="44" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B44" s="5" t="s">
         <v>86</v>
       </c>
@@ -6028,7 +6024,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="45">
+    <row r="45" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B45" s="5" t="s">
         <v>88</v>
       </c>
@@ -6036,7 +6032,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="46">
+    <row r="46" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B46" s="5" t="s">
         <v>90</v>
       </c>
@@ -6044,7 +6040,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="47">
+    <row r="47" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B47" s="5" t="s">
         <v>92</v>
       </c>
@@ -6052,7 +6048,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="48">
+    <row r="48" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B48" s="5" t="s">
         <v>94</v>
       </c>
@@ -6060,7 +6056,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="49">
+    <row r="49" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B49" s="5" t="s">
         <v>96</v>
       </c>
@@ -6068,7 +6064,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="50">
+    <row r="50" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B50" s="5" t="s">
         <v>98</v>
       </c>
@@ -6076,7 +6072,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="51">
+    <row r="51" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B51" s="5" t="s">
         <v>100</v>
       </c>
@@ -6084,7 +6080,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="52">
+    <row r="52" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B52" s="5" t="s">
         <v>102</v>
       </c>
@@ -6092,7 +6088,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="53">
+    <row r="53" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B53" s="5" t="s">
         <v>104</v>
       </c>
@@ -6100,7 +6096,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="54">
+    <row r="54" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B54" s="5" t="s">
         <v>106</v>
       </c>
@@ -6108,7 +6104,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="55">
+    <row r="55" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B55" s="5" t="s">
         <v>108</v>
       </c>
@@ -6116,7 +6112,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="56">
+    <row r="56" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B56" s="5" t="s">
         <v>110</v>
       </c>
@@ -6124,7 +6120,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="57">
+    <row r="57" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B57" s="5" t="s">
         <v>112</v>
       </c>
@@ -6132,7 +6128,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="58">
+    <row r="58" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B58" s="5" t="s">
         <v>114</v>
       </c>
@@ -6140,7 +6136,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="59">
+    <row r="59" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B59" s="5" t="s">
         <v>116</v>
       </c>
@@ -6148,7 +6144,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="60">
+    <row r="60" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B60" s="5" t="s">
         <v>118</v>
       </c>
@@ -6156,7 +6152,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="61">
+    <row r="61" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B61" s="5" t="s">
         <v>120</v>
       </c>
@@ -6164,7 +6160,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="62">
+    <row r="62" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B62" s="5" t="s">
         <v>122</v>
       </c>
@@ -6172,7 +6168,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="63">
+    <row r="63" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B63" s="5" t="s">
         <v>124</v>
       </c>
@@ -6180,7 +6176,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="64">
+    <row r="64" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B64" s="5" t="s">
         <v>126</v>
       </c>
@@ -6188,7 +6184,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="65">
+    <row r="65" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B65" s="5" t="s">
         <v>128</v>
       </c>
@@ -6196,7 +6192,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="66">
+    <row r="66" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B66" s="5" t="s">
         <v>130</v>
       </c>
@@ -6204,7 +6200,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="67">
+    <row r="67" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B67" s="5" t="s">
         <v>132</v>
       </c>
@@ -6212,7 +6208,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="68">
+    <row r="68" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B68" s="5" t="s">
         <v>134</v>
       </c>
@@ -6220,7 +6216,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="69">
+    <row r="69" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B69" s="5" t="s">
         <v>136</v>
       </c>
@@ -6228,7 +6224,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="70">
+    <row r="70" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B70" s="5" t="s">
         <v>138</v>
       </c>
@@ -6236,7 +6232,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="71">
+    <row r="71" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B71" s="5" t="s">
         <v>140</v>
       </c>
@@ -6244,7 +6240,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="72">
+    <row r="72" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B72" s="5" t="s">
         <v>142</v>
       </c>
@@ -6252,7 +6248,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="73">
+    <row r="73" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B73" s="5" t="s">
         <v>144</v>
       </c>
@@ -6260,7 +6256,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="74">
+    <row r="74" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B74" s="5" t="s">
         <v>146</v>
       </c>
@@ -6268,7 +6264,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="75">
+    <row r="75" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B75" s="5" t="s">
         <v>148</v>
       </c>
@@ -6276,7 +6272,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="76">
+    <row r="76" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B76" s="5" t="s">
         <v>150</v>
       </c>
@@ -6284,7 +6280,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="77">
+    <row r="77" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B77" s="5" t="s">
         <v>152</v>
       </c>
@@ -6292,7 +6288,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="78">
+    <row r="78" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B78" s="5" t="s">
         <v>154</v>
       </c>
@@ -6300,7 +6296,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="79">
+    <row r="79" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B79" s="5" t="s">
         <v>156</v>
       </c>
@@ -6308,7 +6304,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="80">
+    <row r="80" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B80" s="5" t="s">
         <v>158</v>
       </c>
@@ -6316,7 +6312,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="81">
+    <row r="81" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B81" s="5" t="s">
         <v>160</v>
       </c>
@@ -6324,7 +6320,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="82">
+    <row r="82" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B82" s="5" t="s">
         <v>162</v>
       </c>
@@ -6332,7 +6328,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="83">
+    <row r="83" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B83" s="5" t="s">
         <v>164</v>
       </c>
@@ -6340,7 +6336,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="84">
+    <row r="84" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B84" s="5" t="s">
         <v>166</v>
       </c>
@@ -6348,7 +6344,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="85">
+    <row r="85" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B85" s="5" t="s">
         <v>168</v>
       </c>
@@ -6356,7 +6352,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="86">
+    <row r="86" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B86" s="5" t="s">
         <v>170</v>
       </c>
@@ -6364,7 +6360,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="87">
+    <row r="87" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B87" s="5" t="s">
         <v>172</v>
       </c>
@@ -6372,7 +6368,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="88">
+    <row r="88" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B88" s="5" t="s">
         <v>174</v>
       </c>
@@ -6380,7 +6376,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="89">
+    <row r="89" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B89" s="5" t="s">
         <v>176</v>
       </c>
@@ -6388,7 +6384,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="90">
+    <row r="90" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B90" s="5" t="s">
         <v>178</v>
       </c>
@@ -6396,7 +6392,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="91">
+    <row r="91" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B91" s="5" t="s">
         <v>180</v>
       </c>
@@ -6404,7 +6400,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="92">
+    <row r="92" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B92" s="5" t="s">
         <v>182</v>
       </c>
@@ -6412,7 +6408,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="93">
+    <row r="93" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B93" s="5" t="s">
         <v>184</v>
       </c>
@@ -6420,7 +6416,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="94">
+    <row r="94" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B94" s="5" t="s">
         <v>186</v>
       </c>
@@ -6428,7 +6424,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="95">
+    <row r="95" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B95" s="5" t="s">
         <v>188</v>
       </c>
@@ -6436,7 +6432,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="96">
+    <row r="96" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B96" s="5" t="s">
         <v>190</v>
       </c>
@@ -6444,7 +6440,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="97">
+    <row r="97" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B97" s="5" t="s">
         <v>192</v>
       </c>
@@ -6452,7 +6448,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="98">
+    <row r="98" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B98" s="5" t="s">
         <v>194</v>
       </c>
@@ -6463,7 +6459,6 @@
   </sheetData>
   <phoneticPr fontId="0" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
@@ -6472,7 +6467,7 @@
   <dimension ref="B1:C68"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
@@ -6480,7 +6475,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B2" s="1" t="s">
         <v>2</v>
       </c>
@@ -6488,7 +6483,7 @@
         <v>734</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B3" s="1" t="s">
         <v>293</v>
       </c>
@@ -6496,7 +6491,7 @@
         <v>735</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B4" s="1" t="s">
         <v>295</v>
       </c>
@@ -6504,7 +6499,7 @@
         <v>736</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B5" s="1" t="s">
         <v>297</v>
       </c>
@@ -6512,7 +6507,7 @@
         <v>737</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B6" s="1" t="s">
         <v>299</v>
       </c>
@@ -6520,7 +6515,7 @@
         <v>738</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B7" s="1" t="s">
         <v>301</v>
       </c>
@@ -6528,7 +6523,7 @@
         <v>736</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B8" s="1" t="s">
         <v>303</v>
       </c>
@@ -6536,7 +6531,7 @@
         <v>739</v>
       </c>
     </row>
-    <row r="9">
+    <row r="9" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B9" s="1" t="s">
         <v>305</v>
       </c>
@@ -6544,7 +6539,7 @@
         <v>740</v>
       </c>
     </row>
-    <row r="10">
+    <row r="10" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B10" s="1" t="s">
         <v>24</v>
       </c>
@@ -6552,7 +6547,7 @@
         <v>741</v>
       </c>
     </row>
-    <row r="11">
+    <row r="11" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B11" s="1" t="s">
         <v>32</v>
       </c>
@@ -6560,7 +6555,7 @@
         <v>742</v>
       </c>
     </row>
-    <row r="12">
+    <row r="12" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B12" s="1" t="s">
         <v>40</v>
       </c>
@@ -6568,7 +6563,7 @@
         <v>743</v>
       </c>
     </row>
-    <row r="13">
+    <row r="13" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B13" s="1" t="s">
         <v>42</v>
       </c>
@@ -6576,7 +6571,7 @@
         <v>744</v>
       </c>
     </row>
-    <row r="14">
+    <row r="14" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B14" s="1" t="s">
         <v>44</v>
       </c>
@@ -6584,7 +6579,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="15">
+    <row r="15" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B15" s="1" t="s">
         <v>746</v>
       </c>
@@ -6592,7 +6587,7 @@
         <v>747</v>
       </c>
     </row>
-    <row r="16">
+    <row r="16" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B16" s="1" t="s">
         <v>748</v>
       </c>
@@ -6600,7 +6595,7 @@
         <v>749</v>
       </c>
     </row>
-    <row r="17">
+    <row r="17" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B17" s="1" t="s">
         <v>48</v>
       </c>
@@ -6608,7 +6603,7 @@
         <v>750</v>
       </c>
     </row>
-    <row r="18">
+    <row r="18" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B18" s="1" t="s">
         <v>751</v>
       </c>
@@ -6616,7 +6611,7 @@
         <v>752</v>
       </c>
     </row>
-    <row r="19">
+    <row r="19" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B19" s="1" t="s">
         <v>50</v>
       </c>
@@ -6624,7 +6619,7 @@
         <v>753</v>
       </c>
     </row>
-    <row r="20">
+    <row r="20" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B20" s="1" t="s">
         <v>52</v>
       </c>
@@ -6632,7 +6627,7 @@
         <v>754</v>
       </c>
     </row>
-    <row r="21">
+    <row r="21" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B21" s="1" t="s">
         <v>54</v>
       </c>
@@ -6640,7 +6635,7 @@
         <v>754</v>
       </c>
     </row>
-    <row r="22">
+    <row r="22" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B22" s="1" t="s">
         <v>56</v>
       </c>
@@ -6648,7 +6643,7 @@
         <v>754</v>
       </c>
     </row>
-    <row r="23">
+    <row r="23" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B23" s="1" t="s">
         <v>58</v>
       </c>
@@ -6656,7 +6651,7 @@
         <v>754</v>
       </c>
     </row>
-    <row r="24">
+    <row r="24" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B24" s="1" t="s">
         <v>60</v>
       </c>
@@ -6664,7 +6659,7 @@
         <v>754</v>
       </c>
     </row>
-    <row r="25">
+    <row r="25" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B25" s="1" t="s">
         <v>62</v>
       </c>
@@ -6672,7 +6667,7 @@
         <v>755</v>
       </c>
     </row>
-    <row r="26">
+    <row r="26" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B26" s="1" t="s">
         <v>64</v>
       </c>
@@ -6680,7 +6675,7 @@
         <v>756</v>
       </c>
     </row>
-    <row r="27">
+    <row r="27" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B27" s="1" t="s">
         <v>757</v>
       </c>
@@ -6688,7 +6683,7 @@
         <v>758</v>
       </c>
     </row>
-    <row r="28">
+    <row r="28" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B28" s="1" t="s">
         <v>759</v>
       </c>
@@ -6696,7 +6691,7 @@
         <v>760</v>
       </c>
     </row>
-    <row r="29">
+    <row r="29" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B29" s="1" t="s">
         <v>761</v>
       </c>
@@ -6704,7 +6699,7 @@
         <v>762</v>
       </c>
     </row>
-    <row r="30">
+    <row r="30" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B30" s="1" t="s">
         <v>763</v>
       </c>
@@ -6712,7 +6707,7 @@
         <v>764</v>
       </c>
     </row>
-    <row r="31">
+    <row r="31" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B31" s="1" t="s">
         <v>70</v>
       </c>
@@ -6720,7 +6715,7 @@
         <v>765</v>
       </c>
     </row>
-    <row r="32">
+    <row r="32" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B32" s="1" t="s">
         <v>92</v>
       </c>
@@ -6728,7 +6723,7 @@
         <v>766</v>
       </c>
     </row>
-    <row r="33">
+    <row r="33" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B33" s="1" t="s">
         <v>767</v>
       </c>
@@ -6736,7 +6731,7 @@
         <v>768</v>
       </c>
     </row>
-    <row r="34">
+    <row r="34" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B34" s="1" t="s">
         <v>769</v>
       </c>
@@ -6744,7 +6739,7 @@
         <v>770</v>
       </c>
     </row>
-    <row r="35">
+    <row r="35" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B35" s="1" t="s">
         <v>76</v>
       </c>
@@ -6752,7 +6747,7 @@
         <v>771</v>
       </c>
     </row>
-    <row r="36">
+    <row r="36" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B36" s="1" t="s">
         <v>78</v>
       </c>
@@ -6760,7 +6755,7 @@
         <v>772</v>
       </c>
     </row>
-    <row r="37">
+    <row r="37" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B37" s="1" t="s">
         <v>80</v>
       </c>
@@ -6768,7 +6763,7 @@
         <v>773</v>
       </c>
     </row>
-    <row r="38">
+    <row r="38" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B38" s="1" t="s">
         <v>82</v>
       </c>
@@ -6776,7 +6771,7 @@
         <v>774</v>
       </c>
     </row>
-    <row r="39">
+    <row r="39" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B39" s="1" t="s">
         <v>201</v>
       </c>
@@ -6784,7 +6779,7 @@
         <v>775</v>
       </c>
     </row>
-    <row r="40">
+    <row r="40" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B40" s="1" t="s">
         <v>84</v>
       </c>
@@ -6792,7 +6787,7 @@
         <v>776</v>
       </c>
     </row>
-    <row r="41">
+    <row r="41" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B41" s="1" t="s">
         <v>86</v>
       </c>
@@ -6800,7 +6795,7 @@
         <v>777</v>
       </c>
     </row>
-    <row r="42">
+    <row r="42" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B42" s="1" t="s">
         <v>88</v>
       </c>
@@ -6808,7 +6803,7 @@
         <v>778</v>
       </c>
     </row>
-    <row r="43">
+    <row r="43" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B43" s="1" t="s">
         <v>90</v>
       </c>
@@ -6816,7 +6811,7 @@
         <v>779</v>
       </c>
     </row>
-    <row r="44">
+    <row r="44" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B44" s="1" t="s">
         <v>114</v>
       </c>
@@ -6824,7 +6819,7 @@
         <v>780</v>
       </c>
     </row>
-    <row r="45">
+    <row r="45" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B45" s="1" t="s">
         <v>94</v>
       </c>
@@ -6832,7 +6827,7 @@
         <v>781</v>
       </c>
     </row>
-    <row r="46">
+    <row r="46" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B46" s="1" t="s">
         <v>96</v>
       </c>
@@ -6840,7 +6835,7 @@
         <v>782</v>
       </c>
     </row>
-    <row r="47">
+    <row r="47" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B47" s="1" t="s">
         <v>98</v>
       </c>
@@ -6848,7 +6843,7 @@
         <v>783</v>
       </c>
     </row>
-    <row r="48">
+    <row r="48" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B48" s="1" t="s">
         <v>100</v>
       </c>
@@ -6856,7 +6851,7 @@
         <v>784</v>
       </c>
     </row>
-    <row r="49">
+    <row r="49" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B49" s="1" t="s">
         <v>102</v>
       </c>
@@ -6864,7 +6859,7 @@
         <v>785</v>
       </c>
     </row>
-    <row r="50">
+    <row r="50" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B50" s="1" t="s">
         <v>104</v>
       </c>
@@ -6872,7 +6867,7 @@
         <v>786</v>
       </c>
     </row>
-    <row r="51">
+    <row r="51" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B51" s="1" t="s">
         <v>106</v>
       </c>
@@ -6880,7 +6875,7 @@
         <v>787</v>
       </c>
     </row>
-    <row r="52">
+    <row r="52" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B52" s="1" t="s">
         <v>108</v>
       </c>
@@ -6888,7 +6883,7 @@
         <v>788</v>
       </c>
     </row>
-    <row r="53">
+    <row r="53" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B53" s="1" t="s">
         <v>110</v>
       </c>
@@ -6896,7 +6891,7 @@
         <v>789</v>
       </c>
     </row>
-    <row r="54">
+    <row r="54" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B54" s="1" t="s">
         <v>112</v>
       </c>
@@ -6904,7 +6899,7 @@
         <v>765</v>
       </c>
     </row>
-    <row r="55">
+    <row r="55" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B55" s="1" t="s">
         <v>116</v>
       </c>
@@ -6912,7 +6907,7 @@
         <v>790</v>
       </c>
     </row>
-    <row r="56">
+    <row r="56" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B56" s="1" t="s">
         <v>118</v>
       </c>
@@ -6920,7 +6915,7 @@
         <v>791</v>
       </c>
     </row>
-    <row r="57">
+    <row r="57" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B57" s="1" t="s">
         <v>120</v>
       </c>
@@ -6928,7 +6923,7 @@
         <v>792</v>
       </c>
     </row>
-    <row r="58">
+    <row r="58" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B58" s="1" t="s">
         <v>793</v>
       </c>
@@ -6936,7 +6931,7 @@
         <v>794</v>
       </c>
     </row>
-    <row r="59">
+    <row r="59" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B59" s="1" t="s">
         <v>795</v>
       </c>
@@ -6944,7 +6939,7 @@
         <v>796</v>
       </c>
     </row>
-    <row r="60">
+    <row r="60" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B60" s="1" t="s">
         <v>797</v>
       </c>
@@ -6952,7 +6947,7 @@
         <v>798</v>
       </c>
     </row>
-    <row r="61">
+    <row r="61" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B61" s="1" t="s">
         <v>647</v>
       </c>
@@ -6960,7 +6955,7 @@
         <v>799</v>
       </c>
     </row>
-    <row r="62">
+    <row r="62" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B62" s="1" t="s">
         <v>649</v>
       </c>
@@ -6968,7 +6963,7 @@
         <v>800</v>
       </c>
     </row>
-    <row r="63">
+    <row r="63" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B63" s="1" t="s">
         <v>651</v>
       </c>
@@ -6976,7 +6971,7 @@
         <v>801</v>
       </c>
     </row>
-    <row r="64">
+    <row r="64" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B64" s="1" t="s">
         <v>653</v>
       </c>
@@ -6984,7 +6979,7 @@
         <v>802</v>
       </c>
     </row>
-    <row r="65">
+    <row r="65" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B65" s="1" t="s">
         <v>655</v>
       </c>
@@ -6992,7 +6987,7 @@
         <v>803</v>
       </c>
     </row>
-    <row r="66">
+    <row r="66" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B66" s="1" t="s">
         <v>804</v>
       </c>
@@ -7000,7 +6995,7 @@
         <v>805</v>
       </c>
     </row>
-    <row r="67">
+    <row r="67" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B67" s="1" t="s">
         <v>806</v>
       </c>
@@ -7008,7 +7003,7 @@
         <v>807</v>
       </c>
     </row>
-    <row r="68">
+    <row r="68" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B68" s="1" t="s">
         <v>808</v>
       </c>
@@ -7019,7 +7014,6 @@
   </sheetData>
   <phoneticPr fontId="0" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
@@ -7028,7 +7022,7 @@
   <dimension ref="B1:C31"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B1" s="4" t="s">
         <v>0</v>
       </c>
@@ -7036,7 +7030,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B2" s="4" t="s">
         <v>810</v>
       </c>
@@ -7044,7 +7038,7 @@
         <v>811</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B3" s="4" t="s">
         <v>22</v>
       </c>
@@ -7052,7 +7046,7 @@
         <v>812</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B4" s="4" t="s">
         <v>813</v>
       </c>
@@ -7060,7 +7054,7 @@
         <v>735</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B5" s="4" t="s">
         <v>814</v>
       </c>
@@ -7068,7 +7062,7 @@
         <v>774</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B6" s="4" t="s">
         <v>6</v>
       </c>
@@ -7076,7 +7070,7 @@
         <v>815</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B7" s="4" t="s">
         <v>8</v>
       </c>
@@ -7084,7 +7078,7 @@
         <v>816</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B8" s="4" t="s">
         <v>10</v>
       </c>
@@ -7092,7 +7086,7 @@
         <v>817</v>
       </c>
     </row>
-    <row r="9">
+    <row r="9" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B9" s="4" t="s">
         <v>12</v>
       </c>
@@ -7100,7 +7094,7 @@
         <v>818</v>
       </c>
     </row>
-    <row r="10">
+    <row r="10" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B10" s="4" t="s">
         <v>14</v>
       </c>
@@ -7108,7 +7102,7 @@
         <v>819</v>
       </c>
     </row>
-    <row r="11">
+    <row r="11" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B11" s="4" t="s">
         <v>16</v>
       </c>
@@ -7116,7 +7110,7 @@
         <v>820</v>
       </c>
     </row>
-    <row r="12">
+    <row r="12" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B12" s="4" t="s">
         <v>18</v>
       </c>
@@ -7124,7 +7118,7 @@
         <v>821</v>
       </c>
     </row>
-    <row r="13">
+    <row r="13" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B13" s="4" t="s">
         <v>20</v>
       </c>
@@ -7132,7 +7126,7 @@
         <v>822</v>
       </c>
     </row>
-    <row r="14">
+    <row r="14" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B14" s="4" t="s">
         <v>46</v>
       </c>
@@ -7140,7 +7134,7 @@
         <v>823</v>
       </c>
     </row>
-    <row r="15">
+    <row r="15" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B15" s="4" t="s">
         <v>30</v>
       </c>
@@ -7148,7 +7142,7 @@
         <v>737</v>
       </c>
     </row>
-    <row r="16">
+    <row r="16" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B16" s="4" t="s">
         <v>32</v>
       </c>
@@ -7156,7 +7150,7 @@
         <v>736</v>
       </c>
     </row>
-    <row r="17">
+    <row r="17" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B17" s="4" t="s">
         <v>40</v>
       </c>
@@ -7164,7 +7158,7 @@
         <v>738</v>
       </c>
     </row>
-    <row r="18">
+    <row r="18" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B18" s="4" t="s">
         <v>42</v>
       </c>
@@ -7172,7 +7166,7 @@
         <v>824</v>
       </c>
     </row>
-    <row r="19">
+    <row r="19" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B19" s="4" t="s">
         <v>44</v>
       </c>
@@ -7180,7 +7174,7 @@
         <v>812</v>
       </c>
     </row>
-    <row r="20">
+    <row r="20" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B20" s="4" t="s">
         <v>825</v>
       </c>
@@ -7188,7 +7182,7 @@
         <v>826</v>
       </c>
     </row>
-    <row r="21">
+    <row r="21" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B21" s="4" t="s">
         <v>66</v>
       </c>
@@ -7196,7 +7190,7 @@
         <v>827</v>
       </c>
     </row>
-    <row r="22">
+    <row r="22" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B22" s="4" t="s">
         <v>68</v>
       </c>
@@ -7204,7 +7198,7 @@
         <v>828</v>
       </c>
     </row>
-    <row r="23">
+    <row r="23" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B23" s="4" t="s">
         <v>72</v>
       </c>
@@ -7212,7 +7206,7 @@
         <v>829</v>
       </c>
     </row>
-    <row r="24">
+    <row r="24" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B24" s="4" t="s">
         <v>830</v>
       </c>
@@ -7220,7 +7214,7 @@
         <v>831</v>
       </c>
     </row>
-    <row r="25">
+    <row r="25" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B25" s="4" t="s">
         <v>92</v>
       </c>
@@ -7228,7 +7222,7 @@
         <v>766</v>
       </c>
     </row>
-    <row r="26">
+    <row r="26" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B26" s="4" t="s">
         <v>114</v>
       </c>
@@ -7236,7 +7230,7 @@
         <v>780</v>
       </c>
     </row>
-    <row r="27">
+    <row r="27" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B27" s="4" t="s">
         <v>832</v>
       </c>
@@ -7244,7 +7238,7 @@
         <v>752</v>
       </c>
     </row>
-    <row r="28">
+    <row r="28" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B28" s="4" t="s">
         <v>833</v>
       </c>
@@ -7252,7 +7246,7 @@
         <v>834</v>
       </c>
     </row>
-    <row r="29">
+    <row r="29" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B29" s="4" t="s">
         <v>835</v>
       </c>
@@ -7260,7 +7254,7 @@
         <v>771</v>
       </c>
     </row>
-    <row r="30">
+    <row r="30" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B30" s="4" t="s">
         <v>836</v>
       </c>
@@ -7268,7 +7262,7 @@
         <v>837</v>
       </c>
     </row>
-    <row r="31">
+    <row r="31" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B31" s="4" t="s">
         <v>838</v>
       </c>
@@ -7279,7 +7273,6 @@
   </sheetData>
   <phoneticPr fontId="0" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
@@ -7288,7 +7281,7 @@
   <dimension ref="B1:C13"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B1" s="2" t="s">
         <v>0</v>
       </c>
@@ -7296,7 +7289,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B2" s="2" t="s">
         <v>22</v>
       </c>
@@ -7304,7 +7297,7 @@
         <v>840</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B3" s="2" t="s">
         <v>813</v>
       </c>
@@ -7312,7 +7305,7 @@
         <v>841</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B4" s="2" t="s">
         <v>814</v>
       </c>
@@ -7320,7 +7313,7 @@
         <v>829</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B5" s="2" t="s">
         <v>6</v>
       </c>
@@ -7328,7 +7321,7 @@
         <v>812</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B6" s="2" t="s">
         <v>46</v>
       </c>
@@ -7336,7 +7329,7 @@
         <v>752</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B7" s="2" t="s">
         <v>825</v>
       </c>
@@ -7344,7 +7337,7 @@
         <v>287</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B8" s="2" t="s">
         <v>830</v>
       </c>
@@ -7352,7 +7345,7 @@
         <v>842</v>
       </c>
     </row>
-    <row r="9">
+    <row r="9" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B9" s="2" t="s">
         <v>832</v>
       </c>
@@ -7360,7 +7353,7 @@
         <v>843</v>
       </c>
     </row>
-    <row r="10">
+    <row r="10" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B10" s="2" t="s">
         <v>833</v>
       </c>
@@ -7368,7 +7361,7 @@
         <v>844</v>
       </c>
     </row>
-    <row r="11">
+    <row r="11" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B11" s="2" t="s">
         <v>835</v>
       </c>
@@ -7376,7 +7369,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="12">
+    <row r="12" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B12" s="2" t="s">
         <v>836</v>
       </c>
@@ -7384,7 +7377,7 @@
         <v>846</v>
       </c>
     </row>
-    <row r="13">
+    <row r="13" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B13" s="2" t="s">
         <v>838</v>
       </c>
@@ -7393,8 +7386,7 @@
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="3" type="noConversion"/>
+  <phoneticPr fontId="0" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <headerFooter/>
 </worksheet>
 </file>
--- a/Assets/Editor/DataDic/Data.xlsx
+++ b/Assets/Editor/DataDic/Data.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="17385" windowHeight="7860" firstSheet="2" activeTab="2"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="17385" windowHeight="7860" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="FishData" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1041" uniqueCount="848">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1183" uniqueCount="976">
   <si>
     <t>Key</t>
   </si>
@@ -45,6 +45,54 @@
     <t>101购买玩家柜台商品 (GameActionData)</t>
   </si>
   <si>
+    <t>102</t>
+  </si>
+  <si>
+    <t>102播放种植指引 (GameActionData)</t>
+  </si>
+  <si>
+    <t>103</t>
+  </si>
+  <si>
+    <t>103播放探索指引 (GameActionData)</t>
+  </si>
+  <si>
+    <t>10</t>
+  </si>
+  <si>
+    <t>10隐藏主角 (GameActionData)</t>
+  </si>
+  <si>
+    <t>110</t>
+  </si>
+  <si>
+    <t>110收割 (GameActionData)</t>
+  </si>
+  <si>
+    <t>111</t>
+  </si>
+  <si>
+    <t>111铲除 (GameActionData)</t>
+  </si>
+  <si>
+    <t>112</t>
+  </si>
+  <si>
+    <t>112开放配方 (GameActionData)</t>
+  </si>
+  <si>
+    <t>114</t>
+  </si>
+  <si>
+    <t>114简易获取动物 (GameActionData)</t>
+  </si>
+  <si>
+    <t>11</t>
+  </si>
+  <si>
+    <t>11显示主角 (GameActionData)</t>
+  </si>
+  <si>
     <t>12</t>
   </si>
   <si>
@@ -63,10 +111,10 @@
     <t>14刷新初始角色与怪物 (GameActionData)</t>
   </si>
   <si>
-    <t>15</t>
-  </si>
-  <si>
-    <t>15打开背包选择物体放在柜台上 (GameActionData)</t>
+    <t>160</t>
+  </si>
+  <si>
+    <t>160设置指引保存数据 (GameActionData)</t>
   </si>
   <si>
     <t>16</t>
@@ -117,6 +165,18 @@
     <t>202恢复碰撞 (GameActionData)</t>
   </si>
   <si>
+    <t>203</t>
+  </si>
+  <si>
+    <t>203是否渔夫 (GameActionData)</t>
+  </si>
+  <si>
+    <t>204</t>
+  </si>
+  <si>
+    <t>204是否渔夫1 (GameActionData)</t>
+  </si>
+  <si>
     <t>20</t>
   </si>
   <si>
@@ -147,6 +207,12 @@
     <t>222创建制革机 (GameActionData)</t>
   </si>
   <si>
+    <t>223</t>
+  </si>
+  <si>
+    <t>223改变内门动画 (GameActionData)</t>
+  </si>
+  <si>
     <t>22</t>
   </si>
   <si>
@@ -165,6 +231,36 @@
     <t>24新手战斗结束恢复电影 (GameActionData)</t>
   </si>
   <si>
+    <t>26</t>
+  </si>
+  <si>
+    <t>25设置角色临时位置 (GameActionData)</t>
+  </si>
+  <si>
+    <t>25</t>
+  </si>
+  <si>
+    <t>26移除角色临时位置 (GameActionData)</t>
+  </si>
+  <si>
+    <t>27</t>
+  </si>
+  <si>
+    <t>27隐藏UI (GameActionData)</t>
+  </si>
+  <si>
+    <t>28</t>
+  </si>
+  <si>
+    <t>28等待4s加载开始 (GameActionData)</t>
+  </si>
+  <si>
+    <t>29</t>
+  </si>
+  <si>
+    <t>29播放初始小镇 (GameActionData)</t>
+  </si>
+  <si>
     <t>2</t>
   </si>
   <si>
@@ -231,6 +327,48 @@
     <t>30播放初始进入小镇 (GameActionData)</t>
   </si>
   <si>
+    <t>311</t>
+  </si>
+  <si>
+    <t>311打开天气界面 (GameActionData)</t>
+  </si>
+  <si>
+    <t>312</t>
+  </si>
+  <si>
+    <t>312检查指引是否完成 (GameActionData)</t>
+  </si>
+  <si>
+    <t>313</t>
+  </si>
+  <si>
+    <t>313打开酒馆 (GameActionData)</t>
+  </si>
+  <si>
+    <t>314</t>
+  </si>
+  <si>
+    <t>314打开装备店 (GameActionData)</t>
+  </si>
+  <si>
+    <t>315</t>
+  </si>
+  <si>
+    <t>315打开服装店 (GameActionData)</t>
+  </si>
+  <si>
+    <t>316</t>
+  </si>
+  <si>
+    <t>316打开渔具店 (GameActionData)</t>
+  </si>
+  <si>
+    <t>317</t>
+  </si>
+  <si>
+    <t>317打开魔法商店 (GameActionData)</t>
+  </si>
+  <si>
     <t>31</t>
   </si>
   <si>
@@ -255,6 +393,48 @@
     <t>33第一晚继续 (GameActionData)</t>
   </si>
   <si>
+    <t>34</t>
+  </si>
+  <si>
+    <t>34新手进入商店 (GameActionData)</t>
+  </si>
+  <si>
+    <t>35</t>
+  </si>
+  <si>
+    <t>35第一天早上 (GameActionData)</t>
+  </si>
+  <si>
+    <t>36</t>
+  </si>
+  <si>
+    <t>36显示柜台交互 (GameActionData)</t>
+  </si>
+  <si>
+    <t>38</t>
+  </si>
+  <si>
+    <t>38新手引导测试 (GameActionData)</t>
+  </si>
+  <si>
+    <t>39</t>
+  </si>
+  <si>
+    <t>39引导结束继续电影 (GameActionData)</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>3显示角色信息UI (GameActionData)</t>
+  </si>
+  <si>
+    <t>400</t>
+  </si>
+  <si>
+    <t>400播种动画 (GameActionData)</t>
+  </si>
+  <si>
     <t>401</t>
   </si>
   <si>
@@ -456,7 +636,7 @@
     <t>432</t>
   </si>
   <si>
-    <t>432关闭界面 (GameActionData)</t>
+    <t>432关闭对话界面 (GameActionData)</t>
   </si>
   <si>
     <t>433</t>
@@ -495,12 +675,24 @@
     <t>438收鱼竿动画 (GameActionData)</t>
   </si>
   <si>
+    <t>439</t>
+  </si>
+  <si>
+    <t>439收割动画 (GameActionData)</t>
+  </si>
+  <si>
     <t>43</t>
   </si>
   <si>
     <t>43回收渔具 (GameActionData)</t>
   </si>
   <si>
+    <t>440</t>
+  </si>
+  <si>
+    <t>440展示随机表情 (GameActionData)</t>
+  </si>
+  <si>
     <t>44</t>
   </si>
   <si>
@@ -531,6 +723,12 @@
     <t>48收获鱼 (GameActionData)</t>
   </si>
   <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>4普通对话 (GameActionData)</t>
+  </si>
+  <si>
     <t>50</t>
   </si>
   <si>
@@ -549,6 +747,96 @@
     <t>52升级牧场 (GameActionData)</t>
   </si>
   <si>
+    <t>53</t>
+  </si>
+  <si>
+    <t>53初始进入城门 (GameActionData)</t>
+  </si>
+  <si>
+    <t>54</t>
+  </si>
+  <si>
+    <t>54初始进入城门Action (GameActionData)</t>
+  </si>
+  <si>
+    <t>60</t>
+  </si>
+  <si>
+    <t>60Npc链接商店 (GameActionData)</t>
+  </si>
+  <si>
+    <t>61</t>
+  </si>
+  <si>
+    <t>61Npc是否在队伍 (GameActionData)</t>
+  </si>
+  <si>
+    <t>70</t>
+  </si>
+  <si>
+    <t>70商店指引结束对话 (GameActionData)</t>
+  </si>
+  <si>
+    <t>71</t>
+  </si>
+  <si>
+    <t>71柜台指引结束对话 (GameActionData)</t>
+  </si>
+  <si>
+    <t>72</t>
+  </si>
+  <si>
+    <t>72播放植物店引导电影 (GameActionData)</t>
+  </si>
+  <si>
+    <t>73</t>
+  </si>
+  <si>
+    <t>73离家触发事件 (GameActionData)</t>
+  </si>
+  <si>
+    <t>74</t>
+  </si>
+  <si>
+    <t>74继续播放住宅区电影 (GameActionData)</t>
+  </si>
+  <si>
+    <t>75</t>
+  </si>
+  <si>
+    <t>75开始购买指引 (GameActionData)</t>
+  </si>
+  <si>
+    <t>76</t>
+  </si>
+  <si>
+    <t>76继续电影 (GameActionData)</t>
+  </si>
+  <si>
+    <t>77</t>
+  </si>
+  <si>
+    <t>77获得锄头 (GameActionData)</t>
+  </si>
+  <si>
+    <t>78</t>
+  </si>
+  <si>
+    <t>78获得水壶 (GameActionData)</t>
+  </si>
+  <si>
+    <t>79</t>
+  </si>
+  <si>
+    <t>79种植引导1 (GameActionData)</t>
+  </si>
+  <si>
+    <t>7</t>
+  </si>
+  <si>
+    <t>7显示电影UI (GameActionData)</t>
+  </si>
+  <si>
     <t>800</t>
   </si>
   <si>
@@ -609,10 +897,148 @@
     <t>809解散团体 (GameActionData)</t>
   </si>
   <si>
+    <t>80</t>
+  </si>
+  <si>
+    <t>80设置快捷栏后继续对话 (GameActionData)</t>
+  </si>
+  <si>
     <t>810</t>
   </si>
   <si>
     <t>810加入团体 (GameActionData)</t>
+  </si>
+  <si>
+    <t>81</t>
+  </si>
+  <si>
+    <t>81对话 (GameActionData)</t>
+  </si>
+  <si>
+    <t>82</t>
+  </si>
+  <si>
+    <t>82播种指引 (GameActionData)</t>
+  </si>
+  <si>
+    <t>83</t>
+  </si>
+  <si>
+    <t>83对话 (GameActionData)</t>
+  </si>
+  <si>
+    <t>84</t>
+  </si>
+  <si>
+    <t>84浇水完毕 (GameActionData)</t>
+  </si>
+  <si>
+    <t>85</t>
+  </si>
+  <si>
+    <t>85结束种植指引 (GameActionData)</t>
+  </si>
+  <si>
+    <t>86</t>
+  </si>
+  <si>
+    <t>86购买结束对话 (GameActionData)</t>
+  </si>
+  <si>
+    <t>87</t>
+  </si>
+  <si>
+    <t>87赠送结束对话 (GameActionData)</t>
+  </si>
+  <si>
+    <t>88</t>
+  </si>
+  <si>
+    <t>88继续植物店电影 (GameActionData)</t>
+  </si>
+  <si>
+    <t>89</t>
+  </si>
+  <si>
+    <t>89继续种植 (GameActionData)</t>
+  </si>
+  <si>
+    <t>8</t>
+  </si>
+  <si>
+    <t>8显示UI (GameActionData)</t>
+  </si>
+  <si>
+    <t>90</t>
+  </si>
+  <si>
+    <t>90隐藏主角播放电影 (GameActionData)</t>
+  </si>
+  <si>
+    <t>91</t>
+  </si>
+  <si>
+    <t>91wait隐藏主角播放电影 (GameActionData)</t>
+  </si>
+  <si>
+    <t>92</t>
+  </si>
+  <si>
+    <t>92组队指引 (GameActionData)</t>
+  </si>
+  <si>
+    <t>93</t>
+  </si>
+  <si>
+    <t>93前进指引 (GameActionData)</t>
+  </si>
+  <si>
+    <t>94</t>
+  </si>
+  <si>
+    <t>94继续电影 (GameActionData)</t>
+  </si>
+  <si>
+    <t>95</t>
+  </si>
+  <si>
+    <t>95结束指引 (GameActionData)</t>
+  </si>
+  <si>
+    <t>96</t>
+  </si>
+  <si>
+    <t>96前进指引 (GameActionData)</t>
+  </si>
+  <si>
+    <t>97</t>
+  </si>
+  <si>
+    <t>97第一次战斗结束 (GameActionData)</t>
+  </si>
+  <si>
+    <t>98</t>
+  </si>
+  <si>
+    <t>98检查指引完成 (GameActionData)</t>
+  </si>
+  <si>
+    <t>9999</t>
+  </si>
+  <si>
+    <t>9999测试 (GameActionData)</t>
+  </si>
+  <si>
+    <t>99</t>
+  </si>
+  <si>
+    <t>99战斗结束回家电影 (GameActionData)</t>
+  </si>
+  <si>
+    <t>9</t>
+  </si>
+  <si>
+    <t>9隐藏UI (GameActionData)</t>
   </si>
   <si>
     <t>别墅二楼</t>
@@ -2287,15 +2713,9 @@
     <t>夏之丛林胜利</t>
   </si>
   <si>
-    <t>25</t>
-  </si>
-  <si>
     <t>秋风之谷胜利</t>
   </si>
   <si>
-    <t>26</t>
-  </si>
-  <si>
     <t>冬之雪原胜利</t>
   </si>
   <si>
@@ -2326,21 +2746,12 @@
     <t>投喂动物</t>
   </si>
   <si>
-    <t>311</t>
-  </si>
-  <si>
     <t>打开天气预报</t>
   </si>
   <si>
-    <t>312</t>
-  </si>
-  <si>
     <t>第一次离开家</t>
   </si>
   <si>
-    <t>313</t>
-  </si>
-  <si>
     <t>查看角色</t>
   </si>
   <si>
@@ -2350,9 +2761,6 @@
     <t>垂钓</t>
   </si>
   <si>
-    <t>400</t>
-  </si>
-  <si>
     <t>创建或打开杂物箱</t>
   </si>
   <si>
@@ -2467,15 +2875,9 @@
     <t>点击鸡</t>
   </si>
   <si>
-    <t>90</t>
-  </si>
-  <si>
     <t>春战斗胜利</t>
   </si>
   <si>
-    <t>97</t>
-  </si>
-  <si>
     <t>第一次战斗结束</t>
   </si>
   <si>
@@ -2488,12 +2890,6 @@
     <t>查看</t>
   </si>
   <si>
-    <t>10</t>
-  </si>
-  <si>
-    <t>11</t>
-  </si>
-  <si>
     <t>开始营业</t>
   </si>
   <si>
@@ -2503,6 +2899,9 @@
     <t>打开</t>
   </si>
   <si>
+    <t>15</t>
+  </si>
+  <si>
     <t>关闭</t>
   </si>
   <si>
@@ -2524,9 +2923,6 @@
     <t>开始生产</t>
   </si>
   <si>
-    <t>3</t>
-  </si>
-  <si>
     <t>设置</t>
   </si>
   <si>
@@ -2539,9 +2935,6 @@
     <t>投喂</t>
   </si>
   <si>
-    <t>4</t>
-  </si>
-  <si>
     <t>聊天</t>
   </si>
   <si>
@@ -2554,16 +2947,7 @@
     <t>打开箱子</t>
   </si>
   <si>
-    <t>7</t>
-  </si>
-  <si>
-    <t>8</t>
-  </si>
-  <si>
     <t>站起</t>
-  </si>
-  <si>
-    <t>9</t>
   </si>
   <si>
     <t>睡眠</t>
@@ -2943,250 +3327,250 @@
     </row>
     <row r="2" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B2" s="6" t="s">
-        <v>702</v>
+        <v>844</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>703</v>
+        <v>845</v>
       </c>
     </row>
     <row r="3" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B3" s="6" t="s">
-        <v>303</v>
+        <v>445</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>704</v>
+        <v>846</v>
       </c>
     </row>
     <row r="4" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B4" s="6" t="s">
-        <v>305</v>
+        <v>447</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>705</v>
+        <v>847</v>
       </c>
     </row>
     <row r="5" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B5" s="6" t="s">
-        <v>307</v>
+        <v>449</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>706</v>
+        <v>848</v>
       </c>
     </row>
     <row r="6" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B6" s="6" t="s">
-        <v>309</v>
+        <v>451</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>707</v>
+        <v>849</v>
       </c>
     </row>
     <row r="7" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B7" s="6" t="s">
-        <v>311</v>
+        <v>453</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>708</v>
+        <v>850</v>
       </c>
     </row>
     <row r="8" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B8" s="6" t="s">
-        <v>315</v>
+        <v>457</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>709</v>
+        <v>851</v>
       </c>
     </row>
     <row r="9" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B9" s="6" t="s">
-        <v>317</v>
+        <v>459</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>710</v>
+        <v>852</v>
       </c>
     </row>
     <row r="10" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B10" s="6" t="s">
-        <v>319</v>
+        <v>461</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>711</v>
+        <v>853</v>
       </c>
     </row>
     <row r="11" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B11" s="6" t="s">
-        <v>321</v>
+        <v>463</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>712</v>
+        <v>854</v>
       </c>
     </row>
     <row r="12" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B12" s="6" t="s">
-        <v>323</v>
+        <v>465</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>713</v>
+        <v>855</v>
       </c>
     </row>
     <row r="13" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B13" s="6" t="s">
-        <v>325</v>
+        <v>467</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>714</v>
+        <v>856</v>
       </c>
     </row>
     <row r="14" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B14" s="6" t="s">
-        <v>329</v>
+        <v>471</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>715</v>
+        <v>857</v>
       </c>
     </row>
     <row r="15" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B15" s="6" t="s">
-        <v>331</v>
+        <v>473</v>
       </c>
       <c r="C15" s="6" t="s">
-        <v>716</v>
+        <v>858</v>
       </c>
     </row>
     <row r="16" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B16" s="6" t="s">
-        <v>333</v>
+        <v>475</v>
       </c>
       <c r="C16" s="6" t="s">
-        <v>717</v>
+        <v>859</v>
       </c>
     </row>
     <row r="17" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B17" s="6" t="s">
-        <v>335</v>
+        <v>477</v>
       </c>
       <c r="C17" s="6" t="s">
-        <v>718</v>
+        <v>860</v>
       </c>
     </row>
     <row r="18" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B18" s="6" t="s">
-        <v>337</v>
+        <v>479</v>
       </c>
       <c r="C18" s="6" t="s">
-        <v>719</v>
+        <v>861</v>
       </c>
     </row>
     <row r="19" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B19" s="6" t="s">
-        <v>485</v>
+        <v>627</v>
       </c>
       <c r="C19" s="6" t="s">
-        <v>720</v>
+        <v>862</v>
       </c>
     </row>
     <row r="20" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B20" s="6" t="s">
-        <v>487</v>
+        <v>629</v>
       </c>
       <c r="C20" s="6" t="s">
-        <v>721</v>
+        <v>863</v>
       </c>
     </row>
     <row r="21" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B21" s="6" t="s">
-        <v>490</v>
+        <v>632</v>
       </c>
       <c r="C21" s="6" t="s">
-        <v>722</v>
+        <v>864</v>
       </c>
     </row>
     <row r="22" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B22" s="6" t="s">
-        <v>494</v>
+        <v>636</v>
       </c>
       <c r="C22" s="6" t="s">
-        <v>723</v>
+        <v>865</v>
       </c>
     </row>
     <row r="23" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B23" s="6" t="s">
-        <v>495</v>
+        <v>637</v>
       </c>
       <c r="C23" s="6" t="s">
-        <v>724</v>
+        <v>866</v>
       </c>
     </row>
     <row r="24" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B24" s="6" t="s">
-        <v>500</v>
+        <v>642</v>
       </c>
       <c r="C24" s="6" t="s">
-        <v>725</v>
+        <v>867</v>
       </c>
     </row>
     <row r="25" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B25" s="6" t="s">
-        <v>502</v>
+        <v>644</v>
       </c>
       <c r="C25" s="6" t="s">
-        <v>726</v>
+        <v>868</v>
       </c>
     </row>
     <row r="26" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B26" s="6" t="s">
-        <v>504</v>
+        <v>646</v>
       </c>
       <c r="C26" s="6" t="s">
-        <v>727</v>
+        <v>869</v>
       </c>
     </row>
     <row r="27" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B27" s="6" t="s">
-        <v>246</v>
+        <v>388</v>
       </c>
       <c r="C27" s="6" t="s">
-        <v>728</v>
+        <v>870</v>
       </c>
     </row>
     <row r="28" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B28" s="6" t="s">
-        <v>507</v>
+        <v>649</v>
       </c>
       <c r="C28" s="6" t="s">
-        <v>729</v>
+        <v>871</v>
       </c>
     </row>
     <row r="29" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B29" s="6" t="s">
-        <v>509</v>
+        <v>651</v>
       </c>
       <c r="C29" s="6" t="s">
-        <v>730</v>
+        <v>872</v>
       </c>
     </row>
     <row r="30" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B30" s="6" t="s">
-        <v>511</v>
+        <v>653</v>
       </c>
       <c r="C30" s="6" t="s">
-        <v>731</v>
+        <v>873</v>
       </c>
     </row>
     <row r="31" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B31" s="6" t="s">
-        <v>512</v>
+        <v>654</v>
       </c>
       <c r="C31" s="6" t="s">
-        <v>732</v>
+        <v>874</v>
       </c>
     </row>
     <row r="32" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B32" s="6" t="s">
-        <v>514</v>
+        <v>656</v>
       </c>
       <c r="C32" s="6" t="s">
-        <v>733</v>
+        <v>875</v>
       </c>
     </row>
   </sheetData>
@@ -3201,7 +3585,7 @@
   <dimension ref="B1:O56"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="22.28515625" style="3" customWidth="1"/>
+    <col min="2" max="2" width="22.28515625" style="4" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:15" x14ac:dyDescent="0.25">
@@ -3214,51 +3598,51 @@
     </row>
     <row r="2" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B2" s="6" t="s">
-        <v>196</v>
+        <v>338</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>197</v>
+        <v>339</v>
       </c>
     </row>
     <row r="3" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B3" s="6" t="s">
-        <v>198</v>
+        <v>340</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>199</v>
+        <v>341</v>
       </c>
     </row>
     <row r="4" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B4" s="6" t="s">
-        <v>200</v>
+        <v>342</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>201</v>
+        <v>343</v>
       </c>
       <c r="G4" s="7" t="s">
-        <v>202</v>
+        <v>344</v>
       </c>
       <c r="I4" s="8" t="s">
-        <v>203</v>
+        <v>345</v>
       </c>
       <c r="J4" s="8" t="s">
-        <v>204</v>
+        <v>346</v>
       </c>
       <c r="K4" s="6" t="s">
-        <v>205</v>
+        <v>347</v>
       </c>
     </row>
     <row r="5" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B5" s="6" t="s">
-        <v>206</v>
+        <v>348</v>
       </c>
       <c r="C5" s="6">
         <v>948</v>
       </c>
       <c r="G5" s="7" t="s">
-        <v>207</v>
-      </c>
-      <c r="I5" s="3">
+        <v>349</v>
+      </c>
+      <c r="I5" s="4">
         <f>VLOOKUP(I4,$B:$C,2,FALSE)</f>
         <v>874</v>
       </c>
@@ -3273,10 +3657,10 @@
     </row>
     <row r="6" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B6" s="6" t="s">
-        <v>208</v>
+        <v>350</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>209</v>
+        <v>351</v>
       </c>
       <c r="G6" s="9" t="str">
         <f>G4&amp;","&amp;G5</f>
@@ -3300,45 +3684,45 @@
     </row>
     <row r="7" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B7" s="6" t="s">
-        <v>210</v>
+        <v>352</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>211</v>
+        <v>353</v>
       </c>
       <c r="G7" s="7" t="s">
-        <v>207</v>
+        <v>349</v>
       </c>
       <c r="I7" s="8" t="s">
-        <v>203</v>
+        <v>345</v>
       </c>
       <c r="J7" s="8" t="s">
-        <v>204</v>
+        <v>346</v>
       </c>
       <c r="K7" s="6" t="s">
-        <v>205</v>
+        <v>347</v>
       </c>
       <c r="L7" s="6" t="s">
-        <v>212</v>
+        <v>354</v>
       </c>
       <c r="M7" s="6" t="s">
-        <v>213</v>
+        <v>355</v>
       </c>
       <c r="N7" s="6" t="s">
-        <v>214</v>
+        <v>356</v>
       </c>
       <c r="O7" s="6" t="s">
-        <v>215</v>
+        <v>357</v>
       </c>
     </row>
     <row r="8" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B8" s="6" t="s">
-        <v>203</v>
+        <v>345</v>
       </c>
       <c r="C8" s="6">
         <v>874</v>
       </c>
       <c r="G8" s="7" t="s">
-        <v>216</v>
+        <v>358</v>
       </c>
       <c r="I8" s="6">
         <f>VLOOKUP(I7,$B:$C,2,FALSE)</f>
@@ -3371,10 +3755,10 @@
     </row>
     <row r="9" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B9" s="6" t="s">
-        <v>217</v>
+        <v>359</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>218</v>
+        <v>360</v>
       </c>
       <c r="G9" s="9" t="str">
         <f>G7&amp;","&amp;G8</f>
@@ -3412,29 +3796,29 @@
     </row>
     <row r="10" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B10" s="6" t="s">
-        <v>219</v>
+        <v>361</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>220</v>
+        <v>362</v>
       </c>
       <c r="G10" s="7" t="s">
-        <v>216</v>
+        <v>358</v>
       </c>
     </row>
     <row r="11" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B11" s="6" t="s">
-        <v>221</v>
+        <v>363</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>222</v>
+        <v>364</v>
       </c>
       <c r="G11" s="7" t="s">
-        <v>223</v>
+        <v>365</v>
       </c>
     </row>
     <row r="12" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B12" s="6" t="s">
-        <v>224</v>
+        <v>366</v>
       </c>
       <c r="C12" s="6">
         <v>1756</v>
@@ -3455,10 +3839,10 @@
     </row>
     <row r="13" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B13" s="6" t="s">
-        <v>225</v>
+        <v>367</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>226</v>
+        <v>368</v>
       </c>
       <c r="F13" s="6"/>
       <c r="G13" s="7"/>
@@ -3473,38 +3857,38 @@
     </row>
     <row r="14" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B14" s="6" t="s">
-        <v>227</v>
+        <v>369</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>228</v>
+        <v>370</v>
       </c>
       <c r="F14" s="6"/>
       <c r="G14" s="7" t="s">
-        <v>223</v>
+        <v>365</v>
       </c>
       <c r="I14" s="6" t="s">
-        <v>212</v>
+        <v>354</v>
       </c>
       <c r="J14" s="6" t="s">
-        <v>213</v>
+        <v>355</v>
       </c>
       <c r="K14" s="6" t="s">
-        <v>214</v>
+        <v>356</v>
       </c>
       <c r="L14" s="6" t="s">
-        <v>215</v>
+        <v>357</v>
       </c>
     </row>
     <row r="15" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B15" s="6" t="s">
-        <v>229</v>
+        <v>371</v>
       </c>
       <c r="C15" s="6" t="s">
-        <v>230</v>
+        <v>372</v>
       </c>
       <c r="F15" s="6"/>
       <c r="G15" s="7" t="s">
-        <v>231</v>
+        <v>373</v>
       </c>
       <c r="H15" s="6"/>
       <c r="I15" s="6" t="str">
@@ -3527,10 +3911,10 @@
     </row>
     <row r="16" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B16" s="6" t="s">
-        <v>219</v>
+        <v>361</v>
       </c>
       <c r="C16" s="6" t="s">
-        <v>232</v>
+        <v>374</v>
       </c>
       <c r="G16" s="9" t="str">
         <f>G14&amp;","&amp;G15</f>
@@ -3558,36 +3942,36 @@
     </row>
     <row r="17" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B17" s="6" t="s">
-        <v>219</v>
+        <v>361</v>
       </c>
       <c r="C17" s="6" t="s">
-        <v>233</v>
+        <v>375</v>
       </c>
       <c r="G17" s="7" t="s">
-        <v>234</v>
+        <v>376</v>
       </c>
       <c r="I17" s="6" t="s">
-        <v>213</v>
+        <v>355</v>
       </c>
       <c r="J17" s="6" t="s">
-        <v>214</v>
+        <v>356</v>
       </c>
       <c r="K17" s="6" t="s">
-        <v>215</v>
+        <v>357</v>
       </c>
       <c r="L17" s="6" t="s">
-        <v>205</v>
+        <v>347</v>
       </c>
     </row>
     <row r="18" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B18" s="6" t="s">
-        <v>235</v>
+        <v>377</v>
       </c>
       <c r="C18" s="6" t="s">
-        <v>236</v>
+        <v>378</v>
       </c>
       <c r="G18" s="7" t="s">
-        <v>237</v>
+        <v>379</v>
       </c>
       <c r="I18" s="6" t="str">
         <f>VLOOKUP(I17,$B:$C,2,FALSE)</f>
@@ -3608,10 +3992,10 @@
     </row>
     <row r="19" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B19" s="6" t="s">
-        <v>238</v>
+        <v>380</v>
       </c>
       <c r="C19" s="6" t="s">
-        <v>239</v>
+        <v>381</v>
       </c>
       <c r="G19" s="9" t="str">
         <f>G17&amp;","&amp;G18</f>
@@ -3639,7 +4023,7 @@
     </row>
     <row r="20" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B20" s="6" t="s">
-        <v>240</v>
+        <v>382</v>
       </c>
       <c r="C20" s="6">
         <v>900</v>
@@ -3648,28 +4032,28 @@
     </row>
     <row r="21" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B21" s="6" t="s">
-        <v>241</v>
+        <v>383</v>
       </c>
       <c r="C21" s="6" t="s">
-        <v>242</v>
+        <v>384</v>
       </c>
     </row>
     <row r="22" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B22" s="6" t="s">
-        <v>243</v>
+        <v>385</v>
       </c>
       <c r="C22" s="6" t="s">
-        <v>244</v>
+        <v>386</v>
       </c>
     </row>
     <row r="23" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B23" s="6" t="s">
-        <v>245</v>
+        <v>387</v>
       </c>
       <c r="C23" s="6" t="s">
-        <v>246</v>
-      </c>
-      <c r="G23" s="3" t="str">
+        <v>388</v>
+      </c>
+      <c r="G23" s="4" t="str">
         <f>G6&amp;","&amp;G9&amp;","&amp;G12&amp;","&amp;G16&amp;","&amp;G19</f>
         <v>6,0,9,0,9,0,17,30,17,30,19,30,19,30, 22,0,22,0,24,0</v>
       </c>
@@ -3677,42 +4061,42 @@
     </row>
     <row r="24" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B24" s="6" t="s">
-        <v>204</v>
+        <v>346</v>
       </c>
       <c r="C24" s="6" t="s">
-        <v>247</v>
+        <v>389</v>
       </c>
     </row>
     <row r="25" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B25" s="6" t="s">
-        <v>248</v>
+        <v>390</v>
       </c>
       <c r="C25" s="6" t="s">
-        <v>249</v>
+        <v>391</v>
       </c>
       <c r="M25" s="6"/>
     </row>
     <row r="26" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B26" s="6" t="s">
-        <v>250</v>
+        <v>392</v>
       </c>
       <c r="C26" s="6" t="s">
-        <v>251</v>
+        <v>393</v>
       </c>
       <c r="M26" s="6"/>
     </row>
     <row r="27" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B27" s="6" t="s">
-        <v>227</v>
+        <v>369</v>
       </c>
       <c r="C27" s="6" t="s">
-        <v>252</v>
+        <v>394</v>
       </c>
       <c r="M27" s="6"/>
     </row>
     <row r="28" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B28" s="6" t="s">
-        <v>253</v>
+        <v>395</v>
       </c>
       <c r="C28" s="6">
         <v>1014</v>
@@ -3721,89 +4105,89 @@
     </row>
     <row r="29" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B29" s="6" t="s">
-        <v>227</v>
+        <v>369</v>
       </c>
       <c r="C29" s="6" t="s">
-        <v>254</v>
+        <v>396</v>
       </c>
       <c r="M29" s="6"/>
     </row>
     <row r="30" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B30" s="6" t="s">
-        <v>215</v>
+        <v>357</v>
       </c>
       <c r="C30" s="6" t="s">
-        <v>255</v>
+        <v>397</v>
       </c>
     </row>
     <row r="31" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B31" s="6" t="s">
-        <v>227</v>
+        <v>369</v>
       </c>
       <c r="C31" s="6" t="s">
-        <v>256</v>
+        <v>398</v>
       </c>
       <c r="M31" s="6" t="s">
-        <v>213</v>
+        <v>355</v>
       </c>
     </row>
     <row r="32" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B32" s="6" t="s">
-        <v>257</v>
+        <v>399</v>
       </c>
       <c r="C32" s="6">
         <v>5309</v>
       </c>
       <c r="M32" s="6" t="s">
-        <v>214</v>
+        <v>356</v>
       </c>
     </row>
     <row r="33" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B33" s="6" t="s">
-        <v>227</v>
+        <v>369</v>
       </c>
       <c r="C33" s="6" t="s">
-        <v>258</v>
+        <v>400</v>
       </c>
       <c r="M33" s="6" t="s">
-        <v>215</v>
+        <v>357</v>
       </c>
     </row>
     <row r="34" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B34" s="6" t="s">
-        <v>213</v>
+        <v>355</v>
       </c>
       <c r="C34" s="6" t="s">
-        <v>259</v>
+        <v>401</v>
       </c>
     </row>
     <row r="35" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B35" s="6" t="s">
-        <v>260</v>
+        <v>402</v>
       </c>
       <c r="C35" s="6" t="s">
-        <v>261</v>
+        <v>403</v>
       </c>
     </row>
     <row r="36" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B36" s="6" t="s">
-        <v>262</v>
+        <v>404</v>
       </c>
       <c r="C36" s="6" t="s">
-        <v>263</v>
+        <v>405</v>
       </c>
     </row>
     <row r="37" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B37" s="6" t="s">
-        <v>264</v>
+        <v>406</v>
       </c>
       <c r="C37" s="6" t="s">
-        <v>265</v>
+        <v>407</v>
       </c>
     </row>
     <row r="38" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B38" s="6" t="s">
-        <v>266</v>
+        <v>408</v>
       </c>
       <c r="C38" s="6">
         <v>3056</v>
@@ -3811,23 +4195,23 @@
     </row>
     <row r="39" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B39" s="6" t="s">
-        <v>267</v>
+        <v>409</v>
       </c>
       <c r="C39" s="6" t="s">
-        <v>268</v>
+        <v>410</v>
       </c>
     </row>
     <row r="40" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B40" s="6" t="s">
-        <v>269</v>
+        <v>411</v>
       </c>
       <c r="C40" s="6" t="s">
-        <v>270</v>
+        <v>412</v>
       </c>
     </row>
     <row r="41" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B41" s="6" t="s">
-        <v>205</v>
+        <v>347</v>
       </c>
       <c r="C41" s="6">
         <v>2497</v>
@@ -3835,79 +4219,79 @@
     </row>
     <row r="42" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B42" s="6" t="s">
-        <v>271</v>
+        <v>413</v>
       </c>
       <c r="C42" s="6" t="s">
-        <v>272</v>
+        <v>414</v>
       </c>
     </row>
     <row r="43" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B43" s="6" t="s">
-        <v>273</v>
+        <v>415</v>
       </c>
       <c r="C43" s="6" t="s">
-        <v>274</v>
+        <v>416</v>
       </c>
     </row>
     <row r="44" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B44" s="6" t="s">
-        <v>227</v>
+        <v>369</v>
       </c>
       <c r="C44" s="6" t="s">
-        <v>275</v>
+        <v>417</v>
       </c>
     </row>
     <row r="45" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B45" s="6" t="s">
-        <v>214</v>
+        <v>356</v>
       </c>
       <c r="C45" s="6" t="s">
-        <v>276</v>
+        <v>418</v>
       </c>
     </row>
     <row r="46" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B46" s="6" t="s">
-        <v>277</v>
+        <v>419</v>
       </c>
       <c r="C46" s="6" t="s">
-        <v>278</v>
+        <v>420</v>
       </c>
     </row>
     <row r="47" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B47" s="6" t="s">
-        <v>279</v>
+        <v>421</v>
       </c>
       <c r="C47" s="6" t="s">
-        <v>280</v>
+        <v>422</v>
       </c>
     </row>
     <row r="48" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B48" s="6" t="s">
-        <v>281</v>
+        <v>423</v>
       </c>
       <c r="C48" s="6" t="s">
-        <v>282</v>
+        <v>424</v>
       </c>
     </row>
     <row r="49" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B49" s="6" t="s">
-        <v>283</v>
+        <v>425</v>
       </c>
       <c r="C49" s="6" t="s">
-        <v>284</v>
+        <v>426</v>
       </c>
     </row>
     <row r="50" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B50" s="6" t="s">
-        <v>285</v>
+        <v>427</v>
       </c>
       <c r="C50" s="6" t="s">
-        <v>286</v>
+        <v>428</v>
       </c>
     </row>
     <row r="51" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B51" s="6" t="s">
-        <v>287</v>
+        <v>429</v>
       </c>
       <c r="C51" s="6">
         <v>547</v>
@@ -3915,42 +4299,42 @@
     </row>
     <row r="52" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B52" s="6" t="s">
-        <v>212</v>
+        <v>354</v>
       </c>
       <c r="C52" s="6" t="s">
-        <v>50</v>
+        <v>82</v>
       </c>
     </row>
     <row r="53" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B53" s="6" t="s">
-        <v>219</v>
+        <v>361</v>
       </c>
       <c r="C53" s="6" t="s">
-        <v>288</v>
+        <v>430</v>
       </c>
     </row>
     <row r="54" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B54" s="6" t="s">
-        <v>219</v>
+        <v>361</v>
       </c>
       <c r="C54" s="6" t="s">
-        <v>289</v>
+        <v>431</v>
       </c>
     </row>
     <row r="55" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B55" s="6" t="s">
-        <v>290</v>
+        <v>432</v>
       </c>
       <c r="C55" s="6" t="s">
-        <v>291</v>
+        <v>433</v>
       </c>
     </row>
     <row r="56" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B56" s="6" t="s">
-        <v>219</v>
+        <v>361</v>
       </c>
       <c r="C56" s="6" t="s">
-        <v>292</v>
+        <v>434</v>
       </c>
     </row>
   </sheetData>
@@ -3975,602 +4359,602 @@
     </row>
     <row r="2" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B2" s="6" t="s">
-        <v>293</v>
+        <v>435</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>294</v>
+        <v>436</v>
       </c>
     </row>
     <row r="3" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B3" s="6" t="s">
-        <v>295</v>
+        <v>437</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>296</v>
+        <v>438</v>
       </c>
     </row>
     <row r="4" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B4" s="6" t="s">
-        <v>297</v>
+        <v>439</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>298</v>
+        <v>440</v>
       </c>
     </row>
     <row r="5" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B5" s="6" t="s">
-        <v>299</v>
+        <v>441</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>300</v>
+        <v>442</v>
       </c>
     </row>
     <row r="6" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B6" s="6" t="s">
-        <v>301</v>
+        <v>443</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>302</v>
+        <v>444</v>
       </c>
     </row>
     <row r="7" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B7" s="6" t="s">
-        <v>303</v>
+        <v>445</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>304</v>
+        <v>446</v>
       </c>
     </row>
     <row r="8" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B8" s="6" t="s">
-        <v>305</v>
+        <v>447</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>304</v>
+        <v>446</v>
       </c>
     </row>
     <row r="9" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B9" s="6" t="s">
-        <v>306</v>
+        <v>448</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>304</v>
+        <v>446</v>
       </c>
     </row>
     <row r="10" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B10" s="6" t="s">
-        <v>307</v>
+        <v>449</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>308</v>
+        <v>450</v>
       </c>
     </row>
     <row r="11" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B11" s="6" t="s">
-        <v>309</v>
+        <v>451</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>310</v>
+        <v>452</v>
       </c>
     </row>
     <row r="12" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B12" s="6" t="s">
-        <v>311</v>
+        <v>453</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>312</v>
+        <v>454</v>
       </c>
     </row>
     <row r="13" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B13" s="6" t="s">
-        <v>313</v>
+        <v>455</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>314</v>
+        <v>456</v>
       </c>
     </row>
     <row r="14" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B14" s="6" t="s">
-        <v>315</v>
+        <v>457</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>316</v>
+        <v>458</v>
       </c>
     </row>
     <row r="15" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B15" s="6" t="s">
-        <v>317</v>
+        <v>459</v>
       </c>
       <c r="C15" s="6" t="s">
-        <v>318</v>
+        <v>460</v>
       </c>
     </row>
     <row r="16" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B16" s="6" t="s">
-        <v>319</v>
+        <v>461</v>
       </c>
       <c r="C16" s="6" t="s">
-        <v>320</v>
+        <v>462</v>
       </c>
     </row>
     <row r="17" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B17" s="6" t="s">
-        <v>321</v>
+        <v>463</v>
       </c>
       <c r="C17" s="6" t="s">
-        <v>322</v>
+        <v>464</v>
       </c>
     </row>
     <row r="18" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B18" s="6" t="s">
-        <v>323</v>
+        <v>465</v>
       </c>
       <c r="C18" s="6" t="s">
-        <v>324</v>
+        <v>466</v>
       </c>
     </row>
     <row r="19" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B19" s="6" t="s">
-        <v>325</v>
+        <v>467</v>
       </c>
       <c r="C19" s="6" t="s">
-        <v>326</v>
+        <v>468</v>
       </c>
     </row>
     <row r="20" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B20" s="6" t="s">
-        <v>327</v>
+        <v>469</v>
       </c>
       <c r="C20" s="6" t="s">
-        <v>328</v>
+        <v>470</v>
       </c>
     </row>
     <row r="21" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B21" s="6" t="s">
-        <v>329</v>
+        <v>471</v>
       </c>
       <c r="C21" s="6" t="s">
-        <v>330</v>
+        <v>472</v>
       </c>
     </row>
     <row r="22" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B22" s="6" t="s">
-        <v>331</v>
+        <v>473</v>
       </c>
       <c r="C22" s="6" t="s">
-        <v>332</v>
+        <v>474</v>
       </c>
     </row>
     <row r="23" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B23" s="6" t="s">
-        <v>333</v>
+        <v>475</v>
       </c>
       <c r="C23" s="6" t="s">
-        <v>334</v>
+        <v>476</v>
       </c>
     </row>
     <row r="24" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B24" s="6" t="s">
-        <v>335</v>
+        <v>477</v>
       </c>
       <c r="C24" s="6" t="s">
-        <v>336</v>
+        <v>478</v>
       </c>
     </row>
     <row r="25" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B25" s="6" t="s">
-        <v>337</v>
+        <v>479</v>
       </c>
       <c r="C25" s="6" t="s">
-        <v>338</v>
+        <v>480</v>
       </c>
     </row>
     <row r="26" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B26" s="6" t="s">
-        <v>339</v>
+        <v>481</v>
       </c>
       <c r="C26" s="6" t="s">
-        <v>340</v>
+        <v>482</v>
       </c>
     </row>
     <row r="27" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B27" s="6" t="s">
-        <v>341</v>
+        <v>483</v>
       </c>
       <c r="C27" s="6" t="s">
-        <v>342</v>
+        <v>484</v>
       </c>
     </row>
     <row r="28" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B28" s="6" t="s">
-        <v>343</v>
+        <v>485</v>
       </c>
       <c r="C28" s="6" t="s">
-        <v>344</v>
+        <v>486</v>
       </c>
     </row>
     <row r="29" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B29" s="6" t="s">
-        <v>345</v>
+        <v>487</v>
       </c>
       <c r="C29" s="6" t="s">
-        <v>346</v>
+        <v>488</v>
       </c>
     </row>
     <row r="30" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B30" s="6" t="s">
-        <v>347</v>
+        <v>489</v>
       </c>
       <c r="C30" s="6" t="s">
-        <v>348</v>
+        <v>490</v>
       </c>
     </row>
     <row r="31" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B31" s="6" t="s">
-        <v>349</v>
+        <v>491</v>
       </c>
       <c r="C31" s="6" t="s">
-        <v>350</v>
+        <v>492</v>
       </c>
     </row>
     <row r="32" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B32" s="6" t="s">
-        <v>351</v>
+        <v>493</v>
       </c>
       <c r="C32" s="6" t="s">
-        <v>352</v>
+        <v>494</v>
       </c>
     </row>
     <row r="33" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B33" s="6" t="s">
-        <v>353</v>
+        <v>495</v>
       </c>
       <c r="C33" s="6" t="s">
-        <v>354</v>
+        <v>496</v>
       </c>
     </row>
     <row r="34" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B34" s="6" t="s">
-        <v>355</v>
+        <v>497</v>
       </c>
       <c r="C34" s="6" t="s">
-        <v>356</v>
+        <v>498</v>
       </c>
     </row>
     <row r="35" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B35" s="6" t="s">
-        <v>357</v>
+        <v>499</v>
       </c>
       <c r="C35" s="6" t="s">
-        <v>358</v>
+        <v>500</v>
       </c>
     </row>
     <row r="36" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B36" s="6" t="s">
-        <v>359</v>
+        <v>501</v>
       </c>
       <c r="C36" s="6" t="s">
-        <v>360</v>
+        <v>502</v>
       </c>
     </row>
     <row r="37" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B37" s="6" t="s">
-        <v>361</v>
+        <v>503</v>
       </c>
       <c r="C37" s="6" t="s">
-        <v>362</v>
+        <v>504</v>
       </c>
     </row>
     <row r="38" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B38" s="6" t="s">
-        <v>363</v>
+        <v>505</v>
       </c>
       <c r="C38" s="6" t="s">
-        <v>364</v>
+        <v>506</v>
       </c>
     </row>
     <row r="39" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B39" s="6" t="s">
-        <v>365</v>
+        <v>507</v>
       </c>
       <c r="C39" s="6" t="s">
-        <v>366</v>
+        <v>508</v>
       </c>
     </row>
     <row r="40" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B40" s="6" t="s">
-        <v>367</v>
+        <v>509</v>
       </c>
       <c r="C40" s="6" t="s">
-        <v>368</v>
+        <v>510</v>
       </c>
     </row>
     <row r="41" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B41" s="6" t="s">
-        <v>369</v>
+        <v>511</v>
       </c>
       <c r="C41" s="6" t="s">
-        <v>370</v>
+        <v>512</v>
       </c>
     </row>
     <row r="42" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B42" s="6" t="s">
-        <v>371</v>
+        <v>513</v>
       </c>
       <c r="C42" s="6" t="s">
-        <v>372</v>
+        <v>514</v>
       </c>
     </row>
     <row r="43" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B43" s="6" t="s">
-        <v>373</v>
+        <v>515</v>
       </c>
       <c r="C43" s="6" t="s">
-        <v>374</v>
+        <v>516</v>
       </c>
     </row>
     <row r="44" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B44" s="6" t="s">
-        <v>375</v>
+        <v>517</v>
       </c>
       <c r="C44" s="6" t="s">
-        <v>376</v>
+        <v>518</v>
       </c>
     </row>
     <row r="45" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B45" s="6" t="s">
-        <v>377</v>
+        <v>519</v>
       </c>
       <c r="C45" s="6" t="s">
-        <v>378</v>
+        <v>520</v>
       </c>
     </row>
     <row r="46" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B46" s="6" t="s">
-        <v>379</v>
+        <v>521</v>
       </c>
       <c r="C46" s="6" t="s">
-        <v>380</v>
+        <v>522</v>
       </c>
     </row>
     <row r="47" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B47" s="6" t="s">
-        <v>381</v>
+        <v>523</v>
       </c>
       <c r="C47" s="6" t="s">
-        <v>382</v>
+        <v>524</v>
       </c>
     </row>
     <row r="48" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B48" s="6" t="s">
-        <v>383</v>
+        <v>525</v>
       </c>
       <c r="C48" s="6" t="s">
-        <v>384</v>
+        <v>526</v>
       </c>
     </row>
     <row r="49" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B49" s="6" t="s">
-        <v>385</v>
+        <v>527</v>
       </c>
       <c r="C49" s="6" t="s">
-        <v>386</v>
+        <v>528</v>
       </c>
     </row>
     <row r="50" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B50" s="6" t="s">
-        <v>387</v>
+        <v>529</v>
       </c>
       <c r="C50" s="6" t="s">
-        <v>388</v>
+        <v>530</v>
       </c>
     </row>
     <row r="51" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B51" s="6" t="s">
-        <v>389</v>
+        <v>531</v>
       </c>
       <c r="C51" s="6" t="s">
-        <v>390</v>
+        <v>532</v>
       </c>
     </row>
     <row r="52" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B52" s="6" t="s">
-        <v>391</v>
+        <v>533</v>
       </c>
       <c r="C52" s="6" t="s">
-        <v>392</v>
+        <v>534</v>
       </c>
     </row>
     <row r="53" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B53" s="6" t="s">
-        <v>393</v>
+        <v>535</v>
       </c>
       <c r="C53" s="6" t="s">
-        <v>394</v>
+        <v>536</v>
       </c>
     </row>
     <row r="54" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B54" s="6" t="s">
-        <v>395</v>
+        <v>537</v>
       </c>
       <c r="C54" s="6" t="s">
-        <v>396</v>
+        <v>538</v>
       </c>
     </row>
     <row r="55" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B55" s="6" t="s">
-        <v>397</v>
+        <v>539</v>
       </c>
       <c r="C55" s="6" t="s">
-        <v>398</v>
+        <v>540</v>
       </c>
     </row>
     <row r="56" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B56" s="6" t="s">
-        <v>399</v>
+        <v>541</v>
       </c>
       <c r="C56" s="6" t="s">
-        <v>400</v>
+        <v>542</v>
       </c>
     </row>
     <row r="57" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B57" s="6" t="s">
-        <v>401</v>
+        <v>543</v>
       </c>
       <c r="C57" s="6" t="s">
-        <v>402</v>
+        <v>544</v>
       </c>
     </row>
     <row r="58" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B58" s="6" t="s">
-        <v>403</v>
+        <v>545</v>
       </c>
       <c r="C58" s="6" t="s">
-        <v>404</v>
+        <v>546</v>
       </c>
     </row>
     <row r="59" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B59" s="6" t="s">
-        <v>405</v>
+        <v>547</v>
       </c>
       <c r="C59" s="6" t="s">
-        <v>406</v>
+        <v>548</v>
       </c>
     </row>
     <row r="60" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B60" s="6" t="s">
-        <v>407</v>
+        <v>549</v>
       </c>
       <c r="C60" s="6" t="s">
-        <v>408</v>
+        <v>550</v>
       </c>
     </row>
     <row r="61" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B61" s="6" t="s">
-        <v>409</v>
+        <v>551</v>
       </c>
       <c r="C61" s="6" t="s">
-        <v>410</v>
+        <v>552</v>
       </c>
     </row>
     <row r="62" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B62" s="6" t="s">
-        <v>411</v>
+        <v>553</v>
       </c>
       <c r="C62" s="6" t="s">
-        <v>412</v>
+        <v>554</v>
       </c>
     </row>
     <row r="63" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B63" s="6" t="s">
-        <v>413</v>
+        <v>555</v>
       </c>
       <c r="C63" s="6" t="s">
-        <v>414</v>
+        <v>556</v>
       </c>
     </row>
     <row r="64" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B64" s="6" t="s">
-        <v>415</v>
+        <v>557</v>
       </c>
       <c r="C64" s="6" t="s">
-        <v>416</v>
+        <v>558</v>
       </c>
     </row>
     <row r="65" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B65" s="6" t="s">
-        <v>417</v>
+        <v>559</v>
       </c>
       <c r="C65" s="6" t="s">
-        <v>418</v>
+        <v>560</v>
       </c>
     </row>
     <row r="66" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B66" s="6" t="s">
-        <v>419</v>
+        <v>561</v>
       </c>
       <c r="C66" s="6" t="s">
-        <v>420</v>
+        <v>562</v>
       </c>
     </row>
     <row r="67" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B67" s="6" t="s">
-        <v>421</v>
+        <v>563</v>
       </c>
       <c r="C67" s="6" t="s">
-        <v>422</v>
+        <v>564</v>
       </c>
     </row>
     <row r="68" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B68" s="6" t="s">
-        <v>423</v>
+        <v>565</v>
       </c>
       <c r="C68" s="6" t="s">
-        <v>424</v>
+        <v>566</v>
       </c>
     </row>
     <row r="69" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B69" s="6" t="s">
-        <v>425</v>
+        <v>567</v>
       </c>
       <c r="C69" s="6" t="s">
-        <v>426</v>
+        <v>568</v>
       </c>
     </row>
     <row r="70" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B70" s="6" t="s">
-        <v>427</v>
+        <v>569</v>
       </c>
       <c r="C70" s="6" t="s">
-        <v>428</v>
+        <v>570</v>
       </c>
     </row>
     <row r="71" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B71" s="6" t="s">
-        <v>429</v>
+        <v>571</v>
       </c>
       <c r="C71" s="6" t="s">
-        <v>430</v>
+        <v>572</v>
       </c>
     </row>
     <row r="72" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B72" s="6" t="s">
-        <v>431</v>
+        <v>573</v>
       </c>
       <c r="C72" s="6" t="s">
-        <v>432</v>
+        <v>574</v>
       </c>
     </row>
     <row r="73" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B73" s="6" t="s">
-        <v>433</v>
+        <v>575</v>
       </c>
       <c r="C73" s="6" t="s">
-        <v>434</v>
+        <v>576</v>
       </c>
     </row>
     <row r="74" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B74" s="6" t="s">
-        <v>435</v>
+        <v>577</v>
       </c>
       <c r="C74" s="6" t="s">
-        <v>436</v>
+        <v>578</v>
       </c>
     </row>
     <row r="75" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B75" s="6" t="s">
-        <v>437</v>
+        <v>579</v>
       </c>
       <c r="C75" s="6" t="s">
-        <v>438</v>
+        <v>580</v>
       </c>
     </row>
     <row r="76" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B76" s="6" t="s">
-        <v>439</v>
+        <v>581</v>
       </c>
       <c r="C76" s="6" t="s">
-        <v>440</v>
+        <v>582</v>
       </c>
     </row>
     <row r="77" spans="2:3" x14ac:dyDescent="0.25">
@@ -4578,1087 +4962,1087 @@
         <v>1077</v>
       </c>
       <c r="C77" s="6" t="s">
-        <v>441</v>
+        <v>583</v>
       </c>
     </row>
     <row r="78" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B78" s="6" t="s">
-        <v>442</v>
+        <v>584</v>
       </c>
       <c r="C78" s="6" t="s">
-        <v>250</v>
+        <v>392</v>
       </c>
     </row>
     <row r="79" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B79" s="6" t="s">
-        <v>443</v>
+        <v>585</v>
       </c>
       <c r="C79" s="6" t="s">
-        <v>444</v>
+        <v>586</v>
       </c>
     </row>
     <row r="80" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B80" s="6" t="s">
-        <v>445</v>
+        <v>587</v>
       </c>
       <c r="C80" s="6" t="s">
-        <v>446</v>
+        <v>588</v>
       </c>
     </row>
     <row r="81" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B81" s="6" t="s">
-        <v>447</v>
+        <v>589</v>
       </c>
       <c r="C81" s="6" t="s">
-        <v>448</v>
+        <v>590</v>
       </c>
     </row>
     <row r="82" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B82" s="6" t="s">
-        <v>449</v>
+        <v>591</v>
       </c>
       <c r="C82" s="6" t="s">
-        <v>450</v>
+        <v>592</v>
       </c>
     </row>
     <row r="83" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B83" s="6" t="s">
-        <v>451</v>
+        <v>593</v>
       </c>
       <c r="C83" s="6" t="s">
-        <v>452</v>
+        <v>594</v>
       </c>
     </row>
     <row r="84" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B84" s="6" t="s">
-        <v>453</v>
+        <v>595</v>
       </c>
       <c r="C84" s="6" t="s">
-        <v>454</v>
+        <v>596</v>
       </c>
     </row>
     <row r="85" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B85" s="6" t="s">
-        <v>455</v>
+        <v>597</v>
       </c>
       <c r="C85" s="6" t="s">
-        <v>456</v>
+        <v>598</v>
       </c>
     </row>
     <row r="86" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B86" s="6" t="s">
-        <v>457</v>
+        <v>599</v>
       </c>
       <c r="C86" s="6" t="s">
-        <v>458</v>
+        <v>600</v>
       </c>
     </row>
     <row r="87" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B87" s="6" t="s">
-        <v>459</v>
+        <v>601</v>
       </c>
       <c r="C87" s="6" t="s">
-        <v>460</v>
+        <v>602</v>
       </c>
     </row>
     <row r="88" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B88" s="6" t="s">
-        <v>461</v>
+        <v>603</v>
       </c>
       <c r="C88" s="6" t="s">
-        <v>462</v>
+        <v>604</v>
       </c>
     </row>
     <row r="89" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B89" s="6" t="s">
-        <v>463</v>
+        <v>605</v>
       </c>
       <c r="C89" s="6" t="s">
-        <v>464</v>
+        <v>606</v>
       </c>
     </row>
     <row r="90" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B90" s="6" t="s">
-        <v>465</v>
+        <v>607</v>
       </c>
       <c r="C90" s="6" t="s">
-        <v>466</v>
+        <v>608</v>
       </c>
     </row>
     <row r="91" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B91" s="6" t="s">
-        <v>467</v>
+        <v>609</v>
       </c>
       <c r="C91" s="6" t="s">
-        <v>468</v>
+        <v>610</v>
       </c>
     </row>
     <row r="92" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B92" s="6" t="s">
-        <v>469</v>
+        <v>611</v>
       </c>
       <c r="C92" s="6" t="s">
-        <v>470</v>
+        <v>612</v>
       </c>
     </row>
     <row r="93" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B93" s="6" t="s">
-        <v>471</v>
+        <v>613</v>
       </c>
       <c r="C93" s="6" t="s">
-        <v>472</v>
+        <v>614</v>
       </c>
     </row>
     <row r="94" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B94" s="6" t="s">
-        <v>473</v>
+        <v>615</v>
       </c>
       <c r="C94" s="6" t="s">
-        <v>474</v>
+        <v>616</v>
       </c>
     </row>
     <row r="95" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B95" s="6" t="s">
-        <v>475</v>
+        <v>617</v>
       </c>
       <c r="C95" s="6" t="s">
-        <v>476</v>
+        <v>618</v>
       </c>
     </row>
     <row r="96" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B96" s="6" t="s">
-        <v>477</v>
+        <v>619</v>
       </c>
       <c r="C96" s="6" t="s">
-        <v>478</v>
+        <v>620</v>
       </c>
     </row>
     <row r="97" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B97" s="6" t="s">
-        <v>479</v>
+        <v>621</v>
       </c>
       <c r="C97" s="6" t="s">
-        <v>480</v>
+        <v>622</v>
       </c>
     </row>
     <row r="98" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B98" s="6" t="s">
-        <v>481</v>
+        <v>623</v>
       </c>
       <c r="C98" s="6" t="s">
-        <v>482</v>
+        <v>624</v>
       </c>
     </row>
     <row r="99" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B99" s="6" t="s">
-        <v>483</v>
+        <v>625</v>
       </c>
       <c r="C99" s="6" t="s">
-        <v>484</v>
+        <v>626</v>
       </c>
     </row>
     <row r="100" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B100" s="6" t="s">
-        <v>485</v>
+        <v>627</v>
       </c>
       <c r="C100" s="6" t="s">
-        <v>486</v>
+        <v>628</v>
       </c>
     </row>
     <row r="101" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B101" s="6" t="s">
-        <v>487</v>
+        <v>629</v>
       </c>
       <c r="C101" s="6" t="s">
-        <v>206</v>
+        <v>348</v>
       </c>
     </row>
     <row r="102" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B102" s="6" t="s">
-        <v>488</v>
+        <v>630</v>
       </c>
       <c r="C102" s="6" t="s">
-        <v>489</v>
+        <v>631</v>
       </c>
     </row>
     <row r="103" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B103" s="6" t="s">
-        <v>490</v>
+        <v>632</v>
       </c>
       <c r="C103" s="6" t="s">
-        <v>491</v>
+        <v>633</v>
       </c>
     </row>
     <row r="104" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B104" s="6" t="s">
-        <v>492</v>
+        <v>634</v>
       </c>
       <c r="C104" s="6" t="s">
-        <v>493</v>
+        <v>635</v>
       </c>
     </row>
     <row r="105" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B105" s="6" t="s">
-        <v>494</v>
+        <v>636</v>
       </c>
       <c r="C105" s="6" t="s">
-        <v>208</v>
+        <v>350</v>
       </c>
     </row>
     <row r="106" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B106" s="6" t="s">
-        <v>495</v>
+        <v>637</v>
       </c>
       <c r="C106" s="6" t="s">
-        <v>496</v>
+        <v>638</v>
       </c>
     </row>
     <row r="107" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B107" s="6" t="s">
-        <v>497</v>
+        <v>639</v>
       </c>
       <c r="C107" s="6" t="s">
-        <v>281</v>
+        <v>423</v>
       </c>
     </row>
     <row r="108" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B108" s="6" t="s">
-        <v>498</v>
+        <v>640</v>
       </c>
       <c r="C108" s="6" t="s">
-        <v>499</v>
+        <v>641</v>
       </c>
     </row>
     <row r="109" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B109" s="6" t="s">
-        <v>500</v>
+        <v>642</v>
       </c>
       <c r="C109" s="6" t="s">
-        <v>501</v>
+        <v>643</v>
       </c>
     </row>
     <row r="110" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B110" s="6" t="s">
-        <v>502</v>
+        <v>644</v>
       </c>
       <c r="C110" s="6" t="s">
-        <v>503</v>
+        <v>645</v>
       </c>
     </row>
     <row r="111" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B111" s="6" t="s">
-        <v>504</v>
+        <v>646</v>
       </c>
       <c r="C111" s="6" t="s">
-        <v>505</v>
+        <v>647</v>
       </c>
     </row>
     <row r="112" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B112" s="6" t="s">
-        <v>246</v>
+        <v>388</v>
       </c>
       <c r="C112" s="6" t="s">
-        <v>506</v>
+        <v>648</v>
       </c>
     </row>
     <row r="113" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B113" s="6" t="s">
-        <v>507</v>
+        <v>649</v>
       </c>
       <c r="C113" s="6" t="s">
-        <v>508</v>
+        <v>650</v>
       </c>
     </row>
     <row r="114" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B114" s="6" t="s">
-        <v>509</v>
+        <v>651</v>
       </c>
       <c r="C114" s="6" t="s">
-        <v>510</v>
+        <v>652</v>
       </c>
     </row>
     <row r="115" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B115" s="6" t="s">
-        <v>511</v>
+        <v>653</v>
       </c>
       <c r="C115" s="6" t="s">
-        <v>450</v>
+        <v>592</v>
       </c>
     </row>
     <row r="116" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B116" s="6" t="s">
-        <v>512</v>
+        <v>654</v>
       </c>
       <c r="C116" s="6" t="s">
-        <v>513</v>
+        <v>655</v>
       </c>
     </row>
     <row r="117" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B117" s="6" t="s">
-        <v>514</v>
+        <v>656</v>
       </c>
       <c r="C117" s="6" t="s">
-        <v>241</v>
+        <v>383</v>
       </c>
     </row>
     <row r="118" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B118" s="6" t="s">
-        <v>515</v>
+        <v>657</v>
       </c>
       <c r="C118" s="6" t="s">
-        <v>225</v>
+        <v>367</v>
       </c>
     </row>
     <row r="119" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B119" s="6" t="s">
-        <v>516</v>
+        <v>658</v>
       </c>
       <c r="C119" s="6" t="s">
-        <v>517</v>
+        <v>659</v>
       </c>
     </row>
     <row r="120" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B120" s="6" t="s">
-        <v>518</v>
+        <v>660</v>
       </c>
       <c r="C120" s="6" t="s">
-        <v>519</v>
+        <v>661</v>
       </c>
     </row>
     <row r="121" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B121" s="6" t="s">
-        <v>520</v>
+        <v>662</v>
       </c>
       <c r="C121" s="6" t="s">
-        <v>521</v>
+        <v>663</v>
       </c>
     </row>
     <row r="122" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B122" s="6" t="s">
-        <v>522</v>
+        <v>664</v>
       </c>
       <c r="C122" s="6" t="s">
-        <v>523</v>
+        <v>665</v>
       </c>
     </row>
     <row r="123" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B123" s="6" t="s">
-        <v>524</v>
+        <v>666</v>
       </c>
       <c r="C123" s="6" t="s">
-        <v>525</v>
+        <v>667</v>
       </c>
     </row>
     <row r="124" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B124" s="6" t="s">
-        <v>526</v>
+        <v>668</v>
       </c>
       <c r="C124" s="6" t="s">
-        <v>527</v>
+        <v>669</v>
       </c>
     </row>
     <row r="125" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B125" s="6" t="s">
-        <v>528</v>
+        <v>670</v>
       </c>
       <c r="C125" s="6" t="s">
-        <v>529</v>
+        <v>671</v>
       </c>
     </row>
     <row r="126" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B126" s="6" t="s">
-        <v>530</v>
+        <v>672</v>
       </c>
       <c r="C126" s="6" t="s">
-        <v>531</v>
+        <v>673</v>
       </c>
     </row>
     <row r="127" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B127" s="6" t="s">
-        <v>532</v>
+        <v>674</v>
       </c>
       <c r="C127" s="6" t="s">
-        <v>533</v>
+        <v>675</v>
       </c>
     </row>
     <row r="128" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B128" s="6" t="s">
-        <v>534</v>
+        <v>676</v>
       </c>
       <c r="C128" s="6" t="s">
-        <v>535</v>
+        <v>677</v>
       </c>
     </row>
     <row r="129" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B129" s="6" t="s">
-        <v>536</v>
+        <v>678</v>
       </c>
       <c r="C129" s="6" t="s">
-        <v>537</v>
+        <v>679</v>
       </c>
     </row>
     <row r="130" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B130" s="6" t="s">
-        <v>538</v>
+        <v>680</v>
       </c>
       <c r="C130" s="6" t="s">
-        <v>539</v>
+        <v>681</v>
       </c>
     </row>
     <row r="131" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B131" s="6" t="s">
-        <v>540</v>
+        <v>682</v>
       </c>
       <c r="C131" s="6" t="s">
-        <v>541</v>
+        <v>683</v>
       </c>
     </row>
     <row r="132" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B132" s="6" t="s">
-        <v>542</v>
+        <v>684</v>
       </c>
       <c r="C132" s="6" t="s">
-        <v>543</v>
+        <v>685</v>
       </c>
     </row>
     <row r="133" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B133" s="6" t="s">
-        <v>544</v>
+        <v>686</v>
       </c>
       <c r="C133" s="6" t="s">
-        <v>545</v>
+        <v>687</v>
       </c>
     </row>
     <row r="134" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B134" s="6" t="s">
-        <v>546</v>
+        <v>688</v>
       </c>
       <c r="C134" s="6" t="s">
-        <v>547</v>
+        <v>689</v>
       </c>
     </row>
     <row r="135" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B135" s="6" t="s">
-        <v>548</v>
+        <v>690</v>
       </c>
       <c r="C135" s="6" t="s">
-        <v>549</v>
+        <v>691</v>
       </c>
     </row>
     <row r="136" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B136" s="6" t="s">
-        <v>550</v>
+        <v>692</v>
       </c>
       <c r="C136" s="6" t="s">
-        <v>551</v>
+        <v>693</v>
       </c>
     </row>
     <row r="137" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B137" s="6" t="s">
-        <v>552</v>
+        <v>694</v>
       </c>
       <c r="C137" s="6" t="s">
-        <v>553</v>
+        <v>695</v>
       </c>
     </row>
     <row r="138" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B138" s="6" t="s">
-        <v>554</v>
+        <v>696</v>
       </c>
       <c r="C138" s="6" t="s">
-        <v>555</v>
+        <v>697</v>
       </c>
     </row>
     <row r="139" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B139" s="6" t="s">
-        <v>556</v>
+        <v>698</v>
       </c>
       <c r="C139" s="6" t="s">
-        <v>557</v>
+        <v>699</v>
       </c>
     </row>
     <row r="140" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B140" s="6" t="s">
-        <v>558</v>
+        <v>700</v>
       </c>
       <c r="C140" s="6" t="s">
-        <v>559</v>
+        <v>701</v>
       </c>
     </row>
     <row r="141" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B141" s="6" t="s">
-        <v>560</v>
+        <v>702</v>
       </c>
       <c r="C141" s="6" t="s">
-        <v>561</v>
+        <v>703</v>
       </c>
     </row>
     <row r="142" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B142" s="6" t="s">
-        <v>562</v>
+        <v>704</v>
       </c>
       <c r="C142" s="6" t="s">
-        <v>563</v>
+        <v>705</v>
       </c>
     </row>
     <row r="143" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B143" s="6" t="s">
-        <v>564</v>
+        <v>706</v>
       </c>
       <c r="C143" s="6" t="s">
-        <v>565</v>
+        <v>707</v>
       </c>
     </row>
     <row r="144" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B144" s="6" t="s">
-        <v>566</v>
+        <v>708</v>
       </c>
       <c r="C144" s="6" t="s">
-        <v>567</v>
+        <v>709</v>
       </c>
     </row>
     <row r="145" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B145" s="6" t="s">
-        <v>568</v>
+        <v>710</v>
       </c>
       <c r="C145" s="6" t="s">
-        <v>569</v>
+        <v>711</v>
       </c>
     </row>
     <row r="146" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B146" s="6" t="s">
-        <v>570</v>
+        <v>712</v>
       </c>
       <c r="C146" s="6" t="s">
-        <v>571</v>
+        <v>713</v>
       </c>
     </row>
     <row r="147" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B147" s="6" t="s">
-        <v>572</v>
+        <v>714</v>
       </c>
       <c r="C147" s="6" t="s">
-        <v>573</v>
+        <v>715</v>
       </c>
     </row>
     <row r="148" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B148" s="6" t="s">
-        <v>574</v>
+        <v>716</v>
       </c>
       <c r="C148" s="6" t="s">
-        <v>575</v>
+        <v>717</v>
       </c>
     </row>
     <row r="149" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B149" s="6" t="s">
-        <v>576</v>
+        <v>718</v>
       </c>
       <c r="C149" s="6" t="s">
-        <v>577</v>
+        <v>719</v>
       </c>
     </row>
     <row r="150" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B150" s="6" t="s">
-        <v>578</v>
+        <v>720</v>
       </c>
       <c r="C150" s="6" t="s">
-        <v>579</v>
+        <v>721</v>
       </c>
     </row>
     <row r="151" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B151" s="6" t="s">
-        <v>580</v>
+        <v>722</v>
       </c>
       <c r="C151" s="6" t="s">
-        <v>581</v>
+        <v>723</v>
       </c>
     </row>
     <row r="152" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B152" s="6" t="s">
-        <v>582</v>
+        <v>724</v>
       </c>
       <c r="C152" s="6" t="s">
-        <v>583</v>
+        <v>725</v>
       </c>
     </row>
     <row r="153" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B153" s="6" t="s">
-        <v>584</v>
+        <v>726</v>
       </c>
       <c r="C153" s="6" t="s">
-        <v>585</v>
+        <v>727</v>
       </c>
     </row>
     <row r="154" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B154" s="6" t="s">
-        <v>586</v>
+        <v>728</v>
       </c>
       <c r="C154" s="6" t="s">
-        <v>587</v>
+        <v>729</v>
       </c>
     </row>
     <row r="155" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B155" s="6" t="s">
-        <v>588</v>
+        <v>730</v>
       </c>
       <c r="C155" s="6" t="s">
-        <v>589</v>
+        <v>731</v>
       </c>
     </row>
     <row r="156" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B156" s="6" t="s">
-        <v>590</v>
+        <v>732</v>
       </c>
       <c r="C156" s="6" t="s">
-        <v>591</v>
+        <v>733</v>
       </c>
     </row>
     <row r="157" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B157" s="6" t="s">
-        <v>592</v>
+        <v>734</v>
       </c>
       <c r="C157" s="6" t="s">
-        <v>593</v>
+        <v>735</v>
       </c>
     </row>
     <row r="158" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B158" s="6" t="s">
-        <v>594</v>
+        <v>736</v>
       </c>
       <c r="C158" s="6" t="s">
-        <v>595</v>
+        <v>737</v>
       </c>
     </row>
     <row r="159" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B159" s="6" t="s">
-        <v>596</v>
+        <v>738</v>
       </c>
       <c r="C159" s="6" t="s">
-        <v>597</v>
+        <v>739</v>
       </c>
     </row>
     <row r="160" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B160" s="6" t="s">
-        <v>598</v>
+        <v>740</v>
       </c>
       <c r="C160" s="6" t="s">
-        <v>599</v>
+        <v>741</v>
       </c>
     </row>
     <row r="161" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B161" s="6" t="s">
-        <v>600</v>
+        <v>742</v>
       </c>
       <c r="C161" s="6" t="s">
-        <v>601</v>
+        <v>743</v>
       </c>
     </row>
     <row r="162" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B162" s="6" t="s">
-        <v>602</v>
+        <v>744</v>
       </c>
       <c r="C162" s="6" t="s">
-        <v>603</v>
+        <v>745</v>
       </c>
     </row>
     <row r="163" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B163" s="6" t="s">
-        <v>604</v>
+        <v>746</v>
       </c>
       <c r="C163" s="6" t="s">
-        <v>605</v>
+        <v>747</v>
       </c>
     </row>
     <row r="164" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B164" s="6" t="s">
-        <v>606</v>
+        <v>748</v>
       </c>
       <c r="C164" s="6" t="s">
-        <v>607</v>
+        <v>749</v>
       </c>
     </row>
     <row r="165" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B165" s="6" t="s">
-        <v>608</v>
+        <v>750</v>
       </c>
       <c r="C165" s="6" t="s">
-        <v>609</v>
+        <v>751</v>
       </c>
     </row>
     <row r="166" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B166" s="6" t="s">
-        <v>610</v>
+        <v>752</v>
       </c>
       <c r="C166" s="6" t="s">
-        <v>611</v>
+        <v>753</v>
       </c>
     </row>
     <row r="167" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B167" s="6" t="s">
-        <v>612</v>
+        <v>754</v>
       </c>
       <c r="C167" s="6" t="s">
-        <v>613</v>
+        <v>755</v>
       </c>
     </row>
     <row r="168" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B168" s="6" t="s">
-        <v>614</v>
+        <v>756</v>
       </c>
       <c r="C168" s="6" t="s">
-        <v>615</v>
+        <v>757</v>
       </c>
     </row>
     <row r="169" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B169" s="6" t="s">
-        <v>616</v>
+        <v>758</v>
       </c>
       <c r="C169" s="6" t="s">
-        <v>617</v>
+        <v>759</v>
       </c>
     </row>
     <row r="170" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B170" s="6" t="s">
-        <v>618</v>
+        <v>760</v>
       </c>
       <c r="C170" s="6" t="s">
-        <v>619</v>
+        <v>761</v>
       </c>
     </row>
     <row r="171" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B171" s="6" t="s">
-        <v>620</v>
+        <v>762</v>
       </c>
       <c r="C171" s="6" t="s">
-        <v>621</v>
+        <v>763</v>
       </c>
     </row>
     <row r="172" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B172" s="6" t="s">
-        <v>622</v>
+        <v>764</v>
       </c>
       <c r="C172" s="6" t="s">
-        <v>623</v>
+        <v>765</v>
       </c>
     </row>
     <row r="173" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B173" s="6" t="s">
-        <v>624</v>
+        <v>766</v>
       </c>
       <c r="C173" s="6" t="s">
-        <v>625</v>
+        <v>767</v>
       </c>
     </row>
     <row r="174" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B174" s="6" t="s">
-        <v>626</v>
+        <v>768</v>
       </c>
       <c r="C174" s="6" t="s">
-        <v>627</v>
+        <v>769</v>
       </c>
     </row>
     <row r="175" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B175" s="6" t="s">
-        <v>251</v>
+        <v>393</v>
       </c>
       <c r="C175" s="6" t="s">
-        <v>628</v>
+        <v>770</v>
       </c>
     </row>
     <row r="176" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B176" s="6" t="s">
-        <v>629</v>
+        <v>771</v>
       </c>
       <c r="C176" s="6" t="s">
-        <v>630</v>
+        <v>772</v>
       </c>
     </row>
     <row r="177" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B177" s="6" t="s">
-        <v>631</v>
+        <v>773</v>
       </c>
       <c r="C177" s="6" t="s">
-        <v>632</v>
+        <v>774</v>
       </c>
     </row>
     <row r="178" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B178" s="6" t="s">
-        <v>633</v>
+        <v>775</v>
       </c>
       <c r="C178" s="6" t="s">
-        <v>634</v>
+        <v>776</v>
       </c>
     </row>
     <row r="179" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B179" s="6" t="s">
-        <v>635</v>
+        <v>777</v>
       </c>
       <c r="C179" s="6" t="s">
-        <v>636</v>
+        <v>778</v>
       </c>
     </row>
     <row r="180" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B180" s="6" t="s">
-        <v>637</v>
+        <v>779</v>
       </c>
       <c r="C180" s="6" t="s">
-        <v>638</v>
+        <v>780</v>
       </c>
     </row>
     <row r="181" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B181" s="6" t="s">
-        <v>639</v>
+        <v>781</v>
       </c>
       <c r="C181" s="6" t="s">
-        <v>640</v>
+        <v>782</v>
       </c>
     </row>
     <row r="182" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B182" s="6" t="s">
-        <v>641</v>
+        <v>783</v>
       </c>
       <c r="C182" s="6" t="s">
-        <v>642</v>
+        <v>784</v>
       </c>
     </row>
     <row r="183" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B183" s="6" t="s">
-        <v>643</v>
+        <v>785</v>
       </c>
       <c r="C183" s="6" t="s">
-        <v>644</v>
+        <v>786</v>
       </c>
     </row>
     <row r="184" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B184" s="6" t="s">
-        <v>645</v>
+        <v>787</v>
       </c>
       <c r="C184" s="6" t="s">
-        <v>646</v>
+        <v>788</v>
       </c>
     </row>
     <row r="185" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B185" s="6" t="s">
-        <v>647</v>
+        <v>789</v>
       </c>
       <c r="C185" s="6" t="s">
-        <v>648</v>
+        <v>790</v>
       </c>
     </row>
     <row r="186" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B186" s="6" t="s">
-        <v>649</v>
+        <v>791</v>
       </c>
       <c r="C186" s="6" t="s">
-        <v>650</v>
+        <v>792</v>
       </c>
     </row>
     <row r="187" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B187" s="6" t="s">
-        <v>651</v>
+        <v>793</v>
       </c>
       <c r="C187" s="6" t="s">
-        <v>652</v>
+        <v>794</v>
       </c>
     </row>
     <row r="188" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B188" s="6" t="s">
-        <v>653</v>
+        <v>795</v>
       </c>
       <c r="C188" s="6" t="s">
-        <v>654</v>
+        <v>796</v>
       </c>
     </row>
     <row r="189" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B189" s="6" t="s">
-        <v>655</v>
+        <v>797</v>
       </c>
       <c r="C189" s="6" t="s">
-        <v>656</v>
+        <v>798</v>
       </c>
     </row>
     <row r="190" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B190" s="6" t="s">
-        <v>657</v>
+        <v>799</v>
       </c>
       <c r="C190" s="6" t="s">
-        <v>658</v>
+        <v>800</v>
       </c>
     </row>
     <row r="191" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B191" s="6" t="s">
-        <v>659</v>
+        <v>801</v>
       </c>
       <c r="C191" s="6" t="s">
-        <v>660</v>
+        <v>802</v>
       </c>
     </row>
     <row r="192" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B192" s="6" t="s">
-        <v>661</v>
+        <v>803</v>
       </c>
       <c r="C192" s="6" t="s">
-        <v>662</v>
+        <v>804</v>
       </c>
     </row>
     <row r="193" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B193" s="6" t="s">
-        <v>663</v>
+        <v>805</v>
       </c>
       <c r="C193" s="6" t="s">
-        <v>664</v>
+        <v>806</v>
       </c>
     </row>
     <row r="194" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B194" s="6" t="s">
-        <v>665</v>
+        <v>807</v>
       </c>
       <c r="C194" s="6" t="s">
-        <v>666</v>
+        <v>808</v>
       </c>
     </row>
     <row r="195" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B195" s="6" t="s">
-        <v>667</v>
+        <v>809</v>
       </c>
       <c r="C195" s="6" t="s">
-        <v>668</v>
+        <v>810</v>
       </c>
     </row>
     <row r="196" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B196" s="6" t="s">
-        <v>669</v>
+        <v>811</v>
       </c>
       <c r="C196" s="6" t="s">
-        <v>670</v>
+        <v>812</v>
       </c>
     </row>
     <row r="197" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B197" s="6" t="s">
-        <v>671</v>
+        <v>813</v>
       </c>
       <c r="C197" s="6" t="s">
-        <v>672</v>
+        <v>814</v>
       </c>
     </row>
     <row r="198" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B198" s="6" t="s">
-        <v>673</v>
+        <v>815</v>
       </c>
       <c r="C198" s="6" t="s">
-        <v>674</v>
+        <v>816</v>
       </c>
     </row>
     <row r="199" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B199" s="6" t="s">
-        <v>675</v>
+        <v>817</v>
       </c>
       <c r="C199" s="6" t="s">
-        <v>676</v>
+        <v>818</v>
       </c>
     </row>
     <row r="200" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B200" s="6" t="s">
-        <v>677</v>
+        <v>819</v>
       </c>
       <c r="C200" s="6" t="s">
-        <v>678</v>
+        <v>820</v>
       </c>
     </row>
     <row r="201" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B201" s="6" t="s">
-        <v>679</v>
+        <v>821</v>
       </c>
       <c r="C201" s="6" t="s">
-        <v>680</v>
+        <v>822</v>
       </c>
     </row>
     <row r="202" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B202" s="6" t="s">
-        <v>681</v>
+        <v>823</v>
       </c>
       <c r="C202" s="6" t="s">
-        <v>682</v>
+        <v>824</v>
       </c>
     </row>
     <row r="203" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B203" s="6" t="s">
-        <v>683</v>
+        <v>825</v>
       </c>
       <c r="C203" s="6" t="s">
-        <v>646</v>
+        <v>788</v>
       </c>
     </row>
     <row r="204" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B204" s="6" t="s">
-        <v>684</v>
+        <v>826</v>
       </c>
       <c r="C204" s="6" t="s">
-        <v>685</v>
+        <v>827</v>
       </c>
     </row>
     <row r="205" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B205" s="6" t="s">
-        <v>686</v>
+        <v>828</v>
       </c>
       <c r="C205" s="6" t="s">
-        <v>687</v>
+        <v>829</v>
       </c>
     </row>
     <row r="206" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B206" s="6" t="s">
-        <v>688</v>
+        <v>830</v>
       </c>
       <c r="C206" s="6" t="s">
-        <v>689</v>
+        <v>831</v>
       </c>
     </row>
     <row r="207" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B207" s="6" t="s">
-        <v>690</v>
+        <v>832</v>
       </c>
       <c r="C207" s="6" t="s">
-        <v>691</v>
+        <v>833</v>
       </c>
     </row>
     <row r="208" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B208" s="6" t="s">
-        <v>692</v>
+        <v>834</v>
       </c>
       <c r="C208" s="6" t="s">
-        <v>693</v>
+        <v>835</v>
       </c>
     </row>
     <row r="209" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B209" s="6" t="s">
-        <v>694</v>
+        <v>836</v>
       </c>
       <c r="C209" s="6" t="s">
-        <v>695</v>
+        <v>837</v>
       </c>
     </row>
     <row r="210" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B210" s="6" t="s">
-        <v>696</v>
+        <v>838</v>
       </c>
       <c r="C210" s="6" t="s">
-        <v>697</v>
+        <v>839</v>
       </c>
     </row>
     <row r="211" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B211" s="6" t="s">
-        <v>698</v>
+        <v>840</v>
       </c>
       <c r="C211" s="6" t="s">
-        <v>699</v>
+        <v>841</v>
       </c>
     </row>
     <row r="212" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B212" s="6" t="s">
-        <v>700</v>
+        <v>842</v>
       </c>
       <c r="C212" s="6" t="s">
-        <v>701</v>
+        <v>843</v>
       </c>
     </row>
   </sheetData>
@@ -5669,791 +6053,1359 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="B1:C98"/>
+  <dimension ref="B1:C169"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B1" s="5" t="s">
+      <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="5" t="s">
+      <c r="C1" s="1" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="2" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B2" s="5" t="s">
+      <c r="B2" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="5" t="s">
+      <c r="C2" s="1" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="3" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B3" s="5" t="s">
+      <c r="B3" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="C3" s="5" t="s">
+      <c r="C3" s="1" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="4" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B4" s="5" t="s">
+      <c r="B4" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C4" s="5" t="s">
+      <c r="C4" s="1" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="5" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B5" s="5" t="s">
+      <c r="B5" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C5" s="5" t="s">
+      <c r="C5" s="1" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="6" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B6" s="5" t="s">
+      <c r="B6" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C6" s="5" t="s">
+      <c r="C6" s="1" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="7" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B7" s="5" t="s">
+      <c r="B7" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="C7" s="5" t="s">
+      <c r="C7" s="1" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="8" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B8" s="5" t="s">
+      <c r="B8" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="C8" s="5" t="s">
+      <c r="C8" s="1" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="9" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B9" s="5" t="s">
+      <c r="B9" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="C9" s="5" t="s">
+      <c r="C9" s="1" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="10" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B10" s="5" t="s">
+      <c r="B10" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="C10" s="5" t="s">
+      <c r="C10" s="1" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="11" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B11" s="5" t="s">
+      <c r="B11" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="C11" s="5" t="s">
+      <c r="C11" s="1" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="12" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B12" s="5" t="s">
+      <c r="B12" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="C12" s="5" t="s">
+      <c r="C12" s="1" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="13" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B13" s="5" t="s">
+      <c r="B13" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="C13" s="5" t="s">
+      <c r="C13" s="1" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="14" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B14" s="5" t="s">
+      <c r="B14" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="C14" s="5" t="s">
+      <c r="C14" s="1" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="15" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B15" s="5" t="s">
+      <c r="B15" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="C15" s="5" t="s">
+      <c r="C15" s="1" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="16" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B16" s="5" t="s">
+      <c r="B16" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="C16" s="5" t="s">
+      <c r="C16" s="1" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="17" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B17" s="5" t="s">
+      <c r="B17" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="C17" s="5" t="s">
+      <c r="C17" s="1" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="18" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B18" s="5" t="s">
+      <c r="B18" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="C18" s="5" t="s">
+      <c r="C18" s="1" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="19" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B19" s="5" t="s">
+      <c r="B19" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="C19" s="5" t="s">
+      <c r="C19" s="1" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="20" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B20" s="5" t="s">
+      <c r="B20" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="C20" s="5" t="s">
+      <c r="C20" s="1" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="21" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B21" s="5" t="s">
+      <c r="B21" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="C21" s="5" t="s">
+      <c r="C21" s="1" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="22" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B22" s="5" t="s">
+      <c r="B22" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="C22" s="5" t="s">
+      <c r="C22" s="1" t="s">
         <v>43</v>
       </c>
     </row>
     <row r="23" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B23" s="5" t="s">
+      <c r="B23" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="C23" s="5" t="s">
+      <c r="C23" s="1" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="24" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B24" s="5" t="s">
+      <c r="B24" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="C24" s="5" t="s">
+      <c r="C24" s="1" t="s">
         <v>47</v>
       </c>
     </row>
     <row r="25" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B25" s="5" t="s">
+      <c r="B25" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="C25" s="5" t="s">
+      <c r="C25" s="1" t="s">
         <v>49</v>
       </c>
     </row>
     <row r="26" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B26" s="5" t="s">
+      <c r="B26" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="C26" s="5" t="s">
+      <c r="C26" s="1" t="s">
         <v>51</v>
       </c>
     </row>
     <row r="27" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B27" s="5" t="s">
+      <c r="B27" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="C27" s="5" t="s">
+      <c r="C27" s="1" t="s">
         <v>53</v>
       </c>
     </row>
     <row r="28" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B28" s="5" t="s">
+      <c r="B28" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="C28" s="5" t="s">
+      <c r="C28" s="1" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="29" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B29" s="5" t="s">
+      <c r="B29" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="C29" s="5" t="s">
+      <c r="C29" s="1" t="s">
         <v>57</v>
       </c>
     </row>
     <row r="30" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B30" s="5" t="s">
+      <c r="B30" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="C30" s="5" t="s">
+      <c r="C30" s="1" t="s">
         <v>59</v>
       </c>
     </row>
     <row r="31" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B31" s="5" t="s">
+      <c r="B31" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="C31" s="5" t="s">
+      <c r="C31" s="1" t="s">
         <v>61</v>
       </c>
     </row>
     <row r="32" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B32" s="5" t="s">
+      <c r="B32" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="C32" s="5" t="s">
+      <c r="C32" s="1" t="s">
         <v>63</v>
       </c>
     </row>
     <row r="33" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B33" s="5" t="s">
+      <c r="B33" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="C33" s="5" t="s">
+      <c r="C33" s="1" t="s">
         <v>65</v>
       </c>
     </row>
     <row r="34" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B34" s="5" t="s">
+      <c r="B34" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="C34" s="5" t="s">
+      <c r="C34" s="1" t="s">
         <v>67</v>
       </c>
     </row>
     <row r="35" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B35" s="5" t="s">
+      <c r="B35" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="C35" s="5" t="s">
+      <c r="C35" s="1" t="s">
         <v>69</v>
       </c>
     </row>
     <row r="36" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B36" s="5" t="s">
+      <c r="B36" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="C36" s="5" t="s">
+      <c r="C36" s="1" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="37" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B37" s="5" t="s">
+      <c r="B37" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="C37" s="5" t="s">
+      <c r="C37" s="1" t="s">
         <v>73</v>
       </c>
     </row>
     <row r="38" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B38" s="5" t="s">
+      <c r="B38" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="C38" s="5" t="s">
+      <c r="C38" s="1" t="s">
         <v>75</v>
       </c>
     </row>
     <row r="39" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B39" s="5" t="s">
+      <c r="B39" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="C39" s="5" t="s">
+      <c r="C39" s="1" t="s">
         <v>77</v>
       </c>
     </row>
     <row r="40" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B40" s="5" t="s">
+      <c r="B40" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="C40" s="5" t="s">
+      <c r="C40" s="1" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="41" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B41" s="5" t="s">
+      <c r="B41" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="C41" s="5" t="s">
+      <c r="C41" s="1" t="s">
         <v>81</v>
       </c>
     </row>
     <row r="42" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B42" s="5" t="s">
+      <c r="B42" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="C42" s="5" t="s">
+      <c r="C42" s="1" t="s">
         <v>83</v>
       </c>
     </row>
     <row r="43" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B43" s="5" t="s">
+      <c r="B43" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="C43" s="5" t="s">
+      <c r="C43" s="1" t="s">
         <v>85</v>
       </c>
     </row>
     <row r="44" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B44" s="5" t="s">
+      <c r="B44" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="C44" s="5" t="s">
+      <c r="C44" s="1" t="s">
         <v>87</v>
       </c>
     </row>
     <row r="45" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B45" s="5" t="s">
+      <c r="B45" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="C45" s="5" t="s">
+      <c r="C45" s="1" t="s">
         <v>89</v>
       </c>
     </row>
     <row r="46" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B46" s="5" t="s">
+      <c r="B46" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="C46" s="5" t="s">
+      <c r="C46" s="1" t="s">
         <v>91</v>
       </c>
     </row>
     <row r="47" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B47" s="5" t="s">
+      <c r="B47" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="C47" s="5" t="s">
+      <c r="C47" s="1" t="s">
         <v>93</v>
       </c>
     </row>
     <row r="48" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B48" s="5" t="s">
+      <c r="B48" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="C48" s="5" t="s">
+      <c r="C48" s="1" t="s">
         <v>95</v>
       </c>
     </row>
     <row r="49" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B49" s="5" t="s">
+      <c r="B49" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="C49" s="5" t="s">
+      <c r="C49" s="1" t="s">
         <v>97</v>
       </c>
     </row>
     <row r="50" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B50" s="5" t="s">
+      <c r="B50" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="C50" s="5" t="s">
+      <c r="C50" s="1" t="s">
         <v>99</v>
       </c>
     </row>
     <row r="51" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B51" s="5" t="s">
+      <c r="B51" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="C51" s="5" t="s">
+      <c r="C51" s="1" t="s">
         <v>101</v>
       </c>
     </row>
     <row r="52" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B52" s="5" t="s">
+      <c r="B52" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="C52" s="5" t="s">
+      <c r="C52" s="1" t="s">
         <v>103</v>
       </c>
     </row>
     <row r="53" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B53" s="5" t="s">
+      <c r="B53" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="C53" s="5" t="s">
+      <c r="C53" s="1" t="s">
         <v>105</v>
       </c>
     </row>
     <row r="54" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B54" s="5" t="s">
+      <c r="B54" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="C54" s="5" t="s">
+      <c r="C54" s="1" t="s">
         <v>107</v>
       </c>
     </row>
     <row r="55" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B55" s="5" t="s">
+      <c r="B55" s="1" t="s">
         <v>108</v>
       </c>
-      <c r="C55" s="5" t="s">
+      <c r="C55" s="1" t="s">
         <v>109</v>
       </c>
     </row>
     <row r="56" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B56" s="5" t="s">
+      <c r="B56" s="1" t="s">
         <v>110</v>
       </c>
-      <c r="C56" s="5" t="s">
+      <c r="C56" s="1" t="s">
         <v>111</v>
       </c>
     </row>
     <row r="57" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B57" s="5" t="s">
+      <c r="B57" s="1" t="s">
         <v>112</v>
       </c>
-      <c r="C57" s="5" t="s">
+      <c r="C57" s="1" t="s">
         <v>113</v>
       </c>
     </row>
     <row r="58" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B58" s="5" t="s">
+      <c r="B58" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="C58" s="5" t="s">
+      <c r="C58" s="1" t="s">
         <v>115</v>
       </c>
     </row>
     <row r="59" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B59" s="5" t="s">
+      <c r="B59" s="1" t="s">
         <v>116</v>
       </c>
-      <c r="C59" s="5" t="s">
+      <c r="C59" s="1" t="s">
         <v>117</v>
       </c>
     </row>
     <row r="60" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B60" s="5" t="s">
+      <c r="B60" s="1" t="s">
         <v>118</v>
       </c>
-      <c r="C60" s="5" t="s">
+      <c r="C60" s="1" t="s">
         <v>119</v>
       </c>
     </row>
     <row r="61" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B61" s="5" t="s">
+      <c r="B61" s="1" t="s">
         <v>120</v>
       </c>
-      <c r="C61" s="5" t="s">
+      <c r="C61" s="1" t="s">
         <v>121</v>
       </c>
     </row>
     <row r="62" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B62" s="5" t="s">
+      <c r="B62" s="1" t="s">
         <v>122</v>
       </c>
-      <c r="C62" s="5" t="s">
+      <c r="C62" s="1" t="s">
         <v>123</v>
       </c>
     </row>
     <row r="63" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B63" s="5" t="s">
+      <c r="B63" s="1" t="s">
         <v>124</v>
       </c>
-      <c r="C63" s="5" t="s">
+      <c r="C63" s="1" t="s">
         <v>125</v>
       </c>
     </row>
     <row r="64" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B64" s="5" t="s">
+      <c r="B64" s="1" t="s">
         <v>126</v>
       </c>
-      <c r="C64" s="5" t="s">
+      <c r="C64" s="1" t="s">
         <v>127</v>
       </c>
     </row>
     <row r="65" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B65" s="5" t="s">
+      <c r="B65" s="1" t="s">
         <v>128</v>
       </c>
-      <c r="C65" s="5" t="s">
+      <c r="C65" s="1" t="s">
         <v>129</v>
       </c>
     </row>
     <row r="66" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B66" s="5" t="s">
+      <c r="B66" s="1" t="s">
         <v>130</v>
       </c>
-      <c r="C66" s="5" t="s">
+      <c r="C66" s="1" t="s">
         <v>131</v>
       </c>
     </row>
     <row r="67" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B67" s="5" t="s">
+      <c r="B67" s="1" t="s">
         <v>132</v>
       </c>
-      <c r="C67" s="5" t="s">
+      <c r="C67" s="1" t="s">
         <v>133</v>
       </c>
     </row>
     <row r="68" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B68" s="5" t="s">
+      <c r="B68" s="1" t="s">
         <v>134</v>
       </c>
-      <c r="C68" s="5" t="s">
+      <c r="C68" s="1" t="s">
         <v>135</v>
       </c>
     </row>
     <row r="69" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B69" s="5" t="s">
+      <c r="B69" s="1" t="s">
         <v>136</v>
       </c>
-      <c r="C69" s="5" t="s">
+      <c r="C69" s="1" t="s">
         <v>137</v>
       </c>
     </row>
     <row r="70" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B70" s="5" t="s">
+      <c r="B70" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="C70" s="5" t="s">
+      <c r="C70" s="1" t="s">
         <v>139</v>
       </c>
     </row>
     <row r="71" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B71" s="5" t="s">
+      <c r="B71" s="1" t="s">
         <v>140</v>
       </c>
-      <c r="C71" s="5" t="s">
+      <c r="C71" s="1" t="s">
         <v>141</v>
       </c>
     </row>
     <row r="72" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B72" s="5" t="s">
+      <c r="B72" s="1" t="s">
         <v>142</v>
       </c>
-      <c r="C72" s="5" t="s">
+      <c r="C72" s="1" t="s">
         <v>143</v>
       </c>
     </row>
     <row r="73" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B73" s="5" t="s">
+      <c r="B73" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="C73" s="5" t="s">
+      <c r="C73" s="1" t="s">
         <v>145</v>
       </c>
     </row>
     <row r="74" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B74" s="5" t="s">
+      <c r="B74" s="1" t="s">
         <v>146</v>
       </c>
-      <c r="C74" s="5" t="s">
+      <c r="C74" s="1" t="s">
         <v>147</v>
       </c>
     </row>
     <row r="75" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B75" s="5" t="s">
+      <c r="B75" s="1" t="s">
         <v>148</v>
       </c>
-      <c r="C75" s="5" t="s">
+      <c r="C75" s="1" t="s">
         <v>149</v>
       </c>
     </row>
     <row r="76" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B76" s="5" t="s">
+      <c r="B76" s="1" t="s">
         <v>150</v>
       </c>
-      <c r="C76" s="5" t="s">
+      <c r="C76" s="1" t="s">
         <v>151</v>
       </c>
     </row>
     <row r="77" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B77" s="5" t="s">
+      <c r="B77" s="1" t="s">
         <v>152</v>
       </c>
-      <c r="C77" s="5" t="s">
+      <c r="C77" s="1" t="s">
         <v>153</v>
       </c>
     </row>
     <row r="78" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B78" s="5" t="s">
+      <c r="B78" s="1" t="s">
         <v>154</v>
       </c>
-      <c r="C78" s="5" t="s">
+      <c r="C78" s="1" t="s">
         <v>155</v>
       </c>
     </row>
     <row r="79" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B79" s="5" t="s">
+      <c r="B79" s="1" t="s">
         <v>156</v>
       </c>
-      <c r="C79" s="5" t="s">
+      <c r="C79" s="1" t="s">
         <v>157</v>
       </c>
     </row>
     <row r="80" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B80" s="5" t="s">
+      <c r="B80" s="1" t="s">
         <v>158</v>
       </c>
-      <c r="C80" s="5" t="s">
+      <c r="C80" s="1" t="s">
         <v>159</v>
       </c>
     </row>
     <row r="81" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B81" s="5" t="s">
+      <c r="B81" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="C81" s="5" t="s">
+      <c r="C81" s="1" t="s">
         <v>161</v>
       </c>
     </row>
     <row r="82" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B82" s="5" t="s">
+      <c r="B82" s="1" t="s">
         <v>162</v>
       </c>
-      <c r="C82" s="5" t="s">
+      <c r="C82" s="1" t="s">
         <v>163</v>
       </c>
     </row>
     <row r="83" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B83" s="5" t="s">
+      <c r="B83" s="1" t="s">
         <v>164</v>
       </c>
-      <c r="C83" s="5" t="s">
+      <c r="C83" s="1" t="s">
         <v>165</v>
       </c>
     </row>
     <row r="84" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B84" s="5" t="s">
+      <c r="B84" s="1" t="s">
         <v>166</v>
       </c>
-      <c r="C84" s="5" t="s">
+      <c r="C84" s="1" t="s">
         <v>167</v>
       </c>
     </row>
     <row r="85" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B85" s="5" t="s">
+      <c r="B85" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="C85" s="5" t="s">
+      <c r="C85" s="1" t="s">
         <v>169</v>
       </c>
     </row>
     <row r="86" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B86" s="5" t="s">
+      <c r="B86" s="1" t="s">
         <v>170</v>
       </c>
-      <c r="C86" s="5" t="s">
+      <c r="C86" s="1" t="s">
         <v>171</v>
       </c>
     </row>
     <row r="87" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B87" s="5" t="s">
+      <c r="B87" s="1" t="s">
         <v>172</v>
       </c>
-      <c r="C87" s="5" t="s">
+      <c r="C87" s="1" t="s">
         <v>173</v>
       </c>
     </row>
     <row r="88" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B88" s="5" t="s">
+      <c r="B88" s="1" t="s">
         <v>174</v>
       </c>
-      <c r="C88" s="5" t="s">
+      <c r="C88" s="1" t="s">
         <v>175</v>
       </c>
     </row>
     <row r="89" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B89" s="5" t="s">
+      <c r="B89" s="1" t="s">
         <v>176</v>
       </c>
-      <c r="C89" s="5" t="s">
+      <c r="C89" s="1" t="s">
         <v>177</v>
       </c>
     </row>
     <row r="90" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B90" s="5" t="s">
+      <c r="B90" s="1" t="s">
         <v>178</v>
       </c>
-      <c r="C90" s="5" t="s">
+      <c r="C90" s="1" t="s">
         <v>179</v>
       </c>
     </row>
     <row r="91" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B91" s="5" t="s">
+      <c r="B91" s="1" t="s">
         <v>180</v>
       </c>
-      <c r="C91" s="5" t="s">
+      <c r="C91" s="1" t="s">
         <v>181</v>
       </c>
     </row>
     <row r="92" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B92" s="5" t="s">
+      <c r="B92" s="1" t="s">
         <v>182</v>
       </c>
-      <c r="C92" s="5" t="s">
+      <c r="C92" s="1" t="s">
         <v>183</v>
       </c>
     </row>
     <row r="93" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B93" s="5" t="s">
+      <c r="B93" s="1" t="s">
         <v>184</v>
       </c>
-      <c r="C93" s="5" t="s">
+      <c r="C93" s="1" t="s">
         <v>185</v>
       </c>
     </row>
     <row r="94" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B94" s="5" t="s">
+      <c r="B94" s="1" t="s">
         <v>186</v>
       </c>
-      <c r="C94" s="5" t="s">
+      <c r="C94" s="1" t="s">
         <v>187</v>
       </c>
     </row>
     <row r="95" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B95" s="5" t="s">
+      <c r="B95" s="1" t="s">
         <v>188</v>
       </c>
-      <c r="C95" s="5" t="s">
+      <c r="C95" s="1" t="s">
         <v>189</v>
       </c>
     </row>
     <row r="96" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B96" s="5" t="s">
+      <c r="B96" s="1" t="s">
         <v>190</v>
       </c>
-      <c r="C96" s="5" t="s">
+      <c r="C96" s="1" t="s">
         <v>191</v>
       </c>
     </row>
     <row r="97" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B97" s="5" t="s">
+      <c r="B97" s="1" t="s">
         <v>192</v>
       </c>
-      <c r="C97" s="5" t="s">
+      <c r="C97" s="1" t="s">
         <v>193</v>
       </c>
     </row>
     <row r="98" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B98" s="5" t="s">
+      <c r="B98" s="1" t="s">
         <v>194</v>
       </c>
-      <c r="C98" s="5" t="s">
+      <c r="C98" s="1" t="s">
         <v>195</v>
+      </c>
+    </row>
+    <row r="99" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B99" s="1" t="s">
+        <v>196</v>
+      </c>
+      <c r="C99" s="1" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="100" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B100" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="C100" s="1" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="101" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B101" s="1" t="s">
+        <v>200</v>
+      </c>
+      <c r="C101" s="1" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="102" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B102" s="1" t="s">
+        <v>202</v>
+      </c>
+      <c r="C102" s="1" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="103" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B103" s="1" t="s">
+        <v>204</v>
+      </c>
+      <c r="C103" s="1" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="104" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B104" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="C104" s="1" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="105" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B105" s="1" t="s">
+        <v>208</v>
+      </c>
+      <c r="C105" s="1" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="106" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B106" s="1" t="s">
+        <v>210</v>
+      </c>
+      <c r="C106" s="1" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="107" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B107" s="1" t="s">
+        <v>212</v>
+      </c>
+      <c r="C107" s="1" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="108" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B108" s="1" t="s">
+        <v>214</v>
+      </c>
+      <c r="C108" s="1" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="109" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B109" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="C109" s="1" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="110" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B110" s="1" t="s">
+        <v>218</v>
+      </c>
+      <c r="C110" s="1" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="111" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B111" s="1" t="s">
+        <v>220</v>
+      </c>
+      <c r="C111" s="1" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="112" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B112" s="1" t="s">
+        <v>222</v>
+      </c>
+      <c r="C112" s="1" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="113" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B113" s="1" t="s">
+        <v>224</v>
+      </c>
+      <c r="C113" s="1" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="114" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B114" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="C114" s="1" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="115" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B115" s="1" t="s">
+        <v>228</v>
+      </c>
+      <c r="C115" s="1" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="116" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B116" s="1" t="s">
+        <v>230</v>
+      </c>
+      <c r="C116" s="1" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="117" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B117" s="1" t="s">
+        <v>232</v>
+      </c>
+      <c r="C117" s="1" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="118" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B118" s="1" t="s">
+        <v>234</v>
+      </c>
+      <c r="C118" s="1" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="119" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B119" s="1" t="s">
+        <v>236</v>
+      </c>
+      <c r="C119" s="1" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="120" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B120" s="1" t="s">
+        <v>238</v>
+      </c>
+      <c r="C120" s="1" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="121" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B121" s="1" t="s">
+        <v>240</v>
+      </c>
+      <c r="C121" s="1" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="122" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B122" s="1" t="s">
+        <v>242</v>
+      </c>
+      <c r="C122" s="1" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="123" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B123" s="1" t="s">
+        <v>244</v>
+      </c>
+      <c r="C123" s="1" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="124" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B124" s="1" t="s">
+        <v>246</v>
+      </c>
+      <c r="C124" s="1" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="125" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B125" s="1" t="s">
+        <v>248</v>
+      </c>
+      <c r="C125" s="1" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="126" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B126" s="1" t="s">
+        <v>250</v>
+      </c>
+      <c r="C126" s="1" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="127" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B127" s="1" t="s">
+        <v>252</v>
+      </c>
+      <c r="C127" s="1" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="128" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B128" s="1" t="s">
+        <v>254</v>
+      </c>
+      <c r="C128" s="1" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="129" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B129" s="1" t="s">
+        <v>256</v>
+      </c>
+      <c r="C129" s="1" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="130" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B130" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="C130" s="1" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="131" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B131" s="1" t="s">
+        <v>260</v>
+      </c>
+      <c r="C131" s="1" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="132" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B132" s="1" t="s">
+        <v>262</v>
+      </c>
+      <c r="C132" s="1" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="133" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B133" s="1" t="s">
+        <v>264</v>
+      </c>
+      <c r="C133" s="1" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="134" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B134" s="1" t="s">
+        <v>266</v>
+      </c>
+      <c r="C134" s="1" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="135" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B135" s="1" t="s">
+        <v>268</v>
+      </c>
+      <c r="C135" s="1" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="136" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B136" s="1" t="s">
+        <v>270</v>
+      </c>
+      <c r="C136" s="1" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="137" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B137" s="1" t="s">
+        <v>272</v>
+      </c>
+      <c r="C137" s="1" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="138" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B138" s="1" t="s">
+        <v>274</v>
+      </c>
+      <c r="C138" s="1" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="139" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B139" s="1" t="s">
+        <v>276</v>
+      </c>
+      <c r="C139" s="1" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="140" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B140" s="1" t="s">
+        <v>278</v>
+      </c>
+      <c r="C140" s="1" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="141" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B141" s="1" t="s">
+        <v>280</v>
+      </c>
+      <c r="C141" s="1" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="142" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B142" s="1" t="s">
+        <v>282</v>
+      </c>
+      <c r="C142" s="1" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="143" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B143" s="1" t="s">
+        <v>284</v>
+      </c>
+      <c r="C143" s="1" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="144" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B144" s="1" t="s">
+        <v>286</v>
+      </c>
+      <c r="C144" s="1" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="145" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B145" s="1" t="s">
+        <v>288</v>
+      </c>
+      <c r="C145" s="1" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="146" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B146" s="1" t="s">
+        <v>290</v>
+      </c>
+      <c r="C146" s="1" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="147" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B147" s="1" t="s">
+        <v>292</v>
+      </c>
+      <c r="C147" s="1" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="148" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B148" s="1" t="s">
+        <v>294</v>
+      </c>
+      <c r="C148" s="1" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="149" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B149" s="1" t="s">
+        <v>296</v>
+      </c>
+      <c r="C149" s="1" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="150" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B150" s="1" t="s">
+        <v>298</v>
+      </c>
+      <c r="C150" s="1" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="151" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B151" s="1" t="s">
+        <v>300</v>
+      </c>
+      <c r="C151" s="1" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="152" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B152" s="1" t="s">
+        <v>302</v>
+      </c>
+      <c r="C152" s="1" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="153" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B153" s="1" t="s">
+        <v>304</v>
+      </c>
+      <c r="C153" s="1" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="154" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B154" s="1" t="s">
+        <v>306</v>
+      </c>
+      <c r="C154" s="1" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="155" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B155" s="1" t="s">
+        <v>308</v>
+      </c>
+      <c r="C155" s="1" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="156" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B156" s="1" t="s">
+        <v>310</v>
+      </c>
+      <c r="C156" s="1" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="157" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B157" s="1" t="s">
+        <v>312</v>
+      </c>
+      <c r="C157" s="1" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="158" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B158" s="1" t="s">
+        <v>314</v>
+      </c>
+      <c r="C158" s="1" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="159" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B159" s="1" t="s">
+        <v>316</v>
+      </c>
+      <c r="C159" s="1" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="160" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B160" s="1" t="s">
+        <v>318</v>
+      </c>
+      <c r="C160" s="1" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="161" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B161" s="1" t="s">
+        <v>320</v>
+      </c>
+      <c r="C161" s="1" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="162" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B162" s="1" t="s">
+        <v>322</v>
+      </c>
+      <c r="C162" s="1" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="163" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B163" s="1" t="s">
+        <v>324</v>
+      </c>
+      <c r="C163" s="1" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="164" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B164" s="1" t="s">
+        <v>326</v>
+      </c>
+      <c r="C164" s="1" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="165" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B165" s="1" t="s">
+        <v>328</v>
+      </c>
+      <c r="C165" s="1" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="166" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B166" s="1" t="s">
+        <v>330</v>
+      </c>
+      <c r="C166" s="1" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="167" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B167" s="1" t="s">
+        <v>332</v>
+      </c>
+      <c r="C167" s="1" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="168" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B168" s="1" t="s">
+        <v>334</v>
+      </c>
+      <c r="C168" s="1" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="169" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B169" s="1" t="s">
+        <v>336</v>
+      </c>
+      <c r="C169" s="1" t="s">
+        <v>337</v>
       </c>
     </row>
   </sheetData>
@@ -6468,547 +7420,547 @@
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="2" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B2" s="1" t="s">
+      <c r="B2" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="1" t="s">
-        <v>734</v>
+      <c r="C2" s="2" t="s">
+        <v>876</v>
       </c>
     </row>
     <row r="3" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B3" s="1" t="s">
-        <v>293</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>735</v>
+      <c r="B3" s="2" t="s">
+        <v>435</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>877</v>
       </c>
     </row>
     <row r="4" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B4" s="1" t="s">
-        <v>295</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>736</v>
+      <c r="B4" s="2" t="s">
+        <v>437</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>878</v>
       </c>
     </row>
     <row r="5" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B5" s="1" t="s">
-        <v>297</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>737</v>
+      <c r="B5" s="2" t="s">
+        <v>439</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>879</v>
       </c>
     </row>
     <row r="6" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B6" s="1" t="s">
-        <v>299</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>738</v>
+      <c r="B6" s="2" t="s">
+        <v>441</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>880</v>
       </c>
     </row>
     <row r="7" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B7" s="1" t="s">
-        <v>301</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>736</v>
+      <c r="B7" s="2" t="s">
+        <v>443</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>878</v>
       </c>
     </row>
     <row r="8" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B8" s="1" t="s">
-        <v>303</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>739</v>
+      <c r="B8" s="2" t="s">
+        <v>445</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>881</v>
       </c>
     </row>
     <row r="9" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B9" s="1" t="s">
-        <v>305</v>
-      </c>
-      <c r="C9" s="1" t="s">
-        <v>740</v>
+      <c r="B9" s="2" t="s">
+        <v>447</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>882</v>
       </c>
     </row>
     <row r="10" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B10" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="C10" s="1" t="s">
-        <v>741</v>
+      <c r="B10" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>883</v>
       </c>
     </row>
     <row r="11" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B11" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="C11" s="1" t="s">
-        <v>742</v>
+      <c r="B11" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>884</v>
       </c>
     </row>
     <row r="12" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B12" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="C12" s="1" t="s">
-        <v>743</v>
+      <c r="B12" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>885</v>
       </c>
     </row>
     <row r="13" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B13" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="C13" s="1" t="s">
-        <v>744</v>
+      <c r="B13" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>886</v>
       </c>
     </row>
     <row r="14" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B14" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="C14" s="1" t="s">
-        <v>745</v>
+      <c r="B14" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>887</v>
       </c>
     </row>
     <row r="15" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B15" s="1" t="s">
-        <v>746</v>
-      </c>
-      <c r="C15" s="1" t="s">
-        <v>747</v>
+      <c r="B15" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>888</v>
       </c>
     </row>
     <row r="16" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B16" s="1" t="s">
-        <v>748</v>
-      </c>
-      <c r="C16" s="1" t="s">
-        <v>749</v>
+      <c r="B16" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>889</v>
       </c>
     </row>
     <row r="17" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B17" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="C17" s="1" t="s">
-        <v>750</v>
+      <c r="B17" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>890</v>
       </c>
     </row>
     <row r="18" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B18" s="1" t="s">
-        <v>751</v>
-      </c>
-      <c r="C18" s="1" t="s">
-        <v>752</v>
+      <c r="B18" s="2" t="s">
+        <v>891</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>892</v>
       </c>
     </row>
     <row r="19" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B19" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="C19" s="1" t="s">
-        <v>753</v>
+      <c r="B19" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>893</v>
       </c>
     </row>
     <row r="20" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B20" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="C20" s="1" t="s">
-        <v>754</v>
+      <c r="B20" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>894</v>
       </c>
     </row>
     <row r="21" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B21" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="C21" s="1" t="s">
-        <v>754</v>
+      <c r="B21" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>894</v>
       </c>
     </row>
     <row r="22" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B22" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="C22" s="1" t="s">
-        <v>754</v>
+      <c r="B22" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>894</v>
       </c>
     </row>
     <row r="23" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B23" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="C23" s="1" t="s">
-        <v>754</v>
+      <c r="B23" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>894</v>
       </c>
     </row>
     <row r="24" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B24" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="C24" s="1" t="s">
-        <v>754</v>
+      <c r="B24" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>894</v>
       </c>
     </row>
     <row r="25" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B25" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="C25" s="1" t="s">
-        <v>755</v>
+      <c r="B25" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>895</v>
       </c>
     </row>
     <row r="26" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B26" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="C26" s="1" t="s">
-        <v>756</v>
+      <c r="B26" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>896</v>
       </c>
     </row>
     <row r="27" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B27" s="1" t="s">
-        <v>757</v>
-      </c>
-      <c r="C27" s="1" t="s">
-        <v>758</v>
+      <c r="B27" s="2" t="s">
+        <v>897</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>898</v>
       </c>
     </row>
     <row r="28" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B28" s="1" t="s">
-        <v>759</v>
-      </c>
-      <c r="C28" s="1" t="s">
-        <v>760</v>
+      <c r="B28" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>899</v>
       </c>
     </row>
     <row r="29" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B29" s="1" t="s">
-        <v>761</v>
-      </c>
-      <c r="C29" s="1" t="s">
-        <v>762</v>
+      <c r="B29" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>900</v>
       </c>
     </row>
     <row r="30" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B30" s="1" t="s">
-        <v>763</v>
-      </c>
-      <c r="C30" s="1" t="s">
-        <v>764</v>
+      <c r="B30" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>901</v>
       </c>
     </row>
     <row r="31" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B31" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="C31" s="1" t="s">
-        <v>765</v>
+      <c r="B31" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="C31" s="2" t="s">
+        <v>902</v>
       </c>
     </row>
     <row r="32" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B32" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="C32" s="1" t="s">
-        <v>766</v>
+      <c r="B32" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="C32" s="2" t="s">
+        <v>903</v>
       </c>
     </row>
     <row r="33" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B33" s="1" t="s">
-        <v>767</v>
-      </c>
-      <c r="C33" s="1" t="s">
-        <v>768</v>
+      <c r="B33" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="C33" s="2" t="s">
+        <v>904</v>
       </c>
     </row>
     <row r="34" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B34" s="1" t="s">
-        <v>769</v>
-      </c>
-      <c r="C34" s="1" t="s">
-        <v>770</v>
+      <c r="B34" s="2" t="s">
+        <v>905</v>
+      </c>
+      <c r="C34" s="2" t="s">
+        <v>906</v>
       </c>
     </row>
     <row r="35" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B35" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="C35" s="1" t="s">
-        <v>771</v>
+      <c r="B35" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="C35" s="2" t="s">
+        <v>907</v>
       </c>
     </row>
     <row r="36" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B36" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="C36" s="1" t="s">
-        <v>772</v>
+      <c r="B36" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="C36" s="2" t="s">
+        <v>908</v>
       </c>
     </row>
     <row r="37" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B37" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="C37" s="1" t="s">
-        <v>773</v>
+      <c r="B37" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="C37" s="2" t="s">
+        <v>909</v>
       </c>
     </row>
     <row r="38" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B38" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="C38" s="1" t="s">
-        <v>774</v>
+      <c r="B38" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="C38" s="2" t="s">
+        <v>910</v>
       </c>
     </row>
     <row r="39" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B39" s="1" t="s">
-        <v>201</v>
-      </c>
-      <c r="C39" s="1" t="s">
-        <v>775</v>
+      <c r="B39" s="2" t="s">
+        <v>343</v>
+      </c>
+      <c r="C39" s="2" t="s">
+        <v>911</v>
       </c>
     </row>
     <row r="40" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B40" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="C40" s="1" t="s">
-        <v>776</v>
+      <c r="B40" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="C40" s="2" t="s">
+        <v>912</v>
       </c>
     </row>
     <row r="41" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B41" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="C41" s="1" t="s">
-        <v>777</v>
+      <c r="B41" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="C41" s="2" t="s">
+        <v>913</v>
       </c>
     </row>
     <row r="42" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B42" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="C42" s="1" t="s">
-        <v>778</v>
+      <c r="B42" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="C42" s="2" t="s">
+        <v>914</v>
       </c>
     </row>
     <row r="43" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B43" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="C43" s="1" t="s">
-        <v>779</v>
+      <c r="B43" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="C43" s="2" t="s">
+        <v>915</v>
       </c>
     </row>
     <row r="44" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B44" s="1" t="s">
-        <v>114</v>
-      </c>
-      <c r="C44" s="1" t="s">
-        <v>780</v>
+      <c r="B44" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="C44" s="2" t="s">
+        <v>916</v>
       </c>
     </row>
     <row r="45" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B45" s="1" t="s">
-        <v>94</v>
-      </c>
-      <c r="C45" s="1" t="s">
-        <v>781</v>
+      <c r="B45" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="C45" s="2" t="s">
+        <v>917</v>
       </c>
     </row>
     <row r="46" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B46" s="1" t="s">
-        <v>96</v>
-      </c>
-      <c r="C46" s="1" t="s">
-        <v>782</v>
+      <c r="B46" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="C46" s="2" t="s">
+        <v>918</v>
       </c>
     </row>
     <row r="47" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B47" s="1" t="s">
-        <v>98</v>
-      </c>
-      <c r="C47" s="1" t="s">
-        <v>783</v>
+      <c r="B47" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="C47" s="2" t="s">
+        <v>919</v>
       </c>
     </row>
     <row r="48" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B48" s="1" t="s">
-        <v>100</v>
-      </c>
-      <c r="C48" s="1" t="s">
-        <v>784</v>
+      <c r="B48" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="C48" s="2" t="s">
+        <v>920</v>
       </c>
     </row>
     <row r="49" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B49" s="1" t="s">
-        <v>102</v>
-      </c>
-      <c r="C49" s="1" t="s">
-        <v>785</v>
+      <c r="B49" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="C49" s="2" t="s">
+        <v>921</v>
       </c>
     </row>
     <row r="50" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B50" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="C50" s="1" t="s">
-        <v>786</v>
+      <c r="B50" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="C50" s="2" t="s">
+        <v>922</v>
       </c>
     </row>
     <row r="51" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B51" s="1" t="s">
-        <v>106</v>
-      </c>
-      <c r="C51" s="1" t="s">
-        <v>787</v>
+      <c r="B51" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="C51" s="2" t="s">
+        <v>923</v>
       </c>
     </row>
     <row r="52" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B52" s="1" t="s">
-        <v>108</v>
-      </c>
-      <c r="C52" s="1" t="s">
-        <v>788</v>
+      <c r="B52" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="C52" s="2" t="s">
+        <v>924</v>
       </c>
     </row>
     <row r="53" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B53" s="1" t="s">
-        <v>110</v>
-      </c>
-      <c r="C53" s="1" t="s">
+      <c r="B53" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="C53" s="2" t="s">
+        <v>925</v>
+      </c>
+    </row>
+    <row r="54" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B54" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="C54" s="2" t="s">
+        <v>902</v>
+      </c>
+    </row>
+    <row r="55" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B55" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="C55" s="2" t="s">
+        <v>926</v>
+      </c>
+    </row>
+    <row r="56" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B56" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="C56" s="2" t="s">
+        <v>927</v>
+      </c>
+    </row>
+    <row r="57" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B57" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="C57" s="2" t="s">
+        <v>928</v>
+      </c>
+    </row>
+    <row r="58" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B58" s="2" t="s">
+        <v>929</v>
+      </c>
+      <c r="C58" s="2" t="s">
+        <v>930</v>
+      </c>
+    </row>
+    <row r="59" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B59" s="2" t="s">
+        <v>931</v>
+      </c>
+      <c r="C59" s="2" t="s">
+        <v>932</v>
+      </c>
+    </row>
+    <row r="60" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B60" s="2" t="s">
+        <v>933</v>
+      </c>
+      <c r="C60" s="2" t="s">
+        <v>934</v>
+      </c>
+    </row>
+    <row r="61" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B61" s="2" t="s">
         <v>789</v>
       </c>
-    </row>
-    <row r="54" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B54" s="1" t="s">
-        <v>112</v>
-      </c>
-      <c r="C54" s="1" t="s">
-        <v>765</v>
-      </c>
-    </row>
-    <row r="55" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B55" s="1" t="s">
-        <v>116</v>
-      </c>
-      <c r="C55" s="1" t="s">
-        <v>790</v>
-      </c>
-    </row>
-    <row r="56" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B56" s="1" t="s">
-        <v>118</v>
-      </c>
-      <c r="C56" s="1" t="s">
+      <c r="C61" s="2" t="s">
+        <v>935</v>
+      </c>
+    </row>
+    <row r="62" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B62" s="2" t="s">
         <v>791</v>
       </c>
-    </row>
-    <row r="57" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B57" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="C57" s="1" t="s">
-        <v>792</v>
-      </c>
-    </row>
-    <row r="58" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B58" s="1" t="s">
+      <c r="C62" s="2" t="s">
+        <v>936</v>
+      </c>
+    </row>
+    <row r="63" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B63" s="2" t="s">
         <v>793</v>
       </c>
-      <c r="C58" s="1" t="s">
-        <v>794</v>
-      </c>
-    </row>
-    <row r="59" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B59" s="1" t="s">
+      <c r="C63" s="2" t="s">
+        <v>937</v>
+      </c>
+    </row>
+    <row r="64" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B64" s="2" t="s">
         <v>795</v>
       </c>
-      <c r="C59" s="1" t="s">
-        <v>796</v>
-      </c>
-    </row>
-    <row r="60" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B60" s="1" t="s">
+      <c r="C64" s="2" t="s">
+        <v>938</v>
+      </c>
+    </row>
+    <row r="65" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B65" s="2" t="s">
         <v>797</v>
       </c>
-      <c r="C60" s="1" t="s">
-        <v>798</v>
-      </c>
-    </row>
-    <row r="61" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B61" s="1" t="s">
-        <v>647</v>
-      </c>
-      <c r="C61" s="1" t="s">
-        <v>799</v>
-      </c>
-    </row>
-    <row r="62" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B62" s="1" t="s">
-        <v>649</v>
-      </c>
-      <c r="C62" s="1" t="s">
-        <v>800</v>
-      </c>
-    </row>
-    <row r="63" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B63" s="1" t="s">
-        <v>651</v>
-      </c>
-      <c r="C63" s="1" t="s">
-        <v>801</v>
-      </c>
-    </row>
-    <row r="64" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B64" s="1" t="s">
-        <v>653</v>
-      </c>
-      <c r="C64" s="1" t="s">
-        <v>802</v>
-      </c>
-    </row>
-    <row r="65" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B65" s="1" t="s">
-        <v>655</v>
-      </c>
-      <c r="C65" s="1" t="s">
-        <v>803</v>
+      <c r="C65" s="2" t="s">
+        <v>939</v>
       </c>
     </row>
     <row r="66" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B66" s="1" t="s">
-        <v>804</v>
-      </c>
-      <c r="C66" s="1" t="s">
-        <v>805</v>
+      <c r="B66" s="2" t="s">
+        <v>940</v>
+      </c>
+      <c r="C66" s="2" t="s">
+        <v>941</v>
       </c>
     </row>
     <row r="67" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B67" s="1" t="s">
-        <v>806</v>
-      </c>
-      <c r="C67" s="1" t="s">
-        <v>807</v>
+      <c r="B67" s="2" t="s">
+        <v>314</v>
+      </c>
+      <c r="C67" s="2" t="s">
+        <v>942</v>
       </c>
     </row>
     <row r="68" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B68" s="1" t="s">
-        <v>808</v>
-      </c>
-      <c r="C68" s="1" t="s">
-        <v>809</v>
+      <c r="B68" s="2" t="s">
+        <v>328</v>
+      </c>
+      <c r="C68" s="2" t="s">
+        <v>943</v>
       </c>
     </row>
   </sheetData>
@@ -7023,251 +7975,251 @@
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B1" s="4" t="s">
+      <c r="B1" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="4" t="s">
+      <c r="C1" s="5" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="2" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B2" s="4" t="s">
-        <v>810</v>
-      </c>
-      <c r="C2" s="4" t="s">
-        <v>811</v>
+      <c r="B2" s="5" t="s">
+        <v>944</v>
+      </c>
+      <c r="C2" s="5" t="s">
+        <v>945</v>
       </c>
     </row>
     <row r="3" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B3" s="4" t="s">
+      <c r="B3" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="C3" s="5" t="s">
+        <v>946</v>
+      </c>
+    </row>
+    <row r="4" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B4" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C4" s="5" t="s">
+        <v>877</v>
+      </c>
+    </row>
+    <row r="5" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B5" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>910</v>
+      </c>
+    </row>
+    <row r="6" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B6" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="C3" s="4" t="s">
-        <v>812</v>
-      </c>
-    </row>
-    <row r="4" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B4" s="4" t="s">
-        <v>813</v>
-      </c>
-      <c r="C4" s="4" t="s">
-        <v>735</v>
-      </c>
-    </row>
-    <row r="5" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B5" s="4" t="s">
-        <v>814</v>
-      </c>
-      <c r="C5" s="4" t="s">
-        <v>774</v>
-      </c>
-    </row>
-    <row r="6" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B6" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>815</v>
+      <c r="C6" s="5" t="s">
+        <v>947</v>
       </c>
     </row>
     <row r="7" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B7" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="C7" s="4" t="s">
-        <v>816</v>
+      <c r="B7" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>948</v>
       </c>
     </row>
     <row r="8" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B8" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="C8" s="4" t="s">
-        <v>817</v>
+      <c r="B8" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="C8" s="5" t="s">
+        <v>949</v>
       </c>
     </row>
     <row r="9" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B9" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="C9" s="4" t="s">
-        <v>818</v>
+      <c r="B9" s="5" t="s">
+        <v>950</v>
+      </c>
+      <c r="C9" s="5" t="s">
+        <v>951</v>
       </c>
     </row>
     <row r="10" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B10" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="C10" s="4" t="s">
-        <v>819</v>
+      <c r="B10" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="C10" s="5" t="s">
+        <v>952</v>
       </c>
     </row>
     <row r="11" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B11" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="C11" s="4" t="s">
-        <v>820</v>
+      <c r="B11" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="C11" s="5" t="s">
+        <v>953</v>
       </c>
     </row>
     <row r="12" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B12" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="C12" s="4" t="s">
-        <v>821</v>
+      <c r="B12" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="C12" s="5" t="s">
+        <v>954</v>
       </c>
     </row>
     <row r="13" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B13" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="C13" s="4" t="s">
-        <v>822</v>
+      <c r="B13" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="C13" s="5" t="s">
+        <v>955</v>
       </c>
     </row>
     <row r="14" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B14" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="C14" s="4" t="s">
-        <v>823</v>
+      <c r="B14" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="C14" s="5" t="s">
+        <v>956</v>
       </c>
     </row>
     <row r="15" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B15" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="C15" s="4" t="s">
-        <v>737</v>
+      <c r="B15" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="C15" s="5" t="s">
+        <v>879</v>
       </c>
     </row>
     <row r="16" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B16" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="C16" s="4" t="s">
-        <v>736</v>
+      <c r="B16" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="C16" s="5" t="s">
+        <v>878</v>
       </c>
     </row>
     <row r="17" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B17" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="C17" s="4" t="s">
-        <v>738</v>
+      <c r="B17" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="C17" s="5" t="s">
+        <v>880</v>
       </c>
     </row>
     <row r="18" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B18" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="C18" s="4" t="s">
-        <v>824</v>
+      <c r="B18" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="C18" s="5" t="s">
+        <v>957</v>
       </c>
     </row>
     <row r="19" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B19" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="C19" s="4" t="s">
-        <v>812</v>
+      <c r="B19" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="C19" s="5" t="s">
+        <v>946</v>
       </c>
     </row>
     <row r="20" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B20" s="4" t="s">
-        <v>825</v>
-      </c>
-      <c r="C20" s="4" t="s">
-        <v>826</v>
+      <c r="B20" s="5" t="s">
+        <v>132</v>
+      </c>
+      <c r="C20" s="5" t="s">
+        <v>958</v>
       </c>
     </row>
     <row r="21" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B21" s="4" t="s">
-        <v>66</v>
-      </c>
-      <c r="C21" s="4" t="s">
-        <v>827</v>
+      <c r="B21" s="5" t="s">
+        <v>98</v>
+      </c>
+      <c r="C21" s="5" t="s">
+        <v>959</v>
       </c>
     </row>
     <row r="22" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B22" s="4" t="s">
-        <v>68</v>
-      </c>
-      <c r="C22" s="4" t="s">
-        <v>828</v>
+      <c r="B22" s="5" t="s">
+        <v>114</v>
+      </c>
+      <c r="C22" s="5" t="s">
+        <v>960</v>
       </c>
     </row>
     <row r="23" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B23" s="4" t="s">
-        <v>72</v>
-      </c>
-      <c r="C23" s="4" t="s">
-        <v>829</v>
+      <c r="B23" s="5" t="s">
+        <v>118</v>
+      </c>
+      <c r="C23" s="5" t="s">
+        <v>961</v>
       </c>
     </row>
     <row r="24" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B24" s="4" t="s">
-        <v>830</v>
-      </c>
-      <c r="C24" s="4" t="s">
-        <v>831</v>
+      <c r="B24" s="5" t="s">
+        <v>232</v>
+      </c>
+      <c r="C24" s="5" t="s">
+        <v>962</v>
       </c>
     </row>
     <row r="25" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B25" s="4" t="s">
-        <v>92</v>
-      </c>
-      <c r="C25" s="4" t="s">
-        <v>766</v>
+      <c r="B25" s="5" t="s">
+        <v>152</v>
+      </c>
+      <c r="C25" s="5" t="s">
+        <v>903</v>
       </c>
     </row>
     <row r="26" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B26" s="4" t="s">
-        <v>114</v>
-      </c>
-      <c r="C26" s="4" t="s">
-        <v>780</v>
+      <c r="B26" s="5" t="s">
+        <v>174</v>
+      </c>
+      <c r="C26" s="5" t="s">
+        <v>916</v>
       </c>
     </row>
     <row r="27" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B27" s="4" t="s">
-        <v>832</v>
-      </c>
-      <c r="C27" s="4" t="s">
-        <v>752</v>
+      <c r="B27" s="5" t="s">
+        <v>963</v>
+      </c>
+      <c r="C27" s="5" t="s">
+        <v>892</v>
       </c>
     </row>
     <row r="28" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B28" s="4" t="s">
-        <v>833</v>
-      </c>
-      <c r="C28" s="4" t="s">
-        <v>834</v>
+      <c r="B28" s="5" t="s">
+        <v>964</v>
+      </c>
+      <c r="C28" s="5" t="s">
+        <v>965</v>
       </c>
     </row>
     <row r="29" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B29" s="4" t="s">
-        <v>835</v>
-      </c>
-      <c r="C29" s="4" t="s">
-        <v>771</v>
+      <c r="B29" s="5" t="s">
+        <v>268</v>
+      </c>
+      <c r="C29" s="5" t="s">
+        <v>907</v>
       </c>
     </row>
     <row r="30" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B30" s="4" t="s">
-        <v>836</v>
-      </c>
-      <c r="C30" s="4" t="s">
-        <v>837</v>
+      <c r="B30" s="5" t="s">
+        <v>312</v>
+      </c>
+      <c r="C30" s="5" t="s">
+        <v>966</v>
       </c>
     </row>
     <row r="31" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B31" s="4" t="s">
-        <v>838</v>
-      </c>
-      <c r="C31" s="4" t="s">
-        <v>839</v>
+      <c r="B31" s="5" t="s">
+        <v>336</v>
+      </c>
+      <c r="C31" s="5" t="s">
+        <v>967</v>
       </c>
     </row>
   </sheetData>
@@ -7282,107 +8234,107 @@
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="3" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="2" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>968</v>
+      </c>
+    </row>
+    <row r="3" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B3" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>969</v>
+      </c>
+    </row>
+    <row r="4" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B4" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>961</v>
+      </c>
+    </row>
+    <row r="5" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B5" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="C2" s="2" t="s">
-        <v>840</v>
-      </c>
-    </row>
-    <row r="3" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B3" s="2" t="s">
-        <v>813</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>841</v>
-      </c>
-    </row>
-    <row r="4" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B4" s="2" t="s">
-        <v>814</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>829</v>
-      </c>
-    </row>
-    <row r="5" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B5" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>812</v>
+      <c r="C5" s="3" t="s">
+        <v>946</v>
       </c>
     </row>
     <row r="6" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B6" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>752</v>
+      <c r="B6" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>892</v>
       </c>
     </row>
     <row r="7" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B7" s="2" t="s">
-        <v>825</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>287</v>
+      <c r="B7" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>429</v>
       </c>
     </row>
     <row r="8" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B8" s="2" t="s">
-        <v>830</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>842</v>
+      <c r="B8" s="3" t="s">
+        <v>232</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>970</v>
       </c>
     </row>
     <row r="9" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B9" s="2" t="s">
-        <v>832</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>843</v>
+      <c r="B9" s="3" t="s">
+        <v>963</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>971</v>
       </c>
     </row>
     <row r="10" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B10" s="2" t="s">
-        <v>833</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>844</v>
+      <c r="B10" s="3" t="s">
+        <v>964</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>972</v>
       </c>
     </row>
     <row r="11" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B11" s="2" t="s">
-        <v>835</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>845</v>
+      <c r="B11" s="3" t="s">
+        <v>268</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>973</v>
       </c>
     </row>
     <row r="12" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B12" s="2" t="s">
-        <v>836</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>846</v>
+      <c r="B12" s="3" t="s">
+        <v>312</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>974</v>
       </c>
     </row>
     <row r="13" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B13" s="2" t="s">
-        <v>838</v>
-      </c>
-      <c r="C13" s="2" t="s">
-        <v>847</v>
+      <c r="B13" s="3" t="s">
+        <v>336</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>975</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/Editor/DataDic/Data.xlsx
+++ b/Assets/Editor/DataDic/Data.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="17385" windowHeight="7860" activeTab="2"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="17385" windowHeight="7860" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="FishData" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1183" uniqueCount="976">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1183" uniqueCount="977">
   <si>
     <t>Key</t>
   </si>
@@ -2976,12 +2976,16 @@
   <si>
     <t>分配</t>
   </si>
+  <si>
+    <t>酒馆</t>
+    <phoneticPr fontId="0" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
@@ -2995,6 +2999,12 @@
       <sz val="11"/>
       <name val="Calibri"/>
       <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
     </font>
   </fonts>
   <fills count="3">
@@ -3023,7 +3033,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1"/>
@@ -3034,6 +3044,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -4266,8 +4277,8 @@
       </c>
     </row>
     <row r="48" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B48" s="6" t="s">
-        <v>423</v>
+      <c r="B48" s="10" t="s">
+        <v>976</v>
       </c>
       <c r="C48" s="6" t="s">
         <v>424</v>

--- a/Assets/Editor/DataDic/Data.xlsx
+++ b/Assets/Editor/DataDic/Data.xlsx
@@ -5,11 +5,11 @@
   <workbookPr defaultThemeVersion="164011"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\MyGame\Rune Factory\Assets\Editor\DataDic\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\MyGame\Rune Factory - Copy\Assets\Editor\DataDic\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="17385" windowHeight="7860" activeTab="1"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="17385" windowHeight="7860" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="FishData" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1183" uniqueCount="977">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1216" uniqueCount="979">
   <si>
     <t>Key</t>
   </si>
@@ -1435,7 +1435,7 @@
     <t>1015</t>
   </si>
   <si>
-    <t>蜡烛1</t>
+    <t>蜡烛</t>
   </si>
   <si>
     <t>1016</t>
@@ -1453,15 +1453,9 @@
     <t>1018</t>
   </si>
   <si>
-    <t>长柜台竖</t>
-  </si>
-  <si>
     <t>1019</t>
   </si>
   <si>
-    <t>长柜台横</t>
-  </si>
-  <si>
     <t>1020</t>
   </si>
   <si>
@@ -1495,15 +1489,12 @@
     <t>1025</t>
   </si>
   <si>
-    <t>武器柜右</t>
+    <t>武器柜</t>
   </si>
   <si>
     <t>1027</t>
   </si>
   <si>
-    <t>壁画1</t>
-  </si>
-  <si>
     <t>1028</t>
   </si>
   <si>
@@ -1531,13 +1522,13 @@
     <t>1032</t>
   </si>
   <si>
-    <t>锻造炉-设施</t>
+    <t>锻造炉</t>
   </si>
   <si>
     <t>1033</t>
   </si>
   <si>
-    <t>储物箱(木)-设施</t>
+    <t>储物箱</t>
   </si>
   <si>
     <t>1034</t>
@@ -1549,7 +1540,7 @@
     <t>1035</t>
   </si>
   <si>
-    <t>商店开关</t>
+    <t>招牌</t>
   </si>
   <si>
     <t>1036</t>
@@ -1591,9 +1582,6 @@
     <t>1042</t>
   </si>
   <si>
-    <t>别墅一楼床</t>
-  </si>
-  <si>
     <t>1043</t>
   </si>
   <si>
@@ -1639,7 +1627,7 @@
     <t>1050</t>
   </si>
   <si>
-    <t>竖长椅</t>
+    <t>长椅</t>
   </si>
   <si>
     <t>1051</t>
@@ -1699,7 +1687,7 @@
     <t>1060</t>
   </si>
   <si>
-    <t>栅栏门</t>
+    <t>栅栏</t>
   </si>
   <si>
     <t>1061</t>
@@ -1723,9 +1711,6 @@
     <t>1064</t>
   </si>
   <si>
-    <t>长椅背面</t>
-  </si>
-  <si>
     <t>1065</t>
   </si>
   <si>
@@ -1747,9 +1732,6 @@
     <t>1068</t>
   </si>
   <si>
-    <t>植物店柜台</t>
-  </si>
-  <si>
     <t>1069</t>
   </si>
   <si>
@@ -1759,15 +1741,9 @@
     <t>1070</t>
   </si>
   <si>
-    <t>单人床</t>
-  </si>
-  <si>
     <t>1071</t>
   </si>
   <si>
-    <t>豪华床</t>
-  </si>
-  <si>
     <t>1072</t>
   </si>
   <si>
@@ -1798,6 +1774,9 @@
     <t>春战场</t>
   </si>
   <si>
+    <t>1077</t>
+  </si>
+  <si>
     <t>秋战场</t>
   </si>
   <si>
@@ -1807,15 +1786,9 @@
     <t>1079</t>
   </si>
   <si>
-    <t>畜牧店柜台</t>
-  </si>
-  <si>
     <t>1080</t>
   </si>
   <si>
-    <t>床绿</t>
-  </si>
-  <si>
     <t>1081</t>
   </si>
   <si>
@@ -1861,9 +1834,6 @@
     <t>1088</t>
   </si>
   <si>
-    <t>家具柜台</t>
-  </si>
-  <si>
     <t>1089</t>
   </si>
   <si>
@@ -1984,9 +1954,6 @@
     <t>1110</t>
   </si>
   <si>
-    <t>水车房</t>
-  </si>
-  <si>
     <t>1111</t>
   </si>
   <si>
@@ -2056,63 +2023,48 @@
     <t>1124</t>
   </si>
   <si>
-    <t>搅拌器-设施</t>
-  </si>
-  <si>
     <t>1125</t>
   </si>
   <si>
-    <t>冰箱-设施</t>
-  </si>
-  <si>
     <t>1126</t>
   </si>
   <si>
-    <t>缝纫机-设施</t>
+    <t>缝纫机</t>
   </si>
   <si>
     <t>1127</t>
   </si>
   <si>
-    <t>绘写台-设施</t>
+    <t>绘写台</t>
   </si>
   <si>
     <t>1128</t>
   </si>
   <si>
-    <t>冷餐台-设施</t>
-  </si>
-  <si>
     <t>1129</t>
   </si>
   <si>
-    <t>蒸煮锅-设施</t>
+    <t>蒸煮锅</t>
   </si>
   <si>
     <t>1130</t>
   </si>
   <si>
-    <t>烘烤炉-设施</t>
+    <t>烘烤炉</t>
   </si>
   <si>
     <t>1131</t>
   </si>
   <si>
-    <t>酿造桶-设施</t>
+    <t>酿造桶</t>
   </si>
   <si>
     <t>1134</t>
   </si>
   <si>
-    <t>储物箱(银)-设施</t>
-  </si>
-  <si>
     <t>1135</t>
   </si>
   <si>
-    <t>储物箱(金)-设施</t>
-  </si>
-  <si>
     <t>1136</t>
   </si>
   <si>
@@ -2164,9 +2116,6 @@
     <t>1144</t>
   </si>
   <si>
-    <t>占卜柜台</t>
-  </si>
-  <si>
     <t>1145</t>
   </si>
   <si>
@@ -2254,9 +2203,6 @@
     <t>1159</t>
   </si>
   <si>
-    <t>纺织店柜台</t>
-  </si>
-  <si>
     <t>1160</t>
   </si>
   <si>
@@ -2272,9 +2218,6 @@
     <t>1162</t>
   </si>
   <si>
-    <t>床白</t>
-  </si>
-  <si>
     <t>1163</t>
   </si>
   <si>
@@ -2290,9 +2233,6 @@
     <t>1165</t>
   </si>
   <si>
-    <t>酒馆柜台</t>
-  </si>
-  <si>
     <t>1166</t>
   </si>
   <si>
@@ -2311,6 +2251,90 @@
     <t>朴素床</t>
   </si>
   <si>
+    <t>1169</t>
+  </si>
+  <si>
+    <t>楼梯下</t>
+  </si>
+  <si>
+    <t>1170</t>
+  </si>
+  <si>
+    <t>双人床</t>
+  </si>
+  <si>
+    <t>1171</t>
+  </si>
+  <si>
+    <t>沙发(蓝)</t>
+  </si>
+  <si>
+    <t>1172</t>
+  </si>
+  <si>
+    <t>沙发(红)</t>
+  </si>
+  <si>
+    <t>1173</t>
+  </si>
+  <si>
+    <t>盆栽1</t>
+  </si>
+  <si>
+    <t>1174</t>
+  </si>
+  <si>
+    <t>盆栽2</t>
+  </si>
+  <si>
+    <t>1175</t>
+  </si>
+  <si>
+    <t>盆栽3</t>
+  </si>
+  <si>
+    <t>1176</t>
+  </si>
+  <si>
+    <t>盆栽4</t>
+  </si>
+  <si>
+    <t>1177</t>
+  </si>
+  <si>
+    <t>盆栽5</t>
+  </si>
+  <si>
+    <t>1178</t>
+  </si>
+  <si>
+    <t>1179</t>
+  </si>
+  <si>
+    <t>船坞栅栏</t>
+  </si>
+  <si>
+    <t>1181</t>
+  </si>
+  <si>
+    <t>装备店柜台</t>
+  </si>
+  <si>
+    <t>1182</t>
+  </si>
+  <si>
+    <t>魔法柜台</t>
+  </si>
+  <si>
+    <t>1183</t>
+  </si>
+  <si>
+    <t>1184</t>
+  </si>
+  <si>
+    <t>船长床</t>
+  </si>
+  <si>
     <t>1200</t>
   </si>
   <si>
@@ -2326,39 +2350,21 @@
     <t>1202</t>
   </si>
   <si>
-    <t>锻造炉</t>
-  </si>
-  <si>
     <t>1203</t>
   </si>
   <si>
-    <t>烘烤炉</t>
-  </si>
-  <si>
     <t>1204</t>
   </si>
   <si>
-    <t>酿造桶</t>
-  </si>
-  <si>
     <t>1205</t>
   </si>
   <si>
-    <t>绘写台</t>
-  </si>
-  <si>
     <t>1206</t>
   </si>
   <si>
-    <t>蒸煮锅</t>
-  </si>
-  <si>
     <t>1207</t>
   </si>
   <si>
-    <t>缝纫机</t>
-  </si>
-  <si>
     <t>纺线机</t>
   </si>
   <si>
@@ -2374,6 +2380,12 @@
     <t>制革机</t>
   </si>
   <si>
+    <t>1211</t>
+  </si>
+  <si>
+    <t>高温熔炉</t>
+  </si>
+  <si>
     <t>1290</t>
   </si>
   <si>
@@ -2401,9 +2413,6 @@
     <t>164</t>
   </si>
   <si>
-    <t>长椅下</t>
-  </si>
-  <si>
     <t>2000</t>
   </si>
   <si>
@@ -2975,10 +2984,6 @@
   </si>
   <si>
     <t>分配</t>
-  </si>
-  <si>
-    <t>酒馆</t>
-    <phoneticPr fontId="0" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -3004,7 +3009,6 @@
       <sz val="11"/>
       <name val="宋体"/>
       <family val="3"/>
-      <charset val="134"/>
     </font>
   </fonts>
   <fills count="3">
@@ -3033,7 +3037,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="12">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1"/>
@@ -3329,259 +3334,259 @@
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B1" s="6" t="s">
+      <c r="B1" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="6" t="s">
+      <c r="C1" s="7" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="2" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B2" s="6" t="s">
-        <v>844</v>
-      </c>
-      <c r="C2" s="6" t="s">
-        <v>845</v>
+      <c r="B2" s="7" t="s">
+        <v>847</v>
+      </c>
+      <c r="C2" s="7" t="s">
+        <v>848</v>
       </c>
     </row>
     <row r="3" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B3" s="6" t="s">
+      <c r="B3" s="7" t="s">
         <v>445</v>
       </c>
-      <c r="C3" s="6" t="s">
-        <v>846</v>
+      <c r="C3" s="7" t="s">
+        <v>849</v>
       </c>
     </row>
     <row r="4" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B4" s="6" t="s">
+      <c r="B4" s="7" t="s">
         <v>447</v>
       </c>
-      <c r="C4" s="6" t="s">
-        <v>847</v>
+      <c r="C4" s="7" t="s">
+        <v>850</v>
       </c>
     </row>
     <row r="5" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B5" s="6" t="s">
+      <c r="B5" s="7" t="s">
         <v>449</v>
       </c>
-      <c r="C5" s="6" t="s">
-        <v>848</v>
+      <c r="C5" s="7" t="s">
+        <v>851</v>
       </c>
     </row>
     <row r="6" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B6" s="6" t="s">
+      <c r="B6" s="7" t="s">
         <v>451</v>
       </c>
-      <c r="C6" s="6" t="s">
-        <v>849</v>
+      <c r="C6" s="7" t="s">
+        <v>852</v>
       </c>
     </row>
     <row r="7" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B7" s="6" t="s">
+      <c r="B7" s="7" t="s">
         <v>453</v>
       </c>
-      <c r="C7" s="6" t="s">
-        <v>850</v>
+      <c r="C7" s="7" t="s">
+        <v>853</v>
       </c>
     </row>
     <row r="8" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B8" s="6" t="s">
+      <c r="B8" s="7" t="s">
         <v>457</v>
       </c>
-      <c r="C8" s="6" t="s">
-        <v>851</v>
+      <c r="C8" s="7" t="s">
+        <v>854</v>
       </c>
     </row>
     <row r="9" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B9" s="6" t="s">
+      <c r="B9" s="7" t="s">
         <v>459</v>
       </c>
-      <c r="C9" s="6" t="s">
-        <v>852</v>
+      <c r="C9" s="7" t="s">
+        <v>855</v>
       </c>
     </row>
     <row r="10" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B10" s="6" t="s">
+      <c r="B10" s="7" t="s">
         <v>461</v>
       </c>
-      <c r="C10" s="6" t="s">
-        <v>853</v>
+      <c r="C10" s="7" t="s">
+        <v>856</v>
       </c>
     </row>
     <row r="11" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B11" s="6" t="s">
+      <c r="B11" s="7" t="s">
         <v>463</v>
       </c>
-      <c r="C11" s="6" t="s">
-        <v>854</v>
+      <c r="C11" s="7" t="s">
+        <v>857</v>
       </c>
     </row>
     <row r="12" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B12" s="6" t="s">
+      <c r="B12" s="7" t="s">
         <v>465</v>
       </c>
-      <c r="C12" s="6" t="s">
-        <v>855</v>
+      <c r="C12" s="7" t="s">
+        <v>858</v>
       </c>
     </row>
     <row r="13" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B13" s="6" t="s">
+      <c r="B13" s="7" t="s">
         <v>467</v>
       </c>
-      <c r="C13" s="6" t="s">
-        <v>856</v>
+      <c r="C13" s="7" t="s">
+        <v>859</v>
       </c>
     </row>
     <row r="14" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B14" s="6" t="s">
+      <c r="B14" s="7" t="s">
+        <v>469</v>
+      </c>
+      <c r="C14" s="7" t="s">
+        <v>860</v>
+      </c>
+    </row>
+    <row r="15" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B15" s="7" t="s">
         <v>471</v>
       </c>
-      <c r="C14" s="6" t="s">
-        <v>857</v>
-      </c>
-    </row>
-    <row r="15" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B15" s="6" t="s">
+      <c r="C15" s="7" t="s">
+        <v>861</v>
+      </c>
+    </row>
+    <row r="16" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B16" s="7" t="s">
         <v>473</v>
       </c>
-      <c r="C15" s="6" t="s">
-        <v>858</v>
-      </c>
-    </row>
-    <row r="16" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B16" s="6" t="s">
+      <c r="C16" s="7" t="s">
+        <v>862</v>
+      </c>
+    </row>
+    <row r="17" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B17" s="7" t="s">
         <v>475</v>
       </c>
-      <c r="C16" s="6" t="s">
-        <v>859</v>
-      </c>
-    </row>
-    <row r="17" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B17" s="6" t="s">
+      <c r="C17" s="7" t="s">
+        <v>863</v>
+      </c>
+    </row>
+    <row r="18" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B18" s="7" t="s">
         <v>477</v>
       </c>
-      <c r="C17" s="6" t="s">
-        <v>860</v>
-      </c>
-    </row>
-    <row r="18" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B18" s="6" t="s">
-        <v>479</v>
-      </c>
-      <c r="C18" s="6" t="s">
-        <v>861</v>
+      <c r="C18" s="7" t="s">
+        <v>864</v>
       </c>
     </row>
     <row r="19" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B19" s="6" t="s">
+      <c r="B19" s="7" t="s">
+        <v>617</v>
+      </c>
+      <c r="C19" s="7" t="s">
+        <v>865</v>
+      </c>
+    </row>
+    <row r="20" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B20" s="7" t="s">
+        <v>619</v>
+      </c>
+      <c r="C20" s="7" t="s">
+        <v>866</v>
+      </c>
+    </row>
+    <row r="21" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B21" s="7" t="s">
+        <v>622</v>
+      </c>
+      <c r="C21" s="7" t="s">
+        <v>867</v>
+      </c>
+    </row>
+    <row r="22" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B22" s="7" t="s">
+        <v>626</v>
+      </c>
+      <c r="C22" s="7" t="s">
+        <v>868</v>
+      </c>
+    </row>
+    <row r="23" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B23" s="7" t="s">
         <v>627</v>
       </c>
-      <c r="C19" s="6" t="s">
-        <v>862</v>
-      </c>
-    </row>
-    <row r="20" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B20" s="6" t="s">
-        <v>629</v>
-      </c>
-      <c r="C20" s="6" t="s">
-        <v>863</v>
-      </c>
-    </row>
-    <row r="21" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B21" s="6" t="s">
+      <c r="C23" s="7" t="s">
+        <v>869</v>
+      </c>
+    </row>
+    <row r="24" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B24" s="7" t="s">
         <v>632</v>
       </c>
-      <c r="C21" s="6" t="s">
-        <v>864</v>
-      </c>
-    </row>
-    <row r="22" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B22" s="6" t="s">
-        <v>636</v>
-      </c>
-      <c r="C22" s="6" t="s">
-        <v>865</v>
-      </c>
-    </row>
-    <row r="23" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B23" s="6" t="s">
-        <v>637</v>
-      </c>
-      <c r="C23" s="6" t="s">
-        <v>866</v>
-      </c>
-    </row>
-    <row r="24" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B24" s="6" t="s">
+      <c r="C24" s="7" t="s">
+        <v>870</v>
+      </c>
+    </row>
+    <row r="25" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B25" s="7" t="s">
+        <v>634</v>
+      </c>
+      <c r="C25" s="7" t="s">
+        <v>871</v>
+      </c>
+    </row>
+    <row r="26" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B26" s="7" t="s">
+        <v>635</v>
+      </c>
+      <c r="C26" s="7" t="s">
+        <v>872</v>
+      </c>
+    </row>
+    <row r="27" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B27" s="7" t="s">
+        <v>388</v>
+      </c>
+      <c r="C27" s="7" t="s">
+        <v>873</v>
+      </c>
+    </row>
+    <row r="28" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B28" s="7" t="s">
+        <v>638</v>
+      </c>
+      <c r="C28" s="7" t="s">
+        <v>874</v>
+      </c>
+    </row>
+    <row r="29" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B29" s="7" t="s">
+        <v>640</v>
+      </c>
+      <c r="C29" s="7" t="s">
+        <v>875</v>
+      </c>
+    </row>
+    <row r="30" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B30" s="7" t="s">
         <v>642</v>
       </c>
-      <c r="C24" s="6" t="s">
-        <v>867</v>
-      </c>
-    </row>
-    <row r="25" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B25" s="6" t="s">
-        <v>644</v>
-      </c>
-      <c r="C25" s="6" t="s">
-        <v>868</v>
-      </c>
-    </row>
-    <row r="26" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B26" s="6" t="s">
-        <v>646</v>
-      </c>
-      <c r="C26" s="6" t="s">
-        <v>869</v>
-      </c>
-    </row>
-    <row r="27" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B27" s="6" t="s">
-        <v>388</v>
-      </c>
-      <c r="C27" s="6" t="s">
-        <v>870</v>
-      </c>
-    </row>
-    <row r="28" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B28" s="6" t="s">
-        <v>649</v>
-      </c>
-      <c r="C28" s="6" t="s">
-        <v>871</v>
-      </c>
-    </row>
-    <row r="29" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B29" s="6" t="s">
-        <v>651</v>
-      </c>
-      <c r="C29" s="6" t="s">
-        <v>872</v>
-      </c>
-    </row>
-    <row r="30" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B30" s="6" t="s">
-        <v>653</v>
-      </c>
-      <c r="C30" s="6" t="s">
-        <v>873</v>
+      <c r="C30" s="7" t="s">
+        <v>876</v>
       </c>
     </row>
     <row r="31" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B31" s="6" t="s">
-        <v>654</v>
-      </c>
-      <c r="C31" s="6" t="s">
-        <v>874</v>
+      <c r="B31" s="7" t="s">
+        <v>643</v>
+      </c>
+      <c r="C31" s="7" t="s">
+        <v>877</v>
       </c>
     </row>
     <row r="32" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B32" s="6" t="s">
-        <v>656</v>
-      </c>
-      <c r="C32" s="6" t="s">
-        <v>875</v>
+      <c r="B32" s="7" t="s">
+        <v>645</v>
+      </c>
+      <c r="C32" s="7" t="s">
+        <v>878</v>
       </c>
     </row>
   </sheetData>
@@ -3596,2464 +3601,2592 @@
   <dimension ref="B1:O56"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="22.28515625" style="4" customWidth="1"/>
+    <col min="2" max="2" width="22.28515625" style="5" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B1" s="6" t="s">
+      <c r="B1" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="6" t="s">
+      <c r="C1" s="7" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="2" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B2" s="6" t="s">
+      <c r="B2" s="7" t="s">
         <v>338</v>
       </c>
-      <c r="C2" s="6" t="s">
+      <c r="C2" s="7" t="s">
         <v>339</v>
       </c>
     </row>
     <row r="3" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B3" s="6" t="s">
+      <c r="B3" s="7" t="s">
         <v>340</v>
       </c>
-      <c r="C3" s="6" t="s">
+      <c r="C3" s="7" t="s">
         <v>341</v>
       </c>
     </row>
     <row r="4" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B4" s="6" t="s">
+      <c r="B4" s="7" t="s">
         <v>342</v>
       </c>
-      <c r="C4" s="6" t="s">
+      <c r="C4" s="7" t="s">
         <v>343</v>
       </c>
-      <c r="G4" s="7" t="s">
+      <c r="G4" s="8" t="s">
         <v>344</v>
       </c>
-      <c r="I4" s="8" t="s">
+      <c r="I4" s="9" t="s">
         <v>345</v>
       </c>
-      <c r="J4" s="8" t="s">
+      <c r="J4" s="9" t="s">
         <v>346</v>
       </c>
-      <c r="K4" s="6" t="s">
+      <c r="K4" s="7" t="s">
         <v>347</v>
       </c>
     </row>
     <row r="5" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B5" s="6" t="s">
+      <c r="B5" s="7" t="s">
         <v>348</v>
       </c>
-      <c r="C5" s="6">
+      <c r="C5" s="7">
         <v>948</v>
       </c>
-      <c r="G5" s="7" t="s">
+      <c r="G5" s="8" t="s">
         <v>349</v>
       </c>
-      <c r="I5" s="4">
+      <c r="I5" s="5">
         <f>VLOOKUP(I4,$B:$C,2,FALSE)</f>
         <v>874</v>
       </c>
-      <c r="J5" s="6" t="str">
+      <c r="J5" s="7" t="str">
         <f t="shared" ref="J5:K5" si="0">VLOOKUP(J4,$B:$C,2,FALSE)</f>
         <v>2355</v>
       </c>
-      <c r="K5" s="6">
+      <c r="K5" s="7">
         <f t="shared" si="0"/>
         <v>2497</v>
       </c>
     </row>
     <row r="6" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B6" s="6" t="s">
+      <c r="B6" s="7" t="s">
         <v>350</v>
       </c>
-      <c r="C6" s="6" t="s">
+      <c r="C6" s="7" t="s">
         <v>351</v>
       </c>
-      <c r="G6" s="9" t="str">
+      <c r="G6" s="10" t="str">
         <f>G4&amp;","&amp;G5</f>
         <v>6,0,9,0</v>
       </c>
-      <c r="H6" s="9"/>
-      <c r="I6" s="9">
+      <c r="H6" s="10"/>
+      <c r="I6" s="10">
         <f>I5</f>
         <v>874</v>
       </c>
-      <c r="J6" s="9" t="str">
+      <c r="J6" s="10" t="str">
         <f>I6&amp;","&amp;J5</f>
         <v>874,2355</v>
       </c>
-      <c r="K6" s="9" t="str">
+      <c r="K6" s="10" t="str">
         <f>J6&amp;","&amp;K5</f>
         <v>874,2355,2497</v>
       </c>
-      <c r="L6" s="6"/>
-      <c r="M6" s="9"/>
+      <c r="L6" s="7"/>
+      <c r="M6" s="10"/>
     </row>
     <row r="7" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B7" s="6" t="s">
+      <c r="B7" s="7" t="s">
         <v>352</v>
       </c>
-      <c r="C7" s="6" t="s">
+      <c r="C7" s="7" t="s">
         <v>353</v>
       </c>
-      <c r="G7" s="7" t="s">
+      <c r="G7" s="8" t="s">
         <v>349</v>
       </c>
-      <c r="I7" s="8" t="s">
+      <c r="I7" s="9" t="s">
         <v>345</v>
       </c>
-      <c r="J7" s="8" t="s">
+      <c r="J7" s="9" t="s">
         <v>346</v>
       </c>
-      <c r="K7" s="6" t="s">
+      <c r="K7" s="7" t="s">
         <v>347</v>
       </c>
-      <c r="L7" s="6" t="s">
+      <c r="L7" s="7" t="s">
         <v>354</v>
       </c>
-      <c r="M7" s="6" t="s">
+      <c r="M7" s="7" t="s">
         <v>355</v>
       </c>
-      <c r="N7" s="6" t="s">
+      <c r="N7" s="7" t="s">
         <v>356</v>
       </c>
-      <c r="O7" s="6" t="s">
+      <c r="O7" s="7" t="s">
         <v>357</v>
       </c>
     </row>
     <row r="8" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B8" s="6" t="s">
+      <c r="B8" s="7" t="s">
         <v>345</v>
       </c>
-      <c r="C8" s="6">
+      <c r="C8" s="7">
         <v>874</v>
       </c>
-      <c r="G8" s="7" t="s">
+      <c r="G8" s="8" t="s">
         <v>358</v>
       </c>
-      <c r="I8" s="6">
+      <c r="I8" s="7">
         <f>VLOOKUP(I7,$B:$C,2,FALSE)</f>
         <v>874</v>
       </c>
-      <c r="J8" s="6" t="str">
+      <c r="J8" s="7" t="str">
         <f>VLOOKUP(J7,$B:$C,2,FALSE)</f>
         <v>2355</v>
       </c>
-      <c r="K8" s="6">
+      <c r="K8" s="7">
         <f t="shared" ref="K8:L8" si="1">VLOOKUP(K7,$B:$C,2,FALSE)</f>
         <v>2497</v>
       </c>
-      <c r="L8" s="6" t="str">
+      <c r="L8" s="7" t="str">
         <f t="shared" si="1"/>
         <v>302</v>
       </c>
-      <c r="M8" s="6" t="str">
+      <c r="M8" s="7" t="str">
         <f>VLOOKUP(M7,$B:$C,2,FALSE)</f>
         <v>889</v>
       </c>
-      <c r="N8" s="6" t="str">
+      <c r="N8" s="7" t="str">
         <f t="shared" ref="N8:O8" si="2">VLOOKUP(N7,$B:$C,2,FALSE)</f>
         <v>695</v>
       </c>
-      <c r="O8" s="6" t="str">
+      <c r="O8" s="7" t="str">
         <f t="shared" si="2"/>
         <v>512</v>
       </c>
     </row>
     <row r="9" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B9" s="6" t="s">
+      <c r="B9" s="7" t="s">
         <v>359</v>
       </c>
-      <c r="C9" s="6" t="s">
+      <c r="C9" s="7" t="s">
         <v>360</v>
       </c>
-      <c r="G9" s="9" t="str">
+      <c r="G9" s="10" t="str">
         <f>G7&amp;","&amp;G8</f>
         <v>9,0,17,30</v>
       </c>
-      <c r="H9" s="9"/>
-      <c r="I9" s="9">
+      <c r="H9" s="10"/>
+      <c r="I9" s="10">
         <f>I8</f>
         <v>874</v>
       </c>
-      <c r="J9" s="9" t="str">
+      <c r="J9" s="10" t="str">
         <f>I9&amp;","&amp;J8</f>
         <v>874,2355</v>
       </c>
-      <c r="K9" s="9" t="str">
+      <c r="K9" s="10" t="str">
         <f t="shared" ref="K9:N9" si="3">J9&amp;","&amp;K8</f>
         <v>874,2355,2497</v>
       </c>
-      <c r="L9" s="9" t="str">
+      <c r="L9" s="10" t="str">
         <f t="shared" si="3"/>
         <v>874,2355,2497,302</v>
       </c>
-      <c r="M9" s="9" t="str">
+      <c r="M9" s="10" t="str">
         <f t="shared" si="3"/>
         <v>874,2355,2497,302,889</v>
       </c>
-      <c r="N9" s="9" t="str">
+      <c r="N9" s="10" t="str">
         <f t="shared" si="3"/>
         <v>874,2355,2497,302,889,695</v>
       </c>
-      <c r="O9" s="9" t="str">
+      <c r="O9" s="10" t="str">
         <f>N9&amp;","&amp;O8</f>
         <v>874,2355,2497,302,889,695,512</v>
       </c>
     </row>
     <row r="10" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B10" s="6" t="s">
+      <c r="B10" s="7" t="s">
         <v>361</v>
       </c>
-      <c r="C10" s="6" t="s">
+      <c r="C10" s="7" t="s">
         <v>362</v>
       </c>
-      <c r="G10" s="7" t="s">
+      <c r="G10" s="8" t="s">
         <v>358</v>
       </c>
     </row>
     <row r="11" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B11" s="6" t="s">
+      <c r="B11" s="7" t="s">
         <v>363</v>
       </c>
-      <c r="C11" s="6" t="s">
+      <c r="C11" s="7" t="s">
         <v>364</v>
       </c>
-      <c r="G11" s="7" t="s">
+      <c r="G11" s="8" t="s">
         <v>365</v>
       </c>
     </row>
     <row r="12" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B12" s="6" t="s">
+      <c r="B12" s="7" t="s">
         <v>366</v>
       </c>
-      <c r="C12" s="6">
+      <c r="C12" s="7">
         <v>1756</v>
       </c>
-      <c r="F12" s="6"/>
-      <c r="G12" s="9" t="str">
+      <c r="F12" s="7"/>
+      <c r="G12" s="10" t="str">
         <f>G10&amp;","&amp;G11</f>
         <v>17,30,19,30</v>
       </c>
-      <c r="H12" s="6"/>
-      <c r="I12" s="6"/>
-      <c r="J12" s="6"/>
-      <c r="K12" s="6"/>
-      <c r="L12" s="6"/>
-      <c r="M12" s="6"/>
-      <c r="N12" s="6"/>
-      <c r="O12" s="6"/>
+      <c r="H12" s="7"/>
+      <c r="I12" s="7"/>
+      <c r="J12" s="7"/>
+      <c r="K12" s="7"/>
+      <c r="L12" s="7"/>
+      <c r="M12" s="7"/>
+      <c r="N12" s="7"/>
+      <c r="O12" s="7"/>
     </row>
     <row r="13" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B13" s="6" t="s">
+      <c r="B13" s="7" t="s">
         <v>367</v>
       </c>
-      <c r="C13" s="6" t="s">
+      <c r="C13" s="7" t="s">
         <v>368</v>
       </c>
-      <c r="F13" s="6"/>
-      <c r="G13" s="7"/>
-      <c r="H13" s="6"/>
-      <c r="I13" s="6"/>
-      <c r="J13" s="6"/>
-      <c r="K13" s="6"/>
-      <c r="L13" s="6"/>
-      <c r="M13" s="6"/>
-      <c r="N13" s="6"/>
-      <c r="O13" s="6"/>
+      <c r="F13" s="7"/>
+      <c r="G13" s="8"/>
+      <c r="H13" s="7"/>
+      <c r="I13" s="7"/>
+      <c r="J13" s="7"/>
+      <c r="K13" s="7"/>
+      <c r="L13" s="7"/>
+      <c r="M13" s="7"/>
+      <c r="N13" s="7"/>
+      <c r="O13" s="7"/>
     </row>
     <row r="14" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B14" s="6" t="s">
+      <c r="B14" s="7" t="s">
         <v>369</v>
       </c>
-      <c r="C14" s="6" t="s">
+      <c r="C14" s="7" t="s">
         <v>370</v>
       </c>
-      <c r="F14" s="6"/>
-      <c r="G14" s="7" t="s">
+      <c r="F14" s="7"/>
+      <c r="G14" s="8" t="s">
         <v>365</v>
       </c>
-      <c r="I14" s="6" t="s">
+      <c r="I14" s="7" t="s">
         <v>354</v>
       </c>
-      <c r="J14" s="6" t="s">
+      <c r="J14" s="7" t="s">
         <v>355</v>
       </c>
-      <c r="K14" s="6" t="s">
+      <c r="K14" s="7" t="s">
         <v>356</v>
       </c>
-      <c r="L14" s="6" t="s">
+      <c r="L14" s="7" t="s">
         <v>357</v>
       </c>
     </row>
     <row r="15" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B15" s="6" t="s">
+      <c r="B15" s="7" t="s">
         <v>371</v>
       </c>
-      <c r="C15" s="6" t="s">
+      <c r="C15" s="7" t="s">
         <v>372</v>
       </c>
-      <c r="F15" s="6"/>
-      <c r="G15" s="7" t="s">
+      <c r="F15" s="7"/>
+      <c r="G15" s="8" t="s">
         <v>373</v>
       </c>
-      <c r="H15" s="6"/>
-      <c r="I15" s="6" t="str">
+      <c r="H15" s="7"/>
+      <c r="I15" s="7" t="str">
         <f>VLOOKUP(I14,$B:$C,2,FALSE)</f>
         <v>302</v>
       </c>
-      <c r="J15" s="6" t="str">
+      <c r="J15" s="7" t="str">
         <f t="shared" ref="J15:L15" si="4">VLOOKUP(J14,$B:$C,2,FALSE)</f>
         <v>889</v>
       </c>
-      <c r="K15" s="6" t="str">
+      <c r="K15" s="7" t="str">
         <f t="shared" si="4"/>
         <v>695</v>
       </c>
-      <c r="L15" s="6" t="str">
+      <c r="L15" s="7" t="str">
         <f t="shared" si="4"/>
         <v>512</v>
       </c>
-      <c r="M15" s="6"/>
+      <c r="M15" s="7"/>
     </row>
     <row r="16" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B16" s="6" t="s">
+      <c r="B16" s="7" t="s">
         <v>361</v>
       </c>
-      <c r="C16" s="6" t="s">
+      <c r="C16" s="7" t="s">
         <v>374</v>
       </c>
-      <c r="G16" s="9" t="str">
+      <c r="G16" s="10" t="str">
         <f>G14&amp;","&amp;G15</f>
         <v>19,30, 22,0</v>
       </c>
-      <c r="H16" s="9"/>
-      <c r="I16" s="9" t="str">
+      <c r="H16" s="10"/>
+      <c r="I16" s="10" t="str">
         <f>I15</f>
         <v>302</v>
       </c>
-      <c r="J16" s="9" t="str">
+      <c r="J16" s="10" t="str">
         <f>I16&amp;","&amp;J15</f>
         <v>302,889</v>
       </c>
-      <c r="K16" s="9" t="str">
+      <c r="K16" s="10" t="str">
         <f>J16&amp;","&amp;K15</f>
         <v>302,889,695</v>
       </c>
-      <c r="L16" s="9" t="str">
+      <c r="L16" s="10" t="str">
         <f>K16&amp;","&amp;L15</f>
         <v>302,889,695,512</v>
       </c>
-      <c r="M16" s="9"/>
-      <c r="N16" s="9"/>
+      <c r="M16" s="10"/>
+      <c r="N16" s="10"/>
     </row>
     <row r="17" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B17" s="6" t="s">
+      <c r="B17" s="7" t="s">
         <v>361</v>
       </c>
-      <c r="C17" s="6" t="s">
+      <c r="C17" s="7" t="s">
         <v>375</v>
       </c>
-      <c r="G17" s="7" t="s">
+      <c r="G17" s="8" t="s">
         <v>376</v>
       </c>
-      <c r="I17" s="6" t="s">
+      <c r="I17" s="7" t="s">
         <v>355</v>
       </c>
-      <c r="J17" s="6" t="s">
+      <c r="J17" s="7" t="s">
         <v>356</v>
       </c>
-      <c r="K17" s="6" t="s">
+      <c r="K17" s="7" t="s">
         <v>357</v>
       </c>
-      <c r="L17" s="6" t="s">
+      <c r="L17" s="7" t="s">
         <v>347</v>
       </c>
     </row>
     <row r="18" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B18" s="6" t="s">
+      <c r="B18" s="7" t="s">
         <v>377</v>
       </c>
-      <c r="C18" s="6" t="s">
+      <c r="C18" s="7" t="s">
         <v>378</v>
       </c>
-      <c r="G18" s="7" t="s">
+      <c r="G18" s="8" t="s">
         <v>379</v>
       </c>
-      <c r="I18" s="6" t="str">
+      <c r="I18" s="7" t="str">
         <f>VLOOKUP(I17,$B:$C,2,FALSE)</f>
         <v>889</v>
       </c>
-      <c r="J18" s="6" t="str">
+      <c r="J18" s="7" t="str">
         <f t="shared" ref="J18:L18" si="5">VLOOKUP(J17,$B:$C,2,FALSE)</f>
         <v>695</v>
       </c>
-      <c r="K18" s="6" t="str">
+      <c r="K18" s="7" t="str">
         <f t="shared" si="5"/>
         <v>512</v>
       </c>
-      <c r="L18" s="6">
+      <c r="L18" s="7">
         <f t="shared" si="5"/>
         <v>2497</v>
       </c>
     </row>
     <row r="19" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B19" s="6" t="s">
+      <c r="B19" s="7" t="s">
         <v>380</v>
       </c>
-      <c r="C19" s="6" t="s">
+      <c r="C19" s="7" t="s">
         <v>381</v>
       </c>
-      <c r="G19" s="9" t="str">
+      <c r="G19" s="10" t="str">
         <f>G17&amp;","&amp;G18</f>
         <v>22,0,24,0</v>
       </c>
-      <c r="H19" s="9"/>
-      <c r="I19" s="9" t="str">
+      <c r="H19" s="10"/>
+      <c r="I19" s="10" t="str">
         <f>I18</f>
         <v>889</v>
       </c>
-      <c r="J19" s="9" t="str">
+      <c r="J19" s="10" t="str">
         <f>I19&amp;","&amp;J18</f>
         <v>889,695</v>
       </c>
-      <c r="K19" s="9" t="str">
+      <c r="K19" s="10" t="str">
         <f t="shared" ref="K19:L19" si="6">J19&amp;","&amp;K18</f>
         <v>889,695,512</v>
       </c>
-      <c r="L19" s="9" t="str">
+      <c r="L19" s="10" t="str">
         <f t="shared" si="6"/>
         <v>889,695,512,2497</v>
       </c>
-      <c r="M19" s="9"/>
-      <c r="N19" s="9"/>
+      <c r="M19" s="10"/>
+      <c r="N19" s="10"/>
     </row>
     <row r="20" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B20" s="6" t="s">
+      <c r="B20" s="7" t="s">
         <v>382</v>
       </c>
-      <c r="C20" s="6">
+      <c r="C20" s="7">
         <v>900</v>
       </c>
-      <c r="G20" s="7"/>
+      <c r="G20" s="8"/>
     </row>
     <row r="21" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B21" s="6" t="s">
+      <c r="B21" s="7" t="s">
         <v>383</v>
       </c>
-      <c r="C21" s="6" t="s">
+      <c r="C21" s="7" t="s">
         <v>384</v>
       </c>
     </row>
     <row r="22" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B22" s="6" t="s">
+      <c r="B22" s="7" t="s">
         <v>385</v>
       </c>
-      <c r="C22" s="6" t="s">
+      <c r="C22" s="7" t="s">
         <v>386</v>
       </c>
     </row>
     <row r="23" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B23" s="6" t="s">
+      <c r="B23" s="7" t="s">
         <v>387</v>
       </c>
-      <c r="C23" s="6" t="s">
+      <c r="C23" s="7" t="s">
         <v>388</v>
       </c>
-      <c r="G23" s="4" t="str">
+      <c r="G23" s="5" t="str">
         <f>G6&amp;","&amp;G9&amp;","&amp;G12&amp;","&amp;G16&amp;","&amp;G19</f>
         <v>6,0,9,0,9,0,17,30,17,30,19,30,19,30, 22,0,22,0,24,0</v>
       </c>
-      <c r="M23" s="6"/>
+      <c r="M23" s="7"/>
     </row>
     <row r="24" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B24" s="6" t="s">
+      <c r="B24" s="7" t="s">
         <v>346</v>
       </c>
-      <c r="C24" s="6" t="s">
+      <c r="C24" s="7" t="s">
         <v>389</v>
       </c>
     </row>
     <row r="25" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B25" s="6" t="s">
+      <c r="B25" s="7" t="s">
         <v>390</v>
       </c>
-      <c r="C25" s="6" t="s">
+      <c r="C25" s="7" t="s">
         <v>391</v>
       </c>
-      <c r="M25" s="6"/>
+      <c r="M25" s="7"/>
     </row>
     <row r="26" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B26" s="6" t="s">
+      <c r="B26" s="7" t="s">
         <v>392</v>
       </c>
-      <c r="C26" s="6" t="s">
+      <c r="C26" s="7" t="s">
         <v>393</v>
       </c>
-      <c r="M26" s="6"/>
+      <c r="M26" s="7"/>
     </row>
     <row r="27" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B27" s="6" t="s">
+      <c r="B27" s="7" t="s">
         <v>369</v>
       </c>
-      <c r="C27" s="6" t="s">
+      <c r="C27" s="7" t="s">
         <v>394</v>
       </c>
-      <c r="M27" s="6"/>
+      <c r="M27" s="7"/>
     </row>
     <row r="28" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B28" s="6" t="s">
+      <c r="B28" s="7" t="s">
         <v>395</v>
       </c>
-      <c r="C28" s="6">
+      <c r="C28" s="7">
         <v>1014</v>
       </c>
-      <c r="M28" s="6"/>
+      <c r="M28" s="7"/>
     </row>
     <row r="29" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B29" s="6" t="s">
+      <c r="B29" s="7" t="s">
         <v>369</v>
       </c>
-      <c r="C29" s="6" t="s">
+      <c r="C29" s="7" t="s">
         <v>396</v>
       </c>
-      <c r="M29" s="6"/>
+      <c r="M29" s="7"/>
     </row>
     <row r="30" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B30" s="6" t="s">
+      <c r="B30" s="7" t="s">
         <v>357</v>
       </c>
-      <c r="C30" s="6" t="s">
+      <c r="C30" s="7" t="s">
         <v>397</v>
       </c>
     </row>
     <row r="31" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B31" s="6" t="s">
+      <c r="B31" s="7" t="s">
         <v>369</v>
       </c>
-      <c r="C31" s="6" t="s">
+      <c r="C31" s="7" t="s">
         <v>398</v>
       </c>
-      <c r="M31" s="6" t="s">
+      <c r="M31" s="7" t="s">
         <v>355</v>
       </c>
     </row>
     <row r="32" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B32" s="6" t="s">
+      <c r="B32" s="7" t="s">
         <v>399</v>
       </c>
-      <c r="C32" s="6">
+      <c r="C32" s="7">
         <v>5309</v>
       </c>
-      <c r="M32" s="6" t="s">
+      <c r="M32" s="7" t="s">
         <v>356</v>
       </c>
     </row>
     <row r="33" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B33" s="6" t="s">
+      <c r="B33" s="7" t="s">
         <v>369</v>
       </c>
-      <c r="C33" s="6" t="s">
+      <c r="C33" s="7" t="s">
         <v>400</v>
       </c>
-      <c r="M33" s="6" t="s">
+      <c r="M33" s="7" t="s">
         <v>357</v>
       </c>
     </row>
     <row r="34" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B34" s="6" t="s">
+      <c r="B34" s="7" t="s">
         <v>355</v>
       </c>
-      <c r="C34" s="6" t="s">
+      <c r="C34" s="7" t="s">
         <v>401</v>
       </c>
     </row>
     <row r="35" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B35" s="6" t="s">
+      <c r="B35" s="7" t="s">
         <v>402</v>
       </c>
-      <c r="C35" s="6" t="s">
+      <c r="C35" s="7" t="s">
         <v>403</v>
       </c>
     </row>
     <row r="36" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B36" s="6" t="s">
+      <c r="B36" s="7" t="s">
         <v>404</v>
       </c>
-      <c r="C36" s="6" t="s">
+      <c r="C36" s="7" t="s">
         <v>405</v>
       </c>
     </row>
     <row r="37" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B37" s="6" t="s">
+      <c r="B37" s="7" t="s">
         <v>406</v>
       </c>
-      <c r="C37" s="6" t="s">
+      <c r="C37" s="7" t="s">
         <v>407</v>
       </c>
     </row>
     <row r="38" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B38" s="6" t="s">
+      <c r="B38" s="7" t="s">
         <v>408</v>
       </c>
-      <c r="C38" s="6">
+      <c r="C38" s="7">
         <v>3056</v>
       </c>
     </row>
     <row r="39" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B39" s="6" t="s">
+      <c r="B39" s="7" t="s">
         <v>409</v>
       </c>
-      <c r="C39" s="6" t="s">
+      <c r="C39" s="7" t="s">
         <v>410</v>
       </c>
     </row>
     <row r="40" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B40" s="6" t="s">
+      <c r="B40" s="7" t="s">
         <v>411</v>
       </c>
-      <c r="C40" s="6" t="s">
+      <c r="C40" s="7" t="s">
         <v>412</v>
       </c>
     </row>
     <row r="41" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B41" s="6" t="s">
+      <c r="B41" s="7" t="s">
         <v>347</v>
       </c>
-      <c r="C41" s="6">
+      <c r="C41" s="7">
         <v>2497</v>
       </c>
     </row>
     <row r="42" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B42" s="6" t="s">
+      <c r="B42" s="7" t="s">
         <v>413</v>
       </c>
-      <c r="C42" s="6" t="s">
+      <c r="C42" s="7" t="s">
         <v>414</v>
       </c>
     </row>
     <row r="43" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B43" s="6" t="s">
+      <c r="B43" s="7" t="s">
         <v>415</v>
       </c>
-      <c r="C43" s="6" t="s">
+      <c r="C43" s="7" t="s">
         <v>416</v>
       </c>
     </row>
     <row r="44" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B44" s="6" t="s">
+      <c r="B44" s="7" t="s">
         <v>369</v>
       </c>
-      <c r="C44" s="6" t="s">
+      <c r="C44" s="7" t="s">
         <v>417</v>
       </c>
     </row>
     <row r="45" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B45" s="6" t="s">
+      <c r="B45" s="7" t="s">
         <v>356</v>
       </c>
-      <c r="C45" s="6" t="s">
+      <c r="C45" s="7" t="s">
         <v>418</v>
       </c>
     </row>
     <row r="46" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B46" s="6" t="s">
+      <c r="B46" s="7" t="s">
         <v>419</v>
       </c>
-      <c r="C46" s="6" t="s">
+      <c r="C46" s="7" t="s">
         <v>420</v>
       </c>
     </row>
     <row r="47" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B47" s="6" t="s">
+      <c r="B47" s="7" t="s">
         <v>421</v>
       </c>
-      <c r="C47" s="6" t="s">
+      <c r="C47" s="7" t="s">
         <v>422</v>
       </c>
     </row>
     <row r="48" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B48" s="10" t="s">
-        <v>976</v>
-      </c>
-      <c r="C48" s="6" t="s">
+      <c r="B48" s="11" t="s">
+        <v>423</v>
+      </c>
+      <c r="C48" s="7" t="s">
         <v>424</v>
       </c>
     </row>
     <row r="49" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B49" s="6" t="s">
+      <c r="B49" s="7" t="s">
         <v>425</v>
       </c>
-      <c r="C49" s="6" t="s">
+      <c r="C49" s="7" t="s">
         <v>426</v>
       </c>
     </row>
     <row r="50" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B50" s="6" t="s">
+      <c r="B50" s="7" t="s">
         <v>427</v>
       </c>
-      <c r="C50" s="6" t="s">
+      <c r="C50" s="7" t="s">
         <v>428</v>
       </c>
     </row>
     <row r="51" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B51" s="6" t="s">
+      <c r="B51" s="7" t="s">
         <v>429</v>
       </c>
-      <c r="C51" s="6">
+      <c r="C51" s="7">
         <v>547</v>
       </c>
     </row>
     <row r="52" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B52" s="6" t="s">
+      <c r="B52" s="7" t="s">
         <v>354</v>
       </c>
-      <c r="C52" s="6" t="s">
+      <c r="C52" s="7" t="s">
         <v>82</v>
       </c>
     </row>
     <row r="53" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B53" s="6" t="s">
+      <c r="B53" s="7" t="s">
         <v>361</v>
       </c>
-      <c r="C53" s="6" t="s">
+      <c r="C53" s="7" t="s">
         <v>430</v>
       </c>
     </row>
     <row r="54" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B54" s="6" t="s">
+      <c r="B54" s="7" t="s">
         <v>361</v>
       </c>
-      <c r="C54" s="6" t="s">
+      <c r="C54" s="7" t="s">
         <v>431</v>
       </c>
     </row>
     <row r="55" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B55" s="6" t="s">
+      <c r="B55" s="7" t="s">
         <v>432</v>
       </c>
-      <c r="C55" s="6" t="s">
+      <c r="C55" s="7" t="s">
         <v>433</v>
       </c>
     </row>
     <row r="56" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B56" s="6" t="s">
+      <c r="B56" s="7" t="s">
         <v>361</v>
       </c>
-      <c r="C56" s="6" t="s">
+      <c r="C56" s="7" t="s">
         <v>434</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="0" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="1200" verticalDpi="1200"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="B1:C212"/>
+  <dimension ref="B1:C228"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B1" s="6" t="s">
+      <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="6" t="s">
+      <c r="C1" s="1" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="2" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B2" s="6" t="s">
+      <c r="B2" s="1" t="s">
         <v>435</v>
       </c>
-      <c r="C2" s="6" t="s">
+      <c r="C2" s="1" t="s">
         <v>436</v>
       </c>
     </row>
     <row r="3" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B3" s="6" t="s">
+      <c r="B3" s="1" t="s">
         <v>437</v>
       </c>
-      <c r="C3" s="6" t="s">
+      <c r="C3" s="1" t="s">
         <v>438</v>
       </c>
     </row>
     <row r="4" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B4" s="6" t="s">
+      <c r="B4" s="1" t="s">
         <v>439</v>
       </c>
-      <c r="C4" s="6" t="s">
+      <c r="C4" s="1" t="s">
         <v>440</v>
       </c>
     </row>
     <row r="5" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B5" s="6" t="s">
+      <c r="B5" s="1" t="s">
         <v>441</v>
       </c>
-      <c r="C5" s="6" t="s">
+      <c r="C5" s="1" t="s">
         <v>442</v>
       </c>
     </row>
     <row r="6" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B6" s="6" t="s">
+      <c r="B6" s="1" t="s">
         <v>443</v>
       </c>
-      <c r="C6" s="6" t="s">
+      <c r="C6" s="1" t="s">
         <v>444</v>
       </c>
     </row>
     <row r="7" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B7" s="6" t="s">
+      <c r="B7" s="1" t="s">
         <v>445</v>
       </c>
-      <c r="C7" s="6" t="s">
+      <c r="C7" s="1" t="s">
         <v>446</v>
       </c>
     </row>
     <row r="8" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B8" s="6" t="s">
+      <c r="B8" s="1" t="s">
         <v>447</v>
       </c>
-      <c r="C8" s="6" t="s">
+      <c r="C8" s="1" t="s">
         <v>446</v>
       </c>
     </row>
     <row r="9" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B9" s="6" t="s">
+      <c r="B9" s="1" t="s">
         <v>448</v>
       </c>
-      <c r="C9" s="6" t="s">
+      <c r="C9" s="1" t="s">
         <v>446</v>
       </c>
     </row>
     <row r="10" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B10" s="6" t="s">
+      <c r="B10" s="1" t="s">
         <v>449</v>
       </c>
-      <c r="C10" s="6" t="s">
+      <c r="C10" s="1" t="s">
         <v>450</v>
       </c>
     </row>
     <row r="11" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B11" s="6" t="s">
+      <c r="B11" s="1" t="s">
         <v>451</v>
       </c>
-      <c r="C11" s="6" t="s">
+      <c r="C11" s="1" t="s">
         <v>452</v>
       </c>
     </row>
     <row r="12" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B12" s="6" t="s">
+      <c r="B12" s="1" t="s">
         <v>453</v>
       </c>
-      <c r="C12" s="6" t="s">
+      <c r="C12" s="1" t="s">
         <v>454</v>
       </c>
     </row>
     <row r="13" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B13" s="6" t="s">
+      <c r="B13" s="1" t="s">
         <v>455</v>
       </c>
-      <c r="C13" s="6" t="s">
+      <c r="C13" s="1" t="s">
         <v>456</v>
       </c>
     </row>
     <row r="14" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B14" s="6" t="s">
+      <c r="B14" s="1" t="s">
         <v>457</v>
       </c>
-      <c r="C14" s="6" t="s">
+      <c r="C14" s="1" t="s">
         <v>458</v>
       </c>
     </row>
     <row r="15" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B15" s="6" t="s">
+      <c r="B15" s="1" t="s">
         <v>459</v>
       </c>
-      <c r="C15" s="6" t="s">
+      <c r="C15" s="1" t="s">
         <v>460</v>
       </c>
     </row>
     <row r="16" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B16" s="6" t="s">
+      <c r="B16" s="1" t="s">
         <v>461</v>
       </c>
-      <c r="C16" s="6" t="s">
+      <c r="C16" s="1" t="s">
         <v>462</v>
       </c>
     </row>
     <row r="17" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B17" s="6" t="s">
+      <c r="B17" s="1" t="s">
         <v>463</v>
       </c>
-      <c r="C17" s="6" t="s">
+      <c r="C17" s="1" t="s">
         <v>464</v>
       </c>
     </row>
     <row r="18" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B18" s="6" t="s">
+      <c r="B18" s="1" t="s">
         <v>465</v>
       </c>
-      <c r="C18" s="6" t="s">
+      <c r="C18" s="1" t="s">
         <v>466</v>
       </c>
     </row>
     <row r="19" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B19" s="6" t="s">
+      <c r="B19" s="1" t="s">
         <v>467</v>
       </c>
-      <c r="C19" s="6" t="s">
+      <c r="C19" s="1" t="s">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="20" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B20" s="1" t="s">
         <v>468</v>
       </c>
-    </row>
-    <row r="20" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B20" s="6" t="s">
+      <c r="C20" s="1" t="s">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="21" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B21" s="1" t="s">
         <v>469</v>
       </c>
-      <c r="C20" s="6" t="s">
+      <c r="C21" s="1" t="s">
         <v>470</v>
       </c>
     </row>
-    <row r="21" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B21" s="6" t="s">
+    <row r="22" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B22" s="1" t="s">
         <v>471</v>
       </c>
-      <c r="C21" s="6" t="s">
+      <c r="C22" s="1" t="s">
         <v>472</v>
       </c>
     </row>
-    <row r="22" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B22" s="6" t="s">
+    <row r="23" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B23" s="1" t="s">
         <v>473</v>
       </c>
-      <c r="C22" s="6" t="s">
+      <c r="C23" s="1" t="s">
         <v>474</v>
       </c>
     </row>
-    <row r="23" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B23" s="6" t="s">
+    <row r="24" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B24" s="1" t="s">
         <v>475</v>
       </c>
-      <c r="C23" s="6" t="s">
+      <c r="C24" s="1" t="s">
         <v>476</v>
       </c>
     </row>
-    <row r="24" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B24" s="6" t="s">
+    <row r="25" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B25" s="1" t="s">
         <v>477</v>
       </c>
-      <c r="C24" s="6" t="s">
+      <c r="C25" s="1" t="s">
         <v>478</v>
       </c>
     </row>
-    <row r="25" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B25" s="6" t="s">
+    <row r="26" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B26" s="1" t="s">
         <v>479</v>
       </c>
-      <c r="C25" s="6" t="s">
+      <c r="C26" s="1" t="s">
         <v>480</v>
       </c>
     </row>
-    <row r="26" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B26" s="6" t="s">
+    <row r="27" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B27" s="1" t="s">
         <v>481</v>
       </c>
-      <c r="C26" s="6" t="s">
+      <c r="C27" s="1" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="28" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B28" s="1" t="s">
         <v>482</v>
       </c>
-    </row>
-    <row r="27" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B27" s="6" t="s">
+      <c r="C28" s="1" t="s">
         <v>483</v>
       </c>
-      <c r="C27" s="6" t="s">
+    </row>
+    <row r="29" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B29" s="1" t="s">
         <v>484</v>
       </c>
-    </row>
-    <row r="28" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B28" s="6" t="s">
+      <c r="C29" s="1" t="s">
         <v>485</v>
       </c>
-      <c r="C28" s="6" t="s">
+    </row>
+    <row r="30" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B30" s="1" t="s">
         <v>486</v>
       </c>
-    </row>
-    <row r="29" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B29" s="6" t="s">
+      <c r="C30" s="1" t="s">
         <v>487</v>
       </c>
-      <c r="C29" s="6" t="s">
+    </row>
+    <row r="31" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B31" s="1" t="s">
         <v>488</v>
       </c>
-    </row>
-    <row r="30" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B30" s="6" t="s">
+      <c r="C31" s="1" t="s">
         <v>489</v>
       </c>
-      <c r="C30" s="6" t="s">
+    </row>
+    <row r="32" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B32" s="1" t="s">
         <v>490</v>
       </c>
-    </row>
-    <row r="31" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B31" s="6" t="s">
+      <c r="C32" s="1" t="s">
         <v>491</v>
       </c>
-      <c r="C31" s="6" t="s">
+    </row>
+    <row r="33" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B33" s="1" t="s">
         <v>492</v>
       </c>
-    </row>
-    <row r="32" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B32" s="6" t="s">
+      <c r="C33" s="1" t="s">
         <v>493</v>
       </c>
-      <c r="C32" s="6" t="s">
+    </row>
+    <row r="34" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B34" s="1" t="s">
         <v>494</v>
       </c>
-    </row>
-    <row r="33" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B33" s="6" t="s">
+      <c r="C34" s="1" t="s">
         <v>495</v>
       </c>
-      <c r="C33" s="6" t="s">
+    </row>
+    <row r="35" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B35" s="1" t="s">
         <v>496</v>
       </c>
-    </row>
-    <row r="34" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B34" s="6" t="s">
+      <c r="C35" s="1" t="s">
         <v>497</v>
       </c>
-      <c r="C34" s="6" t="s">
+    </row>
+    <row r="36" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B36" s="1" t="s">
         <v>498</v>
       </c>
-    </row>
-    <row r="35" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B35" s="6" t="s">
+      <c r="C36" s="1" t="s">
         <v>499</v>
       </c>
-      <c r="C35" s="6" t="s">
+    </row>
+    <row r="37" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B37" s="1" t="s">
         <v>500</v>
       </c>
-    </row>
-    <row r="36" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B36" s="6" t="s">
+      <c r="C37" s="1" t="s">
         <v>501</v>
       </c>
-      <c r="C36" s="6" t="s">
+    </row>
+    <row r="38" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B38" s="1" t="s">
         <v>502</v>
       </c>
-    </row>
-    <row r="37" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B37" s="6" t="s">
+      <c r="C38" s="1" t="s">
         <v>503</v>
       </c>
-      <c r="C37" s="6" t="s">
+    </row>
+    <row r="39" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B39" s="1" t="s">
         <v>504</v>
       </c>
-    </row>
-    <row r="38" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B38" s="6" t="s">
+      <c r="C39" s="1" t="s">
         <v>505</v>
       </c>
-      <c r="C38" s="6" t="s">
+    </row>
+    <row r="40" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B40" s="1" t="s">
         <v>506</v>
       </c>
-    </row>
-    <row r="39" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B39" s="6" t="s">
+      <c r="C40" s="1" t="s">
         <v>507</v>
       </c>
-      <c r="C39" s="6" t="s">
+    </row>
+    <row r="41" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B41" s="1" t="s">
         <v>508</v>
       </c>
-    </row>
-    <row r="40" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B40" s="6" t="s">
+      <c r="C41" s="1" t="s">
         <v>509</v>
       </c>
-      <c r="C40" s="6" t="s">
+    </row>
+    <row r="42" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B42" s="1" t="s">
         <v>510</v>
       </c>
-    </row>
-    <row r="41" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B41" s="6" t="s">
+      <c r="C42" s="1" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="43" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B43" s="1" t="s">
         <v>511</v>
       </c>
-      <c r="C41" s="6" t="s">
+      <c r="C43" s="1" t="s">
         <v>512</v>
       </c>
     </row>
-    <row r="42" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B42" s="6" t="s">
+    <row r="44" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B44" s="1" t="s">
         <v>513</v>
       </c>
-      <c r="C42" s="6" t="s">
+      <c r="C44" s="1" t="s">
         <v>514</v>
       </c>
     </row>
-    <row r="43" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B43" s="6" t="s">
+    <row r="45" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B45" s="1" t="s">
         <v>515</v>
       </c>
-      <c r="C43" s="6" t="s">
+      <c r="C45" s="1" t="s">
         <v>516</v>
       </c>
     </row>
-    <row r="44" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B44" s="6" t="s">
+    <row r="46" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B46" s="1" t="s">
         <v>517</v>
       </c>
-      <c r="C44" s="6" t="s">
+      <c r="C46" s="1" t="s">
         <v>518</v>
       </c>
     </row>
-    <row r="45" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B45" s="6" t="s">
+    <row r="47" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B47" s="1" t="s">
         <v>519</v>
       </c>
-      <c r="C45" s="6" t="s">
+      <c r="C47" s="1" t="s">
         <v>520</v>
       </c>
     </row>
-    <row r="46" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B46" s="6" t="s">
+    <row r="48" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B48" s="1" t="s">
         <v>521</v>
       </c>
-      <c r="C46" s="6" t="s">
+      <c r="C48" s="1" t="s">
         <v>522</v>
       </c>
     </row>
-    <row r="47" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B47" s="6" t="s">
+    <row r="49" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B49" s="1" t="s">
         <v>523</v>
       </c>
-      <c r="C47" s="6" t="s">
+      <c r="C49" s="1" t="s">
         <v>524</v>
       </c>
     </row>
-    <row r="48" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B48" s="6" t="s">
+    <row r="50" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B50" s="1" t="s">
         <v>525</v>
       </c>
-      <c r="C48" s="6" t="s">
+      <c r="C50" s="1" t="s">
         <v>526</v>
       </c>
     </row>
-    <row r="49" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B49" s="6" t="s">
+    <row r="51" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B51" s="1" t="s">
         <v>527</v>
       </c>
-      <c r="C49" s="6" t="s">
+      <c r="C51" s="1" t="s">
         <v>528</v>
       </c>
     </row>
-    <row r="50" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B50" s="6" t="s">
+    <row r="52" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B52" s="1" t="s">
         <v>529</v>
       </c>
-      <c r="C50" s="6" t="s">
+      <c r="C52" s="1" t="s">
         <v>530</v>
       </c>
     </row>
-    <row r="51" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B51" s="6" t="s">
+    <row r="53" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B53" s="1" t="s">
         <v>531</v>
       </c>
-      <c r="C51" s="6" t="s">
+      <c r="C53" s="1" t="s">
         <v>532</v>
       </c>
     </row>
-    <row r="52" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B52" s="6" t="s">
+    <row r="54" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B54" s="1" t="s">
         <v>533</v>
       </c>
-      <c r="C52" s="6" t="s">
+      <c r="C54" s="1" t="s">
         <v>534</v>
       </c>
     </row>
-    <row r="53" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B53" s="6" t="s">
+    <row r="55" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B55" s="1" t="s">
         <v>535</v>
       </c>
-      <c r="C53" s="6" t="s">
+      <c r="C55" s="1" t="s">
         <v>536</v>
       </c>
     </row>
-    <row r="54" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B54" s="6" t="s">
+    <row r="56" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B56" s="1" t="s">
         <v>537</v>
       </c>
-      <c r="C54" s="6" t="s">
+      <c r="C56" s="1" t="s">
         <v>538</v>
       </c>
     </row>
-    <row r="55" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B55" s="6" t="s">
+    <row r="57" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B57" s="1" t="s">
         <v>539</v>
       </c>
-      <c r="C55" s="6" t="s">
+      <c r="C57" s="1" t="s">
         <v>540</v>
       </c>
     </row>
-    <row r="56" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B56" s="6" t="s">
+    <row r="58" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B58" s="1" t="s">
         <v>541</v>
       </c>
-      <c r="C56" s="6" t="s">
+      <c r="C58" s="1" t="s">
         <v>542</v>
       </c>
     </row>
-    <row r="57" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B57" s="6" t="s">
+    <row r="59" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B59" s="1" t="s">
         <v>543</v>
       </c>
-      <c r="C57" s="6" t="s">
+      <c r="C59" s="1" t="s">
         <v>544</v>
       </c>
     </row>
-    <row r="58" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B58" s="6" t="s">
+    <row r="60" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B60" s="1" t="s">
         <v>545</v>
       </c>
-      <c r="C58" s="6" t="s">
+      <c r="C60" s="1" t="s">
         <v>546</v>
       </c>
     </row>
-    <row r="59" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B59" s="6" t="s">
+    <row r="61" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B61" s="1" t="s">
         <v>547</v>
       </c>
-      <c r="C59" s="6" t="s">
+      <c r="C61" s="1" t="s">
         <v>548</v>
       </c>
     </row>
-    <row r="60" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B60" s="6" t="s">
+    <row r="62" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B62" s="1" t="s">
         <v>549</v>
       </c>
-      <c r="C60" s="6" t="s">
+      <c r="C62" s="1" t="s">
         <v>550</v>
       </c>
     </row>
-    <row r="61" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B61" s="6" t="s">
+    <row r="63" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B63" s="1" t="s">
         <v>551</v>
       </c>
-      <c r="C61" s="6" t="s">
+      <c r="C63" s="1" t="s">
         <v>552</v>
       </c>
     </row>
-    <row r="62" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B62" s="6" t="s">
+    <row r="64" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B64" s="1" t="s">
         <v>553</v>
       </c>
-      <c r="C62" s="6" t="s">
+      <c r="C64" s="1" t="s">
+        <v>526</v>
+      </c>
+    </row>
+    <row r="65" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B65" s="1" t="s">
         <v>554</v>
       </c>
-    </row>
-    <row r="63" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B63" s="6" t="s">
+      <c r="C65" s="1" t="s">
         <v>555</v>
       </c>
-      <c r="C63" s="6" t="s">
+    </row>
+    <row r="66" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B66" s="1" t="s">
         <v>556</v>
       </c>
-    </row>
-    <row r="64" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B64" s="6" t="s">
+      <c r="C66" s="1" t="s">
         <v>557</v>
       </c>
-      <c r="C64" s="6" t="s">
+    </row>
+    <row r="67" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B67" s="1" t="s">
         <v>558</v>
       </c>
-    </row>
-    <row r="65" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B65" s="6" t="s">
+      <c r="C67" s="1" t="s">
         <v>559</v>
       </c>
-      <c r="C65" s="6" t="s">
+    </row>
+    <row r="68" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B68" s="1" t="s">
         <v>560</v>
       </c>
-    </row>
-    <row r="66" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B66" s="6" t="s">
+      <c r="C68" s="1" t="s">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="69" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B69" s="1" t="s">
         <v>561</v>
       </c>
-      <c r="C66" s="6" t="s">
+      <c r="C69" s="1" t="s">
         <v>562</v>
       </c>
     </row>
-    <row r="67" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B67" s="6" t="s">
+    <row r="70" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B70" s="1" t="s">
         <v>563</v>
       </c>
-      <c r="C67" s="6" t="s">
+      <c r="C70" s="1" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="71" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B71" s="1" t="s">
         <v>564</v>
       </c>
-    </row>
-    <row r="68" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B68" s="6" t="s">
+      <c r="C71" s="1" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="72" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B72" s="1" t="s">
         <v>565</v>
       </c>
-      <c r="C68" s="6" t="s">
+      <c r="C72" s="1" t="s">
         <v>566</v>
       </c>
     </row>
-    <row r="69" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B69" s="6" t="s">
+    <row r="73" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B73" s="1" t="s">
         <v>567</v>
       </c>
-      <c r="C69" s="6" t="s">
+      <c r="C73" s="1" t="s">
         <v>568</v>
       </c>
     </row>
-    <row r="70" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B70" s="6" t="s">
+    <row r="74" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B74" s="1" t="s">
         <v>569</v>
       </c>
-      <c r="C70" s="6" t="s">
+      <c r="C74" s="1" t="s">
         <v>570</v>
       </c>
     </row>
-    <row r="71" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B71" s="6" t="s">
+    <row r="75" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B75" s="1" t="s">
         <v>571</v>
       </c>
-      <c r="C71" s="6" t="s">
+      <c r="C75" s="1" t="s">
         <v>572</v>
       </c>
     </row>
-    <row r="72" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B72" s="6" t="s">
+    <row r="76" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B76" s="1" t="s">
         <v>573</v>
       </c>
-      <c r="C72" s="6" t="s">
+      <c r="C76" s="1" t="s">
         <v>574</v>
       </c>
     </row>
-    <row r="73" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B73" s="6" t="s">
+    <row r="77" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B77" s="1" t="s">
         <v>575</v>
       </c>
-      <c r="C73" s="6" t="s">
+      <c r="C77" s="1" t="s">
         <v>576</v>
       </c>
     </row>
-    <row r="74" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B74" s="6" t="s">
+    <row r="78" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B78" s="1" t="s">
         <v>577</v>
       </c>
-      <c r="C74" s="6" t="s">
+      <c r="C78" s="1" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="79" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B79" s="1" t="s">
         <v>578</v>
       </c>
-    </row>
-    <row r="75" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B75" s="6" t="s">
+      <c r="C79" s="1" t="s">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="80" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B80" s="1" t="s">
         <v>579</v>
       </c>
-      <c r="C75" s="6" t="s">
+      <c r="C80" s="1" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="81" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B81" s="1" t="s">
         <v>580</v>
       </c>
-    </row>
-    <row r="76" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B76" s="6" t="s">
+      <c r="C81" s="1" t="s">
         <v>581</v>
       </c>
-      <c r="C76" s="6" t="s">
+    </row>
+    <row r="82" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B82" s="1" t="s">
         <v>582</v>
       </c>
-    </row>
-    <row r="77" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B77" s="6">
-        <v>1077</v>
-      </c>
-      <c r="C77" s="6" t="s">
+      <c r="C82" s="1" t="s">
         <v>583</v>
       </c>
     </row>
-    <row r="78" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B78" s="6" t="s">
+    <row r="83" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B83" s="1" t="s">
         <v>584</v>
       </c>
-      <c r="C78" s="6" t="s">
-        <v>392</v>
-      </c>
-    </row>
-    <row r="79" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B79" s="6" t="s">
+      <c r="C83" s="1" t="s">
         <v>585</v>
       </c>
-      <c r="C79" s="6" t="s">
+    </row>
+    <row r="84" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B84" s="1" t="s">
         <v>586</v>
       </c>
-    </row>
-    <row r="80" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B80" s="6" t="s">
+      <c r="C84" s="1" t="s">
         <v>587</v>
       </c>
-      <c r="C80" s="6" t="s">
+    </row>
+    <row r="85" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B85" s="1" t="s">
         <v>588</v>
       </c>
-    </row>
-    <row r="81" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B81" s="6" t="s">
+      <c r="C85" s="1" t="s">
         <v>589</v>
       </c>
-      <c r="C81" s="6" t="s">
+    </row>
+    <row r="86" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B86" s="1" t="s">
         <v>590</v>
       </c>
-    </row>
-    <row r="82" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B82" s="6" t="s">
+      <c r="C86" s="1" t="s">
         <v>591</v>
       </c>
-      <c r="C82" s="6" t="s">
+    </row>
+    <row r="87" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B87" s="1" t="s">
         <v>592</v>
       </c>
-    </row>
-    <row r="83" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B83" s="6" t="s">
+      <c r="C87" s="1" t="s">
         <v>593</v>
       </c>
-      <c r="C83" s="6" t="s">
+    </row>
+    <row r="88" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B88" s="1" t="s">
         <v>594</v>
       </c>
-    </row>
-    <row r="84" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B84" s="6" t="s">
+      <c r="C88" s="1" t="s">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="89" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B89" s="1" t="s">
         <v>595</v>
       </c>
-      <c r="C84" s="6" t="s">
+      <c r="C89" s="1" t="s">
         <v>596</v>
       </c>
     </row>
-    <row r="85" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B85" s="6" t="s">
+    <row r="90" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B90" s="1" t="s">
         <v>597</v>
       </c>
-      <c r="C85" s="6" t="s">
+      <c r="C90" s="1" t="s">
         <v>598</v>
       </c>
     </row>
-    <row r="86" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B86" s="6" t="s">
+    <row r="91" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B91" s="1" t="s">
         <v>599</v>
       </c>
-      <c r="C86" s="6" t="s">
+      <c r="C91" s="1" t="s">
         <v>600</v>
       </c>
     </row>
-    <row r="87" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B87" s="6" t="s">
+    <row r="92" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B92" s="1" t="s">
         <v>601</v>
       </c>
-      <c r="C87" s="6" t="s">
+      <c r="C92" s="1" t="s">
         <v>602</v>
       </c>
     </row>
-    <row r="88" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B88" s="6" t="s">
+    <row r="93" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B93" s="1" t="s">
         <v>603</v>
       </c>
-      <c r="C88" s="6" t="s">
+      <c r="C93" s="1" t="s">
         <v>604</v>
       </c>
     </row>
-    <row r="89" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B89" s="6" t="s">
+    <row r="94" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B94" s="1" t="s">
         <v>605</v>
       </c>
-      <c r="C89" s="6" t="s">
+      <c r="C94" s="1" t="s">
         <v>606</v>
       </c>
     </row>
-    <row r="90" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B90" s="6" t="s">
+    <row r="95" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B95" s="1" t="s">
         <v>607</v>
       </c>
-      <c r="C90" s="6" t="s">
+      <c r="C95" s="1" t="s">
         <v>608</v>
       </c>
     </row>
-    <row r="91" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B91" s="6" t="s">
+    <row r="96" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B96" s="1" t="s">
         <v>609</v>
       </c>
-      <c r="C91" s="6" t="s">
+      <c r="C96" s="1" t="s">
         <v>610</v>
       </c>
     </row>
-    <row r="92" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B92" s="6" t="s">
+    <row r="97" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B97" s="1" t="s">
         <v>611</v>
       </c>
-      <c r="C92" s="6" t="s">
+      <c r="C97" s="1" t="s">
         <v>612</v>
       </c>
     </row>
-    <row r="93" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B93" s="6" t="s">
+    <row r="98" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B98" s="1" t="s">
         <v>613</v>
       </c>
-      <c r="C93" s="6" t="s">
+      <c r="C98" s="1" t="s">
         <v>614</v>
       </c>
     </row>
-    <row r="94" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B94" s="6" t="s">
+    <row r="99" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B99" s="1" t="s">
         <v>615</v>
       </c>
-      <c r="C94" s="6" t="s">
+      <c r="C99" s="1" t="s">
         <v>616</v>
       </c>
     </row>
-    <row r="95" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B95" s="6" t="s">
+    <row r="100" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B100" s="1" t="s">
         <v>617</v>
       </c>
-      <c r="C95" s="6" t="s">
+      <c r="C100" s="1" t="s">
         <v>618</v>
       </c>
     </row>
-    <row r="96" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B96" s="6" t="s">
+    <row r="101" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B101" s="1" t="s">
         <v>619</v>
       </c>
-      <c r="C96" s="6" t="s">
+      <c r="C101" s="1" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="102" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B102" s="1" t="s">
         <v>620</v>
       </c>
-    </row>
-    <row r="97" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B97" s="6" t="s">
+      <c r="C102" s="1" t="s">
         <v>621</v>
       </c>
-      <c r="C97" s="6" t="s">
+    </row>
+    <row r="103" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B103" s="1" t="s">
         <v>622</v>
       </c>
-    </row>
-    <row r="98" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B98" s="6" t="s">
+      <c r="C103" s="1" t="s">
         <v>623</v>
       </c>
-      <c r="C98" s="6" t="s">
+    </row>
+    <row r="104" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B104" s="1" t="s">
         <v>624</v>
       </c>
-    </row>
-    <row r="99" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B99" s="6" t="s">
+      <c r="C104" s="1" t="s">
         <v>625</v>
       </c>
-      <c r="C99" s="6" t="s">
+    </row>
+    <row r="105" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B105" s="1" t="s">
         <v>626</v>
       </c>
-    </row>
-    <row r="100" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B100" s="6" t="s">
+      <c r="C105" s="1" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="106" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B106" s="1" t="s">
         <v>627</v>
       </c>
-      <c r="C100" s="6" t="s">
+      <c r="C106" s="1" t="s">
         <v>628</v>
       </c>
     </row>
-    <row r="101" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B101" s="6" t="s">
+    <row r="107" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B107" s="1" t="s">
         <v>629</v>
       </c>
-      <c r="C101" s="6" t="s">
-        <v>348</v>
-      </c>
-    </row>
-    <row r="102" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B102" s="6" t="s">
+      <c r="C107" s="1" t="s">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="108" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B108" s="1" t="s">
         <v>630</v>
       </c>
-      <c r="C102" s="6" t="s">
+      <c r="C108" s="1" t="s">
         <v>631</v>
       </c>
     </row>
-    <row r="103" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B103" s="6" t="s">
+    <row r="109" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B109" s="1" t="s">
         <v>632</v>
       </c>
-      <c r="C103" s="6" t="s">
+      <c r="C109" s="1" t="s">
         <v>633</v>
       </c>
     </row>
-    <row r="104" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B104" s="6" t="s">
+    <row r="110" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B110" s="1" t="s">
         <v>634</v>
       </c>
-      <c r="C104" s="6" t="s">
+      <c r="C110" s="1" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="111" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B111" s="1" t="s">
         <v>635</v>
       </c>
-    </row>
-    <row r="105" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B105" s="6" t="s">
+      <c r="C111" s="1" t="s">
         <v>636</v>
       </c>
-      <c r="C105" s="6" t="s">
-        <v>350</v>
-      </c>
-    </row>
-    <row r="106" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B106" s="6" t="s">
+    </row>
+    <row r="112" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B112" s="1" t="s">
+        <v>388</v>
+      </c>
+      <c r="C112" s="1" t="s">
         <v>637</v>
       </c>
-      <c r="C106" s="6" t="s">
+    </row>
+    <row r="113" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B113" s="1" t="s">
         <v>638</v>
       </c>
-    </row>
-    <row r="107" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B107" s="6" t="s">
+      <c r="C113" s="1" t="s">
         <v>639</v>
       </c>
-      <c r="C107" s="6" t="s">
-        <v>423</v>
-      </c>
-    </row>
-    <row r="108" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B108" s="6" t="s">
+    </row>
+    <row r="114" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B114" s="1" t="s">
         <v>640</v>
       </c>
-      <c r="C108" s="6" t="s">
+      <c r="C114" s="1" t="s">
         <v>641</v>
       </c>
     </row>
-    <row r="109" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B109" s="6" t="s">
+    <row r="115" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B115" s="1" t="s">
         <v>642</v>
       </c>
-      <c r="C109" s="6" t="s">
+      <c r="C115" s="1" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="116" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B116" s="1" t="s">
         <v>643</v>
       </c>
-    </row>
-    <row r="110" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B110" s="6" t="s">
+      <c r="C116" s="1" t="s">
         <v>644</v>
       </c>
-      <c r="C110" s="6" t="s">
+    </row>
+    <row r="117" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B117" s="1" t="s">
         <v>645</v>
       </c>
-    </row>
-    <row r="111" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B111" s="6" t="s">
+      <c r="C117" s="1" t="s">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="118" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B118" s="1" t="s">
         <v>646</v>
       </c>
-      <c r="C111" s="6" t="s">
+      <c r="C118" s="1" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="119" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B119" s="1" t="s">
         <v>647</v>
       </c>
-    </row>
-    <row r="112" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B112" s="6" t="s">
-        <v>388</v>
-      </c>
-      <c r="C112" s="6" t="s">
+      <c r="C119" s="1" t="s">
         <v>648</v>
       </c>
     </row>
-    <row r="113" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B113" s="6" t="s">
+    <row r="120" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B120" s="1" t="s">
         <v>649</v>
       </c>
-      <c r="C113" s="6" t="s">
+      <c r="C120" s="1" t="s">
         <v>650</v>
       </c>
     </row>
-    <row r="114" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B114" s="6" t="s">
+    <row r="121" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B121" s="1" t="s">
         <v>651</v>
       </c>
-      <c r="C114" s="6" t="s">
+      <c r="C121" s="1" t="s">
         <v>652</v>
       </c>
     </row>
-    <row r="115" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B115" s="6" t="s">
+    <row r="122" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B122" s="1" t="s">
         <v>653</v>
       </c>
-      <c r="C115" s="6" t="s">
-        <v>592</v>
-      </c>
-    </row>
-    <row r="116" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B116" s="6" t="s">
+      <c r="C122" s="1" t="s">
         <v>654</v>
       </c>
-      <c r="C116" s="6" t="s">
+    </row>
+    <row r="123" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B123" s="1" t="s">
         <v>655</v>
       </c>
-    </row>
-    <row r="117" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B117" s="6" t="s">
+      <c r="C123" s="1" t="s">
         <v>656</v>
       </c>
-      <c r="C117" s="6" t="s">
-        <v>383</v>
-      </c>
-    </row>
-    <row r="118" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B118" s="6" t="s">
+    </row>
+    <row r="124" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B124" s="1" t="s">
         <v>657</v>
       </c>
-      <c r="C118" s="6" t="s">
-        <v>367</v>
-      </c>
-    </row>
-    <row r="119" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B119" s="6" t="s">
+      <c r="C124" s="1" t="s">
+        <v>648</v>
+      </c>
+    </row>
+    <row r="125" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B125" s="1" t="s">
         <v>658</v>
       </c>
-      <c r="C119" s="6" t="s">
+      <c r="C125" s="1" t="s">
+        <v>650</v>
+      </c>
+    </row>
+    <row r="126" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B126" s="1" t="s">
         <v>659</v>
       </c>
-    </row>
-    <row r="120" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B120" s="6" t="s">
+      <c r="C126" s="1" t="s">
         <v>660</v>
       </c>
-      <c r="C120" s="6" t="s">
+    </row>
+    <row r="127" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B127" s="1" t="s">
         <v>661</v>
       </c>
-    </row>
-    <row r="121" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B121" s="6" t="s">
+      <c r="C127" s="1" t="s">
         <v>662</v>
       </c>
-      <c r="C121" s="6" t="s">
+    </row>
+    <row r="128" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B128" s="1" t="s">
         <v>663</v>
       </c>
-    </row>
-    <row r="122" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B122" s="6" t="s">
+      <c r="C128" s="1" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="129" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B129" s="1" t="s">
         <v>664</v>
       </c>
-      <c r="C122" s="6" t="s">
+      <c r="C129" s="1" t="s">
         <v>665</v>
       </c>
     </row>
-    <row r="123" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B123" s="6" t="s">
+    <row r="130" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B130" s="1" t="s">
         <v>666</v>
       </c>
-      <c r="C123" s="6" t="s">
+      <c r="C130" s="1" t="s">
         <v>667</v>
       </c>
     </row>
-    <row r="124" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B124" s="6" t="s">
+    <row r="131" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B131" s="1" t="s">
         <v>668</v>
       </c>
-      <c r="C124" s="6" t="s">
+      <c r="C131" s="1" t="s">
         <v>669</v>
       </c>
     </row>
-    <row r="125" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B125" s="6" t="s">
+    <row r="132" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B132" s="1" t="s">
         <v>670</v>
       </c>
-      <c r="C125" s="6" t="s">
+      <c r="C132" s="1" t="s">
+        <v>654</v>
+      </c>
+    </row>
+    <row r="133" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B133" s="1" t="s">
         <v>671</v>
       </c>
-    </row>
-    <row r="126" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B126" s="6" t="s">
+      <c r="C133" s="1" t="s">
+        <v>656</v>
+      </c>
+    </row>
+    <row r="134" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B134" s="1" t="s">
         <v>672</v>
       </c>
-      <c r="C126" s="6" t="s">
+      <c r="C134" s="1" t="s">
         <v>673</v>
       </c>
     </row>
-    <row r="127" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B127" s="6" t="s">
+    <row r="135" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B135" s="1" t="s">
         <v>674</v>
       </c>
-      <c r="C127" s="6" t="s">
+      <c r="C135" s="1" t="s">
         <v>675</v>
       </c>
     </row>
-    <row r="128" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B128" s="6" t="s">
+    <row r="136" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B136" s="1" t="s">
         <v>676</v>
       </c>
-      <c r="C128" s="6" t="s">
+      <c r="C136" s="1" t="s">
         <v>677</v>
       </c>
     </row>
-    <row r="129" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B129" s="6" t="s">
+    <row r="137" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B137" s="1" t="s">
         <v>678</v>
       </c>
-      <c r="C129" s="6" t="s">
+      <c r="C137" s="1" t="s">
         <v>679</v>
       </c>
     </row>
-    <row r="130" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B130" s="6" t="s">
+    <row r="138" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B138" s="1" t="s">
         <v>680</v>
       </c>
-      <c r="C130" s="6" t="s">
+      <c r="C138" s="1" t="s">
         <v>681</v>
       </c>
     </row>
-    <row r="131" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B131" s="6" t="s">
+    <row r="139" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B139" s="1" t="s">
         <v>682</v>
       </c>
-      <c r="C131" s="6" t="s">
+      <c r="C139" s="1" t="s">
         <v>683</v>
       </c>
     </row>
-    <row r="132" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B132" s="6" t="s">
+    <row r="140" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B140" s="1" t="s">
         <v>684</v>
       </c>
-      <c r="C132" s="6" t="s">
+      <c r="C140" s="1" t="s">
         <v>685</v>
       </c>
     </row>
-    <row r="133" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B133" s="6" t="s">
+    <row r="141" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B141" s="1" t="s">
         <v>686</v>
       </c>
-      <c r="C133" s="6" t="s">
+      <c r="C141" s="1" t="s">
         <v>687</v>
       </c>
     </row>
-    <row r="134" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B134" s="6" t="s">
+    <row r="142" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B142" s="1" t="s">
         <v>688</v>
       </c>
-      <c r="C134" s="6" t="s">
+      <c r="C142" s="1" t="s">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="143" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B143" s="1" t="s">
         <v>689</v>
       </c>
-    </row>
-    <row r="135" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B135" s="6" t="s">
+      <c r="C143" s="1" t="s">
         <v>690</v>
       </c>
-      <c r="C135" s="6" t="s">
+    </row>
+    <row r="144" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B144" s="1" t="s">
         <v>691</v>
       </c>
-    </row>
-    <row r="136" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B136" s="6" t="s">
+      <c r="C144" s="1" t="s">
         <v>692</v>
       </c>
-      <c r="C136" s="6" t="s">
+    </row>
+    <row r="145" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B145" s="1" t="s">
         <v>693</v>
       </c>
-    </row>
-    <row r="137" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B137" s="6" t="s">
+      <c r="C145" s="1" t="s">
         <v>694</v>
       </c>
-      <c r="C137" s="6" t="s">
+    </row>
+    <row r="146" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B146" s="1" t="s">
         <v>695</v>
       </c>
-    </row>
-    <row r="138" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B138" s="6" t="s">
+      <c r="C146" s="1" t="s">
         <v>696</v>
       </c>
-      <c r="C138" s="6" t="s">
+    </row>
+    <row r="147" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B147" s="1" t="s">
         <v>697</v>
       </c>
-    </row>
-    <row r="139" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B139" s="6" t="s">
+      <c r="C147" s="1" t="s">
         <v>698</v>
       </c>
-      <c r="C139" s="6" t="s">
+    </row>
+    <row r="148" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B148" s="1" t="s">
         <v>699</v>
       </c>
-    </row>
-    <row r="140" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B140" s="6" t="s">
+      <c r="C148" s="1" t="s">
         <v>700</v>
       </c>
-      <c r="C140" s="6" t="s">
+    </row>
+    <row r="149" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B149" s="1" t="s">
         <v>701</v>
       </c>
-    </row>
-    <row r="141" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B141" s="6" t="s">
+      <c r="C149" s="1" t="s">
         <v>702</v>
       </c>
-      <c r="C141" s="6" t="s">
+    </row>
+    <row r="150" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B150" s="1" t="s">
         <v>703</v>
       </c>
-    </row>
-    <row r="142" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B142" s="6" t="s">
+      <c r="C150" s="1" t="s">
         <v>704</v>
       </c>
-      <c r="C142" s="6" t="s">
+    </row>
+    <row r="151" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B151" s="1" t="s">
         <v>705</v>
       </c>
-    </row>
-    <row r="143" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B143" s="6" t="s">
+      <c r="C151" s="1" t="s">
         <v>706</v>
       </c>
-      <c r="C143" s="6" t="s">
+    </row>
+    <row r="152" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B152" s="1" t="s">
         <v>707</v>
       </c>
-    </row>
-    <row r="144" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B144" s="6" t="s">
+      <c r="C152" s="1" t="s">
         <v>708</v>
       </c>
-      <c r="C144" s="6" t="s">
+    </row>
+    <row r="153" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B153" s="1" t="s">
         <v>709</v>
       </c>
-    </row>
-    <row r="145" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B145" s="6" t="s">
+      <c r="C153" s="1" t="s">
         <v>710</v>
       </c>
-      <c r="C145" s="6" t="s">
+    </row>
+    <row r="154" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B154" s="1" t="s">
         <v>711</v>
       </c>
-    </row>
-    <row r="146" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B146" s="6" t="s">
+      <c r="C154" s="1" t="s">
         <v>712</v>
       </c>
-      <c r="C146" s="6" t="s">
+    </row>
+    <row r="155" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B155" s="1" t="s">
         <v>713</v>
       </c>
-    </row>
-    <row r="147" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B147" s="6" t="s">
+      <c r="C155" s="1" t="s">
         <v>714</v>
       </c>
-      <c r="C147" s="6" t="s">
+    </row>
+    <row r="156" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B156" s="1" t="s">
         <v>715</v>
       </c>
-    </row>
-    <row r="148" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B148" s="6" t="s">
+      <c r="C156" s="1" t="s">
         <v>716</v>
       </c>
-      <c r="C148" s="6" t="s">
+    </row>
+    <row r="157" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B157" s="1" t="s">
         <v>717</v>
       </c>
-    </row>
-    <row r="149" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B149" s="6" t="s">
+      <c r="C157" s="1" t="s">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="158" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B158" s="1" t="s">
         <v>718</v>
       </c>
-      <c r="C149" s="6" t="s">
+      <c r="C158" s="1" t="s">
         <v>719</v>
       </c>
     </row>
-    <row r="150" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B150" s="6" t="s">
+    <row r="159" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B159" s="1" t="s">
         <v>720</v>
       </c>
-      <c r="C150" s="6" t="s">
+      <c r="C159" s="1" t="s">
         <v>721</v>
       </c>
     </row>
-    <row r="151" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B151" s="6" t="s">
+    <row r="160" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B160" s="1" t="s">
         <v>722</v>
       </c>
-      <c r="C151" s="6" t="s">
+      <c r="C160" s="1" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="161" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B161" s="1" t="s">
         <v>723</v>
       </c>
-    </row>
-    <row r="152" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B152" s="6" t="s">
+      <c r="C161" s="1" t="s">
         <v>724</v>
       </c>
-      <c r="C152" s="6" t="s">
+    </row>
+    <row r="162" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B162" s="1" t="s">
         <v>725</v>
       </c>
-    </row>
-    <row r="153" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B153" s="6" t="s">
+      <c r="C162" s="1" t="s">
         <v>726</v>
       </c>
-      <c r="C153" s="6" t="s">
+    </row>
+    <row r="163" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B163" s="1" t="s">
         <v>727</v>
       </c>
-    </row>
-    <row r="154" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B154" s="6" t="s">
+      <c r="C163" s="1" t="s">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="164" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B164" s="1" t="s">
         <v>728</v>
       </c>
-      <c r="C154" s="6" t="s">
+      <c r="C164" s="1" t="s">
         <v>729</v>
       </c>
     </row>
-    <row r="155" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B155" s="6" t="s">
+    <row r="165" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B165" s="1" t="s">
         <v>730</v>
       </c>
-      <c r="C155" s="6" t="s">
+      <c r="C165" s="1" t="s">
         <v>731</v>
       </c>
     </row>
-    <row r="156" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B156" s="6" t="s">
+    <row r="166" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B166" s="1" t="s">
         <v>732</v>
       </c>
-      <c r="C156" s="6" t="s">
+      <c r="C166" s="1" t="s">
         <v>733</v>
       </c>
     </row>
-    <row r="157" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B157" s="6" t="s">
+    <row r="167" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B167" s="1" t="s">
         <v>734</v>
       </c>
-      <c r="C157" s="6" t="s">
+      <c r="C167" s="1" t="s">
         <v>735</v>
       </c>
     </row>
-    <row r="158" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B158" s="6" t="s">
+    <row r="168" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B168" s="1" t="s">
         <v>736</v>
       </c>
-      <c r="C158" s="6" t="s">
+      <c r="C168" s="1" t="s">
         <v>737</v>
       </c>
     </row>
-    <row r="159" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B159" s="6" t="s">
+    <row r="169" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B169" s="1" t="s">
         <v>738</v>
       </c>
-      <c r="C159" s="6" t="s">
+      <c r="C169" s="1" t="s">
         <v>739</v>
       </c>
     </row>
-    <row r="160" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B160" s="6" t="s">
+    <row r="170" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B170" s="1" t="s">
         <v>740</v>
       </c>
-      <c r="C160" s="6" t="s">
+      <c r="C170" s="1" t="s">
         <v>741</v>
       </c>
     </row>
-    <row r="161" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B161" s="6" t="s">
+    <row r="171" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B171" s="1" t="s">
         <v>742</v>
       </c>
-      <c r="C161" s="6" t="s">
+      <c r="C171" s="1" t="s">
         <v>743</v>
       </c>
     </row>
-    <row r="162" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B162" s="6" t="s">
+    <row r="172" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B172" s="1" t="s">
         <v>744</v>
       </c>
-      <c r="C162" s="6" t="s">
+      <c r="C172" s="1" t="s">
         <v>745</v>
       </c>
     </row>
-    <row r="163" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B163" s="6" t="s">
+    <row r="173" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B173" s="1" t="s">
         <v>746</v>
       </c>
-      <c r="C163" s="6" t="s">
+      <c r="C173" s="1" t="s">
         <v>747</v>
       </c>
     </row>
-    <row r="164" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B164" s="6" t="s">
+    <row r="174" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B174" s="1" t="s">
         <v>748</v>
       </c>
-      <c r="C164" s="6" t="s">
+      <c r="C174" s="1" t="s">
         <v>749</v>
       </c>
     </row>
-    <row r="165" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B165" s="6" t="s">
+    <row r="175" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B175" s="1" t="s">
         <v>750</v>
       </c>
-      <c r="C165" s="6" t="s">
+      <c r="C175" s="1" t="s">
         <v>751</v>
       </c>
     </row>
-    <row r="166" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B166" s="6" t="s">
+    <row r="176" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B176" s="1" t="s">
         <v>752</v>
       </c>
-      <c r="C166" s="6" t="s">
+      <c r="C176" s="1" t="s">
+        <v>751</v>
+      </c>
+    </row>
+    <row r="177" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B177" s="1" t="s">
         <v>753</v>
       </c>
-    </row>
-    <row r="167" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B167" s="6" t="s">
+      <c r="C177" s="1" t="s">
         <v>754</v>
       </c>
-      <c r="C167" s="6" t="s">
+    </row>
+    <row r="178" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B178" s="1" t="s">
         <v>755</v>
       </c>
-    </row>
-    <row r="168" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B168" s="6" t="s">
+      <c r="C178" s="1" t="s">
         <v>756</v>
       </c>
-      <c r="C168" s="6" t="s">
+    </row>
+    <row r="179" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B179" s="1" t="s">
         <v>757</v>
       </c>
-    </row>
-    <row r="169" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B169" s="6" t="s">
+      <c r="C179" s="1" t="s">
         <v>758</v>
       </c>
-      <c r="C169" s="6" t="s">
+    </row>
+    <row r="180" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B180" s="1" t="s">
         <v>759</v>
       </c>
-    </row>
-    <row r="170" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B170" s="6" t="s">
+      <c r="C180" s="1" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="181" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B181" s="1" t="s">
         <v>760</v>
       </c>
-      <c r="C170" s="6" t="s">
+      <c r="C181" s="1" t="s">
         <v>761</v>
       </c>
     </row>
-    <row r="171" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B171" s="6" t="s">
+    <row r="182" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B182" s="1" t="s">
         <v>762</v>
       </c>
-      <c r="C171" s="6" t="s">
+      <c r="C182" s="1" t="s">
         <v>763</v>
       </c>
     </row>
-    <row r="172" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B172" s="6" t="s">
+    <row r="183" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B183" s="1" t="s">
         <v>764</v>
       </c>
-      <c r="C172" s="6" t="s">
+      <c r="C183" s="1" t="s">
         <v>765</v>
       </c>
     </row>
-    <row r="173" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B173" s="6" t="s">
+    <row r="184" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B184" s="1" t="s">
         <v>766</v>
       </c>
-      <c r="C173" s="6" t="s">
+      <c r="C184" s="1" t="s">
+        <v>491</v>
+      </c>
+    </row>
+    <row r="185" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B185" s="1" t="s">
         <v>767</v>
       </c>
-    </row>
-    <row r="174" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B174" s="6" t="s">
+      <c r="C185" s="1" t="s">
+        <v>667</v>
+      </c>
+    </row>
+    <row r="186" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B186" s="1" t="s">
         <v>768</v>
       </c>
-      <c r="C174" s="6" t="s">
+      <c r="C186" s="1" t="s">
+        <v>669</v>
+      </c>
+    </row>
+    <row r="187" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B187" s="1" t="s">
         <v>769</v>
       </c>
-    </row>
-    <row r="175" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B175" s="6" t="s">
+      <c r="C187" s="1" t="s">
+        <v>662</v>
+      </c>
+    </row>
+    <row r="188" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B188" s="1" t="s">
+        <v>770</v>
+      </c>
+      <c r="C188" s="1" t="s">
+        <v>665</v>
+      </c>
+    </row>
+    <row r="189" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B189" s="1" t="s">
+        <v>771</v>
+      </c>
+      <c r="C189" s="1" t="s">
+        <v>660</v>
+      </c>
+    </row>
+    <row r="190" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B190" s="1" t="s">
         <v>393</v>
       </c>
-      <c r="C175" s="6" t="s">
-        <v>770</v>
-      </c>
-    </row>
-    <row r="176" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B176" s="6" t="s">
-        <v>771</v>
-      </c>
-      <c r="C176" s="6" t="s">
+      <c r="C190" s="1" t="s">
         <v>772</v>
       </c>
     </row>
-    <row r="177" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B177" s="6" t="s">
+    <row r="191" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B191" s="1" t="s">
         <v>773</v>
       </c>
-      <c r="C177" s="6" t="s">
+      <c r="C191" s="1" t="s">
         <v>774</v>
       </c>
     </row>
-    <row r="178" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B178" s="6" t="s">
+    <row r="192" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B192" s="1" t="s">
         <v>775</v>
       </c>
-      <c r="C178" s="6" t="s">
+      <c r="C192" s="1" t="s">
         <v>776</v>
       </c>
     </row>
-    <row r="179" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B179" s="6" t="s">
+    <row r="193" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B193" s="1" t="s">
         <v>777</v>
       </c>
-      <c r="C179" s="6" t="s">
+      <c r="C193" s="1" t="s">
         <v>778</v>
       </c>
     </row>
-    <row r="180" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B180" s="6" t="s">
+    <row r="194" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B194" s="1" t="s">
         <v>779</v>
       </c>
-      <c r="C180" s="6" t="s">
+      <c r="C194" s="1" t="s">
         <v>780</v>
       </c>
     </row>
-    <row r="181" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B181" s="6" t="s">
+    <row r="195" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B195" s="1" t="s">
         <v>781</v>
       </c>
-      <c r="C181" s="6" t="s">
+      <c r="C195" s="1" t="s">
         <v>782</v>
       </c>
     </row>
-    <row r="182" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B182" s="6" t="s">
+    <row r="196" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B196" s="1" t="s">
         <v>783</v>
       </c>
-      <c r="C182" s="6" t="s">
+      <c r="C196" s="1" t="s">
         <v>784</v>
       </c>
     </row>
-    <row r="183" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B183" s="6" t="s">
+    <row r="197" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B197" s="1" t="s">
         <v>785</v>
       </c>
-      <c r="C183" s="6" t="s">
+      <c r="C197" s="1" t="s">
         <v>786</v>
       </c>
     </row>
-    <row r="184" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B184" s="6" t="s">
+    <row r="198" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B198" s="1" t="s">
         <v>787</v>
       </c>
-      <c r="C184" s="6" t="s">
+      <c r="C198" s="1" t="s">
+        <v>526</v>
+      </c>
+    </row>
+    <row r="199" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B199" s="1" t="s">
         <v>788</v>
       </c>
-    </row>
-    <row r="185" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B185" s="6" t="s">
+      <c r="C199" s="1" t="s">
         <v>789</v>
       </c>
-      <c r="C185" s="6" t="s">
+    </row>
+    <row r="200" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B200" s="1" t="s">
         <v>790</v>
       </c>
-    </row>
-    <row r="186" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B186" s="6" t="s">
+      <c r="C200" s="1" t="s">
         <v>791</v>
       </c>
-      <c r="C186" s="6" t="s">
+    </row>
+    <row r="201" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B201" s="1" t="s">
         <v>792</v>
       </c>
-    </row>
-    <row r="187" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B187" s="6" t="s">
+      <c r="C201" s="1" t="s">
         <v>793</v>
       </c>
-      <c r="C187" s="6" t="s">
+    </row>
+    <row r="202" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B202" s="1" t="s">
         <v>794</v>
       </c>
-    </row>
-    <row r="188" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B188" s="6" t="s">
+      <c r="C202" s="1" t="s">
         <v>795</v>
       </c>
-      <c r="C188" s="6" t="s">
+    </row>
+    <row r="203" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B203" s="1" t="s">
         <v>796</v>
       </c>
-    </row>
-    <row r="189" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B189" s="6" t="s">
+      <c r="C203" s="1" t="s">
         <v>797</v>
       </c>
-      <c r="C189" s="6" t="s">
+    </row>
+    <row r="204" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B204" s="1" t="s">
         <v>798</v>
       </c>
-    </row>
-    <row r="190" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B190" s="6" t="s">
+      <c r="C204" s="1" t="s">
         <v>799</v>
       </c>
-      <c r="C190" s="6" t="s">
+    </row>
+    <row r="205" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B205" s="1" t="s">
         <v>800</v>
       </c>
-    </row>
-    <row r="191" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B191" s="6" t="s">
+      <c r="C205" s="1" t="s">
         <v>801</v>
       </c>
-      <c r="C191" s="6" t="s">
+    </row>
+    <row r="206" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B206" s="1" t="s">
         <v>802</v>
       </c>
-    </row>
-    <row r="192" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B192" s="6" t="s">
+      <c r="C206" s="1" t="s">
         <v>803</v>
       </c>
-      <c r="C192" s="6" t="s">
+    </row>
+    <row r="207" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B207" s="1" t="s">
         <v>804</v>
       </c>
-    </row>
-    <row r="193" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B193" s="6" t="s">
+      <c r="C207" s="1" t="s">
         <v>805</v>
       </c>
-      <c r="C193" s="6" t="s">
+    </row>
+    <row r="208" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B208" s="1" t="s">
         <v>806</v>
       </c>
-    </row>
-    <row r="194" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B194" s="6" t="s">
+      <c r="C208" s="1" t="s">
         <v>807</v>
       </c>
-      <c r="C194" s="6" t="s">
+    </row>
+    <row r="209" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B209" s="1" t="s">
         <v>808</v>
       </c>
-    </row>
-    <row r="195" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B195" s="6" t="s">
+      <c r="C209" s="1" t="s">
         <v>809</v>
       </c>
-      <c r="C195" s="6" t="s">
+    </row>
+    <row r="210" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B210" s="1" t="s">
         <v>810</v>
       </c>
-    </row>
-    <row r="196" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B196" s="6" t="s">
+      <c r="C210" s="1" t="s">
         <v>811</v>
       </c>
-      <c r="C196" s="6" t="s">
+    </row>
+    <row r="211" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B211" s="1" t="s">
         <v>812</v>
       </c>
-    </row>
-    <row r="197" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B197" s="6" t="s">
+      <c r="C211" s="1" t="s">
         <v>813</v>
       </c>
-      <c r="C197" s="6" t="s">
+    </row>
+    <row r="212" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B212" s="1" t="s">
         <v>814</v>
       </c>
-    </row>
-    <row r="198" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B198" s="6" t="s">
+      <c r="C212" s="1" t="s">
         <v>815</v>
       </c>
-      <c r="C198" s="6" t="s">
+    </row>
+    <row r="213" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B213" s="1" t="s">
         <v>816</v>
       </c>
-    </row>
-    <row r="199" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B199" s="6" t="s">
+      <c r="C213" s="1" t="s">
         <v>817</v>
       </c>
-      <c r="C199" s="6" t="s">
+    </row>
+    <row r="214" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B214" s="1" t="s">
         <v>818</v>
       </c>
-    </row>
-    <row r="200" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B200" s="6" t="s">
+      <c r="C214" s="1" t="s">
         <v>819</v>
       </c>
-      <c r="C200" s="6" t="s">
+    </row>
+    <row r="215" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B215" s="1" t="s">
         <v>820</v>
       </c>
-    </row>
-    <row r="201" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B201" s="6" t="s">
+      <c r="C215" s="1" t="s">
         <v>821</v>
       </c>
-      <c r="C201" s="6" t="s">
+    </row>
+    <row r="216" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B216" s="1" t="s">
         <v>822</v>
       </c>
-    </row>
-    <row r="202" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B202" s="6" t="s">
+      <c r="C216" s="1" t="s">
         <v>823</v>
       </c>
-      <c r="C202" s="6" t="s">
+    </row>
+    <row r="217" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B217" s="1" t="s">
         <v>824</v>
       </c>
-    </row>
-    <row r="203" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B203" s="6" t="s">
+      <c r="C217" s="1" t="s">
         <v>825</v>
       </c>
-      <c r="C203" s="6" t="s">
-        <v>788</v>
-      </c>
-    </row>
-    <row r="204" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B204" s="6" t="s">
+    </row>
+    <row r="218" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B218" s="1" t="s">
         <v>826</v>
       </c>
-      <c r="C204" s="6" t="s">
+      <c r="C218" s="1" t="s">
         <v>827</v>
       </c>
     </row>
-    <row r="205" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B205" s="6" t="s">
+    <row r="219" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B219" s="1" t="s">
         <v>828</v>
       </c>
-      <c r="C205" s="6" t="s">
+      <c r="C219" s="1" t="s">
+        <v>791</v>
+      </c>
+    </row>
+    <row r="220" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B220" s="1" t="s">
         <v>829</v>
       </c>
-    </row>
-    <row r="206" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B206" s="6" t="s">
+      <c r="C220" s="1" t="s">
         <v>830</v>
       </c>
-      <c r="C206" s="6" t="s">
+    </row>
+    <row r="221" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B221" s="1" t="s">
         <v>831</v>
       </c>
-    </row>
-    <row r="207" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B207" s="6" t="s">
+      <c r="C221" s="1" t="s">
         <v>832</v>
       </c>
-      <c r="C207" s="6" t="s">
+    </row>
+    <row r="222" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B222" s="1" t="s">
         <v>833</v>
       </c>
-    </row>
-    <row r="208" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B208" s="6" t="s">
+      <c r="C222" s="1" t="s">
         <v>834</v>
       </c>
-      <c r="C208" s="6" t="s">
+    </row>
+    <row r="223" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B223" s="1" t="s">
         <v>835</v>
       </c>
-    </row>
-    <row r="209" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B209" s="6" t="s">
+      <c r="C223" s="1" t="s">
         <v>836</v>
       </c>
-      <c r="C209" s="6" t="s">
+    </row>
+    <row r="224" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B224" s="1" t="s">
         <v>837</v>
       </c>
-    </row>
-    <row r="210" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B210" s="6" t="s">
+      <c r="C224" s="1" t="s">
         <v>838</v>
       </c>
-      <c r="C210" s="6" t="s">
+    </row>
+    <row r="225" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B225" s="1" t="s">
         <v>839</v>
       </c>
-    </row>
-    <row r="211" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B211" s="6" t="s">
+      <c r="C225" s="1" t="s">
         <v>840</v>
       </c>
-      <c r="C211" s="6" t="s">
+    </row>
+    <row r="226" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B226" s="1" t="s">
         <v>841</v>
       </c>
-    </row>
-    <row r="212" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B212" s="6" t="s">
+      <c r="C226" s="1" t="s">
         <v>842</v>
       </c>
-      <c r="C212" s="6" t="s">
+    </row>
+    <row r="227" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B227" s="1" t="s">
         <v>843</v>
+      </c>
+      <c r="C227" s="1" t="s">
+        <v>844</v>
+      </c>
+    </row>
+    <row r="228" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B228" s="1" t="s">
+        <v>845</v>
+      </c>
+      <c r="C228" s="1" t="s">
+        <v>846</v>
       </c>
     </row>
   </sheetData>
@@ -6068,1354 +6201,1354 @@
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="2" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B2" s="1" t="s">
+      <c r="B2" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="C2" s="2" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="3" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B3" s="1" t="s">
+      <c r="B3" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="C3" s="2" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="4" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B4" s="1" t="s">
+      <c r="B4" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="C4" s="1" t="s">
+      <c r="C4" s="2" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="5" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B5" s="1" t="s">
+      <c r="B5" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="C5" s="1" t="s">
+      <c r="C5" s="2" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="6" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B6" s="1" t="s">
+      <c r="B6" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="C6" s="1" t="s">
+      <c r="C6" s="2" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="7" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B7" s="1" t="s">
+      <c r="B7" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="C7" s="1" t="s">
+      <c r="C7" s="2" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="8" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B8" s="1" t="s">
+      <c r="B8" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="C8" s="1" t="s">
+      <c r="C8" s="2" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="9" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B9" s="1" t="s">
+      <c r="B9" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C9" s="1" t="s">
+      <c r="C9" s="2" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="10" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B10" s="1" t="s">
+      <c r="B10" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="C10" s="1" t="s">
+      <c r="C10" s="2" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="11" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B11" s="1" t="s">
+      <c r="B11" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="C11" s="1" t="s">
+      <c r="C11" s="2" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="12" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B12" s="1" t="s">
+      <c r="B12" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="C12" s="1" t="s">
+      <c r="C12" s="2" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="13" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B13" s="1" t="s">
+      <c r="B13" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="C13" s="1" t="s">
+      <c r="C13" s="2" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="14" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B14" s="1" t="s">
+      <c r="B14" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="C14" s="1" t="s">
+      <c r="C14" s="2" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="15" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B15" s="1" t="s">
+      <c r="B15" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="C15" s="1" t="s">
+      <c r="C15" s="2" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="16" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B16" s="1" t="s">
+      <c r="B16" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="C16" s="1" t="s">
+      <c r="C16" s="2" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="17" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B17" s="1" t="s">
+      <c r="B17" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="C17" s="1" t="s">
+      <c r="C17" s="2" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="18" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B18" s="1" t="s">
+      <c r="B18" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="C18" s="1" t="s">
+      <c r="C18" s="2" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="19" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B19" s="1" t="s">
+      <c r="B19" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="C19" s="1" t="s">
+      <c r="C19" s="2" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="20" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B20" s="1" t="s">
+      <c r="B20" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="C20" s="1" t="s">
+      <c r="C20" s="2" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="21" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B21" s="1" t="s">
+      <c r="B21" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="C21" s="1" t="s">
+      <c r="C21" s="2" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="22" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B22" s="1" t="s">
+      <c r="B22" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="C22" s="1" t="s">
+      <c r="C22" s="2" t="s">
         <v>43</v>
       </c>
     </row>
     <row r="23" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B23" s="1" t="s">
+      <c r="B23" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="C23" s="1" t="s">
+      <c r="C23" s="2" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="24" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B24" s="1" t="s">
+      <c r="B24" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="C24" s="1" t="s">
+      <c r="C24" s="2" t="s">
         <v>47</v>
       </c>
     </row>
     <row r="25" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B25" s="1" t="s">
+      <c r="B25" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="C25" s="1" t="s">
+      <c r="C25" s="2" t="s">
         <v>49</v>
       </c>
     </row>
     <row r="26" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B26" s="1" t="s">
+      <c r="B26" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="C26" s="1" t="s">
+      <c r="C26" s="2" t="s">
         <v>51</v>
       </c>
     </row>
     <row r="27" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B27" s="1" t="s">
+      <c r="B27" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="C27" s="1" t="s">
+      <c r="C27" s="2" t="s">
         <v>53</v>
       </c>
     </row>
     <row r="28" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B28" s="1" t="s">
+      <c r="B28" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="C28" s="1" t="s">
+      <c r="C28" s="2" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="29" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B29" s="1" t="s">
+      <c r="B29" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="C29" s="1" t="s">
+      <c r="C29" s="2" t="s">
         <v>57</v>
       </c>
     </row>
     <row r="30" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B30" s="1" t="s">
+      <c r="B30" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="C30" s="1" t="s">
+      <c r="C30" s="2" t="s">
         <v>59</v>
       </c>
     </row>
     <row r="31" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B31" s="1" t="s">
+      <c r="B31" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="C31" s="1" t="s">
+      <c r="C31" s="2" t="s">
         <v>61</v>
       </c>
     </row>
     <row r="32" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B32" s="1" t="s">
+      <c r="B32" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="C32" s="1" t="s">
+      <c r="C32" s="2" t="s">
         <v>63</v>
       </c>
     </row>
     <row r="33" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B33" s="1" t="s">
+      <c r="B33" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="C33" s="1" t="s">
+      <c r="C33" s="2" t="s">
         <v>65</v>
       </c>
     </row>
     <row r="34" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B34" s="1" t="s">
+      <c r="B34" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="C34" s="1" t="s">
+      <c r="C34" s="2" t="s">
         <v>67</v>
       </c>
     </row>
     <row r="35" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B35" s="1" t="s">
+      <c r="B35" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="C35" s="1" t="s">
+      <c r="C35" s="2" t="s">
         <v>69</v>
       </c>
     </row>
     <row r="36" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B36" s="1" t="s">
+      <c r="B36" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="C36" s="1" t="s">
+      <c r="C36" s="2" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="37" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B37" s="1" t="s">
+      <c r="B37" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="C37" s="1" t="s">
+      <c r="C37" s="2" t="s">
         <v>73</v>
       </c>
     </row>
     <row r="38" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B38" s="1" t="s">
+      <c r="B38" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="C38" s="1" t="s">
+      <c r="C38" s="2" t="s">
         <v>75</v>
       </c>
     </row>
     <row r="39" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B39" s="1" t="s">
+      <c r="B39" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="C39" s="1" t="s">
+      <c r="C39" s="2" t="s">
         <v>77</v>
       </c>
     </row>
     <row r="40" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B40" s="1" t="s">
+      <c r="B40" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="C40" s="1" t="s">
+      <c r="C40" s="2" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="41" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B41" s="1" t="s">
+      <c r="B41" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="C41" s="1" t="s">
+      <c r="C41" s="2" t="s">
         <v>81</v>
       </c>
     </row>
     <row r="42" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B42" s="1" t="s">
+      <c r="B42" s="2" t="s">
         <v>82</v>
       </c>
-      <c r="C42" s="1" t="s">
+      <c r="C42" s="2" t="s">
         <v>83</v>
       </c>
     </row>
     <row r="43" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B43" s="1" t="s">
+      <c r="B43" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="C43" s="1" t="s">
+      <c r="C43" s="2" t="s">
         <v>85</v>
       </c>
     </row>
     <row r="44" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B44" s="1" t="s">
+      <c r="B44" s="2" t="s">
         <v>86</v>
       </c>
-      <c r="C44" s="1" t="s">
+      <c r="C44" s="2" t="s">
         <v>87</v>
       </c>
     </row>
     <row r="45" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B45" s="1" t="s">
+      <c r="B45" s="2" t="s">
         <v>88</v>
       </c>
-      <c r="C45" s="1" t="s">
+      <c r="C45" s="2" t="s">
         <v>89</v>
       </c>
     </row>
     <row r="46" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B46" s="1" t="s">
+      <c r="B46" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="C46" s="1" t="s">
+      <c r="C46" s="2" t="s">
         <v>91</v>
       </c>
     </row>
     <row r="47" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B47" s="1" t="s">
+      <c r="B47" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="C47" s="1" t="s">
+      <c r="C47" s="2" t="s">
         <v>93</v>
       </c>
     </row>
     <row r="48" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B48" s="1" t="s">
+      <c r="B48" s="2" t="s">
         <v>94</v>
       </c>
-      <c r="C48" s="1" t="s">
+      <c r="C48" s="2" t="s">
         <v>95</v>
       </c>
     </row>
     <row r="49" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B49" s="1" t="s">
+      <c r="B49" s="2" t="s">
         <v>96</v>
       </c>
-      <c r="C49" s="1" t="s">
+      <c r="C49" s="2" t="s">
         <v>97</v>
       </c>
     </row>
     <row r="50" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B50" s="1" t="s">
+      <c r="B50" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="C50" s="1" t="s">
+      <c r="C50" s="2" t="s">
         <v>99</v>
       </c>
     </row>
     <row r="51" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B51" s="1" t="s">
+      <c r="B51" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="C51" s="1" t="s">
+      <c r="C51" s="2" t="s">
         <v>101</v>
       </c>
     </row>
     <row r="52" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B52" s="1" t="s">
+      <c r="B52" s="2" t="s">
         <v>102</v>
       </c>
-      <c r="C52" s="1" t="s">
+      <c r="C52" s="2" t="s">
         <v>103</v>
       </c>
     </row>
     <row r="53" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B53" s="1" t="s">
+      <c r="B53" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="C53" s="1" t="s">
+      <c r="C53" s="2" t="s">
         <v>105</v>
       </c>
     </row>
     <row r="54" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B54" s="1" t="s">
+      <c r="B54" s="2" t="s">
         <v>106</v>
       </c>
-      <c r="C54" s="1" t="s">
+      <c r="C54" s="2" t="s">
         <v>107</v>
       </c>
     </row>
     <row r="55" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B55" s="1" t="s">
+      <c r="B55" s="2" t="s">
         <v>108</v>
       </c>
-      <c r="C55" s="1" t="s">
+      <c r="C55" s="2" t="s">
         <v>109</v>
       </c>
     </row>
     <row r="56" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B56" s="1" t="s">
+      <c r="B56" s="2" t="s">
         <v>110</v>
       </c>
-      <c r="C56" s="1" t="s">
+      <c r="C56" s="2" t="s">
         <v>111</v>
       </c>
     </row>
     <row r="57" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B57" s="1" t="s">
+      <c r="B57" s="2" t="s">
         <v>112</v>
       </c>
-      <c r="C57" s="1" t="s">
+      <c r="C57" s="2" t="s">
         <v>113</v>
       </c>
     </row>
     <row r="58" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B58" s="1" t="s">
+      <c r="B58" s="2" t="s">
         <v>114</v>
       </c>
-      <c r="C58" s="1" t="s">
+      <c r="C58" s="2" t="s">
         <v>115</v>
       </c>
     </row>
     <row r="59" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B59" s="1" t="s">
+      <c r="B59" s="2" t="s">
         <v>116</v>
       </c>
-      <c r="C59" s="1" t="s">
+      <c r="C59" s="2" t="s">
         <v>117</v>
       </c>
     </row>
     <row r="60" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B60" s="1" t="s">
+      <c r="B60" s="2" t="s">
         <v>118</v>
       </c>
-      <c r="C60" s="1" t="s">
+      <c r="C60" s="2" t="s">
         <v>119</v>
       </c>
     </row>
     <row r="61" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B61" s="1" t="s">
+      <c r="B61" s="2" t="s">
         <v>120</v>
       </c>
-      <c r="C61" s="1" t="s">
+      <c r="C61" s="2" t="s">
         <v>121</v>
       </c>
     </row>
     <row r="62" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B62" s="1" t="s">
+      <c r="B62" s="2" t="s">
         <v>122</v>
       </c>
-      <c r="C62" s="1" t="s">
+      <c r="C62" s="2" t="s">
         <v>123</v>
       </c>
     </row>
     <row r="63" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B63" s="1" t="s">
+      <c r="B63" s="2" t="s">
         <v>124</v>
       </c>
-      <c r="C63" s="1" t="s">
+      <c r="C63" s="2" t="s">
         <v>125</v>
       </c>
     </row>
     <row r="64" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B64" s="1" t="s">
+      <c r="B64" s="2" t="s">
         <v>126</v>
       </c>
-      <c r="C64" s="1" t="s">
+      <c r="C64" s="2" t="s">
         <v>127</v>
       </c>
     </row>
     <row r="65" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B65" s="1" t="s">
+      <c r="B65" s="2" t="s">
         <v>128</v>
       </c>
-      <c r="C65" s="1" t="s">
+      <c r="C65" s="2" t="s">
         <v>129</v>
       </c>
     </row>
     <row r="66" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B66" s="1" t="s">
+      <c r="B66" s="2" t="s">
         <v>130</v>
       </c>
-      <c r="C66" s="1" t="s">
+      <c r="C66" s="2" t="s">
         <v>131</v>
       </c>
     </row>
     <row r="67" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B67" s="1" t="s">
+      <c r="B67" s="2" t="s">
         <v>132</v>
       </c>
-      <c r="C67" s="1" t="s">
+      <c r="C67" s="2" t="s">
         <v>133</v>
       </c>
     </row>
     <row r="68" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B68" s="1" t="s">
+      <c r="B68" s="2" t="s">
         <v>134</v>
       </c>
-      <c r="C68" s="1" t="s">
+      <c r="C68" s="2" t="s">
         <v>135</v>
       </c>
     </row>
     <row r="69" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B69" s="1" t="s">
+      <c r="B69" s="2" t="s">
         <v>136</v>
       </c>
-      <c r="C69" s="1" t="s">
+      <c r="C69" s="2" t="s">
         <v>137</v>
       </c>
     </row>
     <row r="70" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B70" s="1" t="s">
+      <c r="B70" s="2" t="s">
         <v>138</v>
       </c>
-      <c r="C70" s="1" t="s">
+      <c r="C70" s="2" t="s">
         <v>139</v>
       </c>
     </row>
     <row r="71" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B71" s="1" t="s">
+      <c r="B71" s="2" t="s">
         <v>140</v>
       </c>
-      <c r="C71" s="1" t="s">
+      <c r="C71" s="2" t="s">
         <v>141</v>
       </c>
     </row>
     <row r="72" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B72" s="1" t="s">
+      <c r="B72" s="2" t="s">
         <v>142</v>
       </c>
-      <c r="C72" s="1" t="s">
+      <c r="C72" s="2" t="s">
         <v>143</v>
       </c>
     </row>
     <row r="73" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B73" s="1" t="s">
+      <c r="B73" s="2" t="s">
         <v>144</v>
       </c>
-      <c r="C73" s="1" t="s">
+      <c r="C73" s="2" t="s">
         <v>145</v>
       </c>
     </row>
     <row r="74" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B74" s="1" t="s">
+      <c r="B74" s="2" t="s">
         <v>146</v>
       </c>
-      <c r="C74" s="1" t="s">
+      <c r="C74" s="2" t="s">
         <v>147</v>
       </c>
     </row>
     <row r="75" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B75" s="1" t="s">
+      <c r="B75" s="2" t="s">
         <v>148</v>
       </c>
-      <c r="C75" s="1" t="s">
+      <c r="C75" s="2" t="s">
         <v>149</v>
       </c>
     </row>
     <row r="76" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B76" s="1" t="s">
+      <c r="B76" s="2" t="s">
         <v>150</v>
       </c>
-      <c r="C76" s="1" t="s">
+      <c r="C76" s="2" t="s">
         <v>151</v>
       </c>
     </row>
     <row r="77" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B77" s="1" t="s">
+      <c r="B77" s="2" t="s">
         <v>152</v>
       </c>
-      <c r="C77" s="1" t="s">
+      <c r="C77" s="2" t="s">
         <v>153</v>
       </c>
     </row>
     <row r="78" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B78" s="1" t="s">
+      <c r="B78" s="2" t="s">
         <v>154</v>
       </c>
-      <c r="C78" s="1" t="s">
+      <c r="C78" s="2" t="s">
         <v>155</v>
       </c>
     </row>
     <row r="79" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B79" s="1" t="s">
+      <c r="B79" s="2" t="s">
         <v>156</v>
       </c>
-      <c r="C79" s="1" t="s">
+      <c r="C79" s="2" t="s">
         <v>157</v>
       </c>
     </row>
     <row r="80" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B80" s="1" t="s">
+      <c r="B80" s="2" t="s">
         <v>158</v>
       </c>
-      <c r="C80" s="1" t="s">
+      <c r="C80" s="2" t="s">
         <v>159</v>
       </c>
     </row>
     <row r="81" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B81" s="1" t="s">
+      <c r="B81" s="2" t="s">
         <v>160</v>
       </c>
-      <c r="C81" s="1" t="s">
+      <c r="C81" s="2" t="s">
         <v>161</v>
       </c>
     </row>
     <row r="82" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B82" s="1" t="s">
+      <c r="B82" s="2" t="s">
         <v>162</v>
       </c>
-      <c r="C82" s="1" t="s">
+      <c r="C82" s="2" t="s">
         <v>163</v>
       </c>
     </row>
     <row r="83" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B83" s="1" t="s">
+      <c r="B83" s="2" t="s">
         <v>164</v>
       </c>
-      <c r="C83" s="1" t="s">
+      <c r="C83" s="2" t="s">
         <v>165</v>
       </c>
     </row>
     <row r="84" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B84" s="1" t="s">
+      <c r="B84" s="2" t="s">
         <v>166</v>
       </c>
-      <c r="C84" s="1" t="s">
+      <c r="C84" s="2" t="s">
         <v>167</v>
       </c>
     </row>
     <row r="85" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B85" s="1" t="s">
+      <c r="B85" s="2" t="s">
         <v>168</v>
       </c>
-      <c r="C85" s="1" t="s">
+      <c r="C85" s="2" t="s">
         <v>169</v>
       </c>
     </row>
     <row r="86" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B86" s="1" t="s">
+      <c r="B86" s="2" t="s">
         <v>170</v>
       </c>
-      <c r="C86" s="1" t="s">
+      <c r="C86" s="2" t="s">
         <v>171</v>
       </c>
     </row>
     <row r="87" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B87" s="1" t="s">
+      <c r="B87" s="2" t="s">
         <v>172</v>
       </c>
-      <c r="C87" s="1" t="s">
+      <c r="C87" s="2" t="s">
         <v>173</v>
       </c>
     </row>
     <row r="88" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B88" s="1" t="s">
+      <c r="B88" s="2" t="s">
         <v>174</v>
       </c>
-      <c r="C88" s="1" t="s">
+      <c r="C88" s="2" t="s">
         <v>175</v>
       </c>
     </row>
     <row r="89" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B89" s="1" t="s">
+      <c r="B89" s="2" t="s">
         <v>176</v>
       </c>
-      <c r="C89" s="1" t="s">
+      <c r="C89" s="2" t="s">
         <v>177</v>
       </c>
     </row>
     <row r="90" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B90" s="1" t="s">
+      <c r="B90" s="2" t="s">
         <v>178</v>
       </c>
-      <c r="C90" s="1" t="s">
+      <c r="C90" s="2" t="s">
         <v>179</v>
       </c>
     </row>
     <row r="91" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B91" s="1" t="s">
+      <c r="B91" s="2" t="s">
         <v>180</v>
       </c>
-      <c r="C91" s="1" t="s">
+      <c r="C91" s="2" t="s">
         <v>181</v>
       </c>
     </row>
     <row r="92" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B92" s="1" t="s">
+      <c r="B92" s="2" t="s">
         <v>182</v>
       </c>
-      <c r="C92" s="1" t="s">
+      <c r="C92" s="2" t="s">
         <v>183</v>
       </c>
     </row>
     <row r="93" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B93" s="1" t="s">
+      <c r="B93" s="2" t="s">
         <v>184</v>
       </c>
-      <c r="C93" s="1" t="s">
+      <c r="C93" s="2" t="s">
         <v>185</v>
       </c>
     </row>
     <row r="94" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B94" s="1" t="s">
+      <c r="B94" s="2" t="s">
         <v>186</v>
       </c>
-      <c r="C94" s="1" t="s">
+      <c r="C94" s="2" t="s">
         <v>187</v>
       </c>
     </row>
     <row r="95" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B95" s="1" t="s">
+      <c r="B95" s="2" t="s">
         <v>188</v>
       </c>
-      <c r="C95" s="1" t="s">
+      <c r="C95" s="2" t="s">
         <v>189</v>
       </c>
     </row>
     <row r="96" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B96" s="1" t="s">
+      <c r="B96" s="2" t="s">
         <v>190</v>
       </c>
-      <c r="C96" s="1" t="s">
+      <c r="C96" s="2" t="s">
         <v>191</v>
       </c>
     </row>
     <row r="97" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B97" s="1" t="s">
+      <c r="B97" s="2" t="s">
         <v>192</v>
       </c>
-      <c r="C97" s="1" t="s">
+      <c r="C97" s="2" t="s">
         <v>193</v>
       </c>
     </row>
     <row r="98" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B98" s="1" t="s">
+      <c r="B98" s="2" t="s">
         <v>194</v>
       </c>
-      <c r="C98" s="1" t="s">
+      <c r="C98" s="2" t="s">
         <v>195</v>
       </c>
     </row>
     <row r="99" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B99" s="1" t="s">
+      <c r="B99" s="2" t="s">
         <v>196</v>
       </c>
-      <c r="C99" s="1" t="s">
+      <c r="C99" s="2" t="s">
         <v>197</v>
       </c>
     </row>
     <row r="100" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B100" s="1" t="s">
+      <c r="B100" s="2" t="s">
         <v>198</v>
       </c>
-      <c r="C100" s="1" t="s">
+      <c r="C100" s="2" t="s">
         <v>199</v>
       </c>
     </row>
     <row r="101" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B101" s="1" t="s">
+      <c r="B101" s="2" t="s">
         <v>200</v>
       </c>
-      <c r="C101" s="1" t="s">
+      <c r="C101" s="2" t="s">
         <v>201</v>
       </c>
     </row>
     <row r="102" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B102" s="1" t="s">
+      <c r="B102" s="2" t="s">
         <v>202</v>
       </c>
-      <c r="C102" s="1" t="s">
+      <c r="C102" s="2" t="s">
         <v>203</v>
       </c>
     </row>
     <row r="103" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B103" s="1" t="s">
+      <c r="B103" s="2" t="s">
         <v>204</v>
       </c>
-      <c r="C103" s="1" t="s">
+      <c r="C103" s="2" t="s">
         <v>205</v>
       </c>
     </row>
     <row r="104" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B104" s="1" t="s">
+      <c r="B104" s="2" t="s">
         <v>206</v>
       </c>
-      <c r="C104" s="1" t="s">
+      <c r="C104" s="2" t="s">
         <v>207</v>
       </c>
     </row>
     <row r="105" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B105" s="1" t="s">
+      <c r="B105" s="2" t="s">
         <v>208</v>
       </c>
-      <c r="C105" s="1" t="s">
+      <c r="C105" s="2" t="s">
         <v>209</v>
       </c>
     </row>
     <row r="106" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B106" s="1" t="s">
+      <c r="B106" s="2" t="s">
         <v>210</v>
       </c>
-      <c r="C106" s="1" t="s">
+      <c r="C106" s="2" t="s">
         <v>211</v>
       </c>
     </row>
     <row r="107" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B107" s="1" t="s">
+      <c r="B107" s="2" t="s">
         <v>212</v>
       </c>
-      <c r="C107" s="1" t="s">
+      <c r="C107" s="2" t="s">
         <v>213</v>
       </c>
     </row>
     <row r="108" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B108" s="1" t="s">
+      <c r="B108" s="2" t="s">
         <v>214</v>
       </c>
-      <c r="C108" s="1" t="s">
+      <c r="C108" s="2" t="s">
         <v>215</v>
       </c>
     </row>
     <row r="109" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B109" s="1" t="s">
+      <c r="B109" s="2" t="s">
         <v>216</v>
       </c>
-      <c r="C109" s="1" t="s">
+      <c r="C109" s="2" t="s">
         <v>217</v>
       </c>
     </row>
     <row r="110" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B110" s="1" t="s">
+      <c r="B110" s="2" t="s">
         <v>218</v>
       </c>
-      <c r="C110" s="1" t="s">
+      <c r="C110" s="2" t="s">
         <v>219</v>
       </c>
     </row>
     <row r="111" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B111" s="1" t="s">
+      <c r="B111" s="2" t="s">
         <v>220</v>
       </c>
-      <c r="C111" s="1" t="s">
+      <c r="C111" s="2" t="s">
         <v>221</v>
       </c>
     </row>
     <row r="112" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B112" s="1" t="s">
+      <c r="B112" s="2" t="s">
         <v>222</v>
       </c>
-      <c r="C112" s="1" t="s">
+      <c r="C112" s="2" t="s">
         <v>223</v>
       </c>
     </row>
     <row r="113" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B113" s="1" t="s">
+      <c r="B113" s="2" t="s">
         <v>224</v>
       </c>
-      <c r="C113" s="1" t="s">
+      <c r="C113" s="2" t="s">
         <v>225</v>
       </c>
     </row>
     <row r="114" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B114" s="1" t="s">
+      <c r="B114" s="2" t="s">
         <v>226</v>
       </c>
-      <c r="C114" s="1" t="s">
+      <c r="C114" s="2" t="s">
         <v>227</v>
       </c>
     </row>
     <row r="115" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B115" s="1" t="s">
+      <c r="B115" s="2" t="s">
         <v>228</v>
       </c>
-      <c r="C115" s="1" t="s">
+      <c r="C115" s="2" t="s">
         <v>229</v>
       </c>
     </row>
     <row r="116" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B116" s="1" t="s">
+      <c r="B116" s="2" t="s">
         <v>230</v>
       </c>
-      <c r="C116" s="1" t="s">
+      <c r="C116" s="2" t="s">
         <v>231</v>
       </c>
     </row>
     <row r="117" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B117" s="1" t="s">
+      <c r="B117" s="2" t="s">
         <v>232</v>
       </c>
-      <c r="C117" s="1" t="s">
+      <c r="C117" s="2" t="s">
         <v>233</v>
       </c>
     </row>
     <row r="118" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B118" s="1" t="s">
+      <c r="B118" s="2" t="s">
         <v>234</v>
       </c>
-      <c r="C118" s="1" t="s">
+      <c r="C118" s="2" t="s">
         <v>235</v>
       </c>
     </row>
     <row r="119" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B119" s="1" t="s">
+      <c r="B119" s="2" t="s">
         <v>236</v>
       </c>
-      <c r="C119" s="1" t="s">
+      <c r="C119" s="2" t="s">
         <v>237</v>
       </c>
     </row>
     <row r="120" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B120" s="1" t="s">
+      <c r="B120" s="2" t="s">
         <v>238</v>
       </c>
-      <c r="C120" s="1" t="s">
+      <c r="C120" s="2" t="s">
         <v>239</v>
       </c>
     </row>
     <row r="121" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B121" s="1" t="s">
+      <c r="B121" s="2" t="s">
         <v>240</v>
       </c>
-      <c r="C121" s="1" t="s">
+      <c r="C121" s="2" t="s">
         <v>241</v>
       </c>
     </row>
     <row r="122" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B122" s="1" t="s">
+      <c r="B122" s="2" t="s">
         <v>242</v>
       </c>
-      <c r="C122" s="1" t="s">
+      <c r="C122" s="2" t="s">
         <v>243</v>
       </c>
     </row>
     <row r="123" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B123" s="1" t="s">
+      <c r="B123" s="2" t="s">
         <v>244</v>
       </c>
-      <c r="C123" s="1" t="s">
+      <c r="C123" s="2" t="s">
         <v>245</v>
       </c>
     </row>
     <row r="124" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B124" s="1" t="s">
+      <c r="B124" s="2" t="s">
         <v>246</v>
       </c>
-      <c r="C124" s="1" t="s">
+      <c r="C124" s="2" t="s">
         <v>247</v>
       </c>
     </row>
     <row r="125" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B125" s="1" t="s">
+      <c r="B125" s="2" t="s">
         <v>248</v>
       </c>
-      <c r="C125" s="1" t="s">
+      <c r="C125" s="2" t="s">
         <v>249</v>
       </c>
     </row>
     <row r="126" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B126" s="1" t="s">
+      <c r="B126" s="2" t="s">
         <v>250</v>
       </c>
-      <c r="C126" s="1" t="s">
+      <c r="C126" s="2" t="s">
         <v>251</v>
       </c>
     </row>
     <row r="127" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B127" s="1" t="s">
+      <c r="B127" s="2" t="s">
         <v>252</v>
       </c>
-      <c r="C127" s="1" t="s">
+      <c r="C127" s="2" t="s">
         <v>253</v>
       </c>
     </row>
     <row r="128" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B128" s="1" t="s">
+      <c r="B128" s="2" t="s">
         <v>254</v>
       </c>
-      <c r="C128" s="1" t="s">
+      <c r="C128" s="2" t="s">
         <v>255</v>
       </c>
     </row>
     <row r="129" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B129" s="1" t="s">
+      <c r="B129" s="2" t="s">
         <v>256</v>
       </c>
-      <c r="C129" s="1" t="s">
+      <c r="C129" s="2" t="s">
         <v>257</v>
       </c>
     </row>
     <row r="130" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B130" s="1" t="s">
+      <c r="B130" s="2" t="s">
         <v>258</v>
       </c>
-      <c r="C130" s="1" t="s">
+      <c r="C130" s="2" t="s">
         <v>259</v>
       </c>
     </row>
     <row r="131" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B131" s="1" t="s">
+      <c r="B131" s="2" t="s">
         <v>260</v>
       </c>
-      <c r="C131" s="1" t="s">
+      <c r="C131" s="2" t="s">
         <v>261</v>
       </c>
     </row>
     <row r="132" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B132" s="1" t="s">
+      <c r="B132" s="2" t="s">
         <v>262</v>
       </c>
-      <c r="C132" s="1" t="s">
+      <c r="C132" s="2" t="s">
         <v>263</v>
       </c>
     </row>
     <row r="133" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B133" s="1" t="s">
+      <c r="B133" s="2" t="s">
         <v>264</v>
       </c>
-      <c r="C133" s="1" t="s">
+      <c r="C133" s="2" t="s">
         <v>265</v>
       </c>
     </row>
     <row r="134" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B134" s="1" t="s">
+      <c r="B134" s="2" t="s">
         <v>266</v>
       </c>
-      <c r="C134" s="1" t="s">
+      <c r="C134" s="2" t="s">
         <v>267</v>
       </c>
     </row>
     <row r="135" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B135" s="1" t="s">
+      <c r="B135" s="2" t="s">
         <v>268</v>
       </c>
-      <c r="C135" s="1" t="s">
+      <c r="C135" s="2" t="s">
         <v>269</v>
       </c>
     </row>
     <row r="136" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B136" s="1" t="s">
+      <c r="B136" s="2" t="s">
         <v>270</v>
       </c>
-      <c r="C136" s="1" t="s">
+      <c r="C136" s="2" t="s">
         <v>271</v>
       </c>
     </row>
     <row r="137" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B137" s="1" t="s">
+      <c r="B137" s="2" t="s">
         <v>272</v>
       </c>
-      <c r="C137" s="1" t="s">
+      <c r="C137" s="2" t="s">
         <v>273</v>
       </c>
     </row>
     <row r="138" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B138" s="1" t="s">
+      <c r="B138" s="2" t="s">
         <v>274</v>
       </c>
-      <c r="C138" s="1" t="s">
+      <c r="C138" s="2" t="s">
         <v>275</v>
       </c>
     </row>
     <row r="139" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B139" s="1" t="s">
+      <c r="B139" s="2" t="s">
         <v>276</v>
       </c>
-      <c r="C139" s="1" t="s">
+      <c r="C139" s="2" t="s">
         <v>277</v>
       </c>
     </row>
     <row r="140" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B140" s="1" t="s">
+      <c r="B140" s="2" t="s">
         <v>278</v>
       </c>
-      <c r="C140" s="1" t="s">
+      <c r="C140" s="2" t="s">
         <v>279</v>
       </c>
     </row>
     <row r="141" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B141" s="1" t="s">
+      <c r="B141" s="2" t="s">
         <v>280</v>
       </c>
-      <c r="C141" s="1" t="s">
+      <c r="C141" s="2" t="s">
         <v>281</v>
       </c>
     </row>
     <row r="142" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B142" s="1" t="s">
+      <c r="B142" s="2" t="s">
         <v>282</v>
       </c>
-      <c r="C142" s="1" t="s">
+      <c r="C142" s="2" t="s">
         <v>283</v>
       </c>
     </row>
     <row r="143" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B143" s="1" t="s">
+      <c r="B143" s="2" t="s">
         <v>284</v>
       </c>
-      <c r="C143" s="1" t="s">
+      <c r="C143" s="2" t="s">
         <v>285</v>
       </c>
     </row>
     <row r="144" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B144" s="1" t="s">
+      <c r="B144" s="2" t="s">
         <v>286</v>
       </c>
-      <c r="C144" s="1" t="s">
+      <c r="C144" s="2" t="s">
         <v>287</v>
       </c>
     </row>
     <row r="145" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B145" s="1" t="s">
+      <c r="B145" s="2" t="s">
         <v>288</v>
       </c>
-      <c r="C145" s="1" t="s">
+      <c r="C145" s="2" t="s">
         <v>289</v>
       </c>
     </row>
     <row r="146" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B146" s="1" t="s">
+      <c r="B146" s="2" t="s">
         <v>290</v>
       </c>
-      <c r="C146" s="1" t="s">
+      <c r="C146" s="2" t="s">
         <v>291</v>
       </c>
     </row>
     <row r="147" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B147" s="1" t="s">
+      <c r="B147" s="2" t="s">
         <v>292</v>
       </c>
-      <c r="C147" s="1" t="s">
+      <c r="C147" s="2" t="s">
         <v>293</v>
       </c>
     </row>
     <row r="148" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B148" s="1" t="s">
+      <c r="B148" s="2" t="s">
         <v>294</v>
       </c>
-      <c r="C148" s="1" t="s">
+      <c r="C148" s="2" t="s">
         <v>295</v>
       </c>
     </row>
     <row r="149" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B149" s="1" t="s">
+      <c r="B149" s="2" t="s">
         <v>296</v>
       </c>
-      <c r="C149" s="1" t="s">
+      <c r="C149" s="2" t="s">
         <v>297</v>
       </c>
     </row>
     <row r="150" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B150" s="1" t="s">
+      <c r="B150" s="2" t="s">
         <v>298</v>
       </c>
-      <c r="C150" s="1" t="s">
+      <c r="C150" s="2" t="s">
         <v>299</v>
       </c>
     </row>
     <row r="151" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B151" s="1" t="s">
+      <c r="B151" s="2" t="s">
         <v>300</v>
       </c>
-      <c r="C151" s="1" t="s">
+      <c r="C151" s="2" t="s">
         <v>301</v>
       </c>
     </row>
     <row r="152" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B152" s="1" t="s">
+      <c r="B152" s="2" t="s">
         <v>302</v>
       </c>
-      <c r="C152" s="1" t="s">
+      <c r="C152" s="2" t="s">
         <v>303</v>
       </c>
     </row>
     <row r="153" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B153" s="1" t="s">
+      <c r="B153" s="2" t="s">
         <v>304</v>
       </c>
-      <c r="C153" s="1" t="s">
+      <c r="C153" s="2" t="s">
         <v>305</v>
       </c>
     </row>
     <row r="154" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B154" s="1" t="s">
+      <c r="B154" s="2" t="s">
         <v>306</v>
       </c>
-      <c r="C154" s="1" t="s">
+      <c r="C154" s="2" t="s">
         <v>307</v>
       </c>
     </row>
     <row r="155" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B155" s="1" t="s">
+      <c r="B155" s="2" t="s">
         <v>308</v>
       </c>
-      <c r="C155" s="1" t="s">
+      <c r="C155" s="2" t="s">
         <v>309</v>
       </c>
     </row>
     <row r="156" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B156" s="1" t="s">
+      <c r="B156" s="2" t="s">
         <v>310</v>
       </c>
-      <c r="C156" s="1" t="s">
+      <c r="C156" s="2" t="s">
         <v>311</v>
       </c>
     </row>
     <row r="157" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B157" s="1" t="s">
+      <c r="B157" s="2" t="s">
         <v>312</v>
       </c>
-      <c r="C157" s="1" t="s">
+      <c r="C157" s="2" t="s">
         <v>313</v>
       </c>
     </row>
     <row r="158" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B158" s="1" t="s">
+      <c r="B158" s="2" t="s">
         <v>314</v>
       </c>
-      <c r="C158" s="1" t="s">
+      <c r="C158" s="2" t="s">
         <v>315</v>
       </c>
     </row>
     <row r="159" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B159" s="1" t="s">
+      <c r="B159" s="2" t="s">
         <v>316</v>
       </c>
-      <c r="C159" s="1" t="s">
+      <c r="C159" s="2" t="s">
         <v>317</v>
       </c>
     </row>
     <row r="160" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B160" s="1" t="s">
+      <c r="B160" s="2" t="s">
         <v>318</v>
       </c>
-      <c r="C160" s="1" t="s">
+      <c r="C160" s="2" t="s">
         <v>319</v>
       </c>
     </row>
     <row r="161" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B161" s="1" t="s">
+      <c r="B161" s="2" t="s">
         <v>320</v>
       </c>
-      <c r="C161" s="1" t="s">
+      <c r="C161" s="2" t="s">
         <v>321</v>
       </c>
     </row>
     <row r="162" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B162" s="1" t="s">
+      <c r="B162" s="2" t="s">
         <v>322</v>
       </c>
-      <c r="C162" s="1" t="s">
+      <c r="C162" s="2" t="s">
         <v>323</v>
       </c>
     </row>
     <row r="163" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B163" s="1" t="s">
+      <c r="B163" s="2" t="s">
         <v>324</v>
       </c>
-      <c r="C163" s="1" t="s">
+      <c r="C163" s="2" t="s">
         <v>325</v>
       </c>
     </row>
     <row r="164" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B164" s="1" t="s">
+      <c r="B164" s="2" t="s">
         <v>326</v>
       </c>
-      <c r="C164" s="1" t="s">
+      <c r="C164" s="2" t="s">
         <v>327</v>
       </c>
     </row>
     <row r="165" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B165" s="1" t="s">
+      <c r="B165" s="2" t="s">
         <v>328</v>
       </c>
-      <c r="C165" s="1" t="s">
+      <c r="C165" s="2" t="s">
         <v>329</v>
       </c>
     </row>
     <row r="166" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B166" s="1" t="s">
+      <c r="B166" s="2" t="s">
         <v>330</v>
       </c>
-      <c r="C166" s="1" t="s">
+      <c r="C166" s="2" t="s">
         <v>331</v>
       </c>
     </row>
     <row r="167" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B167" s="1" t="s">
+      <c r="B167" s="2" t="s">
         <v>332</v>
       </c>
-      <c r="C167" s="1" t="s">
+      <c r="C167" s="2" t="s">
         <v>333</v>
       </c>
     </row>
     <row r="168" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B168" s="1" t="s">
+      <c r="B168" s="2" t="s">
         <v>334</v>
       </c>
-      <c r="C168" s="1" t="s">
+      <c r="C168" s="2" t="s">
         <v>335</v>
       </c>
     </row>
     <row r="169" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B169" s="1" t="s">
+      <c r="B169" s="2" t="s">
         <v>336</v>
       </c>
-      <c r="C169" s="1" t="s">
+      <c r="C169" s="2" t="s">
         <v>337</v>
       </c>
     </row>
@@ -7431,547 +7564,547 @@
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="3" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="2" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="2" t="s">
-        <v>876</v>
+      <c r="C2" s="3" t="s">
+        <v>879</v>
       </c>
     </row>
     <row r="3" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B3" s="2" t="s">
+      <c r="B3" s="3" t="s">
         <v>435</v>
       </c>
-      <c r="C3" s="2" t="s">
-        <v>877</v>
+      <c r="C3" s="3" t="s">
+        <v>880</v>
       </c>
     </row>
     <row r="4" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B4" s="2" t="s">
+      <c r="B4" s="3" t="s">
         <v>437</v>
       </c>
-      <c r="C4" s="2" t="s">
-        <v>878</v>
+      <c r="C4" s="3" t="s">
+        <v>881</v>
       </c>
     </row>
     <row r="5" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B5" s="2" t="s">
+      <c r="B5" s="3" t="s">
         <v>439</v>
       </c>
-      <c r="C5" s="2" t="s">
-        <v>879</v>
+      <c r="C5" s="3" t="s">
+        <v>882</v>
       </c>
     </row>
     <row r="6" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B6" s="2" t="s">
+      <c r="B6" s="3" t="s">
         <v>441</v>
       </c>
-      <c r="C6" s="2" t="s">
-        <v>880</v>
+      <c r="C6" s="3" t="s">
+        <v>883</v>
       </c>
     </row>
     <row r="7" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B7" s="2" t="s">
+      <c r="B7" s="3" t="s">
         <v>443</v>
       </c>
-      <c r="C7" s="2" t="s">
-        <v>878</v>
+      <c r="C7" s="3" t="s">
+        <v>881</v>
       </c>
     </row>
     <row r="8" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B8" s="2" t="s">
+      <c r="B8" s="3" t="s">
         <v>445</v>
       </c>
-      <c r="C8" s="2" t="s">
-        <v>881</v>
+      <c r="C8" s="3" t="s">
+        <v>884</v>
       </c>
     </row>
     <row r="9" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B9" s="2" t="s">
+      <c r="B9" s="3" t="s">
         <v>447</v>
       </c>
-      <c r="C9" s="2" t="s">
-        <v>882</v>
+      <c r="C9" s="3" t="s">
+        <v>885</v>
       </c>
     </row>
     <row r="10" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B10" s="2" t="s">
+      <c r="B10" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="C10" s="2" t="s">
-        <v>883</v>
+      <c r="C10" s="3" t="s">
+        <v>886</v>
       </c>
     </row>
     <row r="11" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B11" s="2" t="s">
+      <c r="B11" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="C11" s="2" t="s">
-        <v>884</v>
+      <c r="C11" s="3" t="s">
+        <v>887</v>
       </c>
     </row>
     <row r="12" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B12" s="2" t="s">
+      <c r="B12" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="C12" s="2" t="s">
-        <v>885</v>
+      <c r="C12" s="3" t="s">
+        <v>888</v>
       </c>
     </row>
     <row r="13" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B13" s="2" t="s">
+      <c r="B13" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="C13" s="2" t="s">
-        <v>886</v>
+      <c r="C13" s="3" t="s">
+        <v>889</v>
       </c>
     </row>
     <row r="14" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B14" s="2" t="s">
+      <c r="B14" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="C14" s="2" t="s">
-        <v>887</v>
+      <c r="C14" s="3" t="s">
+        <v>890</v>
       </c>
     </row>
     <row r="15" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B15" s="2" t="s">
+      <c r="B15" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="C15" s="2" t="s">
-        <v>888</v>
+      <c r="C15" s="3" t="s">
+        <v>891</v>
       </c>
     </row>
     <row r="16" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B16" s="2" t="s">
+      <c r="B16" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="C16" s="2" t="s">
-        <v>889</v>
+      <c r="C16" s="3" t="s">
+        <v>892</v>
       </c>
     </row>
     <row r="17" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B17" s="2" t="s">
+      <c r="B17" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="C17" s="2" t="s">
-        <v>890</v>
+      <c r="C17" s="3" t="s">
+        <v>893</v>
       </c>
     </row>
     <row r="18" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B18" s="2" t="s">
-        <v>891</v>
-      </c>
-      <c r="C18" s="2" t="s">
-        <v>892</v>
+      <c r="B18" s="3" t="s">
+        <v>894</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>895</v>
       </c>
     </row>
     <row r="19" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B19" s="2" t="s">
+      <c r="B19" s="3" t="s">
         <v>82</v>
       </c>
-      <c r="C19" s="2" t="s">
-        <v>893</v>
+      <c r="C19" s="3" t="s">
+        <v>896</v>
       </c>
     </row>
     <row r="20" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B20" s="2" t="s">
+      <c r="B20" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="C20" s="2" t="s">
-        <v>894</v>
+      <c r="C20" s="3" t="s">
+        <v>897</v>
       </c>
     </row>
     <row r="21" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B21" s="2" t="s">
+      <c r="B21" s="3" t="s">
         <v>86</v>
       </c>
-      <c r="C21" s="2" t="s">
-        <v>894</v>
+      <c r="C21" s="3" t="s">
+        <v>897</v>
       </c>
     </row>
     <row r="22" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B22" s="2" t="s">
+      <c r="B22" s="3" t="s">
         <v>88</v>
       </c>
-      <c r="C22" s="2" t="s">
-        <v>894</v>
+      <c r="C22" s="3" t="s">
+        <v>897</v>
       </c>
     </row>
     <row r="23" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B23" s="2" t="s">
+      <c r="B23" s="3" t="s">
         <v>90</v>
       </c>
-      <c r="C23" s="2" t="s">
-        <v>894</v>
+      <c r="C23" s="3" t="s">
+        <v>897</v>
       </c>
     </row>
     <row r="24" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B24" s="2" t="s">
+      <c r="B24" s="3" t="s">
         <v>92</v>
       </c>
-      <c r="C24" s="2" t="s">
-        <v>894</v>
+      <c r="C24" s="3" t="s">
+        <v>897</v>
       </c>
     </row>
     <row r="25" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B25" s="2" t="s">
+      <c r="B25" s="3" t="s">
         <v>94</v>
       </c>
-      <c r="C25" s="2" t="s">
-        <v>895</v>
+      <c r="C25" s="3" t="s">
+        <v>898</v>
       </c>
     </row>
     <row r="26" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B26" s="2" t="s">
+      <c r="B26" s="3" t="s">
         <v>96</v>
       </c>
-      <c r="C26" s="2" t="s">
-        <v>896</v>
+      <c r="C26" s="3" t="s">
+        <v>899</v>
       </c>
     </row>
     <row r="27" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B27" s="2" t="s">
-        <v>897</v>
-      </c>
-      <c r="C27" s="2" t="s">
-        <v>898</v>
+      <c r="B27" s="3" t="s">
+        <v>900</v>
+      </c>
+      <c r="C27" s="3" t="s">
+        <v>901</v>
       </c>
     </row>
     <row r="28" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B28" s="2" t="s">
+      <c r="B28" s="3" t="s">
         <v>100</v>
       </c>
-      <c r="C28" s="2" t="s">
-        <v>899</v>
+      <c r="C28" s="3" t="s">
+        <v>902</v>
       </c>
     </row>
     <row r="29" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B29" s="2" t="s">
+      <c r="B29" s="3" t="s">
         <v>102</v>
       </c>
-      <c r="C29" s="2" t="s">
-        <v>900</v>
+      <c r="C29" s="3" t="s">
+        <v>903</v>
       </c>
     </row>
     <row r="30" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B30" s="2" t="s">
+      <c r="B30" s="3" t="s">
         <v>104</v>
       </c>
-      <c r="C30" s="2" t="s">
-        <v>901</v>
+      <c r="C30" s="3" t="s">
+        <v>904</v>
       </c>
     </row>
     <row r="31" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B31" s="2" t="s">
+      <c r="B31" s="3" t="s">
         <v>116</v>
       </c>
-      <c r="C31" s="2" t="s">
-        <v>902</v>
+      <c r="C31" s="3" t="s">
+        <v>905</v>
       </c>
     </row>
     <row r="32" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B32" s="2" t="s">
+      <c r="B32" s="3" t="s">
         <v>152</v>
       </c>
-      <c r="C32" s="2" t="s">
-        <v>903</v>
+      <c r="C32" s="3" t="s">
+        <v>906</v>
       </c>
     </row>
     <row r="33" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B33" s="2" t="s">
+      <c r="B33" s="3" t="s">
         <v>134</v>
       </c>
-      <c r="C33" s="2" t="s">
-        <v>904</v>
+      <c r="C33" s="3" t="s">
+        <v>907</v>
       </c>
     </row>
     <row r="34" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B34" s="2" t="s">
+      <c r="B34" s="3" t="s">
+        <v>908</v>
+      </c>
+      <c r="C34" s="3" t="s">
+        <v>909</v>
+      </c>
+    </row>
+    <row r="35" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B35" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="C35" s="3" t="s">
+        <v>910</v>
+      </c>
+    </row>
+    <row r="36" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B36" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="C36" s="3" t="s">
+        <v>911</v>
+      </c>
+    </row>
+    <row r="37" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B37" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="C37" s="3" t="s">
+        <v>912</v>
+      </c>
+    </row>
+    <row r="38" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B38" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="C38" s="3" t="s">
+        <v>913</v>
+      </c>
+    </row>
+    <row r="39" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B39" s="3" t="s">
+        <v>343</v>
+      </c>
+      <c r="C39" s="3" t="s">
+        <v>914</v>
+      </c>
+    </row>
+    <row r="40" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B40" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="C40" s="3" t="s">
+        <v>915</v>
+      </c>
+    </row>
+    <row r="41" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B41" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="C41" s="3" t="s">
+        <v>916</v>
+      </c>
+    </row>
+    <row r="42" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B42" s="3" t="s">
+        <v>148</v>
+      </c>
+      <c r="C42" s="3" t="s">
+        <v>917</v>
+      </c>
+    </row>
+    <row r="43" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B43" s="3" t="s">
+        <v>150</v>
+      </c>
+      <c r="C43" s="3" t="s">
+        <v>918</v>
+      </c>
+    </row>
+    <row r="44" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B44" s="3" t="s">
+        <v>174</v>
+      </c>
+      <c r="C44" s="3" t="s">
+        <v>919</v>
+      </c>
+    </row>
+    <row r="45" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B45" s="3" t="s">
+        <v>154</v>
+      </c>
+      <c r="C45" s="3" t="s">
+        <v>920</v>
+      </c>
+    </row>
+    <row r="46" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B46" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="C46" s="3" t="s">
+        <v>921</v>
+      </c>
+    </row>
+    <row r="47" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B47" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="C47" s="3" t="s">
+        <v>922</v>
+      </c>
+    </row>
+    <row r="48" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B48" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="C48" s="3" t="s">
+        <v>923</v>
+      </c>
+    </row>
+    <row r="49" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B49" s="3" t="s">
+        <v>162</v>
+      </c>
+      <c r="C49" s="3" t="s">
+        <v>924</v>
+      </c>
+    </row>
+    <row r="50" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B50" s="3" t="s">
+        <v>164</v>
+      </c>
+      <c r="C50" s="3" t="s">
+        <v>925</v>
+      </c>
+    </row>
+    <row r="51" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B51" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="C51" s="3" t="s">
+        <v>926</v>
+      </c>
+    </row>
+    <row r="52" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B52" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="C52" s="3" t="s">
+        <v>927</v>
+      </c>
+    </row>
+    <row r="53" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B53" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="C53" s="3" t="s">
+        <v>928</v>
+      </c>
+    </row>
+    <row r="54" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B54" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="C54" s="3" t="s">
         <v>905</v>
       </c>
-      <c r="C34" s="2" t="s">
-        <v>906</v>
-      </c>
-    </row>
-    <row r="35" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B35" s="2" t="s">
-        <v>136</v>
-      </c>
-      <c r="C35" s="2" t="s">
-        <v>907</v>
-      </c>
-    </row>
-    <row r="36" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B36" s="2" t="s">
-        <v>138</v>
-      </c>
-      <c r="C36" s="2" t="s">
-        <v>908</v>
-      </c>
-    </row>
-    <row r="37" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B37" s="2" t="s">
-        <v>140</v>
-      </c>
-      <c r="C37" s="2" t="s">
-        <v>909</v>
-      </c>
-    </row>
-    <row r="38" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B38" s="2" t="s">
-        <v>142</v>
-      </c>
-      <c r="C38" s="2" t="s">
-        <v>910</v>
-      </c>
-    </row>
-    <row r="39" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B39" s="2" t="s">
-        <v>343</v>
-      </c>
-      <c r="C39" s="2" t="s">
-        <v>911</v>
-      </c>
-    </row>
-    <row r="40" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B40" s="2" t="s">
-        <v>144</v>
-      </c>
-      <c r="C40" s="2" t="s">
-        <v>912</v>
-      </c>
-    </row>
-    <row r="41" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B41" s="2" t="s">
-        <v>146</v>
-      </c>
-      <c r="C41" s="2" t="s">
-        <v>913</v>
-      </c>
-    </row>
-    <row r="42" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B42" s="2" t="s">
-        <v>148</v>
-      </c>
-      <c r="C42" s="2" t="s">
-        <v>914</v>
-      </c>
-    </row>
-    <row r="43" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B43" s="2" t="s">
-        <v>150</v>
-      </c>
-      <c r="C43" s="2" t="s">
-        <v>915</v>
-      </c>
-    </row>
-    <row r="44" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B44" s="2" t="s">
-        <v>174</v>
-      </c>
-      <c r="C44" s="2" t="s">
-        <v>916</v>
-      </c>
-    </row>
-    <row r="45" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B45" s="2" t="s">
-        <v>154</v>
-      </c>
-      <c r="C45" s="2" t="s">
-        <v>917</v>
-      </c>
-    </row>
-    <row r="46" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B46" s="2" t="s">
-        <v>156</v>
-      </c>
-      <c r="C46" s="2" t="s">
-        <v>918</v>
-      </c>
-    </row>
-    <row r="47" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B47" s="2" t="s">
-        <v>158</v>
-      </c>
-      <c r="C47" s="2" t="s">
-        <v>919</v>
-      </c>
-    </row>
-    <row r="48" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B48" s="2" t="s">
-        <v>160</v>
-      </c>
-      <c r="C48" s="2" t="s">
-        <v>920</v>
-      </c>
-    </row>
-    <row r="49" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B49" s="2" t="s">
-        <v>162</v>
-      </c>
-      <c r="C49" s="2" t="s">
-        <v>921</v>
-      </c>
-    </row>
-    <row r="50" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B50" s="2" t="s">
-        <v>164</v>
-      </c>
-      <c r="C50" s="2" t="s">
-        <v>922</v>
-      </c>
-    </row>
-    <row r="51" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B51" s="2" t="s">
-        <v>166</v>
-      </c>
-      <c r="C51" s="2" t="s">
-        <v>923</v>
-      </c>
-    </row>
-    <row r="52" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B52" s="2" t="s">
-        <v>168</v>
-      </c>
-      <c r="C52" s="2" t="s">
-        <v>924</v>
-      </c>
-    </row>
-    <row r="53" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B53" s="2" t="s">
-        <v>170</v>
-      </c>
-      <c r="C53" s="2" t="s">
-        <v>925</v>
-      </c>
-    </row>
-    <row r="54" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B54" s="2" t="s">
-        <v>172</v>
-      </c>
-      <c r="C54" s="2" t="s">
-        <v>902</v>
-      </c>
     </row>
     <row r="55" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B55" s="2" t="s">
+      <c r="B55" s="3" t="s">
         <v>176</v>
       </c>
-      <c r="C55" s="2" t="s">
-        <v>926</v>
+      <c r="C55" s="3" t="s">
+        <v>929</v>
       </c>
     </row>
     <row r="56" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B56" s="2" t="s">
+      <c r="B56" s="3" t="s">
         <v>178</v>
       </c>
-      <c r="C56" s="2" t="s">
-        <v>927</v>
+      <c r="C56" s="3" t="s">
+        <v>930</v>
       </c>
     </row>
     <row r="57" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B57" s="2" t="s">
+      <c r="B57" s="3" t="s">
         <v>180</v>
       </c>
-      <c r="C57" s="2" t="s">
-        <v>928</v>
+      <c r="C57" s="3" t="s">
+        <v>931</v>
       </c>
     </row>
     <row r="58" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B58" s="2" t="s">
-        <v>929</v>
-      </c>
-      <c r="C58" s="2" t="s">
-        <v>930</v>
+      <c r="B58" s="3" t="s">
+        <v>932</v>
+      </c>
+      <c r="C58" s="3" t="s">
+        <v>933</v>
       </c>
     </row>
     <row r="59" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B59" s="2" t="s">
-        <v>931</v>
-      </c>
-      <c r="C59" s="2" t="s">
-        <v>932</v>
+      <c r="B59" s="3" t="s">
+        <v>934</v>
+      </c>
+      <c r="C59" s="3" t="s">
+        <v>935</v>
       </c>
     </row>
     <row r="60" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B60" s="2" t="s">
-        <v>933</v>
-      </c>
-      <c r="C60" s="2" t="s">
-        <v>934</v>
+      <c r="B60" s="3" t="s">
+        <v>936</v>
+      </c>
+      <c r="C60" s="3" t="s">
+        <v>937</v>
       </c>
     </row>
     <row r="61" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B61" s="2" t="s">
-        <v>789</v>
-      </c>
-      <c r="C61" s="2" t="s">
-        <v>935</v>
+      <c r="B61" s="3" t="s">
+        <v>792</v>
+      </c>
+      <c r="C61" s="3" t="s">
+        <v>938</v>
       </c>
     </row>
     <row r="62" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B62" s="2" t="s">
-        <v>791</v>
-      </c>
-      <c r="C62" s="2" t="s">
-        <v>936</v>
+      <c r="B62" s="3" t="s">
+        <v>794</v>
+      </c>
+      <c r="C62" s="3" t="s">
+        <v>939</v>
       </c>
     </row>
     <row r="63" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B63" s="2" t="s">
-        <v>793</v>
-      </c>
-      <c r="C63" s="2" t="s">
-        <v>937</v>
+      <c r="B63" s="3" t="s">
+        <v>796</v>
+      </c>
+      <c r="C63" s="3" t="s">
+        <v>940</v>
       </c>
     </row>
     <row r="64" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B64" s="2" t="s">
-        <v>795</v>
-      </c>
-      <c r="C64" s="2" t="s">
-        <v>938</v>
+      <c r="B64" s="3" t="s">
+        <v>798</v>
+      </c>
+      <c r="C64" s="3" t="s">
+        <v>941</v>
       </c>
     </row>
     <row r="65" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B65" s="2" t="s">
-        <v>797</v>
-      </c>
-      <c r="C65" s="2" t="s">
-        <v>939</v>
+      <c r="B65" s="3" t="s">
+        <v>800</v>
+      </c>
+      <c r="C65" s="3" t="s">
+        <v>942</v>
       </c>
     </row>
     <row r="66" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B66" s="2" t="s">
-        <v>940</v>
-      </c>
-      <c r="C66" s="2" t="s">
-        <v>941</v>
+      <c r="B66" s="3" t="s">
+        <v>943</v>
+      </c>
+      <c r="C66" s="3" t="s">
+        <v>944</v>
       </c>
     </row>
     <row r="67" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B67" s="2" t="s">
+      <c r="B67" s="3" t="s">
         <v>314</v>
       </c>
-      <c r="C67" s="2" t="s">
-        <v>942</v>
+      <c r="C67" s="3" t="s">
+        <v>945</v>
       </c>
     </row>
     <row r="68" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B68" s="2" t="s">
+      <c r="B68" s="3" t="s">
         <v>328</v>
       </c>
-      <c r="C68" s="2" t="s">
-        <v>943</v>
+      <c r="C68" s="3" t="s">
+        <v>946</v>
       </c>
     </row>
   </sheetData>
@@ -7986,251 +8119,251 @@
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B1" s="5" t="s">
+      <c r="B1" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="5" t="s">
+      <c r="C1" s="6" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="2" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B2" s="5" t="s">
-        <v>944</v>
-      </c>
-      <c r="C2" s="5" t="s">
-        <v>945</v>
+      <c r="B2" s="6" t="s">
+        <v>947</v>
+      </c>
+      <c r="C2" s="6" t="s">
+        <v>948</v>
       </c>
     </row>
     <row r="3" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B3" s="5" t="s">
+      <c r="B3" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="C3" s="5" t="s">
-        <v>946</v>
+      <c r="C3" s="6" t="s">
+        <v>949</v>
       </c>
     </row>
     <row r="4" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B4" s="5" t="s">
+      <c r="B4" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="C4" s="5" t="s">
-        <v>877</v>
+      <c r="C4" s="6" t="s">
+        <v>880</v>
       </c>
     </row>
     <row r="5" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B5" s="5" t="s">
+      <c r="B5" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="C5" s="5" t="s">
+      <c r="C5" s="6" t="s">
+        <v>913</v>
+      </c>
+    </row>
+    <row r="6" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B6" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="C6" s="6" t="s">
+        <v>950</v>
+      </c>
+    </row>
+    <row r="7" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B7" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C7" s="6" t="s">
+        <v>951</v>
+      </c>
+    </row>
+    <row r="8" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B8" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="C8" s="6" t="s">
+        <v>952</v>
+      </c>
+    </row>
+    <row r="9" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B9" s="6" t="s">
+        <v>953</v>
+      </c>
+      <c r="C9" s="6" t="s">
+        <v>954</v>
+      </c>
+    </row>
+    <row r="10" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B10" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="C10" s="6" t="s">
+        <v>955</v>
+      </c>
+    </row>
+    <row r="11" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B11" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="C11" s="6" t="s">
+        <v>956</v>
+      </c>
+    </row>
+    <row r="12" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B12" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="C12" s="6" t="s">
+        <v>957</v>
+      </c>
+    </row>
+    <row r="13" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B13" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="C13" s="6" t="s">
+        <v>958</v>
+      </c>
+    </row>
+    <row r="14" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B14" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="C14" s="6" t="s">
+        <v>959</v>
+      </c>
+    </row>
+    <row r="15" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B15" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="C15" s="6" t="s">
+        <v>882</v>
+      </c>
+    </row>
+    <row r="16" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B16" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="C16" s="6" t="s">
+        <v>881</v>
+      </c>
+    </row>
+    <row r="17" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B17" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="C17" s="6" t="s">
+        <v>883</v>
+      </c>
+    </row>
+    <row r="18" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B18" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="C18" s="6" t="s">
+        <v>960</v>
+      </c>
+    </row>
+    <row r="19" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B19" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="C19" s="6" t="s">
+        <v>949</v>
+      </c>
+    </row>
+    <row r="20" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B20" s="6" t="s">
+        <v>132</v>
+      </c>
+      <c r="C20" s="6" t="s">
+        <v>961</v>
+      </c>
+    </row>
+    <row r="21" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B21" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="C21" s="6" t="s">
+        <v>962</v>
+      </c>
+    </row>
+    <row r="22" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B22" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="C22" s="6" t="s">
+        <v>963</v>
+      </c>
+    </row>
+    <row r="23" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B23" s="6" t="s">
+        <v>118</v>
+      </c>
+      <c r="C23" s="6" t="s">
+        <v>964</v>
+      </c>
+    </row>
+    <row r="24" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B24" s="6" t="s">
+        <v>232</v>
+      </c>
+      <c r="C24" s="6" t="s">
+        <v>965</v>
+      </c>
+    </row>
+    <row r="25" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B25" s="6" t="s">
+        <v>152</v>
+      </c>
+      <c r="C25" s="6" t="s">
+        <v>906</v>
+      </c>
+    </row>
+    <row r="26" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B26" s="6" t="s">
+        <v>174</v>
+      </c>
+      <c r="C26" s="6" t="s">
+        <v>919</v>
+      </c>
+    </row>
+    <row r="27" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B27" s="6" t="s">
+        <v>966</v>
+      </c>
+      <c r="C27" s="6" t="s">
+        <v>895</v>
+      </c>
+    </row>
+    <row r="28" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B28" s="6" t="s">
+        <v>967</v>
+      </c>
+      <c r="C28" s="6" t="s">
+        <v>968</v>
+      </c>
+    </row>
+    <row r="29" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B29" s="6" t="s">
+        <v>268</v>
+      </c>
+      <c r="C29" s="6" t="s">
         <v>910</v>
       </c>
     </row>
-    <row r="6" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B6" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="C6" s="5" t="s">
-        <v>947</v>
-      </c>
-    </row>
-    <row r="7" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B7" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C7" s="5" t="s">
-        <v>948</v>
-      </c>
-    </row>
-    <row r="8" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B8" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="C8" s="5" t="s">
-        <v>949</v>
-      </c>
-    </row>
-    <row r="9" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B9" s="5" t="s">
-        <v>950</v>
-      </c>
-      <c r="C9" s="5" t="s">
-        <v>951</v>
-      </c>
-    </row>
-    <row r="10" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B10" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="C10" s="5" t="s">
-        <v>952</v>
-      </c>
-    </row>
-    <row r="11" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B11" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="C11" s="5" t="s">
-        <v>953</v>
-      </c>
-    </row>
-    <row r="12" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B12" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="C12" s="5" t="s">
-        <v>954</v>
-      </c>
-    </row>
-    <row r="13" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B13" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="C13" s="5" t="s">
-        <v>955</v>
-      </c>
-    </row>
-    <row r="14" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B14" s="5" t="s">
-        <v>78</v>
-      </c>
-      <c r="C14" s="5" t="s">
-        <v>956</v>
-      </c>
-    </row>
-    <row r="15" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B15" s="5" t="s">
-        <v>50</v>
-      </c>
-      <c r="C15" s="5" t="s">
-        <v>879</v>
-      </c>
-    </row>
-    <row r="16" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B16" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="C16" s="5" t="s">
-        <v>878</v>
-      </c>
-    </row>
-    <row r="17" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B17" s="5" t="s">
-        <v>62</v>
-      </c>
-      <c r="C17" s="5" t="s">
-        <v>880</v>
-      </c>
-    </row>
-    <row r="18" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B18" s="5" t="s">
-        <v>64</v>
-      </c>
-      <c r="C18" s="5" t="s">
-        <v>957</v>
-      </c>
-    </row>
-    <row r="19" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B19" s="5" t="s">
-        <v>66</v>
-      </c>
-      <c r="C19" s="5" t="s">
-        <v>946</v>
-      </c>
-    </row>
-    <row r="20" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B20" s="5" t="s">
-        <v>132</v>
-      </c>
-      <c r="C20" s="5" t="s">
-        <v>958</v>
-      </c>
-    </row>
-    <row r="21" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B21" s="5" t="s">
-        <v>98</v>
-      </c>
-      <c r="C21" s="5" t="s">
-        <v>959</v>
-      </c>
-    </row>
-    <row r="22" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B22" s="5" t="s">
-        <v>114</v>
-      </c>
-      <c r="C22" s="5" t="s">
-        <v>960</v>
-      </c>
-    </row>
-    <row r="23" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B23" s="5" t="s">
-        <v>118</v>
-      </c>
-      <c r="C23" s="5" t="s">
-        <v>961</v>
-      </c>
-    </row>
-    <row r="24" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B24" s="5" t="s">
-        <v>232</v>
-      </c>
-      <c r="C24" s="5" t="s">
-        <v>962</v>
-      </c>
-    </row>
-    <row r="25" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B25" s="5" t="s">
-        <v>152</v>
-      </c>
-      <c r="C25" s="5" t="s">
-        <v>903</v>
-      </c>
-    </row>
-    <row r="26" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B26" s="5" t="s">
-        <v>174</v>
-      </c>
-      <c r="C26" s="5" t="s">
-        <v>916</v>
-      </c>
-    </row>
-    <row r="27" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B27" s="5" t="s">
-        <v>963</v>
-      </c>
-      <c r="C27" s="5" t="s">
-        <v>892</v>
-      </c>
-    </row>
-    <row r="28" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B28" s="5" t="s">
-        <v>964</v>
-      </c>
-      <c r="C28" s="5" t="s">
-        <v>965</v>
-      </c>
-    </row>
-    <row r="29" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B29" s="5" t="s">
-        <v>268</v>
-      </c>
-      <c r="C29" s="5" t="s">
-        <v>907</v>
-      </c>
-    </row>
     <row r="30" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B30" s="5" t="s">
+      <c r="B30" s="6" t="s">
         <v>312</v>
       </c>
-      <c r="C30" s="5" t="s">
-        <v>966</v>
+      <c r="C30" s="6" t="s">
+        <v>969</v>
       </c>
     </row>
     <row r="31" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B31" s="5" t="s">
+      <c r="B31" s="6" t="s">
         <v>336</v>
       </c>
-      <c r="C31" s="5" t="s">
-        <v>967</v>
+      <c r="C31" s="6" t="s">
+        <v>970</v>
       </c>
     </row>
   </sheetData>
@@ -8245,107 +8378,107 @@
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="4" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="2" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B2" s="3" t="s">
+      <c r="B2" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="C2" s="3" t="s">
-        <v>968</v>
+      <c r="C2" s="4" t="s">
+        <v>971</v>
       </c>
     </row>
     <row r="3" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B3" s="3" t="s">
+      <c r="B3" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="C3" s="3" t="s">
-        <v>969</v>
+      <c r="C3" s="4" t="s">
+        <v>972</v>
       </c>
     </row>
     <row r="4" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B4" s="3" t="s">
+      <c r="B4" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="C4" s="3" t="s">
-        <v>961</v>
+      <c r="C4" s="4" t="s">
+        <v>964</v>
       </c>
     </row>
     <row r="5" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B5" s="3" t="s">
+      <c r="B5" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="C5" s="3" t="s">
-        <v>946</v>
+      <c r="C5" s="4" t="s">
+        <v>949</v>
       </c>
     </row>
     <row r="6" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B6" s="3" t="s">
+      <c r="B6" s="4" t="s">
         <v>78</v>
       </c>
-      <c r="C6" s="3" t="s">
-        <v>892</v>
+      <c r="C6" s="4" t="s">
+        <v>895</v>
       </c>
     </row>
     <row r="7" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B7" s="3" t="s">
+      <c r="B7" s="4" t="s">
         <v>132</v>
       </c>
-      <c r="C7" s="3" t="s">
+      <c r="C7" s="4" t="s">
         <v>429</v>
       </c>
     </row>
     <row r="8" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B8" s="3" t="s">
+      <c r="B8" s="4" t="s">
         <v>232</v>
       </c>
-      <c r="C8" s="3" t="s">
-        <v>970</v>
+      <c r="C8" s="4" t="s">
+        <v>973</v>
       </c>
     </row>
     <row r="9" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B9" s="3" t="s">
-        <v>963</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>971</v>
+      <c r="B9" s="4" t="s">
+        <v>966</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>974</v>
       </c>
     </row>
     <row r="10" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B10" s="3" t="s">
-        <v>964</v>
-      </c>
-      <c r="C10" s="3" t="s">
-        <v>972</v>
+      <c r="B10" s="4" t="s">
+        <v>967</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>975</v>
       </c>
     </row>
     <row r="11" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B11" s="3" t="s">
+      <c r="B11" s="4" t="s">
         <v>268</v>
       </c>
-      <c r="C11" s="3" t="s">
-        <v>973</v>
+      <c r="C11" s="4" t="s">
+        <v>976</v>
       </c>
     </row>
     <row r="12" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B12" s="3" t="s">
+      <c r="B12" s="4" t="s">
         <v>312</v>
       </c>
-      <c r="C12" s="3" t="s">
-        <v>974</v>
+      <c r="C12" s="4" t="s">
+        <v>977</v>
       </c>
     </row>
     <row r="13" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B13" s="3" t="s">
+      <c r="B13" s="4" t="s">
         <v>336</v>
       </c>
-      <c r="C13" s="3" t="s">
-        <v>975</v>
+      <c r="C13" s="4" t="s">
+        <v>978</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/Editor/DataDic/Data.xlsx
+++ b/Assets/Editor/DataDic/Data.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1216" uniqueCount="979">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="973" uniqueCount="808">
   <si>
     <t>Key</t>
   </si>
@@ -1393,9 +1393,6 @@
     <t>1007</t>
   </si>
   <si>
-    <t>1008</t>
-  </si>
-  <si>
     <t>1009</t>
   </si>
   <si>
@@ -1414,9 +1411,6 @@
     <t>窗</t>
   </si>
   <si>
-    <t>1012</t>
-  </si>
-  <si>
     <t>箱子</t>
   </si>
   <si>
@@ -1435,7 +1429,7 @@
     <t>1015</t>
   </si>
   <si>
-    <t>蜡烛</t>
+    <t>蜡烛1</t>
   </si>
   <si>
     <t>1016</t>
@@ -1453,7 +1447,10 @@
     <t>1018</t>
   </si>
   <si>
-    <t>1019</t>
+    <t>长柜台竖</t>
+  </si>
+  <si>
+    <t>长柜台横</t>
   </si>
   <si>
     <t>1020</t>
@@ -1486,942 +1483,498 @@
     <t>武器柜横</t>
   </si>
   <si>
-    <t>1025</t>
-  </si>
-  <si>
-    <t>武器柜</t>
-  </si>
-  <si>
-    <t>1027</t>
-  </si>
-  <si>
-    <t>1028</t>
+    <t>武器柜右</t>
+  </si>
+  <si>
+    <t>壁画1</t>
   </si>
   <si>
     <t>桌子</t>
   </si>
   <si>
-    <t>1029</t>
-  </si>
-  <si>
     <t>提灯</t>
   </si>
   <si>
-    <t>1030</t>
-  </si>
-  <si>
     <t>蜡烛吊灯</t>
   </si>
   <si>
-    <t>1031</t>
-  </si>
-  <si>
     <t>内门1</t>
   </si>
   <si>
-    <t>1032</t>
+    <t>锻造炉-设施</t>
+  </si>
+  <si>
+    <t>储物箱(木)-设施</t>
+  </si>
+  <si>
+    <t>楼梯上</t>
+  </si>
+  <si>
+    <t>商店开关</t>
+  </si>
+  <si>
+    <t>外窗1</t>
+  </si>
+  <si>
+    <t>外窗2</t>
+  </si>
+  <si>
+    <t>外窗3</t>
+  </si>
+  <si>
+    <t>外窗招牌</t>
+  </si>
+  <si>
+    <t>宽门</t>
+  </si>
+  <si>
+    <t>红窄门</t>
+  </si>
+  <si>
+    <t>别墅一楼床</t>
+  </si>
+  <si>
+    <t>秋千</t>
+  </si>
+  <si>
+    <t>城内河</t>
+  </si>
+  <si>
+    <t>我的大门</t>
+  </si>
+  <si>
+    <t>公所大门</t>
+  </si>
+  <si>
+    <t>黄窄门</t>
+  </si>
+  <si>
+    <t>双门</t>
+  </si>
+  <si>
+    <t>棚子门</t>
+  </si>
+  <si>
+    <t>竖长椅</t>
+  </si>
+  <si>
+    <t>广场河</t>
+  </si>
+  <si>
+    <t>农田</t>
+  </si>
+  <si>
+    <t>稻草人</t>
+  </si>
+  <si>
+    <t>树墩</t>
+  </si>
+  <si>
+    <t>提灯侧</t>
+  </si>
+  <si>
+    <t>篝火</t>
+  </si>
+  <si>
+    <t>柴棚</t>
+  </si>
+  <si>
+    <t>牲畜棚</t>
+  </si>
+  <si>
+    <t>农场河</t>
+  </si>
+  <si>
+    <t>栅栏门</t>
+  </si>
+  <si>
+    <t>提灯外</t>
+  </si>
+  <si>
+    <t>商店街河</t>
+  </si>
+  <si>
+    <t>水井</t>
+  </si>
+  <si>
+    <t>长椅背面</t>
+  </si>
+  <si>
+    <t>普通门</t>
+  </si>
+  <si>
+    <t>黄门2</t>
+  </si>
+  <si>
+    <t>二楼门</t>
+  </si>
+  <si>
+    <t>植物店柜台</t>
+  </si>
+  <si>
+    <t>壁炉</t>
+  </si>
+  <si>
+    <t>单人床</t>
+  </si>
+  <si>
+    <t>豪华床</t>
+  </si>
+  <si>
+    <t>植物店书桌</t>
+  </si>
+  <si>
+    <t>红椅子左</t>
+  </si>
+  <si>
+    <t>红椅子斜右</t>
+  </si>
+  <si>
+    <t>壁画老女</t>
+  </si>
+  <si>
+    <t>春战场</t>
+  </si>
+  <si>
+    <t>秋战场</t>
+  </si>
+  <si>
+    <t>畜牧店柜台</t>
+  </si>
+  <si>
+    <t>床绿</t>
+  </si>
+  <si>
+    <t>床红</t>
+  </si>
+  <si>
+    <t>磨坊</t>
+  </si>
+  <si>
+    <t>帐篷</t>
+  </si>
+  <si>
+    <t>无偏转内门</t>
+  </si>
+  <si>
+    <t>夏战场</t>
+  </si>
+  <si>
+    <t>冬战场</t>
+  </si>
+  <si>
+    <t>旗子</t>
+  </si>
+  <si>
+    <t>家具柜台</t>
+  </si>
+  <si>
+    <t>家具店大床</t>
+  </si>
+  <si>
+    <t>家具店小床</t>
+  </si>
+  <si>
+    <t>冷餐台</t>
+  </si>
+  <si>
+    <t>破损牲畜棚</t>
+  </si>
+  <si>
+    <t>初级牲口棚</t>
+  </si>
+  <si>
+    <t>食物槽</t>
+  </si>
+  <si>
+    <t>水槽</t>
+  </si>
+  <si>
+    <t>收获篮</t>
+  </si>
+  <si>
+    <t>传送门</t>
+  </si>
+  <si>
+    <t>山地湖</t>
+  </si>
+  <si>
+    <t>城门河</t>
+  </si>
+  <si>
+    <t>1100</t>
+  </si>
+  <si>
+    <t>我的家</t>
+  </si>
+  <si>
+    <t>1101</t>
+  </si>
+  <si>
+    <t>民居1</t>
+  </si>
+  <si>
+    <t>1103</t>
+  </si>
+  <si>
+    <t>民居2</t>
+  </si>
+  <si>
+    <t>镇公所</t>
+  </si>
+  <si>
+    <t>1105</t>
+  </si>
+  <si>
+    <t>1106</t>
+  </si>
+  <si>
+    <t>钟楼</t>
+  </si>
+  <si>
+    <t>动物店</t>
+  </si>
+  <si>
+    <t>1109</t>
+  </si>
+  <si>
+    <t>装备店</t>
+  </si>
+  <si>
+    <t>1110</t>
+  </si>
+  <si>
+    <t>水车房</t>
+  </si>
+  <si>
+    <t>1111</t>
+  </si>
+  <si>
+    <t>民宅1</t>
+  </si>
+  <si>
+    <t>民宅2</t>
+  </si>
+  <si>
+    <t>1113</t>
+  </si>
+  <si>
+    <t>摊位</t>
+  </si>
+  <si>
+    <t>1114</t>
+  </si>
+  <si>
+    <t>大摊位</t>
+  </si>
+  <si>
+    <t>1115</t>
+  </si>
+  <si>
+    <t>1116</t>
+  </si>
+  <si>
+    <t>鱼店</t>
+  </si>
+  <si>
+    <t>1117</t>
+  </si>
+  <si>
+    <t>搅拌器</t>
+  </si>
+  <si>
+    <t>冰箱</t>
+  </si>
+  <si>
+    <t>储物箱(木)</t>
+  </si>
+  <si>
+    <t>储物箱(银)</t>
+  </si>
+  <si>
+    <t>储物箱(金)</t>
+  </si>
+  <si>
+    <t>搅拌器-设施</t>
+  </si>
+  <si>
+    <t>冰箱-设施</t>
+  </si>
+  <si>
+    <t>缝纫机-设施</t>
+  </si>
+  <si>
+    <t>绘写台-设施</t>
+  </si>
+  <si>
+    <t>冷餐台-设施</t>
+  </si>
+  <si>
+    <t>蒸煮锅-设施</t>
+  </si>
+  <si>
+    <t>烘烤炉-设施</t>
+  </si>
+  <si>
+    <t>酿造桶-设施</t>
+  </si>
+  <si>
+    <t>储物箱(银)-设施</t>
+  </si>
+  <si>
+    <t>储物箱(金)-设施</t>
+  </si>
+  <si>
+    <t>红椅子</t>
+  </si>
+  <si>
+    <t>时钟</t>
+  </si>
+  <si>
+    <t>紫椅子</t>
+  </si>
+  <si>
+    <t>别墅床</t>
+  </si>
+  <si>
+    <t>豪华梳妆台</t>
+  </si>
+  <si>
+    <t>钢琴</t>
+  </si>
+  <si>
+    <t>紫椅子翻转</t>
+  </si>
+  <si>
+    <t>占卜屋床</t>
+  </si>
+  <si>
+    <t>占卜柜台</t>
+  </si>
+  <si>
+    <t>魔镜</t>
+  </si>
+  <si>
+    <t>坐垫小凳</t>
+  </si>
+  <si>
+    <t>客栈双人床</t>
+  </si>
+  <si>
+    <t>红长沙发左</t>
+  </si>
+  <si>
+    <t>红长沙右</t>
+  </si>
+  <si>
+    <t>沙发红上</t>
+  </si>
+  <si>
+    <t>红椅子下</t>
+  </si>
+  <si>
+    <t>椅子红斜</t>
+  </si>
+  <si>
+    <t>红色单人床</t>
+  </si>
+  <si>
+    <t>客栈柜台</t>
+  </si>
+  <si>
+    <t>沙发侧暗</t>
+  </si>
+  <si>
+    <t>单人床黄</t>
+  </si>
+  <si>
+    <t>长沙发蓝左</t>
+  </si>
+  <si>
+    <t>蓝椅子下</t>
+  </si>
+  <si>
+    <t>纺织店柜台</t>
+  </si>
+  <si>
+    <t>椅子红下</t>
+  </si>
+  <si>
+    <t>椅子红上</t>
+  </si>
+  <si>
+    <t>床白</t>
+  </si>
+  <si>
+    <t>望远镜</t>
+  </si>
+  <si>
+    <t>教堂讲台</t>
+  </si>
+  <si>
+    <t>酒馆柜台</t>
+  </si>
+  <si>
+    <t>地铺</t>
+  </si>
+  <si>
+    <t>地铺2</t>
+  </si>
+  <si>
+    <t>朴素床</t>
+  </si>
+  <si>
+    <t>海边</t>
+  </si>
+  <si>
+    <t>纺织机</t>
   </si>
   <si>
     <t>锻造炉</t>
   </si>
   <si>
-    <t>1033</t>
-  </si>
-  <si>
-    <t>储物箱</t>
-  </si>
-  <si>
-    <t>1034</t>
-  </si>
-  <si>
-    <t>楼梯上</t>
-  </si>
-  <si>
-    <t>1035</t>
-  </si>
-  <si>
-    <t>招牌</t>
-  </si>
-  <si>
-    <t>1036</t>
-  </si>
-  <si>
-    <t>外窗1</t>
-  </si>
-  <si>
-    <t>1037</t>
-  </si>
-  <si>
-    <t>外窗2</t>
-  </si>
-  <si>
-    <t>1038</t>
-  </si>
-  <si>
-    <t>外窗3</t>
-  </si>
-  <si>
-    <t>1039</t>
-  </si>
-  <si>
-    <t>外窗招牌</t>
-  </si>
-  <si>
-    <t>1040</t>
-  </si>
-  <si>
-    <t>宽门</t>
-  </si>
-  <si>
-    <t>1041</t>
-  </si>
-  <si>
-    <t>红窄门</t>
-  </si>
-  <si>
-    <t>1042</t>
-  </si>
-  <si>
-    <t>1043</t>
-  </si>
-  <si>
-    <t>秋千</t>
-  </si>
-  <si>
-    <t>1044</t>
-  </si>
-  <si>
-    <t>城内河</t>
-  </si>
-  <si>
-    <t>1045</t>
-  </si>
-  <si>
-    <t>我的大门</t>
-  </si>
-  <si>
-    <t>1046</t>
-  </si>
-  <si>
-    <t>公所大门</t>
-  </si>
-  <si>
-    <t>1047</t>
-  </si>
-  <si>
-    <t>黄窄门</t>
-  </si>
-  <si>
-    <t>1048</t>
-  </si>
-  <si>
-    <t>双门</t>
-  </si>
-  <si>
-    <t>1049</t>
-  </si>
-  <si>
-    <t>棚子门</t>
-  </si>
-  <si>
-    <t>1050</t>
-  </si>
-  <si>
-    <t>长椅</t>
-  </si>
-  <si>
-    <t>1051</t>
-  </si>
-  <si>
-    <t>广场河</t>
-  </si>
-  <si>
-    <t>1052</t>
-  </si>
-  <si>
-    <t>农田</t>
-  </si>
-  <si>
-    <t>1053</t>
-  </si>
-  <si>
-    <t>稻草人</t>
-  </si>
-  <si>
-    <t>1054</t>
-  </si>
-  <si>
-    <t>树墩</t>
-  </si>
-  <si>
-    <t>1055</t>
-  </si>
-  <si>
-    <t>提灯侧</t>
-  </si>
-  <si>
-    <t>1056</t>
-  </si>
-  <si>
-    <t>篝火</t>
-  </si>
-  <si>
-    <t>1057</t>
-  </si>
-  <si>
-    <t>柴棚</t>
-  </si>
-  <si>
-    <t>1058</t>
-  </si>
-  <si>
-    <t>牲畜棚</t>
-  </si>
-  <si>
-    <t>1059</t>
-  </si>
-  <si>
-    <t>农场河</t>
-  </si>
-  <si>
-    <t>1060</t>
-  </si>
-  <si>
-    <t>栅栏</t>
-  </si>
-  <si>
-    <t>1061</t>
-  </si>
-  <si>
-    <t>提灯外</t>
-  </si>
-  <si>
-    <t>1062</t>
-  </si>
-  <si>
-    <t>商店街河</t>
-  </si>
-  <si>
-    <t>1063</t>
-  </si>
-  <si>
-    <t>水井</t>
-  </si>
-  <si>
-    <t>1064</t>
-  </si>
-  <si>
-    <t>1065</t>
-  </si>
-  <si>
-    <t>普通门</t>
-  </si>
-  <si>
-    <t>1066</t>
-  </si>
-  <si>
-    <t>黄门2</t>
-  </si>
-  <si>
-    <t>1067</t>
-  </si>
-  <si>
-    <t>二楼门</t>
-  </si>
-  <si>
-    <t>1068</t>
-  </si>
-  <si>
-    <t>1069</t>
-  </si>
-  <si>
-    <t>壁炉</t>
-  </si>
-  <si>
-    <t>1070</t>
-  </si>
-  <si>
-    <t>1071</t>
-  </si>
-  <si>
-    <t>1072</t>
-  </si>
-  <si>
-    <t>植物店书桌</t>
-  </si>
-  <si>
-    <t>1073</t>
-  </si>
-  <si>
-    <t>红椅子左</t>
-  </si>
-  <si>
-    <t>1074</t>
-  </si>
-  <si>
-    <t>红椅子斜右</t>
-  </si>
-  <si>
-    <t>1075</t>
-  </si>
-  <si>
-    <t>壁画老女</t>
-  </si>
-  <si>
-    <t>1076</t>
-  </si>
-  <si>
-    <t>春战场</t>
-  </si>
-  <si>
-    <t>1077</t>
-  </si>
-  <si>
-    <t>秋战场</t>
-  </si>
-  <si>
-    <t>1078</t>
-  </si>
-  <si>
-    <t>1079</t>
-  </si>
-  <si>
-    <t>1080</t>
-  </si>
-  <si>
-    <t>1081</t>
-  </si>
-  <si>
-    <t>床红</t>
-  </si>
-  <si>
-    <t>1082</t>
-  </si>
-  <si>
-    <t>磨坊</t>
-  </si>
-  <si>
-    <t>1083</t>
-  </si>
-  <si>
-    <t>帐篷</t>
-  </si>
-  <si>
-    <t>1084</t>
-  </si>
-  <si>
-    <t>无偏转内门</t>
-  </si>
-  <si>
-    <t>1085</t>
-  </si>
-  <si>
-    <t>夏战场</t>
-  </si>
-  <si>
-    <t>1086</t>
-  </si>
-  <si>
-    <t>冬战场</t>
-  </si>
-  <si>
-    <t>1087</t>
-  </si>
-  <si>
-    <t>旗子</t>
-  </si>
-  <si>
-    <t>1088</t>
-  </si>
-  <si>
-    <t>1089</t>
-  </si>
-  <si>
-    <t>家具店大床</t>
-  </si>
-  <si>
-    <t>1090</t>
-  </si>
-  <si>
-    <t>家具店小床</t>
-  </si>
-  <si>
-    <t>1091</t>
-  </si>
-  <si>
-    <t>冷餐台</t>
-  </si>
-  <si>
-    <t>1092</t>
-  </si>
-  <si>
-    <t>破损牲畜棚</t>
-  </si>
-  <si>
-    <t>1093</t>
-  </si>
-  <si>
-    <t>初级牲口棚</t>
-  </si>
-  <si>
-    <t>1094</t>
-  </si>
-  <si>
-    <t>食物槽</t>
-  </si>
-  <si>
-    <t>1095</t>
-  </si>
-  <si>
-    <t>水槽</t>
-  </si>
-  <si>
-    <t>1096</t>
-  </si>
-  <si>
-    <t>收获篮</t>
-  </si>
-  <si>
-    <t>1097</t>
-  </si>
-  <si>
-    <t>传送门</t>
-  </si>
-  <si>
-    <t>1098</t>
-  </si>
-  <si>
-    <t>山地湖</t>
-  </si>
-  <si>
-    <t>1099</t>
-  </si>
-  <si>
-    <t>城门河</t>
-  </si>
-  <si>
-    <t>1100</t>
-  </si>
-  <si>
-    <t>我的家</t>
-  </si>
-  <si>
-    <t>1101</t>
-  </si>
-  <si>
-    <t>1102</t>
-  </si>
-  <si>
-    <t>民居1</t>
-  </si>
-  <si>
-    <t>1103</t>
-  </si>
-  <si>
-    <t>民居2</t>
-  </si>
-  <si>
-    <t>1104</t>
-  </si>
-  <si>
-    <t>镇公所</t>
-  </si>
-  <si>
-    <t>1105</t>
-  </si>
-  <si>
-    <t>1106</t>
-  </si>
-  <si>
-    <t>钟楼</t>
-  </si>
-  <si>
-    <t>1107</t>
-  </si>
-  <si>
-    <t>1108</t>
-  </si>
-  <si>
-    <t>动物店</t>
-  </si>
-  <si>
-    <t>1109</t>
-  </si>
-  <si>
-    <t>装备店</t>
-  </si>
-  <si>
-    <t>1110</t>
-  </si>
-  <si>
-    <t>1111</t>
-  </si>
-  <si>
-    <t>民宅1</t>
-  </si>
-  <si>
-    <t>民宅2</t>
-  </si>
-  <si>
-    <t>1113</t>
-  </si>
-  <si>
-    <t>摊位</t>
-  </si>
-  <si>
-    <t>1114</t>
-  </si>
-  <si>
-    <t>大摊位</t>
-  </si>
-  <si>
-    <t>1115</t>
-  </si>
-  <si>
-    <t>1116</t>
-  </si>
-  <si>
-    <t>鱼店</t>
-  </si>
-  <si>
-    <t>1117</t>
-  </si>
-  <si>
-    <t>1118</t>
-  </si>
-  <si>
-    <t>1119</t>
-  </si>
-  <si>
-    <t>搅拌器</t>
-  </si>
-  <si>
-    <t>1120</t>
-  </si>
-  <si>
-    <t>冰箱</t>
-  </si>
-  <si>
-    <t>1121</t>
-  </si>
-  <si>
-    <t>储物箱(木)</t>
-  </si>
-  <si>
-    <t>1122</t>
-  </si>
-  <si>
-    <t>储物箱(银)</t>
-  </si>
-  <si>
-    <t>1123</t>
-  </si>
-  <si>
-    <t>储物箱(金)</t>
-  </si>
-  <si>
-    <t>1124</t>
-  </si>
-  <si>
-    <t>1125</t>
-  </si>
-  <si>
-    <t>1126</t>
+    <t>烘烤炉</t>
+  </si>
+  <si>
+    <t>酿造桶</t>
+  </si>
+  <si>
+    <t>绘写台</t>
+  </si>
+  <si>
+    <t>蒸煮锅</t>
   </si>
   <si>
     <t>缝纫机</t>
   </si>
   <si>
-    <t>1127</t>
-  </si>
-  <si>
-    <t>绘写台</t>
-  </si>
-  <si>
-    <t>1128</t>
-  </si>
-  <si>
-    <t>1129</t>
-  </si>
-  <si>
-    <t>蒸煮锅</t>
-  </si>
-  <si>
-    <t>1130</t>
-  </si>
-  <si>
-    <t>烘烤炉</t>
-  </si>
-  <si>
-    <t>1131</t>
-  </si>
-  <si>
-    <t>酿造桶</t>
-  </si>
-  <si>
-    <t>1134</t>
-  </si>
-  <si>
-    <t>1135</t>
-  </si>
-  <si>
-    <t>1136</t>
-  </si>
-  <si>
-    <t>红椅子</t>
-  </si>
-  <si>
-    <t>1137</t>
-  </si>
-  <si>
-    <t>时钟</t>
-  </si>
-  <si>
-    <t>1138</t>
-  </si>
-  <si>
-    <t>紫椅子</t>
-  </si>
-  <si>
-    <t>1139</t>
-  </si>
-  <si>
-    <t>别墅床</t>
-  </si>
-  <si>
-    <t>1140</t>
-  </si>
-  <si>
-    <t>豪华梳妆台</t>
-  </si>
-  <si>
-    <t>1141</t>
-  </si>
-  <si>
-    <t>钢琴</t>
-  </si>
-  <si>
-    <t>1142</t>
-  </si>
-  <si>
-    <t>紫椅子翻转</t>
-  </si>
-  <si>
-    <t>1143</t>
-  </si>
-  <si>
-    <t>占卜屋床</t>
-  </si>
-  <si>
-    <t>1144</t>
-  </si>
-  <si>
-    <t>1145</t>
-  </si>
-  <si>
-    <t>魔镜</t>
-  </si>
-  <si>
-    <t>1146</t>
-  </si>
-  <si>
-    <t>坐垫小凳</t>
-  </si>
-  <si>
-    <t>1147</t>
-  </si>
-  <si>
-    <t>客栈双人床</t>
-  </si>
-  <si>
-    <t>1148</t>
-  </si>
-  <si>
-    <t>红长沙发左</t>
-  </si>
-  <si>
-    <t>1149</t>
-  </si>
-  <si>
-    <t>红长沙右</t>
-  </si>
-  <si>
-    <t>1150</t>
-  </si>
-  <si>
-    <t>沙发红上</t>
-  </si>
-  <si>
-    <t>1151</t>
-  </si>
-  <si>
-    <t>红椅子下</t>
-  </si>
-  <si>
-    <t>1152</t>
-  </si>
-  <si>
-    <t>椅子红斜</t>
-  </si>
-  <si>
-    <t>1153</t>
-  </si>
-  <si>
-    <t>红色单人床</t>
-  </si>
-  <si>
-    <t>1154</t>
-  </si>
-  <si>
-    <t>客栈柜台</t>
-  </si>
-  <si>
-    <t>1155</t>
-  </si>
-  <si>
-    <t>沙发侧暗</t>
-  </si>
-  <si>
-    <t>1156</t>
-  </si>
-  <si>
-    <t>单人床黄</t>
-  </si>
-  <si>
-    <t>1157</t>
-  </si>
-  <si>
-    <t>长沙发蓝左</t>
-  </si>
-  <si>
-    <t>1158</t>
-  </si>
-  <si>
-    <t>蓝椅子下</t>
-  </si>
-  <si>
-    <t>1159</t>
-  </si>
-  <si>
-    <t>1160</t>
-  </si>
-  <si>
-    <t>椅子红下</t>
-  </si>
-  <si>
-    <t>1161</t>
-  </si>
-  <si>
-    <t>椅子红上</t>
-  </si>
-  <si>
-    <t>1162</t>
-  </si>
-  <si>
-    <t>1163</t>
-  </si>
-  <si>
-    <t>望远镜</t>
-  </si>
-  <si>
-    <t>1164</t>
-  </si>
-  <si>
-    <t>教堂讲台</t>
-  </si>
-  <si>
-    <t>1165</t>
-  </si>
-  <si>
-    <t>1166</t>
-  </si>
-  <si>
-    <t>地铺</t>
-  </si>
-  <si>
-    <t>1167</t>
-  </si>
-  <si>
-    <t>地铺2</t>
-  </si>
-  <si>
-    <t>1168</t>
-  </si>
-  <si>
-    <t>朴素床</t>
-  </si>
-  <si>
-    <t>1169</t>
-  </si>
-  <si>
-    <t>楼梯下</t>
-  </si>
-  <si>
-    <t>1170</t>
-  </si>
-  <si>
-    <t>双人床</t>
-  </si>
-  <si>
-    <t>1171</t>
-  </si>
-  <si>
-    <t>沙发(蓝)</t>
-  </si>
-  <si>
-    <t>1172</t>
-  </si>
-  <si>
-    <t>沙发(红)</t>
-  </si>
-  <si>
-    <t>1173</t>
-  </si>
-  <si>
-    <t>盆栽1</t>
-  </si>
-  <si>
-    <t>1174</t>
-  </si>
-  <si>
-    <t>盆栽2</t>
-  </si>
-  <si>
-    <t>1175</t>
-  </si>
-  <si>
-    <t>盆栽3</t>
-  </si>
-  <si>
-    <t>1176</t>
-  </si>
-  <si>
-    <t>盆栽4</t>
-  </si>
-  <si>
-    <t>1177</t>
-  </si>
-  <si>
-    <t>盆栽5</t>
-  </si>
-  <si>
-    <t>1178</t>
-  </si>
-  <si>
-    <t>1179</t>
-  </si>
-  <si>
-    <t>船坞栅栏</t>
-  </si>
-  <si>
-    <t>1181</t>
-  </si>
-  <si>
-    <t>装备店柜台</t>
-  </si>
-  <si>
-    <t>1182</t>
-  </si>
-  <si>
-    <t>魔法柜台</t>
-  </si>
-  <si>
-    <t>1183</t>
-  </si>
-  <si>
-    <t>1184</t>
-  </si>
-  <si>
-    <t>船长床</t>
-  </si>
-  <si>
-    <t>1200</t>
-  </si>
-  <si>
-    <t>海边</t>
-  </si>
-  <si>
-    <t>1201</t>
-  </si>
-  <si>
-    <t>纺织机</t>
-  </si>
-  <si>
-    <t>1202</t>
-  </si>
-  <si>
-    <t>1203</t>
-  </si>
-  <si>
-    <t>1204</t>
-  </si>
-  <si>
-    <t>1205</t>
-  </si>
-  <si>
-    <t>1206</t>
-  </si>
-  <si>
-    <t>1207</t>
-  </si>
-  <si>
     <t>纺线机</t>
   </si>
   <si>
-    <t>1209</t>
-  </si>
-  <si>
     <t>织布机</t>
   </si>
   <si>
-    <t>1210</t>
-  </si>
-  <si>
     <t>制革机</t>
   </si>
   <si>
-    <t>1211</t>
-  </si>
-  <si>
-    <t>高温熔炉</t>
-  </si>
-  <si>
-    <t>1290</t>
-  </si>
-  <si>
     <t>自宅门</t>
   </si>
   <si>
-    <t>1300</t>
-  </si>
-  <si>
     <t>客栈</t>
   </si>
   <si>
-    <t>1301</t>
-  </si>
-  <si>
     <t>别墅</t>
   </si>
   <si>
-    <t>1302</t>
-  </si>
-  <si>
     <t>自宅</t>
   </si>
   <si>
-    <t>164</t>
-  </si>
-  <si>
-    <t>2000</t>
+    <t>长椅下</t>
   </si>
   <si>
     <t>水坑</t>
   </si>
   <si>
-    <t>8000</t>
-  </si>
-  <si>
     <t>玉米</t>
   </si>
   <si>
@@ -2455,138 +2008,69 @@
     <t>紫甘蓝</t>
   </si>
   <si>
-    <t>8006</t>
-  </si>
-  <si>
     <t>黄瓜</t>
   </si>
   <si>
-    <t>8007</t>
-  </si>
-  <si>
     <t>西兰花</t>
   </si>
   <si>
-    <t>8008</t>
-  </si>
-  <si>
     <t>番茄</t>
   </si>
   <si>
-    <t>8009</t>
-  </si>
-  <si>
     <t>胡萝卜</t>
   </si>
   <si>
-    <t>8010</t>
-  </si>
-  <si>
     <t>西瓜</t>
   </si>
   <si>
-    <t>8011</t>
-  </si>
-  <si>
     <t>辣椒</t>
   </si>
   <si>
-    <t>8012</t>
-  </si>
-  <si>
     <t>奇异果</t>
   </si>
   <si>
-    <t>8013</t>
-  </si>
-  <si>
     <t>茄子</t>
   </si>
   <si>
-    <t>8014</t>
-  </si>
-  <si>
     <t>豌豆</t>
   </si>
   <si>
-    <t>8015</t>
-  </si>
-  <si>
     <t>土豆</t>
   </si>
   <si>
-    <t>8016</t>
-  </si>
-  <si>
     <t>大蒜</t>
   </si>
   <si>
-    <t>8017</t>
-  </si>
-  <si>
     <t>芦笋</t>
   </si>
   <si>
-    <t>8018</t>
-  </si>
-  <si>
     <t>南瓜</t>
   </si>
   <si>
-    <t>8019</t>
-  </si>
-  <si>
-    <t>8020</t>
-  </si>
-  <si>
     <t>小麦</t>
   </si>
   <si>
-    <t>8021</t>
-  </si>
-  <si>
     <t>啤酒花</t>
   </si>
   <si>
-    <t>8022</t>
-  </si>
-  <si>
     <t>葡萄</t>
   </si>
   <si>
-    <t>8023</t>
-  </si>
-  <si>
     <t>菠萝</t>
   </si>
   <si>
-    <t>8024</t>
-  </si>
-  <si>
     <t>咖啡</t>
   </si>
   <si>
-    <t>8025</t>
-  </si>
-  <si>
     <t>草莓</t>
   </si>
   <si>
-    <t>8026</t>
-  </si>
-  <si>
     <t>蓝莓</t>
   </si>
   <si>
-    <t>8027</t>
-  </si>
-  <si>
     <t>红薯</t>
   </si>
   <si>
-    <t>8028</t>
-  </si>
-  <si>
     <t>甜菜</t>
   </si>
   <si>
@@ -2984,6 +2468,10 @@
   </si>
   <si>
     <t>分配</t>
+  </si>
+  <si>
+    <t>酒馆</t>
+    <phoneticPr fontId="0" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -3009,6 +2497,7 @@
       <sz val="11"/>
       <name val="宋体"/>
       <family val="3"/>
+      <charset val="134"/>
     </font>
   </fonts>
   <fills count="3">
@@ -3037,8 +2526,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1"/>
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1"/>
@@ -3334,259 +2822,259 @@
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B1" s="7" t="s">
+      <c r="B1" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="7" t="s">
+      <c r="C1" s="6" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="2" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B2" s="7" t="s">
-        <v>847</v>
-      </c>
-      <c r="C2" s="7" t="s">
-        <v>848</v>
+      <c r="B2" s="6" t="s">
+        <v>675</v>
+      </c>
+      <c r="C2" s="6" t="s">
+        <v>676</v>
       </c>
     </row>
     <row r="3" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B3" s="7" t="s">
+      <c r="B3" s="6" t="s">
         <v>445</v>
       </c>
-      <c r="C3" s="7" t="s">
-        <v>849</v>
+      <c r="C3" s="6" t="s">
+        <v>677</v>
       </c>
     </row>
     <row r="4" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B4" s="7" t="s">
+      <c r="B4" s="6" t="s">
         <v>447</v>
       </c>
-      <c r="C4" s="7" t="s">
-        <v>850</v>
+      <c r="C4" s="6" t="s">
+        <v>678</v>
       </c>
     </row>
     <row r="5" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B5" s="7" t="s">
-        <v>449</v>
-      </c>
-      <c r="C5" s="7" t="s">
-        <v>851</v>
+      <c r="B5" s="6" t="s">
+        <v>448</v>
+      </c>
+      <c r="C5" s="6" t="s">
+        <v>679</v>
       </c>
     </row>
     <row r="6" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B6" s="7" t="s">
-        <v>451</v>
-      </c>
-      <c r="C6" s="7" t="s">
-        <v>852</v>
+      <c r="B6" s="6" t="s">
+        <v>450</v>
+      </c>
+      <c r="C6" s="6" t="s">
+        <v>680</v>
       </c>
     </row>
     <row r="7" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B7" s="7" t="s">
-        <v>453</v>
-      </c>
-      <c r="C7" s="7" t="s">
-        <v>853</v>
+      <c r="B7" s="6" t="s">
+        <v>452</v>
+      </c>
+      <c r="C7" s="6" t="s">
+        <v>681</v>
       </c>
     </row>
     <row r="8" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B8" s="7" t="s">
+      <c r="B8" s="6" t="s">
+        <v>455</v>
+      </c>
+      <c r="C8" s="6" t="s">
+        <v>682</v>
+      </c>
+    </row>
+    <row r="9" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B9" s="6" t="s">
         <v>457</v>
       </c>
-      <c r="C8" s="7" t="s">
-        <v>854</v>
-      </c>
-    </row>
-    <row r="9" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B9" s="7" t="s">
+      <c r="C9" s="6" t="s">
+        <v>683</v>
+      </c>
+    </row>
+    <row r="10" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B10" s="6" t="s">
         <v>459</v>
       </c>
-      <c r="C9" s="7" t="s">
-        <v>855</v>
-      </c>
-    </row>
-    <row r="10" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B10" s="7" t="s">
+      <c r="C10" s="6" t="s">
+        <v>684</v>
+      </c>
+    </row>
+    <row r="11" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B11" s="6" t="s">
         <v>461</v>
       </c>
-      <c r="C10" s="7" t="s">
-        <v>856</v>
-      </c>
-    </row>
-    <row r="11" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B11" s="7" t="s">
+      <c r="C11" s="6" t="s">
+        <v>685</v>
+      </c>
+    </row>
+    <row r="12" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B12" s="6" t="s">
         <v>463</v>
       </c>
-      <c r="C11" s="7" t="s">
-        <v>857</v>
-      </c>
-    </row>
-    <row r="12" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B12" s="7" t="s">
+      <c r="C12" s="6" t="s">
+        <v>686</v>
+      </c>
+    </row>
+    <row r="13" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B13" s="6" t="s">
         <v>465</v>
       </c>
-      <c r="C12" s="7" t="s">
-        <v>858</v>
-      </c>
-    </row>
-    <row r="13" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B13" s="7" t="s">
-        <v>467</v>
-      </c>
-      <c r="C13" s="7" t="s">
-        <v>859</v>
+      <c r="C13" s="6" t="s">
+        <v>687</v>
       </c>
     </row>
     <row r="14" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B14" s="7" t="s">
-        <v>469</v>
-      </c>
-      <c r="C14" s="7" t="s">
-        <v>860</v>
+      <c r="B14" s="6" t="s">
+        <v>468</v>
+      </c>
+      <c r="C14" s="6" t="s">
+        <v>688</v>
       </c>
     </row>
     <row r="15" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B15" s="7" t="s">
-        <v>471</v>
-      </c>
-      <c r="C15" s="7" t="s">
-        <v>861</v>
+      <c r="B15" s="6" t="s">
+        <v>470</v>
+      </c>
+      <c r="C15" s="6" t="s">
+        <v>689</v>
       </c>
     </row>
     <row r="16" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B16" s="7" t="s">
-        <v>473</v>
-      </c>
-      <c r="C16" s="7" t="s">
-        <v>862</v>
+      <c r="B16" s="6" t="s">
+        <v>472</v>
+      </c>
+      <c r="C16" s="6" t="s">
+        <v>690</v>
       </c>
     </row>
     <row r="17" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B17" s="7" t="s">
-        <v>475</v>
-      </c>
-      <c r="C17" s="7" t="s">
-        <v>863</v>
+      <c r="B17" s="6" t="s">
+        <v>474</v>
+      </c>
+      <c r="C17" s="6" t="s">
+        <v>691</v>
       </c>
     </row>
     <row r="18" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B18" s="7" t="s">
-        <v>477</v>
-      </c>
-      <c r="C18" s="7" t="s">
-        <v>864</v>
+      <c r="B18" s="6" t="s">
+        <v>476</v>
+      </c>
+      <c r="C18" s="6" t="s">
+        <v>692</v>
       </c>
     </row>
     <row r="19" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B19" s="7" t="s">
-        <v>617</v>
-      </c>
-      <c r="C19" s="7" t="s">
-        <v>865</v>
+      <c r="B19" s="6" t="s">
+        <v>551</v>
+      </c>
+      <c r="C19" s="6" t="s">
+        <v>693</v>
       </c>
     </row>
     <row r="20" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B20" s="7" t="s">
-        <v>619</v>
-      </c>
-      <c r="C20" s="7" t="s">
-        <v>866</v>
+      <c r="B20" s="6" t="s">
+        <v>553</v>
+      </c>
+      <c r="C20" s="6" t="s">
+        <v>694</v>
       </c>
     </row>
     <row r="21" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B21" s="7" t="s">
-        <v>622</v>
-      </c>
-      <c r="C21" s="7" t="s">
-        <v>867</v>
+      <c r="B21" s="6" t="s">
+        <v>555</v>
+      </c>
+      <c r="C21" s="6" t="s">
+        <v>695</v>
       </c>
     </row>
     <row r="22" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B22" s="7" t="s">
-        <v>626</v>
-      </c>
-      <c r="C22" s="7" t="s">
-        <v>868</v>
+      <c r="B22" s="6" t="s">
+        <v>558</v>
+      </c>
+      <c r="C22" s="6" t="s">
+        <v>696</v>
       </c>
     </row>
     <row r="23" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B23" s="7" t="s">
-        <v>627</v>
-      </c>
-      <c r="C23" s="7" t="s">
-        <v>869</v>
+      <c r="B23" s="6" t="s">
+        <v>559</v>
+      </c>
+      <c r="C23" s="6" t="s">
+        <v>697</v>
       </c>
     </row>
     <row r="24" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B24" s="7" t="s">
-        <v>632</v>
-      </c>
-      <c r="C24" s="7" t="s">
-        <v>870</v>
+      <c r="B24" s="6" t="s">
+        <v>562</v>
+      </c>
+      <c r="C24" s="6" t="s">
+        <v>698</v>
       </c>
     </row>
     <row r="25" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B25" s="7" t="s">
-        <v>634</v>
-      </c>
-      <c r="C25" s="7" t="s">
-        <v>871</v>
+      <c r="B25" s="6" t="s">
+        <v>564</v>
+      </c>
+      <c r="C25" s="6" t="s">
+        <v>699</v>
       </c>
     </row>
     <row r="26" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B26" s="7" t="s">
-        <v>635</v>
-      </c>
-      <c r="C26" s="7" t="s">
-        <v>872</v>
+      <c r="B26" s="6" t="s">
+        <v>566</v>
+      </c>
+      <c r="C26" s="6" t="s">
+        <v>700</v>
       </c>
     </row>
     <row r="27" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B27" s="7" t="s">
+      <c r="B27" s="6" t="s">
         <v>388</v>
       </c>
-      <c r="C27" s="7" t="s">
-        <v>873</v>
+      <c r="C27" s="6" t="s">
+        <v>701</v>
       </c>
     </row>
     <row r="28" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B28" s="7" t="s">
-        <v>638</v>
-      </c>
-      <c r="C28" s="7" t="s">
-        <v>874</v>
+      <c r="B28" s="6" t="s">
+        <v>569</v>
+      </c>
+      <c r="C28" s="6" t="s">
+        <v>702</v>
       </c>
     </row>
     <row r="29" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B29" s="7" t="s">
-        <v>640</v>
-      </c>
-      <c r="C29" s="7" t="s">
-        <v>875</v>
+      <c r="B29" s="6" t="s">
+        <v>571</v>
+      </c>
+      <c r="C29" s="6" t="s">
+        <v>703</v>
       </c>
     </row>
     <row r="30" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B30" s="7" t="s">
-        <v>642</v>
-      </c>
-      <c r="C30" s="7" t="s">
-        <v>876</v>
+      <c r="B30" s="6" t="s">
+        <v>573</v>
+      </c>
+      <c r="C30" s="6" t="s">
+        <v>704</v>
       </c>
     </row>
     <row r="31" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B31" s="7" t="s">
-        <v>643</v>
-      </c>
-      <c r="C31" s="7" t="s">
-        <v>877</v>
+      <c r="B31" s="6" t="s">
+        <v>574</v>
+      </c>
+      <c r="C31" s="6" t="s">
+        <v>705</v>
       </c>
     </row>
     <row r="32" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B32" s="7" t="s">
-        <v>645</v>
-      </c>
-      <c r="C32" s="7" t="s">
-        <v>878</v>
+      <c r="B32" s="6" t="s">
+        <v>576</v>
+      </c>
+      <c r="C32" s="6" t="s">
+        <v>706</v>
       </c>
     </row>
   </sheetData>
@@ -3601,2592 +3089,2464 @@
   <dimension ref="B1:O56"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="22.28515625" style="5" customWidth="1"/>
+    <col min="2" max="2" width="22.28515625" style="4" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B1" s="7" t="s">
+      <c r="B1" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="7" t="s">
+      <c r="C1" s="6" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="2" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B2" s="7" t="s">
+      <c r="B2" s="6" t="s">
         <v>338</v>
       </c>
-      <c r="C2" s="7" t="s">
+      <c r="C2" s="6" t="s">
         <v>339</v>
       </c>
     </row>
     <row r="3" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B3" s="7" t="s">
+      <c r="B3" s="6" t="s">
         <v>340</v>
       </c>
-      <c r="C3" s="7" t="s">
+      <c r="C3" s="6" t="s">
         <v>341</v>
       </c>
     </row>
     <row r="4" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B4" s="7" t="s">
+      <c r="B4" s="6" t="s">
         <v>342</v>
       </c>
-      <c r="C4" s="7" t="s">
+      <c r="C4" s="6" t="s">
         <v>343</v>
       </c>
-      <c r="G4" s="8" t="s">
+      <c r="G4" s="7" t="s">
         <v>344</v>
       </c>
-      <c r="I4" s="9" t="s">
+      <c r="I4" s="8" t="s">
         <v>345</v>
       </c>
-      <c r="J4" s="9" t="s">
+      <c r="J4" s="8" t="s">
         <v>346</v>
       </c>
-      <c r="K4" s="7" t="s">
+      <c r="K4" s="6" t="s">
         <v>347</v>
       </c>
     </row>
     <row r="5" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B5" s="7" t="s">
+      <c r="B5" s="6" t="s">
         <v>348</v>
       </c>
-      <c r="C5" s="7">
+      <c r="C5" s="6">
         <v>948</v>
       </c>
-      <c r="G5" s="8" t="s">
+      <c r="G5" s="7" t="s">
         <v>349</v>
       </c>
-      <c r="I5" s="5">
+      <c r="I5" s="4">
         <f>VLOOKUP(I4,$B:$C,2,FALSE)</f>
         <v>874</v>
       </c>
-      <c r="J5" s="7" t="str">
+      <c r="J5" s="6" t="str">
         <f t="shared" ref="J5:K5" si="0">VLOOKUP(J4,$B:$C,2,FALSE)</f>
         <v>2355</v>
       </c>
-      <c r="K5" s="7">
+      <c r="K5" s="6">
         <f t="shared" si="0"/>
         <v>2497</v>
       </c>
     </row>
     <row r="6" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B6" s="7" t="s">
+      <c r="B6" s="6" t="s">
         <v>350</v>
       </c>
-      <c r="C6" s="7" t="s">
+      <c r="C6" s="6" t="s">
         <v>351</v>
       </c>
-      <c r="G6" s="10" t="str">
+      <c r="G6" s="9" t="str">
         <f>G4&amp;","&amp;G5</f>
         <v>6,0,9,0</v>
       </c>
-      <c r="H6" s="10"/>
-      <c r="I6" s="10">
+      <c r="H6" s="9"/>
+      <c r="I6" s="9">
         <f>I5</f>
         <v>874</v>
       </c>
-      <c r="J6" s="10" t="str">
+      <c r="J6" s="9" t="str">
         <f>I6&amp;","&amp;J5</f>
         <v>874,2355</v>
       </c>
-      <c r="K6" s="10" t="str">
+      <c r="K6" s="9" t="str">
         <f>J6&amp;","&amp;K5</f>
         <v>874,2355,2497</v>
       </c>
-      <c r="L6" s="7"/>
-      <c r="M6" s="10"/>
+      <c r="L6" s="6"/>
+      <c r="M6" s="9"/>
     </row>
     <row r="7" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B7" s="7" t="s">
+      <c r="B7" s="6" t="s">
         <v>352</v>
       </c>
-      <c r="C7" s="7" t="s">
+      <c r="C7" s="6" t="s">
         <v>353</v>
       </c>
-      <c r="G7" s="8" t="s">
+      <c r="G7" s="7" t="s">
         <v>349</v>
       </c>
-      <c r="I7" s="9" t="s">
+      <c r="I7" s="8" t="s">
         <v>345</v>
       </c>
-      <c r="J7" s="9" t="s">
+      <c r="J7" s="8" t="s">
         <v>346</v>
       </c>
-      <c r="K7" s="7" t="s">
+      <c r="K7" s="6" t="s">
         <v>347</v>
       </c>
-      <c r="L7" s="7" t="s">
+      <c r="L7" s="6" t="s">
         <v>354</v>
       </c>
-      <c r="M7" s="7" t="s">
+      <c r="M7" s="6" t="s">
         <v>355</v>
       </c>
-      <c r="N7" s="7" t="s">
+      <c r="N7" s="6" t="s">
         <v>356</v>
       </c>
-      <c r="O7" s="7" t="s">
+      <c r="O7" s="6" t="s">
         <v>357</v>
       </c>
     </row>
     <row r="8" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B8" s="7" t="s">
+      <c r="B8" s="6" t="s">
         <v>345</v>
       </c>
-      <c r="C8" s="7">
+      <c r="C8" s="6">
         <v>874</v>
       </c>
-      <c r="G8" s="8" t="s">
+      <c r="G8" s="7" t="s">
         <v>358</v>
       </c>
-      <c r="I8" s="7">
+      <c r="I8" s="6">
         <f>VLOOKUP(I7,$B:$C,2,FALSE)</f>
         <v>874</v>
       </c>
-      <c r="J8" s="7" t="str">
+      <c r="J8" s="6" t="str">
         <f>VLOOKUP(J7,$B:$C,2,FALSE)</f>
         <v>2355</v>
       </c>
-      <c r="K8" s="7">
+      <c r="K8" s="6">
         <f t="shared" ref="K8:L8" si="1">VLOOKUP(K7,$B:$C,2,FALSE)</f>
         <v>2497</v>
       </c>
-      <c r="L8" s="7" t="str">
+      <c r="L8" s="6" t="str">
         <f t="shared" si="1"/>
         <v>302</v>
       </c>
-      <c r="M8" s="7" t="str">
+      <c r="M8" s="6" t="str">
         <f>VLOOKUP(M7,$B:$C,2,FALSE)</f>
         <v>889</v>
       </c>
-      <c r="N8" s="7" t="str">
+      <c r="N8" s="6" t="str">
         <f t="shared" ref="N8:O8" si="2">VLOOKUP(N7,$B:$C,2,FALSE)</f>
         <v>695</v>
       </c>
-      <c r="O8" s="7" t="str">
+      <c r="O8" s="6" t="str">
         <f t="shared" si="2"/>
         <v>512</v>
       </c>
     </row>
     <row r="9" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B9" s="7" t="s">
+      <c r="B9" s="6" t="s">
         <v>359</v>
       </c>
-      <c r="C9" s="7" t="s">
+      <c r="C9" s="6" t="s">
         <v>360</v>
       </c>
-      <c r="G9" s="10" t="str">
+      <c r="G9" s="9" t="str">
         <f>G7&amp;","&amp;G8</f>
         <v>9,0,17,30</v>
       </c>
-      <c r="H9" s="10"/>
-      <c r="I9" s="10">
+      <c r="H9" s="9"/>
+      <c r="I9" s="9">
         <f>I8</f>
         <v>874</v>
       </c>
-      <c r="J9" s="10" t="str">
+      <c r="J9" s="9" t="str">
         <f>I9&amp;","&amp;J8</f>
         <v>874,2355</v>
       </c>
-      <c r="K9" s="10" t="str">
+      <c r="K9" s="9" t="str">
         <f t="shared" ref="K9:N9" si="3">J9&amp;","&amp;K8</f>
         <v>874,2355,2497</v>
       </c>
-      <c r="L9" s="10" t="str">
+      <c r="L9" s="9" t="str">
         <f t="shared" si="3"/>
         <v>874,2355,2497,302</v>
       </c>
-      <c r="M9" s="10" t="str">
+      <c r="M9" s="9" t="str">
         <f t="shared" si="3"/>
         <v>874,2355,2497,302,889</v>
       </c>
-      <c r="N9" s="10" t="str">
+      <c r="N9" s="9" t="str">
         <f t="shared" si="3"/>
         <v>874,2355,2497,302,889,695</v>
       </c>
-      <c r="O9" s="10" t="str">
+      <c r="O9" s="9" t="str">
         <f>N9&amp;","&amp;O8</f>
         <v>874,2355,2497,302,889,695,512</v>
       </c>
     </row>
     <row r="10" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B10" s="7" t="s">
+      <c r="B10" s="6" t="s">
         <v>361</v>
       </c>
-      <c r="C10" s="7" t="s">
+      <c r="C10" s="6" t="s">
         <v>362</v>
       </c>
-      <c r="G10" s="8" t="s">
+      <c r="G10" s="7" t="s">
         <v>358</v>
       </c>
     </row>
     <row r="11" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B11" s="7" t="s">
+      <c r="B11" s="6" t="s">
         <v>363</v>
       </c>
-      <c r="C11" s="7" t="s">
+      <c r="C11" s="6" t="s">
         <v>364</v>
       </c>
-      <c r="G11" s="8" t="s">
+      <c r="G11" s="7" t="s">
         <v>365</v>
       </c>
     </row>
     <row r="12" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B12" s="7" t="s">
+      <c r="B12" s="6" t="s">
         <v>366</v>
       </c>
-      <c r="C12" s="7">
+      <c r="C12" s="6">
         <v>1756</v>
       </c>
-      <c r="F12" s="7"/>
-      <c r="G12" s="10" t="str">
+      <c r="F12" s="6"/>
+      <c r="G12" s="9" t="str">
         <f>G10&amp;","&amp;G11</f>
         <v>17,30,19,30</v>
       </c>
-      <c r="H12" s="7"/>
-      <c r="I12" s="7"/>
-      <c r="J12" s="7"/>
-      <c r="K12" s="7"/>
-      <c r="L12" s="7"/>
-      <c r="M12" s="7"/>
-      <c r="N12" s="7"/>
-      <c r="O12" s="7"/>
+      <c r="H12" s="6"/>
+      <c r="I12" s="6"/>
+      <c r="J12" s="6"/>
+      <c r="K12" s="6"/>
+      <c r="L12" s="6"/>
+      <c r="M12" s="6"/>
+      <c r="N12" s="6"/>
+      <c r="O12" s="6"/>
     </row>
     <row r="13" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B13" s="7" t="s">
+      <c r="B13" s="6" t="s">
         <v>367</v>
       </c>
-      <c r="C13" s="7" t="s">
+      <c r="C13" s="6" t="s">
         <v>368</v>
       </c>
-      <c r="F13" s="7"/>
-      <c r="G13" s="8"/>
-      <c r="H13" s="7"/>
-      <c r="I13" s="7"/>
-      <c r="J13" s="7"/>
-      <c r="K13" s="7"/>
-      <c r="L13" s="7"/>
-      <c r="M13" s="7"/>
-      <c r="N13" s="7"/>
-      <c r="O13" s="7"/>
+      <c r="F13" s="6"/>
+      <c r="G13" s="7"/>
+      <c r="H13" s="6"/>
+      <c r="I13" s="6"/>
+      <c r="J13" s="6"/>
+      <c r="K13" s="6"/>
+      <c r="L13" s="6"/>
+      <c r="M13" s="6"/>
+      <c r="N13" s="6"/>
+      <c r="O13" s="6"/>
     </row>
     <row r="14" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B14" s="7" t="s">
+      <c r="B14" s="6" t="s">
         <v>369</v>
       </c>
-      <c r="C14" s="7" t="s">
+      <c r="C14" s="6" t="s">
         <v>370</v>
       </c>
-      <c r="F14" s="7"/>
-      <c r="G14" s="8" t="s">
+      <c r="F14" s="6"/>
+      <c r="G14" s="7" t="s">
         <v>365</v>
       </c>
-      <c r="I14" s="7" t="s">
+      <c r="I14" s="6" t="s">
         <v>354</v>
       </c>
-      <c r="J14" s="7" t="s">
+      <c r="J14" s="6" t="s">
         <v>355</v>
       </c>
-      <c r="K14" s="7" t="s">
+      <c r="K14" s="6" t="s">
         <v>356</v>
       </c>
-      <c r="L14" s="7" t="s">
+      <c r="L14" s="6" t="s">
         <v>357</v>
       </c>
     </row>
     <row r="15" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B15" s="7" t="s">
+      <c r="B15" s="6" t="s">
         <v>371</v>
       </c>
-      <c r="C15" s="7" t="s">
+      <c r="C15" s="6" t="s">
         <v>372</v>
       </c>
-      <c r="F15" s="7"/>
-      <c r="G15" s="8" t="s">
+      <c r="F15" s="6"/>
+      <c r="G15" s="7" t="s">
         <v>373</v>
       </c>
-      <c r="H15" s="7"/>
-      <c r="I15" s="7" t="str">
+      <c r="H15" s="6"/>
+      <c r="I15" s="6" t="str">
         <f>VLOOKUP(I14,$B:$C,2,FALSE)</f>
         <v>302</v>
       </c>
-      <c r="J15" s="7" t="str">
+      <c r="J15" s="6" t="str">
         <f t="shared" ref="J15:L15" si="4">VLOOKUP(J14,$B:$C,2,FALSE)</f>
         <v>889</v>
       </c>
-      <c r="K15" s="7" t="str">
+      <c r="K15" s="6" t="str">
         <f t="shared" si="4"/>
         <v>695</v>
       </c>
-      <c r="L15" s="7" t="str">
+      <c r="L15" s="6" t="str">
         <f t="shared" si="4"/>
         <v>512</v>
       </c>
-      <c r="M15" s="7"/>
+      <c r="M15" s="6"/>
     </row>
     <row r="16" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B16" s="7" t="s">
+      <c r="B16" s="6" t="s">
         <v>361</v>
       </c>
-      <c r="C16" s="7" t="s">
+      <c r="C16" s="6" t="s">
         <v>374</v>
       </c>
-      <c r="G16" s="10" t="str">
+      <c r="G16" s="9" t="str">
         <f>G14&amp;","&amp;G15</f>
         <v>19,30, 22,0</v>
       </c>
-      <c r="H16" s="10"/>
-      <c r="I16" s="10" t="str">
+      <c r="H16" s="9"/>
+      <c r="I16" s="9" t="str">
         <f>I15</f>
         <v>302</v>
       </c>
-      <c r="J16" s="10" t="str">
+      <c r="J16" s="9" t="str">
         <f>I16&amp;","&amp;J15</f>
         <v>302,889</v>
       </c>
-      <c r="K16" s="10" t="str">
+      <c r="K16" s="9" t="str">
         <f>J16&amp;","&amp;K15</f>
         <v>302,889,695</v>
       </c>
-      <c r="L16" s="10" t="str">
+      <c r="L16" s="9" t="str">
         <f>K16&amp;","&amp;L15</f>
         <v>302,889,695,512</v>
       </c>
-      <c r="M16" s="10"/>
-      <c r="N16" s="10"/>
+      <c r="M16" s="9"/>
+      <c r="N16" s="9"/>
     </row>
     <row r="17" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B17" s="7" t="s">
+      <c r="B17" s="6" t="s">
         <v>361</v>
       </c>
-      <c r="C17" s="7" t="s">
+      <c r="C17" s="6" t="s">
         <v>375</v>
       </c>
-      <c r="G17" s="8" t="s">
+      <c r="G17" s="7" t="s">
         <v>376</v>
       </c>
-      <c r="I17" s="7" t="s">
+      <c r="I17" s="6" t="s">
         <v>355</v>
       </c>
-      <c r="J17" s="7" t="s">
+      <c r="J17" s="6" t="s">
         <v>356</v>
       </c>
-      <c r="K17" s="7" t="s">
+      <c r="K17" s="6" t="s">
         <v>357</v>
       </c>
-      <c r="L17" s="7" t="s">
+      <c r="L17" s="6" t="s">
         <v>347</v>
       </c>
     </row>
     <row r="18" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B18" s="7" t="s">
+      <c r="B18" s="6" t="s">
         <v>377</v>
       </c>
-      <c r="C18" s="7" t="s">
+      <c r="C18" s="6" t="s">
         <v>378</v>
       </c>
-      <c r="G18" s="8" t="s">
+      <c r="G18" s="7" t="s">
         <v>379</v>
       </c>
-      <c r="I18" s="7" t="str">
+      <c r="I18" s="6" t="str">
         <f>VLOOKUP(I17,$B:$C,2,FALSE)</f>
         <v>889</v>
       </c>
-      <c r="J18" s="7" t="str">
+      <c r="J18" s="6" t="str">
         <f t="shared" ref="J18:L18" si="5">VLOOKUP(J17,$B:$C,2,FALSE)</f>
         <v>695</v>
       </c>
-      <c r="K18" s="7" t="str">
+      <c r="K18" s="6" t="str">
         <f t="shared" si="5"/>
         <v>512</v>
       </c>
-      <c r="L18" s="7">
+      <c r="L18" s="6">
         <f t="shared" si="5"/>
         <v>2497</v>
       </c>
     </row>
     <row r="19" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B19" s="7" t="s">
+      <c r="B19" s="6" t="s">
         <v>380</v>
       </c>
-      <c r="C19" s="7" t="s">
+      <c r="C19" s="6" t="s">
         <v>381</v>
       </c>
-      <c r="G19" s="10" t="str">
+      <c r="G19" s="9" t="str">
         <f>G17&amp;","&amp;G18</f>
         <v>22,0,24,0</v>
       </c>
-      <c r="H19" s="10"/>
-      <c r="I19" s="10" t="str">
+      <c r="H19" s="9"/>
+      <c r="I19" s="9" t="str">
         <f>I18</f>
         <v>889</v>
       </c>
-      <c r="J19" s="10" t="str">
+      <c r="J19" s="9" t="str">
         <f>I19&amp;","&amp;J18</f>
         <v>889,695</v>
       </c>
-      <c r="K19" s="10" t="str">
+      <c r="K19" s="9" t="str">
         <f t="shared" ref="K19:L19" si="6">J19&amp;","&amp;K18</f>
         <v>889,695,512</v>
       </c>
-      <c r="L19" s="10" t="str">
+      <c r="L19" s="9" t="str">
         <f t="shared" si="6"/>
         <v>889,695,512,2497</v>
       </c>
-      <c r="M19" s="10"/>
-      <c r="N19" s="10"/>
+      <c r="M19" s="9"/>
+      <c r="N19" s="9"/>
     </row>
     <row r="20" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B20" s="7" t="s">
+      <c r="B20" s="6" t="s">
         <v>382</v>
       </c>
-      <c r="C20" s="7">
+      <c r="C20" s="6">
         <v>900</v>
       </c>
-      <c r="G20" s="8"/>
+      <c r="G20" s="7"/>
     </row>
     <row r="21" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B21" s="7" t="s">
+      <c r="B21" s="6" t="s">
         <v>383</v>
       </c>
-      <c r="C21" s="7" t="s">
+      <c r="C21" s="6" t="s">
         <v>384</v>
       </c>
     </row>
     <row r="22" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B22" s="7" t="s">
+      <c r="B22" s="6" t="s">
         <v>385</v>
       </c>
-      <c r="C22" s="7" t="s">
+      <c r="C22" s="6" t="s">
         <v>386</v>
       </c>
     </row>
     <row r="23" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B23" s="7" t="s">
+      <c r="B23" s="6" t="s">
         <v>387</v>
       </c>
-      <c r="C23" s="7" t="s">
+      <c r="C23" s="6" t="s">
         <v>388</v>
       </c>
-      <c r="G23" s="5" t="str">
+      <c r="G23" s="4" t="str">
         <f>G6&amp;","&amp;G9&amp;","&amp;G12&amp;","&amp;G16&amp;","&amp;G19</f>
         <v>6,0,9,0,9,0,17,30,17,30,19,30,19,30, 22,0,22,0,24,0</v>
       </c>
-      <c r="M23" s="7"/>
+      <c r="M23" s="6"/>
     </row>
     <row r="24" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B24" s="7" t="s">
+      <c r="B24" s="6" t="s">
         <v>346</v>
       </c>
-      <c r="C24" s="7" t="s">
+      <c r="C24" s="6" t="s">
         <v>389</v>
       </c>
     </row>
     <row r="25" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B25" s="7" t="s">
+      <c r="B25" s="6" t="s">
         <v>390</v>
       </c>
-      <c r="C25" s="7" t="s">
+      <c r="C25" s="6" t="s">
         <v>391</v>
       </c>
-      <c r="M25" s="7"/>
+      <c r="M25" s="6"/>
     </row>
     <row r="26" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B26" s="7" t="s">
+      <c r="B26" s="6" t="s">
         <v>392</v>
       </c>
-      <c r="C26" s="7" t="s">
+      <c r="C26" s="6" t="s">
         <v>393</v>
       </c>
-      <c r="M26" s="7"/>
+      <c r="M26" s="6"/>
     </row>
     <row r="27" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B27" s="7" t="s">
+      <c r="B27" s="6" t="s">
         <v>369</v>
       </c>
-      <c r="C27" s="7" t="s">
+      <c r="C27" s="6" t="s">
         <v>394</v>
       </c>
-      <c r="M27" s="7"/>
+      <c r="M27" s="6"/>
     </row>
     <row r="28" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B28" s="7" t="s">
+      <c r="B28" s="6" t="s">
         <v>395</v>
       </c>
-      <c r="C28" s="7">
+      <c r="C28" s="6">
         <v>1014</v>
       </c>
-      <c r="M28" s="7"/>
+      <c r="M28" s="6"/>
     </row>
     <row r="29" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B29" s="7" t="s">
+      <c r="B29" s="6" t="s">
         <v>369</v>
       </c>
-      <c r="C29" s="7" t="s">
+      <c r="C29" s="6" t="s">
         <v>396</v>
       </c>
-      <c r="M29" s="7"/>
+      <c r="M29" s="6"/>
     </row>
     <row r="30" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B30" s="7" t="s">
+      <c r="B30" s="6" t="s">
         <v>357</v>
       </c>
-      <c r="C30" s="7" t="s">
+      <c r="C30" s="6" t="s">
         <v>397</v>
       </c>
     </row>
     <row r="31" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B31" s="7" t="s">
+      <c r="B31" s="6" t="s">
         <v>369</v>
       </c>
-      <c r="C31" s="7" t="s">
+      <c r="C31" s="6" t="s">
         <v>398</v>
       </c>
-      <c r="M31" s="7" t="s">
+      <c r="M31" s="6" t="s">
         <v>355</v>
       </c>
     </row>
     <row r="32" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B32" s="7" t="s">
+      <c r="B32" s="6" t="s">
         <v>399</v>
       </c>
-      <c r="C32" s="7">
+      <c r="C32" s="6">
         <v>5309</v>
       </c>
-      <c r="M32" s="7" t="s">
+      <c r="M32" s="6" t="s">
         <v>356</v>
       </c>
     </row>
     <row r="33" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B33" s="7" t="s">
+      <c r="B33" s="6" t="s">
         <v>369</v>
       </c>
-      <c r="C33" s="7" t="s">
+      <c r="C33" s="6" t="s">
         <v>400</v>
       </c>
-      <c r="M33" s="7" t="s">
+      <c r="M33" s="6" t="s">
         <v>357</v>
       </c>
     </row>
     <row r="34" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B34" s="7" t="s">
+      <c r="B34" s="6" t="s">
         <v>355</v>
       </c>
-      <c r="C34" s="7" t="s">
+      <c r="C34" s="6" t="s">
         <v>401</v>
       </c>
     </row>
     <row r="35" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B35" s="7" t="s">
+      <c r="B35" s="6" t="s">
         <v>402</v>
       </c>
-      <c r="C35" s="7" t="s">
+      <c r="C35" s="6" t="s">
         <v>403</v>
       </c>
     </row>
     <row r="36" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B36" s="7" t="s">
+      <c r="B36" s="6" t="s">
         <v>404</v>
       </c>
-      <c r="C36" s="7" t="s">
+      <c r="C36" s="6" t="s">
         <v>405</v>
       </c>
     </row>
     <row r="37" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B37" s="7" t="s">
+      <c r="B37" s="6" t="s">
         <v>406</v>
       </c>
-      <c r="C37" s="7" t="s">
+      <c r="C37" s="6" t="s">
         <v>407</v>
       </c>
     </row>
     <row r="38" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B38" s="7" t="s">
+      <c r="B38" s="6" t="s">
         <v>408</v>
       </c>
-      <c r="C38" s="7">
+      <c r="C38" s="6">
         <v>3056</v>
       </c>
     </row>
     <row r="39" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B39" s="7" t="s">
+      <c r="B39" s="6" t="s">
         <v>409</v>
       </c>
-      <c r="C39" s="7" t="s">
+      <c r="C39" s="6" t="s">
         <v>410</v>
       </c>
     </row>
     <row r="40" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B40" s="7" t="s">
+      <c r="B40" s="6" t="s">
         <v>411</v>
       </c>
-      <c r="C40" s="7" t="s">
+      <c r="C40" s="6" t="s">
         <v>412</v>
       </c>
     </row>
     <row r="41" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B41" s="7" t="s">
+      <c r="B41" s="6" t="s">
         <v>347</v>
       </c>
-      <c r="C41" s="7">
+      <c r="C41" s="6">
         <v>2497</v>
       </c>
     </row>
     <row r="42" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B42" s="7" t="s">
+      <c r="B42" s="6" t="s">
         <v>413</v>
       </c>
-      <c r="C42" s="7" t="s">
+      <c r="C42" s="6" t="s">
         <v>414</v>
       </c>
     </row>
     <row r="43" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B43" s="7" t="s">
+      <c r="B43" s="6" t="s">
         <v>415</v>
       </c>
-      <c r="C43" s="7" t="s">
+      <c r="C43" s="6" t="s">
         <v>416</v>
       </c>
     </row>
     <row r="44" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B44" s="7" t="s">
+      <c r="B44" s="6" t="s">
         <v>369</v>
       </c>
-      <c r="C44" s="7" t="s">
+      <c r="C44" s="6" t="s">
         <v>417</v>
       </c>
     </row>
     <row r="45" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B45" s="7" t="s">
+      <c r="B45" s="6" t="s">
         <v>356</v>
       </c>
-      <c r="C45" s="7" t="s">
+      <c r="C45" s="6" t="s">
         <v>418</v>
       </c>
     </row>
     <row r="46" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B46" s="7" t="s">
+      <c r="B46" s="6" t="s">
         <v>419</v>
       </c>
-      <c r="C46" s="7" t="s">
+      <c r="C46" s="6" t="s">
         <v>420</v>
       </c>
     </row>
     <row r="47" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B47" s="7" t="s">
+      <c r="B47" s="6" t="s">
         <v>421</v>
       </c>
-      <c r="C47" s="7" t="s">
+      <c r="C47" s="6" t="s">
         <v>422</v>
       </c>
     </row>
     <row r="48" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B48" s="11" t="s">
-        <v>423</v>
-      </c>
-      <c r="C48" s="7" t="s">
+      <c r="B48" s="10" t="s">
+        <v>807</v>
+      </c>
+      <c r="C48" s="6" t="s">
         <v>424</v>
       </c>
     </row>
     <row r="49" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B49" s="7" t="s">
+      <c r="B49" s="6" t="s">
         <v>425</v>
       </c>
-      <c r="C49" s="7" t="s">
+      <c r="C49" s="6" t="s">
         <v>426</v>
       </c>
     </row>
     <row r="50" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B50" s="7" t="s">
+      <c r="B50" s="6" t="s">
         <v>427</v>
       </c>
-      <c r="C50" s="7" t="s">
+      <c r="C50" s="6" t="s">
         <v>428</v>
       </c>
     </row>
     <row r="51" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B51" s="7" t="s">
+      <c r="B51" s="6" t="s">
         <v>429</v>
       </c>
-      <c r="C51" s="7">
+      <c r="C51" s="6">
         <v>547</v>
       </c>
     </row>
     <row r="52" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B52" s="7" t="s">
+      <c r="B52" s="6" t="s">
         <v>354</v>
       </c>
-      <c r="C52" s="7" t="s">
+      <c r="C52" s="6" t="s">
         <v>82</v>
       </c>
     </row>
     <row r="53" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B53" s="7" t="s">
+      <c r="B53" s="6" t="s">
         <v>361</v>
       </c>
-      <c r="C53" s="7" t="s">
+      <c r="C53" s="6" t="s">
         <v>430</v>
       </c>
     </row>
     <row r="54" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B54" s="7" t="s">
+      <c r="B54" s="6" t="s">
         <v>361</v>
       </c>
-      <c r="C54" s="7" t="s">
+      <c r="C54" s="6" t="s">
         <v>431</v>
       </c>
     </row>
     <row r="55" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B55" s="7" t="s">
+      <c r="B55" s="6" t="s">
         <v>432</v>
       </c>
-      <c r="C55" s="7" t="s">
+      <c r="C55" s="6" t="s">
         <v>433</v>
       </c>
     </row>
     <row r="56" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B56" s="7" t="s">
+      <c r="B56" s="6" t="s">
         <v>361</v>
       </c>
-      <c r="C56" s="7" t="s">
+      <c r="C56" s="6" t="s">
         <v>434</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="0" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="1200" verticalDpi="1200"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="B1:C228"/>
+  <dimension ref="B1:C212"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="6" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="2" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B2" s="1" t="s">
-        <v>435</v>
-      </c>
-      <c r="C2" s="1" t="s">
+      <c r="B2" s="6">
+        <v>1001</v>
+      </c>
+      <c r="C2" s="6" t="s">
         <v>436</v>
       </c>
     </row>
     <row r="3" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B3" s="1" t="s">
-        <v>437</v>
-      </c>
-      <c r="C3" s="1" t="s">
+      <c r="B3" s="6">
+        <v>1002</v>
+      </c>
+      <c r="C3" s="6" t="s">
         <v>438</v>
       </c>
     </row>
     <row r="4" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B4" s="1" t="s">
-        <v>439</v>
-      </c>
-      <c r="C4" s="1" t="s">
+      <c r="B4" s="6">
+        <v>1003</v>
+      </c>
+      <c r="C4" s="6" t="s">
         <v>440</v>
       </c>
     </row>
     <row r="5" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B5" s="1" t="s">
-        <v>441</v>
-      </c>
-      <c r="C5" s="1" t="s">
+      <c r="B5" s="6">
+        <v>1004</v>
+      </c>
+      <c r="C5" s="6" t="s">
         <v>442</v>
       </c>
     </row>
     <row r="6" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B6" s="1" t="s">
-        <v>443</v>
-      </c>
-      <c r="C6" s="1" t="s">
+      <c r="B6" s="6">
+        <v>1005</v>
+      </c>
+      <c r="C6" s="6" t="s">
         <v>444</v>
       </c>
     </row>
     <row r="7" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B7" s="1" t="s">
-        <v>445</v>
-      </c>
-      <c r="C7" s="1" t="s">
+      <c r="B7" s="6">
+        <v>1006</v>
+      </c>
+      <c r="C7" s="6" t="s">
         <v>446</v>
       </c>
     </row>
     <row r="8" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B8" s="1" t="s">
-        <v>447</v>
-      </c>
-      <c r="C8" s="1" t="s">
+      <c r="B8" s="6">
+        <v>1007</v>
+      </c>
+      <c r="C8" s="6" t="s">
         <v>446</v>
       </c>
     </row>
     <row r="9" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B9" s="1" t="s">
-        <v>448</v>
-      </c>
-      <c r="C9" s="1" t="s">
+      <c r="B9" s="6">
+        <v>1008</v>
+      </c>
+      <c r="C9" s="6" t="s">
         <v>446</v>
       </c>
     </row>
     <row r="10" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B10" s="1" t="s">
+      <c r="B10" s="6">
+        <v>1009</v>
+      </c>
+      <c r="C10" s="6" t="s">
         <v>449</v>
       </c>
-      <c r="C10" s="1" t="s">
-        <v>450</v>
-      </c>
     </row>
     <row r="11" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B11" s="1" t="s">
+      <c r="B11" s="6">
+        <v>1010</v>
+      </c>
+      <c r="C11" s="6" t="s">
         <v>451</v>
       </c>
-      <c r="C11" s="1" t="s">
-        <v>452</v>
-      </c>
     </row>
     <row r="12" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B12" s="1" t="s">
+      <c r="B12" s="6">
+        <v>1011</v>
+      </c>
+      <c r="C12" s="6" t="s">
         <v>453</v>
       </c>
-      <c r="C12" s="1" t="s">
+    </row>
+    <row r="13" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B13" s="6">
+        <v>1012</v>
+      </c>
+      <c r="C13" s="6" t="s">
         <v>454</v>
       </c>
     </row>
-    <row r="13" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B13" s="1" t="s">
-        <v>455</v>
-      </c>
-      <c r="C13" s="1" t="s">
+    <row r="14" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B14" s="6">
+        <v>1013</v>
+      </c>
+      <c r="C14" s="6" t="s">
         <v>456</v>
       </c>
     </row>
-    <row r="14" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B14" s="1" t="s">
-        <v>457</v>
-      </c>
-      <c r="C14" s="1" t="s">
+    <row r="15" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B15" s="6">
+        <v>1014</v>
+      </c>
+      <c r="C15" s="6" t="s">
         <v>458</v>
       </c>
     </row>
-    <row r="15" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B15" s="1" t="s">
-        <v>459</v>
-      </c>
-      <c r="C15" s="1" t="s">
+    <row r="16" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B16" s="6">
+        <v>1015</v>
+      </c>
+      <c r="C16" s="6" t="s">
         <v>460</v>
       </c>
     </row>
-    <row r="16" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B16" s="1" t="s">
-        <v>461</v>
-      </c>
-      <c r="C16" s="1" t="s">
+    <row r="17" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B17" s="6">
+        <v>1016</v>
+      </c>
+      <c r="C17" s="6" t="s">
         <v>462</v>
       </c>
     </row>
-    <row r="17" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B17" s="1" t="s">
-        <v>463</v>
-      </c>
-      <c r="C17" s="1" t="s">
+    <row r="18" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B18" s="6">
+        <v>1017</v>
+      </c>
+      <c r="C18" s="6" t="s">
         <v>464</v>
       </c>
     </row>
-    <row r="18" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B18" s="1" t="s">
-        <v>465</v>
-      </c>
-      <c r="C18" s="1" t="s">
+    <row r="19" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B19" s="6">
+        <v>1018</v>
+      </c>
+      <c r="C19" s="6" t="s">
         <v>466</v>
       </c>
     </row>
-    <row r="19" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B19" s="1" t="s">
+    <row r="20" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B20" s="6">
+        <v>1019</v>
+      </c>
+      <c r="C20" s="6" t="s">
         <v>467</v>
       </c>
-      <c r="C19" s="1" t="s">
-        <v>466</v>
-      </c>
-    </row>
-    <row r="20" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B20" s="1" t="s">
-        <v>468</v>
-      </c>
-      <c r="C20" s="1" t="s">
-        <v>466</v>
-      </c>
     </row>
     <row r="21" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B21" s="1" t="s">
+      <c r="B21" s="6">
+        <v>1020</v>
+      </c>
+      <c r="C21" s="6" t="s">
         <v>469</v>
       </c>
-      <c r="C21" s="1" t="s">
-        <v>470</v>
-      </c>
     </row>
     <row r="22" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B22" s="1" t="s">
+      <c r="B22" s="6">
+        <v>1021</v>
+      </c>
+      <c r="C22" s="6" t="s">
         <v>471</v>
       </c>
-      <c r="C22" s="1" t="s">
-        <v>472</v>
-      </c>
     </row>
     <row r="23" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B23" s="1" t="s">
+      <c r="B23" s="6">
+        <v>1022</v>
+      </c>
+      <c r="C23" s="6" t="s">
         <v>473</v>
       </c>
-      <c r="C23" s="1" t="s">
-        <v>474</v>
-      </c>
     </row>
     <row r="24" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B24" s="1" t="s">
+      <c r="B24" s="6">
+        <v>1023</v>
+      </c>
+      <c r="C24" s="6" t="s">
         <v>475</v>
       </c>
-      <c r="C24" s="1" t="s">
-        <v>476</v>
-      </c>
     </row>
     <row r="25" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B25" s="1" t="s">
+      <c r="B25" s="6">
+        <v>1024</v>
+      </c>
+      <c r="C25" s="6" t="s">
         <v>477</v>
       </c>
-      <c r="C25" s="1" t="s">
+    </row>
+    <row r="26" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B26" s="6">
+        <v>1025</v>
+      </c>
+      <c r="C26" s="6" t="s">
         <v>478</v>
       </c>
     </row>
-    <row r="26" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B26" s="1" t="s">
+    <row r="27" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B27" s="6">
+        <v>1027</v>
+      </c>
+      <c r="C27" s="6" t="s">
         <v>479</v>
       </c>
-      <c r="C26" s="1" t="s">
+    </row>
+    <row r="28" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B28" s="6">
+        <v>1028</v>
+      </c>
+      <c r="C28" s="6" t="s">
         <v>480</v>
       </c>
     </row>
-    <row r="27" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B27" s="1" t="s">
+    <row r="29" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B29" s="6">
+        <v>1029</v>
+      </c>
+      <c r="C29" s="6" t="s">
         <v>481</v>
       </c>
-      <c r="C27" s="1" t="s">
-        <v>442</v>
-      </c>
-    </row>
-    <row r="28" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B28" s="1" t="s">
+    </row>
+    <row r="30" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B30" s="6">
+        <v>1030</v>
+      </c>
+      <c r="C30" s="6" t="s">
         <v>482</v>
       </c>
-      <c r="C28" s="1" t="s">
+    </row>
+    <row r="31" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B31" s="6">
+        <v>1031</v>
+      </c>
+      <c r="C31" s="6" t="s">
         <v>483</v>
       </c>
     </row>
-    <row r="29" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B29" s="1" t="s">
+    <row r="32" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B32" s="6">
+        <v>1032</v>
+      </c>
+      <c r="C32" s="6" t="s">
         <v>484</v>
       </c>
-      <c r="C29" s="1" t="s">
+    </row>
+    <row r="33" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B33" s="6">
+        <v>1033</v>
+      </c>
+      <c r="C33" s="6" t="s">
         <v>485</v>
       </c>
     </row>
-    <row r="30" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B30" s="1" t="s">
+    <row r="34" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B34" s="6">
+        <v>1034</v>
+      </c>
+      <c r="C34" s="6" t="s">
         <v>486</v>
       </c>
-      <c r="C30" s="1" t="s">
+    </row>
+    <row r="35" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B35" s="6">
+        <v>1035</v>
+      </c>
+      <c r="C35" s="6" t="s">
         <v>487</v>
       </c>
     </row>
-    <row r="31" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B31" s="1" t="s">
+    <row r="36" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B36" s="6">
+        <v>1036</v>
+      </c>
+      <c r="C36" s="6" t="s">
         <v>488</v>
       </c>
-      <c r="C31" s="1" t="s">
+    </row>
+    <row r="37" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B37" s="6">
+        <v>1037</v>
+      </c>
+      <c r="C37" s="6" t="s">
         <v>489</v>
       </c>
     </row>
-    <row r="32" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B32" s="1" t="s">
+    <row r="38" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B38" s="6">
+        <v>1038</v>
+      </c>
+      <c r="C38" s="6" t="s">
         <v>490</v>
       </c>
-      <c r="C32" s="1" t="s">
+    </row>
+    <row r="39" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B39" s="6">
+        <v>1039</v>
+      </c>
+      <c r="C39" s="6" t="s">
         <v>491</v>
       </c>
     </row>
-    <row r="33" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B33" s="1" t="s">
+    <row r="40" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B40" s="6">
+        <v>1040</v>
+      </c>
+      <c r="C40" s="6" t="s">
         <v>492</v>
       </c>
-      <c r="C33" s="1" t="s">
+    </row>
+    <row r="41" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B41" s="6">
+        <v>1041</v>
+      </c>
+      <c r="C41" s="6" t="s">
         <v>493</v>
       </c>
     </row>
-    <row r="34" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B34" s="1" t="s">
+    <row r="42" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B42" s="6">
+        <v>1042</v>
+      </c>
+      <c r="C42" s="6" t="s">
         <v>494</v>
       </c>
-      <c r="C34" s="1" t="s">
+    </row>
+    <row r="43" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B43" s="6">
+        <v>1043</v>
+      </c>
+      <c r="C43" s="6" t="s">
         <v>495</v>
       </c>
     </row>
-    <row r="35" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B35" s="1" t="s">
+    <row r="44" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B44" s="6">
+        <v>1044</v>
+      </c>
+      <c r="C44" s="6" t="s">
         <v>496</v>
       </c>
-      <c r="C35" s="1" t="s">
+    </row>
+    <row r="45" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B45" s="6">
+        <v>1045</v>
+      </c>
+      <c r="C45" s="6" t="s">
         <v>497</v>
       </c>
     </row>
-    <row r="36" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B36" s="1" t="s">
+    <row r="46" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B46" s="6">
+        <v>1046</v>
+      </c>
+      <c r="C46" s="6" t="s">
         <v>498</v>
       </c>
-      <c r="C36" s="1" t="s">
+    </row>
+    <row r="47" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B47" s="6">
+        <v>1047</v>
+      </c>
+      <c r="C47" s="6" t="s">
         <v>499</v>
       </c>
     </row>
-    <row r="37" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B37" s="1" t="s">
+    <row r="48" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B48" s="6">
+        <v>1048</v>
+      </c>
+      <c r="C48" s="6" t="s">
         <v>500</v>
       </c>
-      <c r="C37" s="1" t="s">
+    </row>
+    <row r="49" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B49" s="6">
+        <v>1049</v>
+      </c>
+      <c r="C49" s="6" t="s">
         <v>501</v>
       </c>
     </row>
-    <row r="38" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B38" s="1" t="s">
+    <row r="50" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B50" s="6">
+        <v>1050</v>
+      </c>
+      <c r="C50" s="6" t="s">
         <v>502</v>
       </c>
-      <c r="C38" s="1" t="s">
+    </row>
+    <row r="51" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B51" s="6">
+        <v>1051</v>
+      </c>
+      <c r="C51" s="6" t="s">
         <v>503</v>
       </c>
     </row>
-    <row r="39" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B39" s="1" t="s">
+    <row r="52" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B52" s="6">
+        <v>1052</v>
+      </c>
+      <c r="C52" s="6" t="s">
         <v>504</v>
       </c>
-      <c r="C39" s="1" t="s">
+    </row>
+    <row r="53" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B53" s="6">
+        <v>1053</v>
+      </c>
+      <c r="C53" s="6" t="s">
         <v>505</v>
       </c>
     </row>
-    <row r="40" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B40" s="1" t="s">
+    <row r="54" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B54" s="6">
+        <v>1054</v>
+      </c>
+      <c r="C54" s="6" t="s">
         <v>506</v>
       </c>
-      <c r="C40" s="1" t="s">
+    </row>
+    <row r="55" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B55" s="6">
+        <v>1055</v>
+      </c>
+      <c r="C55" s="6" t="s">
         <v>507</v>
       </c>
     </row>
-    <row r="41" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B41" s="1" t="s">
+    <row r="56" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B56" s="6">
+        <v>1056</v>
+      </c>
+      <c r="C56" s="6" t="s">
         <v>508</v>
       </c>
-      <c r="C41" s="1" t="s">
+    </row>
+    <row r="57" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B57" s="6">
+        <v>1057</v>
+      </c>
+      <c r="C57" s="6" t="s">
         <v>509</v>
       </c>
     </row>
-    <row r="42" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B42" s="1" t="s">
+    <row r="58" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B58" s="6">
+        <v>1058</v>
+      </c>
+      <c r="C58" s="6" t="s">
         <v>510</v>
       </c>
-      <c r="C42" s="1" t="s">
-        <v>436</v>
-      </c>
-    </row>
-    <row r="43" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B43" s="1" t="s">
+    </row>
+    <row r="59" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B59" s="6">
+        <v>1059</v>
+      </c>
+      <c r="C59" s="6" t="s">
         <v>511</v>
       </c>
-      <c r="C43" s="1" t="s">
+    </row>
+    <row r="60" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B60" s="6">
+        <v>1060</v>
+      </c>
+      <c r="C60" s="6" t="s">
         <v>512</v>
       </c>
     </row>
-    <row r="44" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B44" s="1" t="s">
+    <row r="61" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B61" s="6">
+        <v>1061</v>
+      </c>
+      <c r="C61" s="6" t="s">
         <v>513</v>
       </c>
-      <c r="C44" s="1" t="s">
+    </row>
+    <row r="62" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B62" s="6">
+        <v>1062</v>
+      </c>
+      <c r="C62" s="6" t="s">
         <v>514</v>
       </c>
     </row>
-    <row r="45" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B45" s="1" t="s">
+    <row r="63" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B63" s="6">
+        <v>1063</v>
+      </c>
+      <c r="C63" s="6" t="s">
         <v>515</v>
       </c>
-      <c r="C45" s="1" t="s">
+    </row>
+    <row r="64" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B64" s="6">
+        <v>1064</v>
+      </c>
+      <c r="C64" s="6" t="s">
         <v>516</v>
       </c>
     </row>
-    <row r="46" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B46" s="1" t="s">
+    <row r="65" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B65" s="6">
+        <v>1065</v>
+      </c>
+      <c r="C65" s="6" t="s">
         <v>517</v>
       </c>
-      <c r="C46" s="1" t="s">
+    </row>
+    <row r="66" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B66" s="6">
+        <v>1066</v>
+      </c>
+      <c r="C66" s="6" t="s">
         <v>518</v>
       </c>
     </row>
-    <row r="47" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B47" s="1" t="s">
+    <row r="67" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B67" s="6">
+        <v>1067</v>
+      </c>
+      <c r="C67" s="6" t="s">
         <v>519</v>
       </c>
-      <c r="C47" s="1" t="s">
+    </row>
+    <row r="68" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B68" s="6">
+        <v>1068</v>
+      </c>
+      <c r="C68" s="6" t="s">
         <v>520</v>
       </c>
     </row>
-    <row r="48" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B48" s="1" t="s">
+    <row r="69" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B69" s="6">
+        <v>1069</v>
+      </c>
+      <c r="C69" s="6" t="s">
         <v>521</v>
       </c>
-      <c r="C48" s="1" t="s">
+    </row>
+    <row r="70" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B70" s="6">
+        <v>1070</v>
+      </c>
+      <c r="C70" s="6" t="s">
         <v>522</v>
       </c>
     </row>
-    <row r="49" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B49" s="1" t="s">
+    <row r="71" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B71" s="6">
+        <v>1071</v>
+      </c>
+      <c r="C71" s="6" t="s">
         <v>523</v>
       </c>
-      <c r="C49" s="1" t="s">
+    </row>
+    <row r="72" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B72" s="6">
+        <v>1072</v>
+      </c>
+      <c r="C72" s="6" t="s">
         <v>524</v>
       </c>
     </row>
-    <row r="50" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B50" s="1" t="s">
+    <row r="73" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B73" s="6">
+        <v>1073</v>
+      </c>
+      <c r="C73" s="6" t="s">
         <v>525</v>
       </c>
-      <c r="C50" s="1" t="s">
+    </row>
+    <row r="74" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B74" s="6">
+        <v>1074</v>
+      </c>
+      <c r="C74" s="6" t="s">
         <v>526</v>
       </c>
     </row>
-    <row r="51" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B51" s="1" t="s">
+    <row r="75" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B75" s="6">
+        <v>1075</v>
+      </c>
+      <c r="C75" s="6" t="s">
         <v>527</v>
       </c>
-      <c r="C51" s="1" t="s">
+    </row>
+    <row r="76" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B76" s="6">
+        <v>1076</v>
+      </c>
+      <c r="C76" s="6" t="s">
         <v>528</v>
       </c>
     </row>
-    <row r="52" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B52" s="1" t="s">
+    <row r="77" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B77" s="6">
+        <v>1077</v>
+      </c>
+      <c r="C77" s="6" t="s">
         <v>529</v>
       </c>
-      <c r="C52" s="1" t="s">
+    </row>
+    <row r="78" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B78" s="6">
+        <v>1078</v>
+      </c>
+      <c r="C78" s="6" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="79" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B79" s="6">
+        <v>1079</v>
+      </c>
+      <c r="C79" s="6" t="s">
         <v>530</v>
       </c>
     </row>
-    <row r="53" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B53" s="1" t="s">
+    <row r="80" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B80" s="6">
+        <v>1080</v>
+      </c>
+      <c r="C80" s="6" t="s">
         <v>531</v>
       </c>
-      <c r="C53" s="1" t="s">
+    </row>
+    <row r="81" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B81" s="6">
+        <v>1081</v>
+      </c>
+      <c r="C81" s="6" t="s">
         <v>532</v>
       </c>
     </row>
-    <row r="54" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B54" s="1" t="s">
+    <row r="82" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B82" s="6">
+        <v>1082</v>
+      </c>
+      <c r="C82" s="6" t="s">
         <v>533</v>
       </c>
-      <c r="C54" s="1" t="s">
+    </row>
+    <row r="83" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B83" s="6">
+        <v>1083</v>
+      </c>
+      <c r="C83" s="6" t="s">
         <v>534</v>
       </c>
     </row>
-    <row r="55" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B55" s="1" t="s">
+    <row r="84" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B84" s="6">
+        <v>1084</v>
+      </c>
+      <c r="C84" s="6" t="s">
         <v>535</v>
       </c>
-      <c r="C55" s="1" t="s">
+    </row>
+    <row r="85" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B85" s="6">
+        <v>1085</v>
+      </c>
+      <c r="C85" s="6" t="s">
         <v>536</v>
       </c>
     </row>
-    <row r="56" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B56" s="1" t="s">
+    <row r="86" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B86" s="6">
+        <v>1086</v>
+      </c>
+      <c r="C86" s="6" t="s">
         <v>537</v>
       </c>
-      <c r="C56" s="1" t="s">
+    </row>
+    <row r="87" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B87" s="6">
+        <v>1087</v>
+      </c>
+      <c r="C87" s="6" t="s">
         <v>538</v>
       </c>
     </row>
-    <row r="57" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B57" s="1" t="s">
+    <row r="88" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B88" s="6">
+        <v>1088</v>
+      </c>
+      <c r="C88" s="6" t="s">
         <v>539</v>
       </c>
-      <c r="C57" s="1" t="s">
+    </row>
+    <row r="89" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B89" s="6">
+        <v>1089</v>
+      </c>
+      <c r="C89" s="6" t="s">
         <v>540</v>
       </c>
     </row>
-    <row r="58" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B58" s="1" t="s">
+    <row r="90" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B90" s="6">
+        <v>1090</v>
+      </c>
+      <c r="C90" s="6" t="s">
         <v>541</v>
       </c>
-      <c r="C58" s="1" t="s">
+    </row>
+    <row r="91" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B91" s="6">
+        <v>1091</v>
+      </c>
+      <c r="C91" s="6" t="s">
         <v>542</v>
       </c>
     </row>
-    <row r="59" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B59" s="1" t="s">
+    <row r="92" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B92" s="6">
+        <v>1092</v>
+      </c>
+      <c r="C92" s="6" t="s">
         <v>543</v>
       </c>
-      <c r="C59" s="1" t="s">
+    </row>
+    <row r="93" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B93" s="6">
+        <v>1093</v>
+      </c>
+      <c r="C93" s="6" t="s">
         <v>544</v>
       </c>
     </row>
-    <row r="60" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B60" s="1" t="s">
+    <row r="94" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B94" s="6">
+        <v>1094</v>
+      </c>
+      <c r="C94" s="6" t="s">
         <v>545</v>
       </c>
-      <c r="C60" s="1" t="s">
+    </row>
+    <row r="95" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B95" s="6">
+        <v>1095</v>
+      </c>
+      <c r="C95" s="6" t="s">
         <v>546</v>
       </c>
     </row>
-    <row r="61" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B61" s="1" t="s">
+    <row r="96" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B96" s="6">
+        <v>1096</v>
+      </c>
+      <c r="C96" s="6" t="s">
         <v>547</v>
       </c>
-      <c r="C61" s="1" t="s">
+    </row>
+    <row r="97" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B97" s="6">
+        <v>1097</v>
+      </c>
+      <c r="C97" s="6" t="s">
         <v>548</v>
       </c>
     </row>
-    <row r="62" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B62" s="1" t="s">
+    <row r="98" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B98" s="6">
+        <v>1098</v>
+      </c>
+      <c r="C98" s="6" t="s">
         <v>549</v>
       </c>
-      <c r="C62" s="1" t="s">
+    </row>
+    <row r="99" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B99" s="6">
+        <v>1099</v>
+      </c>
+      <c r="C99" s="6" t="s">
         <v>550</v>
       </c>
     </row>
-    <row r="63" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B63" s="1" t="s">
-        <v>551</v>
-      </c>
-      <c r="C63" s="1" t="s">
+    <row r="100" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B100" s="6">
+        <v>1100</v>
+      </c>
+      <c r="C100" s="6" t="s">
         <v>552</v>
       </c>
     </row>
-    <row r="64" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B64" s="1" t="s">
-        <v>553</v>
-      </c>
-      <c r="C64" s="1" t="s">
-        <v>526</v>
-      </c>
-    </row>
-    <row r="65" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B65" s="1" t="s">
+    <row r="101" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B101" s="6">
+        <v>1101</v>
+      </c>
+      <c r="C101" s="6" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="102" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B102" s="6">
+        <v>1102</v>
+      </c>
+      <c r="C102" s="6" t="s">
         <v>554</v>
       </c>
-      <c r="C65" s="1" t="s">
-        <v>555</v>
-      </c>
-    </row>
-    <row r="66" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B66" s="1" t="s">
+    </row>
+    <row r="103" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B103" s="6">
+        <v>1103</v>
+      </c>
+      <c r="C103" s="6" t="s">
         <v>556</v>
       </c>
-      <c r="C66" s="1" t="s">
+    </row>
+    <row r="104" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B104" s="6">
+        <v>1104</v>
+      </c>
+      <c r="C104" s="6" t="s">
         <v>557</v>
       </c>
     </row>
-    <row r="67" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B67" s="1" t="s">
-        <v>558</v>
-      </c>
-      <c r="C67" s="1" t="s">
-        <v>559</v>
-      </c>
-    </row>
-    <row r="68" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B68" s="1" t="s">
+    <row r="105" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B105" s="6">
+        <v>1105</v>
+      </c>
+      <c r="C105" s="6" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="106" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B106" s="6">
+        <v>1106</v>
+      </c>
+      <c r="C106" s="6" t="s">
         <v>560</v>
       </c>
-      <c r="C68" s="1" t="s">
-        <v>466</v>
-      </c>
-    </row>
-    <row r="69" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B69" s="1" t="s">
+    </row>
+    <row r="107" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B107" s="6">
+        <v>1107</v>
+      </c>
+      <c r="C107" s="6" t="s">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="108" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B108" s="6">
+        <v>1108</v>
+      </c>
+      <c r="C108" s="6" t="s">
         <v>561</v>
       </c>
-      <c r="C69" s="1" t="s">
-        <v>562</v>
-      </c>
-    </row>
-    <row r="70" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B70" s="1" t="s">
+    </row>
+    <row r="109" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B109" s="6">
+        <v>1109</v>
+      </c>
+      <c r="C109" s="6" t="s">
         <v>563</v>
       </c>
-      <c r="C70" s="1" t="s">
-        <v>436</v>
-      </c>
-    </row>
-    <row r="71" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B71" s="1" t="s">
-        <v>564</v>
-      </c>
-      <c r="C71" s="1" t="s">
-        <v>436</v>
-      </c>
-    </row>
-    <row r="72" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B72" s="1" t="s">
+    </row>
+    <row r="110" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B110" s="6">
+        <v>1110</v>
+      </c>
+      <c r="C110" s="6" t="s">
         <v>565</v>
       </c>
-      <c r="C72" s="1" t="s">
-        <v>566</v>
-      </c>
-    </row>
-    <row r="73" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B73" s="1" t="s">
+    </row>
+    <row r="111" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B111" s="6">
+        <v>1111</v>
+      </c>
+      <c r="C111" s="6" t="s">
         <v>567</v>
       </c>
-      <c r="C73" s="1" t="s">
+    </row>
+    <row r="112" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B112" s="6">
+        <v>1112</v>
+      </c>
+      <c r="C112" s="6" t="s">
         <v>568</v>
       </c>
     </row>
-    <row r="74" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B74" s="1" t="s">
-        <v>569</v>
-      </c>
-      <c r="C74" s="1" t="s">
+    <row r="113" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B113" s="6">
+        <v>1113</v>
+      </c>
+      <c r="C113" s="6" t="s">
         <v>570</v>
       </c>
     </row>
-    <row r="75" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B75" s="1" t="s">
-        <v>571</v>
-      </c>
-      <c r="C75" s="1" t="s">
+    <row r="114" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B114" s="6">
+        <v>1114</v>
+      </c>
+      <c r="C114" s="6" t="s">
         <v>572</v>
       </c>
     </row>
-    <row r="76" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B76" s="1" t="s">
-        <v>573</v>
-      </c>
-      <c r="C76" s="1" t="s">
-        <v>574</v>
-      </c>
-    </row>
-    <row r="77" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B77" s="1" t="s">
+    <row r="115" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B115" s="6">
+        <v>1115</v>
+      </c>
+      <c r="C115" s="6" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="116" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B116" s="6">
+        <v>1116</v>
+      </c>
+      <c r="C116" s="6" t="s">
         <v>575</v>
       </c>
-      <c r="C77" s="1" t="s">
-        <v>576</v>
-      </c>
-    </row>
-    <row r="78" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B78" s="1" t="s">
+    </row>
+    <row r="117" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B117" s="6">
+        <v>1117</v>
+      </c>
+      <c r="C117" s="6" t="s">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="118" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B118" s="6">
+        <v>1118</v>
+      </c>
+      <c r="C118" s="6" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="119" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B119" s="6">
+        <v>1119</v>
+      </c>
+      <c r="C119" s="6" t="s">
         <v>577</v>
       </c>
-      <c r="C78" s="1" t="s">
-        <v>392</v>
-      </c>
-    </row>
-    <row r="79" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B79" s="1" t="s">
+    </row>
+    <row r="120" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B120" s="6">
+        <v>1120</v>
+      </c>
+      <c r="C120" s="6" t="s">
         <v>578</v>
       </c>
-      <c r="C79" s="1" t="s">
-        <v>466</v>
-      </c>
-    </row>
-    <row r="80" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B80" s="1" t="s">
+    </row>
+    <row r="121" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B121" s="6">
+        <v>1121</v>
+      </c>
+      <c r="C121" s="6" t="s">
         <v>579</v>
       </c>
-      <c r="C80" s="1" t="s">
-        <v>436</v>
-      </c>
-    </row>
-    <row r="81" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B81" s="1" t="s">
+    </row>
+    <row r="122" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B122" s="6">
+        <v>1122</v>
+      </c>
+      <c r="C122" s="6" t="s">
         <v>580</v>
       </c>
-      <c r="C81" s="1" t="s">
+    </row>
+    <row r="123" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B123" s="6">
+        <v>1123</v>
+      </c>
+      <c r="C123" s="6" t="s">
         <v>581</v>
       </c>
     </row>
-    <row r="82" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B82" s="1" t="s">
+    <row r="124" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B124" s="6">
+        <v>1124</v>
+      </c>
+      <c r="C124" s="6" t="s">
         <v>582</v>
       </c>
-      <c r="C82" s="1" t="s">
+    </row>
+    <row r="125" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B125" s="6">
+        <v>1125</v>
+      </c>
+      <c r="C125" s="6" t="s">
         <v>583</v>
       </c>
     </row>
-    <row r="83" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B83" s="1" t="s">
+    <row r="126" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B126" s="6">
+        <v>1126</v>
+      </c>
+      <c r="C126" s="6" t="s">
         <v>584</v>
       </c>
-      <c r="C83" s="1" t="s">
+    </row>
+    <row r="127" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B127" s="6">
+        <v>1127</v>
+      </c>
+      <c r="C127" s="6" t="s">
         <v>585</v>
       </c>
     </row>
-    <row r="84" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B84" s="1" t="s">
+    <row r="128" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B128" s="6">
+        <v>1128</v>
+      </c>
+      <c r="C128" s="6" t="s">
         <v>586</v>
       </c>
-      <c r="C84" s="1" t="s">
+    </row>
+    <row r="129" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B129" s="6">
+        <v>1129</v>
+      </c>
+      <c r="C129" s="6" t="s">
         <v>587</v>
       </c>
     </row>
-    <row r="85" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B85" s="1" t="s">
+    <row r="130" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B130" s="6">
+        <v>1130</v>
+      </c>
+      <c r="C130" s="6" t="s">
         <v>588</v>
       </c>
-      <c r="C85" s="1" t="s">
+    </row>
+    <row r="131" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B131" s="6">
+        <v>1131</v>
+      </c>
+      <c r="C131" s="6" t="s">
         <v>589</v>
       </c>
     </row>
-    <row r="86" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B86" s="1" t="s">
+    <row r="132" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B132" s="6">
+        <v>1134</v>
+      </c>
+      <c r="C132" s="6" t="s">
         <v>590</v>
       </c>
-      <c r="C86" s="1" t="s">
+    </row>
+    <row r="133" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B133" s="6">
+        <v>1135</v>
+      </c>
+      <c r="C133" s="6" t="s">
         <v>591</v>
       </c>
     </row>
-    <row r="87" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B87" s="1" t="s">
+    <row r="134" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B134" s="6">
+        <v>1136</v>
+      </c>
+      <c r="C134" s="6" t="s">
         <v>592</v>
       </c>
-      <c r="C87" s="1" t="s">
+    </row>
+    <row r="135" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B135" s="6">
+        <v>1137</v>
+      </c>
+      <c r="C135" s="6" t="s">
         <v>593</v>
       </c>
     </row>
-    <row r="88" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B88" s="1" t="s">
+    <row r="136" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B136" s="6">
+        <v>1138</v>
+      </c>
+      <c r="C136" s="6" t="s">
         <v>594</v>
       </c>
-      <c r="C88" s="1" t="s">
-        <v>466</v>
-      </c>
-    </row>
-    <row r="89" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B89" s="1" t="s">
+    </row>
+    <row r="137" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B137" s="6">
+        <v>1139</v>
+      </c>
+      <c r="C137" s="6" t="s">
         <v>595</v>
       </c>
-      <c r="C89" s="1" t="s">
+    </row>
+    <row r="138" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B138" s="6">
+        <v>1140</v>
+      </c>
+      <c r="C138" s="6" t="s">
         <v>596</v>
       </c>
     </row>
-    <row r="90" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B90" s="1" t="s">
+    <row r="139" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B139" s="6">
+        <v>1141</v>
+      </c>
+      <c r="C139" s="6" t="s">
         <v>597</v>
       </c>
-      <c r="C90" s="1" t="s">
+    </row>
+    <row r="140" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B140" s="6">
+        <v>1142</v>
+      </c>
+      <c r="C140" s="6" t="s">
         <v>598</v>
       </c>
     </row>
-    <row r="91" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B91" s="1" t="s">
+    <row r="141" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B141" s="6">
+        <v>1143</v>
+      </c>
+      <c r="C141" s="6" t="s">
         <v>599</v>
       </c>
-      <c r="C91" s="1" t="s">
+    </row>
+    <row r="142" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B142" s="6">
+        <v>1144</v>
+      </c>
+      <c r="C142" s="6" t="s">
         <v>600</v>
       </c>
     </row>
-    <row r="92" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B92" s="1" t="s">
+    <row r="143" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B143" s="6">
+        <v>1145</v>
+      </c>
+      <c r="C143" s="6" t="s">
         <v>601</v>
       </c>
-      <c r="C92" s="1" t="s">
+    </row>
+    <row r="144" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B144" s="6">
+        <v>1146</v>
+      </c>
+      <c r="C144" s="6" t="s">
         <v>602</v>
       </c>
     </row>
-    <row r="93" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B93" s="1" t="s">
+    <row r="145" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B145" s="6">
+        <v>1147</v>
+      </c>
+      <c r="C145" s="6" t="s">
         <v>603</v>
       </c>
-      <c r="C93" s="1" t="s">
+    </row>
+    <row r="146" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B146" s="6">
+        <v>1148</v>
+      </c>
+      <c r="C146" s="6" t="s">
         <v>604</v>
       </c>
     </row>
-    <row r="94" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B94" s="1" t="s">
+    <row r="147" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B147" s="6">
+        <v>1149</v>
+      </c>
+      <c r="C147" s="6" t="s">
         <v>605</v>
       </c>
-      <c r="C94" s="1" t="s">
+    </row>
+    <row r="148" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B148" s="6">
+        <v>1150</v>
+      </c>
+      <c r="C148" s="6" t="s">
         <v>606</v>
       </c>
     </row>
-    <row r="95" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B95" s="1" t="s">
+    <row r="149" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B149" s="6">
+        <v>1151</v>
+      </c>
+      <c r="C149" s="6" t="s">
         <v>607</v>
       </c>
-      <c r="C95" s="1" t="s">
+    </row>
+    <row r="150" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B150" s="6">
+        <v>1152</v>
+      </c>
+      <c r="C150" s="6" t="s">
         <v>608</v>
       </c>
     </row>
-    <row r="96" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B96" s="1" t="s">
+    <row r="151" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B151" s="6">
+        <v>1153</v>
+      </c>
+      <c r="C151" s="6" t="s">
         <v>609</v>
       </c>
-      <c r="C96" s="1" t="s">
+    </row>
+    <row r="152" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B152" s="6">
+        <v>1154</v>
+      </c>
+      <c r="C152" s="6" t="s">
         <v>610</v>
       </c>
     </row>
-    <row r="97" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B97" s="1" t="s">
+    <row r="153" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B153" s="6">
+        <v>1155</v>
+      </c>
+      <c r="C153" s="6" t="s">
         <v>611</v>
       </c>
-      <c r="C97" s="1" t="s">
+    </row>
+    <row r="154" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B154" s="6">
+        <v>1156</v>
+      </c>
+      <c r="C154" s="6" t="s">
         <v>612</v>
       </c>
     </row>
-    <row r="98" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B98" s="1" t="s">
+    <row r="155" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B155" s="6">
+        <v>1157</v>
+      </c>
+      <c r="C155" s="6" t="s">
         <v>613</v>
       </c>
-      <c r="C98" s="1" t="s">
+    </row>
+    <row r="156" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B156" s="6">
+        <v>1158</v>
+      </c>
+      <c r="C156" s="6" t="s">
         <v>614</v>
       </c>
     </row>
-    <row r="99" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B99" s="1" t="s">
+    <row r="157" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B157" s="6">
+        <v>1159</v>
+      </c>
+      <c r="C157" s="6" t="s">
         <v>615</v>
       </c>
-      <c r="C99" s="1" t="s">
+    </row>
+    <row r="158" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B158" s="6">
+        <v>1160</v>
+      </c>
+      <c r="C158" s="6" t="s">
         <v>616</v>
       </c>
     </row>
-    <row r="100" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B100" s="1" t="s">
+    <row r="159" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B159" s="6">
+        <v>1161</v>
+      </c>
+      <c r="C159" s="6" t="s">
         <v>617</v>
       </c>
-      <c r="C100" s="1" t="s">
+    </row>
+    <row r="160" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B160" s="6">
+        <v>1162</v>
+      </c>
+      <c r="C160" s="6" t="s">
         <v>618</v>
       </c>
     </row>
-    <row r="101" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B101" s="1" t="s">
+    <row r="161" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B161" s="6">
+        <v>1163</v>
+      </c>
+      <c r="C161" s="6" t="s">
         <v>619</v>
       </c>
-      <c r="C101" s="1" t="s">
-        <v>348</v>
-      </c>
-    </row>
-    <row r="102" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B102" s="1" t="s">
+    </row>
+    <row r="162" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B162" s="6">
+        <v>1164</v>
+      </c>
+      <c r="C162" s="6" t="s">
         <v>620</v>
       </c>
-      <c r="C102" s="1" t="s">
+    </row>
+    <row r="163" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B163" s="6">
+        <v>1165</v>
+      </c>
+      <c r="C163" s="6" t="s">
         <v>621</v>
       </c>
     </row>
-    <row r="103" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B103" s="1" t="s">
+    <row r="164" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B164" s="6">
+        <v>1166</v>
+      </c>
+      <c r="C164" s="6" t="s">
         <v>622</v>
       </c>
-      <c r="C103" s="1" t="s">
+    </row>
+    <row r="165" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B165" s="6">
+        <v>1167</v>
+      </c>
+      <c r="C165" s="6" t="s">
         <v>623</v>
       </c>
     </row>
-    <row r="104" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B104" s="1" t="s">
+    <row r="166" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B166" s="6">
+        <v>1168</v>
+      </c>
+      <c r="C166" s="6" t="s">
         <v>624</v>
       </c>
-      <c r="C104" s="1" t="s">
+    </row>
+    <row r="167" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B167" s="6">
+        <v>1200</v>
+      </c>
+      <c r="C167" s="6" t="s">
         <v>625</v>
       </c>
     </row>
-    <row r="105" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B105" s="1" t="s">
+    <row r="168" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B168" s="6">
+        <v>1201</v>
+      </c>
+      <c r="C168" s="6" t="s">
         <v>626</v>
       </c>
-      <c r="C105" s="1" t="s">
-        <v>350</v>
-      </c>
-    </row>
-    <row r="106" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B106" s="1" t="s">
+    </row>
+    <row r="169" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B169" s="6">
+        <v>1202</v>
+      </c>
+      <c r="C169" s="6" t="s">
         <v>627</v>
       </c>
-      <c r="C106" s="1" t="s">
+    </row>
+    <row r="170" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B170" s="6">
+        <v>1203</v>
+      </c>
+      <c r="C170" s="6" t="s">
         <v>628</v>
       </c>
     </row>
-    <row r="107" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B107" s="1" t="s">
+    <row r="171" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B171" s="6">
+        <v>1204</v>
+      </c>
+      <c r="C171" s="6" t="s">
         <v>629</v>
       </c>
-      <c r="C107" s="1" t="s">
-        <v>423</v>
-      </c>
-    </row>
-    <row r="108" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B108" s="1" t="s">
+    </row>
+    <row r="172" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B172" s="6">
+        <v>1205</v>
+      </c>
+      <c r="C172" s="6" t="s">
         <v>630</v>
       </c>
-      <c r="C108" s="1" t="s">
+    </row>
+    <row r="173" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B173" s="6">
+        <v>1206</v>
+      </c>
+      <c r="C173" s="6" t="s">
         <v>631</v>
       </c>
     </row>
-    <row r="109" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B109" s="1" t="s">
+    <row r="174" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B174" s="6">
+        <v>1207</v>
+      </c>
+      <c r="C174" s="6" t="s">
         <v>632</v>
       </c>
-      <c r="C109" s="1" t="s">
+    </row>
+    <row r="175" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B175" s="6">
+        <v>1208</v>
+      </c>
+      <c r="C175" s="6" t="s">
         <v>633</v>
       </c>
     </row>
-    <row r="110" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B110" s="1" t="s">
+    <row r="176" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B176" s="6">
+        <v>1209</v>
+      </c>
+      <c r="C176" s="6" t="s">
         <v>634</v>
       </c>
-      <c r="C110" s="1" t="s">
-        <v>395</v>
-      </c>
-    </row>
-    <row r="111" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B111" s="1" t="s">
+    </row>
+    <row r="177" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B177" s="6">
+        <v>1210</v>
+      </c>
+      <c r="C177" s="6" t="s">
         <v>635</v>
       </c>
-      <c r="C111" s="1" t="s">
+    </row>
+    <row r="178" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B178" s="6">
+        <v>1290</v>
+      </c>
+      <c r="C178" s="6" t="s">
         <v>636</v>
       </c>
     </row>
-    <row r="112" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B112" s="1" t="s">
-        <v>388</v>
-      </c>
-      <c r="C112" s="1" t="s">
+    <row r="179" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B179" s="6">
+        <v>1300</v>
+      </c>
+      <c r="C179" s="6" t="s">
         <v>637</v>
       </c>
     </row>
-    <row r="113" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B113" s="1" t="s">
+    <row r="180" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B180" s="6">
+        <v>1301</v>
+      </c>
+      <c r="C180" s="6" t="s">
         <v>638</v>
       </c>
-      <c r="C113" s="1" t="s">
+    </row>
+    <row r="181" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B181" s="6">
+        <v>1302</v>
+      </c>
+      <c r="C181" s="6" t="s">
         <v>639</v>
       </c>
     </row>
-    <row r="114" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B114" s="1" t="s">
+    <row r="182" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B182" s="6">
+        <v>164</v>
+      </c>
+      <c r="C182" s="6" t="s">
         <v>640</v>
       </c>
-      <c r="C114" s="1" t="s">
+    </row>
+    <row r="183" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B183" s="6">
+        <v>2000</v>
+      </c>
+      <c r="C183" s="6" t="s">
         <v>641</v>
       </c>
     </row>
-    <row r="115" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B115" s="1" t="s">
+    <row r="184" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B184" s="6">
+        <v>8000</v>
+      </c>
+      <c r="C184" s="6" t="s">
         <v>642</v>
       </c>
-      <c r="C115" s="1" t="s">
-        <v>583</v>
-      </c>
-    </row>
-    <row r="116" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B116" s="1" t="s">
-        <v>643</v>
-      </c>
-      <c r="C116" s="1" t="s">
+    </row>
+    <row r="185" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B185" s="6">
+        <v>8001</v>
+      </c>
+      <c r="C185" s="6" t="s">
         <v>644</v>
       </c>
     </row>
-    <row r="117" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B117" s="1" t="s">
-        <v>645</v>
-      </c>
-      <c r="C117" s="1" t="s">
-        <v>383</v>
-      </c>
-    </row>
-    <row r="118" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B118" s="1" t="s">
+    <row r="186" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B186" s="6">
+        <v>8002</v>
+      </c>
+      <c r="C186" s="6" t="s">
         <v>646</v>
       </c>
-      <c r="C118" s="1" t="s">
-        <v>367</v>
-      </c>
-    </row>
-    <row r="119" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B119" s="1" t="s">
-        <v>647</v>
-      </c>
-      <c r="C119" s="1" t="s">
+    </row>
+    <row r="187" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B187" s="6">
+        <v>8003</v>
+      </c>
+      <c r="C187" s="6" t="s">
         <v>648</v>
       </c>
     </row>
-    <row r="120" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B120" s="1" t="s">
-        <v>649</v>
-      </c>
-      <c r="C120" s="1" t="s">
+    <row r="188" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B188" s="6">
+        <v>8004</v>
+      </c>
+      <c r="C188" s="6" t="s">
         <v>650</v>
       </c>
     </row>
-    <row r="121" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B121" s="1" t="s">
-        <v>651</v>
-      </c>
-      <c r="C121" s="1" t="s">
+    <row r="189" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B189" s="6">
+        <v>8005</v>
+      </c>
+      <c r="C189" s="6" t="s">
         <v>652</v>
       </c>
     </row>
-    <row r="122" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B122" s="1" t="s">
+    <row r="190" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B190" s="6">
+        <v>8006</v>
+      </c>
+      <c r="C190" s="6" t="s">
         <v>653</v>
       </c>
-      <c r="C122" s="1" t="s">
+    </row>
+    <row r="191" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B191" s="6">
+        <v>8007</v>
+      </c>
+      <c r="C191" s="6" t="s">
         <v>654</v>
       </c>
     </row>
-    <row r="123" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B123" s="1" t="s">
+    <row r="192" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B192" s="6">
+        <v>8008</v>
+      </c>
+      <c r="C192" s="6" t="s">
         <v>655</v>
       </c>
-      <c r="C123" s="1" t="s">
+    </row>
+    <row r="193" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B193" s="6">
+        <v>8009</v>
+      </c>
+      <c r="C193" s="6" t="s">
         <v>656</v>
       </c>
     </row>
-    <row r="124" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B124" s="1" t="s">
+    <row r="194" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B194" s="6">
+        <v>8010</v>
+      </c>
+      <c r="C194" s="6" t="s">
         <v>657</v>
       </c>
-      <c r="C124" s="1" t="s">
-        <v>648</v>
-      </c>
-    </row>
-    <row r="125" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B125" s="1" t="s">
+    </row>
+    <row r="195" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B195" s="6">
+        <v>8011</v>
+      </c>
+      <c r="C195" s="6" t="s">
         <v>658</v>
       </c>
-      <c r="C125" s="1" t="s">
-        <v>650</v>
-      </c>
-    </row>
-    <row r="126" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B126" s="1" t="s">
+    </row>
+    <row r="196" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B196" s="6">
+        <v>8012</v>
+      </c>
+      <c r="C196" s="6" t="s">
         <v>659</v>
       </c>
-      <c r="C126" s="1" t="s">
+    </row>
+    <row r="197" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B197" s="6">
+        <v>8013</v>
+      </c>
+      <c r="C197" s="6" t="s">
         <v>660</v>
       </c>
     </row>
-    <row r="127" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B127" s="1" t="s">
+    <row r="198" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B198" s="6">
+        <v>8014</v>
+      </c>
+      <c r="C198" s="6" t="s">
         <v>661</v>
       </c>
-      <c r="C127" s="1" t="s">
+    </row>
+    <row r="199" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B199" s="6">
+        <v>8015</v>
+      </c>
+      <c r="C199" s="6" t="s">
         <v>662</v>
       </c>
     </row>
-    <row r="128" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B128" s="1" t="s">
+    <row r="200" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B200" s="6">
+        <v>8016</v>
+      </c>
+      <c r="C200" s="6" t="s">
         <v>663</v>
       </c>
-      <c r="C128" s="1" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="129" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B129" s="1" t="s">
+    </row>
+    <row r="201" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B201" s="6">
+        <v>8017</v>
+      </c>
+      <c r="C201" s="6" t="s">
         <v>664</v>
       </c>
-      <c r="C129" s="1" t="s">
+    </row>
+    <row r="202" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B202" s="6">
+        <v>8018</v>
+      </c>
+      <c r="C202" s="6" t="s">
         <v>665</v>
       </c>
     </row>
-    <row r="130" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B130" s="1" t="s">
+    <row r="203" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B203" s="6">
+        <v>8019</v>
+      </c>
+      <c r="C203" s="6" t="s">
+        <v>642</v>
+      </c>
+    </row>
+    <row r="204" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B204" s="6">
+        <v>8020</v>
+      </c>
+      <c r="C204" s="6" t="s">
         <v>666</v>
       </c>
-      <c r="C130" s="1" t="s">
+    </row>
+    <row r="205" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B205" s="6">
+        <v>8021</v>
+      </c>
+      <c r="C205" s="6" t="s">
         <v>667</v>
       </c>
     </row>
-    <row r="131" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B131" s="1" t="s">
+    <row r="206" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B206" s="6">
+        <v>8022</v>
+      </c>
+      <c r="C206" s="6" t="s">
         <v>668</v>
       </c>
-      <c r="C131" s="1" t="s">
+    </row>
+    <row r="207" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B207" s="6">
+        <v>8023</v>
+      </c>
+      <c r="C207" s="6" t="s">
         <v>669</v>
       </c>
     </row>
-    <row r="132" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B132" s="1" t="s">
+    <row r="208" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B208" s="6">
+        <v>8024</v>
+      </c>
+      <c r="C208" s="6" t="s">
         <v>670</v>
       </c>
-      <c r="C132" s="1" t="s">
-        <v>654</v>
-      </c>
-    </row>
-    <row r="133" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B133" s="1" t="s">
+    </row>
+    <row r="209" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B209" s="6">
+        <v>8025</v>
+      </c>
+      <c r="C209" s="6" t="s">
         <v>671</v>
       </c>
-      <c r="C133" s="1" t="s">
-        <v>656</v>
-      </c>
-    </row>
-    <row r="134" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B134" s="1" t="s">
+    </row>
+    <row r="210" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B210" s="6">
+        <v>8026</v>
+      </c>
+      <c r="C210" s="6" t="s">
         <v>672</v>
       </c>
-      <c r="C134" s="1" t="s">
+    </row>
+    <row r="211" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B211" s="6">
+        <v>8027</v>
+      </c>
+      <c r="C211" s="6" t="s">
         <v>673</v>
       </c>
     </row>
-    <row r="135" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B135" s="1" t="s">
+    <row r="212" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B212" s="6">
+        <v>8028</v>
+      </c>
+      <c r="C212" s="6" t="s">
         <v>674</v>
-      </c>
-      <c r="C135" s="1" t="s">
-        <v>675</v>
-      </c>
-    </row>
-    <row r="136" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B136" s="1" t="s">
-        <v>676</v>
-      </c>
-      <c r="C136" s="1" t="s">
-        <v>677</v>
-      </c>
-    </row>
-    <row r="137" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B137" s="1" t="s">
-        <v>678</v>
-      </c>
-      <c r="C137" s="1" t="s">
-        <v>679</v>
-      </c>
-    </row>
-    <row r="138" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B138" s="1" t="s">
-        <v>680</v>
-      </c>
-      <c r="C138" s="1" t="s">
-        <v>681</v>
-      </c>
-    </row>
-    <row r="139" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B139" s="1" t="s">
-        <v>682</v>
-      </c>
-      <c r="C139" s="1" t="s">
-        <v>683</v>
-      </c>
-    </row>
-    <row r="140" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B140" s="1" t="s">
-        <v>684</v>
-      </c>
-      <c r="C140" s="1" t="s">
-        <v>685</v>
-      </c>
-    </row>
-    <row r="141" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B141" s="1" t="s">
-        <v>686</v>
-      </c>
-      <c r="C141" s="1" t="s">
-        <v>687</v>
-      </c>
-    </row>
-    <row r="142" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B142" s="1" t="s">
-        <v>688</v>
-      </c>
-      <c r="C142" s="1" t="s">
-        <v>466</v>
-      </c>
-    </row>
-    <row r="143" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B143" s="1" t="s">
-        <v>689</v>
-      </c>
-      <c r="C143" s="1" t="s">
-        <v>690</v>
-      </c>
-    </row>
-    <row r="144" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B144" s="1" t="s">
-        <v>691</v>
-      </c>
-      <c r="C144" s="1" t="s">
-        <v>692</v>
-      </c>
-    </row>
-    <row r="145" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B145" s="1" t="s">
-        <v>693</v>
-      </c>
-      <c r="C145" s="1" t="s">
-        <v>694</v>
-      </c>
-    </row>
-    <row r="146" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B146" s="1" t="s">
-        <v>695</v>
-      </c>
-      <c r="C146" s="1" t="s">
-        <v>696</v>
-      </c>
-    </row>
-    <row r="147" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B147" s="1" t="s">
-        <v>697</v>
-      </c>
-      <c r="C147" s="1" t="s">
-        <v>698</v>
-      </c>
-    </row>
-    <row r="148" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B148" s="1" t="s">
-        <v>699</v>
-      </c>
-      <c r="C148" s="1" t="s">
-        <v>700</v>
-      </c>
-    </row>
-    <row r="149" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B149" s="1" t="s">
-        <v>701</v>
-      </c>
-      <c r="C149" s="1" t="s">
-        <v>702</v>
-      </c>
-    </row>
-    <row r="150" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B150" s="1" t="s">
-        <v>703</v>
-      </c>
-      <c r="C150" s="1" t="s">
-        <v>704</v>
-      </c>
-    </row>
-    <row r="151" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B151" s="1" t="s">
-        <v>705</v>
-      </c>
-      <c r="C151" s="1" t="s">
-        <v>706</v>
-      </c>
-    </row>
-    <row r="152" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B152" s="1" t="s">
-        <v>707</v>
-      </c>
-      <c r="C152" s="1" t="s">
-        <v>708</v>
-      </c>
-    </row>
-    <row r="153" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B153" s="1" t="s">
-        <v>709</v>
-      </c>
-      <c r="C153" s="1" t="s">
-        <v>710</v>
-      </c>
-    </row>
-    <row r="154" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B154" s="1" t="s">
-        <v>711</v>
-      </c>
-      <c r="C154" s="1" t="s">
-        <v>712</v>
-      </c>
-    </row>
-    <row r="155" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B155" s="1" t="s">
-        <v>713</v>
-      </c>
-      <c r="C155" s="1" t="s">
-        <v>714</v>
-      </c>
-    </row>
-    <row r="156" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B156" s="1" t="s">
-        <v>715</v>
-      </c>
-      <c r="C156" s="1" t="s">
-        <v>716</v>
-      </c>
-    </row>
-    <row r="157" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B157" s="1" t="s">
-        <v>717</v>
-      </c>
-      <c r="C157" s="1" t="s">
-        <v>466</v>
-      </c>
-    </row>
-    <row r="158" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B158" s="1" t="s">
-        <v>718</v>
-      </c>
-      <c r="C158" s="1" t="s">
-        <v>719</v>
-      </c>
-    </row>
-    <row r="159" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B159" s="1" t="s">
-        <v>720</v>
-      </c>
-      <c r="C159" s="1" t="s">
-        <v>721</v>
-      </c>
-    </row>
-    <row r="160" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B160" s="1" t="s">
-        <v>722</v>
-      </c>
-      <c r="C160" s="1" t="s">
-        <v>436</v>
-      </c>
-    </row>
-    <row r="161" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B161" s="1" t="s">
-        <v>723</v>
-      </c>
-      <c r="C161" s="1" t="s">
-        <v>724</v>
-      </c>
-    </row>
-    <row r="162" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B162" s="1" t="s">
-        <v>725</v>
-      </c>
-      <c r="C162" s="1" t="s">
-        <v>726</v>
-      </c>
-    </row>
-    <row r="163" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B163" s="1" t="s">
-        <v>727</v>
-      </c>
-      <c r="C163" s="1" t="s">
-        <v>466</v>
-      </c>
-    </row>
-    <row r="164" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B164" s="1" t="s">
-        <v>728</v>
-      </c>
-      <c r="C164" s="1" t="s">
-        <v>729</v>
-      </c>
-    </row>
-    <row r="165" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B165" s="1" t="s">
-        <v>730</v>
-      </c>
-      <c r="C165" s="1" t="s">
-        <v>731</v>
-      </c>
-    </row>
-    <row r="166" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B166" s="1" t="s">
-        <v>732</v>
-      </c>
-      <c r="C166" s="1" t="s">
-        <v>733</v>
-      </c>
-    </row>
-    <row r="167" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B167" s="1" t="s">
-        <v>734</v>
-      </c>
-      <c r="C167" s="1" t="s">
-        <v>735</v>
-      </c>
-    </row>
-    <row r="168" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B168" s="1" t="s">
-        <v>736</v>
-      </c>
-      <c r="C168" s="1" t="s">
-        <v>737</v>
-      </c>
-    </row>
-    <row r="169" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B169" s="1" t="s">
-        <v>738</v>
-      </c>
-      <c r="C169" s="1" t="s">
-        <v>739</v>
-      </c>
-    </row>
-    <row r="170" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B170" s="1" t="s">
-        <v>740</v>
-      </c>
-      <c r="C170" s="1" t="s">
-        <v>741</v>
-      </c>
-    </row>
-    <row r="171" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B171" s="1" t="s">
-        <v>742</v>
-      </c>
-      <c r="C171" s="1" t="s">
-        <v>743</v>
-      </c>
-    </row>
-    <row r="172" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B172" s="1" t="s">
-        <v>744</v>
-      </c>
-      <c r="C172" s="1" t="s">
-        <v>745</v>
-      </c>
-    </row>
-    <row r="173" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B173" s="1" t="s">
-        <v>746</v>
-      </c>
-      <c r="C173" s="1" t="s">
-        <v>747</v>
-      </c>
-    </row>
-    <row r="174" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B174" s="1" t="s">
-        <v>748</v>
-      </c>
-      <c r="C174" s="1" t="s">
-        <v>749</v>
-      </c>
-    </row>
-    <row r="175" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B175" s="1" t="s">
-        <v>750</v>
-      </c>
-      <c r="C175" s="1" t="s">
-        <v>751</v>
-      </c>
-    </row>
-    <row r="176" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B176" s="1" t="s">
-        <v>752</v>
-      </c>
-      <c r="C176" s="1" t="s">
-        <v>751</v>
-      </c>
-    </row>
-    <row r="177" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B177" s="1" t="s">
-        <v>753</v>
-      </c>
-      <c r="C177" s="1" t="s">
-        <v>754</v>
-      </c>
-    </row>
-    <row r="178" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B178" s="1" t="s">
-        <v>755</v>
-      </c>
-      <c r="C178" s="1" t="s">
-        <v>756</v>
-      </c>
-    </row>
-    <row r="179" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B179" s="1" t="s">
-        <v>757</v>
-      </c>
-      <c r="C179" s="1" t="s">
-        <v>758</v>
-      </c>
-    </row>
-    <row r="180" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B180" s="1" t="s">
-        <v>759</v>
-      </c>
-      <c r="C180" s="1" t="s">
-        <v>583</v>
-      </c>
-    </row>
-    <row r="181" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B181" s="1" t="s">
-        <v>760</v>
-      </c>
-      <c r="C181" s="1" t="s">
-        <v>761</v>
-      </c>
-    </row>
-    <row r="182" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B182" s="1" t="s">
-        <v>762</v>
-      </c>
-      <c r="C182" s="1" t="s">
-        <v>763</v>
-      </c>
-    </row>
-    <row r="183" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B183" s="1" t="s">
-        <v>764</v>
-      </c>
-      <c r="C183" s="1" t="s">
-        <v>765</v>
-      </c>
-    </row>
-    <row r="184" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B184" s="1" t="s">
-        <v>766</v>
-      </c>
-      <c r="C184" s="1" t="s">
-        <v>491</v>
-      </c>
-    </row>
-    <row r="185" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B185" s="1" t="s">
-        <v>767</v>
-      </c>
-      <c r="C185" s="1" t="s">
-        <v>667</v>
-      </c>
-    </row>
-    <row r="186" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B186" s="1" t="s">
-        <v>768</v>
-      </c>
-      <c r="C186" s="1" t="s">
-        <v>669</v>
-      </c>
-    </row>
-    <row r="187" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B187" s="1" t="s">
-        <v>769</v>
-      </c>
-      <c r="C187" s="1" t="s">
-        <v>662</v>
-      </c>
-    </row>
-    <row r="188" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B188" s="1" t="s">
-        <v>770</v>
-      </c>
-      <c r="C188" s="1" t="s">
-        <v>665</v>
-      </c>
-    </row>
-    <row r="189" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B189" s="1" t="s">
-        <v>771</v>
-      </c>
-      <c r="C189" s="1" t="s">
-        <v>660</v>
-      </c>
-    </row>
-    <row r="190" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B190" s="1" t="s">
-        <v>393</v>
-      </c>
-      <c r="C190" s="1" t="s">
-        <v>772</v>
-      </c>
-    </row>
-    <row r="191" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B191" s="1" t="s">
-        <v>773</v>
-      </c>
-      <c r="C191" s="1" t="s">
-        <v>774</v>
-      </c>
-    </row>
-    <row r="192" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B192" s="1" t="s">
-        <v>775</v>
-      </c>
-      <c r="C192" s="1" t="s">
-        <v>776</v>
-      </c>
-    </row>
-    <row r="193" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B193" s="1" t="s">
-        <v>777</v>
-      </c>
-      <c r="C193" s="1" t="s">
-        <v>778</v>
-      </c>
-    </row>
-    <row r="194" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B194" s="1" t="s">
-        <v>779</v>
-      </c>
-      <c r="C194" s="1" t="s">
-        <v>780</v>
-      </c>
-    </row>
-    <row r="195" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B195" s="1" t="s">
-        <v>781</v>
-      </c>
-      <c r="C195" s="1" t="s">
-        <v>782</v>
-      </c>
-    </row>
-    <row r="196" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B196" s="1" t="s">
-        <v>783</v>
-      </c>
-      <c r="C196" s="1" t="s">
-        <v>784</v>
-      </c>
-    </row>
-    <row r="197" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B197" s="1" t="s">
-        <v>785</v>
-      </c>
-      <c r="C197" s="1" t="s">
-        <v>786</v>
-      </c>
-    </row>
-    <row r="198" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B198" s="1" t="s">
-        <v>787</v>
-      </c>
-      <c r="C198" s="1" t="s">
-        <v>526</v>
-      </c>
-    </row>
-    <row r="199" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B199" s="1" t="s">
-        <v>788</v>
-      </c>
-      <c r="C199" s="1" t="s">
-        <v>789</v>
-      </c>
-    </row>
-    <row r="200" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B200" s="1" t="s">
-        <v>790</v>
-      </c>
-      <c r="C200" s="1" t="s">
-        <v>791</v>
-      </c>
-    </row>
-    <row r="201" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B201" s="1" t="s">
-        <v>792</v>
-      </c>
-      <c r="C201" s="1" t="s">
-        <v>793</v>
-      </c>
-    </row>
-    <row r="202" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B202" s="1" t="s">
-        <v>794</v>
-      </c>
-      <c r="C202" s="1" t="s">
-        <v>795</v>
-      </c>
-    </row>
-    <row r="203" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B203" s="1" t="s">
-        <v>796</v>
-      </c>
-      <c r="C203" s="1" t="s">
-        <v>797</v>
-      </c>
-    </row>
-    <row r="204" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B204" s="1" t="s">
-        <v>798</v>
-      </c>
-      <c r="C204" s="1" t="s">
-        <v>799</v>
-      </c>
-    </row>
-    <row r="205" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B205" s="1" t="s">
-        <v>800</v>
-      </c>
-      <c r="C205" s="1" t="s">
-        <v>801</v>
-      </c>
-    </row>
-    <row r="206" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B206" s="1" t="s">
-        <v>802</v>
-      </c>
-      <c r="C206" s="1" t="s">
-        <v>803</v>
-      </c>
-    </row>
-    <row r="207" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B207" s="1" t="s">
-        <v>804</v>
-      </c>
-      <c r="C207" s="1" t="s">
-        <v>805</v>
-      </c>
-    </row>
-    <row r="208" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B208" s="1" t="s">
-        <v>806</v>
-      </c>
-      <c r="C208" s="1" t="s">
-        <v>807</v>
-      </c>
-    </row>
-    <row r="209" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B209" s="1" t="s">
-        <v>808</v>
-      </c>
-      <c r="C209" s="1" t="s">
-        <v>809</v>
-      </c>
-    </row>
-    <row r="210" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B210" s="1" t="s">
-        <v>810</v>
-      </c>
-      <c r="C210" s="1" t="s">
-        <v>811</v>
-      </c>
-    </row>
-    <row r="211" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B211" s="1" t="s">
-        <v>812</v>
-      </c>
-      <c r="C211" s="1" t="s">
-        <v>813</v>
-      </c>
-    </row>
-    <row r="212" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B212" s="1" t="s">
-        <v>814</v>
-      </c>
-      <c r="C212" s="1" t="s">
-        <v>815</v>
-      </c>
-    </row>
-    <row r="213" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B213" s="1" t="s">
-        <v>816</v>
-      </c>
-      <c r="C213" s="1" t="s">
-        <v>817</v>
-      </c>
-    </row>
-    <row r="214" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B214" s="1" t="s">
-        <v>818</v>
-      </c>
-      <c r="C214" s="1" t="s">
-        <v>819</v>
-      </c>
-    </row>
-    <row r="215" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B215" s="1" t="s">
-        <v>820</v>
-      </c>
-      <c r="C215" s="1" t="s">
-        <v>821</v>
-      </c>
-    </row>
-    <row r="216" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B216" s="1" t="s">
-        <v>822</v>
-      </c>
-      <c r="C216" s="1" t="s">
-        <v>823</v>
-      </c>
-    </row>
-    <row r="217" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B217" s="1" t="s">
-        <v>824</v>
-      </c>
-      <c r="C217" s="1" t="s">
-        <v>825</v>
-      </c>
-    </row>
-    <row r="218" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B218" s="1" t="s">
-        <v>826</v>
-      </c>
-      <c r="C218" s="1" t="s">
-        <v>827</v>
-      </c>
-    </row>
-    <row r="219" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B219" s="1" t="s">
-        <v>828</v>
-      </c>
-      <c r="C219" s="1" t="s">
-        <v>791</v>
-      </c>
-    </row>
-    <row r="220" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B220" s="1" t="s">
-        <v>829</v>
-      </c>
-      <c r="C220" s="1" t="s">
-        <v>830</v>
-      </c>
-    </row>
-    <row r="221" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B221" s="1" t="s">
-        <v>831</v>
-      </c>
-      <c r="C221" s="1" t="s">
-        <v>832</v>
-      </c>
-    </row>
-    <row r="222" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B222" s="1" t="s">
-        <v>833</v>
-      </c>
-      <c r="C222" s="1" t="s">
-        <v>834</v>
-      </c>
-    </row>
-    <row r="223" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B223" s="1" t="s">
-        <v>835</v>
-      </c>
-      <c r="C223" s="1" t="s">
-        <v>836</v>
-      </c>
-    </row>
-    <row r="224" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B224" s="1" t="s">
-        <v>837</v>
-      </c>
-      <c r="C224" s="1" t="s">
-        <v>838</v>
-      </c>
-    </row>
-    <row r="225" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B225" s="1" t="s">
-        <v>839</v>
-      </c>
-      <c r="C225" s="1" t="s">
-        <v>840</v>
-      </c>
-    </row>
-    <row r="226" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B226" s="1" t="s">
-        <v>841</v>
-      </c>
-      <c r="C226" s="1" t="s">
-        <v>842</v>
-      </c>
-    </row>
-    <row r="227" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B227" s="1" t="s">
-        <v>843</v>
-      </c>
-      <c r="C227" s="1" t="s">
-        <v>844</v>
-      </c>
-    </row>
-    <row r="228" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B228" s="1" t="s">
-        <v>845</v>
-      </c>
-      <c r="C228" s="1" t="s">
-        <v>846</v>
       </c>
     </row>
   </sheetData>
@@ -6201,1354 +5561,1354 @@
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="1" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="2" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="C2" s="1" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="3" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B3" s="2" t="s">
+      <c r="B3" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="C3" s="1" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="4" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B4" s="2" t="s">
+      <c r="B4" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="C4" s="1" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="5" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B5" s="2" t="s">
+      <c r="B5" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C5" s="2" t="s">
+      <c r="C5" s="1" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="6" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B6" s="2" t="s">
+      <c r="B6" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C6" s="2" t="s">
+      <c r="C6" s="1" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="7" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B7" s="2" t="s">
+      <c r="B7" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="C7" s="2" t="s">
+      <c r="C7" s="1" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="8" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B8" s="2" t="s">
+      <c r="B8" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="C8" s="2" t="s">
+      <c r="C8" s="1" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="9" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B9" s="2" t="s">
+      <c r="B9" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="C9" s="2" t="s">
+      <c r="C9" s="1" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="10" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B10" s="2" t="s">
+      <c r="B10" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="C10" s="2" t="s">
+      <c r="C10" s="1" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="11" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B11" s="2" t="s">
+      <c r="B11" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="C11" s="2" t="s">
+      <c r="C11" s="1" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="12" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B12" s="2" t="s">
+      <c r="B12" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="C12" s="2" t="s">
+      <c r="C12" s="1" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="13" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B13" s="2" t="s">
+      <c r="B13" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="C13" s="2" t="s">
+      <c r="C13" s="1" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="14" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B14" s="2" t="s">
+      <c r="B14" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="C14" s="2" t="s">
+      <c r="C14" s="1" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="15" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B15" s="2" t="s">
+      <c r="B15" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="C15" s="2" t="s">
+      <c r="C15" s="1" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="16" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B16" s="2" t="s">
+      <c r="B16" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="C16" s="2" t="s">
+      <c r="C16" s="1" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="17" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B17" s="2" t="s">
+      <c r="B17" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="C17" s="2" t="s">
+      <c r="C17" s="1" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="18" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B18" s="2" t="s">
+      <c r="B18" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="C18" s="2" t="s">
+      <c r="C18" s="1" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="19" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B19" s="2" t="s">
+      <c r="B19" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="C19" s="2" t="s">
+      <c r="C19" s="1" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="20" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B20" s="2" t="s">
+      <c r="B20" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="C20" s="2" t="s">
+      <c r="C20" s="1" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="21" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B21" s="2" t="s">
+      <c r="B21" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="C21" s="2" t="s">
+      <c r="C21" s="1" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="22" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B22" s="2" t="s">
+      <c r="B22" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="C22" s="2" t="s">
+      <c r="C22" s="1" t="s">
         <v>43</v>
       </c>
     </row>
     <row r="23" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B23" s="2" t="s">
+      <c r="B23" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="C23" s="2" t="s">
+      <c r="C23" s="1" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="24" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B24" s="2" t="s">
+      <c r="B24" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="C24" s="2" t="s">
+      <c r="C24" s="1" t="s">
         <v>47</v>
       </c>
     </row>
     <row r="25" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B25" s="2" t="s">
+      <c r="B25" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="C25" s="2" t="s">
+      <c r="C25" s="1" t="s">
         <v>49</v>
       </c>
     </row>
     <row r="26" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B26" s="2" t="s">
+      <c r="B26" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="C26" s="2" t="s">
+      <c r="C26" s="1" t="s">
         <v>51</v>
       </c>
     </row>
     <row r="27" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B27" s="2" t="s">
+      <c r="B27" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="C27" s="2" t="s">
+      <c r="C27" s="1" t="s">
         <v>53</v>
       </c>
     </row>
     <row r="28" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B28" s="2" t="s">
+      <c r="B28" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="C28" s="2" t="s">
+      <c r="C28" s="1" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="29" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B29" s="2" t="s">
+      <c r="B29" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="C29" s="2" t="s">
+      <c r="C29" s="1" t="s">
         <v>57</v>
       </c>
     </row>
     <row r="30" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B30" s="2" t="s">
+      <c r="B30" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="C30" s="2" t="s">
+      <c r="C30" s="1" t="s">
         <v>59</v>
       </c>
     </row>
     <row r="31" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B31" s="2" t="s">
+      <c r="B31" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="C31" s="2" t="s">
+      <c r="C31" s="1" t="s">
         <v>61</v>
       </c>
     </row>
     <row r="32" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B32" s="2" t="s">
+      <c r="B32" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="C32" s="2" t="s">
+      <c r="C32" s="1" t="s">
         <v>63</v>
       </c>
     </row>
     <row r="33" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B33" s="2" t="s">
+      <c r="B33" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="C33" s="2" t="s">
+      <c r="C33" s="1" t="s">
         <v>65</v>
       </c>
     </row>
     <row r="34" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B34" s="2" t="s">
+      <c r="B34" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="C34" s="2" t="s">
+      <c r="C34" s="1" t="s">
         <v>67</v>
       </c>
     </row>
     <row r="35" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B35" s="2" t="s">
+      <c r="B35" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="C35" s="2" t="s">
+      <c r="C35" s="1" t="s">
         <v>69</v>
       </c>
     </row>
     <row r="36" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B36" s="2" t="s">
+      <c r="B36" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="C36" s="2" t="s">
+      <c r="C36" s="1" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="37" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B37" s="2" t="s">
+      <c r="B37" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="C37" s="2" t="s">
+      <c r="C37" s="1" t="s">
         <v>73</v>
       </c>
     </row>
     <row r="38" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B38" s="2" t="s">
+      <c r="B38" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="C38" s="2" t="s">
+      <c r="C38" s="1" t="s">
         <v>75</v>
       </c>
     </row>
     <row r="39" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B39" s="2" t="s">
+      <c r="B39" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="C39" s="2" t="s">
+      <c r="C39" s="1" t="s">
         <v>77</v>
       </c>
     </row>
     <row r="40" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B40" s="2" t="s">
+      <c r="B40" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="C40" s="2" t="s">
+      <c r="C40" s="1" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="41" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B41" s="2" t="s">
+      <c r="B41" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="C41" s="2" t="s">
+      <c r="C41" s="1" t="s">
         <v>81</v>
       </c>
     </row>
     <row r="42" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B42" s="2" t="s">
+      <c r="B42" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="C42" s="2" t="s">
+      <c r="C42" s="1" t="s">
         <v>83</v>
       </c>
     </row>
     <row r="43" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B43" s="2" t="s">
+      <c r="B43" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="C43" s="2" t="s">
+      <c r="C43" s="1" t="s">
         <v>85</v>
       </c>
     </row>
     <row r="44" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B44" s="2" t="s">
+      <c r="B44" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="C44" s="2" t="s">
+      <c r="C44" s="1" t="s">
         <v>87</v>
       </c>
     </row>
     <row r="45" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B45" s="2" t="s">
+      <c r="B45" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="C45" s="2" t="s">
+      <c r="C45" s="1" t="s">
         <v>89</v>
       </c>
     </row>
     <row r="46" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B46" s="2" t="s">
+      <c r="B46" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="C46" s="2" t="s">
+      <c r="C46" s="1" t="s">
         <v>91</v>
       </c>
     </row>
     <row r="47" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B47" s="2" t="s">
+      <c r="B47" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="C47" s="2" t="s">
+      <c r="C47" s="1" t="s">
         <v>93</v>
       </c>
     </row>
     <row r="48" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B48" s="2" t="s">
+      <c r="B48" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="C48" s="2" t="s">
+      <c r="C48" s="1" t="s">
         <v>95</v>
       </c>
     </row>
     <row r="49" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B49" s="2" t="s">
+      <c r="B49" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="C49" s="2" t="s">
+      <c r="C49" s="1" t="s">
         <v>97</v>
       </c>
     </row>
     <row r="50" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B50" s="2" t="s">
+      <c r="B50" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="C50" s="2" t="s">
+      <c r="C50" s="1" t="s">
         <v>99</v>
       </c>
     </row>
     <row r="51" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B51" s="2" t="s">
+      <c r="B51" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="C51" s="2" t="s">
+      <c r="C51" s="1" t="s">
         <v>101</v>
       </c>
     </row>
     <row r="52" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B52" s="2" t="s">
+      <c r="B52" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="C52" s="2" t="s">
+      <c r="C52" s="1" t="s">
         <v>103</v>
       </c>
     </row>
     <row r="53" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B53" s="2" t="s">
+      <c r="B53" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="C53" s="2" t="s">
+      <c r="C53" s="1" t="s">
         <v>105</v>
       </c>
     </row>
     <row r="54" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B54" s="2" t="s">
+      <c r="B54" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="C54" s="2" t="s">
+      <c r="C54" s="1" t="s">
         <v>107</v>
       </c>
     </row>
     <row r="55" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B55" s="2" t="s">
+      <c r="B55" s="1" t="s">
         <v>108</v>
       </c>
-      <c r="C55" s="2" t="s">
+      <c r="C55" s="1" t="s">
         <v>109</v>
       </c>
     </row>
     <row r="56" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B56" s="2" t="s">
+      <c r="B56" s="1" t="s">
         <v>110</v>
       </c>
-      <c r="C56" s="2" t="s">
+      <c r="C56" s="1" t="s">
         <v>111</v>
       </c>
     </row>
     <row r="57" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B57" s="2" t="s">
+      <c r="B57" s="1" t="s">
         <v>112</v>
       </c>
-      <c r="C57" s="2" t="s">
+      <c r="C57" s="1" t="s">
         <v>113</v>
       </c>
     </row>
     <row r="58" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B58" s="2" t="s">
+      <c r="B58" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="C58" s="2" t="s">
+      <c r="C58" s="1" t="s">
         <v>115</v>
       </c>
     </row>
     <row r="59" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B59" s="2" t="s">
+      <c r="B59" s="1" t="s">
         <v>116</v>
       </c>
-      <c r="C59" s="2" t="s">
+      <c r="C59" s="1" t="s">
         <v>117</v>
       </c>
     </row>
     <row r="60" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B60" s="2" t="s">
+      <c r="B60" s="1" t="s">
         <v>118</v>
       </c>
-      <c r="C60" s="2" t="s">
+      <c r="C60" s="1" t="s">
         <v>119</v>
       </c>
     </row>
     <row r="61" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B61" s="2" t="s">
+      <c r="B61" s="1" t="s">
         <v>120</v>
       </c>
-      <c r="C61" s="2" t="s">
+      <c r="C61" s="1" t="s">
         <v>121</v>
       </c>
     </row>
     <row r="62" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B62" s="2" t="s">
+      <c r="B62" s="1" t="s">
         <v>122</v>
       </c>
-      <c r="C62" s="2" t="s">
+      <c r="C62" s="1" t="s">
         <v>123</v>
       </c>
     </row>
     <row r="63" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B63" s="2" t="s">
+      <c r="B63" s="1" t="s">
         <v>124</v>
       </c>
-      <c r="C63" s="2" t="s">
+      <c r="C63" s="1" t="s">
         <v>125</v>
       </c>
     </row>
     <row r="64" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B64" s="2" t="s">
+      <c r="B64" s="1" t="s">
         <v>126</v>
       </c>
-      <c r="C64" s="2" t="s">
+      <c r="C64" s="1" t="s">
         <v>127</v>
       </c>
     </row>
     <row r="65" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B65" s="2" t="s">
+      <c r="B65" s="1" t="s">
         <v>128</v>
       </c>
-      <c r="C65" s="2" t="s">
+      <c r="C65" s="1" t="s">
         <v>129</v>
       </c>
     </row>
     <row r="66" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B66" s="2" t="s">
+      <c r="B66" s="1" t="s">
         <v>130</v>
       </c>
-      <c r="C66" s="2" t="s">
+      <c r="C66" s="1" t="s">
         <v>131</v>
       </c>
     </row>
     <row r="67" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B67" s="2" t="s">
+      <c r="B67" s="1" t="s">
         <v>132</v>
       </c>
-      <c r="C67" s="2" t="s">
+      <c r="C67" s="1" t="s">
         <v>133</v>
       </c>
     </row>
     <row r="68" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B68" s="2" t="s">
+      <c r="B68" s="1" t="s">
         <v>134</v>
       </c>
-      <c r="C68" s="2" t="s">
+      <c r="C68" s="1" t="s">
         <v>135</v>
       </c>
     </row>
     <row r="69" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B69" s="2" t="s">
+      <c r="B69" s="1" t="s">
         <v>136</v>
       </c>
-      <c r="C69" s="2" t="s">
+      <c r="C69" s="1" t="s">
         <v>137</v>
       </c>
     </row>
     <row r="70" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B70" s="2" t="s">
+      <c r="B70" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="C70" s="2" t="s">
+      <c r="C70" s="1" t="s">
         <v>139</v>
       </c>
     </row>
     <row r="71" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B71" s="2" t="s">
+      <c r="B71" s="1" t="s">
         <v>140</v>
       </c>
-      <c r="C71" s="2" t="s">
+      <c r="C71" s="1" t="s">
         <v>141</v>
       </c>
     </row>
     <row r="72" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B72" s="2" t="s">
+      <c r="B72" s="1" t="s">
         <v>142</v>
       </c>
-      <c r="C72" s="2" t="s">
+      <c r="C72" s="1" t="s">
         <v>143</v>
       </c>
     </row>
     <row r="73" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B73" s="2" t="s">
+      <c r="B73" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="C73" s="2" t="s">
+      <c r="C73" s="1" t="s">
         <v>145</v>
       </c>
     </row>
     <row r="74" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B74" s="2" t="s">
+      <c r="B74" s="1" t="s">
         <v>146</v>
       </c>
-      <c r="C74" s="2" t="s">
+      <c r="C74" s="1" t="s">
         <v>147</v>
       </c>
     </row>
     <row r="75" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B75" s="2" t="s">
+      <c r="B75" s="1" t="s">
         <v>148</v>
       </c>
-      <c r="C75" s="2" t="s">
+      <c r="C75" s="1" t="s">
         <v>149</v>
       </c>
     </row>
     <row r="76" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B76" s="2" t="s">
+      <c r="B76" s="1" t="s">
         <v>150</v>
       </c>
-      <c r="C76" s="2" t="s">
+      <c r="C76" s="1" t="s">
         <v>151</v>
       </c>
     </row>
     <row r="77" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B77" s="2" t="s">
+      <c r="B77" s="1" t="s">
         <v>152</v>
       </c>
-      <c r="C77" s="2" t="s">
+      <c r="C77" s="1" t="s">
         <v>153</v>
       </c>
     </row>
     <row r="78" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B78" s="2" t="s">
+      <c r="B78" s="1" t="s">
         <v>154</v>
       </c>
-      <c r="C78" s="2" t="s">
+      <c r="C78" s="1" t="s">
         <v>155</v>
       </c>
     </row>
     <row r="79" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B79" s="2" t="s">
+      <c r="B79" s="1" t="s">
         <v>156</v>
       </c>
-      <c r="C79" s="2" t="s">
+      <c r="C79" s="1" t="s">
         <v>157</v>
       </c>
     </row>
     <row r="80" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B80" s="2" t="s">
+      <c r="B80" s="1" t="s">
         <v>158</v>
       </c>
-      <c r="C80" s="2" t="s">
+      <c r="C80" s="1" t="s">
         <v>159</v>
       </c>
     </row>
     <row r="81" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B81" s="2" t="s">
+      <c r="B81" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="C81" s="2" t="s">
+      <c r="C81" s="1" t="s">
         <v>161</v>
       </c>
     </row>
     <row r="82" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B82" s="2" t="s">
+      <c r="B82" s="1" t="s">
         <v>162</v>
       </c>
-      <c r="C82" s="2" t="s">
+      <c r="C82" s="1" t="s">
         <v>163</v>
       </c>
     </row>
     <row r="83" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B83" s="2" t="s">
+      <c r="B83" s="1" t="s">
         <v>164</v>
       </c>
-      <c r="C83" s="2" t="s">
+      <c r="C83" s="1" t="s">
         <v>165</v>
       </c>
     </row>
     <row r="84" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B84" s="2" t="s">
+      <c r="B84" s="1" t="s">
         <v>166</v>
       </c>
-      <c r="C84" s="2" t="s">
+      <c r="C84" s="1" t="s">
         <v>167</v>
       </c>
     </row>
     <row r="85" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B85" s="2" t="s">
+      <c r="B85" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="C85" s="2" t="s">
+      <c r="C85" s="1" t="s">
         <v>169</v>
       </c>
     </row>
     <row r="86" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B86" s="2" t="s">
+      <c r="B86" s="1" t="s">
         <v>170</v>
       </c>
-      <c r="C86" s="2" t="s">
+      <c r="C86" s="1" t="s">
         <v>171</v>
       </c>
     </row>
     <row r="87" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B87" s="2" t="s">
+      <c r="B87" s="1" t="s">
         <v>172</v>
       </c>
-      <c r="C87" s="2" t="s">
+      <c r="C87" s="1" t="s">
         <v>173</v>
       </c>
     </row>
     <row r="88" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B88" s="2" t="s">
+      <c r="B88" s="1" t="s">
         <v>174</v>
       </c>
-      <c r="C88" s="2" t="s">
+      <c r="C88" s="1" t="s">
         <v>175</v>
       </c>
     </row>
     <row r="89" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B89" s="2" t="s">
+      <c r="B89" s="1" t="s">
         <v>176</v>
       </c>
-      <c r="C89" s="2" t="s">
+      <c r="C89" s="1" t="s">
         <v>177</v>
       </c>
     </row>
     <row r="90" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B90" s="2" t="s">
+      <c r="B90" s="1" t="s">
         <v>178</v>
       </c>
-      <c r="C90" s="2" t="s">
+      <c r="C90" s="1" t="s">
         <v>179</v>
       </c>
     </row>
     <row r="91" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B91" s="2" t="s">
+      <c r="B91" s="1" t="s">
         <v>180</v>
       </c>
-      <c r="C91" s="2" t="s">
+      <c r="C91" s="1" t="s">
         <v>181</v>
       </c>
     </row>
     <row r="92" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B92" s="2" t="s">
+      <c r="B92" s="1" t="s">
         <v>182</v>
       </c>
-      <c r="C92" s="2" t="s">
+      <c r="C92" s="1" t="s">
         <v>183</v>
       </c>
     </row>
     <row r="93" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B93" s="2" t="s">
+      <c r="B93" s="1" t="s">
         <v>184</v>
       </c>
-      <c r="C93" s="2" t="s">
+      <c r="C93" s="1" t="s">
         <v>185</v>
       </c>
     </row>
     <row r="94" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B94" s="2" t="s">
+      <c r="B94" s="1" t="s">
         <v>186</v>
       </c>
-      <c r="C94" s="2" t="s">
+      <c r="C94" s="1" t="s">
         <v>187</v>
       </c>
     </row>
     <row r="95" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B95" s="2" t="s">
+      <c r="B95" s="1" t="s">
         <v>188</v>
       </c>
-      <c r="C95" s="2" t="s">
+      <c r="C95" s="1" t="s">
         <v>189</v>
       </c>
     </row>
     <row r="96" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B96" s="2" t="s">
+      <c r="B96" s="1" t="s">
         <v>190</v>
       </c>
-      <c r="C96" s="2" t="s">
+      <c r="C96" s="1" t="s">
         <v>191</v>
       </c>
     </row>
     <row r="97" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B97" s="2" t="s">
+      <c r="B97" s="1" t="s">
         <v>192</v>
       </c>
-      <c r="C97" s="2" t="s">
+      <c r="C97" s="1" t="s">
         <v>193</v>
       </c>
     </row>
     <row r="98" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B98" s="2" t="s">
+      <c r="B98" s="1" t="s">
         <v>194</v>
       </c>
-      <c r="C98" s="2" t="s">
+      <c r="C98" s="1" t="s">
         <v>195</v>
       </c>
     </row>
     <row r="99" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B99" s="2" t="s">
+      <c r="B99" s="1" t="s">
         <v>196</v>
       </c>
-      <c r="C99" s="2" t="s">
+      <c r="C99" s="1" t="s">
         <v>197</v>
       </c>
     </row>
     <row r="100" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B100" s="2" t="s">
+      <c r="B100" s="1" t="s">
         <v>198</v>
       </c>
-      <c r="C100" s="2" t="s">
+      <c r="C100" s="1" t="s">
         <v>199</v>
       </c>
     </row>
     <row r="101" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B101" s="2" t="s">
+      <c r="B101" s="1" t="s">
         <v>200</v>
       </c>
-      <c r="C101" s="2" t="s">
+      <c r="C101" s="1" t="s">
         <v>201</v>
       </c>
     </row>
     <row r="102" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B102" s="2" t="s">
+      <c r="B102" s="1" t="s">
         <v>202</v>
       </c>
-      <c r="C102" s="2" t="s">
+      <c r="C102" s="1" t="s">
         <v>203</v>
       </c>
     </row>
     <row r="103" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B103" s="2" t="s">
+      <c r="B103" s="1" t="s">
         <v>204</v>
       </c>
-      <c r="C103" s="2" t="s">
+      <c r="C103" s="1" t="s">
         <v>205</v>
       </c>
     </row>
     <row r="104" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B104" s="2" t="s">
+      <c r="B104" s="1" t="s">
         <v>206</v>
       </c>
-      <c r="C104" s="2" t="s">
+      <c r="C104" s="1" t="s">
         <v>207</v>
       </c>
     </row>
     <row r="105" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B105" s="2" t="s">
+      <c r="B105" s="1" t="s">
         <v>208</v>
       </c>
-      <c r="C105" s="2" t="s">
+      <c r="C105" s="1" t="s">
         <v>209</v>
       </c>
     </row>
     <row r="106" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B106" s="2" t="s">
+      <c r="B106" s="1" t="s">
         <v>210</v>
       </c>
-      <c r="C106" s="2" t="s">
+      <c r="C106" s="1" t="s">
         <v>211</v>
       </c>
     </row>
     <row r="107" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B107" s="2" t="s">
+      <c r="B107" s="1" t="s">
         <v>212</v>
       </c>
-      <c r="C107" s="2" t="s">
+      <c r="C107" s="1" t="s">
         <v>213</v>
       </c>
     </row>
     <row r="108" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B108" s="2" t="s">
+      <c r="B108" s="1" t="s">
         <v>214</v>
       </c>
-      <c r="C108" s="2" t="s">
+      <c r="C108" s="1" t="s">
         <v>215</v>
       </c>
     </row>
     <row r="109" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B109" s="2" t="s">
+      <c r="B109" s="1" t="s">
         <v>216</v>
       </c>
-      <c r="C109" s="2" t="s">
+      <c r="C109" s="1" t="s">
         <v>217</v>
       </c>
     </row>
     <row r="110" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B110" s="2" t="s">
+      <c r="B110" s="1" t="s">
         <v>218</v>
       </c>
-      <c r="C110" s="2" t="s">
+      <c r="C110" s="1" t="s">
         <v>219</v>
       </c>
     </row>
     <row r="111" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B111" s="2" t="s">
+      <c r="B111" s="1" t="s">
         <v>220</v>
       </c>
-      <c r="C111" s="2" t="s">
+      <c r="C111" s="1" t="s">
         <v>221</v>
       </c>
     </row>
     <row r="112" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B112" s="2" t="s">
+      <c r="B112" s="1" t="s">
         <v>222</v>
       </c>
-      <c r="C112" s="2" t="s">
+      <c r="C112" s="1" t="s">
         <v>223</v>
       </c>
     </row>
     <row r="113" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B113" s="2" t="s">
+      <c r="B113" s="1" t="s">
         <v>224</v>
       </c>
-      <c r="C113" s="2" t="s">
+      <c r="C113" s="1" t="s">
         <v>225</v>
       </c>
     </row>
     <row r="114" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B114" s="2" t="s">
+      <c r="B114" s="1" t="s">
         <v>226</v>
       </c>
-      <c r="C114" s="2" t="s">
+      <c r="C114" s="1" t="s">
         <v>227</v>
       </c>
     </row>
     <row r="115" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B115" s="2" t="s">
+      <c r="B115" s="1" t="s">
         <v>228</v>
       </c>
-      <c r="C115" s="2" t="s">
+      <c r="C115" s="1" t="s">
         <v>229</v>
       </c>
     </row>
     <row r="116" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B116" s="2" t="s">
+      <c r="B116" s="1" t="s">
         <v>230</v>
       </c>
-      <c r="C116" s="2" t="s">
+      <c r="C116" s="1" t="s">
         <v>231</v>
       </c>
     </row>
     <row r="117" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B117" s="2" t="s">
+      <c r="B117" s="1" t="s">
         <v>232</v>
       </c>
-      <c r="C117" s="2" t="s">
+      <c r="C117" s="1" t="s">
         <v>233</v>
       </c>
     </row>
     <row r="118" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B118" s="2" t="s">
+      <c r="B118" s="1" t="s">
         <v>234</v>
       </c>
-      <c r="C118" s="2" t="s">
+      <c r="C118" s="1" t="s">
         <v>235</v>
       </c>
     </row>
     <row r="119" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B119" s="2" t="s">
+      <c r="B119" s="1" t="s">
         <v>236</v>
       </c>
-      <c r="C119" s="2" t="s">
+      <c r="C119" s="1" t="s">
         <v>237</v>
       </c>
     </row>
     <row r="120" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B120" s="2" t="s">
+      <c r="B120" s="1" t="s">
         <v>238</v>
       </c>
-      <c r="C120" s="2" t="s">
+      <c r="C120" s="1" t="s">
         <v>239</v>
       </c>
     </row>
     <row r="121" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B121" s="2" t="s">
+      <c r="B121" s="1" t="s">
         <v>240</v>
       </c>
-      <c r="C121" s="2" t="s">
+      <c r="C121" s="1" t="s">
         <v>241</v>
       </c>
     </row>
     <row r="122" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B122" s="2" t="s">
+      <c r="B122" s="1" t="s">
         <v>242</v>
       </c>
-      <c r="C122" s="2" t="s">
+      <c r="C122" s="1" t="s">
         <v>243</v>
       </c>
     </row>
     <row r="123" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B123" s="2" t="s">
+      <c r="B123" s="1" t="s">
         <v>244</v>
       </c>
-      <c r="C123" s="2" t="s">
+      <c r="C123" s="1" t="s">
         <v>245</v>
       </c>
     </row>
     <row r="124" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B124" s="2" t="s">
+      <c r="B124" s="1" t="s">
         <v>246</v>
       </c>
-      <c r="C124" s="2" t="s">
+      <c r="C124" s="1" t="s">
         <v>247</v>
       </c>
     </row>
     <row r="125" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B125" s="2" t="s">
+      <c r="B125" s="1" t="s">
         <v>248</v>
       </c>
-      <c r="C125" s="2" t="s">
+      <c r="C125" s="1" t="s">
         <v>249</v>
       </c>
     </row>
     <row r="126" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B126" s="2" t="s">
+      <c r="B126" s="1" t="s">
         <v>250</v>
       </c>
-      <c r="C126" s="2" t="s">
+      <c r="C126" s="1" t="s">
         <v>251</v>
       </c>
     </row>
     <row r="127" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B127" s="2" t="s">
+      <c r="B127" s="1" t="s">
         <v>252</v>
       </c>
-      <c r="C127" s="2" t="s">
+      <c r="C127" s="1" t="s">
         <v>253</v>
       </c>
     </row>
     <row r="128" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B128" s="2" t="s">
+      <c r="B128" s="1" t="s">
         <v>254</v>
       </c>
-      <c r="C128" s="2" t="s">
+      <c r="C128" s="1" t="s">
         <v>255</v>
       </c>
     </row>
     <row r="129" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B129" s="2" t="s">
+      <c r="B129" s="1" t="s">
         <v>256</v>
       </c>
-      <c r="C129" s="2" t="s">
+      <c r="C129" s="1" t="s">
         <v>257</v>
       </c>
     </row>
     <row r="130" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B130" s="2" t="s">
+      <c r="B130" s="1" t="s">
         <v>258</v>
       </c>
-      <c r="C130" s="2" t="s">
+      <c r="C130" s="1" t="s">
         <v>259</v>
       </c>
     </row>
     <row r="131" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B131" s="2" t="s">
+      <c r="B131" s="1" t="s">
         <v>260</v>
       </c>
-      <c r="C131" s="2" t="s">
+      <c r="C131" s="1" t="s">
         <v>261</v>
       </c>
     </row>
     <row r="132" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B132" s="2" t="s">
+      <c r="B132" s="1" t="s">
         <v>262</v>
       </c>
-      <c r="C132" s="2" t="s">
+      <c r="C132" s="1" t="s">
         <v>263</v>
       </c>
     </row>
     <row r="133" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B133" s="2" t="s">
+      <c r="B133" s="1" t="s">
         <v>264</v>
       </c>
-      <c r="C133" s="2" t="s">
+      <c r="C133" s="1" t="s">
         <v>265</v>
       </c>
     </row>
     <row r="134" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B134" s="2" t="s">
+      <c r="B134" s="1" t="s">
         <v>266</v>
       </c>
-      <c r="C134" s="2" t="s">
+      <c r="C134" s="1" t="s">
         <v>267</v>
       </c>
     </row>
     <row r="135" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B135" s="2" t="s">
+      <c r="B135" s="1" t="s">
         <v>268</v>
       </c>
-      <c r="C135" s="2" t="s">
+      <c r="C135" s="1" t="s">
         <v>269</v>
       </c>
     </row>
     <row r="136" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B136" s="2" t="s">
+      <c r="B136" s="1" t="s">
         <v>270</v>
       </c>
-      <c r="C136" s="2" t="s">
+      <c r="C136" s="1" t="s">
         <v>271</v>
       </c>
     </row>
     <row r="137" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B137" s="2" t="s">
+      <c r="B137" s="1" t="s">
         <v>272</v>
       </c>
-      <c r="C137" s="2" t="s">
+      <c r="C137" s="1" t="s">
         <v>273</v>
       </c>
     </row>
     <row r="138" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B138" s="2" t="s">
+      <c r="B138" s="1" t="s">
         <v>274</v>
       </c>
-      <c r="C138" s="2" t="s">
+      <c r="C138" s="1" t="s">
         <v>275</v>
       </c>
     </row>
     <row r="139" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B139" s="2" t="s">
+      <c r="B139" s="1" t="s">
         <v>276</v>
       </c>
-      <c r="C139" s="2" t="s">
+      <c r="C139" s="1" t="s">
         <v>277</v>
       </c>
     </row>
     <row r="140" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B140" s="2" t="s">
+      <c r="B140" s="1" t="s">
         <v>278</v>
       </c>
-      <c r="C140" s="2" t="s">
+      <c r="C140" s="1" t="s">
         <v>279</v>
       </c>
     </row>
     <row r="141" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B141" s="2" t="s">
+      <c r="B141" s="1" t="s">
         <v>280</v>
       </c>
-      <c r="C141" s="2" t="s">
+      <c r="C141" s="1" t="s">
         <v>281</v>
       </c>
     </row>
     <row r="142" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B142" s="2" t="s">
+      <c r="B142" s="1" t="s">
         <v>282</v>
       </c>
-      <c r="C142" s="2" t="s">
+      <c r="C142" s="1" t="s">
         <v>283</v>
       </c>
     </row>
     <row r="143" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B143" s="2" t="s">
+      <c r="B143" s="1" t="s">
         <v>284</v>
       </c>
-      <c r="C143" s="2" t="s">
+      <c r="C143" s="1" t="s">
         <v>285</v>
       </c>
     </row>
     <row r="144" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B144" s="2" t="s">
+      <c r="B144" s="1" t="s">
         <v>286</v>
       </c>
-      <c r="C144" s="2" t="s">
+      <c r="C144" s="1" t="s">
         <v>287</v>
       </c>
     </row>
     <row r="145" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B145" s="2" t="s">
+      <c r="B145" s="1" t="s">
         <v>288</v>
       </c>
-      <c r="C145" s="2" t="s">
+      <c r="C145" s="1" t="s">
         <v>289</v>
       </c>
     </row>
     <row r="146" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B146" s="2" t="s">
+      <c r="B146" s="1" t="s">
         <v>290</v>
       </c>
-      <c r="C146" s="2" t="s">
+      <c r="C146" s="1" t="s">
         <v>291</v>
       </c>
     </row>
     <row r="147" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B147" s="2" t="s">
+      <c r="B147" s="1" t="s">
         <v>292</v>
       </c>
-      <c r="C147" s="2" t="s">
+      <c r="C147" s="1" t="s">
         <v>293</v>
       </c>
     </row>
     <row r="148" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B148" s="2" t="s">
+      <c r="B148" s="1" t="s">
         <v>294</v>
       </c>
-      <c r="C148" s="2" t="s">
+      <c r="C148" s="1" t="s">
         <v>295</v>
       </c>
     </row>
     <row r="149" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B149" s="2" t="s">
+      <c r="B149" s="1" t="s">
         <v>296</v>
       </c>
-      <c r="C149" s="2" t="s">
+      <c r="C149" s="1" t="s">
         <v>297</v>
       </c>
     </row>
     <row r="150" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B150" s="2" t="s">
+      <c r="B150" s="1" t="s">
         <v>298</v>
       </c>
-      <c r="C150" s="2" t="s">
+      <c r="C150" s="1" t="s">
         <v>299</v>
       </c>
     </row>
     <row r="151" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B151" s="2" t="s">
+      <c r="B151" s="1" t="s">
         <v>300</v>
       </c>
-      <c r="C151" s="2" t="s">
+      <c r="C151" s="1" t="s">
         <v>301</v>
       </c>
     </row>
     <row r="152" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B152" s="2" t="s">
+      <c r="B152" s="1" t="s">
         <v>302</v>
       </c>
-      <c r="C152" s="2" t="s">
+      <c r="C152" s="1" t="s">
         <v>303</v>
       </c>
     </row>
     <row r="153" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B153" s="2" t="s">
+      <c r="B153" s="1" t="s">
         <v>304</v>
       </c>
-      <c r="C153" s="2" t="s">
+      <c r="C153" s="1" t="s">
         <v>305</v>
       </c>
     </row>
     <row r="154" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B154" s="2" t="s">
+      <c r="B154" s="1" t="s">
         <v>306</v>
       </c>
-      <c r="C154" s="2" t="s">
+      <c r="C154" s="1" t="s">
         <v>307</v>
       </c>
     </row>
     <row r="155" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B155" s="2" t="s">
+      <c r="B155" s="1" t="s">
         <v>308</v>
       </c>
-      <c r="C155" s="2" t="s">
+      <c r="C155" s="1" t="s">
         <v>309</v>
       </c>
     </row>
     <row r="156" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B156" s="2" t="s">
+      <c r="B156" s="1" t="s">
         <v>310</v>
       </c>
-      <c r="C156" s="2" t="s">
+      <c r="C156" s="1" t="s">
         <v>311</v>
       </c>
     </row>
     <row r="157" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B157" s="2" t="s">
+      <c r="B157" s="1" t="s">
         <v>312</v>
       </c>
-      <c r="C157" s="2" t="s">
+      <c r="C157" s="1" t="s">
         <v>313</v>
       </c>
     </row>
     <row r="158" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B158" s="2" t="s">
+      <c r="B158" s="1" t="s">
         <v>314</v>
       </c>
-      <c r="C158" s="2" t="s">
+      <c r="C158" s="1" t="s">
         <v>315</v>
       </c>
     </row>
     <row r="159" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B159" s="2" t="s">
+      <c r="B159" s="1" t="s">
         <v>316</v>
       </c>
-      <c r="C159" s="2" t="s">
+      <c r="C159" s="1" t="s">
         <v>317</v>
       </c>
     </row>
     <row r="160" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B160" s="2" t="s">
+      <c r="B160" s="1" t="s">
         <v>318</v>
       </c>
-      <c r="C160" s="2" t="s">
+      <c r="C160" s="1" t="s">
         <v>319</v>
       </c>
     </row>
     <row r="161" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B161" s="2" t="s">
+      <c r="B161" s="1" t="s">
         <v>320</v>
       </c>
-      <c r="C161" s="2" t="s">
+      <c r="C161" s="1" t="s">
         <v>321</v>
       </c>
     </row>
     <row r="162" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B162" s="2" t="s">
+      <c r="B162" s="1" t="s">
         <v>322</v>
       </c>
-      <c r="C162" s="2" t="s">
+      <c r="C162" s="1" t="s">
         <v>323</v>
       </c>
     </row>
     <row r="163" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B163" s="2" t="s">
+      <c r="B163" s="1" t="s">
         <v>324</v>
       </c>
-      <c r="C163" s="2" t="s">
+      <c r="C163" s="1" t="s">
         <v>325</v>
       </c>
     </row>
     <row r="164" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B164" s="2" t="s">
+      <c r="B164" s="1" t="s">
         <v>326</v>
       </c>
-      <c r="C164" s="2" t="s">
+      <c r="C164" s="1" t="s">
         <v>327</v>
       </c>
     </row>
     <row r="165" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B165" s="2" t="s">
+      <c r="B165" s="1" t="s">
         <v>328</v>
       </c>
-      <c r="C165" s="2" t="s">
+      <c r="C165" s="1" t="s">
         <v>329</v>
       </c>
     </row>
     <row r="166" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B166" s="2" t="s">
+      <c r="B166" s="1" t="s">
         <v>330</v>
       </c>
-      <c r="C166" s="2" t="s">
+      <c r="C166" s="1" t="s">
         <v>331</v>
       </c>
     </row>
     <row r="167" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B167" s="2" t="s">
+      <c r="B167" s="1" t="s">
         <v>332</v>
       </c>
-      <c r="C167" s="2" t="s">
+      <c r="C167" s="1" t="s">
         <v>333</v>
       </c>
     </row>
     <row r="168" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B168" s="2" t="s">
+      <c r="B168" s="1" t="s">
         <v>334</v>
       </c>
-      <c r="C168" s="2" t="s">
+      <c r="C168" s="1" t="s">
         <v>335</v>
       </c>
     </row>
     <row r="169" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B169" s="2" t="s">
+      <c r="B169" s="1" t="s">
         <v>336</v>
       </c>
-      <c r="C169" s="2" t="s">
+      <c r="C169" s="1" t="s">
         <v>337</v>
       </c>
     </row>
@@ -7564,547 +6924,547 @@
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="2" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B2" s="3" t="s">
+      <c r="B2" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="3" t="s">
-        <v>879</v>
+      <c r="C2" s="2" t="s">
+        <v>707</v>
       </c>
     </row>
     <row r="3" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B3" s="3" t="s">
+      <c r="B3" s="2" t="s">
         <v>435</v>
       </c>
-      <c r="C3" s="3" t="s">
-        <v>880</v>
+      <c r="C3" s="2" t="s">
+        <v>708</v>
       </c>
     </row>
     <row r="4" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B4" s="3" t="s">
+      <c r="B4" s="2" t="s">
         <v>437</v>
       </c>
-      <c r="C4" s="3" t="s">
-        <v>881</v>
+      <c r="C4" s="2" t="s">
+        <v>709</v>
       </c>
     </row>
     <row r="5" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B5" s="3" t="s">
+      <c r="B5" s="2" t="s">
         <v>439</v>
       </c>
-      <c r="C5" s="3" t="s">
-        <v>882</v>
+      <c r="C5" s="2" t="s">
+        <v>710</v>
       </c>
     </row>
     <row r="6" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B6" s="3" t="s">
+      <c r="B6" s="2" t="s">
         <v>441</v>
       </c>
-      <c r="C6" s="3" t="s">
-        <v>883</v>
+      <c r="C6" s="2" t="s">
+        <v>711</v>
       </c>
     </row>
     <row r="7" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B7" s="3" t="s">
+      <c r="B7" s="2" t="s">
         <v>443</v>
       </c>
-      <c r="C7" s="3" t="s">
-        <v>881</v>
+      <c r="C7" s="2" t="s">
+        <v>709</v>
       </c>
     </row>
     <row r="8" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B8" s="3" t="s">
+      <c r="B8" s="2" t="s">
         <v>445</v>
       </c>
-      <c r="C8" s="3" t="s">
-        <v>884</v>
+      <c r="C8" s="2" t="s">
+        <v>712</v>
       </c>
     </row>
     <row r="9" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B9" s="3" t="s">
+      <c r="B9" s="2" t="s">
         <v>447</v>
       </c>
-      <c r="C9" s="3" t="s">
-        <v>885</v>
+      <c r="C9" s="2" t="s">
+        <v>713</v>
       </c>
     </row>
     <row r="10" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B10" s="3" t="s">
+      <c r="B10" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="C10" s="3" t="s">
-        <v>886</v>
+      <c r="C10" s="2" t="s">
+        <v>714</v>
       </c>
     </row>
     <row r="11" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B11" s="3" t="s">
+      <c r="B11" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="C11" s="3" t="s">
-        <v>887</v>
+      <c r="C11" s="2" t="s">
+        <v>715</v>
       </c>
     </row>
     <row r="12" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B12" s="3" t="s">
+      <c r="B12" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="C12" s="3" t="s">
-        <v>888</v>
+      <c r="C12" s="2" t="s">
+        <v>716</v>
       </c>
     </row>
     <row r="13" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B13" s="3" t="s">
+      <c r="B13" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="C13" s="3" t="s">
-        <v>889</v>
+      <c r="C13" s="2" t="s">
+        <v>717</v>
       </c>
     </row>
     <row r="14" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B14" s="3" t="s">
+      <c r="B14" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="C14" s="3" t="s">
-        <v>890</v>
+      <c r="C14" s="2" t="s">
+        <v>718</v>
       </c>
     </row>
     <row r="15" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B15" s="3" t="s">
+      <c r="B15" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="C15" s="3" t="s">
-        <v>891</v>
+      <c r="C15" s="2" t="s">
+        <v>719</v>
       </c>
     </row>
     <row r="16" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B16" s="3" t="s">
+      <c r="B16" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="C16" s="3" t="s">
-        <v>892</v>
+      <c r="C16" s="2" t="s">
+        <v>720</v>
       </c>
     </row>
     <row r="17" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B17" s="3" t="s">
+      <c r="B17" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="C17" s="3" t="s">
-        <v>893</v>
+      <c r="C17" s="2" t="s">
+        <v>721</v>
       </c>
     </row>
     <row r="18" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B18" s="3" t="s">
-        <v>894</v>
-      </c>
-      <c r="C18" s="3" t="s">
-        <v>895</v>
+      <c r="B18" s="2" t="s">
+        <v>722</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>723</v>
       </c>
     </row>
     <row r="19" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B19" s="3" t="s">
+      <c r="B19" s="2" t="s">
         <v>82</v>
       </c>
-      <c r="C19" s="3" t="s">
-        <v>896</v>
+      <c r="C19" s="2" t="s">
+        <v>724</v>
       </c>
     </row>
     <row r="20" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B20" s="3" t="s">
+      <c r="B20" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="C20" s="3" t="s">
-        <v>897</v>
+      <c r="C20" s="2" t="s">
+        <v>725</v>
       </c>
     </row>
     <row r="21" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B21" s="3" t="s">
+      <c r="B21" s="2" t="s">
         <v>86</v>
       </c>
-      <c r="C21" s="3" t="s">
-        <v>897</v>
+      <c r="C21" s="2" t="s">
+        <v>725</v>
       </c>
     </row>
     <row r="22" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B22" s="3" t="s">
+      <c r="B22" s="2" t="s">
         <v>88</v>
       </c>
-      <c r="C22" s="3" t="s">
-        <v>897</v>
+      <c r="C22" s="2" t="s">
+        <v>725</v>
       </c>
     </row>
     <row r="23" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B23" s="3" t="s">
+      <c r="B23" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="C23" s="3" t="s">
-        <v>897</v>
+      <c r="C23" s="2" t="s">
+        <v>725</v>
       </c>
     </row>
     <row r="24" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B24" s="3" t="s">
+      <c r="B24" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="C24" s="3" t="s">
-        <v>897</v>
+      <c r="C24" s="2" t="s">
+        <v>725</v>
       </c>
     </row>
     <row r="25" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B25" s="3" t="s">
+      <c r="B25" s="2" t="s">
         <v>94</v>
       </c>
-      <c r="C25" s="3" t="s">
-        <v>898</v>
+      <c r="C25" s="2" t="s">
+        <v>726</v>
       </c>
     </row>
     <row r="26" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B26" s="3" t="s">
+      <c r="B26" s="2" t="s">
         <v>96</v>
       </c>
-      <c r="C26" s="3" t="s">
-        <v>899</v>
+      <c r="C26" s="2" t="s">
+        <v>727</v>
       </c>
     </row>
     <row r="27" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B27" s="3" t="s">
-        <v>900</v>
-      </c>
-      <c r="C27" s="3" t="s">
-        <v>901</v>
+      <c r="B27" s="2" t="s">
+        <v>728</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>729</v>
       </c>
     </row>
     <row r="28" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B28" s="3" t="s">
+      <c r="B28" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="C28" s="3" t="s">
-        <v>902</v>
+      <c r="C28" s="2" t="s">
+        <v>730</v>
       </c>
     </row>
     <row r="29" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B29" s="3" t="s">
+      <c r="B29" s="2" t="s">
         <v>102</v>
       </c>
-      <c r="C29" s="3" t="s">
-        <v>903</v>
+      <c r="C29" s="2" t="s">
+        <v>731</v>
       </c>
     </row>
     <row r="30" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B30" s="3" t="s">
+      <c r="B30" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="C30" s="3" t="s">
-        <v>904</v>
+      <c r="C30" s="2" t="s">
+        <v>732</v>
       </c>
     </row>
     <row r="31" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B31" s="3" t="s">
+      <c r="B31" s="2" t="s">
         <v>116</v>
       </c>
-      <c r="C31" s="3" t="s">
-        <v>905</v>
+      <c r="C31" s="2" t="s">
+        <v>733</v>
       </c>
     </row>
     <row r="32" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B32" s="3" t="s">
+      <c r="B32" s="2" t="s">
         <v>152</v>
       </c>
-      <c r="C32" s="3" t="s">
-        <v>906</v>
+      <c r="C32" s="2" t="s">
+        <v>734</v>
       </c>
     </row>
     <row r="33" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B33" s="3" t="s">
+      <c r="B33" s="2" t="s">
         <v>134</v>
       </c>
-      <c r="C33" s="3" t="s">
-        <v>907</v>
+      <c r="C33" s="2" t="s">
+        <v>735</v>
       </c>
     </row>
     <row r="34" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B34" s="3" t="s">
-        <v>908</v>
-      </c>
-      <c r="C34" s="3" t="s">
-        <v>909</v>
+      <c r="B34" s="2" t="s">
+        <v>736</v>
+      </c>
+      <c r="C34" s="2" t="s">
+        <v>737</v>
       </c>
     </row>
     <row r="35" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B35" s="3" t="s">
+      <c r="B35" s="2" t="s">
         <v>136</v>
       </c>
-      <c r="C35" s="3" t="s">
-        <v>910</v>
+      <c r="C35" s="2" t="s">
+        <v>738</v>
       </c>
     </row>
     <row r="36" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B36" s="3" t="s">
+      <c r="B36" s="2" t="s">
         <v>138</v>
       </c>
-      <c r="C36" s="3" t="s">
-        <v>911</v>
+      <c r="C36" s="2" t="s">
+        <v>739</v>
       </c>
     </row>
     <row r="37" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B37" s="3" t="s">
+      <c r="B37" s="2" t="s">
         <v>140</v>
       </c>
-      <c r="C37" s="3" t="s">
-        <v>912</v>
+      <c r="C37" s="2" t="s">
+        <v>740</v>
       </c>
     </row>
     <row r="38" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B38" s="3" t="s">
+      <c r="B38" s="2" t="s">
         <v>142</v>
       </c>
-      <c r="C38" s="3" t="s">
-        <v>913</v>
+      <c r="C38" s="2" t="s">
+        <v>741</v>
       </c>
     </row>
     <row r="39" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B39" s="3" t="s">
+      <c r="B39" s="2" t="s">
         <v>343</v>
       </c>
-      <c r="C39" s="3" t="s">
-        <v>914</v>
+      <c r="C39" s="2" t="s">
+        <v>742</v>
       </c>
     </row>
     <row r="40" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B40" s="3" t="s">
+      <c r="B40" s="2" t="s">
         <v>144</v>
       </c>
-      <c r="C40" s="3" t="s">
-        <v>915</v>
+      <c r="C40" s="2" t="s">
+        <v>743</v>
       </c>
     </row>
     <row r="41" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B41" s="3" t="s">
+      <c r="B41" s="2" t="s">
         <v>146</v>
       </c>
-      <c r="C41" s="3" t="s">
-        <v>916</v>
+      <c r="C41" s="2" t="s">
+        <v>744</v>
       </c>
     </row>
     <row r="42" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B42" s="3" t="s">
+      <c r="B42" s="2" t="s">
         <v>148</v>
       </c>
-      <c r="C42" s="3" t="s">
-        <v>917</v>
+      <c r="C42" s="2" t="s">
+        <v>745</v>
       </c>
     </row>
     <row r="43" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B43" s="3" t="s">
+      <c r="B43" s="2" t="s">
         <v>150</v>
       </c>
-      <c r="C43" s="3" t="s">
-        <v>918</v>
+      <c r="C43" s="2" t="s">
+        <v>746</v>
       </c>
     </row>
     <row r="44" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B44" s="3" t="s">
+      <c r="B44" s="2" t="s">
         <v>174</v>
       </c>
-      <c r="C44" s="3" t="s">
-        <v>919</v>
+      <c r="C44" s="2" t="s">
+        <v>747</v>
       </c>
     </row>
     <row r="45" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B45" s="3" t="s">
+      <c r="B45" s="2" t="s">
         <v>154</v>
       </c>
-      <c r="C45" s="3" t="s">
-        <v>920</v>
+      <c r="C45" s="2" t="s">
+        <v>748</v>
       </c>
     </row>
     <row r="46" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B46" s="3" t="s">
+      <c r="B46" s="2" t="s">
         <v>156</v>
       </c>
-      <c r="C46" s="3" t="s">
-        <v>921</v>
+      <c r="C46" s="2" t="s">
+        <v>749</v>
       </c>
     </row>
     <row r="47" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B47" s="3" t="s">
+      <c r="B47" s="2" t="s">
         <v>158</v>
       </c>
-      <c r="C47" s="3" t="s">
-        <v>922</v>
+      <c r="C47" s="2" t="s">
+        <v>750</v>
       </c>
     </row>
     <row r="48" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B48" s="3" t="s">
+      <c r="B48" s="2" t="s">
         <v>160</v>
       </c>
-      <c r="C48" s="3" t="s">
-        <v>923</v>
+      <c r="C48" s="2" t="s">
+        <v>751</v>
       </c>
     </row>
     <row r="49" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B49" s="3" t="s">
+      <c r="B49" s="2" t="s">
         <v>162</v>
       </c>
-      <c r="C49" s="3" t="s">
-        <v>924</v>
+      <c r="C49" s="2" t="s">
+        <v>752</v>
       </c>
     </row>
     <row r="50" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B50" s="3" t="s">
+      <c r="B50" s="2" t="s">
         <v>164</v>
       </c>
-      <c r="C50" s="3" t="s">
-        <v>925</v>
+      <c r="C50" s="2" t="s">
+        <v>753</v>
       </c>
     </row>
     <row r="51" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B51" s="3" t="s">
+      <c r="B51" s="2" t="s">
         <v>166</v>
       </c>
-      <c r="C51" s="3" t="s">
-        <v>926</v>
+      <c r="C51" s="2" t="s">
+        <v>754</v>
       </c>
     </row>
     <row r="52" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B52" s="3" t="s">
+      <c r="B52" s="2" t="s">
         <v>168</v>
       </c>
-      <c r="C52" s="3" t="s">
-        <v>927</v>
+      <c r="C52" s="2" t="s">
+        <v>755</v>
       </c>
     </row>
     <row r="53" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B53" s="3" t="s">
+      <c r="B53" s="2" t="s">
         <v>170</v>
       </c>
-      <c r="C53" s="3" t="s">
-        <v>928</v>
+      <c r="C53" s="2" t="s">
+        <v>756</v>
       </c>
     </row>
     <row r="54" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B54" s="3" t="s">
+      <c r="B54" s="2" t="s">
         <v>172</v>
       </c>
-      <c r="C54" s="3" t="s">
-        <v>905</v>
+      <c r="C54" s="2" t="s">
+        <v>733</v>
       </c>
     </row>
     <row r="55" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B55" s="3" t="s">
+      <c r="B55" s="2" t="s">
         <v>176</v>
       </c>
-      <c r="C55" s="3" t="s">
-        <v>929</v>
+      <c r="C55" s="2" t="s">
+        <v>757</v>
       </c>
     </row>
     <row r="56" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B56" s="3" t="s">
+      <c r="B56" s="2" t="s">
         <v>178</v>
       </c>
-      <c r="C56" s="3" t="s">
-        <v>930</v>
+      <c r="C56" s="2" t="s">
+        <v>758</v>
       </c>
     </row>
     <row r="57" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B57" s="3" t="s">
+      <c r="B57" s="2" t="s">
         <v>180</v>
       </c>
-      <c r="C57" s="3" t="s">
-        <v>931</v>
+      <c r="C57" s="2" t="s">
+        <v>759</v>
       </c>
     </row>
     <row r="58" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B58" s="3" t="s">
-        <v>932</v>
-      </c>
-      <c r="C58" s="3" t="s">
-        <v>933</v>
+      <c r="B58" s="2" t="s">
+        <v>760</v>
+      </c>
+      <c r="C58" s="2" t="s">
+        <v>761</v>
       </c>
     </row>
     <row r="59" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B59" s="3" t="s">
-        <v>934</v>
-      </c>
-      <c r="C59" s="3" t="s">
-        <v>935</v>
+      <c r="B59" s="2" t="s">
+        <v>762</v>
+      </c>
+      <c r="C59" s="2" t="s">
+        <v>763</v>
       </c>
     </row>
     <row r="60" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B60" s="3" t="s">
-        <v>936</v>
-      </c>
-      <c r="C60" s="3" t="s">
-        <v>937</v>
+      <c r="B60" s="2" t="s">
+        <v>764</v>
+      </c>
+      <c r="C60" s="2" t="s">
+        <v>765</v>
       </c>
     </row>
     <row r="61" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B61" s="3" t="s">
-        <v>792</v>
-      </c>
-      <c r="C61" s="3" t="s">
-        <v>938</v>
+      <c r="B61" s="2" t="s">
+        <v>643</v>
+      </c>
+      <c r="C61" s="2" t="s">
+        <v>766</v>
       </c>
     </row>
     <row r="62" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B62" s="3" t="s">
-        <v>794</v>
-      </c>
-      <c r="C62" s="3" t="s">
-        <v>939</v>
+      <c r="B62" s="2" t="s">
+        <v>645</v>
+      </c>
+      <c r="C62" s="2" t="s">
+        <v>767</v>
       </c>
     </row>
     <row r="63" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B63" s="3" t="s">
-        <v>796</v>
-      </c>
-      <c r="C63" s="3" t="s">
-        <v>940</v>
+      <c r="B63" s="2" t="s">
+        <v>647</v>
+      </c>
+      <c r="C63" s="2" t="s">
+        <v>768</v>
       </c>
     </row>
     <row r="64" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B64" s="3" t="s">
-        <v>798</v>
-      </c>
-      <c r="C64" s="3" t="s">
-        <v>941</v>
+      <c r="B64" s="2" t="s">
+        <v>649</v>
+      </c>
+      <c r="C64" s="2" t="s">
+        <v>769</v>
       </c>
     </row>
     <row r="65" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B65" s="3" t="s">
-        <v>800</v>
-      </c>
-      <c r="C65" s="3" t="s">
-        <v>942</v>
+      <c r="B65" s="2" t="s">
+        <v>651</v>
+      </c>
+      <c r="C65" s="2" t="s">
+        <v>770</v>
       </c>
     </row>
     <row r="66" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B66" s="3" t="s">
-        <v>943</v>
-      </c>
-      <c r="C66" s="3" t="s">
-        <v>944</v>
+      <c r="B66" s="2" t="s">
+        <v>771</v>
+      </c>
+      <c r="C66" s="2" t="s">
+        <v>772</v>
       </c>
     </row>
     <row r="67" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B67" s="3" t="s">
+      <c r="B67" s="2" t="s">
         <v>314</v>
       </c>
-      <c r="C67" s="3" t="s">
-        <v>945</v>
+      <c r="C67" s="2" t="s">
+        <v>773</v>
       </c>
     </row>
     <row r="68" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B68" s="3" t="s">
+      <c r="B68" s="2" t="s">
         <v>328</v>
       </c>
-      <c r="C68" s="3" t="s">
-        <v>946</v>
+      <c r="C68" s="2" t="s">
+        <v>774</v>
       </c>
     </row>
   </sheetData>
@@ -8119,251 +7479,251 @@
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B1" s="6" t="s">
+      <c r="B1" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="6" t="s">
+      <c r="C1" s="5" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="2" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B2" s="6" t="s">
-        <v>947</v>
-      </c>
-      <c r="C2" s="6" t="s">
-        <v>948</v>
+      <c r="B2" s="5" t="s">
+        <v>775</v>
+      </c>
+      <c r="C2" s="5" t="s">
+        <v>776</v>
       </c>
     </row>
     <row r="3" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B3" s="6" t="s">
+      <c r="B3" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="C3" s="6" t="s">
-        <v>949</v>
+      <c r="C3" s="5" t="s">
+        <v>777</v>
       </c>
     </row>
     <row r="4" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B4" s="6" t="s">
+      <c r="B4" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="C4" s="6" t="s">
-        <v>880</v>
+      <c r="C4" s="5" t="s">
+        <v>708</v>
       </c>
     </row>
     <row r="5" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B5" s="6" t="s">
+      <c r="B5" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="C5" s="6" t="s">
-        <v>913</v>
+      <c r="C5" s="5" t="s">
+        <v>741</v>
       </c>
     </row>
     <row r="6" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B6" s="6" t="s">
+      <c r="B6" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="C6" s="6" t="s">
-        <v>950</v>
+      <c r="C6" s="5" t="s">
+        <v>778</v>
       </c>
     </row>
     <row r="7" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B7" s="6" t="s">
+      <c r="B7" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="C7" s="6" t="s">
-        <v>951</v>
+      <c r="C7" s="5" t="s">
+        <v>779</v>
       </c>
     </row>
     <row r="8" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B8" s="6" t="s">
+      <c r="B8" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="C8" s="6" t="s">
-        <v>952</v>
+      <c r="C8" s="5" t="s">
+        <v>780</v>
       </c>
     </row>
     <row r="9" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B9" s="6" t="s">
-        <v>953</v>
-      </c>
-      <c r="C9" s="6" t="s">
-        <v>954</v>
+      <c r="B9" s="5" t="s">
+        <v>781</v>
+      </c>
+      <c r="C9" s="5" t="s">
+        <v>782</v>
       </c>
     </row>
     <row r="10" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B10" s="6" t="s">
+      <c r="B10" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="C10" s="6" t="s">
-        <v>955</v>
+      <c r="C10" s="5" t="s">
+        <v>783</v>
       </c>
     </row>
     <row r="11" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B11" s="6" t="s">
+      <c r="B11" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="C11" s="6" t="s">
-        <v>956</v>
+      <c r="C11" s="5" t="s">
+        <v>784</v>
       </c>
     </row>
     <row r="12" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B12" s="6" t="s">
+      <c r="B12" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="C12" s="6" t="s">
-        <v>957</v>
+      <c r="C12" s="5" t="s">
+        <v>785</v>
       </c>
     </row>
     <row r="13" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B13" s="6" t="s">
+      <c r="B13" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="C13" s="6" t="s">
-        <v>958</v>
+      <c r="C13" s="5" t="s">
+        <v>786</v>
       </c>
     </row>
     <row r="14" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B14" s="6" t="s">
+      <c r="B14" s="5" t="s">
         <v>78</v>
       </c>
-      <c r="C14" s="6" t="s">
-        <v>959</v>
+      <c r="C14" s="5" t="s">
+        <v>787</v>
       </c>
     </row>
     <row r="15" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B15" s="6" t="s">
+      <c r="B15" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="C15" s="6" t="s">
-        <v>882</v>
+      <c r="C15" s="5" t="s">
+        <v>710</v>
       </c>
     </row>
     <row r="16" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B16" s="6" t="s">
+      <c r="B16" s="5" t="s">
         <v>52</v>
       </c>
-      <c r="C16" s="6" t="s">
-        <v>881</v>
+      <c r="C16" s="5" t="s">
+        <v>709</v>
       </c>
     </row>
     <row r="17" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B17" s="6" t="s">
+      <c r="B17" s="5" t="s">
         <v>62</v>
       </c>
-      <c r="C17" s="6" t="s">
-        <v>883</v>
+      <c r="C17" s="5" t="s">
+        <v>711</v>
       </c>
     </row>
     <row r="18" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B18" s="6" t="s">
+      <c r="B18" s="5" t="s">
         <v>64</v>
       </c>
-      <c r="C18" s="6" t="s">
-        <v>960</v>
+      <c r="C18" s="5" t="s">
+        <v>788</v>
       </c>
     </row>
     <row r="19" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B19" s="6" t="s">
+      <c r="B19" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="C19" s="6" t="s">
-        <v>949</v>
+      <c r="C19" s="5" t="s">
+        <v>777</v>
       </c>
     </row>
     <row r="20" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B20" s="6" t="s">
+      <c r="B20" s="5" t="s">
         <v>132</v>
       </c>
-      <c r="C20" s="6" t="s">
-        <v>961</v>
+      <c r="C20" s="5" t="s">
+        <v>789</v>
       </c>
     </row>
     <row r="21" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B21" s="6" t="s">
+      <c r="B21" s="5" t="s">
         <v>98</v>
       </c>
-      <c r="C21" s="6" t="s">
-        <v>962</v>
+      <c r="C21" s="5" t="s">
+        <v>790</v>
       </c>
     </row>
     <row r="22" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B22" s="6" t="s">
+      <c r="B22" s="5" t="s">
         <v>114</v>
       </c>
-      <c r="C22" s="6" t="s">
-        <v>963</v>
+      <c r="C22" s="5" t="s">
+        <v>791</v>
       </c>
     </row>
     <row r="23" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B23" s="6" t="s">
+      <c r="B23" s="5" t="s">
         <v>118</v>
       </c>
-      <c r="C23" s="6" t="s">
-        <v>964</v>
+      <c r="C23" s="5" t="s">
+        <v>792</v>
       </c>
     </row>
     <row r="24" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B24" s="6" t="s">
+      <c r="B24" s="5" t="s">
         <v>232</v>
       </c>
-      <c r="C24" s="6" t="s">
-        <v>965</v>
+      <c r="C24" s="5" t="s">
+        <v>793</v>
       </c>
     </row>
     <row r="25" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B25" s="6" t="s">
+      <c r="B25" s="5" t="s">
         <v>152</v>
       </c>
-      <c r="C25" s="6" t="s">
-        <v>906</v>
+      <c r="C25" s="5" t="s">
+        <v>734</v>
       </c>
     </row>
     <row r="26" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B26" s="6" t="s">
+      <c r="B26" s="5" t="s">
         <v>174</v>
       </c>
-      <c r="C26" s="6" t="s">
-        <v>919</v>
+      <c r="C26" s="5" t="s">
+        <v>747</v>
       </c>
     </row>
     <row r="27" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B27" s="6" t="s">
-        <v>966</v>
-      </c>
-      <c r="C27" s="6" t="s">
-        <v>895</v>
+      <c r="B27" s="5" t="s">
+        <v>794</v>
+      </c>
+      <c r="C27" s="5" t="s">
+        <v>723</v>
       </c>
     </row>
     <row r="28" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B28" s="6" t="s">
-        <v>967</v>
-      </c>
-      <c r="C28" s="6" t="s">
-        <v>968</v>
+      <c r="B28" s="5" t="s">
+        <v>795</v>
+      </c>
+      <c r="C28" s="5" t="s">
+        <v>796</v>
       </c>
     </row>
     <row r="29" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B29" s="6" t="s">
+      <c r="B29" s="5" t="s">
         <v>268</v>
       </c>
-      <c r="C29" s="6" t="s">
-        <v>910</v>
+      <c r="C29" s="5" t="s">
+        <v>738</v>
       </c>
     </row>
     <row r="30" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B30" s="6" t="s">
+      <c r="B30" s="5" t="s">
         <v>312</v>
       </c>
-      <c r="C30" s="6" t="s">
-        <v>969</v>
+      <c r="C30" s="5" t="s">
+        <v>797</v>
       </c>
     </row>
     <row r="31" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B31" s="6" t="s">
+      <c r="B31" s="5" t="s">
         <v>336</v>
       </c>
-      <c r="C31" s="6" t="s">
-        <v>970</v>
+      <c r="C31" s="5" t="s">
+        <v>798</v>
       </c>
     </row>
   </sheetData>
@@ -8378,107 +7738,107 @@
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B1" s="4" t="s">
+      <c r="B1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="4" t="s">
+      <c r="C1" s="3" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="2" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B2" s="4" t="s">
+      <c r="B2" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="C2" s="4" t="s">
-        <v>971</v>
+      <c r="C2" s="3" t="s">
+        <v>799</v>
       </c>
     </row>
     <row r="3" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B3" s="4" t="s">
+      <c r="B3" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C3" s="4" t="s">
-        <v>972</v>
+      <c r="C3" s="3" t="s">
+        <v>800</v>
       </c>
     </row>
     <row r="4" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B4" s="4" t="s">
+      <c r="B4" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="C4" s="4" t="s">
-        <v>964</v>
+      <c r="C4" s="3" t="s">
+        <v>792</v>
       </c>
     </row>
     <row r="5" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B5" s="4" t="s">
+      <c r="B5" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="C5" s="4" t="s">
-        <v>949</v>
+      <c r="C5" s="3" t="s">
+        <v>777</v>
       </c>
     </row>
     <row r="6" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B6" s="4" t="s">
+      <c r="B6" s="3" t="s">
         <v>78</v>
       </c>
-      <c r="C6" s="4" t="s">
-        <v>895</v>
+      <c r="C6" s="3" t="s">
+        <v>723</v>
       </c>
     </row>
     <row r="7" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B7" s="4" t="s">
+      <c r="B7" s="3" t="s">
         <v>132</v>
       </c>
-      <c r="C7" s="4" t="s">
+      <c r="C7" s="3" t="s">
         <v>429</v>
       </c>
     </row>
     <row r="8" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B8" s="4" t="s">
+      <c r="B8" s="3" t="s">
         <v>232</v>
       </c>
-      <c r="C8" s="4" t="s">
-        <v>973</v>
+      <c r="C8" s="3" t="s">
+        <v>801</v>
       </c>
     </row>
     <row r="9" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B9" s="4" t="s">
-        <v>966</v>
-      </c>
-      <c r="C9" s="4" t="s">
-        <v>974</v>
+      <c r="B9" s="3" t="s">
+        <v>794</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>802</v>
       </c>
     </row>
     <row r="10" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B10" s="4" t="s">
-        <v>967</v>
-      </c>
-      <c r="C10" s="4" t="s">
-        <v>975</v>
+      <c r="B10" s="3" t="s">
+        <v>795</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>803</v>
       </c>
     </row>
     <row r="11" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B11" s="4" t="s">
+      <c r="B11" s="3" t="s">
         <v>268</v>
       </c>
-      <c r="C11" s="4" t="s">
-        <v>976</v>
+      <c r="C11" s="3" t="s">
+        <v>804</v>
       </c>
     </row>
     <row r="12" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B12" s="4" t="s">
+      <c r="B12" s="3" t="s">
         <v>312</v>
       </c>
-      <c r="C12" s="4" t="s">
-        <v>977</v>
+      <c r="C12" s="3" t="s">
+        <v>805</v>
       </c>
     </row>
     <row r="13" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B13" s="4" t="s">
+      <c r="B13" s="3" t="s">
         <v>336</v>
       </c>
-      <c r="C13" s="4" t="s">
-        <v>978</v>
+      <c r="C13" s="3" t="s">
+        <v>806</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/Editor/DataDic/Data.xlsx
+++ b/Assets/Editor/DataDic/Data.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="17385" windowHeight="7860" activeTab="2"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="17385" windowHeight="7860" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="FishData" sheetId="1" r:id="rId1"/>
@@ -20,12 +20,15 @@
     <sheet name="OperateData" sheetId="7" r:id="rId6"/>
     <sheet name="NPCFunctionData" sheetId="8" r:id="rId7"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">测试!$B$1:$C$56</definedName>
+  </definedNames>
   <calcPr calcId="162913"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="973" uniqueCount="808">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="927" uniqueCount="765">
   <si>
     <t>Key</t>
   </si>
@@ -1044,13 +1047,7 @@
     <t>别墅二楼</t>
   </si>
   <si>
-    <t>4765</t>
-  </si>
-  <si>
     <t>酒馆卧室</t>
-  </si>
-  <si>
-    <t>2270</t>
   </si>
   <si>
     <t>卧室</t>
@@ -1102,15 +1099,9 @@
     <t>教堂</t>
   </si>
   <si>
-    <t>3115</t>
-  </si>
-  <si>
     <t>村公所卧室</t>
   </si>
   <si>
-    <t>2015</t>
-  </si>
-  <si>
     <t>城门</t>
   </si>
   <si>
@@ -1129,21 +1120,12 @@
     <t>俱乐部阁楼</t>
   </si>
   <si>
-    <t>3300</t>
-  </si>
-  <si>
     <t>棚子</t>
   </si>
   <si>
-    <t>3891</t>
-  </si>
-  <si>
     <t>客栈二楼</t>
   </si>
   <si>
-    <t>5013</t>
-  </si>
-  <si>
     <t>19,30</t>
   </si>
   <si>
@@ -1153,1324 +1135,1217 @@
     <t>船坞</t>
   </si>
   <si>
-    <t>2637</t>
-  </si>
-  <si>
     <t>小棚子</t>
   </si>
   <si>
-    <t>3981</t>
-  </si>
-  <si>
     <t>我的农场</t>
   </si>
   <si>
-    <t>759</t>
-  </si>
-  <si>
     <t xml:space="preserve"> 22,0</t>
   </si>
   <si>
-    <t>3639</t>
-  </si>
-  <si>
-    <t>3404</t>
-  </si>
-  <si>
     <t>22,0</t>
   </si>
   <si>
     <t>村公所大厅</t>
   </si>
   <si>
-    <t>1420</t>
-  </si>
-  <si>
     <t>24,0</t>
   </si>
   <si>
     <t>工坊</t>
   </si>
   <si>
-    <t>1328</t>
-  </si>
-  <si>
     <t>畜牧店</t>
   </si>
   <si>
     <t>俱乐部</t>
   </si>
   <si>
-    <t>3297</t>
-  </si>
-  <si>
     <t>塔楼顶部</t>
   </si>
   <si>
-    <t>3350</t>
-  </si>
-  <si>
     <t>家具店偏室</t>
   </si>
   <si>
     <t>1112</t>
   </si>
   <si>
-    <t>2355</t>
-  </si>
-  <si>
     <t>水车房内部</t>
   </si>
   <si>
-    <t>4529</t>
-  </si>
-  <si>
     <t>小木屋</t>
   </si>
   <si>
-    <t>1208</t>
-  </si>
-  <si>
-    <t>4189</t>
-  </si>
-  <si>
     <t>家具店</t>
   </si>
   <si>
-    <t>4075</t>
-  </si>
-  <si>
-    <t>512</t>
-  </si>
-  <si>
-    <t>4409</t>
-  </si>
-  <si>
     <t>纺织店</t>
   </si>
   <si>
-    <t>4380</t>
-  </si>
-  <si>
-    <t>889</t>
-  </si>
-  <si>
     <t>塔楼</t>
   </si>
   <si>
-    <t>3286</t>
-  </si>
-  <si>
     <t>治安室</t>
   </si>
   <si>
-    <t>1912</t>
+    <t>帐篷内部</t>
+  </si>
+  <si>
+    <t>风车内部</t>
+  </si>
+  <si>
+    <t>客栈一楼</t>
+  </si>
+  <si>
+    <t>鱼摊内部</t>
+  </si>
+  <si>
+    <t>船坞二层</t>
+  </si>
+  <si>
+    <t>别墅大厅</t>
+  </si>
+  <si>
+    <t>教堂二楼</t>
+  </si>
+  <si>
+    <t>酒馆</t>
+  </si>
+  <si>
+    <t>村公所宴会厅</t>
+  </si>
+  <si>
+    <t>科学研究室</t>
+  </si>
+  <si>
+    <t>商店</t>
+  </si>
+  <si>
+    <t>武器店二楼</t>
+  </si>
+  <si>
+    <t>1001</t>
+  </si>
+  <si>
+    <t>床</t>
+  </si>
+  <si>
+    <t>1002</t>
+  </si>
+  <si>
+    <t>书架</t>
+  </si>
+  <si>
+    <t>1003</t>
+  </si>
+  <si>
+    <t>圆凳</t>
+  </si>
+  <si>
+    <t>1004</t>
+  </si>
+  <si>
+    <t>壁画</t>
+  </si>
+  <si>
+    <t>1005</t>
+  </si>
+  <si>
+    <t>梳妆台</t>
+  </si>
+  <si>
+    <t>1006</t>
+  </si>
+  <si>
+    <t>椅子</t>
+  </si>
+  <si>
+    <t>1007</t>
+  </si>
+  <si>
+    <t>1009</t>
+  </si>
+  <si>
+    <t>楼梯</t>
+  </si>
+  <si>
+    <t>1010</t>
+  </si>
+  <si>
+    <t>矮柜</t>
+  </si>
+  <si>
+    <t>1011</t>
+  </si>
+  <si>
+    <t>窗</t>
+  </si>
+  <si>
+    <t>箱子</t>
+  </si>
+  <si>
+    <t>1013</t>
+  </si>
+  <si>
+    <t>花盆</t>
+  </si>
+  <si>
+    <t>1014</t>
+  </si>
+  <si>
+    <t>蜡烛0</t>
+  </si>
+  <si>
+    <t>1015</t>
+  </si>
+  <si>
+    <t>蜡烛1</t>
+  </si>
+  <si>
+    <t>1016</t>
+  </si>
+  <si>
+    <t>长桌</t>
+  </si>
+  <si>
+    <t>1017</t>
+  </si>
+  <si>
+    <t>柜台</t>
+  </si>
+  <si>
+    <t>1018</t>
+  </si>
+  <si>
+    <t>长柜台竖</t>
+  </si>
+  <si>
+    <t>长柜台横</t>
+  </si>
+  <si>
+    <t>1020</t>
+  </si>
+  <si>
+    <t>窗户</t>
+  </si>
+  <si>
+    <t>1021</t>
+  </si>
+  <si>
+    <t>绿植1</t>
+  </si>
+  <si>
+    <t>1022</t>
+  </si>
+  <si>
+    <t>武器架</t>
+  </si>
+  <si>
+    <t>1023</t>
+  </si>
+  <si>
+    <t>服饰架</t>
+  </si>
+  <si>
+    <t>1024</t>
+  </si>
+  <si>
+    <t>武器柜横</t>
+  </si>
+  <si>
+    <t>武器柜右</t>
+  </si>
+  <si>
+    <t>壁画1</t>
+  </si>
+  <si>
+    <t>桌子</t>
+  </si>
+  <si>
+    <t>提灯</t>
+  </si>
+  <si>
+    <t>蜡烛吊灯</t>
+  </si>
+  <si>
+    <t>内门1</t>
+  </si>
+  <si>
+    <t>锻造炉-设施</t>
+  </si>
+  <si>
+    <t>储物箱(木)-设施</t>
+  </si>
+  <si>
+    <t>楼梯上</t>
+  </si>
+  <si>
+    <t>商店开关</t>
+  </si>
+  <si>
+    <t>外窗1</t>
+  </si>
+  <si>
+    <t>外窗2</t>
+  </si>
+  <si>
+    <t>外窗3</t>
+  </si>
+  <si>
+    <t>外窗招牌</t>
+  </si>
+  <si>
+    <t>宽门</t>
+  </si>
+  <si>
+    <t>红窄门</t>
+  </si>
+  <si>
+    <t>别墅一楼床</t>
+  </si>
+  <si>
+    <t>秋千</t>
+  </si>
+  <si>
+    <t>城内河</t>
+  </si>
+  <si>
+    <t>我的大门</t>
+  </si>
+  <si>
+    <t>公所大门</t>
+  </si>
+  <si>
+    <t>黄窄门</t>
+  </si>
+  <si>
+    <t>双门</t>
+  </si>
+  <si>
+    <t>棚子门</t>
+  </si>
+  <si>
+    <t>竖长椅</t>
+  </si>
+  <si>
+    <t>广场河</t>
+  </si>
+  <si>
+    <t>农田</t>
+  </si>
+  <si>
+    <t>稻草人</t>
+  </si>
+  <si>
+    <t>树墩</t>
+  </si>
+  <si>
+    <t>提灯侧</t>
+  </si>
+  <si>
+    <t>篝火</t>
+  </si>
+  <si>
+    <t>柴棚</t>
+  </si>
+  <si>
+    <t>牲畜棚</t>
+  </si>
+  <si>
+    <t>农场河</t>
+  </si>
+  <si>
+    <t>栅栏门</t>
+  </si>
+  <si>
+    <t>提灯外</t>
+  </si>
+  <si>
+    <t>商店街河</t>
+  </si>
+  <si>
+    <t>水井</t>
+  </si>
+  <si>
+    <t>长椅背面</t>
+  </si>
+  <si>
+    <t>普通门</t>
+  </si>
+  <si>
+    <t>黄门2</t>
+  </si>
+  <si>
+    <t>二楼门</t>
+  </si>
+  <si>
+    <t>植物店柜台</t>
+  </si>
+  <si>
+    <t>壁炉</t>
+  </si>
+  <si>
+    <t>单人床</t>
+  </si>
+  <si>
+    <t>豪华床</t>
+  </si>
+  <si>
+    <t>植物店书桌</t>
+  </si>
+  <si>
+    <t>红椅子左</t>
+  </si>
+  <si>
+    <t>红椅子斜右</t>
+  </si>
+  <si>
+    <t>壁画老女</t>
+  </si>
+  <si>
+    <t>春战场</t>
+  </si>
+  <si>
+    <t>秋战场</t>
+  </si>
+  <si>
+    <t>畜牧店柜台</t>
+  </si>
+  <si>
+    <t>床绿</t>
+  </si>
+  <si>
+    <t>床红</t>
+  </si>
+  <si>
+    <t>磨坊</t>
+  </si>
+  <si>
+    <t>帐篷</t>
+  </si>
+  <si>
+    <t>无偏转内门</t>
+  </si>
+  <si>
+    <t>夏战场</t>
+  </si>
+  <si>
+    <t>冬战场</t>
+  </si>
+  <si>
+    <t>旗子</t>
+  </si>
+  <si>
+    <t>家具柜台</t>
+  </si>
+  <si>
+    <t>家具店大床</t>
+  </si>
+  <si>
+    <t>家具店小床</t>
+  </si>
+  <si>
+    <t>冷餐台</t>
+  </si>
+  <si>
+    <t>破损牲畜棚</t>
+  </si>
+  <si>
+    <t>初级牲口棚</t>
+  </si>
+  <si>
+    <t>食物槽</t>
+  </si>
+  <si>
+    <t>水槽</t>
+  </si>
+  <si>
+    <t>收获篮</t>
+  </si>
+  <si>
+    <t>传送门</t>
+  </si>
+  <si>
+    <t>山地湖</t>
+  </si>
+  <si>
+    <t>城门河</t>
+  </si>
+  <si>
+    <t>1100</t>
+  </si>
+  <si>
+    <t>我的家</t>
+  </si>
+  <si>
+    <t>1101</t>
+  </si>
+  <si>
+    <t>民居1</t>
+  </si>
+  <si>
+    <t>1103</t>
+  </si>
+  <si>
+    <t>民居2</t>
+  </si>
+  <si>
+    <t>镇公所</t>
+  </si>
+  <si>
+    <t>1105</t>
+  </si>
+  <si>
+    <t>1106</t>
+  </si>
+  <si>
+    <t>钟楼</t>
+  </si>
+  <si>
+    <t>动物店</t>
+  </si>
+  <si>
+    <t>1109</t>
+  </si>
+  <si>
+    <t>装备店</t>
+  </si>
+  <si>
+    <t>1110</t>
+  </si>
+  <si>
+    <t>水车房</t>
+  </si>
+  <si>
+    <t>1111</t>
+  </si>
+  <si>
+    <t>民宅1</t>
+  </si>
+  <si>
+    <t>民宅2</t>
+  </si>
+  <si>
+    <t>1113</t>
+  </si>
+  <si>
+    <t>摊位</t>
+  </si>
+  <si>
+    <t>1114</t>
+  </si>
+  <si>
+    <t>大摊位</t>
+  </si>
+  <si>
+    <t>1115</t>
+  </si>
+  <si>
+    <t>1116</t>
+  </si>
+  <si>
+    <t>鱼店</t>
+  </si>
+  <si>
+    <t>1117</t>
+  </si>
+  <si>
+    <t>搅拌器</t>
+  </si>
+  <si>
+    <t>冰箱</t>
+  </si>
+  <si>
+    <t>储物箱(木)</t>
+  </si>
+  <si>
+    <t>储物箱(银)</t>
+  </si>
+  <si>
+    <t>储物箱(金)</t>
+  </si>
+  <si>
+    <t>搅拌器-设施</t>
+  </si>
+  <si>
+    <t>冰箱-设施</t>
+  </si>
+  <si>
+    <t>缝纫机-设施</t>
+  </si>
+  <si>
+    <t>绘写台-设施</t>
+  </si>
+  <si>
+    <t>冷餐台-设施</t>
+  </si>
+  <si>
+    <t>蒸煮锅-设施</t>
+  </si>
+  <si>
+    <t>烘烤炉-设施</t>
+  </si>
+  <si>
+    <t>酿造桶-设施</t>
+  </si>
+  <si>
+    <t>储物箱(银)-设施</t>
+  </si>
+  <si>
+    <t>储物箱(金)-设施</t>
+  </si>
+  <si>
+    <t>红椅子</t>
+  </si>
+  <si>
+    <t>时钟</t>
+  </si>
+  <si>
+    <t>紫椅子</t>
+  </si>
+  <si>
+    <t>别墅床</t>
+  </si>
+  <si>
+    <t>豪华梳妆台</t>
+  </si>
+  <si>
+    <t>钢琴</t>
+  </si>
+  <si>
+    <t>紫椅子翻转</t>
+  </si>
+  <si>
+    <t>占卜屋床</t>
+  </si>
+  <si>
+    <t>占卜柜台</t>
+  </si>
+  <si>
+    <t>魔镜</t>
+  </si>
+  <si>
+    <t>坐垫小凳</t>
+  </si>
+  <si>
+    <t>客栈双人床</t>
+  </si>
+  <si>
+    <t>红长沙发左</t>
+  </si>
+  <si>
+    <t>红长沙右</t>
+  </si>
+  <si>
+    <t>沙发红上</t>
+  </si>
+  <si>
+    <t>红椅子下</t>
+  </si>
+  <si>
+    <t>椅子红斜</t>
+  </si>
+  <si>
+    <t>红色单人床</t>
+  </si>
+  <si>
+    <t>客栈柜台</t>
+  </si>
+  <si>
+    <t>沙发侧暗</t>
+  </si>
+  <si>
+    <t>单人床黄</t>
+  </si>
+  <si>
+    <t>长沙发蓝左</t>
+  </si>
+  <si>
+    <t>蓝椅子下</t>
+  </si>
+  <si>
+    <t>纺织店柜台</t>
+  </si>
+  <si>
+    <t>椅子红下</t>
+  </si>
+  <si>
+    <t>椅子红上</t>
+  </si>
+  <si>
+    <t>床白</t>
+  </si>
+  <si>
+    <t>望远镜</t>
+  </si>
+  <si>
+    <t>教堂讲台</t>
+  </si>
+  <si>
+    <t>酒馆柜台</t>
+  </si>
+  <si>
+    <t>地铺</t>
+  </si>
+  <si>
+    <t>地铺2</t>
+  </si>
+  <si>
+    <t>朴素床</t>
+  </si>
+  <si>
+    <t>海边</t>
+  </si>
+  <si>
+    <t>纺织机</t>
+  </si>
+  <si>
+    <t>锻造炉</t>
+  </si>
+  <si>
+    <t>烘烤炉</t>
+  </si>
+  <si>
+    <t>酿造桶</t>
+  </si>
+  <si>
+    <t>绘写台</t>
+  </si>
+  <si>
+    <t>蒸煮锅</t>
+  </si>
+  <si>
+    <t>缝纫机</t>
+  </si>
+  <si>
+    <t>纺线机</t>
+  </si>
+  <si>
+    <t>织布机</t>
+  </si>
+  <si>
+    <t>制革机</t>
+  </si>
+  <si>
+    <t>自宅门</t>
+  </si>
+  <si>
+    <t>客栈</t>
+  </si>
+  <si>
+    <t>别墅</t>
+  </si>
+  <si>
+    <t>自宅</t>
+  </si>
+  <si>
+    <t>长椅下</t>
+  </si>
+  <si>
+    <t>水坑</t>
+  </si>
+  <si>
+    <t>玉米</t>
+  </si>
+  <si>
+    <t>8001</t>
+  </si>
+  <si>
+    <t>芜菁</t>
+  </si>
+  <si>
+    <t>8002</t>
+  </si>
+  <si>
+    <t>卷心菜</t>
+  </si>
+  <si>
+    <t>8003</t>
+  </si>
+  <si>
+    <t>大葱</t>
+  </si>
+  <si>
+    <t>8004</t>
+  </si>
+  <si>
+    <t>萝卜</t>
+  </si>
+  <si>
+    <t>8005</t>
+  </si>
+  <si>
+    <t>紫甘蓝</t>
+  </si>
+  <si>
+    <t>黄瓜</t>
+  </si>
+  <si>
+    <t>西兰花</t>
+  </si>
+  <si>
+    <t>番茄</t>
+  </si>
+  <si>
+    <t>胡萝卜</t>
+  </si>
+  <si>
+    <t>西瓜</t>
+  </si>
+  <si>
+    <t>辣椒</t>
+  </si>
+  <si>
+    <t>奇异果</t>
+  </si>
+  <si>
+    <t>茄子</t>
+  </si>
+  <si>
+    <t>豌豆</t>
+  </si>
+  <si>
+    <t>土豆</t>
+  </si>
+  <si>
+    <t>大蒜</t>
+  </si>
+  <si>
+    <t>芦笋</t>
+  </si>
+  <si>
+    <t>南瓜</t>
+  </si>
+  <si>
+    <t>小麦</t>
+  </si>
+  <si>
+    <t>啤酒花</t>
+  </si>
+  <si>
+    <t>葡萄</t>
+  </si>
+  <si>
+    <t>菠萝</t>
+  </si>
+  <si>
+    <t>咖啡</t>
+  </si>
+  <si>
+    <t>草莓</t>
+  </si>
+  <si>
+    <t>蓝莓</t>
+  </si>
+  <si>
+    <t>红薯</t>
+  </si>
+  <si>
+    <t>甜菜</t>
+  </si>
+  <si>
+    <t>1000</t>
+  </si>
+  <si>
+    <t>鲫鱼</t>
+  </si>
+  <si>
+    <t>鲮鱼</t>
+  </si>
+  <si>
+    <t>手套蟹.</t>
+  </si>
+  <si>
+    <t>丁鱼</t>
+  </si>
+  <si>
+    <t>锦鲤</t>
+  </si>
+  <si>
+    <t>线鱼</t>
+  </si>
+  <si>
+    <t>兰寿金鱼</t>
+  </si>
+  <si>
+    <t>樱桃鲑鱼</t>
+  </si>
+  <si>
+    <t>虹鳟鱼</t>
+  </si>
+  <si>
+    <t>鲷鱼</t>
+  </si>
+  <si>
+    <t>金鳟鱼</t>
+  </si>
+  <si>
+    <t>霓虹脂鲤</t>
+  </si>
+  <si>
+    <t>桃花鱼</t>
+  </si>
+  <si>
+    <t>鲑鱼</t>
+  </si>
+  <si>
+    <t>孔雀鱼</t>
+  </si>
+  <si>
+    <t>银龙鱼</t>
+  </si>
+  <si>
+    <t>洞穴天使鱼</t>
+  </si>
+  <si>
+    <t>沙丁鱼</t>
+  </si>
+  <si>
+    <t>竹荚鱼</t>
+  </si>
+  <si>
+    <t>海鳗</t>
+  </si>
+  <si>
+    <t>章鱼</t>
+  </si>
+  <si>
+    <t>比目鱼</t>
+  </si>
+  <si>
+    <t>河豚鱼</t>
+  </si>
+  <si>
+    <t>水母</t>
+  </si>
+  <si>
+    <t>条石鲷</t>
+  </si>
+  <si>
+    <t>红鲷鱼</t>
+  </si>
+  <si>
+    <t>蓝蟹</t>
+  </si>
+  <si>
+    <t>鲯鳅鱼</t>
+  </si>
+  <si>
+    <t>龙虾</t>
+  </si>
+  <si>
+    <t>金枪鱼</t>
+  </si>
+  <si>
+    <t>斑马狮子鱼</t>
+  </si>
+  <si>
+    <t>点击虚拟NPC</t>
+  </si>
+  <si>
+    <t>锄地</t>
+  </si>
+  <si>
+    <t>浇水</t>
+  </si>
+  <si>
+    <t>播种</t>
+  </si>
+  <si>
+    <t>收获</t>
+  </si>
+  <si>
+    <t>收割</t>
+  </si>
+  <si>
+    <t>铲除</t>
+  </si>
+  <si>
+    <t>点击虚拟NPC事件</t>
+  </si>
+  <si>
+    <t>移动物体事件</t>
+  </si>
+  <si>
+    <t>卸载战斗、恢复电影</t>
+  </si>
+  <si>
+    <t>春之山脉胜利</t>
+  </si>
+  <si>
+    <t>夏之丛林胜利</t>
+  </si>
+  <si>
+    <t>秋风之谷胜利</t>
+  </si>
+  <si>
+    <t>冬之雪原胜利</t>
+  </si>
+  <si>
+    <t>点击NPC赠送</t>
+  </si>
+  <si>
+    <t>301</t>
+  </si>
+  <si>
+    <t>表白</t>
+  </si>
+  <si>
+    <t>打开商店</t>
+  </si>
+  <si>
+    <t>队伍邀请</t>
+  </si>
+  <si>
+    <t>分配牧场</t>
+  </si>
+  <si>
+    <t>放生动物</t>
+  </si>
+  <si>
+    <t>310</t>
+  </si>
+  <si>
+    <t>投喂动物</t>
+  </si>
+  <si>
+    <t>打开天气预报</t>
+  </si>
+  <si>
+    <t>第一次离开家</t>
+  </si>
+  <si>
+    <t>查看角色</t>
+  </si>
+  <si>
+    <t>打开联装背包</t>
+  </si>
+  <si>
+    <t>垂钓</t>
+  </si>
+  <si>
+    <t>创建或打开杂物箱</t>
+  </si>
+  <si>
+    <t>4001</t>
+  </si>
+  <si>
+    <t>商店地图事件</t>
+  </si>
+  <si>
+    <t>坐下</t>
+  </si>
+  <si>
+    <t>离开椅子</t>
+  </si>
+  <si>
+    <t>选择睡眠</t>
+  </si>
+  <si>
+    <t>跳转地图到卧室</t>
+  </si>
+  <si>
+    <t>跳转地图 卧室-大厅</t>
+  </si>
+  <si>
+    <t>商店开门</t>
+  </si>
+  <si>
+    <t>商店关门</t>
+  </si>
+  <si>
+    <t>关闭栅栏</t>
+  </si>
+  <si>
+    <t>打开栅栏</t>
+  </si>
+  <si>
+    <t>收竿</t>
+  </si>
+  <si>
+    <t>装满水</t>
+  </si>
+  <si>
+    <t>第一晚限制</t>
+  </si>
+  <si>
+    <t>赠送礼物</t>
+  </si>
+  <si>
+    <t>打开春战场</t>
+  </si>
+  <si>
+    <t>打开夏战场</t>
+  </si>
+  <si>
+    <t>打开秋战场</t>
+  </si>
+  <si>
+    <t>打开冬战场</t>
+  </si>
+  <si>
+    <t>打开商店界面</t>
+  </si>
+  <si>
+    <t>建造牲畜棚</t>
+  </si>
+  <si>
+    <t>升级牧场</t>
+  </si>
+  <si>
+    <t>坐到沙发上</t>
+  </si>
+  <si>
+    <t>离开沙发</t>
+  </si>
+  <si>
+    <t>500</t>
+  </si>
+  <si>
+    <t>第一天睡醒</t>
+  </si>
+  <si>
+    <t>7000</t>
+  </si>
+  <si>
+    <t>传送事件</t>
+  </si>
+  <si>
+    <t>7001</t>
+  </si>
+  <si>
+    <t>吃食物</t>
+  </si>
+  <si>
+    <t>点击NPC事件</t>
+  </si>
+  <si>
+    <t>点击布莱兹</t>
+  </si>
+  <si>
+    <t>点击玛德琳</t>
+  </si>
+  <si>
+    <t>点击丝特芬妮</t>
+  </si>
+  <si>
+    <t>点击格吉尔</t>
+  </si>
+  <si>
+    <t>8100</t>
+  </si>
+  <si>
+    <t>点击鸡</t>
+  </si>
+  <si>
+    <t>春战斗胜利</t>
+  </si>
+  <si>
+    <t>第一次战斗结束</t>
+  </si>
+  <si>
+    <t>0</t>
+  </si>
+  <si>
+    <t>....</t>
+  </si>
+  <si>
+    <t>查看</t>
+  </si>
+  <si>
+    <t>开始营业</t>
+  </si>
+  <si>
+    <t>结束营业</t>
+  </si>
+  <si>
+    <t>打开</t>
+  </si>
+  <si>
+    <t>15</t>
+  </si>
+  <si>
+    <t>关闭</t>
+  </si>
+  <si>
+    <t>装水</t>
+  </si>
+  <si>
+    <t>查看植物店</t>
+  </si>
+  <si>
+    <t>查看家具店</t>
+  </si>
+  <si>
+    <t>查看动物店</t>
+  </si>
+  <si>
+    <t>移动</t>
+  </si>
+  <si>
+    <t>开始生产</t>
+  </si>
+  <si>
+    <t>设置</t>
+  </si>
+  <si>
+    <t>建造牧场</t>
+  </si>
+  <si>
+    <t>扩建</t>
+  </si>
+  <si>
+    <t>投喂</t>
+  </si>
+  <si>
+    <t>聊天</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>6</t>
+  </si>
+  <si>
+    <t>打开箱子</t>
+  </si>
+  <si>
+    <t>站起</t>
+  </si>
+  <si>
+    <t>睡眠</t>
+  </si>
+  <si>
+    <t>赠送</t>
+  </si>
+  <si>
+    <t>放生</t>
+  </si>
+  <si>
+    <t>组队</t>
+  </si>
+  <si>
+    <t>约会</t>
+  </si>
+  <si>
+    <t>结婚</t>
+  </si>
+  <si>
+    <t>分手</t>
+  </si>
+  <si>
+    <t>索要</t>
+  </si>
+  <si>
+    <t>分配</t>
+  </si>
+  <si>
+    <t>酒馆</t>
+    <phoneticPr fontId="0" type="noConversion"/>
   </si>
   <si>
     <t>占卜屋</t>
-  </si>
-  <si>
-    <t>4800</t>
-  </si>
-  <si>
-    <t>帐篷内部</t>
-  </si>
-  <si>
-    <t>风车内部</t>
-  </si>
-  <si>
-    <t>2527</t>
-  </si>
-  <si>
-    <t>客栈一楼</t>
-  </si>
-  <si>
-    <t>4918</t>
-  </si>
-  <si>
-    <t>鱼摊内部</t>
-  </si>
-  <si>
-    <t>2902</t>
-  </si>
-  <si>
-    <t>船坞二层</t>
-  </si>
-  <si>
-    <t>5476</t>
-  </si>
-  <si>
-    <t>4262</t>
-  </si>
-  <si>
-    <t>695</t>
-  </si>
-  <si>
-    <t>别墅大厅</t>
-  </si>
-  <si>
-    <t>4696</t>
-  </si>
-  <si>
-    <t>教堂二楼</t>
-  </si>
-  <si>
-    <t>5170</t>
-  </si>
-  <si>
-    <t>酒馆</t>
-  </si>
-  <si>
-    <t>2180</t>
-  </si>
-  <si>
-    <t>村公所宴会厅</t>
-  </si>
-  <si>
-    <t>1557</t>
-  </si>
-  <si>
-    <t>科学研究室</t>
-  </si>
-  <si>
-    <t>5293</t>
-  </si>
-  <si>
-    <t>商店</t>
-  </si>
-  <si>
-    <t>3793</t>
-  </si>
-  <si>
-    <t>3558</t>
-  </si>
-  <si>
-    <t>武器店二楼</t>
-  </si>
-  <si>
-    <t>1856</t>
-  </si>
-  <si>
-    <t>1698</t>
-  </si>
-  <si>
-    <t>1001</t>
-  </si>
-  <si>
-    <t>床</t>
-  </si>
-  <si>
-    <t>1002</t>
-  </si>
-  <si>
-    <t>书架</t>
-  </si>
-  <si>
-    <t>1003</t>
-  </si>
-  <si>
-    <t>圆凳</t>
-  </si>
-  <si>
-    <t>1004</t>
-  </si>
-  <si>
-    <t>壁画</t>
-  </si>
-  <si>
-    <t>1005</t>
-  </si>
-  <si>
-    <t>梳妆台</t>
-  </si>
-  <si>
-    <t>1006</t>
-  </si>
-  <si>
-    <t>椅子</t>
-  </si>
-  <si>
-    <t>1007</t>
-  </si>
-  <si>
-    <t>1009</t>
-  </si>
-  <si>
-    <t>楼梯</t>
-  </si>
-  <si>
-    <t>1010</t>
-  </si>
-  <si>
-    <t>矮柜</t>
-  </si>
-  <si>
-    <t>1011</t>
-  </si>
-  <si>
-    <t>窗</t>
-  </si>
-  <si>
-    <t>箱子</t>
-  </si>
-  <si>
-    <t>1013</t>
-  </si>
-  <si>
-    <t>花盆</t>
-  </si>
-  <si>
-    <t>1014</t>
-  </si>
-  <si>
-    <t>蜡烛0</t>
-  </si>
-  <si>
-    <t>1015</t>
-  </si>
-  <si>
-    <t>蜡烛1</t>
-  </si>
-  <si>
-    <t>1016</t>
-  </si>
-  <si>
-    <t>长桌</t>
-  </si>
-  <si>
-    <t>1017</t>
-  </si>
-  <si>
-    <t>柜台</t>
-  </si>
-  <si>
-    <t>1018</t>
-  </si>
-  <si>
-    <t>长柜台竖</t>
-  </si>
-  <si>
-    <t>长柜台横</t>
-  </si>
-  <si>
-    <t>1020</t>
-  </si>
-  <si>
-    <t>窗户</t>
-  </si>
-  <si>
-    <t>1021</t>
-  </si>
-  <si>
-    <t>绿植1</t>
-  </si>
-  <si>
-    <t>1022</t>
-  </si>
-  <si>
-    <t>武器架</t>
-  </si>
-  <si>
-    <t>1023</t>
-  </si>
-  <si>
-    <t>服饰架</t>
-  </si>
-  <si>
-    <t>1024</t>
-  </si>
-  <si>
-    <t>武器柜横</t>
-  </si>
-  <si>
-    <t>武器柜右</t>
-  </si>
-  <si>
-    <t>壁画1</t>
-  </si>
-  <si>
-    <t>桌子</t>
-  </si>
-  <si>
-    <t>提灯</t>
-  </si>
-  <si>
-    <t>蜡烛吊灯</t>
-  </si>
-  <si>
-    <t>内门1</t>
-  </si>
-  <si>
-    <t>锻造炉-设施</t>
-  </si>
-  <si>
-    <t>储物箱(木)-设施</t>
-  </si>
-  <si>
-    <t>楼梯上</t>
-  </si>
-  <si>
-    <t>商店开关</t>
-  </si>
-  <si>
-    <t>外窗1</t>
-  </si>
-  <si>
-    <t>外窗2</t>
-  </si>
-  <si>
-    <t>外窗3</t>
-  </si>
-  <si>
-    <t>外窗招牌</t>
-  </si>
-  <si>
-    <t>宽门</t>
-  </si>
-  <si>
-    <t>红窄门</t>
-  </si>
-  <si>
-    <t>别墅一楼床</t>
-  </si>
-  <si>
-    <t>秋千</t>
-  </si>
-  <si>
-    <t>城内河</t>
-  </si>
-  <si>
-    <t>我的大门</t>
-  </si>
-  <si>
-    <t>公所大门</t>
-  </si>
-  <si>
-    <t>黄窄门</t>
-  </si>
-  <si>
-    <t>双门</t>
-  </si>
-  <si>
-    <t>棚子门</t>
-  </si>
-  <si>
-    <t>竖长椅</t>
-  </si>
-  <si>
-    <t>广场河</t>
-  </si>
-  <si>
-    <t>农田</t>
-  </si>
-  <si>
-    <t>稻草人</t>
-  </si>
-  <si>
-    <t>树墩</t>
-  </si>
-  <si>
-    <t>提灯侧</t>
-  </si>
-  <si>
-    <t>篝火</t>
-  </si>
-  <si>
-    <t>柴棚</t>
-  </si>
-  <si>
-    <t>牲畜棚</t>
-  </si>
-  <si>
-    <t>农场河</t>
-  </si>
-  <si>
-    <t>栅栏门</t>
-  </si>
-  <si>
-    <t>提灯外</t>
-  </si>
-  <si>
-    <t>商店街河</t>
-  </si>
-  <si>
-    <t>水井</t>
-  </si>
-  <si>
-    <t>长椅背面</t>
-  </si>
-  <si>
-    <t>普通门</t>
-  </si>
-  <si>
-    <t>黄门2</t>
-  </si>
-  <si>
-    <t>二楼门</t>
-  </si>
-  <si>
-    <t>植物店柜台</t>
-  </si>
-  <si>
-    <t>壁炉</t>
-  </si>
-  <si>
-    <t>单人床</t>
-  </si>
-  <si>
-    <t>豪华床</t>
-  </si>
-  <si>
-    <t>植物店书桌</t>
-  </si>
-  <si>
-    <t>红椅子左</t>
-  </si>
-  <si>
-    <t>红椅子斜右</t>
-  </si>
-  <si>
-    <t>壁画老女</t>
-  </si>
-  <si>
-    <t>春战场</t>
-  </si>
-  <si>
-    <t>秋战场</t>
-  </si>
-  <si>
-    <t>畜牧店柜台</t>
-  </si>
-  <si>
-    <t>床绿</t>
-  </si>
-  <si>
-    <t>床红</t>
-  </si>
-  <si>
-    <t>磨坊</t>
-  </si>
-  <si>
-    <t>帐篷</t>
-  </si>
-  <si>
-    <t>无偏转内门</t>
-  </si>
-  <si>
-    <t>夏战场</t>
-  </si>
-  <si>
-    <t>冬战场</t>
-  </si>
-  <si>
-    <t>旗子</t>
-  </si>
-  <si>
-    <t>家具柜台</t>
-  </si>
-  <si>
-    <t>家具店大床</t>
-  </si>
-  <si>
-    <t>家具店小床</t>
-  </si>
-  <si>
-    <t>冷餐台</t>
-  </si>
-  <si>
-    <t>破损牲畜棚</t>
-  </si>
-  <si>
-    <t>初级牲口棚</t>
-  </si>
-  <si>
-    <t>食物槽</t>
-  </si>
-  <si>
-    <t>水槽</t>
-  </si>
-  <si>
-    <t>收获篮</t>
-  </si>
-  <si>
-    <t>传送门</t>
-  </si>
-  <si>
-    <t>山地湖</t>
-  </si>
-  <si>
-    <t>城门河</t>
-  </si>
-  <si>
-    <t>1100</t>
-  </si>
-  <si>
-    <t>我的家</t>
-  </si>
-  <si>
-    <t>1101</t>
-  </si>
-  <si>
-    <t>民居1</t>
-  </si>
-  <si>
-    <t>1103</t>
-  </si>
-  <si>
-    <t>民居2</t>
-  </si>
-  <si>
-    <t>镇公所</t>
-  </si>
-  <si>
-    <t>1105</t>
-  </si>
-  <si>
-    <t>1106</t>
-  </si>
-  <si>
-    <t>钟楼</t>
-  </si>
-  <si>
-    <t>动物店</t>
-  </si>
-  <si>
-    <t>1109</t>
-  </si>
-  <si>
-    <t>装备店</t>
-  </si>
-  <si>
-    <t>1110</t>
-  </si>
-  <si>
-    <t>水车房</t>
-  </si>
-  <si>
-    <t>1111</t>
-  </si>
-  <si>
-    <t>民宅1</t>
-  </si>
-  <si>
-    <t>民宅2</t>
-  </si>
-  <si>
-    <t>1113</t>
-  </si>
-  <si>
-    <t>摊位</t>
-  </si>
-  <si>
-    <t>1114</t>
-  </si>
-  <si>
-    <t>大摊位</t>
-  </si>
-  <si>
-    <t>1115</t>
-  </si>
-  <si>
-    <t>1116</t>
-  </si>
-  <si>
-    <t>鱼店</t>
-  </si>
-  <si>
-    <t>1117</t>
-  </si>
-  <si>
-    <t>搅拌器</t>
-  </si>
-  <si>
-    <t>冰箱</t>
-  </si>
-  <si>
-    <t>储物箱(木)</t>
-  </si>
-  <si>
-    <t>储物箱(银)</t>
-  </si>
-  <si>
-    <t>储物箱(金)</t>
-  </si>
-  <si>
-    <t>搅拌器-设施</t>
-  </si>
-  <si>
-    <t>冰箱-设施</t>
-  </si>
-  <si>
-    <t>缝纫机-设施</t>
-  </si>
-  <si>
-    <t>绘写台-设施</t>
-  </si>
-  <si>
-    <t>冷餐台-设施</t>
-  </si>
-  <si>
-    <t>蒸煮锅-设施</t>
-  </si>
-  <si>
-    <t>烘烤炉-设施</t>
-  </si>
-  <si>
-    <t>酿造桶-设施</t>
-  </si>
-  <si>
-    <t>储物箱(银)-设施</t>
-  </si>
-  <si>
-    <t>储物箱(金)-设施</t>
-  </si>
-  <si>
-    <t>红椅子</t>
-  </si>
-  <si>
-    <t>时钟</t>
-  </si>
-  <si>
-    <t>紫椅子</t>
-  </si>
-  <si>
-    <t>别墅床</t>
-  </si>
-  <si>
-    <t>豪华梳妆台</t>
-  </si>
-  <si>
-    <t>钢琴</t>
-  </si>
-  <si>
-    <t>紫椅子翻转</t>
-  </si>
-  <si>
-    <t>占卜屋床</t>
-  </si>
-  <si>
-    <t>占卜柜台</t>
-  </si>
-  <si>
-    <t>魔镜</t>
-  </si>
-  <si>
-    <t>坐垫小凳</t>
-  </si>
-  <si>
-    <t>客栈双人床</t>
-  </si>
-  <si>
-    <t>红长沙发左</t>
-  </si>
-  <si>
-    <t>红长沙右</t>
-  </si>
-  <si>
-    <t>沙发红上</t>
-  </si>
-  <si>
-    <t>红椅子下</t>
-  </si>
-  <si>
-    <t>椅子红斜</t>
-  </si>
-  <si>
-    <t>红色单人床</t>
-  </si>
-  <si>
-    <t>客栈柜台</t>
-  </si>
-  <si>
-    <t>沙发侧暗</t>
-  </si>
-  <si>
-    <t>单人床黄</t>
-  </si>
-  <si>
-    <t>长沙发蓝左</t>
-  </si>
-  <si>
-    <t>蓝椅子下</t>
-  </si>
-  <si>
-    <t>纺织店柜台</t>
-  </si>
-  <si>
-    <t>椅子红下</t>
-  </si>
-  <si>
-    <t>椅子红上</t>
-  </si>
-  <si>
-    <t>床白</t>
-  </si>
-  <si>
-    <t>望远镜</t>
-  </si>
-  <si>
-    <t>教堂讲台</t>
-  </si>
-  <si>
-    <t>酒馆柜台</t>
-  </si>
-  <si>
-    <t>地铺</t>
-  </si>
-  <si>
-    <t>地铺2</t>
-  </si>
-  <si>
-    <t>朴素床</t>
-  </si>
-  <si>
-    <t>海边</t>
-  </si>
-  <si>
-    <t>纺织机</t>
-  </si>
-  <si>
-    <t>锻造炉</t>
-  </si>
-  <si>
-    <t>烘烤炉</t>
-  </si>
-  <si>
-    <t>酿造桶</t>
-  </si>
-  <si>
-    <t>绘写台</t>
-  </si>
-  <si>
-    <t>蒸煮锅</t>
-  </si>
-  <si>
-    <t>缝纫机</t>
-  </si>
-  <si>
-    <t>纺线机</t>
-  </si>
-  <si>
-    <t>织布机</t>
-  </si>
-  <si>
-    <t>制革机</t>
-  </si>
-  <si>
-    <t>自宅门</t>
-  </si>
-  <si>
-    <t>客栈</t>
-  </si>
-  <si>
-    <t>别墅</t>
-  </si>
-  <si>
-    <t>自宅</t>
-  </si>
-  <si>
-    <t>长椅下</t>
-  </si>
-  <si>
-    <t>水坑</t>
-  </si>
-  <si>
-    <t>玉米</t>
-  </si>
-  <si>
-    <t>8001</t>
-  </si>
-  <si>
-    <t>芜菁</t>
-  </si>
-  <si>
-    <t>8002</t>
-  </si>
-  <si>
-    <t>卷心菜</t>
-  </si>
-  <si>
-    <t>8003</t>
-  </si>
-  <si>
-    <t>大葱</t>
-  </si>
-  <si>
-    <t>8004</t>
-  </si>
-  <si>
-    <t>萝卜</t>
-  </si>
-  <si>
-    <t>8005</t>
-  </si>
-  <si>
-    <t>紫甘蓝</t>
-  </si>
-  <si>
-    <t>黄瓜</t>
-  </si>
-  <si>
-    <t>西兰花</t>
-  </si>
-  <si>
-    <t>番茄</t>
-  </si>
-  <si>
-    <t>胡萝卜</t>
-  </si>
-  <si>
-    <t>西瓜</t>
-  </si>
-  <si>
-    <t>辣椒</t>
-  </si>
-  <si>
-    <t>奇异果</t>
-  </si>
-  <si>
-    <t>茄子</t>
-  </si>
-  <si>
-    <t>豌豆</t>
-  </si>
-  <si>
-    <t>土豆</t>
-  </si>
-  <si>
-    <t>大蒜</t>
-  </si>
-  <si>
-    <t>芦笋</t>
-  </si>
-  <si>
-    <t>南瓜</t>
-  </si>
-  <si>
-    <t>小麦</t>
-  </si>
-  <si>
-    <t>啤酒花</t>
-  </si>
-  <si>
-    <t>葡萄</t>
-  </si>
-  <si>
-    <t>菠萝</t>
-  </si>
-  <si>
-    <t>咖啡</t>
-  </si>
-  <si>
-    <t>草莓</t>
-  </si>
-  <si>
-    <t>蓝莓</t>
-  </si>
-  <si>
-    <t>红薯</t>
-  </si>
-  <si>
-    <t>甜菜</t>
-  </si>
-  <si>
-    <t>1000</t>
-  </si>
-  <si>
-    <t>鲫鱼</t>
-  </si>
-  <si>
-    <t>鲮鱼</t>
-  </si>
-  <si>
-    <t>手套蟹.</t>
-  </si>
-  <si>
-    <t>丁鱼</t>
-  </si>
-  <si>
-    <t>锦鲤</t>
-  </si>
-  <si>
-    <t>线鱼</t>
-  </si>
-  <si>
-    <t>兰寿金鱼</t>
-  </si>
-  <si>
-    <t>樱桃鲑鱼</t>
-  </si>
-  <si>
-    <t>虹鳟鱼</t>
-  </si>
-  <si>
-    <t>鲷鱼</t>
-  </si>
-  <si>
-    <t>金鳟鱼</t>
-  </si>
-  <si>
-    <t>霓虹脂鲤</t>
-  </si>
-  <si>
-    <t>桃花鱼</t>
-  </si>
-  <si>
-    <t>鲑鱼</t>
-  </si>
-  <si>
-    <t>孔雀鱼</t>
-  </si>
-  <si>
-    <t>银龙鱼</t>
-  </si>
-  <si>
-    <t>洞穴天使鱼</t>
-  </si>
-  <si>
-    <t>沙丁鱼</t>
-  </si>
-  <si>
-    <t>竹荚鱼</t>
-  </si>
-  <si>
-    <t>海鳗</t>
-  </si>
-  <si>
-    <t>章鱼</t>
-  </si>
-  <si>
-    <t>比目鱼</t>
-  </si>
-  <si>
-    <t>河豚鱼</t>
-  </si>
-  <si>
-    <t>水母</t>
-  </si>
-  <si>
-    <t>条石鲷</t>
-  </si>
-  <si>
-    <t>红鲷鱼</t>
-  </si>
-  <si>
-    <t>蓝蟹</t>
-  </si>
-  <si>
-    <t>鲯鳅鱼</t>
-  </si>
-  <si>
-    <t>龙虾</t>
-  </si>
-  <si>
-    <t>金枪鱼</t>
-  </si>
-  <si>
-    <t>斑马狮子鱼</t>
-  </si>
-  <si>
-    <t>点击虚拟NPC</t>
-  </si>
-  <si>
-    <t>锄地</t>
-  </si>
-  <si>
-    <t>浇水</t>
-  </si>
-  <si>
-    <t>播种</t>
-  </si>
-  <si>
-    <t>收获</t>
-  </si>
-  <si>
-    <t>收割</t>
-  </si>
-  <si>
-    <t>铲除</t>
-  </si>
-  <si>
-    <t>点击虚拟NPC事件</t>
-  </si>
-  <si>
-    <t>移动物体事件</t>
-  </si>
-  <si>
-    <t>卸载战斗、恢复电影</t>
-  </si>
-  <si>
-    <t>春之山脉胜利</t>
-  </si>
-  <si>
-    <t>夏之丛林胜利</t>
-  </si>
-  <si>
-    <t>秋风之谷胜利</t>
-  </si>
-  <si>
-    <t>冬之雪原胜利</t>
-  </si>
-  <si>
-    <t>点击NPC赠送</t>
-  </si>
-  <si>
-    <t>301</t>
-  </si>
-  <si>
-    <t>表白</t>
-  </si>
-  <si>
-    <t>打开商店</t>
-  </si>
-  <si>
-    <t>队伍邀请</t>
-  </si>
-  <si>
-    <t>分配牧场</t>
-  </si>
-  <si>
-    <t>放生动物</t>
-  </si>
-  <si>
-    <t>310</t>
-  </si>
-  <si>
-    <t>投喂动物</t>
-  </si>
-  <si>
-    <t>打开天气预报</t>
-  </si>
-  <si>
-    <t>第一次离开家</t>
-  </si>
-  <si>
-    <t>查看角色</t>
-  </si>
-  <si>
-    <t>打开联装背包</t>
-  </si>
-  <si>
-    <t>垂钓</t>
-  </si>
-  <si>
-    <t>创建或打开杂物箱</t>
-  </si>
-  <si>
-    <t>4001</t>
-  </si>
-  <si>
-    <t>商店地图事件</t>
-  </si>
-  <si>
-    <t>坐下</t>
-  </si>
-  <si>
-    <t>离开椅子</t>
-  </si>
-  <si>
-    <t>选择睡眠</t>
-  </si>
-  <si>
-    <t>跳转地图到卧室</t>
-  </si>
-  <si>
-    <t>跳转地图 卧室-大厅</t>
-  </si>
-  <si>
-    <t>商店开门</t>
-  </si>
-  <si>
-    <t>商店关门</t>
-  </si>
-  <si>
-    <t>关闭栅栏</t>
-  </si>
-  <si>
-    <t>打开栅栏</t>
-  </si>
-  <si>
-    <t>收竿</t>
-  </si>
-  <si>
-    <t>装满水</t>
-  </si>
-  <si>
-    <t>第一晚限制</t>
-  </si>
-  <si>
-    <t>赠送礼物</t>
-  </si>
-  <si>
-    <t>打开春战场</t>
-  </si>
-  <si>
-    <t>打开夏战场</t>
-  </si>
-  <si>
-    <t>打开秋战场</t>
-  </si>
-  <si>
-    <t>打开冬战场</t>
-  </si>
-  <si>
-    <t>打开商店界面</t>
-  </si>
-  <si>
-    <t>建造牲畜棚</t>
-  </si>
-  <si>
-    <t>升级牧场</t>
-  </si>
-  <si>
-    <t>坐到沙发上</t>
-  </si>
-  <si>
-    <t>离开沙发</t>
-  </si>
-  <si>
-    <t>500</t>
-  </si>
-  <si>
-    <t>第一天睡醒</t>
-  </si>
-  <si>
-    <t>7000</t>
-  </si>
-  <si>
-    <t>传送事件</t>
-  </si>
-  <si>
-    <t>7001</t>
-  </si>
-  <si>
-    <t>吃食物</t>
-  </si>
-  <si>
-    <t>点击NPC事件</t>
-  </si>
-  <si>
-    <t>点击布莱兹</t>
-  </si>
-  <si>
-    <t>点击玛德琳</t>
-  </si>
-  <si>
-    <t>点击丝特芬妮</t>
-  </si>
-  <si>
-    <t>点击格吉尔</t>
-  </si>
-  <si>
-    <t>8100</t>
-  </si>
-  <si>
-    <t>点击鸡</t>
-  </si>
-  <si>
-    <t>春战斗胜利</t>
-  </si>
-  <si>
-    <t>第一次战斗结束</t>
-  </si>
-  <si>
-    <t>0</t>
-  </si>
-  <si>
-    <t>....</t>
-  </si>
-  <si>
-    <t>查看</t>
-  </si>
-  <si>
-    <t>开始营业</t>
-  </si>
-  <si>
-    <t>结束营业</t>
-  </si>
-  <si>
-    <t>打开</t>
-  </si>
-  <si>
-    <t>15</t>
-  </si>
-  <si>
-    <t>关闭</t>
-  </si>
-  <si>
-    <t>装水</t>
-  </si>
-  <si>
-    <t>查看植物店</t>
-  </si>
-  <si>
-    <t>查看家具店</t>
-  </si>
-  <si>
-    <t>查看动物店</t>
-  </si>
-  <si>
-    <t>移动</t>
-  </si>
-  <si>
-    <t>开始生产</t>
-  </si>
-  <si>
-    <t>设置</t>
-  </si>
-  <si>
-    <t>建造牧场</t>
-  </si>
-  <si>
-    <t>扩建</t>
-  </si>
-  <si>
-    <t>投喂</t>
-  </si>
-  <si>
-    <t>聊天</t>
-  </si>
-  <si>
-    <t>5</t>
-  </si>
-  <si>
-    <t>6</t>
-  </si>
-  <si>
-    <t>打开箱子</t>
-  </si>
-  <si>
-    <t>站起</t>
-  </si>
-  <si>
-    <t>睡眠</t>
-  </si>
-  <si>
-    <t>赠送</t>
-  </si>
-  <si>
-    <t>放生</t>
-  </si>
-  <si>
-    <t>组队</t>
-  </si>
-  <si>
-    <t>约会</t>
-  </si>
-  <si>
-    <t>结婚</t>
-  </si>
-  <si>
-    <t>分手</t>
-  </si>
-  <si>
-    <t>索要</t>
-  </si>
-  <si>
-    <t>分配</t>
-  </si>
-  <si>
-    <t>酒馆</t>
     <phoneticPr fontId="0" type="noConversion"/>
   </si>
 </sst>
@@ -2500,7 +2375,7 @@
       <charset val="134"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -2510,6 +2385,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.59999389629810485"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2526,7 +2407,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1"/>
@@ -2538,6 +2419,8 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -2831,250 +2714,250 @@
     </row>
     <row r="2" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B2" s="6" t="s">
-        <v>675</v>
+        <v>631</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>676</v>
+        <v>632</v>
       </c>
     </row>
     <row r="3" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B3" s="6" t="s">
-        <v>445</v>
+        <v>401</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>677</v>
+        <v>633</v>
       </c>
     </row>
     <row r="4" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B4" s="6" t="s">
-        <v>447</v>
+        <v>403</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>678</v>
+        <v>634</v>
       </c>
     </row>
     <row r="5" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B5" s="6" t="s">
-        <v>448</v>
+        <v>404</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>679</v>
+        <v>635</v>
       </c>
     </row>
     <row r="6" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B6" s="6" t="s">
-        <v>450</v>
+        <v>406</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>680</v>
+        <v>636</v>
       </c>
     </row>
     <row r="7" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B7" s="6" t="s">
-        <v>452</v>
+        <v>408</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>681</v>
+        <v>637</v>
       </c>
     </row>
     <row r="8" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B8" s="6" t="s">
-        <v>455</v>
+        <v>411</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>682</v>
+        <v>638</v>
       </c>
     </row>
     <row r="9" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B9" s="6" t="s">
-        <v>457</v>
+        <v>413</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>683</v>
+        <v>639</v>
       </c>
     </row>
     <row r="10" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B10" s="6" t="s">
-        <v>459</v>
+        <v>415</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>684</v>
+        <v>640</v>
       </c>
     </row>
     <row r="11" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B11" s="6" t="s">
-        <v>461</v>
+        <v>417</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>685</v>
+        <v>641</v>
       </c>
     </row>
     <row r="12" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B12" s="6" t="s">
-        <v>463</v>
+        <v>419</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>686</v>
+        <v>642</v>
       </c>
     </row>
     <row r="13" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B13" s="6" t="s">
-        <v>465</v>
+        <v>421</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>687</v>
+        <v>643</v>
       </c>
     </row>
     <row r="14" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B14" s="6" t="s">
-        <v>468</v>
+        <v>424</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>688</v>
+        <v>644</v>
       </c>
     </row>
     <row r="15" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B15" s="6" t="s">
-        <v>470</v>
+        <v>426</v>
       </c>
       <c r="C15" s="6" t="s">
-        <v>689</v>
+        <v>645</v>
       </c>
     </row>
     <row r="16" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B16" s="6" t="s">
-        <v>472</v>
+        <v>428</v>
       </c>
       <c r="C16" s="6" t="s">
-        <v>690</v>
+        <v>646</v>
       </c>
     </row>
     <row r="17" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B17" s="6" t="s">
-        <v>474</v>
+        <v>430</v>
       </c>
       <c r="C17" s="6" t="s">
-        <v>691</v>
+        <v>647</v>
       </c>
     </row>
     <row r="18" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B18" s="6" t="s">
-        <v>476</v>
+        <v>432</v>
       </c>
       <c r="C18" s="6" t="s">
-        <v>692</v>
+        <v>648</v>
       </c>
     </row>
     <row r="19" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B19" s="6" t="s">
-        <v>551</v>
+        <v>507</v>
       </c>
       <c r="C19" s="6" t="s">
-        <v>693</v>
+        <v>649</v>
       </c>
     </row>
     <row r="20" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B20" s="6" t="s">
-        <v>553</v>
+        <v>509</v>
       </c>
       <c r="C20" s="6" t="s">
-        <v>694</v>
+        <v>650</v>
       </c>
     </row>
     <row r="21" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B21" s="6" t="s">
-        <v>555</v>
+        <v>511</v>
       </c>
       <c r="C21" s="6" t="s">
-        <v>695</v>
+        <v>651</v>
       </c>
     </row>
     <row r="22" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B22" s="6" t="s">
-        <v>558</v>
+        <v>514</v>
       </c>
       <c r="C22" s="6" t="s">
-        <v>696</v>
+        <v>652</v>
       </c>
     </row>
     <row r="23" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B23" s="6" t="s">
-        <v>559</v>
+        <v>515</v>
       </c>
       <c r="C23" s="6" t="s">
-        <v>697</v>
+        <v>653</v>
       </c>
     </row>
     <row r="24" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B24" s="6" t="s">
-        <v>562</v>
+        <v>518</v>
       </c>
       <c r="C24" s="6" t="s">
-        <v>698</v>
+        <v>654</v>
       </c>
     </row>
     <row r="25" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B25" s="6" t="s">
-        <v>564</v>
+        <v>520</v>
       </c>
       <c r="C25" s="6" t="s">
-        <v>699</v>
+        <v>655</v>
       </c>
     </row>
     <row r="26" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B26" s="6" t="s">
-        <v>566</v>
+        <v>522</v>
       </c>
       <c r="C26" s="6" t="s">
-        <v>700</v>
+        <v>656</v>
       </c>
     </row>
     <row r="27" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B27" s="6" t="s">
-        <v>388</v>
+        <v>372</v>
       </c>
       <c r="C27" s="6" t="s">
-        <v>701</v>
+        <v>657</v>
       </c>
     </row>
     <row r="28" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B28" s="6" t="s">
-        <v>569</v>
+        <v>525</v>
       </c>
       <c r="C28" s="6" t="s">
-        <v>702</v>
+        <v>658</v>
       </c>
     </row>
     <row r="29" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B29" s="6" t="s">
-        <v>571</v>
+        <v>527</v>
       </c>
       <c r="C29" s="6" t="s">
-        <v>703</v>
+        <v>659</v>
       </c>
     </row>
     <row r="30" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B30" s="6" t="s">
-        <v>573</v>
+        <v>529</v>
       </c>
       <c r="C30" s="6" t="s">
-        <v>704</v>
+        <v>660</v>
       </c>
     </row>
     <row r="31" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B31" s="6" t="s">
-        <v>574</v>
+        <v>530</v>
       </c>
       <c r="C31" s="6" t="s">
-        <v>705</v>
+        <v>661</v>
       </c>
     </row>
     <row r="32" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B32" s="6" t="s">
-        <v>576</v>
+        <v>532</v>
       </c>
       <c r="C32" s="6" t="s">
-        <v>706</v>
+        <v>662</v>
       </c>
     </row>
   </sheetData>
@@ -3090,6 +2973,7 @@
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="22.28515625" style="4" customWidth="1"/>
+    <col min="3" max="3" width="9.140625" style="6"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:15" x14ac:dyDescent="0.25">
@@ -3102,55 +2986,55 @@
     </row>
     <row r="2" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B2" s="6" t="s">
-        <v>338</v>
-      </c>
-      <c r="C2" s="6" t="s">
-        <v>339</v>
+        <v>350</v>
+      </c>
+      <c r="C2" s="6">
+        <v>302</v>
       </c>
     </row>
     <row r="3" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B3" s="6" t="s">
         <v>340</v>
       </c>
-      <c r="C3" s="6" t="s">
-        <v>341</v>
+      <c r="C3" s="6">
+        <v>405</v>
       </c>
     </row>
     <row r="4" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B4" s="6" t="s">
+        <v>353</v>
+      </c>
+      <c r="C4" s="6">
+        <v>512</v>
+      </c>
+      <c r="G4" s="7" t="s">
         <v>342</v>
       </c>
-      <c r="C4" s="6" t="s">
+      <c r="I4" s="8" t="s">
         <v>343</v>
       </c>
-      <c r="G4" s="7" t="s">
+      <c r="J4" s="8" t="s">
         <v>344</v>
       </c>
-      <c r="I4" s="8" t="s">
+      <c r="K4" s="6" t="s">
         <v>345</v>
-      </c>
-      <c r="J4" s="8" t="s">
-        <v>346</v>
-      </c>
-      <c r="K4" s="6" t="s">
-        <v>347</v>
       </c>
     </row>
     <row r="5" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B5" s="6" t="s">
-        <v>348</v>
+        <v>389</v>
       </c>
       <c r="C5" s="6">
-        <v>948</v>
+        <v>547</v>
       </c>
       <c r="G5" s="7" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="I5" s="4">
         <f>VLOOKUP(I4,$B:$C,2,FALSE)</f>
         <v>874</v>
       </c>
-      <c r="J5" s="6" t="str">
+      <c r="J5" s="6">
         <f t="shared" ref="J5:K5" si="0">VLOOKUP(J4,$B:$C,2,FALSE)</f>
         <v>2355</v>
       </c>
@@ -3161,10 +3045,10 @@
     </row>
     <row r="6" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B6" s="6" t="s">
-        <v>350</v>
-      </c>
-      <c r="C6" s="6" t="s">
-        <v>351</v>
+        <v>352</v>
+      </c>
+      <c r="C6" s="6">
+        <v>695</v>
       </c>
       <c r="G6" s="9" t="str">
         <f>G4&amp;","&amp;G5</f>
@@ -3188,51 +3072,51 @@
     </row>
     <row r="7" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B7" s="6" t="s">
+        <v>362</v>
+      </c>
+      <c r="C7" s="6">
+        <v>759</v>
+      </c>
+      <c r="G7" s="7" t="s">
+        <v>347</v>
+      </c>
+      <c r="I7" s="8" t="s">
+        <v>343</v>
+      </c>
+      <c r="J7" s="8" t="s">
+        <v>344</v>
+      </c>
+      <c r="K7" s="6" t="s">
+        <v>345</v>
+      </c>
+      <c r="L7" s="6" t="s">
+        <v>350</v>
+      </c>
+      <c r="M7" s="6" t="s">
+        <v>351</v>
+      </c>
+      <c r="N7" s="6" t="s">
         <v>352</v>
       </c>
-      <c r="C7" s="6" t="s">
+      <c r="O7" s="6" t="s">
         <v>353</v>
-      </c>
-      <c r="G7" s="7" t="s">
-        <v>349</v>
-      </c>
-      <c r="I7" s="8" t="s">
-        <v>345</v>
-      </c>
-      <c r="J7" s="8" t="s">
-        <v>346</v>
-      </c>
-      <c r="K7" s="6" t="s">
-        <v>347</v>
-      </c>
-      <c r="L7" s="6" t="s">
-        <v>354</v>
-      </c>
-      <c r="M7" s="6" t="s">
-        <v>355</v>
-      </c>
-      <c r="N7" s="6" t="s">
-        <v>356</v>
-      </c>
-      <c r="O7" s="6" t="s">
-        <v>357</v>
       </c>
     </row>
     <row r="8" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B8" s="6" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="C8" s="6">
         <v>874</v>
       </c>
       <c r="G8" s="7" t="s">
-        <v>358</v>
+        <v>354</v>
       </c>
       <c r="I8" s="6">
         <f>VLOOKUP(I7,$B:$C,2,FALSE)</f>
         <v>874</v>
       </c>
-      <c r="J8" s="6" t="str">
+      <c r="J8" s="6">
         <f>VLOOKUP(J7,$B:$C,2,FALSE)</f>
         <v>2355</v>
       </c>
@@ -3240,29 +3124,29 @@
         <f t="shared" ref="K8:L8" si="1">VLOOKUP(K7,$B:$C,2,FALSE)</f>
         <v>2497</v>
       </c>
-      <c r="L8" s="6" t="str">
+      <c r="L8" s="6">
         <f t="shared" si="1"/>
         <v>302</v>
       </c>
-      <c r="M8" s="6" t="str">
+      <c r="M8" s="6">
         <f>VLOOKUP(M7,$B:$C,2,FALSE)</f>
         <v>889</v>
       </c>
-      <c r="N8" s="6" t="str">
+      <c r="N8" s="6">
         <f t="shared" ref="N8:O8" si="2">VLOOKUP(N7,$B:$C,2,FALSE)</f>
         <v>695</v>
       </c>
-      <c r="O8" s="6" t="str">
+      <c r="O8" s="6">
         <f t="shared" si="2"/>
         <v>512</v>
       </c>
     </row>
     <row r="9" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B9" s="6" t="s">
-        <v>359</v>
-      </c>
-      <c r="C9" s="6" t="s">
-        <v>360</v>
+        <v>351</v>
+      </c>
+      <c r="C9" s="6">
+        <v>889</v>
       </c>
       <c r="G9" s="9" t="str">
         <f>G7&amp;","&amp;G8</f>
@@ -3300,32 +3184,32 @@
     </row>
     <row r="10" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B10" s="6" t="s">
-        <v>361</v>
-      </c>
-      <c r="C10" s="6" t="s">
-        <v>362</v>
+        <v>368</v>
+      </c>
+      <c r="C10" s="6">
+        <v>900</v>
       </c>
       <c r="G10" s="7" t="s">
-        <v>358</v>
+        <v>354</v>
       </c>
     </row>
     <row r="11" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B11" s="6" t="s">
-        <v>363</v>
-      </c>
-      <c r="C11" s="6" t="s">
-        <v>364</v>
+        <v>346</v>
+      </c>
+      <c r="C11" s="6">
+        <v>948</v>
       </c>
       <c r="G11" s="7" t="s">
-        <v>365</v>
+        <v>358</v>
       </c>
     </row>
     <row r="12" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B12" s="6" t="s">
-        <v>366</v>
+      <c r="B12" s="11" t="s">
+        <v>375</v>
       </c>
       <c r="C12" s="6">
-        <v>1756</v>
+        <v>1014</v>
       </c>
       <c r="F12" s="6"/>
       <c r="G12" s="9" t="str">
@@ -3343,10 +3227,10 @@
     </row>
     <row r="13" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B13" s="6" t="s">
-        <v>367</v>
-      </c>
-      <c r="C13" s="6" t="s">
-        <v>368</v>
+        <v>371</v>
+      </c>
+      <c r="C13" s="6">
+        <v>1112</v>
       </c>
       <c r="F13" s="6"/>
       <c r="G13" s="7"/>
@@ -3361,53 +3245,53 @@
     </row>
     <row r="14" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B14" s="6" t="s">
-        <v>369</v>
-      </c>
-      <c r="C14" s="6" t="s">
-        <v>370</v>
+        <v>374</v>
+      </c>
+      <c r="C14" s="6">
+        <v>1208</v>
       </c>
       <c r="F14" s="6"/>
       <c r="G14" s="7" t="s">
-        <v>365</v>
+        <v>358</v>
       </c>
       <c r="I14" s="6" t="s">
-        <v>354</v>
+        <v>350</v>
       </c>
       <c r="J14" s="6" t="s">
-        <v>355</v>
+        <v>351</v>
       </c>
       <c r="K14" s="6" t="s">
-        <v>356</v>
+        <v>352</v>
       </c>
       <c r="L14" s="6" t="s">
-        <v>357</v>
+        <v>353</v>
       </c>
     </row>
     <row r="15" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B15" s="6" t="s">
-        <v>371</v>
-      </c>
-      <c r="C15" s="6" t="s">
-        <v>372</v>
+        <v>367</v>
+      </c>
+      <c r="C15" s="6">
+        <v>1328</v>
       </c>
       <c r="F15" s="6"/>
       <c r="G15" s="7" t="s">
-        <v>373</v>
+        <v>363</v>
       </c>
       <c r="H15" s="6"/>
-      <c r="I15" s="6" t="str">
+      <c r="I15" s="6">
         <f>VLOOKUP(I14,$B:$C,2,FALSE)</f>
         <v>302</v>
       </c>
-      <c r="J15" s="6" t="str">
+      <c r="J15" s="6">
         <f t="shared" ref="J15:L15" si="4">VLOOKUP(J14,$B:$C,2,FALSE)</f>
         <v>889</v>
       </c>
-      <c r="K15" s="6" t="str">
+      <c r="K15" s="6">
         <f t="shared" si="4"/>
         <v>695</v>
       </c>
-      <c r="L15" s="6" t="str">
+      <c r="L15" s="6">
         <f t="shared" si="4"/>
         <v>512</v>
       </c>
@@ -3415,17 +3299,17 @@
     </row>
     <row r="16" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B16" s="6" t="s">
-        <v>361</v>
-      </c>
-      <c r="C16" s="6" t="s">
-        <v>374</v>
+        <v>365</v>
+      </c>
+      <c r="C16" s="6">
+        <v>1420</v>
       </c>
       <c r="G16" s="9" t="str">
         <f>G14&amp;","&amp;G15</f>
         <v>19,30, 22,0</v>
       </c>
       <c r="H16" s="9"/>
-      <c r="I16" s="9" t="str">
+      <c r="I16" s="9">
         <f>I15</f>
         <v>302</v>
       </c>
@@ -3446,46 +3330,46 @@
     </row>
     <row r="17" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B17" s="6" t="s">
-        <v>361</v>
-      </c>
-      <c r="C17" s="6" t="s">
-        <v>375</v>
+        <v>387</v>
+      </c>
+      <c r="C17" s="6">
+        <v>1557</v>
       </c>
       <c r="G17" s="7" t="s">
-        <v>376</v>
+        <v>364</v>
       </c>
       <c r="I17" s="6" t="s">
-        <v>355</v>
+        <v>351</v>
       </c>
       <c r="J17" s="6" t="s">
-        <v>356</v>
+        <v>352</v>
       </c>
       <c r="K17" s="6" t="s">
-        <v>357</v>
+        <v>353</v>
       </c>
       <c r="L17" s="6" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
     </row>
     <row r="18" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B18" s="6" t="s">
-        <v>377</v>
-      </c>
-      <c r="C18" s="6" t="s">
-        <v>378</v>
+        <v>356</v>
+      </c>
+      <c r="C18" s="6">
+        <v>1698</v>
       </c>
       <c r="G18" s="7" t="s">
-        <v>379</v>
-      </c>
-      <c r="I18" s="6" t="str">
+        <v>366</v>
+      </c>
+      <c r="I18" s="6">
         <f>VLOOKUP(I17,$B:$C,2,FALSE)</f>
         <v>889</v>
       </c>
-      <c r="J18" s="6" t="str">
+      <c r="J18" s="6">
         <f t="shared" ref="J18:L18" si="5">VLOOKUP(J17,$B:$C,2,FALSE)</f>
         <v>695</v>
       </c>
-      <c r="K18" s="6" t="str">
+      <c r="K18" s="6">
         <f t="shared" si="5"/>
         <v>512</v>
       </c>
@@ -3496,17 +3380,17 @@
     </row>
     <row r="19" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B19" s="6" t="s">
-        <v>380</v>
-      </c>
-      <c r="C19" s="6" t="s">
-        <v>381</v>
+        <v>359</v>
+      </c>
+      <c r="C19" s="6">
+        <v>1756</v>
       </c>
       <c r="G19" s="9" t="str">
         <f>G17&amp;","&amp;G18</f>
         <v>22,0,24,0</v>
       </c>
       <c r="H19" s="9"/>
-      <c r="I19" s="9" t="str">
+      <c r="I19" s="9">
         <f>I18</f>
         <v>889</v>
       </c>
@@ -3527,35 +3411,35 @@
     </row>
     <row r="20" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B20" s="6" t="s">
-        <v>382</v>
+        <v>390</v>
       </c>
       <c r="C20" s="6">
-        <v>900</v>
+        <v>1856</v>
       </c>
       <c r="G20" s="7"/>
     </row>
     <row r="21" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B21" s="6" t="s">
-        <v>383</v>
-      </c>
-      <c r="C21" s="6" t="s">
-        <v>384</v>
+        <v>378</v>
+      </c>
+      <c r="C21" s="6">
+        <v>1912</v>
       </c>
     </row>
     <row r="22" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B22" s="6" t="s">
-        <v>385</v>
-      </c>
-      <c r="C22" s="6" t="s">
-        <v>386</v>
+        <v>349</v>
+      </c>
+      <c r="C22" s="6">
+        <v>2015</v>
       </c>
     </row>
     <row r="23" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B23" s="6" t="s">
-        <v>387</v>
-      </c>
-      <c r="C23" s="6" t="s">
-        <v>388</v>
+      <c r="B23" s="10" t="s">
+        <v>763</v>
+      </c>
+      <c r="C23" s="6">
+        <v>2180</v>
       </c>
       <c r="G23" s="4" t="str">
         <f>G6&amp;","&amp;G9&amp;","&amp;G12&amp;","&amp;G16&amp;","&amp;G19</f>
@@ -3565,283 +3449,288 @@
     </row>
     <row r="24" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B24" s="6" t="s">
-        <v>346</v>
-      </c>
-      <c r="C24" s="6" t="s">
-        <v>389</v>
+        <v>339</v>
+      </c>
+      <c r="C24" s="6">
+        <v>2270</v>
       </c>
     </row>
     <row r="25" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B25" s="6" t="s">
-        <v>390</v>
-      </c>
-      <c r="C25" s="6" t="s">
-        <v>391</v>
+        <v>344</v>
+      </c>
+      <c r="C25" s="6">
+        <v>2355</v>
       </c>
       <c r="M25" s="6"/>
     </row>
     <row r="26" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B26" s="6" t="s">
-        <v>392</v>
-      </c>
-      <c r="C26" s="6" t="s">
-        <v>393</v>
+        <v>345</v>
+      </c>
+      <c r="C26" s="6">
+        <v>2497</v>
       </c>
       <c r="M26" s="6"/>
     </row>
     <row r="27" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B27" s="6" t="s">
-        <v>369</v>
-      </c>
-      <c r="C27" s="6" t="s">
-        <v>394</v>
+        <v>380</v>
+      </c>
+      <c r="C27" s="6">
+        <v>2527</v>
       </c>
       <c r="M27" s="6"/>
     </row>
     <row r="28" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B28" s="6" t="s">
-        <v>395</v>
+      <c r="B28" s="11" t="s">
+        <v>360</v>
       </c>
       <c r="C28" s="6">
-        <v>1014</v>
+        <v>2637</v>
       </c>
       <c r="M28" s="6"/>
     </row>
     <row r="29" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B29" s="6" t="s">
-        <v>369</v>
-      </c>
-      <c r="C29" s="6" t="s">
-        <v>396</v>
+      <c r="B29" s="11" t="s">
+        <v>382</v>
+      </c>
+      <c r="C29" s="6">
+        <v>2902</v>
       </c>
       <c r="M29" s="6"/>
     </row>
     <row r="30" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B30" s="6" t="s">
-        <v>357</v>
-      </c>
-      <c r="C30" s="6" t="s">
-        <v>397</v>
+        <v>379</v>
+      </c>
+      <c r="C30" s="6">
+        <v>3056</v>
       </c>
     </row>
     <row r="31" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B31" s="6" t="s">
-        <v>369</v>
-      </c>
-      <c r="C31" s="6" t="s">
-        <v>398</v>
+        <v>348</v>
+      </c>
+      <c r="C31" s="6">
+        <v>3115</v>
       </c>
       <c r="M31" s="6" t="s">
-        <v>355</v>
+        <v>351</v>
       </c>
     </row>
     <row r="32" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B32" s="6" t="s">
-        <v>399</v>
+        <v>377</v>
       </c>
       <c r="C32" s="6">
-        <v>5309</v>
+        <v>3286</v>
       </c>
       <c r="M32" s="6" t="s">
-        <v>356</v>
+        <v>352</v>
       </c>
     </row>
     <row r="33" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B33" s="6" t="s">
         <v>369</v>
       </c>
-      <c r="C33" s="6" t="s">
-        <v>400</v>
+      <c r="C33" s="6">
+        <v>3297</v>
       </c>
       <c r="M33" s="6" t="s">
-        <v>357</v>
+        <v>353</v>
       </c>
     </row>
     <row r="34" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B34" s="6" t="s">
         <v>355</v>
       </c>
-      <c r="C34" s="6" t="s">
-        <v>401</v>
+      <c r="C34" s="6">
+        <v>3300</v>
       </c>
     </row>
     <row r="35" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B35" s="6" t="s">
-        <v>402</v>
-      </c>
-      <c r="C35" s="6" t="s">
-        <v>403</v>
+        <v>370</v>
+      </c>
+      <c r="C35" s="6">
+        <v>3350</v>
       </c>
     </row>
     <row r="36" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B36" s="6" t="s">
-        <v>404</v>
-      </c>
-      <c r="C36" s="6" t="s">
-        <v>405</v>
+        <v>356</v>
+      </c>
+      <c r="C36" s="6">
+        <v>3404</v>
       </c>
     </row>
     <row r="37" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B37" s="6" t="s">
-        <v>406</v>
-      </c>
-      <c r="C37" s="6" t="s">
-        <v>407</v>
+        <v>356</v>
+      </c>
+      <c r="C37" s="6">
+        <v>3558</v>
       </c>
     </row>
     <row r="38" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B38" s="6" t="s">
-        <v>408</v>
+        <v>356</v>
       </c>
       <c r="C38" s="6">
-        <v>3056</v>
+        <v>3639</v>
       </c>
     </row>
     <row r="39" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B39" s="6" t="s">
-        <v>409</v>
-      </c>
-      <c r="C39" s="6" t="s">
-        <v>410</v>
+        <v>356</v>
+      </c>
+      <c r="C39" s="6">
+        <v>3793</v>
       </c>
     </row>
     <row r="40" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B40" s="6" t="s">
-        <v>411</v>
-      </c>
-      <c r="C40" s="6" t="s">
-        <v>412</v>
+        <v>356</v>
+      </c>
+      <c r="C40" s="6">
+        <v>3891</v>
       </c>
     </row>
     <row r="41" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B41" s="6" t="s">
-        <v>347</v>
+        <v>361</v>
       </c>
       <c r="C41" s="6">
-        <v>2497</v>
+        <v>3981</v>
       </c>
     </row>
     <row r="42" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B42" s="6" t="s">
-        <v>413</v>
-      </c>
-      <c r="C42" s="6" t="s">
-        <v>414</v>
+        <v>361</v>
+      </c>
+      <c r="C42" s="6">
+        <v>4075</v>
       </c>
     </row>
     <row r="43" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B43" s="6" t="s">
-        <v>415</v>
-      </c>
-      <c r="C43" s="6" t="s">
-        <v>416</v>
+        <v>361</v>
+      </c>
+      <c r="C43" s="6">
+        <v>4189</v>
       </c>
     </row>
     <row r="44" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B44" s="6" t="s">
-        <v>369</v>
-      </c>
-      <c r="C44" s="6" t="s">
-        <v>417</v>
+        <v>361</v>
+      </c>
+      <c r="C44" s="6">
+        <v>4262</v>
       </c>
     </row>
     <row r="45" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B45" s="6" t="s">
-        <v>356</v>
-      </c>
-      <c r="C45" s="6" t="s">
-        <v>418</v>
+        <v>361</v>
+      </c>
+      <c r="C45" s="6">
+        <v>4380</v>
       </c>
     </row>
     <row r="46" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B46" s="6" t="s">
-        <v>419</v>
-      </c>
-      <c r="C46" s="6" t="s">
-        <v>420</v>
+        <v>361</v>
+      </c>
+      <c r="C46" s="6">
+        <v>4409</v>
       </c>
     </row>
     <row r="47" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B47" s="6" t="s">
-        <v>421</v>
-      </c>
-      <c r="C47" s="6" t="s">
-        <v>422</v>
+        <v>373</v>
+      </c>
+      <c r="C47" s="6">
+        <v>4529</v>
       </c>
     </row>
     <row r="48" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B48" s="10" t="s">
-        <v>807</v>
-      </c>
-      <c r="C48" s="6" t="s">
-        <v>424</v>
+      <c r="B48" s="6" t="s">
+        <v>384</v>
+      </c>
+      <c r="C48" s="6">
+        <v>4696</v>
       </c>
     </row>
     <row r="49" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B49" s="6" t="s">
-        <v>425</v>
-      </c>
-      <c r="C49" s="6" t="s">
-        <v>426</v>
+        <v>338</v>
+      </c>
+      <c r="C49" s="6">
+        <v>4765</v>
       </c>
     </row>
     <row r="50" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B50" s="6" t="s">
-        <v>427</v>
-      </c>
-      <c r="C50" s="6" t="s">
-        <v>428</v>
+      <c r="B50" s="12" t="s">
+        <v>764</v>
+      </c>
+      <c r="C50" s="6">
+        <v>4800</v>
       </c>
     </row>
     <row r="51" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B51" s="6" t="s">
-        <v>429</v>
+        <v>381</v>
       </c>
       <c r="C51" s="6">
-        <v>547</v>
+        <v>4918</v>
       </c>
     </row>
     <row r="52" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B52" s="6" t="s">
-        <v>354</v>
-      </c>
-      <c r="C52" s="6" t="s">
-        <v>82</v>
+        <v>357</v>
+      </c>
+      <c r="C52" s="6">
+        <v>5013</v>
       </c>
     </row>
     <row r="53" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B53" s="6" t="s">
-        <v>361</v>
-      </c>
-      <c r="C53" s="6" t="s">
-        <v>430</v>
+        <v>385</v>
+      </c>
+      <c r="C53" s="6">
+        <v>5170</v>
       </c>
     </row>
     <row r="54" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B54" s="6" t="s">
-        <v>361</v>
-      </c>
-      <c r="C54" s="6" t="s">
-        <v>431</v>
+        <v>388</v>
+      </c>
+      <c r="C54" s="6">
+        <v>5293</v>
       </c>
     </row>
     <row r="55" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B55" s="6" t="s">
-        <v>432</v>
-      </c>
-      <c r="C55" s="6" t="s">
-        <v>433</v>
+        <v>376</v>
+      </c>
+      <c r="C55" s="6">
+        <v>5309</v>
       </c>
     </row>
     <row r="56" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B56" s="6" t="s">
-        <v>361</v>
-      </c>
-      <c r="C56" s="6" t="s">
-        <v>434</v>
+        <v>383</v>
+      </c>
+      <c r="C56" s="6">
+        <v>5476</v>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="B1:C56">
+    <sortState ref="B2:C56">
+      <sortCondition ref="C1"/>
+    </sortState>
+  </autoFilter>
   <phoneticPr fontId="0" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
@@ -3866,7 +3755,7 @@
         <v>1001</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>436</v>
+        <v>392</v>
       </c>
     </row>
     <row r="3" spans="2:3" x14ac:dyDescent="0.25">
@@ -3874,7 +3763,7 @@
         <v>1002</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>438</v>
+        <v>394</v>
       </c>
     </row>
     <row r="4" spans="2:3" x14ac:dyDescent="0.25">
@@ -3882,7 +3771,7 @@
         <v>1003</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>440</v>
+        <v>396</v>
       </c>
     </row>
     <row r="5" spans="2:3" x14ac:dyDescent="0.25">
@@ -3890,7 +3779,7 @@
         <v>1004</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>442</v>
+        <v>398</v>
       </c>
     </row>
     <row r="6" spans="2:3" x14ac:dyDescent="0.25">
@@ -3898,7 +3787,7 @@
         <v>1005</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>444</v>
+        <v>400</v>
       </c>
     </row>
     <row r="7" spans="2:3" x14ac:dyDescent="0.25">
@@ -3906,7 +3795,7 @@
         <v>1006</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>446</v>
+        <v>402</v>
       </c>
     </row>
     <row r="8" spans="2:3" x14ac:dyDescent="0.25">
@@ -3914,7 +3803,7 @@
         <v>1007</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>446</v>
+        <v>402</v>
       </c>
     </row>
     <row r="9" spans="2:3" x14ac:dyDescent="0.25">
@@ -3922,7 +3811,7 @@
         <v>1008</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>446</v>
+        <v>402</v>
       </c>
     </row>
     <row r="10" spans="2:3" x14ac:dyDescent="0.25">
@@ -3930,7 +3819,7 @@
         <v>1009</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>449</v>
+        <v>405</v>
       </c>
     </row>
     <row r="11" spans="2:3" x14ac:dyDescent="0.25">
@@ -3938,7 +3827,7 @@
         <v>1010</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>451</v>
+        <v>407</v>
       </c>
     </row>
     <row r="12" spans="2:3" x14ac:dyDescent="0.25">
@@ -3946,7 +3835,7 @@
         <v>1011</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>453</v>
+        <v>409</v>
       </c>
     </row>
     <row r="13" spans="2:3" x14ac:dyDescent="0.25">
@@ -3954,7 +3843,7 @@
         <v>1012</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>454</v>
+        <v>410</v>
       </c>
     </row>
     <row r="14" spans="2:3" x14ac:dyDescent="0.25">
@@ -3962,7 +3851,7 @@
         <v>1013</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>456</v>
+        <v>412</v>
       </c>
     </row>
     <row r="15" spans="2:3" x14ac:dyDescent="0.25">
@@ -3970,7 +3859,7 @@
         <v>1014</v>
       </c>
       <c r="C15" s="6" t="s">
-        <v>458</v>
+        <v>414</v>
       </c>
     </row>
     <row r="16" spans="2:3" x14ac:dyDescent="0.25">
@@ -3978,7 +3867,7 @@
         <v>1015</v>
       </c>
       <c r="C16" s="6" t="s">
-        <v>460</v>
+        <v>416</v>
       </c>
     </row>
     <row r="17" spans="2:3" x14ac:dyDescent="0.25">
@@ -3986,7 +3875,7 @@
         <v>1016</v>
       </c>
       <c r="C17" s="6" t="s">
-        <v>462</v>
+        <v>418</v>
       </c>
     </row>
     <row r="18" spans="2:3" x14ac:dyDescent="0.25">
@@ -3994,7 +3883,7 @@
         <v>1017</v>
       </c>
       <c r="C18" s="6" t="s">
-        <v>464</v>
+        <v>420</v>
       </c>
     </row>
     <row r="19" spans="2:3" x14ac:dyDescent="0.25">
@@ -4002,7 +3891,7 @@
         <v>1018</v>
       </c>
       <c r="C19" s="6" t="s">
-        <v>466</v>
+        <v>422</v>
       </c>
     </row>
     <row r="20" spans="2:3" x14ac:dyDescent="0.25">
@@ -4010,7 +3899,7 @@
         <v>1019</v>
       </c>
       <c r="C20" s="6" t="s">
-        <v>467</v>
+        <v>423</v>
       </c>
     </row>
     <row r="21" spans="2:3" x14ac:dyDescent="0.25">
@@ -4018,7 +3907,7 @@
         <v>1020</v>
       </c>
       <c r="C21" s="6" t="s">
-        <v>469</v>
+        <v>425</v>
       </c>
     </row>
     <row r="22" spans="2:3" x14ac:dyDescent="0.25">
@@ -4026,7 +3915,7 @@
         <v>1021</v>
       </c>
       <c r="C22" s="6" t="s">
-        <v>471</v>
+        <v>427</v>
       </c>
     </row>
     <row r="23" spans="2:3" x14ac:dyDescent="0.25">
@@ -4034,7 +3923,7 @@
         <v>1022</v>
       </c>
       <c r="C23" s="6" t="s">
-        <v>473</v>
+        <v>429</v>
       </c>
     </row>
     <row r="24" spans="2:3" x14ac:dyDescent="0.25">
@@ -4042,7 +3931,7 @@
         <v>1023</v>
       </c>
       <c r="C24" s="6" t="s">
-        <v>475</v>
+        <v>431</v>
       </c>
     </row>
     <row r="25" spans="2:3" x14ac:dyDescent="0.25">
@@ -4050,7 +3939,7 @@
         <v>1024</v>
       </c>
       <c r="C25" s="6" t="s">
-        <v>477</v>
+        <v>433</v>
       </c>
     </row>
     <row r="26" spans="2:3" x14ac:dyDescent="0.25">
@@ -4058,7 +3947,7 @@
         <v>1025</v>
       </c>
       <c r="C26" s="6" t="s">
-        <v>478</v>
+        <v>434</v>
       </c>
     </row>
     <row r="27" spans="2:3" x14ac:dyDescent="0.25">
@@ -4066,7 +3955,7 @@
         <v>1027</v>
       </c>
       <c r="C27" s="6" t="s">
-        <v>479</v>
+        <v>435</v>
       </c>
     </row>
     <row r="28" spans="2:3" x14ac:dyDescent="0.25">
@@ -4074,7 +3963,7 @@
         <v>1028</v>
       </c>
       <c r="C28" s="6" t="s">
-        <v>480</v>
+        <v>436</v>
       </c>
     </row>
     <row r="29" spans="2:3" x14ac:dyDescent="0.25">
@@ -4082,7 +3971,7 @@
         <v>1029</v>
       </c>
       <c r="C29" s="6" t="s">
-        <v>481</v>
+        <v>437</v>
       </c>
     </row>
     <row r="30" spans="2:3" x14ac:dyDescent="0.25">
@@ -4090,7 +3979,7 @@
         <v>1030</v>
       </c>
       <c r="C30" s="6" t="s">
-        <v>482</v>
+        <v>438</v>
       </c>
     </row>
     <row r="31" spans="2:3" x14ac:dyDescent="0.25">
@@ -4098,7 +3987,7 @@
         <v>1031</v>
       </c>
       <c r="C31" s="6" t="s">
-        <v>483</v>
+        <v>439</v>
       </c>
     </row>
     <row r="32" spans="2:3" x14ac:dyDescent="0.25">
@@ -4106,7 +3995,7 @@
         <v>1032</v>
       </c>
       <c r="C32" s="6" t="s">
-        <v>484</v>
+        <v>440</v>
       </c>
     </row>
     <row r="33" spans="2:3" x14ac:dyDescent="0.25">
@@ -4114,7 +4003,7 @@
         <v>1033</v>
       </c>
       <c r="C33" s="6" t="s">
-        <v>485</v>
+        <v>441</v>
       </c>
     </row>
     <row r="34" spans="2:3" x14ac:dyDescent="0.25">
@@ -4122,7 +4011,7 @@
         <v>1034</v>
       </c>
       <c r="C34" s="6" t="s">
-        <v>486</v>
+        <v>442</v>
       </c>
     </row>
     <row r="35" spans="2:3" x14ac:dyDescent="0.25">
@@ -4130,7 +4019,7 @@
         <v>1035</v>
       </c>
       <c r="C35" s="6" t="s">
-        <v>487</v>
+        <v>443</v>
       </c>
     </row>
     <row r="36" spans="2:3" x14ac:dyDescent="0.25">
@@ -4138,7 +4027,7 @@
         <v>1036</v>
       </c>
       <c r="C36" s="6" t="s">
-        <v>488</v>
+        <v>444</v>
       </c>
     </row>
     <row r="37" spans="2:3" x14ac:dyDescent="0.25">
@@ -4146,7 +4035,7 @@
         <v>1037</v>
       </c>
       <c r="C37" s="6" t="s">
-        <v>489</v>
+        <v>445</v>
       </c>
     </row>
     <row r="38" spans="2:3" x14ac:dyDescent="0.25">
@@ -4154,7 +4043,7 @@
         <v>1038</v>
       </c>
       <c r="C38" s="6" t="s">
-        <v>490</v>
+        <v>446</v>
       </c>
     </row>
     <row r="39" spans="2:3" x14ac:dyDescent="0.25">
@@ -4162,7 +4051,7 @@
         <v>1039</v>
       </c>
       <c r="C39" s="6" t="s">
-        <v>491</v>
+        <v>447</v>
       </c>
     </row>
     <row r="40" spans="2:3" x14ac:dyDescent="0.25">
@@ -4170,7 +4059,7 @@
         <v>1040</v>
       </c>
       <c r="C40" s="6" t="s">
-        <v>492</v>
+        <v>448</v>
       </c>
     </row>
     <row r="41" spans="2:3" x14ac:dyDescent="0.25">
@@ -4178,7 +4067,7 @@
         <v>1041</v>
       </c>
       <c r="C41" s="6" t="s">
-        <v>493</v>
+        <v>449</v>
       </c>
     </row>
     <row r="42" spans="2:3" x14ac:dyDescent="0.25">
@@ -4186,7 +4075,7 @@
         <v>1042</v>
       </c>
       <c r="C42" s="6" t="s">
-        <v>494</v>
+        <v>450</v>
       </c>
     </row>
     <row r="43" spans="2:3" x14ac:dyDescent="0.25">
@@ -4194,7 +4083,7 @@
         <v>1043</v>
       </c>
       <c r="C43" s="6" t="s">
-        <v>495</v>
+        <v>451</v>
       </c>
     </row>
     <row r="44" spans="2:3" x14ac:dyDescent="0.25">
@@ -4202,7 +4091,7 @@
         <v>1044</v>
       </c>
       <c r="C44" s="6" t="s">
-        <v>496</v>
+        <v>452</v>
       </c>
     </row>
     <row r="45" spans="2:3" x14ac:dyDescent="0.25">
@@ -4210,7 +4099,7 @@
         <v>1045</v>
       </c>
       <c r="C45" s="6" t="s">
-        <v>497</v>
+        <v>453</v>
       </c>
     </row>
     <row r="46" spans="2:3" x14ac:dyDescent="0.25">
@@ -4218,7 +4107,7 @@
         <v>1046</v>
       </c>
       <c r="C46" s="6" t="s">
-        <v>498</v>
+        <v>454</v>
       </c>
     </row>
     <row r="47" spans="2:3" x14ac:dyDescent="0.25">
@@ -4226,7 +4115,7 @@
         <v>1047</v>
       </c>
       <c r="C47" s="6" t="s">
-        <v>499</v>
+        <v>455</v>
       </c>
     </row>
     <row r="48" spans="2:3" x14ac:dyDescent="0.25">
@@ -4234,7 +4123,7 @@
         <v>1048</v>
       </c>
       <c r="C48" s="6" t="s">
-        <v>500</v>
+        <v>456</v>
       </c>
     </row>
     <row r="49" spans="2:3" x14ac:dyDescent="0.25">
@@ -4242,7 +4131,7 @@
         <v>1049</v>
       </c>
       <c r="C49" s="6" t="s">
-        <v>501</v>
+        <v>457</v>
       </c>
     </row>
     <row r="50" spans="2:3" x14ac:dyDescent="0.25">
@@ -4250,7 +4139,7 @@
         <v>1050</v>
       </c>
       <c r="C50" s="6" t="s">
-        <v>502</v>
+        <v>458</v>
       </c>
     </row>
     <row r="51" spans="2:3" x14ac:dyDescent="0.25">
@@ -4258,7 +4147,7 @@
         <v>1051</v>
       </c>
       <c r="C51" s="6" t="s">
-        <v>503</v>
+        <v>459</v>
       </c>
     </row>
     <row r="52" spans="2:3" x14ac:dyDescent="0.25">
@@ -4266,7 +4155,7 @@
         <v>1052</v>
       </c>
       <c r="C52" s="6" t="s">
-        <v>504</v>
+        <v>460</v>
       </c>
     </row>
     <row r="53" spans="2:3" x14ac:dyDescent="0.25">
@@ -4274,7 +4163,7 @@
         <v>1053</v>
       </c>
       <c r="C53" s="6" t="s">
-        <v>505</v>
+        <v>461</v>
       </c>
     </row>
     <row r="54" spans="2:3" x14ac:dyDescent="0.25">
@@ -4282,7 +4171,7 @@
         <v>1054</v>
       </c>
       <c r="C54" s="6" t="s">
-        <v>506</v>
+        <v>462</v>
       </c>
     </row>
     <row r="55" spans="2:3" x14ac:dyDescent="0.25">
@@ -4290,7 +4179,7 @@
         <v>1055</v>
       </c>
       <c r="C55" s="6" t="s">
-        <v>507</v>
+        <v>463</v>
       </c>
     </row>
     <row r="56" spans="2:3" x14ac:dyDescent="0.25">
@@ -4298,7 +4187,7 @@
         <v>1056</v>
       </c>
       <c r="C56" s="6" t="s">
-        <v>508</v>
+        <v>464</v>
       </c>
     </row>
     <row r="57" spans="2:3" x14ac:dyDescent="0.25">
@@ -4306,7 +4195,7 @@
         <v>1057</v>
       </c>
       <c r="C57" s="6" t="s">
-        <v>509</v>
+        <v>465</v>
       </c>
     </row>
     <row r="58" spans="2:3" x14ac:dyDescent="0.25">
@@ -4314,7 +4203,7 @@
         <v>1058</v>
       </c>
       <c r="C58" s="6" t="s">
-        <v>510</v>
+        <v>466</v>
       </c>
     </row>
     <row r="59" spans="2:3" x14ac:dyDescent="0.25">
@@ -4322,7 +4211,7 @@
         <v>1059</v>
       </c>
       <c r="C59" s="6" t="s">
-        <v>511</v>
+        <v>467</v>
       </c>
     </row>
     <row r="60" spans="2:3" x14ac:dyDescent="0.25">
@@ -4330,7 +4219,7 @@
         <v>1060</v>
       </c>
       <c r="C60" s="6" t="s">
-        <v>512</v>
+        <v>468</v>
       </c>
     </row>
     <row r="61" spans="2:3" x14ac:dyDescent="0.25">
@@ -4338,7 +4227,7 @@
         <v>1061</v>
       </c>
       <c r="C61" s="6" t="s">
-        <v>513</v>
+        <v>469</v>
       </c>
     </row>
     <row r="62" spans="2:3" x14ac:dyDescent="0.25">
@@ -4346,7 +4235,7 @@
         <v>1062</v>
       </c>
       <c r="C62" s="6" t="s">
-        <v>514</v>
+        <v>470</v>
       </c>
     </row>
     <row r="63" spans="2:3" x14ac:dyDescent="0.25">
@@ -4354,7 +4243,7 @@
         <v>1063</v>
       </c>
       <c r="C63" s="6" t="s">
-        <v>515</v>
+        <v>471</v>
       </c>
     </row>
     <row r="64" spans="2:3" x14ac:dyDescent="0.25">
@@ -4362,7 +4251,7 @@
         <v>1064</v>
       </c>
       <c r="C64" s="6" t="s">
-        <v>516</v>
+        <v>472</v>
       </c>
     </row>
     <row r="65" spans="2:3" x14ac:dyDescent="0.25">
@@ -4370,7 +4259,7 @@
         <v>1065</v>
       </c>
       <c r="C65" s="6" t="s">
-        <v>517</v>
+        <v>473</v>
       </c>
     </row>
     <row r="66" spans="2:3" x14ac:dyDescent="0.25">
@@ -4378,7 +4267,7 @@
         <v>1066</v>
       </c>
       <c r="C66" s="6" t="s">
-        <v>518</v>
+        <v>474</v>
       </c>
     </row>
     <row r="67" spans="2:3" x14ac:dyDescent="0.25">
@@ -4386,7 +4275,7 @@
         <v>1067</v>
       </c>
       <c r="C67" s="6" t="s">
-        <v>519</v>
+        <v>475</v>
       </c>
     </row>
     <row r="68" spans="2:3" x14ac:dyDescent="0.25">
@@ -4394,7 +4283,7 @@
         <v>1068</v>
       </c>
       <c r="C68" s="6" t="s">
-        <v>520</v>
+        <v>476</v>
       </c>
     </row>
     <row r="69" spans="2:3" x14ac:dyDescent="0.25">
@@ -4402,7 +4291,7 @@
         <v>1069</v>
       </c>
       <c r="C69" s="6" t="s">
-        <v>521</v>
+        <v>477</v>
       </c>
     </row>
     <row r="70" spans="2:3" x14ac:dyDescent="0.25">
@@ -4410,7 +4299,7 @@
         <v>1070</v>
       </c>
       <c r="C70" s="6" t="s">
-        <v>522</v>
+        <v>478</v>
       </c>
     </row>
     <row r="71" spans="2:3" x14ac:dyDescent="0.25">
@@ -4418,7 +4307,7 @@
         <v>1071</v>
       </c>
       <c r="C71" s="6" t="s">
-        <v>523</v>
+        <v>479</v>
       </c>
     </row>
     <row r="72" spans="2:3" x14ac:dyDescent="0.25">
@@ -4426,7 +4315,7 @@
         <v>1072</v>
       </c>
       <c r="C72" s="6" t="s">
-        <v>524</v>
+        <v>480</v>
       </c>
     </row>
     <row r="73" spans="2:3" x14ac:dyDescent="0.25">
@@ -4434,7 +4323,7 @@
         <v>1073</v>
       </c>
       <c r="C73" s="6" t="s">
-        <v>525</v>
+        <v>481</v>
       </c>
     </row>
     <row r="74" spans="2:3" x14ac:dyDescent="0.25">
@@ -4442,7 +4331,7 @@
         <v>1074</v>
       </c>
       <c r="C74" s="6" t="s">
-        <v>526</v>
+        <v>482</v>
       </c>
     </row>
     <row r="75" spans="2:3" x14ac:dyDescent="0.25">
@@ -4450,7 +4339,7 @@
         <v>1075</v>
       </c>
       <c r="C75" s="6" t="s">
-        <v>527</v>
+        <v>483</v>
       </c>
     </row>
     <row r="76" spans="2:3" x14ac:dyDescent="0.25">
@@ -4458,7 +4347,7 @@
         <v>1076</v>
       </c>
       <c r="C76" s="6" t="s">
-        <v>528</v>
+        <v>484</v>
       </c>
     </row>
     <row r="77" spans="2:3" x14ac:dyDescent="0.25">
@@ -4466,7 +4355,7 @@
         <v>1077</v>
       </c>
       <c r="C77" s="6" t="s">
-        <v>529</v>
+        <v>485</v>
       </c>
     </row>
     <row r="78" spans="2:3" x14ac:dyDescent="0.25">
@@ -4474,7 +4363,7 @@
         <v>1078</v>
       </c>
       <c r="C78" s="6" t="s">
-        <v>392</v>
+        <v>374</v>
       </c>
     </row>
     <row r="79" spans="2:3" x14ac:dyDescent="0.25">
@@ -4482,7 +4371,7 @@
         <v>1079</v>
       </c>
       <c r="C79" s="6" t="s">
-        <v>530</v>
+        <v>486</v>
       </c>
     </row>
     <row r="80" spans="2:3" x14ac:dyDescent="0.25">
@@ -4490,7 +4379,7 @@
         <v>1080</v>
       </c>
       <c r="C80" s="6" t="s">
-        <v>531</v>
+        <v>487</v>
       </c>
     </row>
     <row r="81" spans="2:3" x14ac:dyDescent="0.25">
@@ -4498,7 +4387,7 @@
         <v>1081</v>
       </c>
       <c r="C81" s="6" t="s">
-        <v>532</v>
+        <v>488</v>
       </c>
     </row>
     <row r="82" spans="2:3" x14ac:dyDescent="0.25">
@@ -4506,7 +4395,7 @@
         <v>1082</v>
       </c>
       <c r="C82" s="6" t="s">
-        <v>533</v>
+        <v>489</v>
       </c>
     </row>
     <row r="83" spans="2:3" x14ac:dyDescent="0.25">
@@ -4514,7 +4403,7 @@
         <v>1083</v>
       </c>
       <c r="C83" s="6" t="s">
-        <v>534</v>
+        <v>490</v>
       </c>
     </row>
     <row r="84" spans="2:3" x14ac:dyDescent="0.25">
@@ -4522,7 +4411,7 @@
         <v>1084</v>
       </c>
       <c r="C84" s="6" t="s">
-        <v>535</v>
+        <v>491</v>
       </c>
     </row>
     <row r="85" spans="2:3" x14ac:dyDescent="0.25">
@@ -4530,7 +4419,7 @@
         <v>1085</v>
       </c>
       <c r="C85" s="6" t="s">
-        <v>536</v>
+        <v>492</v>
       </c>
     </row>
     <row r="86" spans="2:3" x14ac:dyDescent="0.25">
@@ -4538,7 +4427,7 @@
         <v>1086</v>
       </c>
       <c r="C86" s="6" t="s">
-        <v>537</v>
+        <v>493</v>
       </c>
     </row>
     <row r="87" spans="2:3" x14ac:dyDescent="0.25">
@@ -4546,7 +4435,7 @@
         <v>1087</v>
       </c>
       <c r="C87" s="6" t="s">
-        <v>538</v>
+        <v>494</v>
       </c>
     </row>
     <row r="88" spans="2:3" x14ac:dyDescent="0.25">
@@ -4554,7 +4443,7 @@
         <v>1088</v>
       </c>
       <c r="C88" s="6" t="s">
-        <v>539</v>
+        <v>495</v>
       </c>
     </row>
     <row r="89" spans="2:3" x14ac:dyDescent="0.25">
@@ -4562,7 +4451,7 @@
         <v>1089</v>
       </c>
       <c r="C89" s="6" t="s">
-        <v>540</v>
+        <v>496</v>
       </c>
     </row>
     <row r="90" spans="2:3" x14ac:dyDescent="0.25">
@@ -4570,7 +4459,7 @@
         <v>1090</v>
       </c>
       <c r="C90" s="6" t="s">
-        <v>541</v>
+        <v>497</v>
       </c>
     </row>
     <row r="91" spans="2:3" x14ac:dyDescent="0.25">
@@ -4578,7 +4467,7 @@
         <v>1091</v>
       </c>
       <c r="C91" s="6" t="s">
-        <v>542</v>
+        <v>498</v>
       </c>
     </row>
     <row r="92" spans="2:3" x14ac:dyDescent="0.25">
@@ -4586,7 +4475,7 @@
         <v>1092</v>
       </c>
       <c r="C92" s="6" t="s">
-        <v>543</v>
+        <v>499</v>
       </c>
     </row>
     <row r="93" spans="2:3" x14ac:dyDescent="0.25">
@@ -4594,7 +4483,7 @@
         <v>1093</v>
       </c>
       <c r="C93" s="6" t="s">
-        <v>544</v>
+        <v>500</v>
       </c>
     </row>
     <row r="94" spans="2:3" x14ac:dyDescent="0.25">
@@ -4602,7 +4491,7 @@
         <v>1094</v>
       </c>
       <c r="C94" s="6" t="s">
-        <v>545</v>
+        <v>501</v>
       </c>
     </row>
     <row r="95" spans="2:3" x14ac:dyDescent="0.25">
@@ -4610,7 +4499,7 @@
         <v>1095</v>
       </c>
       <c r="C95" s="6" t="s">
-        <v>546</v>
+        <v>502</v>
       </c>
     </row>
     <row r="96" spans="2:3" x14ac:dyDescent="0.25">
@@ -4618,7 +4507,7 @@
         <v>1096</v>
       </c>
       <c r="C96" s="6" t="s">
-        <v>547</v>
+        <v>503</v>
       </c>
     </row>
     <row r="97" spans="2:3" x14ac:dyDescent="0.25">
@@ -4626,7 +4515,7 @@
         <v>1097</v>
       </c>
       <c r="C97" s="6" t="s">
-        <v>548</v>
+        <v>504</v>
       </c>
     </row>
     <row r="98" spans="2:3" x14ac:dyDescent="0.25">
@@ -4634,7 +4523,7 @@
         <v>1098</v>
       </c>
       <c r="C98" s="6" t="s">
-        <v>549</v>
+        <v>505</v>
       </c>
     </row>
     <row r="99" spans="2:3" x14ac:dyDescent="0.25">
@@ -4642,7 +4531,7 @@
         <v>1099</v>
       </c>
       <c r="C99" s="6" t="s">
-        <v>550</v>
+        <v>506</v>
       </c>
     </row>
     <row r="100" spans="2:3" x14ac:dyDescent="0.25">
@@ -4650,7 +4539,7 @@
         <v>1100</v>
       </c>
       <c r="C100" s="6" t="s">
-        <v>552</v>
+        <v>508</v>
       </c>
     </row>
     <row r="101" spans="2:3" x14ac:dyDescent="0.25">
@@ -4658,7 +4547,7 @@
         <v>1101</v>
       </c>
       <c r="C101" s="6" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
     </row>
     <row r="102" spans="2:3" x14ac:dyDescent="0.25">
@@ -4666,7 +4555,7 @@
         <v>1102</v>
       </c>
       <c r="C102" s="6" t="s">
-        <v>554</v>
+        <v>510</v>
       </c>
     </row>
     <row r="103" spans="2:3" x14ac:dyDescent="0.25">
@@ -4674,7 +4563,7 @@
         <v>1103</v>
       </c>
       <c r="C103" s="6" t="s">
-        <v>556</v>
+        <v>512</v>
       </c>
     </row>
     <row r="104" spans="2:3" x14ac:dyDescent="0.25">
@@ -4682,7 +4571,7 @@
         <v>1104</v>
       </c>
       <c r="C104" s="6" t="s">
-        <v>557</v>
+        <v>513</v>
       </c>
     </row>
     <row r="105" spans="2:3" x14ac:dyDescent="0.25">
@@ -4690,7 +4579,7 @@
         <v>1105</v>
       </c>
       <c r="C105" s="6" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
     </row>
     <row r="106" spans="2:3" x14ac:dyDescent="0.25">
@@ -4698,7 +4587,7 @@
         <v>1106</v>
       </c>
       <c r="C106" s="6" t="s">
-        <v>560</v>
+        <v>516</v>
       </c>
     </row>
     <row r="107" spans="2:3" x14ac:dyDescent="0.25">
@@ -4706,7 +4595,7 @@
         <v>1107</v>
       </c>
       <c r="C107" s="6" t="s">
-        <v>423</v>
+        <v>386</v>
       </c>
     </row>
     <row r="108" spans="2:3" x14ac:dyDescent="0.25">
@@ -4714,7 +4603,7 @@
         <v>1108</v>
       </c>
       <c r="C108" s="6" t="s">
-        <v>561</v>
+        <v>517</v>
       </c>
     </row>
     <row r="109" spans="2:3" x14ac:dyDescent="0.25">
@@ -4722,7 +4611,7 @@
         <v>1109</v>
       </c>
       <c r="C109" s="6" t="s">
-        <v>563</v>
+        <v>519</v>
       </c>
     </row>
     <row r="110" spans="2:3" x14ac:dyDescent="0.25">
@@ -4730,7 +4619,7 @@
         <v>1110</v>
       </c>
       <c r="C110" s="6" t="s">
-        <v>565</v>
+        <v>521</v>
       </c>
     </row>
     <row r="111" spans="2:3" x14ac:dyDescent="0.25">
@@ -4738,7 +4627,7 @@
         <v>1111</v>
       </c>
       <c r="C111" s="6" t="s">
-        <v>567</v>
+        <v>523</v>
       </c>
     </row>
     <row r="112" spans="2:3" x14ac:dyDescent="0.25">
@@ -4746,7 +4635,7 @@
         <v>1112</v>
       </c>
       <c r="C112" s="6" t="s">
-        <v>568</v>
+        <v>524</v>
       </c>
     </row>
     <row r="113" spans="2:3" x14ac:dyDescent="0.25">
@@ -4754,7 +4643,7 @@
         <v>1113</v>
       </c>
       <c r="C113" s="6" t="s">
-        <v>570</v>
+        <v>526</v>
       </c>
     </row>
     <row r="114" spans="2:3" x14ac:dyDescent="0.25">
@@ -4762,7 +4651,7 @@
         <v>1114</v>
       </c>
       <c r="C114" s="6" t="s">
-        <v>572</v>
+        <v>528</v>
       </c>
     </row>
     <row r="115" spans="2:3" x14ac:dyDescent="0.25">
@@ -4770,7 +4659,7 @@
         <v>1115</v>
       </c>
       <c r="C115" s="6" t="s">
-        <v>533</v>
+        <v>489</v>
       </c>
     </row>
     <row r="116" spans="2:3" x14ac:dyDescent="0.25">
@@ -4778,7 +4667,7 @@
         <v>1116</v>
       </c>
       <c r="C116" s="6" t="s">
-        <v>575</v>
+        <v>531</v>
       </c>
     </row>
     <row r="117" spans="2:3" x14ac:dyDescent="0.25">
@@ -4786,7 +4675,7 @@
         <v>1117</v>
       </c>
       <c r="C117" s="6" t="s">
-        <v>383</v>
+        <v>369</v>
       </c>
     </row>
     <row r="118" spans="2:3" x14ac:dyDescent="0.25">
@@ -4794,7 +4683,7 @@
         <v>1118</v>
       </c>
       <c r="C118" s="6" t="s">
-        <v>367</v>
+        <v>360</v>
       </c>
     </row>
     <row r="119" spans="2:3" x14ac:dyDescent="0.25">
@@ -4802,7 +4691,7 @@
         <v>1119</v>
       </c>
       <c r="C119" s="6" t="s">
-        <v>577</v>
+        <v>533</v>
       </c>
     </row>
     <row r="120" spans="2:3" x14ac:dyDescent="0.25">
@@ -4810,7 +4699,7 @@
         <v>1120</v>
       </c>
       <c r="C120" s="6" t="s">
-        <v>578</v>
+        <v>534</v>
       </c>
     </row>
     <row r="121" spans="2:3" x14ac:dyDescent="0.25">
@@ -4818,7 +4707,7 @@
         <v>1121</v>
       </c>
       <c r="C121" s="6" t="s">
-        <v>579</v>
+        <v>535</v>
       </c>
     </row>
     <row r="122" spans="2:3" x14ac:dyDescent="0.25">
@@ -4826,7 +4715,7 @@
         <v>1122</v>
       </c>
       <c r="C122" s="6" t="s">
-        <v>580</v>
+        <v>536</v>
       </c>
     </row>
     <row r="123" spans="2:3" x14ac:dyDescent="0.25">
@@ -4834,7 +4723,7 @@
         <v>1123</v>
       </c>
       <c r="C123" s="6" t="s">
-        <v>581</v>
+        <v>537</v>
       </c>
     </row>
     <row r="124" spans="2:3" x14ac:dyDescent="0.25">
@@ -4842,7 +4731,7 @@
         <v>1124</v>
       </c>
       <c r="C124" s="6" t="s">
-        <v>582</v>
+        <v>538</v>
       </c>
     </row>
     <row r="125" spans="2:3" x14ac:dyDescent="0.25">
@@ -4850,7 +4739,7 @@
         <v>1125</v>
       </c>
       <c r="C125" s="6" t="s">
-        <v>583</v>
+        <v>539</v>
       </c>
     </row>
     <row r="126" spans="2:3" x14ac:dyDescent="0.25">
@@ -4858,7 +4747,7 @@
         <v>1126</v>
       </c>
       <c r="C126" s="6" t="s">
-        <v>584</v>
+        <v>540</v>
       </c>
     </row>
     <row r="127" spans="2:3" x14ac:dyDescent="0.25">
@@ -4866,7 +4755,7 @@
         <v>1127</v>
       </c>
       <c r="C127" s="6" t="s">
-        <v>585</v>
+        <v>541</v>
       </c>
     </row>
     <row r="128" spans="2:3" x14ac:dyDescent="0.25">
@@ -4874,7 +4763,7 @@
         <v>1128</v>
       </c>
       <c r="C128" s="6" t="s">
-        <v>586</v>
+        <v>542</v>
       </c>
     </row>
     <row r="129" spans="2:3" x14ac:dyDescent="0.25">
@@ -4882,7 +4771,7 @@
         <v>1129</v>
       </c>
       <c r="C129" s="6" t="s">
-        <v>587</v>
+        <v>543</v>
       </c>
     </row>
     <row r="130" spans="2:3" x14ac:dyDescent="0.25">
@@ -4890,7 +4779,7 @@
         <v>1130</v>
       </c>
       <c r="C130" s="6" t="s">
-        <v>588</v>
+        <v>544</v>
       </c>
     </row>
     <row r="131" spans="2:3" x14ac:dyDescent="0.25">
@@ -4898,7 +4787,7 @@
         <v>1131</v>
       </c>
       <c r="C131" s="6" t="s">
-        <v>589</v>
+        <v>545</v>
       </c>
     </row>
     <row r="132" spans="2:3" x14ac:dyDescent="0.25">
@@ -4906,7 +4795,7 @@
         <v>1134</v>
       </c>
       <c r="C132" s="6" t="s">
-        <v>590</v>
+        <v>546</v>
       </c>
     </row>
     <row r="133" spans="2:3" x14ac:dyDescent="0.25">
@@ -4914,7 +4803,7 @@
         <v>1135</v>
       </c>
       <c r="C133" s="6" t="s">
-        <v>591</v>
+        <v>547</v>
       </c>
     </row>
     <row r="134" spans="2:3" x14ac:dyDescent="0.25">
@@ -4922,7 +4811,7 @@
         <v>1136</v>
       </c>
       <c r="C134" s="6" t="s">
-        <v>592</v>
+        <v>548</v>
       </c>
     </row>
     <row r="135" spans="2:3" x14ac:dyDescent="0.25">
@@ -4930,7 +4819,7 @@
         <v>1137</v>
       </c>
       <c r="C135" s="6" t="s">
-        <v>593</v>
+        <v>549</v>
       </c>
     </row>
     <row r="136" spans="2:3" x14ac:dyDescent="0.25">
@@ -4938,7 +4827,7 @@
         <v>1138</v>
       </c>
       <c r="C136" s="6" t="s">
-        <v>594</v>
+        <v>550</v>
       </c>
     </row>
     <row r="137" spans="2:3" x14ac:dyDescent="0.25">
@@ -4946,7 +4835,7 @@
         <v>1139</v>
       </c>
       <c r="C137" s="6" t="s">
-        <v>595</v>
+        <v>551</v>
       </c>
     </row>
     <row r="138" spans="2:3" x14ac:dyDescent="0.25">
@@ -4954,7 +4843,7 @@
         <v>1140</v>
       </c>
       <c r="C138" s="6" t="s">
-        <v>596</v>
+        <v>552</v>
       </c>
     </row>
     <row r="139" spans="2:3" x14ac:dyDescent="0.25">
@@ -4962,7 +4851,7 @@
         <v>1141</v>
       </c>
       <c r="C139" s="6" t="s">
-        <v>597</v>
+        <v>553</v>
       </c>
     </row>
     <row r="140" spans="2:3" x14ac:dyDescent="0.25">
@@ -4970,7 +4859,7 @@
         <v>1142</v>
       </c>
       <c r="C140" s="6" t="s">
-        <v>598</v>
+        <v>554</v>
       </c>
     </row>
     <row r="141" spans="2:3" x14ac:dyDescent="0.25">
@@ -4978,7 +4867,7 @@
         <v>1143</v>
       </c>
       <c r="C141" s="6" t="s">
-        <v>599</v>
+        <v>555</v>
       </c>
     </row>
     <row r="142" spans="2:3" x14ac:dyDescent="0.25">
@@ -4986,7 +4875,7 @@
         <v>1144</v>
       </c>
       <c r="C142" s="6" t="s">
-        <v>600</v>
+        <v>556</v>
       </c>
     </row>
     <row r="143" spans="2:3" x14ac:dyDescent="0.25">
@@ -4994,7 +4883,7 @@
         <v>1145</v>
       </c>
       <c r="C143" s="6" t="s">
-        <v>601</v>
+        <v>557</v>
       </c>
     </row>
     <row r="144" spans="2:3" x14ac:dyDescent="0.25">
@@ -5002,7 +4891,7 @@
         <v>1146</v>
       </c>
       <c r="C144" s="6" t="s">
-        <v>602</v>
+        <v>558</v>
       </c>
     </row>
     <row r="145" spans="2:3" x14ac:dyDescent="0.25">
@@ -5010,7 +4899,7 @@
         <v>1147</v>
       </c>
       <c r="C145" s="6" t="s">
-        <v>603</v>
+        <v>559</v>
       </c>
     </row>
     <row r="146" spans="2:3" x14ac:dyDescent="0.25">
@@ -5018,7 +4907,7 @@
         <v>1148</v>
       </c>
       <c r="C146" s="6" t="s">
-        <v>604</v>
+        <v>560</v>
       </c>
     </row>
     <row r="147" spans="2:3" x14ac:dyDescent="0.25">
@@ -5026,7 +4915,7 @@
         <v>1149</v>
       </c>
       <c r="C147" s="6" t="s">
-        <v>605</v>
+        <v>561</v>
       </c>
     </row>
     <row r="148" spans="2:3" x14ac:dyDescent="0.25">
@@ -5034,7 +4923,7 @@
         <v>1150</v>
       </c>
       <c r="C148" s="6" t="s">
-        <v>606</v>
+        <v>562</v>
       </c>
     </row>
     <row r="149" spans="2:3" x14ac:dyDescent="0.25">
@@ -5042,7 +4931,7 @@
         <v>1151</v>
       </c>
       <c r="C149" s="6" t="s">
-        <v>607</v>
+        <v>563</v>
       </c>
     </row>
     <row r="150" spans="2:3" x14ac:dyDescent="0.25">
@@ -5050,7 +4939,7 @@
         <v>1152</v>
       </c>
       <c r="C150" s="6" t="s">
-        <v>608</v>
+        <v>564</v>
       </c>
     </row>
     <row r="151" spans="2:3" x14ac:dyDescent="0.25">
@@ -5058,7 +4947,7 @@
         <v>1153</v>
       </c>
       <c r="C151" s="6" t="s">
-        <v>609</v>
+        <v>565</v>
       </c>
     </row>
     <row r="152" spans="2:3" x14ac:dyDescent="0.25">
@@ -5066,7 +4955,7 @@
         <v>1154</v>
       </c>
       <c r="C152" s="6" t="s">
-        <v>610</v>
+        <v>566</v>
       </c>
     </row>
     <row r="153" spans="2:3" x14ac:dyDescent="0.25">
@@ -5074,7 +4963,7 @@
         <v>1155</v>
       </c>
       <c r="C153" s="6" t="s">
-        <v>611</v>
+        <v>567</v>
       </c>
     </row>
     <row r="154" spans="2:3" x14ac:dyDescent="0.25">
@@ -5082,7 +4971,7 @@
         <v>1156</v>
       </c>
       <c r="C154" s="6" t="s">
-        <v>612</v>
+        <v>568</v>
       </c>
     </row>
     <row r="155" spans="2:3" x14ac:dyDescent="0.25">
@@ -5090,7 +4979,7 @@
         <v>1157</v>
       </c>
       <c r="C155" s="6" t="s">
-        <v>613</v>
+        <v>569</v>
       </c>
     </row>
     <row r="156" spans="2:3" x14ac:dyDescent="0.25">
@@ -5098,7 +4987,7 @@
         <v>1158</v>
       </c>
       <c r="C156" s="6" t="s">
-        <v>614</v>
+        <v>570</v>
       </c>
     </row>
     <row r="157" spans="2:3" x14ac:dyDescent="0.25">
@@ -5106,7 +4995,7 @@
         <v>1159</v>
       </c>
       <c r="C157" s="6" t="s">
-        <v>615</v>
+        <v>571</v>
       </c>
     </row>
     <row r="158" spans="2:3" x14ac:dyDescent="0.25">
@@ -5114,7 +5003,7 @@
         <v>1160</v>
       </c>
       <c r="C158" s="6" t="s">
-        <v>616</v>
+        <v>572</v>
       </c>
     </row>
     <row r="159" spans="2:3" x14ac:dyDescent="0.25">
@@ -5122,7 +5011,7 @@
         <v>1161</v>
       </c>
       <c r="C159" s="6" t="s">
-        <v>617</v>
+        <v>573</v>
       </c>
     </row>
     <row r="160" spans="2:3" x14ac:dyDescent="0.25">
@@ -5130,7 +5019,7 @@
         <v>1162</v>
       </c>
       <c r="C160" s="6" t="s">
-        <v>618</v>
+        <v>574</v>
       </c>
     </row>
     <row r="161" spans="2:3" x14ac:dyDescent="0.25">
@@ -5138,7 +5027,7 @@
         <v>1163</v>
       </c>
       <c r="C161" s="6" t="s">
-        <v>619</v>
+        <v>575</v>
       </c>
     </row>
     <row r="162" spans="2:3" x14ac:dyDescent="0.25">
@@ -5146,7 +5035,7 @@
         <v>1164</v>
       </c>
       <c r="C162" s="6" t="s">
-        <v>620</v>
+        <v>576</v>
       </c>
     </row>
     <row r="163" spans="2:3" x14ac:dyDescent="0.25">
@@ -5154,7 +5043,7 @@
         <v>1165</v>
       </c>
       <c r="C163" s="6" t="s">
-        <v>621</v>
+        <v>577</v>
       </c>
     </row>
     <row r="164" spans="2:3" x14ac:dyDescent="0.25">
@@ -5162,7 +5051,7 @@
         <v>1166</v>
       </c>
       <c r="C164" s="6" t="s">
-        <v>622</v>
+        <v>578</v>
       </c>
     </row>
     <row r="165" spans="2:3" x14ac:dyDescent="0.25">
@@ -5170,7 +5059,7 @@
         <v>1167</v>
       </c>
       <c r="C165" s="6" t="s">
-        <v>623</v>
+        <v>579</v>
       </c>
     </row>
     <row r="166" spans="2:3" x14ac:dyDescent="0.25">
@@ -5178,7 +5067,7 @@
         <v>1168</v>
       </c>
       <c r="C166" s="6" t="s">
-        <v>624</v>
+        <v>580</v>
       </c>
     </row>
     <row r="167" spans="2:3" x14ac:dyDescent="0.25">
@@ -5186,7 +5075,7 @@
         <v>1200</v>
       </c>
       <c r="C167" s="6" t="s">
-        <v>625</v>
+        <v>581</v>
       </c>
     </row>
     <row r="168" spans="2:3" x14ac:dyDescent="0.25">
@@ -5194,7 +5083,7 @@
         <v>1201</v>
       </c>
       <c r="C168" s="6" t="s">
-        <v>626</v>
+        <v>582</v>
       </c>
     </row>
     <row r="169" spans="2:3" x14ac:dyDescent="0.25">
@@ -5202,7 +5091,7 @@
         <v>1202</v>
       </c>
       <c r="C169" s="6" t="s">
-        <v>627</v>
+        <v>583</v>
       </c>
     </row>
     <row r="170" spans="2:3" x14ac:dyDescent="0.25">
@@ -5210,7 +5099,7 @@
         <v>1203</v>
       </c>
       <c r="C170" s="6" t="s">
-        <v>628</v>
+        <v>584</v>
       </c>
     </row>
     <row r="171" spans="2:3" x14ac:dyDescent="0.25">
@@ -5218,7 +5107,7 @@
         <v>1204</v>
       </c>
       <c r="C171" s="6" t="s">
-        <v>629</v>
+        <v>585</v>
       </c>
     </row>
     <row r="172" spans="2:3" x14ac:dyDescent="0.25">
@@ -5226,7 +5115,7 @@
         <v>1205</v>
       </c>
       <c r="C172" s="6" t="s">
-        <v>630</v>
+        <v>586</v>
       </c>
     </row>
     <row r="173" spans="2:3" x14ac:dyDescent="0.25">
@@ -5234,7 +5123,7 @@
         <v>1206</v>
       </c>
       <c r="C173" s="6" t="s">
-        <v>631</v>
+        <v>587</v>
       </c>
     </row>
     <row r="174" spans="2:3" x14ac:dyDescent="0.25">
@@ -5242,7 +5131,7 @@
         <v>1207</v>
       </c>
       <c r="C174" s="6" t="s">
-        <v>632</v>
+        <v>588</v>
       </c>
     </row>
     <row r="175" spans="2:3" x14ac:dyDescent="0.25">
@@ -5250,7 +5139,7 @@
         <v>1208</v>
       </c>
       <c r="C175" s="6" t="s">
-        <v>633</v>
+        <v>589</v>
       </c>
     </row>
     <row r="176" spans="2:3" x14ac:dyDescent="0.25">
@@ -5258,7 +5147,7 @@
         <v>1209</v>
       </c>
       <c r="C176" s="6" t="s">
-        <v>634</v>
+        <v>590</v>
       </c>
     </row>
     <row r="177" spans="2:3" x14ac:dyDescent="0.25">
@@ -5266,7 +5155,7 @@
         <v>1210</v>
       </c>
       <c r="C177" s="6" t="s">
-        <v>635</v>
+        <v>591</v>
       </c>
     </row>
     <row r="178" spans="2:3" x14ac:dyDescent="0.25">
@@ -5274,7 +5163,7 @@
         <v>1290</v>
       </c>
       <c r="C178" s="6" t="s">
-        <v>636</v>
+        <v>592</v>
       </c>
     </row>
     <row r="179" spans="2:3" x14ac:dyDescent="0.25">
@@ -5282,7 +5171,7 @@
         <v>1300</v>
       </c>
       <c r="C179" s="6" t="s">
-        <v>637</v>
+        <v>593</v>
       </c>
     </row>
     <row r="180" spans="2:3" x14ac:dyDescent="0.25">
@@ -5290,7 +5179,7 @@
         <v>1301</v>
       </c>
       <c r="C180" s="6" t="s">
-        <v>638</v>
+        <v>594</v>
       </c>
     </row>
     <row r="181" spans="2:3" x14ac:dyDescent="0.25">
@@ -5298,7 +5187,7 @@
         <v>1302</v>
       </c>
       <c r="C181" s="6" t="s">
-        <v>639</v>
+        <v>595</v>
       </c>
     </row>
     <row r="182" spans="2:3" x14ac:dyDescent="0.25">
@@ -5306,7 +5195,7 @@
         <v>164</v>
       </c>
       <c r="C182" s="6" t="s">
-        <v>640</v>
+        <v>596</v>
       </c>
     </row>
     <row r="183" spans="2:3" x14ac:dyDescent="0.25">
@@ -5314,7 +5203,7 @@
         <v>2000</v>
       </c>
       <c r="C183" s="6" t="s">
-        <v>641</v>
+        <v>597</v>
       </c>
     </row>
     <row r="184" spans="2:3" x14ac:dyDescent="0.25">
@@ -5322,7 +5211,7 @@
         <v>8000</v>
       </c>
       <c r="C184" s="6" t="s">
-        <v>642</v>
+        <v>598</v>
       </c>
     </row>
     <row r="185" spans="2:3" x14ac:dyDescent="0.25">
@@ -5330,7 +5219,7 @@
         <v>8001</v>
       </c>
       <c r="C185" s="6" t="s">
-        <v>644</v>
+        <v>600</v>
       </c>
     </row>
     <row r="186" spans="2:3" x14ac:dyDescent="0.25">
@@ -5338,7 +5227,7 @@
         <v>8002</v>
       </c>
       <c r="C186" s="6" t="s">
-        <v>646</v>
+        <v>602</v>
       </c>
     </row>
     <row r="187" spans="2:3" x14ac:dyDescent="0.25">
@@ -5346,7 +5235,7 @@
         <v>8003</v>
       </c>
       <c r="C187" s="6" t="s">
-        <v>648</v>
+        <v>604</v>
       </c>
     </row>
     <row r="188" spans="2:3" x14ac:dyDescent="0.25">
@@ -5354,7 +5243,7 @@
         <v>8004</v>
       </c>
       <c r="C188" s="6" t="s">
-        <v>650</v>
+        <v>606</v>
       </c>
     </row>
     <row r="189" spans="2:3" x14ac:dyDescent="0.25">
@@ -5362,7 +5251,7 @@
         <v>8005</v>
       </c>
       <c r="C189" s="6" t="s">
-        <v>652</v>
+        <v>608</v>
       </c>
     </row>
     <row r="190" spans="2:3" x14ac:dyDescent="0.25">
@@ -5370,7 +5259,7 @@
         <v>8006</v>
       </c>
       <c r="C190" s="6" t="s">
-        <v>653</v>
+        <v>609</v>
       </c>
     </row>
     <row r="191" spans="2:3" x14ac:dyDescent="0.25">
@@ -5378,7 +5267,7 @@
         <v>8007</v>
       </c>
       <c r="C191" s="6" t="s">
-        <v>654</v>
+        <v>610</v>
       </c>
     </row>
     <row r="192" spans="2:3" x14ac:dyDescent="0.25">
@@ -5386,7 +5275,7 @@
         <v>8008</v>
       </c>
       <c r="C192" s="6" t="s">
-        <v>655</v>
+        <v>611</v>
       </c>
     </row>
     <row r="193" spans="2:3" x14ac:dyDescent="0.25">
@@ -5394,7 +5283,7 @@
         <v>8009</v>
       </c>
       <c r="C193" s="6" t="s">
-        <v>656</v>
+        <v>612</v>
       </c>
     </row>
     <row r="194" spans="2:3" x14ac:dyDescent="0.25">
@@ -5402,7 +5291,7 @@
         <v>8010</v>
       </c>
       <c r="C194" s="6" t="s">
-        <v>657</v>
+        <v>613</v>
       </c>
     </row>
     <row r="195" spans="2:3" x14ac:dyDescent="0.25">
@@ -5410,7 +5299,7 @@
         <v>8011</v>
       </c>
       <c r="C195" s="6" t="s">
-        <v>658</v>
+        <v>614</v>
       </c>
     </row>
     <row r="196" spans="2:3" x14ac:dyDescent="0.25">
@@ -5418,7 +5307,7 @@
         <v>8012</v>
       </c>
       <c r="C196" s="6" t="s">
-        <v>659</v>
+        <v>615</v>
       </c>
     </row>
     <row r="197" spans="2:3" x14ac:dyDescent="0.25">
@@ -5426,7 +5315,7 @@
         <v>8013</v>
       </c>
       <c r="C197" s="6" t="s">
-        <v>660</v>
+        <v>616</v>
       </c>
     </row>
     <row r="198" spans="2:3" x14ac:dyDescent="0.25">
@@ -5434,7 +5323,7 @@
         <v>8014</v>
       </c>
       <c r="C198" s="6" t="s">
-        <v>661</v>
+        <v>617</v>
       </c>
     </row>
     <row r="199" spans="2:3" x14ac:dyDescent="0.25">
@@ -5442,7 +5331,7 @@
         <v>8015</v>
       </c>
       <c r="C199" s="6" t="s">
-        <v>662</v>
+        <v>618</v>
       </c>
     </row>
     <row r="200" spans="2:3" x14ac:dyDescent="0.25">
@@ -5450,7 +5339,7 @@
         <v>8016</v>
       </c>
       <c r="C200" s="6" t="s">
-        <v>663</v>
+        <v>619</v>
       </c>
     </row>
     <row r="201" spans="2:3" x14ac:dyDescent="0.25">
@@ -5458,7 +5347,7 @@
         <v>8017</v>
       </c>
       <c r="C201" s="6" t="s">
-        <v>664</v>
+        <v>620</v>
       </c>
     </row>
     <row r="202" spans="2:3" x14ac:dyDescent="0.25">
@@ -5466,7 +5355,7 @@
         <v>8018</v>
       </c>
       <c r="C202" s="6" t="s">
-        <v>665</v>
+        <v>621</v>
       </c>
     </row>
     <row r="203" spans="2:3" x14ac:dyDescent="0.25">
@@ -5474,7 +5363,7 @@
         <v>8019</v>
       </c>
       <c r="C203" s="6" t="s">
-        <v>642</v>
+        <v>598</v>
       </c>
     </row>
     <row r="204" spans="2:3" x14ac:dyDescent="0.25">
@@ -5482,7 +5371,7 @@
         <v>8020</v>
       </c>
       <c r="C204" s="6" t="s">
-        <v>666</v>
+        <v>622</v>
       </c>
     </row>
     <row r="205" spans="2:3" x14ac:dyDescent="0.25">
@@ -5490,7 +5379,7 @@
         <v>8021</v>
       </c>
       <c r="C205" s="6" t="s">
-        <v>667</v>
+        <v>623</v>
       </c>
     </row>
     <row r="206" spans="2:3" x14ac:dyDescent="0.25">
@@ -5498,7 +5387,7 @@
         <v>8022</v>
       </c>
       <c r="C206" s="6" t="s">
-        <v>668</v>
+        <v>624</v>
       </c>
     </row>
     <row r="207" spans="2:3" x14ac:dyDescent="0.25">
@@ -5506,7 +5395,7 @@
         <v>8023</v>
       </c>
       <c r="C207" s="6" t="s">
-        <v>669</v>
+        <v>625</v>
       </c>
     </row>
     <row r="208" spans="2:3" x14ac:dyDescent="0.25">
@@ -5514,7 +5403,7 @@
         <v>8024</v>
       </c>
       <c r="C208" s="6" t="s">
-        <v>670</v>
+        <v>626</v>
       </c>
     </row>
     <row r="209" spans="2:3" x14ac:dyDescent="0.25">
@@ -5522,7 +5411,7 @@
         <v>8025</v>
       </c>
       <c r="C209" s="6" t="s">
-        <v>671</v>
+        <v>627</v>
       </c>
     </row>
     <row r="210" spans="2:3" x14ac:dyDescent="0.25">
@@ -5530,7 +5419,7 @@
         <v>8026</v>
       </c>
       <c r="C210" s="6" t="s">
-        <v>672</v>
+        <v>628</v>
       </c>
     </row>
     <row r="211" spans="2:3" x14ac:dyDescent="0.25">
@@ -5538,7 +5427,7 @@
         <v>8027</v>
       </c>
       <c r="C211" s="6" t="s">
-        <v>673</v>
+        <v>629</v>
       </c>
     </row>
     <row r="212" spans="2:3" x14ac:dyDescent="0.25">
@@ -5546,7 +5435,7 @@
         <v>8028</v>
       </c>
       <c r="C212" s="6" t="s">
-        <v>674</v>
+        <v>630</v>
       </c>
     </row>
   </sheetData>
@@ -6936,63 +6825,63 @@
         <v>2</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>707</v>
+        <v>663</v>
       </c>
     </row>
     <row r="3" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B3" s="2" t="s">
-        <v>435</v>
+        <v>391</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>708</v>
+        <v>664</v>
       </c>
     </row>
     <row r="4" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B4" s="2" t="s">
-        <v>437</v>
+        <v>393</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>709</v>
+        <v>665</v>
       </c>
     </row>
     <row r="5" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B5" s="2" t="s">
-        <v>439</v>
+        <v>395</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>710</v>
+        <v>666</v>
       </c>
     </row>
     <row r="6" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B6" s="2" t="s">
-        <v>441</v>
+        <v>397</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>711</v>
+        <v>667</v>
       </c>
     </row>
     <row r="7" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B7" s="2" t="s">
-        <v>443</v>
+        <v>399</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>709</v>
+        <v>665</v>
       </c>
     </row>
     <row r="8" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B8" s="2" t="s">
-        <v>445</v>
+        <v>401</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>712</v>
+        <v>668</v>
       </c>
     </row>
     <row r="9" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B9" s="2" t="s">
-        <v>447</v>
+        <v>403</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>713</v>
+        <v>669</v>
       </c>
     </row>
     <row r="10" spans="2:3" x14ac:dyDescent="0.25">
@@ -7000,7 +6889,7 @@
         <v>40</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>714</v>
+        <v>670</v>
       </c>
     </row>
     <row r="11" spans="2:3" x14ac:dyDescent="0.25">
@@ -7008,7 +6897,7 @@
         <v>52</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>715</v>
+        <v>671</v>
       </c>
     </row>
     <row r="12" spans="2:3" x14ac:dyDescent="0.25">
@@ -7016,7 +6905,7 @@
         <v>62</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>716</v>
+        <v>672</v>
       </c>
     </row>
     <row r="13" spans="2:3" x14ac:dyDescent="0.25">
@@ -7024,7 +6913,7 @@
         <v>64</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>717</v>
+        <v>673</v>
       </c>
     </row>
     <row r="14" spans="2:3" x14ac:dyDescent="0.25">
@@ -7032,7 +6921,7 @@
         <v>66</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>718</v>
+        <v>674</v>
       </c>
     </row>
     <row r="15" spans="2:3" x14ac:dyDescent="0.25">
@@ -7040,7 +6929,7 @@
         <v>70</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>719</v>
+        <v>675</v>
       </c>
     </row>
     <row r="16" spans="2:3" x14ac:dyDescent="0.25">
@@ -7048,7 +6937,7 @@
         <v>68</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>720</v>
+        <v>676</v>
       </c>
     </row>
     <row r="17" spans="2:3" x14ac:dyDescent="0.25">
@@ -7056,15 +6945,15 @@
         <v>80</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>721</v>
+        <v>677</v>
       </c>
     </row>
     <row r="18" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B18" s="2" t="s">
-        <v>722</v>
+        <v>678</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>723</v>
+        <v>679</v>
       </c>
     </row>
     <row r="19" spans="2:3" x14ac:dyDescent="0.25">
@@ -7072,7 +6961,7 @@
         <v>82</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>724</v>
+        <v>680</v>
       </c>
     </row>
     <row r="20" spans="2:3" x14ac:dyDescent="0.25">
@@ -7080,7 +6969,7 @@
         <v>84</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>725</v>
+        <v>681</v>
       </c>
     </row>
     <row r="21" spans="2:3" x14ac:dyDescent="0.25">
@@ -7088,7 +6977,7 @@
         <v>86</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>725</v>
+        <v>681</v>
       </c>
     </row>
     <row r="22" spans="2:3" x14ac:dyDescent="0.25">
@@ -7096,7 +6985,7 @@
         <v>88</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>725</v>
+        <v>681</v>
       </c>
     </row>
     <row r="23" spans="2:3" x14ac:dyDescent="0.25">
@@ -7104,7 +6993,7 @@
         <v>90</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>725</v>
+        <v>681</v>
       </c>
     </row>
     <row r="24" spans="2:3" x14ac:dyDescent="0.25">
@@ -7112,7 +7001,7 @@
         <v>92</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>725</v>
+        <v>681</v>
       </c>
     </row>
     <row r="25" spans="2:3" x14ac:dyDescent="0.25">
@@ -7120,7 +7009,7 @@
         <v>94</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>726</v>
+        <v>682</v>
       </c>
     </row>
     <row r="26" spans="2:3" x14ac:dyDescent="0.25">
@@ -7128,15 +7017,15 @@
         <v>96</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>727</v>
+        <v>683</v>
       </c>
     </row>
     <row r="27" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B27" s="2" t="s">
-        <v>728</v>
+        <v>684</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>729</v>
+        <v>685</v>
       </c>
     </row>
     <row r="28" spans="2:3" x14ac:dyDescent="0.25">
@@ -7144,7 +7033,7 @@
         <v>100</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>730</v>
+        <v>686</v>
       </c>
     </row>
     <row r="29" spans="2:3" x14ac:dyDescent="0.25">
@@ -7152,7 +7041,7 @@
         <v>102</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>731</v>
+        <v>687</v>
       </c>
     </row>
     <row r="30" spans="2:3" x14ac:dyDescent="0.25">
@@ -7160,7 +7049,7 @@
         <v>104</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>732</v>
+        <v>688</v>
       </c>
     </row>
     <row r="31" spans="2:3" x14ac:dyDescent="0.25">
@@ -7168,7 +7057,7 @@
         <v>116</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>733</v>
+        <v>689</v>
       </c>
     </row>
     <row r="32" spans="2:3" x14ac:dyDescent="0.25">
@@ -7176,7 +7065,7 @@
         <v>152</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>734</v>
+        <v>690</v>
       </c>
     </row>
     <row r="33" spans="2:3" x14ac:dyDescent="0.25">
@@ -7184,15 +7073,15 @@
         <v>134</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>735</v>
+        <v>691</v>
       </c>
     </row>
     <row r="34" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B34" s="2" t="s">
-        <v>736</v>
+        <v>692</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>737</v>
+        <v>693</v>
       </c>
     </row>
     <row r="35" spans="2:3" x14ac:dyDescent="0.25">
@@ -7200,7 +7089,7 @@
         <v>136</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>738</v>
+        <v>694</v>
       </c>
     </row>
     <row r="36" spans="2:3" x14ac:dyDescent="0.25">
@@ -7208,7 +7097,7 @@
         <v>138</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>739</v>
+        <v>695</v>
       </c>
     </row>
     <row r="37" spans="2:3" x14ac:dyDescent="0.25">
@@ -7216,7 +7105,7 @@
         <v>140</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>740</v>
+        <v>696</v>
       </c>
     </row>
     <row r="38" spans="2:3" x14ac:dyDescent="0.25">
@@ -7224,15 +7113,15 @@
         <v>142</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>741</v>
+        <v>697</v>
       </c>
     </row>
     <row r="39" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B39" s="2" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>742</v>
+        <v>698</v>
       </c>
     </row>
     <row r="40" spans="2:3" x14ac:dyDescent="0.25">
@@ -7240,7 +7129,7 @@
         <v>144</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>743</v>
+        <v>699</v>
       </c>
     </row>
     <row r="41" spans="2:3" x14ac:dyDescent="0.25">
@@ -7248,7 +7137,7 @@
         <v>146</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>744</v>
+        <v>700</v>
       </c>
     </row>
     <row r="42" spans="2:3" x14ac:dyDescent="0.25">
@@ -7256,7 +7145,7 @@
         <v>148</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>745</v>
+        <v>701</v>
       </c>
     </row>
     <row r="43" spans="2:3" x14ac:dyDescent="0.25">
@@ -7264,7 +7153,7 @@
         <v>150</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>746</v>
+        <v>702</v>
       </c>
     </row>
     <row r="44" spans="2:3" x14ac:dyDescent="0.25">
@@ -7272,7 +7161,7 @@
         <v>174</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>747</v>
+        <v>703</v>
       </c>
     </row>
     <row r="45" spans="2:3" x14ac:dyDescent="0.25">
@@ -7280,7 +7169,7 @@
         <v>154</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>748</v>
+        <v>704</v>
       </c>
     </row>
     <row r="46" spans="2:3" x14ac:dyDescent="0.25">
@@ -7288,7 +7177,7 @@
         <v>156</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>749</v>
+        <v>705</v>
       </c>
     </row>
     <row r="47" spans="2:3" x14ac:dyDescent="0.25">
@@ -7296,7 +7185,7 @@
         <v>158</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>750</v>
+        <v>706</v>
       </c>
     </row>
     <row r="48" spans="2:3" x14ac:dyDescent="0.25">
@@ -7304,7 +7193,7 @@
         <v>160</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>751</v>
+        <v>707</v>
       </c>
     </row>
     <row r="49" spans="2:3" x14ac:dyDescent="0.25">
@@ -7312,7 +7201,7 @@
         <v>162</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>752</v>
+        <v>708</v>
       </c>
     </row>
     <row r="50" spans="2:3" x14ac:dyDescent="0.25">
@@ -7320,7 +7209,7 @@
         <v>164</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>753</v>
+        <v>709</v>
       </c>
     </row>
     <row r="51" spans="2:3" x14ac:dyDescent="0.25">
@@ -7328,7 +7217,7 @@
         <v>166</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>754</v>
+        <v>710</v>
       </c>
     </row>
     <row r="52" spans="2:3" x14ac:dyDescent="0.25">
@@ -7336,7 +7225,7 @@
         <v>168</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>755</v>
+        <v>711</v>
       </c>
     </row>
     <row r="53" spans="2:3" x14ac:dyDescent="0.25">
@@ -7344,7 +7233,7 @@
         <v>170</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>756</v>
+        <v>712</v>
       </c>
     </row>
     <row r="54" spans="2:3" x14ac:dyDescent="0.25">
@@ -7352,7 +7241,7 @@
         <v>172</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>733</v>
+        <v>689</v>
       </c>
     </row>
     <row r="55" spans="2:3" x14ac:dyDescent="0.25">
@@ -7360,7 +7249,7 @@
         <v>176</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>757</v>
+        <v>713</v>
       </c>
     </row>
     <row r="56" spans="2:3" x14ac:dyDescent="0.25">
@@ -7368,7 +7257,7 @@
         <v>178</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>758</v>
+        <v>714</v>
       </c>
     </row>
     <row r="57" spans="2:3" x14ac:dyDescent="0.25">
@@ -7376,79 +7265,79 @@
         <v>180</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>759</v>
+        <v>715</v>
       </c>
     </row>
     <row r="58" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B58" s="2" t="s">
-        <v>760</v>
+        <v>716</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>761</v>
+        <v>717</v>
       </c>
     </row>
     <row r="59" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B59" s="2" t="s">
-        <v>762</v>
+        <v>718</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>763</v>
+        <v>719</v>
       </c>
     </row>
     <row r="60" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B60" s="2" t="s">
-        <v>764</v>
+        <v>720</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>765</v>
+        <v>721</v>
       </c>
     </row>
     <row r="61" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B61" s="2" t="s">
-        <v>643</v>
+        <v>599</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>766</v>
+        <v>722</v>
       </c>
     </row>
     <row r="62" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B62" s="2" t="s">
-        <v>645</v>
+        <v>601</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>767</v>
+        <v>723</v>
       </c>
     </row>
     <row r="63" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B63" s="2" t="s">
-        <v>647</v>
+        <v>603</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>768</v>
+        <v>724</v>
       </c>
     </row>
     <row r="64" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B64" s="2" t="s">
-        <v>649</v>
+        <v>605</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>769</v>
+        <v>725</v>
       </c>
     </row>
     <row r="65" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B65" s="2" t="s">
-        <v>651</v>
+        <v>607</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>770</v>
+        <v>726</v>
       </c>
     </row>
     <row r="66" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B66" s="2" t="s">
-        <v>771</v>
+        <v>727</v>
       </c>
       <c r="C66" s="2" t="s">
-        <v>772</v>
+        <v>728</v>
       </c>
     </row>
     <row r="67" spans="2:3" x14ac:dyDescent="0.25">
@@ -7456,7 +7345,7 @@
         <v>314</v>
       </c>
       <c r="C67" s="2" t="s">
-        <v>773</v>
+        <v>729</v>
       </c>
     </row>
     <row r="68" spans="2:3" x14ac:dyDescent="0.25">
@@ -7464,7 +7353,7 @@
         <v>328</v>
       </c>
       <c r="C68" s="2" t="s">
-        <v>774</v>
+        <v>730</v>
       </c>
     </row>
   </sheetData>
@@ -7488,10 +7377,10 @@
     </row>
     <row r="2" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B2" s="5" t="s">
-        <v>775</v>
+        <v>731</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>776</v>
+        <v>732</v>
       </c>
     </row>
     <row r="3" spans="2:3" x14ac:dyDescent="0.25">
@@ -7499,7 +7388,7 @@
         <v>38</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>777</v>
+        <v>733</v>
       </c>
     </row>
     <row r="4" spans="2:3" x14ac:dyDescent="0.25">
@@ -7507,7 +7396,7 @@
         <v>10</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>708</v>
+        <v>664</v>
       </c>
     </row>
     <row r="5" spans="2:3" x14ac:dyDescent="0.25">
@@ -7515,7 +7404,7 @@
         <v>20</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>741</v>
+        <v>697</v>
       </c>
     </row>
     <row r="6" spans="2:3" x14ac:dyDescent="0.25">
@@ -7523,7 +7412,7 @@
         <v>22</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>778</v>
+        <v>734</v>
       </c>
     </row>
     <row r="7" spans="2:3" x14ac:dyDescent="0.25">
@@ -7531,7 +7420,7 @@
         <v>24</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>779</v>
+        <v>735</v>
       </c>
     </row>
     <row r="8" spans="2:3" x14ac:dyDescent="0.25">
@@ -7539,15 +7428,15 @@
         <v>26</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>780</v>
+        <v>736</v>
       </c>
     </row>
     <row r="9" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B9" s="5" t="s">
-        <v>781</v>
+        <v>737</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>782</v>
+        <v>738</v>
       </c>
     </row>
     <row r="10" spans="2:3" x14ac:dyDescent="0.25">
@@ -7555,7 +7444,7 @@
         <v>30</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>783</v>
+        <v>739</v>
       </c>
     </row>
     <row r="11" spans="2:3" x14ac:dyDescent="0.25">
@@ -7563,7 +7452,7 @@
         <v>32</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>784</v>
+        <v>740</v>
       </c>
     </row>
     <row r="12" spans="2:3" x14ac:dyDescent="0.25">
@@ -7571,7 +7460,7 @@
         <v>34</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>785</v>
+        <v>741</v>
       </c>
     </row>
     <row r="13" spans="2:3" x14ac:dyDescent="0.25">
@@ -7579,7 +7468,7 @@
         <v>36</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>786</v>
+        <v>742</v>
       </c>
     </row>
     <row r="14" spans="2:3" x14ac:dyDescent="0.25">
@@ -7587,7 +7476,7 @@
         <v>78</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>787</v>
+        <v>743</v>
       </c>
     </row>
     <row r="15" spans="2:3" x14ac:dyDescent="0.25">
@@ -7595,7 +7484,7 @@
         <v>50</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>710</v>
+        <v>666</v>
       </c>
     </row>
     <row r="16" spans="2:3" x14ac:dyDescent="0.25">
@@ -7603,7 +7492,7 @@
         <v>52</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>709</v>
+        <v>665</v>
       </c>
     </row>
     <row r="17" spans="2:3" x14ac:dyDescent="0.25">
@@ -7611,7 +7500,7 @@
         <v>62</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>711</v>
+        <v>667</v>
       </c>
     </row>
     <row r="18" spans="2:3" x14ac:dyDescent="0.25">
@@ -7619,7 +7508,7 @@
         <v>64</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>788</v>
+        <v>744</v>
       </c>
     </row>
     <row r="19" spans="2:3" x14ac:dyDescent="0.25">
@@ -7627,7 +7516,7 @@
         <v>66</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>777</v>
+        <v>733</v>
       </c>
     </row>
     <row r="20" spans="2:3" x14ac:dyDescent="0.25">
@@ -7635,7 +7524,7 @@
         <v>132</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>789</v>
+        <v>745</v>
       </c>
     </row>
     <row r="21" spans="2:3" x14ac:dyDescent="0.25">
@@ -7643,7 +7532,7 @@
         <v>98</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>790</v>
+        <v>746</v>
       </c>
     </row>
     <row r="22" spans="2:3" x14ac:dyDescent="0.25">
@@ -7651,7 +7540,7 @@
         <v>114</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>791</v>
+        <v>747</v>
       </c>
     </row>
     <row r="23" spans="2:3" x14ac:dyDescent="0.25">
@@ -7659,7 +7548,7 @@
         <v>118</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>792</v>
+        <v>748</v>
       </c>
     </row>
     <row r="24" spans="2:3" x14ac:dyDescent="0.25">
@@ -7667,7 +7556,7 @@
         <v>232</v>
       </c>
       <c r="C24" s="5" t="s">
-        <v>793</v>
+        <v>749</v>
       </c>
     </row>
     <row r="25" spans="2:3" x14ac:dyDescent="0.25">
@@ -7675,7 +7564,7 @@
         <v>152</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>734</v>
+        <v>690</v>
       </c>
     </row>
     <row r="26" spans="2:3" x14ac:dyDescent="0.25">
@@ -7683,23 +7572,23 @@
         <v>174</v>
       </c>
       <c r="C26" s="5" t="s">
-        <v>747</v>
+        <v>703</v>
       </c>
     </row>
     <row r="27" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B27" s="5" t="s">
-        <v>794</v>
+        <v>750</v>
       </c>
       <c r="C27" s="5" t="s">
-        <v>723</v>
+        <v>679</v>
       </c>
     </row>
     <row r="28" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B28" s="5" t="s">
-        <v>795</v>
+        <v>751</v>
       </c>
       <c r="C28" s="5" t="s">
-        <v>796</v>
+        <v>752</v>
       </c>
     </row>
     <row r="29" spans="2:3" x14ac:dyDescent="0.25">
@@ -7707,7 +7596,7 @@
         <v>268</v>
       </c>
       <c r="C29" s="5" t="s">
-        <v>738</v>
+        <v>694</v>
       </c>
     </row>
     <row r="30" spans="2:3" x14ac:dyDescent="0.25">
@@ -7715,7 +7604,7 @@
         <v>312</v>
       </c>
       <c r="C30" s="5" t="s">
-        <v>797</v>
+        <v>753</v>
       </c>
     </row>
     <row r="31" spans="2:3" x14ac:dyDescent="0.25">
@@ -7723,7 +7612,7 @@
         <v>336</v>
       </c>
       <c r="C31" s="5" t="s">
-        <v>798</v>
+        <v>754</v>
       </c>
     </row>
   </sheetData>
@@ -7750,7 +7639,7 @@
         <v>38</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>799</v>
+        <v>755</v>
       </c>
     </row>
     <row r="3" spans="2:3" x14ac:dyDescent="0.25">
@@ -7758,7 +7647,7 @@
         <v>10</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>800</v>
+        <v>756</v>
       </c>
     </row>
     <row r="4" spans="2:3" x14ac:dyDescent="0.25">
@@ -7766,7 +7655,7 @@
         <v>20</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>792</v>
+        <v>748</v>
       </c>
     </row>
     <row r="5" spans="2:3" x14ac:dyDescent="0.25">
@@ -7774,7 +7663,7 @@
         <v>22</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>777</v>
+        <v>733</v>
       </c>
     </row>
     <row r="6" spans="2:3" x14ac:dyDescent="0.25">
@@ -7782,7 +7671,7 @@
         <v>78</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>723</v>
+        <v>679</v>
       </c>
     </row>
     <row r="7" spans="2:3" x14ac:dyDescent="0.25">
@@ -7790,7 +7679,7 @@
         <v>132</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>429</v>
+        <v>389</v>
       </c>
     </row>
     <row r="8" spans="2:3" x14ac:dyDescent="0.25">
@@ -7798,23 +7687,23 @@
         <v>232</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>801</v>
+        <v>757</v>
       </c>
     </row>
     <row r="9" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B9" s="3" t="s">
-        <v>794</v>
+        <v>750</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>802</v>
+        <v>758</v>
       </c>
     </row>
     <row r="10" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B10" s="3" t="s">
-        <v>795</v>
+        <v>751</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>803</v>
+        <v>759</v>
       </c>
     </row>
     <row r="11" spans="2:3" x14ac:dyDescent="0.25">
@@ -7822,7 +7711,7 @@
         <v>268</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>804</v>
+        <v>760</v>
       </c>
     </row>
     <row r="12" spans="2:3" x14ac:dyDescent="0.25">
@@ -7830,7 +7719,7 @@
         <v>312</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>805</v>
+        <v>761</v>
       </c>
     </row>
     <row r="13" spans="2:3" x14ac:dyDescent="0.25">
@@ -7838,7 +7727,7 @@
         <v>336</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>806</v>
+        <v>762</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/Editor/DataDic/Data.xlsx
+++ b/Assets/Editor/DataDic/Data.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="17385" windowHeight="7860" activeTab="1"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="17385" windowHeight="7860" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="FishData" sheetId="1" r:id="rId1"/>

--- a/Assets/Editor/DataDic/Data.xlsx
+++ b/Assets/Editor/DataDic/Data.xlsx
@@ -9,16 +9,17 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="17385" windowHeight="7860" activeTab="2"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="17385" windowHeight="7860" firstSheet="1" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="FishData" sheetId="1" r:id="rId1"/>
     <sheet name="测试" sheetId="3" r:id="rId2"/>
-    <sheet name="MapItemData" sheetId="4" r:id="rId3"/>
-    <sheet name="GameActionData" sheetId="5" r:id="rId4"/>
-    <sheet name="GameEventData" sheetId="6" r:id="rId5"/>
-    <sheet name="OperateData" sheetId="7" r:id="rId6"/>
-    <sheet name="NPCFunctionData" sheetId="8" r:id="rId7"/>
+    <sheet name="Sheet1" sheetId="9" r:id="rId3"/>
+    <sheet name="MapItemData" sheetId="4" r:id="rId4"/>
+    <sheet name="GameActionData" sheetId="5" r:id="rId5"/>
+    <sheet name="GameEventData" sheetId="6" r:id="rId6"/>
+    <sheet name="OperateData" sheetId="7" r:id="rId7"/>
+    <sheet name="NPCFunctionData" sheetId="8" r:id="rId8"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">测试!$B$1:$C$56</definedName>
@@ -2353,7 +2354,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
@@ -2374,8 +2375,14 @@
       <family val="3"/>
       <charset val="134"/>
     </font>
+    <font>
+      <sz val="9"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -2394,8 +2401,26 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -2403,11 +2428,26 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1"/>
@@ -2421,6 +2461,11 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1"/>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -3142,10 +3187,10 @@
       </c>
     </row>
     <row r="9" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B9" s="6" t="s">
+      <c r="B9" s="13" t="s">
         <v>351</v>
       </c>
-      <c r="C9" s="6">
+      <c r="C9" s="13">
         <v>889</v>
       </c>
       <c r="G9" s="9" t="str">
@@ -3456,19 +3501,19 @@
       </c>
     </row>
     <row r="25" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B25" s="6" t="s">
+      <c r="B25" s="13" t="s">
         <v>344</v>
       </c>
-      <c r="C25" s="6">
+      <c r="C25" s="13">
         <v>2355</v>
       </c>
       <c r="M25" s="6"/>
     </row>
     <row r="26" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B26" s="6" t="s">
+      <c r="B26" s="13" t="s">
         <v>345</v>
       </c>
-      <c r="C26" s="6">
+      <c r="C26" s="13">
         <v>2497</v>
       </c>
       <c r="M26" s="6"/>
@@ -3483,7 +3528,7 @@
       <c r="M27" s="6"/>
     </row>
     <row r="28" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B28" s="11" t="s">
+      <c r="B28" s="6" t="s">
         <v>360</v>
       </c>
       <c r="C28" s="6">
@@ -3492,7 +3537,7 @@
       <c r="M28" s="6"/>
     </row>
     <row r="29" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B29" s="11" t="s">
+      <c r="B29" s="6" t="s">
         <v>382</v>
       </c>
       <c r="C29" s="6">
@@ -3531,10 +3576,10 @@
       </c>
     </row>
     <row r="33" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B33" s="6" t="s">
+      <c r="B33" s="13" t="s">
         <v>369</v>
       </c>
-      <c r="C33" s="6">
+      <c r="C33" s="13">
         <v>3297</v>
       </c>
       <c r="M33" s="6" t="s">
@@ -3694,10 +3739,10 @@
       </c>
     </row>
     <row r="53" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B53" s="6" t="s">
+      <c r="B53" s="13" t="s">
         <v>385</v>
       </c>
-      <c r="C53" s="6">
+      <c r="C53" s="13">
         <v>5170</v>
       </c>
     </row>
@@ -3739,6 +3784,86 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="AH9:AS16"/>
+  <sheetFormatPr defaultColWidth="3.28515625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="9" spans="34:45" x14ac:dyDescent="0.25">
+      <c r="AH9" s="15"/>
+      <c r="AI9" s="15"/>
+      <c r="AJ9" s="15"/>
+      <c r="AO9" s="14"/>
+      <c r="AP9" s="14"/>
+      <c r="AQ9" s="14"/>
+      <c r="AR9" s="14"/>
+      <c r="AS9" s="14"/>
+    </row>
+    <row r="10" spans="34:45" x14ac:dyDescent="0.25">
+      <c r="AH10" s="15"/>
+      <c r="AI10" s="15"/>
+      <c r="AJ10" s="15"/>
+      <c r="AO10" s="14"/>
+      <c r="AP10" s="15"/>
+      <c r="AQ10" s="15"/>
+      <c r="AR10" s="15"/>
+      <c r="AS10" s="14"/>
+    </row>
+    <row r="11" spans="34:45" x14ac:dyDescent="0.25">
+      <c r="AH11" s="15"/>
+      <c r="AI11" s="16"/>
+      <c r="AJ11" s="15"/>
+      <c r="AO11" s="14"/>
+      <c r="AP11" s="15"/>
+      <c r="AQ11" s="15"/>
+      <c r="AR11" s="15"/>
+      <c r="AS11" s="14"/>
+    </row>
+    <row r="12" spans="34:45" x14ac:dyDescent="0.25">
+      <c r="AH12" s="15"/>
+      <c r="AI12" s="15"/>
+      <c r="AJ12" s="15"/>
+      <c r="AO12" s="14"/>
+      <c r="AP12" s="15"/>
+      <c r="AQ12" s="17"/>
+      <c r="AR12" s="15"/>
+      <c r="AS12" s="14"/>
+    </row>
+    <row r="13" spans="34:45" x14ac:dyDescent="0.25">
+      <c r="AO13" s="14"/>
+      <c r="AP13" s="15"/>
+      <c r="AQ13" s="15"/>
+      <c r="AR13" s="15"/>
+      <c r="AS13" s="14"/>
+    </row>
+    <row r="14" spans="34:45" x14ac:dyDescent="0.25">
+      <c r="AO14" s="14"/>
+      <c r="AP14" s="14"/>
+      <c r="AQ14" s="14"/>
+      <c r="AR14" s="14"/>
+      <c r="AS14" s="14"/>
+    </row>
+    <row r="15" spans="34:45" x14ac:dyDescent="0.25">
+      <c r="AO15" s="14"/>
+      <c r="AP15" s="14"/>
+      <c r="AQ15" s="14"/>
+      <c r="AR15" s="14"/>
+      <c r="AS15" s="14"/>
+    </row>
+    <row r="16" spans="34:45" x14ac:dyDescent="0.25">
+      <c r="AO16" s="14"/>
+      <c r="AP16" s="14"/>
+      <c r="AQ16" s="14"/>
+      <c r="AR16" s="14"/>
+      <c r="AS16" s="14"/>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="4" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B1:C212"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -5436,1369 +5561,6 @@
       </c>
       <c r="C212" s="6" t="s">
         <v>630</v>
-      </c>
-    </row>
-  </sheetData>
-  <phoneticPr fontId="0" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="B1:C169"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData>
-    <row r="1" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="2" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B2" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="3" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B3" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="4" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B4" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="5" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B5" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="6" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B6" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="7" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B7" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="8" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B8" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="9" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B9" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="C9" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="10" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B10" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="C10" s="1" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="11" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B11" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="C11" s="1" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="12" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B12" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="C12" s="1" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="13" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B13" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="C13" s="1" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="14" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B14" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="C14" s="1" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="15" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B15" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="C15" s="1" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="16" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B16" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="C16" s="1" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="17" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B17" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="C17" s="1" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="18" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B18" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="C18" s="1" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="19" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B19" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="C19" s="1" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="20" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B20" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="C20" s="1" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="21" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B21" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="C21" s="1" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="22" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B22" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="C22" s="1" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="23" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B23" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="C23" s="1" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="24" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B24" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="C24" s="1" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="25" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B25" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="C25" s="1" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="26" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B26" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="C26" s="1" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="27" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B27" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="C27" s="1" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="28" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B28" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="C28" s="1" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="29" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B29" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="C29" s="1" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="30" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B30" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="C30" s="1" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="31" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B31" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="C31" s="1" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="32" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B32" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="C32" s="1" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="33" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B33" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="C33" s="1" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="34" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B34" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="C34" s="1" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="35" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B35" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="C35" s="1" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="36" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B36" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="C36" s="1" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="37" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B37" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="C37" s="1" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="38" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B38" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="C38" s="1" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="39" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B39" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="C39" s="1" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="40" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B40" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="C40" s="1" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="41" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B41" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="C41" s="1" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="42" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B42" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="C42" s="1" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="43" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B43" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="C43" s="1" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="44" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B44" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="C44" s="1" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="45" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B45" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="C45" s="1" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="46" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B46" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="C46" s="1" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="47" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B47" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="C47" s="1" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="48" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B48" s="1" t="s">
-        <v>94</v>
-      </c>
-      <c r="C48" s="1" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="49" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B49" s="1" t="s">
-        <v>96</v>
-      </c>
-      <c r="C49" s="1" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="50" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B50" s="1" t="s">
-        <v>98</v>
-      </c>
-      <c r="C50" s="1" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="51" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B51" s="1" t="s">
-        <v>100</v>
-      </c>
-      <c r="C51" s="1" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="52" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B52" s="1" t="s">
-        <v>102</v>
-      </c>
-      <c r="C52" s="1" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="53" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B53" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="C53" s="1" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="54" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B54" s="1" t="s">
-        <v>106</v>
-      </c>
-      <c r="C54" s="1" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="55" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B55" s="1" t="s">
-        <v>108</v>
-      </c>
-      <c r="C55" s="1" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="56" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B56" s="1" t="s">
-        <v>110</v>
-      </c>
-      <c r="C56" s="1" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="57" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B57" s="1" t="s">
-        <v>112</v>
-      </c>
-      <c r="C57" s="1" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="58" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B58" s="1" t="s">
-        <v>114</v>
-      </c>
-      <c r="C58" s="1" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="59" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B59" s="1" t="s">
-        <v>116</v>
-      </c>
-      <c r="C59" s="1" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="60" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B60" s="1" t="s">
-        <v>118</v>
-      </c>
-      <c r="C60" s="1" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="61" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B61" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="C61" s="1" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="62" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B62" s="1" t="s">
-        <v>122</v>
-      </c>
-      <c r="C62" s="1" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="63" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B63" s="1" t="s">
-        <v>124</v>
-      </c>
-      <c r="C63" s="1" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="64" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B64" s="1" t="s">
-        <v>126</v>
-      </c>
-      <c r="C64" s="1" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="65" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B65" s="1" t="s">
-        <v>128</v>
-      </c>
-      <c r="C65" s="1" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="66" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B66" s="1" t="s">
-        <v>130</v>
-      </c>
-      <c r="C66" s="1" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="67" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B67" s="1" t="s">
-        <v>132</v>
-      </c>
-      <c r="C67" s="1" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="68" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B68" s="1" t="s">
-        <v>134</v>
-      </c>
-      <c r="C68" s="1" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="69" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B69" s="1" t="s">
-        <v>136</v>
-      </c>
-      <c r="C69" s="1" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="70" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B70" s="1" t="s">
-        <v>138</v>
-      </c>
-      <c r="C70" s="1" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="71" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B71" s="1" t="s">
-        <v>140</v>
-      </c>
-      <c r="C71" s="1" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="72" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B72" s="1" t="s">
-        <v>142</v>
-      </c>
-      <c r="C72" s="1" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="73" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B73" s="1" t="s">
-        <v>144</v>
-      </c>
-      <c r="C73" s="1" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="74" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B74" s="1" t="s">
-        <v>146</v>
-      </c>
-      <c r="C74" s="1" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="75" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B75" s="1" t="s">
-        <v>148</v>
-      </c>
-      <c r="C75" s="1" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="76" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B76" s="1" t="s">
-        <v>150</v>
-      </c>
-      <c r="C76" s="1" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="77" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B77" s="1" t="s">
-        <v>152</v>
-      </c>
-      <c r="C77" s="1" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="78" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B78" s="1" t="s">
-        <v>154</v>
-      </c>
-      <c r="C78" s="1" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="79" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B79" s="1" t="s">
-        <v>156</v>
-      </c>
-      <c r="C79" s="1" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="80" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B80" s="1" t="s">
-        <v>158</v>
-      </c>
-      <c r="C80" s="1" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="81" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B81" s="1" t="s">
-        <v>160</v>
-      </c>
-      <c r="C81" s="1" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="82" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B82" s="1" t="s">
-        <v>162</v>
-      </c>
-      <c r="C82" s="1" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="83" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B83" s="1" t="s">
-        <v>164</v>
-      </c>
-      <c r="C83" s="1" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="84" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B84" s="1" t="s">
-        <v>166</v>
-      </c>
-      <c r="C84" s="1" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="85" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B85" s="1" t="s">
-        <v>168</v>
-      </c>
-      <c r="C85" s="1" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="86" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B86" s="1" t="s">
-        <v>170</v>
-      </c>
-      <c r="C86" s="1" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="87" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B87" s="1" t="s">
-        <v>172</v>
-      </c>
-      <c r="C87" s="1" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="88" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B88" s="1" t="s">
-        <v>174</v>
-      </c>
-      <c r="C88" s="1" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="89" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B89" s="1" t="s">
-        <v>176</v>
-      </c>
-      <c r="C89" s="1" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="90" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B90" s="1" t="s">
-        <v>178</v>
-      </c>
-      <c r="C90" s="1" t="s">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="91" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B91" s="1" t="s">
-        <v>180</v>
-      </c>
-      <c r="C91" s="1" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="92" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B92" s="1" t="s">
-        <v>182</v>
-      </c>
-      <c r="C92" s="1" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="93" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B93" s="1" t="s">
-        <v>184</v>
-      </c>
-      <c r="C93" s="1" t="s">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="94" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B94" s="1" t="s">
-        <v>186</v>
-      </c>
-      <c r="C94" s="1" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="95" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B95" s="1" t="s">
-        <v>188</v>
-      </c>
-      <c r="C95" s="1" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="96" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B96" s="1" t="s">
-        <v>190</v>
-      </c>
-      <c r="C96" s="1" t="s">
-        <v>191</v>
-      </c>
-    </row>
-    <row r="97" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B97" s="1" t="s">
-        <v>192</v>
-      </c>
-      <c r="C97" s="1" t="s">
-        <v>193</v>
-      </c>
-    </row>
-    <row r="98" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B98" s="1" t="s">
-        <v>194</v>
-      </c>
-      <c r="C98" s="1" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="99" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B99" s="1" t="s">
-        <v>196</v>
-      </c>
-      <c r="C99" s="1" t="s">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="100" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B100" s="1" t="s">
-        <v>198</v>
-      </c>
-      <c r="C100" s="1" t="s">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="101" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B101" s="1" t="s">
-        <v>200</v>
-      </c>
-      <c r="C101" s="1" t="s">
-        <v>201</v>
-      </c>
-    </row>
-    <row r="102" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B102" s="1" t="s">
-        <v>202</v>
-      </c>
-      <c r="C102" s="1" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="103" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B103" s="1" t="s">
-        <v>204</v>
-      </c>
-      <c r="C103" s="1" t="s">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="104" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B104" s="1" t="s">
-        <v>206</v>
-      </c>
-      <c r="C104" s="1" t="s">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="105" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B105" s="1" t="s">
-        <v>208</v>
-      </c>
-      <c r="C105" s="1" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="106" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B106" s="1" t="s">
-        <v>210</v>
-      </c>
-      <c r="C106" s="1" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="107" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B107" s="1" t="s">
-        <v>212</v>
-      </c>
-      <c r="C107" s="1" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="108" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B108" s="1" t="s">
-        <v>214</v>
-      </c>
-      <c r="C108" s="1" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="109" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B109" s="1" t="s">
-        <v>216</v>
-      </c>
-      <c r="C109" s="1" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="110" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B110" s="1" t="s">
-        <v>218</v>
-      </c>
-      <c r="C110" s="1" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="111" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B111" s="1" t="s">
-        <v>220</v>
-      </c>
-      <c r="C111" s="1" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="112" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B112" s="1" t="s">
-        <v>222</v>
-      </c>
-      <c r="C112" s="1" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="113" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B113" s="1" t="s">
-        <v>224</v>
-      </c>
-      <c r="C113" s="1" t="s">
-        <v>225</v>
-      </c>
-    </row>
-    <row r="114" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B114" s="1" t="s">
-        <v>226</v>
-      </c>
-      <c r="C114" s="1" t="s">
-        <v>227</v>
-      </c>
-    </row>
-    <row r="115" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B115" s="1" t="s">
-        <v>228</v>
-      </c>
-      <c r="C115" s="1" t="s">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="116" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B116" s="1" t="s">
-        <v>230</v>
-      </c>
-      <c r="C116" s="1" t="s">
-        <v>231</v>
-      </c>
-    </row>
-    <row r="117" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B117" s="1" t="s">
-        <v>232</v>
-      </c>
-      <c r="C117" s="1" t="s">
-        <v>233</v>
-      </c>
-    </row>
-    <row r="118" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B118" s="1" t="s">
-        <v>234</v>
-      </c>
-      <c r="C118" s="1" t="s">
-        <v>235</v>
-      </c>
-    </row>
-    <row r="119" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B119" s="1" t="s">
-        <v>236</v>
-      </c>
-      <c r="C119" s="1" t="s">
-        <v>237</v>
-      </c>
-    </row>
-    <row r="120" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B120" s="1" t="s">
-        <v>238</v>
-      </c>
-      <c r="C120" s="1" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="121" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B121" s="1" t="s">
-        <v>240</v>
-      </c>
-      <c r="C121" s="1" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="122" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B122" s="1" t="s">
-        <v>242</v>
-      </c>
-      <c r="C122" s="1" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="123" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B123" s="1" t="s">
-        <v>244</v>
-      </c>
-      <c r="C123" s="1" t="s">
-        <v>245</v>
-      </c>
-    </row>
-    <row r="124" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B124" s="1" t="s">
-        <v>246</v>
-      </c>
-      <c r="C124" s="1" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="125" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B125" s="1" t="s">
-        <v>248</v>
-      </c>
-      <c r="C125" s="1" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="126" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B126" s="1" t="s">
-        <v>250</v>
-      </c>
-      <c r="C126" s="1" t="s">
-        <v>251</v>
-      </c>
-    </row>
-    <row r="127" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B127" s="1" t="s">
-        <v>252</v>
-      </c>
-      <c r="C127" s="1" t="s">
-        <v>253</v>
-      </c>
-    </row>
-    <row r="128" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B128" s="1" t="s">
-        <v>254</v>
-      </c>
-      <c r="C128" s="1" t="s">
-        <v>255</v>
-      </c>
-    </row>
-    <row r="129" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B129" s="1" t="s">
-        <v>256</v>
-      </c>
-      <c r="C129" s="1" t="s">
-        <v>257</v>
-      </c>
-    </row>
-    <row r="130" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B130" s="1" t="s">
-        <v>258</v>
-      </c>
-      <c r="C130" s="1" t="s">
-        <v>259</v>
-      </c>
-    </row>
-    <row r="131" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B131" s="1" t="s">
-        <v>260</v>
-      </c>
-      <c r="C131" s="1" t="s">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="132" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B132" s="1" t="s">
-        <v>262</v>
-      </c>
-      <c r="C132" s="1" t="s">
-        <v>263</v>
-      </c>
-    </row>
-    <row r="133" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B133" s="1" t="s">
-        <v>264</v>
-      </c>
-      <c r="C133" s="1" t="s">
-        <v>265</v>
-      </c>
-    </row>
-    <row r="134" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B134" s="1" t="s">
-        <v>266</v>
-      </c>
-      <c r="C134" s="1" t="s">
-        <v>267</v>
-      </c>
-    </row>
-    <row r="135" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B135" s="1" t="s">
-        <v>268</v>
-      </c>
-      <c r="C135" s="1" t="s">
-        <v>269</v>
-      </c>
-    </row>
-    <row r="136" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B136" s="1" t="s">
-        <v>270</v>
-      </c>
-      <c r="C136" s="1" t="s">
-        <v>271</v>
-      </c>
-    </row>
-    <row r="137" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B137" s="1" t="s">
-        <v>272</v>
-      </c>
-      <c r="C137" s="1" t="s">
-        <v>273</v>
-      </c>
-    </row>
-    <row r="138" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B138" s="1" t="s">
-        <v>274</v>
-      </c>
-      <c r="C138" s="1" t="s">
-        <v>275</v>
-      </c>
-    </row>
-    <row r="139" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B139" s="1" t="s">
-        <v>276</v>
-      </c>
-      <c r="C139" s="1" t="s">
-        <v>277</v>
-      </c>
-    </row>
-    <row r="140" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B140" s="1" t="s">
-        <v>278</v>
-      </c>
-      <c r="C140" s="1" t="s">
-        <v>279</v>
-      </c>
-    </row>
-    <row r="141" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B141" s="1" t="s">
-        <v>280</v>
-      </c>
-      <c r="C141" s="1" t="s">
-        <v>281</v>
-      </c>
-    </row>
-    <row r="142" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B142" s="1" t="s">
-        <v>282</v>
-      </c>
-      <c r="C142" s="1" t="s">
-        <v>283</v>
-      </c>
-    </row>
-    <row r="143" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B143" s="1" t="s">
-        <v>284</v>
-      </c>
-      <c r="C143" s="1" t="s">
-        <v>285</v>
-      </c>
-    </row>
-    <row r="144" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B144" s="1" t="s">
-        <v>286</v>
-      </c>
-      <c r="C144" s="1" t="s">
-        <v>287</v>
-      </c>
-    </row>
-    <row r="145" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B145" s="1" t="s">
-        <v>288</v>
-      </c>
-      <c r="C145" s="1" t="s">
-        <v>289</v>
-      </c>
-    </row>
-    <row r="146" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B146" s="1" t="s">
-        <v>290</v>
-      </c>
-      <c r="C146" s="1" t="s">
-        <v>291</v>
-      </c>
-    </row>
-    <row r="147" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B147" s="1" t="s">
-        <v>292</v>
-      </c>
-      <c r="C147" s="1" t="s">
-        <v>293</v>
-      </c>
-    </row>
-    <row r="148" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B148" s="1" t="s">
-        <v>294</v>
-      </c>
-      <c r="C148" s="1" t="s">
-        <v>295</v>
-      </c>
-    </row>
-    <row r="149" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B149" s="1" t="s">
-        <v>296</v>
-      </c>
-      <c r="C149" s="1" t="s">
-        <v>297</v>
-      </c>
-    </row>
-    <row r="150" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B150" s="1" t="s">
-        <v>298</v>
-      </c>
-      <c r="C150" s="1" t="s">
-        <v>299</v>
-      </c>
-    </row>
-    <row r="151" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B151" s="1" t="s">
-        <v>300</v>
-      </c>
-      <c r="C151" s="1" t="s">
-        <v>301</v>
-      </c>
-    </row>
-    <row r="152" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B152" s="1" t="s">
-        <v>302</v>
-      </c>
-      <c r="C152" s="1" t="s">
-        <v>303</v>
-      </c>
-    </row>
-    <row r="153" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B153" s="1" t="s">
-        <v>304</v>
-      </c>
-      <c r="C153" s="1" t="s">
-        <v>305</v>
-      </c>
-    </row>
-    <row r="154" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B154" s="1" t="s">
-        <v>306</v>
-      </c>
-      <c r="C154" s="1" t="s">
-        <v>307</v>
-      </c>
-    </row>
-    <row r="155" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B155" s="1" t="s">
-        <v>308</v>
-      </c>
-      <c r="C155" s="1" t="s">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="156" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B156" s="1" t="s">
-        <v>310</v>
-      </c>
-      <c r="C156" s="1" t="s">
-        <v>311</v>
-      </c>
-    </row>
-    <row r="157" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B157" s="1" t="s">
-        <v>312</v>
-      </c>
-      <c r="C157" s="1" t="s">
-        <v>313</v>
-      </c>
-    </row>
-    <row r="158" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B158" s="1" t="s">
-        <v>314</v>
-      </c>
-      <c r="C158" s="1" t="s">
-        <v>315</v>
-      </c>
-    </row>
-    <row r="159" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B159" s="1" t="s">
-        <v>316</v>
-      </c>
-      <c r="C159" s="1" t="s">
-        <v>317</v>
-      </c>
-    </row>
-    <row r="160" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B160" s="1" t="s">
-        <v>318</v>
-      </c>
-      <c r="C160" s="1" t="s">
-        <v>319</v>
-      </c>
-    </row>
-    <row r="161" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B161" s="1" t="s">
-        <v>320</v>
-      </c>
-      <c r="C161" s="1" t="s">
-        <v>321</v>
-      </c>
-    </row>
-    <row r="162" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B162" s="1" t="s">
-        <v>322</v>
-      </c>
-      <c r="C162" s="1" t="s">
-        <v>323</v>
-      </c>
-    </row>
-    <row r="163" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B163" s="1" t="s">
-        <v>324</v>
-      </c>
-      <c r="C163" s="1" t="s">
-        <v>325</v>
-      </c>
-    </row>
-    <row r="164" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B164" s="1" t="s">
-        <v>326</v>
-      </c>
-      <c r="C164" s="1" t="s">
-        <v>327</v>
-      </c>
-    </row>
-    <row r="165" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B165" s="1" t="s">
-        <v>328</v>
-      </c>
-      <c r="C165" s="1" t="s">
-        <v>329</v>
-      </c>
-    </row>
-    <row r="166" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B166" s="1" t="s">
-        <v>330</v>
-      </c>
-      <c r="C166" s="1" t="s">
-        <v>331</v>
-      </c>
-    </row>
-    <row r="167" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B167" s="1" t="s">
-        <v>332</v>
-      </c>
-      <c r="C167" s="1" t="s">
-        <v>333</v>
-      </c>
-    </row>
-    <row r="168" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B168" s="1" t="s">
-        <v>334</v>
-      </c>
-      <c r="C168" s="1" t="s">
-        <v>335</v>
-      </c>
-    </row>
-    <row r="169" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B169" s="1" t="s">
-        <v>336</v>
-      </c>
-      <c r="C169" s="1" t="s">
-        <v>337</v>
       </c>
     </row>
   </sheetData>
@@ -6809,551 +5571,1359 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="B1:C68"/>
+  <dimension ref="B1:C169"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="1" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="2" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="2" t="s">
-        <v>663</v>
+      <c r="C2" s="1" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="3" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B3" s="2" t="s">
-        <v>391</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>664</v>
+      <c r="B3" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="4" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B4" s="2" t="s">
-        <v>393</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>665</v>
+      <c r="B4" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="5" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B5" s="2" t="s">
-        <v>395</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>666</v>
+      <c r="B5" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="6" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B6" s="2" t="s">
-        <v>397</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>667</v>
+      <c r="B6" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="7" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B7" s="2" t="s">
-        <v>399</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>665</v>
+      <c r="B7" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="8" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B8" s="2" t="s">
-        <v>401</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>668</v>
+      <c r="B8" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="9" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B9" s="2" t="s">
-        <v>403</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>669</v>
+      <c r="B9" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="10" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B10" s="2" t="s">
+      <c r="B10" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="11" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B11" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="12" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B12" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="13" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B13" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="14" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B14" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="15" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B15" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="16" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B16" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="17" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B17" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="18" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B18" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="19" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B19" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="20" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B20" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="21" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B21" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="C10" s="2" t="s">
-        <v>670</v>
-      </c>
-    </row>
-    <row r="11" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B11" s="2" t="s">
+      <c r="C21" s="1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="22" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B22" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="23" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B23" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="24" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B24" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="25" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B25" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="26" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B26" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="27" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B27" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="C11" s="2" t="s">
-        <v>671</v>
-      </c>
-    </row>
-    <row r="12" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B12" s="2" t="s">
+      <c r="C27" s="1" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="28" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B28" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="C28" s="1" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="29" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B29" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C29" s="1" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="30" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B30" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="C30" s="1" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="31" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B31" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="C31" s="1" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="32" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B32" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="C12" s="2" t="s">
-        <v>672</v>
-      </c>
-    </row>
-    <row r="13" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B13" s="2" t="s">
+      <c r="C32" s="1" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="33" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B33" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="C13" s="2" t="s">
-        <v>673</v>
-      </c>
-    </row>
-    <row r="14" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B14" s="2" t="s">
+      <c r="C33" s="1" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="34" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B34" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="C14" s="2" t="s">
-        <v>674</v>
-      </c>
-    </row>
-    <row r="15" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B15" s="2" t="s">
+      <c r="C34" s="1" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="35" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B35" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="C35" s="1" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="36" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B36" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="C15" s="2" t="s">
-        <v>675</v>
-      </c>
-    </row>
-    <row r="16" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B16" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="C16" s="2" t="s">
-        <v>676</v>
-      </c>
-    </row>
-    <row r="17" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B17" s="2" t="s">
+      <c r="C36" s="1" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="37" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B37" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="C37" s="1" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="38" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B38" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="C38" s="1" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="39" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B39" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="C39" s="1" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="40" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B40" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="C40" s="1" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="41" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B41" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="C17" s="2" t="s">
-        <v>677</v>
-      </c>
-    </row>
-    <row r="18" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B18" s="2" t="s">
-        <v>678</v>
-      </c>
-      <c r="C18" s="2" t="s">
-        <v>679</v>
-      </c>
-    </row>
-    <row r="19" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B19" s="2" t="s">
+      <c r="C41" s="1" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="42" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B42" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="C19" s="2" t="s">
-        <v>680</v>
-      </c>
-    </row>
-    <row r="20" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B20" s="2" t="s">
+      <c r="C42" s="1" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="43" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B43" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="C20" s="2" t="s">
-        <v>681</v>
-      </c>
-    </row>
-    <row r="21" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B21" s="2" t="s">
+      <c r="C43" s="1" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="44" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B44" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="C21" s="2" t="s">
-        <v>681</v>
-      </c>
-    </row>
-    <row r="22" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B22" s="2" t="s">
+      <c r="C44" s="1" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="45" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B45" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="C22" s="2" t="s">
-        <v>681</v>
-      </c>
-    </row>
-    <row r="23" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B23" s="2" t="s">
+      <c r="C45" s="1" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="46" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B46" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="C23" s="2" t="s">
-        <v>681</v>
-      </c>
-    </row>
-    <row r="24" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B24" s="2" t="s">
+      <c r="C46" s="1" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="47" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B47" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="C24" s="2" t="s">
-        <v>681</v>
-      </c>
-    </row>
-    <row r="25" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B25" s="2" t="s">
+      <c r="C47" s="1" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="48" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B48" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="C25" s="2" t="s">
-        <v>682</v>
-      </c>
-    </row>
-    <row r="26" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B26" s="2" t="s">
+      <c r="C48" s="1" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="49" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B49" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="C26" s="2" t="s">
-        <v>683</v>
-      </c>
-    </row>
-    <row r="27" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B27" s="2" t="s">
-        <v>684</v>
-      </c>
-      <c r="C27" s="2" t="s">
-        <v>685</v>
-      </c>
-    </row>
-    <row r="28" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B28" s="2" t="s">
+      <c r="C49" s="1" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="50" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B50" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="C50" s="1" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="51" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B51" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="C28" s="2" t="s">
-        <v>686</v>
-      </c>
-    </row>
-    <row r="29" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B29" s="2" t="s">
+      <c r="C51" s="1" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="52" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B52" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="C29" s="2" t="s">
-        <v>687</v>
-      </c>
-    </row>
-    <row r="30" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B30" s="2" t="s">
+      <c r="C52" s="1" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="53" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B53" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="C30" s="2" t="s">
-        <v>688</v>
-      </c>
-    </row>
-    <row r="31" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B31" s="2" t="s">
+      <c r="C53" s="1" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="54" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B54" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="C54" s="1" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="55" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B55" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="C55" s="1" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="56" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B56" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="C56" s="1" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="57" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B57" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="C57" s="1" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="58" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B58" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="C58" s="1" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="59" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B59" s="1" t="s">
         <v>116</v>
       </c>
-      <c r="C31" s="2" t="s">
-        <v>689</v>
-      </c>
-    </row>
-    <row r="32" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B32" s="2" t="s">
+      <c r="C59" s="1" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="60" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B60" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="C60" s="1" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="61" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B61" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="C61" s="1" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="62" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B62" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="C62" s="1" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="63" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B63" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="C63" s="1" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="64" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B64" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="C64" s="1" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="65" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B65" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="C65" s="1" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="66" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B66" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="C66" s="1" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="67" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B67" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="C67" s="1" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="68" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B68" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="C68" s="1" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="69" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B69" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="C69" s="1" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="70" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B70" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="C70" s="1" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="71" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B71" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="C71" s="1" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="72" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B72" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="C72" s="1" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="73" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B73" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="C73" s="1" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="74" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B74" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="C74" s="1" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="75" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B75" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="C75" s="1" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="76" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B76" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="C76" s="1" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="77" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B77" s="1" t="s">
         <v>152</v>
       </c>
-      <c r="C32" s="2" t="s">
-        <v>690</v>
-      </c>
-    </row>
-    <row r="33" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B33" s="2" t="s">
-        <v>134</v>
-      </c>
-      <c r="C33" s="2" t="s">
-        <v>691</v>
-      </c>
-    </row>
-    <row r="34" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B34" s="2" t="s">
-        <v>692</v>
-      </c>
-      <c r="C34" s="2" t="s">
-        <v>693</v>
-      </c>
-    </row>
-    <row r="35" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B35" s="2" t="s">
-        <v>136</v>
-      </c>
-      <c r="C35" s="2" t="s">
-        <v>694</v>
-      </c>
-    </row>
-    <row r="36" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B36" s="2" t="s">
-        <v>138</v>
-      </c>
-      <c r="C36" s="2" t="s">
-        <v>695</v>
-      </c>
-    </row>
-    <row r="37" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B37" s="2" t="s">
-        <v>140</v>
-      </c>
-      <c r="C37" s="2" t="s">
-        <v>696</v>
-      </c>
-    </row>
-    <row r="38" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B38" s="2" t="s">
-        <v>142</v>
-      </c>
-      <c r="C38" s="2" t="s">
-        <v>697</v>
-      </c>
-    </row>
-    <row r="39" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B39" s="2" t="s">
-        <v>341</v>
-      </c>
-      <c r="C39" s="2" t="s">
-        <v>698</v>
-      </c>
-    </row>
-    <row r="40" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B40" s="2" t="s">
-        <v>144</v>
-      </c>
-      <c r="C40" s="2" t="s">
-        <v>699</v>
-      </c>
-    </row>
-    <row r="41" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B41" s="2" t="s">
-        <v>146</v>
-      </c>
-      <c r="C41" s="2" t="s">
-        <v>700</v>
-      </c>
-    </row>
-    <row r="42" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B42" s="2" t="s">
-        <v>148</v>
-      </c>
-      <c r="C42" s="2" t="s">
-        <v>701</v>
-      </c>
-    </row>
-    <row r="43" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B43" s="2" t="s">
-        <v>150</v>
-      </c>
-      <c r="C43" s="2" t="s">
-        <v>702</v>
-      </c>
-    </row>
-    <row r="44" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B44" s="2" t="s">
+      <c r="C77" s="1" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="78" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B78" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="C78" s="1" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="79" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B79" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="C79" s="1" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="80" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B80" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="C80" s="1" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="81" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B81" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="C81" s="1" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="82" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B82" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="C82" s="1" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="83" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B83" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="C83" s="1" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="84" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B84" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="C84" s="1" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="85" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B85" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="C85" s="1" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="86" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B86" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="C86" s="1" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="87" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B87" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="C87" s="1" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="88" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B88" s="1" t="s">
         <v>174</v>
       </c>
-      <c r="C44" s="2" t="s">
-        <v>703</v>
-      </c>
-    </row>
-    <row r="45" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B45" s="2" t="s">
-        <v>154</v>
-      </c>
-      <c r="C45" s="2" t="s">
-        <v>704</v>
-      </c>
-    </row>
-    <row r="46" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B46" s="2" t="s">
-        <v>156</v>
-      </c>
-      <c r="C46" s="2" t="s">
-        <v>705</v>
-      </c>
-    </row>
-    <row r="47" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B47" s="2" t="s">
-        <v>158</v>
-      </c>
-      <c r="C47" s="2" t="s">
-        <v>706</v>
-      </c>
-    </row>
-    <row r="48" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B48" s="2" t="s">
-        <v>160</v>
-      </c>
-      <c r="C48" s="2" t="s">
-        <v>707</v>
-      </c>
-    </row>
-    <row r="49" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B49" s="2" t="s">
-        <v>162</v>
-      </c>
-      <c r="C49" s="2" t="s">
-        <v>708</v>
-      </c>
-    </row>
-    <row r="50" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B50" s="2" t="s">
-        <v>164</v>
-      </c>
-      <c r="C50" s="2" t="s">
-        <v>709</v>
-      </c>
-    </row>
-    <row r="51" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B51" s="2" t="s">
-        <v>166</v>
-      </c>
-      <c r="C51" s="2" t="s">
-        <v>710</v>
-      </c>
-    </row>
-    <row r="52" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B52" s="2" t="s">
-        <v>168</v>
-      </c>
-      <c r="C52" s="2" t="s">
-        <v>711</v>
-      </c>
-    </row>
-    <row r="53" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B53" s="2" t="s">
-        <v>170</v>
-      </c>
-      <c r="C53" s="2" t="s">
-        <v>712</v>
-      </c>
-    </row>
-    <row r="54" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B54" s="2" t="s">
-        <v>172</v>
-      </c>
-      <c r="C54" s="2" t="s">
-        <v>689</v>
-      </c>
-    </row>
-    <row r="55" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B55" s="2" t="s">
+      <c r="C88" s="1" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="89" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B89" s="1" t="s">
         <v>176</v>
       </c>
-      <c r="C55" s="2" t="s">
-        <v>713</v>
-      </c>
-    </row>
-    <row r="56" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B56" s="2" t="s">
+      <c r="C89" s="1" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="90" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B90" s="1" t="s">
         <v>178</v>
       </c>
-      <c r="C56" s="2" t="s">
-        <v>714</v>
-      </c>
-    </row>
-    <row r="57" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B57" s="2" t="s">
+      <c r="C90" s="1" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="91" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B91" s="1" t="s">
         <v>180</v>
       </c>
-      <c r="C57" s="2" t="s">
-        <v>715</v>
-      </c>
-    </row>
-    <row r="58" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B58" s="2" t="s">
-        <v>716</v>
-      </c>
-      <c r="C58" s="2" t="s">
-        <v>717</v>
-      </c>
-    </row>
-    <row r="59" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B59" s="2" t="s">
-        <v>718</v>
-      </c>
-      <c r="C59" s="2" t="s">
-        <v>719</v>
-      </c>
-    </row>
-    <row r="60" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B60" s="2" t="s">
-        <v>720</v>
-      </c>
-      <c r="C60" s="2" t="s">
-        <v>721</v>
-      </c>
-    </row>
-    <row r="61" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B61" s="2" t="s">
-        <v>599</v>
-      </c>
-      <c r="C61" s="2" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="62" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B62" s="2" t="s">
-        <v>601</v>
-      </c>
-      <c r="C62" s="2" t="s">
-        <v>723</v>
-      </c>
-    </row>
-    <row r="63" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B63" s="2" t="s">
-        <v>603</v>
-      </c>
-      <c r="C63" s="2" t="s">
-        <v>724</v>
-      </c>
-    </row>
-    <row r="64" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B64" s="2" t="s">
-        <v>605</v>
-      </c>
-      <c r="C64" s="2" t="s">
-        <v>725</v>
-      </c>
-    </row>
-    <row r="65" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B65" s="2" t="s">
-        <v>607</v>
-      </c>
-      <c r="C65" s="2" t="s">
-        <v>726</v>
-      </c>
-    </row>
-    <row r="66" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B66" s="2" t="s">
-        <v>727</v>
-      </c>
-      <c r="C66" s="2" t="s">
-        <v>728</v>
-      </c>
-    </row>
-    <row r="67" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B67" s="2" t="s">
+      <c r="C91" s="1" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="92" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B92" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="C92" s="1" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="93" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B93" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="C93" s="1" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="94" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B94" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="C94" s="1" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="95" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B95" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="C95" s="1" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="96" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B96" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="C96" s="1" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="97" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B97" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="C97" s="1" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="98" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B98" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="C98" s="1" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="99" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B99" s="1" t="s">
+        <v>196</v>
+      </c>
+      <c r="C99" s="1" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="100" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B100" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="C100" s="1" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="101" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B101" s="1" t="s">
+        <v>200</v>
+      </c>
+      <c r="C101" s="1" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="102" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B102" s="1" t="s">
+        <v>202</v>
+      </c>
+      <c r="C102" s="1" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="103" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B103" s="1" t="s">
+        <v>204</v>
+      </c>
+      <c r="C103" s="1" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="104" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B104" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="C104" s="1" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="105" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B105" s="1" t="s">
+        <v>208</v>
+      </c>
+      <c r="C105" s="1" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="106" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B106" s="1" t="s">
+        <v>210</v>
+      </c>
+      <c r="C106" s="1" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="107" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B107" s="1" t="s">
+        <v>212</v>
+      </c>
+      <c r="C107" s="1" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="108" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B108" s="1" t="s">
+        <v>214</v>
+      </c>
+      <c r="C108" s="1" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="109" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B109" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="C109" s="1" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="110" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B110" s="1" t="s">
+        <v>218</v>
+      </c>
+      <c r="C110" s="1" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="111" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B111" s="1" t="s">
+        <v>220</v>
+      </c>
+      <c r="C111" s="1" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="112" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B112" s="1" t="s">
+        <v>222</v>
+      </c>
+      <c r="C112" s="1" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="113" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B113" s="1" t="s">
+        <v>224</v>
+      </c>
+      <c r="C113" s="1" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="114" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B114" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="C114" s="1" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="115" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B115" s="1" t="s">
+        <v>228</v>
+      </c>
+      <c r="C115" s="1" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="116" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B116" s="1" t="s">
+        <v>230</v>
+      </c>
+      <c r="C116" s="1" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="117" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B117" s="1" t="s">
+        <v>232</v>
+      </c>
+      <c r="C117" s="1" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="118" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B118" s="1" t="s">
+        <v>234</v>
+      </c>
+      <c r="C118" s="1" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="119" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B119" s="1" t="s">
+        <v>236</v>
+      </c>
+      <c r="C119" s="1" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="120" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B120" s="1" t="s">
+        <v>238</v>
+      </c>
+      <c r="C120" s="1" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="121" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B121" s="1" t="s">
+        <v>240</v>
+      </c>
+      <c r="C121" s="1" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="122" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B122" s="1" t="s">
+        <v>242</v>
+      </c>
+      <c r="C122" s="1" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="123" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B123" s="1" t="s">
+        <v>244</v>
+      </c>
+      <c r="C123" s="1" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="124" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B124" s="1" t="s">
+        <v>246</v>
+      </c>
+      <c r="C124" s="1" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="125" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B125" s="1" t="s">
+        <v>248</v>
+      </c>
+      <c r="C125" s="1" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="126" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B126" s="1" t="s">
+        <v>250</v>
+      </c>
+      <c r="C126" s="1" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="127" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B127" s="1" t="s">
+        <v>252</v>
+      </c>
+      <c r="C127" s="1" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="128" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B128" s="1" t="s">
+        <v>254</v>
+      </c>
+      <c r="C128" s="1" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="129" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B129" s="1" t="s">
+        <v>256</v>
+      </c>
+      <c r="C129" s="1" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="130" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B130" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="C130" s="1" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="131" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B131" s="1" t="s">
+        <v>260</v>
+      </c>
+      <c r="C131" s="1" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="132" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B132" s="1" t="s">
+        <v>262</v>
+      </c>
+      <c r="C132" s="1" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="133" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B133" s="1" t="s">
+        <v>264</v>
+      </c>
+      <c r="C133" s="1" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="134" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B134" s="1" t="s">
+        <v>266</v>
+      </c>
+      <c r="C134" s="1" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="135" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B135" s="1" t="s">
+        <v>268</v>
+      </c>
+      <c r="C135" s="1" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="136" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B136" s="1" t="s">
+        <v>270</v>
+      </c>
+      <c r="C136" s="1" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="137" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B137" s="1" t="s">
+        <v>272</v>
+      </c>
+      <c r="C137" s="1" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="138" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B138" s="1" t="s">
+        <v>274</v>
+      </c>
+      <c r="C138" s="1" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="139" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B139" s="1" t="s">
+        <v>276</v>
+      </c>
+      <c r="C139" s="1" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="140" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B140" s="1" t="s">
+        <v>278</v>
+      </c>
+      <c r="C140" s="1" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="141" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B141" s="1" t="s">
+        <v>280</v>
+      </c>
+      <c r="C141" s="1" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="142" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B142" s="1" t="s">
+        <v>282</v>
+      </c>
+      <c r="C142" s="1" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="143" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B143" s="1" t="s">
+        <v>284</v>
+      </c>
+      <c r="C143" s="1" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="144" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B144" s="1" t="s">
+        <v>286</v>
+      </c>
+      <c r="C144" s="1" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="145" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B145" s="1" t="s">
+        <v>288</v>
+      </c>
+      <c r="C145" s="1" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="146" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B146" s="1" t="s">
+        <v>290</v>
+      </c>
+      <c r="C146" s="1" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="147" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B147" s="1" t="s">
+        <v>292</v>
+      </c>
+      <c r="C147" s="1" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="148" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B148" s="1" t="s">
+        <v>294</v>
+      </c>
+      <c r="C148" s="1" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="149" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B149" s="1" t="s">
+        <v>296</v>
+      </c>
+      <c r="C149" s="1" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="150" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B150" s="1" t="s">
+        <v>298</v>
+      </c>
+      <c r="C150" s="1" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="151" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B151" s="1" t="s">
+        <v>300</v>
+      </c>
+      <c r="C151" s="1" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="152" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B152" s="1" t="s">
+        <v>302</v>
+      </c>
+      <c r="C152" s="1" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="153" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B153" s="1" t="s">
+        <v>304</v>
+      </c>
+      <c r="C153" s="1" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="154" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B154" s="1" t="s">
+        <v>306</v>
+      </c>
+      <c r="C154" s="1" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="155" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B155" s="1" t="s">
+        <v>308</v>
+      </c>
+      <c r="C155" s="1" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="156" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B156" s="1" t="s">
+        <v>310</v>
+      </c>
+      <c r="C156" s="1" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="157" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B157" s="1" t="s">
+        <v>312</v>
+      </c>
+      <c r="C157" s="1" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="158" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B158" s="1" t="s">
         <v>314</v>
       </c>
-      <c r="C67" s="2" t="s">
-        <v>729</v>
-      </c>
-    </row>
-    <row r="68" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B68" s="2" t="s">
+      <c r="C158" s="1" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="159" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B159" s="1" t="s">
+        <v>316</v>
+      </c>
+      <c r="C159" s="1" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="160" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B160" s="1" t="s">
+        <v>318</v>
+      </c>
+      <c r="C160" s="1" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="161" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B161" s="1" t="s">
+        <v>320</v>
+      </c>
+      <c r="C161" s="1" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="162" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B162" s="1" t="s">
+        <v>322</v>
+      </c>
+      <c r="C162" s="1" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="163" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B163" s="1" t="s">
+        <v>324</v>
+      </c>
+      <c r="C163" s="1" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="164" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B164" s="1" t="s">
+        <v>326</v>
+      </c>
+      <c r="C164" s="1" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="165" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B165" s="1" t="s">
         <v>328</v>
       </c>
-      <c r="C68" s="2" t="s">
-        <v>730</v>
+      <c r="C165" s="1" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="166" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B166" s="1" t="s">
+        <v>330</v>
+      </c>
+      <c r="C166" s="1" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="167" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B167" s="1" t="s">
+        <v>332</v>
+      </c>
+      <c r="C167" s="1" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="168" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B168" s="1" t="s">
+        <v>334</v>
+      </c>
+      <c r="C168" s="1" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="169" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B169" s="1" t="s">
+        <v>336</v>
+      </c>
+      <c r="C169" s="1" t="s">
+        <v>337</v>
       </c>
     </row>
   </sheetData>
@@ -7364,255 +6934,551 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="B1:C31"/>
+  <dimension ref="B1:C68"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B1" s="5" t="s">
+      <c r="B1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="5" t="s">
+      <c r="C1" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="2" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B2" s="5" t="s">
-        <v>731</v>
-      </c>
-      <c r="C2" s="5" t="s">
-        <v>732</v>
+      <c r="B2" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>663</v>
       </c>
     </row>
     <row r="3" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B3" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="C3" s="5" t="s">
-        <v>733</v>
+      <c r="B3" s="2" t="s">
+        <v>391</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>664</v>
       </c>
     </row>
     <row r="4" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B4" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C4" s="5" t="s">
-        <v>664</v>
+      <c r="B4" s="2" t="s">
+        <v>393</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>665</v>
       </c>
     </row>
     <row r="5" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B5" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="C5" s="5" t="s">
+      <c r="B5" s="2" t="s">
+        <v>395</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>666</v>
+      </c>
+    </row>
+    <row r="6" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B6" s="2" t="s">
+        <v>397</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>667</v>
+      </c>
+    </row>
+    <row r="7" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B7" s="2" t="s">
+        <v>399</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>665</v>
+      </c>
+    </row>
+    <row r="8" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B8" s="2" t="s">
+        <v>401</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>668</v>
+      </c>
+    </row>
+    <row r="9" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B9" s="2" t="s">
+        <v>403</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>669</v>
+      </c>
+    </row>
+    <row r="10" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B10" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>670</v>
+      </c>
+    </row>
+    <row r="11" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B11" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>671</v>
+      </c>
+    </row>
+    <row r="12" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B12" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>672</v>
+      </c>
+    </row>
+    <row r="13" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B13" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>673</v>
+      </c>
+    </row>
+    <row r="14" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B14" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>674</v>
+      </c>
+    </row>
+    <row r="15" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B15" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>675</v>
+      </c>
+    </row>
+    <row r="16" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B16" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>676</v>
+      </c>
+    </row>
+    <row r="17" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B17" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>677</v>
+      </c>
+    </row>
+    <row r="18" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B18" s="2" t="s">
+        <v>678</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>679</v>
+      </c>
+    </row>
+    <row r="19" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B19" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>680</v>
+      </c>
+    </row>
+    <row r="20" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B20" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>681</v>
+      </c>
+    </row>
+    <row r="21" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B21" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>681</v>
+      </c>
+    </row>
+    <row r="22" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B22" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>681</v>
+      </c>
+    </row>
+    <row r="23" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B23" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>681</v>
+      </c>
+    </row>
+    <row r="24" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B24" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>681</v>
+      </c>
+    </row>
+    <row r="25" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B25" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>682</v>
+      </c>
+    </row>
+    <row r="26" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B26" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>683</v>
+      </c>
+    </row>
+    <row r="27" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B27" s="2" t="s">
+        <v>684</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>685</v>
+      </c>
+    </row>
+    <row r="28" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B28" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>686</v>
+      </c>
+    </row>
+    <row r="29" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B29" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>687</v>
+      </c>
+    </row>
+    <row r="30" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B30" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>688</v>
+      </c>
+    </row>
+    <row r="31" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B31" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="C31" s="2" t="s">
+        <v>689</v>
+      </c>
+    </row>
+    <row r="32" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B32" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="C32" s="2" t="s">
+        <v>690</v>
+      </c>
+    </row>
+    <row r="33" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B33" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="C33" s="2" t="s">
+        <v>691</v>
+      </c>
+    </row>
+    <row r="34" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B34" s="2" t="s">
+        <v>692</v>
+      </c>
+      <c r="C34" s="2" t="s">
+        <v>693</v>
+      </c>
+    </row>
+    <row r="35" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B35" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="C35" s="2" t="s">
+        <v>694</v>
+      </c>
+    </row>
+    <row r="36" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B36" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="C36" s="2" t="s">
+        <v>695</v>
+      </c>
+    </row>
+    <row r="37" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B37" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="C37" s="2" t="s">
+        <v>696</v>
+      </c>
+    </row>
+    <row r="38" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B38" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="C38" s="2" t="s">
         <v>697</v>
       </c>
     </row>
-    <row r="6" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B6" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="C6" s="5" t="s">
-        <v>734</v>
-      </c>
-    </row>
-    <row r="7" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B7" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C7" s="5" t="s">
-        <v>735</v>
-      </c>
-    </row>
-    <row r="8" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B8" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="C8" s="5" t="s">
-        <v>736</v>
-      </c>
-    </row>
-    <row r="9" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B9" s="5" t="s">
-        <v>737</v>
-      </c>
-      <c r="C9" s="5" t="s">
-        <v>738</v>
-      </c>
-    </row>
-    <row r="10" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B10" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="C10" s="5" t="s">
-        <v>739</v>
-      </c>
-    </row>
-    <row r="11" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B11" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="C11" s="5" t="s">
-        <v>740</v>
-      </c>
-    </row>
-    <row r="12" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B12" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="C12" s="5" t="s">
-        <v>741</v>
-      </c>
-    </row>
-    <row r="13" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B13" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="C13" s="5" t="s">
-        <v>742</v>
-      </c>
-    </row>
-    <row r="14" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B14" s="5" t="s">
-        <v>78</v>
-      </c>
-      <c r="C14" s="5" t="s">
-        <v>743</v>
-      </c>
-    </row>
-    <row r="15" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B15" s="5" t="s">
-        <v>50</v>
-      </c>
-      <c r="C15" s="5" t="s">
-        <v>666</v>
-      </c>
-    </row>
-    <row r="16" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B16" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="C16" s="5" t="s">
-        <v>665</v>
-      </c>
-    </row>
-    <row r="17" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B17" s="5" t="s">
-        <v>62</v>
-      </c>
-      <c r="C17" s="5" t="s">
-        <v>667</v>
-      </c>
-    </row>
-    <row r="18" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B18" s="5" t="s">
-        <v>64</v>
-      </c>
-      <c r="C18" s="5" t="s">
-        <v>744</v>
-      </c>
-    </row>
-    <row r="19" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B19" s="5" t="s">
-        <v>66</v>
-      </c>
-      <c r="C19" s="5" t="s">
-        <v>733</v>
-      </c>
-    </row>
-    <row r="20" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B20" s="5" t="s">
-        <v>132</v>
-      </c>
-      <c r="C20" s="5" t="s">
-        <v>745</v>
-      </c>
-    </row>
-    <row r="21" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B21" s="5" t="s">
-        <v>98</v>
-      </c>
-      <c r="C21" s="5" t="s">
-        <v>746</v>
-      </c>
-    </row>
-    <row r="22" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B22" s="5" t="s">
-        <v>114</v>
-      </c>
-      <c r="C22" s="5" t="s">
-        <v>747</v>
-      </c>
-    </row>
-    <row r="23" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B23" s="5" t="s">
-        <v>118</v>
-      </c>
-      <c r="C23" s="5" t="s">
-        <v>748</v>
-      </c>
-    </row>
-    <row r="24" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B24" s="5" t="s">
-        <v>232</v>
-      </c>
-      <c r="C24" s="5" t="s">
-        <v>749</v>
-      </c>
-    </row>
-    <row r="25" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B25" s="5" t="s">
-        <v>152</v>
-      </c>
-      <c r="C25" s="5" t="s">
-        <v>690</v>
-      </c>
-    </row>
-    <row r="26" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B26" s="5" t="s">
+    <row r="39" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B39" s="2" t="s">
+        <v>341</v>
+      </c>
+      <c r="C39" s="2" t="s">
+        <v>698</v>
+      </c>
+    </row>
+    <row r="40" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B40" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="C40" s="2" t="s">
+        <v>699</v>
+      </c>
+    </row>
+    <row r="41" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B41" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="C41" s="2" t="s">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="42" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B42" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="C42" s="2" t="s">
+        <v>701</v>
+      </c>
+    </row>
+    <row r="43" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B43" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="C43" s="2" t="s">
+        <v>702</v>
+      </c>
+    </row>
+    <row r="44" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B44" s="2" t="s">
         <v>174</v>
       </c>
-      <c r="C26" s="5" t="s">
+      <c r="C44" s="2" t="s">
         <v>703</v>
       </c>
     </row>
-    <row r="27" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B27" s="5" t="s">
-        <v>750</v>
-      </c>
-      <c r="C27" s="5" t="s">
-        <v>679</v>
-      </c>
-    </row>
-    <row r="28" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B28" s="5" t="s">
-        <v>751</v>
-      </c>
-      <c r="C28" s="5" t="s">
-        <v>752</v>
-      </c>
-    </row>
-    <row r="29" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B29" s="5" t="s">
-        <v>268</v>
-      </c>
-      <c r="C29" s="5" t="s">
-        <v>694</v>
-      </c>
-    </row>
-    <row r="30" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B30" s="5" t="s">
-        <v>312</v>
-      </c>
-      <c r="C30" s="5" t="s">
-        <v>753</v>
-      </c>
-    </row>
-    <row r="31" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B31" s="5" t="s">
-        <v>336</v>
-      </c>
-      <c r="C31" s="5" t="s">
-        <v>754</v>
+    <row r="45" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B45" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="C45" s="2" t="s">
+        <v>704</v>
+      </c>
+    </row>
+    <row r="46" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B46" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="C46" s="2" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="47" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B47" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="C47" s="2" t="s">
+        <v>706</v>
+      </c>
+    </row>
+    <row r="48" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B48" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="C48" s="2" t="s">
+        <v>707</v>
+      </c>
+    </row>
+    <row r="49" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B49" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="C49" s="2" t="s">
+        <v>708</v>
+      </c>
+    </row>
+    <row r="50" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B50" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="C50" s="2" t="s">
+        <v>709</v>
+      </c>
+    </row>
+    <row r="51" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B51" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="C51" s="2" t="s">
+        <v>710</v>
+      </c>
+    </row>
+    <row r="52" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B52" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="C52" s="2" t="s">
+        <v>711</v>
+      </c>
+    </row>
+    <row r="53" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B53" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="C53" s="2" t="s">
+        <v>712</v>
+      </c>
+    </row>
+    <row r="54" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B54" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="C54" s="2" t="s">
+        <v>689</v>
+      </c>
+    </row>
+    <row r="55" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B55" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="C55" s="2" t="s">
+        <v>713</v>
+      </c>
+    </row>
+    <row r="56" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B56" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="C56" s="2" t="s">
+        <v>714</v>
+      </c>
+    </row>
+    <row r="57" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B57" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="C57" s="2" t="s">
+        <v>715</v>
+      </c>
+    </row>
+    <row r="58" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B58" s="2" t="s">
+        <v>716</v>
+      </c>
+      <c r="C58" s="2" t="s">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="59" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B59" s="2" t="s">
+        <v>718</v>
+      </c>
+      <c r="C59" s="2" t="s">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="60" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B60" s="2" t="s">
+        <v>720</v>
+      </c>
+      <c r="C60" s="2" t="s">
+        <v>721</v>
+      </c>
+    </row>
+    <row r="61" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B61" s="2" t="s">
+        <v>599</v>
+      </c>
+      <c r="C61" s="2" t="s">
+        <v>722</v>
+      </c>
+    </row>
+    <row r="62" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B62" s="2" t="s">
+        <v>601</v>
+      </c>
+      <c r="C62" s="2" t="s">
+        <v>723</v>
+      </c>
+    </row>
+    <row r="63" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B63" s="2" t="s">
+        <v>603</v>
+      </c>
+      <c r="C63" s="2" t="s">
+        <v>724</v>
+      </c>
+    </row>
+    <row r="64" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B64" s="2" t="s">
+        <v>605</v>
+      </c>
+      <c r="C64" s="2" t="s">
+        <v>725</v>
+      </c>
+    </row>
+    <row r="65" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B65" s="2" t="s">
+        <v>607</v>
+      </c>
+      <c r="C65" s="2" t="s">
+        <v>726</v>
+      </c>
+    </row>
+    <row r="66" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B66" s="2" t="s">
+        <v>727</v>
+      </c>
+      <c r="C66" s="2" t="s">
+        <v>728</v>
+      </c>
+    </row>
+    <row r="67" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B67" s="2" t="s">
+        <v>314</v>
+      </c>
+      <c r="C67" s="2" t="s">
+        <v>729</v>
+      </c>
+    </row>
+    <row r="68" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B68" s="2" t="s">
+        <v>328</v>
+      </c>
+      <c r="C68" s="2" t="s">
+        <v>730</v>
       </c>
     </row>
   </sheetData>
@@ -7623,6 +7489,265 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="B1:C31"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B1" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="5" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B2" s="5" t="s">
+        <v>731</v>
+      </c>
+      <c r="C2" s="5" t="s">
+        <v>732</v>
+      </c>
+    </row>
+    <row r="3" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B3" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="C3" s="5" t="s">
+        <v>733</v>
+      </c>
+    </row>
+    <row r="4" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B4" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C4" s="5" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="5" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B5" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>697</v>
+      </c>
+    </row>
+    <row r="6" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B6" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>734</v>
+      </c>
+    </row>
+    <row r="7" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B7" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="8" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B8" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="C8" s="5" t="s">
+        <v>736</v>
+      </c>
+    </row>
+    <row r="9" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B9" s="5" t="s">
+        <v>737</v>
+      </c>
+      <c r="C9" s="5" t="s">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="10" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B10" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="C10" s="5" t="s">
+        <v>739</v>
+      </c>
+    </row>
+    <row r="11" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B11" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="C11" s="5" t="s">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="12" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B12" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="C12" s="5" t="s">
+        <v>741</v>
+      </c>
+    </row>
+    <row r="13" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B13" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="C13" s="5" t="s">
+        <v>742</v>
+      </c>
+    </row>
+    <row r="14" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B14" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="C14" s="5" t="s">
+        <v>743</v>
+      </c>
+    </row>
+    <row r="15" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B15" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="C15" s="5" t="s">
+        <v>666</v>
+      </c>
+    </row>
+    <row r="16" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B16" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="C16" s="5" t="s">
+        <v>665</v>
+      </c>
+    </row>
+    <row r="17" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B17" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="C17" s="5" t="s">
+        <v>667</v>
+      </c>
+    </row>
+    <row r="18" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B18" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="C18" s="5" t="s">
+        <v>744</v>
+      </c>
+    </row>
+    <row r="19" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B19" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="C19" s="5" t="s">
+        <v>733</v>
+      </c>
+    </row>
+    <row r="20" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B20" s="5" t="s">
+        <v>132</v>
+      </c>
+      <c r="C20" s="5" t="s">
+        <v>745</v>
+      </c>
+    </row>
+    <row r="21" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B21" s="5" t="s">
+        <v>98</v>
+      </c>
+      <c r="C21" s="5" t="s">
+        <v>746</v>
+      </c>
+    </row>
+    <row r="22" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B22" s="5" t="s">
+        <v>114</v>
+      </c>
+      <c r="C22" s="5" t="s">
+        <v>747</v>
+      </c>
+    </row>
+    <row r="23" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B23" s="5" t="s">
+        <v>118</v>
+      </c>
+      <c r="C23" s="5" t="s">
+        <v>748</v>
+      </c>
+    </row>
+    <row r="24" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B24" s="5" t="s">
+        <v>232</v>
+      </c>
+      <c r="C24" s="5" t="s">
+        <v>749</v>
+      </c>
+    </row>
+    <row r="25" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B25" s="5" t="s">
+        <v>152</v>
+      </c>
+      <c r="C25" s="5" t="s">
+        <v>690</v>
+      </c>
+    </row>
+    <row r="26" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B26" s="5" t="s">
+        <v>174</v>
+      </c>
+      <c r="C26" s="5" t="s">
+        <v>703</v>
+      </c>
+    </row>
+    <row r="27" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B27" s="5" t="s">
+        <v>750</v>
+      </c>
+      <c r="C27" s="5" t="s">
+        <v>679</v>
+      </c>
+    </row>
+    <row r="28" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B28" s="5" t="s">
+        <v>751</v>
+      </c>
+      <c r="C28" s="5" t="s">
+        <v>752</v>
+      </c>
+    </row>
+    <row r="29" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B29" s="5" t="s">
+        <v>268</v>
+      </c>
+      <c r="C29" s="5" t="s">
+        <v>694</v>
+      </c>
+    </row>
+    <row r="30" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B30" s="5" t="s">
+        <v>312</v>
+      </c>
+      <c r="C30" s="5" t="s">
+        <v>753</v>
+      </c>
+    </row>
+    <row r="31" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B31" s="5" t="s">
+        <v>336</v>
+      </c>
+      <c r="C31" s="5" t="s">
+        <v>754</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="0" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B1:C13"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
